--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3755,7 +3755,7 @@
         <v>1513</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <v>15</v>
@@ -4043,7 +4043,7 @@
         <v>46680</v>
       </c>
       <c r="CU3" s="1">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="CV3" s="1">
         <v>863</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="BE5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5" s="1">
         <v>7</v>
@@ -4659,7 +4659,7 @@
         <v>319</v>
       </c>
       <c r="CW5" s="1">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -4682,7 +4682,7 @@
         <v>42</v>
       </c>
       <c r="G6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
@@ -4784,7 +4784,7 @@
         <v>7</v>
       </c>
       <c r="AO6" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP6" s="1">
         <v>1</v>
@@ -4928,7 +4928,7 @@
         <v>39</v>
       </c>
       <c r="CK6" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="CL6" s="1">
         <v>1</v>
@@ -4958,13 +4958,13 @@
         <v>2245</v>
       </c>
       <c r="CU6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV6" s="1">
         <v>51</v>
       </c>
       <c r="CW6" s="1">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="BE9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF9" s="1">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>50</v>
       </c>
       <c r="CW9" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7735,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
         <v>3</v>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="2">
         <v>39</v>
@@ -8011,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="CV16" s="1">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="CW16" s="1">
         <v>99</v>
@@ -9012,7 +9012,7 @@
         <v>116</v>
       </c>
       <c r="AA20" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="2">
         <v>4</v>
@@ -9228,7 +9228,7 @@
         <v>20685</v>
       </c>
       <c r="CU20" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="CV20" s="1">
         <v>387</v>
@@ -11542,7 +11542,7 @@
         <v>0</v>
       </c>
       <c r="BE28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF28" s="1">
         <v>94</v>
@@ -11674,7 +11674,7 @@
         <v>262</v>
       </c>
       <c r="CW28" s="1">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12905,7 +12905,7 @@
         <v>79</v>
       </c>
       <c r="C33" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2">
         <v>11</v>
@@ -12917,7 +12917,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2">
         <v>4</v>
@@ -13193,7 +13193,7 @@
         <v>116</v>
       </c>
       <c r="CU33" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CV33" s="1">
         <v>15</v>
@@ -13249,7 +13249,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q34" s="2">
         <v>56</v>
@@ -13501,7 +13501,7 @@
         <v>12</v>
       </c>
       <c r="CV34" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="CW34" s="1">
         <v>142</v>
@@ -19023,7 +19023,7 @@
         <v>2</v>
       </c>
       <c r="I53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -19299,7 +19299,7 @@
         <v>41</v>
       </c>
       <c r="CW53" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -21445,7 +21445,7 @@
         <v>6512</v>
       </c>
       <c r="C61" s="2">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="D61" s="2">
         <v>212</v>
@@ -21733,7 +21733,7 @@
         <v>65929</v>
       </c>
       <c r="CU61" s="1">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="CV61" s="1">
         <v>457</v>
@@ -22055,7 +22055,7 @@
         <v>513</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" s="2">
         <v>14</v>
@@ -22205,7 +22205,7 @@
         <v>1</v>
       </c>
       <c r="BA63" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BB63" s="1">
         <v>4</v>
@@ -22343,13 +22343,13 @@
         <v>2871</v>
       </c>
       <c r="CU63" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV63" s="1">
         <v>93</v>
       </c>
       <c r="CW63" s="1">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22447,7 +22447,7 @@
         <v>2</v>
       </c>
       <c r="AF64" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG64" s="2">
         <v>176</v>
@@ -22651,7 +22651,7 @@
         <v>81</v>
       </c>
       <c r="CV64" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CW64" s="1">
         <v>488</v>
@@ -22671,7 +22671,7 @@
         <v>33</v>
       </c>
       <c r="E65" s="2">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22959,7 +22959,7 @@
         <v>1769</v>
       </c>
       <c r="CW65" s="1">
-        <v>3560</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25500,7 +25500,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25665,7 +25665,7 @@
         <v>64</v>
       </c>
       <c r="CJ74" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="CK74" s="2">
         <v>401</v>
@@ -25701,10 +25701,10 @@
         <v>184</v>
       </c>
       <c r="CV74" s="1">
-        <v>1851</v>
+        <v>1846</v>
       </c>
       <c r="CW74" s="1">
-        <v>4394</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25841,7 +25841,7 @@
         <v>3</v>
       </c>
       <c r="AS75" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT75" s="1">
         <v>0</v>
@@ -25973,7 +25973,7 @@
         <v>8</v>
       </c>
       <c r="CK75" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CL75" s="1">
         <v>8</v>
@@ -26009,7 +26009,7 @@
         <v>15</v>
       </c>
       <c r="CW75" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -26397,7 +26397,7 @@
         <v>132</v>
       </c>
       <c r="AA77" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB77" s="2">
         <v>4</v>
@@ -26613,7 +26613,7 @@
         <v>390875</v>
       </c>
       <c r="CU77" s="1">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="CV77" s="1">
         <v>10228</v>
@@ -26974,7 +26974,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="2">
-        <v>497</v>
+        <v>391</v>
       </c>
       <c r="Q79" s="2">
         <v>1139</v>
@@ -27226,7 +27226,7 @@
         <v>85</v>
       </c>
       <c r="CV79" s="1">
-        <v>761</v>
+        <v>655</v>
       </c>
       <c r="CW79" s="1">
         <v>1860</v>
@@ -27659,7 +27659,7 @@
         <v>4</v>
       </c>
       <c r="AO81" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP81" s="1">
         <v>58</v>
@@ -27815,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="CO81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP81" s="1">
         <v>0</v>
@@ -27839,7 +27839,7 @@
         <v>153</v>
       </c>
       <c r="CW81" s="1">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28227,7 +28227,7 @@
         <v>115</v>
       </c>
       <c r="AA83" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="2">
         <v>3</v>
@@ -28443,7 +28443,7 @@
         <v>423791</v>
       </c>
       <c r="CU83" s="1">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="CV83" s="1">
         <v>887</v>
@@ -29073,7 +29073,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
@@ -29361,7 +29361,7 @@
         <v>4</v>
       </c>
       <c r="CV86" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CW86" s="1">
         <v>74</v>
@@ -31241,7 +31241,7 @@
         <v>869</v>
       </c>
       <c r="O93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" s="2">
         <v>16</v>
@@ -31493,7 +31493,7 @@
         <v>1178</v>
       </c>
       <c r="CU93" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV93" s="1">
         <v>29</v>
@@ -32135,7 +32135,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" s="2">
         <v>5</v>
@@ -32411,7 +32411,7 @@
         <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW96" s="1">
         <v>40</v>
@@ -32548,7 +32548,7 @@
         <v>0</v>
       </c>
       <c r="AR97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS97" s="2">
         <v>5</v>
@@ -32680,7 +32680,7 @@
         <v>0</v>
       </c>
       <c r="CJ97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CK97" s="2">
         <v>5</v>
@@ -32716,7 +32716,7 @@
         <v>1</v>
       </c>
       <c r="CV97" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CW97" s="1">
         <v>16</v>
@@ -32742,7 +32742,7 @@
         <v>76</v>
       </c>
       <c r="G98" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H98" s="2">
         <v>7</v>
@@ -33018,7 +33018,7 @@
         <v>81</v>
       </c>
       <c r="CU98" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CV98" s="1">
         <v>7</v>
@@ -35792,7 +35792,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2">
         <v>1</v>
@@ -36068,7 +36068,7 @@
         <v>942</v>
       </c>
       <c r="CU108" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV108" s="1">
         <v>24</v>
@@ -39150,7 +39150,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I119" s="2">
         <v>4</v>
@@ -39261,7 +39261,7 @@
         <v>2</v>
       </c>
       <c r="AS119" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT119" s="1">
         <v>0</v>
@@ -39393,7 +39393,7 @@
         <v>0</v>
       </c>
       <c r="CK119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL119" s="1">
         <v>90</v>
@@ -39405,7 +39405,7 @@
         <v>2</v>
       </c>
       <c r="CO119" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CP119" s="1">
         <v>0</v>
@@ -39426,10 +39426,10 @@
         <v>5</v>
       </c>
       <c r="CV119" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW119" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -42604,7 +42604,7 @@
         <v>17</v>
       </c>
       <c r="AO130" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AP130" s="1">
         <v>0</v>
@@ -42748,7 +42748,7 @@
         <v>24</v>
       </c>
       <c r="CK130" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CL130" s="1">
         <v>0</v>
@@ -42784,7 +42784,7 @@
         <v>130</v>
       </c>
       <c r="CW130" s="1">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43713,7 +43713,7 @@
         <v>8</v>
       </c>
       <c r="D134" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E134" s="2">
         <v>30</v>
@@ -44001,7 +44001,7 @@
         <v>28</v>
       </c>
       <c r="CV134" s="1">
-        <v>2558</v>
+        <v>2552</v>
       </c>
       <c r="CW134" s="1">
         <v>5812</v>
@@ -44102,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="AF135" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG135" s="2">
         <v>764</v>
@@ -44249,7 +44249,7 @@
         <v>0</v>
       </c>
       <c r="CC135" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD135" s="1">
         <v>13</v>
@@ -44306,10 +44306,10 @@
         <v>150</v>
       </c>
       <c r="CV135" s="1">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="CW135" s="1">
-        <v>2757</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44332,7 +44332,7 @@
         <v>17</v>
       </c>
       <c r="G136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="2">
         <v>1</v>
@@ -44608,7 +44608,7 @@
         <v>158871</v>
       </c>
       <c r="CU136" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV136" s="1">
         <v>5081</v>
@@ -46177,7 +46177,7 @@
         <v>15</v>
       </c>
       <c r="L142" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M142" s="2">
         <v>54</v>
@@ -46441,7 +46441,7 @@
         <v>21</v>
       </c>
       <c r="CV142" s="1">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="CW142" s="1">
         <v>104</v>
@@ -47705,7 +47705,7 @@
         <v>2</v>
       </c>
       <c r="M147" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N147" s="1">
         <v>18</v>
@@ -47969,7 +47969,7 @@
         <v>14</v>
       </c>
       <c r="CW147" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -49517,7 +49517,7 @@
         <v>32</v>
       </c>
       <c r="G153" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H153" s="2">
         <v>3</v>
@@ -49793,7 +49793,7 @@
         <v>161</v>
       </c>
       <c r="CU153" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV153" s="1">
         <v>3</v>
@@ -52872,7 +52872,7 @@
         <v>59</v>
       </c>
       <c r="G164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H164" s="2">
         <v>3</v>
@@ -52884,7 +52884,7 @@
         <v>100</v>
       </c>
       <c r="K164" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L164" s="2">
         <v>16</v>
@@ -53148,7 +53148,7 @@
         <v>1125</v>
       </c>
       <c r="CU164" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CV164" s="1">
         <v>106</v>
@@ -53506,7 +53506,7 @@
         <v>2217</v>
       </c>
       <c r="O166" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P166" s="2">
         <v>46</v>
@@ -53758,7 +53758,7 @@
         <v>5253</v>
       </c>
       <c r="CU166" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="CV166" s="1">
         <v>132</v>
@@ -54194,7 +54194,7 @@
         <v>1</v>
       </c>
       <c r="AO168" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP168" s="1">
         <v>34</v>
@@ -54338,7 +54338,7 @@
         <v>24</v>
       </c>
       <c r="CK168" s="2">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54374,7 +54374,7 @@
         <v>156</v>
       </c>
       <c r="CW168" s="1">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54400,7 +54400,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2">
         <v>5</v>
@@ -54676,7 +54676,7 @@
         <v>12</v>
       </c>
       <c r="CV169" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CW169" s="1">
         <v>60</v>
@@ -54774,7 +54774,7 @@
         <v>3602</v>
       </c>
       <c r="AE170" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF170" s="2">
         <v>126</v>
@@ -54978,7 +54978,7 @@
         <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
@@ -57546,7 +57546,7 @@
         <v>0</v>
       </c>
       <c r="AN179" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO179" s="2">
         <v>38</v>
@@ -57726,7 +57726,7 @@
         <v>1</v>
       </c>
       <c r="CV179" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CW179" s="1">
         <v>68</v>
@@ -57866,7 +57866,7 @@
         <v>0</v>
       </c>
       <c r="AS180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT180" s="1">
         <v>0</v>
@@ -58034,7 +58034,7 @@
         <v>1244</v>
       </c>
       <c r="CW180" s="1">
-        <v>2741</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -61523,7 +61523,7 @@
         <v>0</v>
       </c>
       <c r="AR192" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS192" s="2">
         <v>4</v>
@@ -61655,7 +61655,7 @@
         <v>-2</v>
       </c>
       <c r="CJ192" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CK192" s="2">
         <v>12</v>
@@ -61691,7 +61691,7 @@
         <v>-1</v>
       </c>
       <c r="CV192" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW192" s="1">
         <v>23</v>
@@ -62082,7 +62082,7 @@
         <v>127</v>
       </c>
       <c r="AA194" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB194" s="2">
         <v>4</v>
@@ -62298,7 +62298,7 @@
         <v>32848</v>
       </c>
       <c r="CU194" s="1">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="CV194" s="1">
         <v>576</v>
@@ -63879,7 +63879,7 @@
         <v>0</v>
       </c>
       <c r="P200" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q200" s="2">
         <v>85</v>
@@ -64131,7 +64131,7 @@
         <v>64</v>
       </c>
       <c r="CV200" s="1">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CW200" s="1">
         <v>513</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>2156</v>
       </c>
       <c r="CI4" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CJ4" s="2">
         <v>58</v>
@@ -4348,13 +4348,13 @@
         <v>42911</v>
       </c>
       <c r="CU4" s="1">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="CV4" s="1">
         <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1261</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -7810,7 +7810,7 @@
         <v>8</v>
       </c>
       <c r="AG16" s="2">
-        <v>37</v>
+        <v>-98</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
       <c r="CW16" s="1">
-        <v>99</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -12630,7 +12630,7 @@
         <v>53</v>
       </c>
       <c r="M32" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="N32" s="1">
         <v>6579</v>
@@ -12894,7 +12894,7 @@
         <v>223</v>
       </c>
       <c r="CW32" s="1">
-        <v>578</v>
+        <v>563</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -15991,7 +15991,7 @@
         <v>352</v>
       </c>
       <c r="O43" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P43" s="2">
         <v>20</v>
@@ -16243,7 +16243,7 @@
         <v>565</v>
       </c>
       <c r="CU43" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="CV43" s="1">
         <v>26</v>
@@ -16284,7 +16284,7 @@
         <v>1347</v>
       </c>
       <c r="K44" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>54</v>
@@ -16548,7 +16548,7 @@
         <v>50636</v>
       </c>
       <c r="CU44" s="1">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="CV44" s="1">
         <v>1953</v>
@@ -19436,7 +19436,7 @@
         <v>0</v>
       </c>
       <c r="AS54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>17</v>
       </c>
       <c r="CK54" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CL54" s="1">
         <v>8</v>
@@ -19604,7 +19604,7 @@
         <v>21</v>
       </c>
       <c r="CW54" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -20010,7 +20010,7 @@
         <v>21</v>
       </c>
       <c r="AG56" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -20214,7 +20214,7 @@
         <v>118</v>
       </c>
       <c r="CW56" s="1">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -21445,7 +21445,7 @@
         <v>6512</v>
       </c>
       <c r="C61" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="D61" s="2">
         <v>212</v>
@@ -21733,7 +21733,7 @@
         <v>65929</v>
       </c>
       <c r="CU61" s="1">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="CV61" s="1">
         <v>457</v>
@@ -22205,7 +22205,7 @@
         <v>1</v>
       </c>
       <c r="BA63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB63" s="1">
         <v>4</v>
@@ -22349,7 +22349,7 @@
         <v>93</v>
       </c>
       <c r="CW63" s="1">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -25733,7 +25733,7 @@
         <v>2</v>
       </c>
       <c r="I75" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J75" s="1">
         <v>0</v>
@@ -26009,7 +26009,7 @@
         <v>15</v>
       </c>
       <c r="CW75" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -26935,7 +26935,7 @@
         <v>4278</v>
       </c>
       <c r="C79" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D79" s="2">
         <v>43</v>
@@ -27223,7 +27223,7 @@
         <v>90617</v>
       </c>
       <c r="CU79" s="1">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="CV79" s="1">
         <v>655</v>
@@ -27246,7 +27246,7 @@
         <v>5</v>
       </c>
       <c r="E80" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F80" s="1">
         <v>17</v>
@@ -27534,7 +27534,7 @@
         <v>144</v>
       </c>
       <c r="CW80" s="1">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -28478,7 +28478,7 @@
         <v>3</v>
       </c>
       <c r="I84" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J84" s="1">
         <v>0</v>
@@ -28754,7 +28754,7 @@
         <v>3</v>
       </c>
       <c r="CW84" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:101">
@@ -30625,7 +30625,7 @@
         <v>185</v>
       </c>
       <c r="M91" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30889,7 +30889,7 @@
         <v>412</v>
       </c>
       <c r="CW91" s="1">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -34022,7 +34022,7 @@
         <v>127</v>
       </c>
       <c r="AA102" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB102" s="2">
         <v>4</v>
@@ -34238,7 +34238,7 @@
         <v>43024</v>
       </c>
       <c r="CU102" s="1">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="CV102" s="1">
         <v>781</v>
@@ -36701,7 +36701,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="1">
         <v>71</v>
@@ -36989,7 +36989,7 @@
         <v>39</v>
       </c>
       <c r="CW111" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37311,7 +37311,7 @@
         <v>0</v>
       </c>
       <c r="E113" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -37599,7 +37599,7 @@
         <v>482</v>
       </c>
       <c r="CW113" s="1">
-        <v>9936</v>
+        <v>9884</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -47071,7 +47071,7 @@
         <v>10</v>
       </c>
       <c r="E145" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -47095,7 +47095,7 @@
         <v>10</v>
       </c>
       <c r="M145" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N145" s="1">
         <v>815</v>
@@ -47359,7 +47359,7 @@
         <v>51</v>
       </c>
       <c r="CW145" s="1">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -49224,7 +49224,7 @@
         <v>857</v>
       </c>
       <c r="K152" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L152" s="2">
         <v>32</v>
@@ -49488,7 +49488,7 @@
         <v>3009</v>
       </c>
       <c r="CU152" s="1">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="CV152" s="1">
         <v>102</v>
@@ -52017,7 +52017,7 @@
         <v>120</v>
       </c>
       <c r="AA161" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB161" s="2">
         <v>4</v>
@@ -52233,7 +52233,7 @@
         <v>22379</v>
       </c>
       <c r="CU161" s="1">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="CV161" s="1">
         <v>743</v>
@@ -53494,7 +53494,7 @@
         <v>1698</v>
       </c>
       <c r="K166" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2">
         <v>62</v>
@@ -53758,7 +53758,7 @@
         <v>5253</v>
       </c>
       <c r="CU166" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="CV166" s="1">
         <v>132</v>
@@ -54403,7 +54403,7 @@
         <v>2</v>
       </c>
       <c r="I169" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169" s="1">
         <v>0</v>
@@ -54679,7 +54679,7 @@
         <v>19</v>
       </c>
       <c r="CW169" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54774,7 +54774,7 @@
         <v>3602</v>
       </c>
       <c r="AE170" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF170" s="2">
         <v>126</v>
@@ -54978,7 +54978,7 @@
         <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
@@ -57992,7 +57992,7 @@
         <v>2038</v>
       </c>
       <c r="CI180" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CJ180" s="2">
         <v>52</v>
@@ -58028,7 +58028,7 @@
         <v>51139</v>
       </c>
       <c r="CU180" s="1">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="CV180" s="1">
         <v>1244</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
@@ -4961,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="CV6" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CW6" s="1">
         <v>103</v>
@@ -9198,7 +9198,7 @@
         <v>30</v>
       </c>
       <c r="CK20" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9234,7 +9234,7 @@
         <v>387</v>
       </c>
       <c r="CW20" s="1">
-        <v>918</v>
+        <v>934</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -12322,7 +12322,7 @@
         <v>8</v>
       </c>
       <c r="L31" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="M31" s="2">
         <v>68</v>
@@ -12586,7 +12586,7 @@
         <v>29</v>
       </c>
       <c r="CV31" s="1">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="CW31" s="1">
         <v>447</v>
@@ -19119,7 +19119,7 @@
         <v>18</v>
       </c>
       <c r="AO53" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AP53" s="1">
         <v>1</v>
@@ -19248,7 +19248,7 @@
         <v>0</v>
       </c>
       <c r="CF53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG53" s="2">
         <v>1</v>
@@ -19263,7 +19263,7 @@
         <v>20</v>
       </c>
       <c r="CK53" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CL53" s="1">
         <v>1</v>
@@ -19296,10 +19296,10 @@
         <v>15</v>
       </c>
       <c r="CV53" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="CW53" s="1">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -22058,7 +22058,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E63" s="2">
         <v>25</v>
@@ -22178,10 +22178,10 @@
         <v>2</v>
       </c>
       <c r="AR63" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS63" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22310,7 +22310,7 @@
         <v>19</v>
       </c>
       <c r="CJ63" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="CK63" s="2">
         <v>45</v>
@@ -22346,10 +22346,10 @@
         <v>24</v>
       </c>
       <c r="CV63" s="1">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="CW63" s="1">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -25500,7 +25500,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25521,7 +25521,7 @@
         <v>52</v>
       </c>
       <c r="AN74" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AO74" s="2">
         <v>402</v>
@@ -25665,7 +25665,7 @@
         <v>64</v>
       </c>
       <c r="CJ74" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CK74" s="2">
         <v>401</v>
@@ -25701,10 +25701,10 @@
         <v>184</v>
       </c>
       <c r="CV74" s="1">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="CW74" s="1">
-        <v>4396</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26352,7 +26352,7 @@
         <v>44</v>
       </c>
       <c r="L77" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M77" s="2">
         <v>342</v>
@@ -26580,10 +26580,10 @@
         <v>112</v>
       </c>
       <c r="CJ77" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="CK77" s="2">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26616,10 +26616,10 @@
         <v>194</v>
       </c>
       <c r="CV77" s="1">
-        <v>10228</v>
+        <v>10236</v>
       </c>
       <c r="CW77" s="1">
-        <v>16085</v>
+        <v>16069</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27551,7 +27551,7 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F81" s="1">
         <v>5</v>
@@ -27692,7 +27692,7 @@
         <v>1</v>
       </c>
       <c r="AZ81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA81" s="2">
         <v>3</v>
@@ -27836,10 +27836,10 @@
         <v>36</v>
       </c>
       <c r="CV81" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="CW81" s="1">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28245,7 +28245,7 @@
         <v>176</v>
       </c>
       <c r="AG83" s="2">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28449,7 +28449,7 @@
         <v>887</v>
       </c>
       <c r="CW83" s="1">
-        <v>5419</v>
+        <v>5417</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28891,7 +28891,7 @@
         <v>2</v>
       </c>
       <c r="AS85" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT85" s="1">
         <v>0</v>
@@ -29023,7 +29023,7 @@
         <v>24</v>
       </c>
       <c r="CK85" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="CL85" s="1">
         <v>0</v>
@@ -29059,7 +29059,7 @@
         <v>30</v>
       </c>
       <c r="CW85" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -30099,7 +30099,7 @@
         <v>0</v>
       </c>
       <c r="AO89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP89" s="1">
         <v>42</v>
@@ -30108,7 +30108,7 @@
         <v>1</v>
       </c>
       <c r="AR89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS89" s="2">
         <v>5</v>
@@ -30240,10 +30240,10 @@
         <v>0</v>
       </c>
       <c r="CJ89" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CK89" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CL89" s="1">
         <v>10</v>
@@ -30276,10 +30276,10 @@
         <v>11</v>
       </c>
       <c r="CV89" s="1">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="CW89" s="1">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -33992,7 +33992,7 @@
         <v>210</v>
       </c>
       <c r="Q102" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34244,7 +34244,7 @@
         <v>781</v>
       </c>
       <c r="CW102" s="1">
-        <v>1819</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -37027,7 +37027,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M112" s="2">
         <v>82</v>
@@ -37291,7 +37291,7 @@
         <v>19</v>
       </c>
       <c r="CV112" s="1">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="CW112" s="1">
         <v>655</v>
@@ -37332,7 +37332,7 @@
         <v>63</v>
       </c>
       <c r="L113" s="2">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="M113" s="2">
         <v>414</v>
@@ -37596,7 +37596,7 @@
         <v>101</v>
       </c>
       <c r="CV113" s="1">
-        <v>482</v>
+        <v>413</v>
       </c>
       <c r="CW113" s="1">
         <v>9884</v>
@@ -38499,7 +38499,7 @@
         <v>0</v>
       </c>
       <c r="CR116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS116" s="2">
         <v>1</v>
@@ -38511,7 +38511,7 @@
         <v>84</v>
       </c>
       <c r="CV116" s="1">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="CW116" s="1">
         <v>1154</v>
@@ -38555,7 +38555,7 @@
         <v>3</v>
       </c>
       <c r="M117" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N117" s="1">
         <v>2543</v>
@@ -38819,7 +38819,7 @@
         <v>586</v>
       </c>
       <c r="CW117" s="1">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -38845,7 +38845,7 @@
         <v>2</v>
       </c>
       <c r="H118" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I118" s="2">
         <v>4</v>
@@ -39121,7 +39121,7 @@
         <v>8</v>
       </c>
       <c r="CV118" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="CW118" s="1">
         <v>36</v>
@@ -42200,7 +42200,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I129" s="2">
         <v>5</v>
@@ -42476,7 +42476,7 @@
         <v>5</v>
       </c>
       <c r="CV129" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="CW129" s="1">
         <v>293</v>
@@ -44105,7 +44105,7 @@
         <v>158</v>
       </c>
       <c r="AG135" s="2">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44309,7 +44309,7 @@
         <v>1014</v>
       </c>
       <c r="CW135" s="1">
-        <v>2756</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44957,7 +44957,7 @@
         <v>14</v>
       </c>
       <c r="L138" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M138" s="2">
         <v>65</v>
@@ -45221,7 +45221,7 @@
         <v>19</v>
       </c>
       <c r="CV138" s="1">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="CW138" s="1">
         <v>273</v>
@@ -45750,7 +45750,7 @@
         <v>1</v>
       </c>
       <c r="BU140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV140" s="1">
         <v>0</v>
@@ -45834,7 +45834,7 @@
         <v>12</v>
       </c>
       <c r="CW140" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -46766,7 +46766,7 @@
         <v>0</v>
       </c>
       <c r="E144" s="2">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F144" s="1">
         <v>15</v>
@@ -47054,7 +47054,7 @@
         <v>14</v>
       </c>
       <c r="CW144" s="1">
-        <v>67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47690,7 +47690,7 @@
         <v>0</v>
       </c>
       <c r="H147" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I147" s="2">
         <v>6</v>
@@ -47966,7 +47966,7 @@
         <v>2</v>
       </c>
       <c r="CV147" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW147" s="1">
         <v>27</v>
@@ -48480,7 +48480,7 @@
         <v>0</v>
       </c>
       <c r="BP149" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ149" s="2">
         <v>10</v>
@@ -48576,7 +48576,7 @@
         <v>2</v>
       </c>
       <c r="CV149" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CW149" s="1">
         <v>64</v>
@@ -49455,7 +49455,7 @@
         <v>2</v>
       </c>
       <c r="CJ152" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CK152" s="2">
         <v>37</v>
@@ -49491,7 +49491,7 @@
         <v>4</v>
       </c>
       <c r="CV152" s="1">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="CW152" s="1">
         <v>297</v>
@@ -51072,7 +51072,7 @@
         <v>55</v>
       </c>
       <c r="Q158" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51324,7 +51324,7 @@
         <v>840</v>
       </c>
       <c r="CW158" s="1">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51984,7 +51984,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q161" s="2">
         <v>477</v>
@@ -52236,7 +52236,7 @@
         <v>61</v>
       </c>
       <c r="CV161" s="1">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="CW161" s="1">
         <v>1273</v>
@@ -55025,7 +55025,7 @@
         <v>17</v>
       </c>
       <c r="M171" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N171" s="1">
         <v>2698</v>
@@ -55289,7 +55289,7 @@
         <v>45</v>
       </c>
       <c r="CW171" s="1">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -57441,7 +57441,7 @@
         <v>0</v>
       </c>
       <c r="E179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="1">
         <v>27</v>
@@ -57729,7 +57729,7 @@
         <v>42</v>
       </c>
       <c r="CW179" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -57851,7 +57851,7 @@
         <v>4</v>
       </c>
       <c r="AN180" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO180" s="2">
         <v>13</v>
@@ -58031,7 +58031,7 @@
         <v>35</v>
       </c>
       <c r="CV180" s="1">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="CW180" s="1">
         <v>2740</v>
@@ -59391,7 +59391,7 @@
         <v>3</v>
       </c>
       <c r="AS185" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT185" s="1">
         <v>0</v>
@@ -59535,7 +59535,7 @@
         <v>2</v>
       </c>
       <c r="CO185" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP185" s="1">
         <v>0</v>
@@ -59559,7 +59559,7 @@
         <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -62049,7 +62049,7 @@
         <v>17</v>
       </c>
       <c r="P194" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q194" s="2">
         <v>1228</v>
@@ -62301,7 +62301,7 @@
         <v>43</v>
       </c>
       <c r="CV194" s="1">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="CW194" s="1">
         <v>1370</v>
@@ -62342,7 +62342,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M195" s="2">
         <v>11</v>
@@ -62606,7 +62606,7 @@
         <v>12</v>
       </c>
       <c r="CV195" s="1">
-        <v>3371</v>
+        <v>3367</v>
       </c>
       <c r="CW195" s="1">
         <v>5331</v>
@@ -62650,7 +62650,7 @@
         <v>14</v>
       </c>
       <c r="M196" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N196" s="1">
         <v>3415</v>
@@ -62914,7 +62914,7 @@
         <v>91</v>
       </c>
       <c r="CW196" s="1">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63951,7 +63951,7 @@
         <v>4</v>
       </c>
       <c r="AN200" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO200" s="2">
         <v>15</v>
@@ -64095,7 +64095,7 @@
         <v>17</v>
       </c>
       <c r="CJ200" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CK200" s="2">
         <v>72</v>
@@ -64131,7 +64131,7 @@
         <v>64</v>
       </c>
       <c r="CV200" s="1">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="CW200" s="1">
         <v>513</v>
@@ -66295,7 +66295,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I208" s="2">
         <v>2</v>
@@ -66571,7 +66571,7 @@
         <v>2</v>
       </c>
       <c r="CV208" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW208" s="1">
         <v>12</v>
@@ -66840,7 +66840,7 @@
         <v>17</v>
       </c>
       <c r="CJ209" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="CK209" s="2">
         <v>78</v>
@@ -66876,7 +66876,7 @@
         <v>21</v>
       </c>
       <c r="CV209" s="1">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="CW209" s="1">
         <v>113</v>
@@ -67916,7 +67916,7 @@
         <v>3</v>
       </c>
       <c r="AN213" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO213" s="2">
         <v>10</v>
@@ -68060,7 +68060,7 @@
         <v>0</v>
       </c>
       <c r="CJ213" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CK213" s="2">
         <v>17</v>
@@ -68096,7 +68096,7 @@
         <v>4</v>
       </c>
       <c r="CV213" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CW213" s="1">
         <v>36</v>
@@ -69677,7 +69677,7 @@
         <v>582</v>
       </c>
       <c r="D63">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E63" t="s">
         <v>715</v>
@@ -69857,7 +69857,7 @@
         <v>591</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E72" t="s">
         <v>726</v>
@@ -69897,7 +69897,7 @@
         <v>593</v>
       </c>
       <c r="D74">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="E74" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3761,7 +3761,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>863</v>
       </c>
       <c r="CW3" s="1">
-        <v>2063</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -7451,7 +7451,7 @@
         <v>2786</v>
       </c>
       <c r="O15" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2">
         <v>155</v>
@@ -7703,7 +7703,7 @@
         <v>3415</v>
       </c>
       <c r="CU15" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CV15" s="1">
         <v>179</v>
@@ -10017,7 +10017,7 @@
         <v>0</v>
       </c>
       <c r="BE23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF23" s="1">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>27</v>
       </c>
       <c r="CW23" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -11189,7 +11189,7 @@
         <v>12</v>
       </c>
       <c r="AO27" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP27" s="1">
         <v>12</v>
@@ -11333,7 +11333,7 @@
         <v>18</v>
       </c>
       <c r="CK27" s="2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="CL27" s="1">
         <v>1</v>
@@ -11369,7 +11369,7 @@
         <v>39</v>
       </c>
       <c r="CW27" s="1">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -12672,7 +12672,7 @@
         <v>117</v>
       </c>
       <c r="AA32" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="2">
         <v>4</v>
@@ -12888,7 +12888,7 @@
         <v>11125</v>
       </c>
       <c r="CU32" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="CV32" s="1">
         <v>223</v>
@@ -16081,7 +16081,7 @@
         <v>3</v>
       </c>
       <c r="AS43" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -16225,7 +16225,7 @@
         <v>3</v>
       </c>
       <c r="CO43" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CP43" s="1">
         <v>0</v>
@@ -16249,7 +16249,7 @@
         <v>26</v>
       </c>
       <c r="CW43" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -20548,7 +20548,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20656,7 +20656,7 @@
         <v>2</v>
       </c>
       <c r="AS58" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -20800,7 +20800,7 @@
         <v>2</v>
       </c>
       <c r="CO58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
@@ -20824,7 +20824,7 @@
         <v>18</v>
       </c>
       <c r="CW58" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -21445,7 +21445,7 @@
         <v>6512</v>
       </c>
       <c r="C61" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D61" s="2">
         <v>212</v>
@@ -21733,7 +21733,7 @@
         <v>65929</v>
       </c>
       <c r="CU61" s="1">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="CV61" s="1">
         <v>457</v>
@@ -25518,7 +25518,7 @@
         <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AN74" s="2">
         <v>131</v>
@@ -25662,7 +25662,7 @@
         <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CJ74" s="2">
         <v>188</v>
@@ -25698,7 +25698,7 @@
         <v>171614</v>
       </c>
       <c r="CU74" s="1">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="CV74" s="1">
         <v>1844</v>
@@ -26439,7 +26439,7 @@
         <v>50</v>
       </c>
       <c r="AO77" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26619,7 +26619,7 @@
         <v>10236</v>
       </c>
       <c r="CW77" s="1">
-        <v>16069</v>
+        <v>16066</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -28245,7 +28245,7 @@
         <v>176</v>
       </c>
       <c r="AG83" s="2">
-        <v>3481</v>
+        <v>3497</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28293,7 +28293,7 @@
         <v>3</v>
       </c>
       <c r="AW83" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX83" s="1">
         <v>17</v>
@@ -28449,7 +28449,7 @@
         <v>887</v>
       </c>
       <c r="CW83" s="1">
-        <v>5417</v>
+        <v>5432</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -32132,7 +32132,7 @@
         <v>48</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="2">
         <v>2</v>
@@ -32408,7 +32408,7 @@
         <v>964</v>
       </c>
       <c r="CU96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV96" s="1">
         <v>16</v>
@@ -33992,7 +33992,7 @@
         <v>210</v>
       </c>
       <c r="Q102" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="R102" s="1">
         <v>0</v>
@@ -34088,7 +34088,7 @@
         <v>2</v>
       </c>
       <c r="AW102" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX102" s="1">
         <v>17</v>
@@ -38549,7 +38549,7 @@
         <v>332</v>
       </c>
       <c r="K117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2">
         <v>3</v>
@@ -38651,7 +38651,7 @@
         <v>1</v>
       </c>
       <c r="AS117" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT117" s="1">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         <v>165</v>
       </c>
       <c r="CI117" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ117" s="2">
         <v>7</v>
       </c>
       <c r="CK117" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CL117" s="1">
         <v>28</v>
@@ -38813,13 +38813,13 @@
         <v>13155</v>
       </c>
       <c r="CU117" s="1">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="CV117" s="1">
         <v>586</v>
       </c>
       <c r="CW117" s="1">
-        <v>1214</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -38842,7 +38842,7 @@
         <v>40</v>
       </c>
       <c r="G118" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" s="2">
         <v>2</v>
@@ -39118,7 +39118,7 @@
         <v>134</v>
       </c>
       <c r="CU118" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV118" s="1">
         <v>33</v>
@@ -39147,7 +39147,7 @@
         <v>62</v>
       </c>
       <c r="G119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="2">
         <v>1</v>
@@ -39423,7 +39423,7 @@
         <v>842</v>
       </c>
       <c r="CU119" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV119" s="1">
         <v>13</v>
@@ -39554,7 +39554,7 @@
         <v>19</v>
       </c>
       <c r="AO120" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP120" s="1">
         <v>0</v>
@@ -39698,7 +39698,7 @@
         <v>26</v>
       </c>
       <c r="CK120" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CL120" s="1">
         <v>0</v>
@@ -39734,7 +39734,7 @@
         <v>47</v>
       </c>
       <c r="CW120" s="1">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -41288,7 +41288,7 @@
         <v>3</v>
       </c>
       <c r="I126" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J126" s="1">
         <v>0</v>
@@ -41564,7 +41564,7 @@
         <v>14</v>
       </c>
       <c r="CW126" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:101">
@@ -46473,7 +46473,7 @@
         <v>3</v>
       </c>
       <c r="I143" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J143" s="1">
         <v>0</v>
@@ -46581,7 +46581,7 @@
         <v>2</v>
       </c>
       <c r="AS143" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT143" s="1">
         <v>0</v>
@@ -46749,7 +46749,7 @@
         <v>13</v>
       </c>
       <c r="CW143" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -46886,7 +46886,7 @@
         <v>2</v>
       </c>
       <c r="AS144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT144" s="1">
         <v>0</v>
@@ -47030,7 +47030,7 @@
         <v>2</v>
       </c>
       <c r="CO144" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP144" s="1">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>14</v>
       </c>
       <c r="CW144" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47939,7 +47939,7 @@
         <v>25</v>
       </c>
       <c r="CM147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN147" s="2">
         <v>2</v>
@@ -47963,7 +47963,7 @@
         <v>219</v>
       </c>
       <c r="CU147" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV147" s="1">
         <v>13</v>
@@ -51066,7 +51066,7 @@
         <v>3024</v>
       </c>
       <c r="O158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P158" s="2">
         <v>55</v>
@@ -51318,7 +51318,7 @@
         <v>25461</v>
       </c>
       <c r="CU158" s="1">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CV158" s="1">
         <v>840</v>
@@ -54780,7 +54780,7 @@
         <v>126</v>
       </c>
       <c r="AG170" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54984,7 +54984,7 @@
         <v>501</v>
       </c>
       <c r="CW170" s="1">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -54995,7 +54995,7 @@
         <v>504</v>
       </c>
       <c r="C171" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D171" s="2">
         <v>3</v>
@@ -55283,7 +55283,7 @@
         <v>5829</v>
       </c>
       <c r="CU171" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV171" s="1">
         <v>45</v>
@@ -64145,7 +64145,7 @@
         <v>8407</v>
       </c>
       <c r="C201" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D201" s="2">
         <v>-1</v>
@@ -64169,7 +64169,7 @@
         <v>3540</v>
       </c>
       <c r="K201" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L201" s="2">
         <v>118</v>
@@ -64433,7 +64433,7 @@
         <v>88076</v>
       </c>
       <c r="CU201" s="1">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="CV201" s="1">
         <v>2006</v>
@@ -69534,7 +69534,7 @@
         <v>575</v>
       </c>
       <c r="D56">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" t="s">
         <v>715</v>
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3836,16 +3836,16 @@
         <v>4</v>
       </c>
       <c r="AD3" s="1">
-        <v>18287</v>
+        <v>18286</v>
       </c>
       <c r="AE3" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF3" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG3" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46680</v>
+        <v>46679</v>
       </c>
       <c r="CU3" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="CV3" s="1">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="CW3" s="1">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -5711,7 +5711,7 @@
         <v>3</v>
       </c>
       <c r="AS9" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="CO9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP9" s="1">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>50</v>
       </c>
       <c r="CW9" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7215,28 +7215,28 @@
         <v>0</v>
       </c>
       <c r="AL14" s="1">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AM14" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN14" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AO14" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AP14" s="1">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="AQ14" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR14" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AS14" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AT14" s="1">
         <v>0</v>
@@ -7359,16 +7359,16 @@
         <v>0</v>
       </c>
       <c r="CH14" s="1">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="CI14" s="2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="CJ14" s="2">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="CK14" s="2">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="CL14" s="1">
         <v>29</v>
@@ -7395,16 +7395,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3097</v>
+        <v>3183</v>
       </c>
       <c r="CU14" s="1">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="CV14" s="1">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="CW14" s="1">
-        <v>278</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7750,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" s="1">
         <v>338</v>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
       <c r="CW16" s="1">
-        <v>-36</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -10714,16 +10714,16 @@
         <v>0</v>
       </c>
       <c r="CH25" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="CI25" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CJ25" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CK25" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CL25" s="1">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         <v>0</v>
       </c>
       <c r="CT25" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CU25" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV25" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CW25" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:101">
@@ -11078,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
         <v>6</v>
@@ -11366,7 +11366,7 @@
         <v>10</v>
       </c>
       <c r="CV27" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="CW27" s="1">
         <v>61</v>
@@ -11383,7 +11383,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2">
         <v>8</v>
@@ -11671,7 +11671,7 @@
         <v>16</v>
       </c>
       <c r="CV28" s="1">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="CW28" s="1">
         <v>780</v>
@@ -13219,16 +13219,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="1">
         <v>499</v>
@@ -13495,16 +13495,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="CU34" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV34" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CW34" s="1">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -15354,16 +15354,16 @@
         <v>6</v>
       </c>
       <c r="F41" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
@@ -15450,16 +15450,16 @@
         <v>0</v>
       </c>
       <c r="AL41" s="1">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AM41" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN41" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO41" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AP41" s="1">
         <v>11</v>
@@ -15594,16 +15594,16 @@
         <v>0</v>
       </c>
       <c r="CH41" s="1">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="CI41" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CJ41" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="CK41" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="CL41" s="1">
         <v>6</v>
@@ -15630,16 +15630,16 @@
         <v>0</v>
       </c>
       <c r="CT41" s="1">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="CU41" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CV41" s="1">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="CW41" s="1">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:101">
@@ -16266,7 +16266,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1">
         <v>13</v>
@@ -16554,7 +16554,7 @@
         <v>1953</v>
       </c>
       <c r="CW44" s="1">
-        <v>2461</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -20010,7 +20010,7 @@
         <v>21</v>
       </c>
       <c r="AG56" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -20214,7 +20214,7 @@
         <v>118</v>
       </c>
       <c r="CW56" s="1">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20545,7 +20545,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
@@ -20653,7 +20653,7 @@
         <v>1</v>
       </c>
       <c r="AR58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS58" s="2">
         <v>3</v>
@@ -20797,7 +20797,7 @@
         <v>1</v>
       </c>
       <c r="CN58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO58" s="2">
         <v>2</v>
@@ -20821,7 +20821,7 @@
         <v>3</v>
       </c>
       <c r="CV58" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CW58" s="1">
         <v>31</v>
@@ -21442,16 +21442,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6512</v>
+        <v>6502</v>
       </c>
       <c r="C61" s="2">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="D61" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E61" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65929</v>
+        <v>65919</v>
       </c>
       <c r="CU61" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="CV61" s="1">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="CW61" s="1">
-        <v>964</v>
+        <v>954</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -24953,16 +24953,16 @@
         <v>0</v>
       </c>
       <c r="BB72" s="1">
+        <v>3</v>
+      </c>
+      <c r="BC72" s="2">
         <v>2</v>
       </c>
-      <c r="BC72" s="2">
-        <v>1</v>
-      </c>
       <c r="BD72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF72" s="1">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="CU72" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV72" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CW72" s="1">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25665,7 +25665,7 @@
         <v>63</v>
       </c>
       <c r="CJ74" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="CK74" s="2">
         <v>401</v>
@@ -25701,7 +25701,7 @@
         <v>181</v>
       </c>
       <c r="CV74" s="1">
-        <v>1844</v>
+        <v>1837</v>
       </c>
       <c r="CW74" s="1">
         <v>4399</v>
@@ -26146,7 +26146,7 @@
         <v>2</v>
       </c>
       <c r="AS76" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT76" s="1">
         <v>26</v>
@@ -26278,7 +26278,7 @@
         <v>41</v>
       </c>
       <c r="CK76" s="2">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="CL76" s="1">
         <v>7</v>
@@ -26314,7 +26314,7 @@
         <v>1337</v>
       </c>
       <c r="CW76" s="1">
-        <v>3748</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26439,7 +26439,7 @@
         <v>50</v>
       </c>
       <c r="AO77" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7297</v>
+        <v>7298</v>
       </c>
       <c r="CI77" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="CJ77" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="CK77" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,13 +26610,13 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390875</v>
+        <v>390876</v>
       </c>
       <c r="CU77" s="1">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="CV77" s="1">
-        <v>10236</v>
+        <v>10237</v>
       </c>
       <c r="CW77" s="1">
         <v>16066</v>
@@ -27868,7 +27868,7 @@
         <v>3</v>
       </c>
       <c r="I82" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -27976,7 +27976,7 @@
         <v>3</v>
       </c>
       <c r="AS82" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -28120,7 +28120,7 @@
         <v>2</v>
       </c>
       <c r="CO82" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP82" s="1">
         <v>0</v>
@@ -28144,7 +28144,7 @@
         <v>10</v>
       </c>
       <c r="CW82" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28245,7 +28245,7 @@
         <v>176</v>
       </c>
       <c r="AG83" s="2">
-        <v>3497</v>
+        <v>3521</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28305,7 +28305,7 @@
         <v>1</v>
       </c>
       <c r="BA83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB83" s="1">
         <v>14</v>
@@ -28449,7 +28449,7 @@
         <v>887</v>
       </c>
       <c r="CW83" s="1">
-        <v>5432</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28876,22 +28876,22 @@
         <v>0</v>
       </c>
       <c r="AN85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO85" s="2">
         <v>1</v>
       </c>
       <c r="AP85" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ85" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR85" s="2">
         <v>2</v>
       </c>
       <c r="AS85" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT85" s="1">
         <v>0</v>
@@ -29014,16 +29014,16 @@
         <v>0</v>
       </c>
       <c r="CH85" s="1">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="CI85" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CJ85" s="2">
         <v>24</v>
       </c>
       <c r="CK85" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="CL85" s="1">
         <v>0</v>
@@ -29050,16 +29050,16 @@
         <v>0</v>
       </c>
       <c r="CT85" s="1">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="CU85" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="CV85" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CW85" s="1">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -30625,7 +30625,7 @@
         <v>185</v>
       </c>
       <c r="M91" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30889,7 +30889,7 @@
         <v>412</v>
       </c>
       <c r="CW91" s="1">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33989,7 +33989,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Q102" s="2">
         <v>534</v>
@@ -34241,7 +34241,7 @@
         <v>186</v>
       </c>
       <c r="CV102" s="1">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="CW102" s="1">
         <v>1813</v>
@@ -35176,7 +35176,7 @@
         <v>270</v>
       </c>
       <c r="E106" s="2">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35464,7 +35464,7 @@
         <v>1155</v>
       </c>
       <c r="CW106" s="1">
-        <v>2632</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35472,28 +35472,28 @@
         <v>206</v>
       </c>
       <c r="B107" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="1">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G107" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I107" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J107" s="1">
         <v>0</v>
@@ -35760,16 +35760,16 @@
         <v>0</v>
       </c>
       <c r="CT107" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CU107" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV107" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CW107" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:101">
@@ -35789,16 +35789,16 @@
         <v>6</v>
       </c>
       <c r="F108" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I108" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" s="1">
         <v>0</v>
@@ -36065,16 +36065,16 @@
         <v>0</v>
       </c>
       <c r="CT108" s="1">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="CU108" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV108" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CW108" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36809,7 +36809,7 @@
         <v>9</v>
       </c>
       <c r="AO111" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP111" s="1">
         <v>45</v>
@@ -36953,7 +36953,7 @@
         <v>25</v>
       </c>
       <c r="CK111" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36989,7 +36989,7 @@
         <v>39</v>
       </c>
       <c r="CW111" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -38546,16 +38546,16 @@
         <v>0</v>
       </c>
       <c r="J117" s="1">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K117" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L117" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M117" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N117" s="1">
         <v>2543</v>
@@ -38810,16 +38810,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>13155</v>
+        <v>13158</v>
       </c>
       <c r="CU117" s="1">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="CV117" s="1">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="CW117" s="1">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -43716,7 +43716,7 @@
         <v>12</v>
       </c>
       <c r="E134" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -44004,7 +44004,7 @@
         <v>2552</v>
       </c>
       <c r="CW134" s="1">
-        <v>5812</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44096,16 +44096,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11788</v>
+        <v>11787</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF135" s="2">
         <v>158</v>
       </c>
       <c r="AG135" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62642</v>
+        <v>62641</v>
       </c>
       <c r="CU135" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="CV135" s="1">
         <v>1014</v>
       </c>
       <c r="CW135" s="1">
-        <v>2742</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -45962,16 +45962,16 @@
         <v>1</v>
       </c>
       <c r="AP141" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AQ141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS141" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT141" s="1">
         <v>0</v>
@@ -46106,16 +46106,16 @@
         <v>2</v>
       </c>
       <c r="CL141" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="CM141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO141" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP141" s="1">
         <v>0</v>
@@ -46130,16 +46130,16 @@
         <v>0</v>
       </c>
       <c r="CT141" s="1">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="CU141" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV141" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CW141" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -47684,16 +47684,16 @@
         <v>0</v>
       </c>
       <c r="F147" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I147" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J147" s="1">
         <v>18</v>
@@ -47798,7 +47798,7 @@
         <v>0</v>
       </c>
       <c r="AR147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS147" s="2">
         <v>4</v>
@@ -47942,7 +47942,7 @@
         <v>0</v>
       </c>
       <c r="CN147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO147" s="2">
         <v>3</v>
@@ -47960,16 +47960,16 @@
         <v>0</v>
       </c>
       <c r="CT147" s="1">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="CU147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV147" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW147" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -51643,7 +51643,7 @@
         <v>0</v>
       </c>
       <c r="D160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" s="2">
         <v>4</v>
@@ -51655,7 +51655,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="2">
         <v>4</v>
@@ -51931,7 +51931,7 @@
         <v>0</v>
       </c>
       <c r="CV160" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CW160" s="1">
         <v>8</v>
@@ -51975,7 +51975,7 @@
         <v>86</v>
       </c>
       <c r="M161" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N161" s="1">
         <v>10033</v>
@@ -51984,7 +51984,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q161" s="2">
         <v>477</v>
@@ -52236,10 +52236,10 @@
         <v>61</v>
       </c>
       <c r="CV161" s="1">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="CW161" s="1">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -54496,7 +54496,7 @@
         <v>3</v>
       </c>
       <c r="AN169" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO169" s="2">
         <v>17</v>
@@ -54676,7 +54676,7 @@
         <v>12</v>
       </c>
       <c r="CV169" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CW169" s="1">
         <v>59</v>
@@ -55943,16 +55943,16 @@
         <v>0</v>
       </c>
       <c r="N174" s="1">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="O174" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P174" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q174" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R174" s="1">
         <v>0</v>
@@ -56015,16 +56015,16 @@
         <v>0</v>
       </c>
       <c r="AL174" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP174" s="1">
         <v>109</v>
@@ -56195,16 +56195,16 @@
         <v>0</v>
       </c>
       <c r="CT174" s="1">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="CU174" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="CV174" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="CW174" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -57746,7 +57746,7 @@
         <v>113</v>
       </c>
       <c r="E180" s="2">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -58034,7 +58034,7 @@
         <v>1243</v>
       </c>
       <c r="CW180" s="1">
-        <v>2740</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -59382,16 +59382,16 @@
         <v>0</v>
       </c>
       <c r="AP185" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ185" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR185" s="2">
         <v>3</v>
       </c>
       <c r="AS185" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT185" s="1">
         <v>0</v>
@@ -59526,16 +59526,16 @@
         <v>1</v>
       </c>
       <c r="CL185" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CM185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN185" s="2">
         <v>2</v>
       </c>
       <c r="CO185" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP185" s="1">
         <v>0</v>
@@ -59550,16 +59550,16 @@
         <v>0</v>
       </c>
       <c r="CT185" s="1">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="CU185" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CV185" s="1">
         <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -62133,7 +62133,7 @@
         <v>1</v>
       </c>
       <c r="AR194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS194" s="2">
         <v>6</v>
@@ -62265,7 +62265,7 @@
         <v>4</v>
       </c>
       <c r="CJ194" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK194" s="2">
         <v>13</v>
@@ -62301,7 +62301,7 @@
         <v>43</v>
       </c>
       <c r="CV194" s="1">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="CW194" s="1">
         <v>1370</v>
@@ -62336,16 +62336,16 @@
         <v>2</v>
       </c>
       <c r="J195" s="1">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K195" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L195" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M195" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N195" s="1">
         <v>976</v>
@@ -62600,16 +62600,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71191</v>
+        <v>71195</v>
       </c>
       <c r="CU195" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CV195" s="1">
-        <v>3367</v>
+        <v>3371</v>
       </c>
       <c r="CW195" s="1">
-        <v>5331</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -67222,22 +67222,22 @@
         <v>16</v>
       </c>
       <c r="L211" s="2">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="M211" s="2">
         <v>67</v>
       </c>
       <c r="N211" s="1">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="O211" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P211" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q211" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R211" s="1">
         <v>0</v>
@@ -67480,16 +67480,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>6273</v>
+        <v>6274</v>
       </c>
       <c r="CU211" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CV211" s="1">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="CW211" s="1">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -14589,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE38" s="2">
         <v>22</v>
@@ -14721,7 +14721,7 @@
         <v>15</v>
       </c>
       <c r="CV38" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CW38" s="1">
         <v>118</v>
@@ -21445,7 +21445,7 @@
         <v>6502</v>
       </c>
       <c r="C61" s="2">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="D61" s="2">
         <v>202</v>
@@ -21733,7 +21733,7 @@
         <v>65919</v>
       </c>
       <c r="CU61" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CV61" s="1">
         <v>447</v>
@@ -22970,7 +22970,7 @@
         <v>670</v>
       </c>
       <c r="C66" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D66" s="2">
         <v>9</v>
@@ -22994,7 +22994,7 @@
         <v>976</v>
       </c>
       <c r="K66" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="L66" s="2">
         <v>61</v>
@@ -23258,7 +23258,7 @@
         <v>1658</v>
       </c>
       <c r="CU66" s="1">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="CV66" s="1">
         <v>70</v>
@@ -24214,7 +24214,7 @@
         <v>281</v>
       </c>
       <c r="K70" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2">
         <v>20</v>
@@ -24478,7 +24478,7 @@
         <v>2258</v>
       </c>
       <c r="CU70" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="CV70" s="1">
         <v>44</v>
@@ -25216,7 +25216,7 @@
         <v>1</v>
       </c>
       <c r="AN73" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO73" s="2">
         <v>7</v>
@@ -25360,7 +25360,7 @@
         <v>18</v>
       </c>
       <c r="CJ73" s="2">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="CK73" s="2">
         <v>79</v>
@@ -25396,7 +25396,7 @@
         <v>21</v>
       </c>
       <c r="CV73" s="1">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="CW73" s="1">
         <v>96</v>
@@ -25518,7 +25518,7 @@
         <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AN74" s="2">
         <v>131</v>
@@ -25662,7 +25662,7 @@
         <v>16168</v>
       </c>
       <c r="CI74" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="CJ74" s="2">
         <v>181</v>
@@ -25698,7 +25698,7 @@
         <v>171614</v>
       </c>
       <c r="CU74" s="1">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="CV74" s="1">
         <v>1837</v>
@@ -26601,7 +26601,7 @@
         <v>14</v>
       </c>
       <c r="CQ77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR77" s="2">
         <v>1</v>
@@ -26613,7 +26613,7 @@
         <v>390876</v>
       </c>
       <c r="CU77" s="1">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="CV77" s="1">
         <v>10237</v>
@@ -29997,7 +29997,7 @@
         <v>38</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="2">
         <v>1</v>
@@ -30105,7 +30105,7 @@
         <v>42</v>
       </c>
       <c r="AQ89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR89" s="2">
         <v>2</v>
@@ -30249,7 +30249,7 @@
         <v>10</v>
       </c>
       <c r="CM89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN89" s="2">
         <v>1</v>
@@ -30273,7 +30273,7 @@
         <v>2171</v>
       </c>
       <c r="CU89" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CV89" s="1">
         <v>81</v>
@@ -31316,7 +31316,7 @@
         <v>3</v>
       </c>
       <c r="AN93" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO93" s="2">
         <v>5</v>
@@ -31460,7 +31460,7 @@
         <v>0</v>
       </c>
       <c r="CJ93" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CK93" s="2">
         <v>9</v>
@@ -31469,7 +31469,7 @@
         <v>36</v>
       </c>
       <c r="CM93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN93" s="2">
         <v>1</v>
@@ -31493,10 +31493,10 @@
         <v>1178</v>
       </c>
       <c r="CU93" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV93" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CW93" s="1">
         <v>65</v>
@@ -32363,7 +32363,7 @@
         <v>0</v>
       </c>
       <c r="CF96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG96" s="2">
         <v>1</v>
@@ -32411,7 +32411,7 @@
         <v>0</v>
       </c>
       <c r="CV96" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW96" s="1">
         <v>40</v>
@@ -35816,7 +35816,7 @@
         <v>498</v>
       </c>
       <c r="O108" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P108" s="2">
         <v>8</v>
@@ -36068,7 +36068,7 @@
         <v>943</v>
       </c>
       <c r="CU108" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="CV108" s="1">
         <v>25</v>
@@ -36417,7 +36417,7 @@
         <v>88</v>
       </c>
       <c r="L110" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M110" s="2">
         <v>416</v>
@@ -36681,7 +36681,7 @@
         <v>154</v>
       </c>
       <c r="CV110" s="1">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="CW110" s="1">
         <v>1011</v>
@@ -37123,7 +37123,7 @@
         <v>1</v>
       </c>
       <c r="AR112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS112" s="2">
         <v>6</v>
@@ -37255,7 +37255,7 @@
         <v>6</v>
       </c>
       <c r="CJ112" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CK112" s="2">
         <v>20</v>
@@ -37291,7 +37291,7 @@
         <v>19</v>
       </c>
       <c r="CV112" s="1">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="CW112" s="1">
         <v>655</v>
@@ -39085,7 +39085,7 @@
         <v>3</v>
       </c>
       <c r="CJ118" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="CK118" s="2">
         <v>27</v>
@@ -39121,7 +39121,7 @@
         <v>7</v>
       </c>
       <c r="CV118" s="1">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="CW118" s="1">
         <v>36</v>
@@ -42490,7 +42490,7 @@
         <v>76</v>
       </c>
       <c r="C130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" s="2">
         <v>4</v>
@@ -42778,7 +42778,7 @@
         <v>1089</v>
       </c>
       <c r="CU130" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV130" s="1">
         <v>130</v>
@@ -46880,7 +46880,7 @@
         <v>60</v>
       </c>
       <c r="AQ144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR144" s="2">
         <v>2</v>
@@ -47024,7 +47024,7 @@
         <v>69</v>
       </c>
       <c r="CM144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN144" s="2">
         <v>2</v>
@@ -47048,7 +47048,7 @@
         <v>1182</v>
       </c>
       <c r="CU144" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV144" s="1">
         <v>14</v>
@@ -47702,7 +47702,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M147" s="2">
         <v>2</v>
@@ -47966,7 +47966,7 @@
         <v>2</v>
       </c>
       <c r="CV147" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW147" s="1">
         <v>28</v>
@@ -50507,7 +50507,7 @@
         <v>2</v>
       </c>
       <c r="AF156" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG156" s="2">
         <v>332</v>
@@ -50711,7 +50711,7 @@
         <v>43</v>
       </c>
       <c r="CV156" s="1">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="CW156" s="1">
         <v>2533</v>
@@ -57995,7 +57995,7 @@
         <v>0</v>
       </c>
       <c r="CJ180" s="2">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="CK180" s="2">
         <v>92</v>
@@ -58031,7 +58031,7 @@
         <v>35</v>
       </c>
       <c r="CV180" s="1">
-        <v>1243</v>
+        <v>1227</v>
       </c>
       <c r="CW180" s="1">
         <v>2685</v>
@@ -60192,7 +60192,7 @@
         <v>73</v>
       </c>
       <c r="G188" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H188" s="2">
         <v>73</v>
@@ -60468,7 +60468,7 @@
         <v>161</v>
       </c>
       <c r="CU188" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CV188" s="1">
         <v>161</v>
@@ -65709,7 +65709,7 @@
         <v>0</v>
       </c>
       <c r="P206" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q206" s="2">
         <v>22</v>
@@ -65961,7 +65961,7 @@
         <v>14</v>
       </c>
       <c r="CV206" s="1">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="CW206" s="1">
         <v>22</v>
@@ -67447,7 +67447,7 @@
         <v>677</v>
       </c>
       <c r="CI211" s="2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CJ211" s="2">
         <v>45</v>
@@ -67483,7 +67483,7 @@
         <v>6274</v>
       </c>
       <c r="CU211" s="1">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="CV211" s="1">
         <v>488</v>
@@ -68471,7 +68471,7 @@
         <v>534</v>
       </c>
       <c r="D3">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E3" t="s">
         <v>715</v>
@@ -70463,7 +70463,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="E102" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -6605,16 +6605,16 @@
         <v>0</v>
       </c>
       <c r="AL12" s="1">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="AM12" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN12" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AO12" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AP12" s="1">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>1</v>
       </c>
       <c r="CH12" s="1">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="CI12" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ12" s="2">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="CK12" s="2">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="CL12" s="1">
         <v>0</v>
@@ -6785,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="CT12" s="1">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="CU12" s="1">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="CV12" s="1">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="CW12" s="1">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7475,7 +7475,7 @@
         <v>9</v>
       </c>
       <c r="W15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="2">
         <v>1</v>
@@ -7703,7 +7703,7 @@
         <v>3415</v>
       </c>
       <c r="CU15" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV15" s="1">
         <v>179</v>
@@ -8961,16 +8961,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="K20" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M20" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N20" s="1">
         <v>12653</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20685</v>
+        <v>20687</v>
       </c>
       <c r="CU20" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CV20" s="1">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="CW20" s="1">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -10717,7 +10717,7 @@
         <v>48</v>
       </c>
       <c r="CI25" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CJ25" s="2">
         <v>17</v>
@@ -10753,7 +10753,7 @@
         <v>110</v>
       </c>
       <c r="CU25" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CV25" s="1">
         <v>17</v>
@@ -12316,16 +12316,16 @@
         <v>1</v>
       </c>
       <c r="J31" s="1">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="K31" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L31" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M31" s="2">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="N31" s="1">
         <v>1982</v>
@@ -12580,16 +12580,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>5995</v>
+        <v>6004</v>
       </c>
       <c r="CU31" s="1">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="CV31" s="1">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="CW31" s="1">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -15342,16 +15342,16 @@
         <v>140</v>
       </c>
       <c r="B41" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="1">
         <v>47</v>
@@ -15450,16 +15450,16 @@
         <v>0</v>
       </c>
       <c r="AL41" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM41" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN41" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO41" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP41" s="1">
         <v>11</v>
@@ -15594,16 +15594,16 @@
         <v>0</v>
       </c>
       <c r="CH41" s="1">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="CI41" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="CJ41" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="CK41" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="CL41" s="1">
         <v>6</v>
@@ -15630,16 +15630,16 @@
         <v>0</v>
       </c>
       <c r="CT41" s="1">
-        <v>679</v>
+        <v>692</v>
       </c>
       <c r="CU41" s="1">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="CV41" s="1">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="CW41" s="1">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:101">
@@ -16257,16 +16257,16 @@
         <v>143</v>
       </c>
       <c r="B44" s="1">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C44" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" s="1">
         <v>13</v>
@@ -16281,16 +16281,16 @@
         <v>1</v>
       </c>
       <c r="J44" s="1">
-        <v>1347</v>
+        <v>1365</v>
       </c>
       <c r="K44" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L44" s="2">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M44" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="N44" s="1">
         <v>1597</v>
@@ -16545,16 +16545,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50636</v>
+        <v>50655</v>
       </c>
       <c r="CU44" s="1">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="CV44" s="1">
-        <v>1953</v>
+        <v>1972</v>
       </c>
       <c r="CW44" s="1">
-        <v>2455</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -18644,16 +18644,16 @@
         <v>0</v>
       </c>
       <c r="CH51" s="1">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="CI51" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CJ51" s="2">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="CK51" s="2">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18680,16 +18680,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1794</v>
+        <v>1820</v>
       </c>
       <c r="CU51" s="1">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="CV51" s="1">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="CW51" s="1">
-        <v>205</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20539,16 +20539,16 @@
         <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20647,16 +20647,16 @@
         <v>9</v>
       </c>
       <c r="AP58" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -20791,40 +20791,40 @@
         <v>12</v>
       </c>
       <c r="CL58" s="1">
+        <v>19</v>
+      </c>
+      <c r="CM58" s="2">
+        <v>2</v>
+      </c>
+      <c r="CN58" s="2">
+        <v>2</v>
+      </c>
+      <c r="CO58" s="2">
+        <v>3</v>
+      </c>
+      <c r="CP58" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ58" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR58" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS58" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT58" s="1">
+        <v>181</v>
+      </c>
+      <c r="CU58" s="1">
+        <v>6</v>
+      </c>
+      <c r="CV58" s="1">
         <v>18</v>
       </c>
-      <c r="CM58" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN58" s="2">
-        <v>1</v>
-      </c>
-      <c r="CO58" s="2">
-        <v>2</v>
-      </c>
-      <c r="CP58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT58" s="1">
-        <v>178</v>
-      </c>
-      <c r="CU58" s="1">
-        <v>3</v>
-      </c>
-      <c r="CV58" s="1">
-        <v>15</v>
-      </c>
       <c r="CW58" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="K59" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2">
         <v>6</v>
@@ -20955,7 +20955,7 @@
         <v>73</v>
       </c>
       <c r="AQ59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR59" s="2">
         <v>2</v>
@@ -21087,7 +21087,7 @@
         <v>79</v>
       </c>
       <c r="CI59" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ59" s="2">
         <v>9</v>
@@ -21123,7 +21123,7 @@
         <v>856</v>
       </c>
       <c r="CU59" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CV59" s="1">
         <v>34</v>
@@ -21442,16 +21442,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6502</v>
+        <v>6499</v>
       </c>
       <c r="C61" s="2">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="D61" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E61" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65919</v>
+        <v>65916</v>
       </c>
       <c r="CU61" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CV61" s="1">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="CW61" s="1">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -24211,16 +24211,16 @@
         <v>3</v>
       </c>
       <c r="J70" s="1">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K70" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M70" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N70" s="1">
         <v>1259</v>
@@ -24475,16 +24475,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2258</v>
+        <v>2262</v>
       </c>
       <c r="CU70" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CW70" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25518,7 +25518,7 @@
         <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN74" s="2">
         <v>131</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16168</v>
+        <v>16172</v>
       </c>
       <c r="CI74" s="2">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="CJ74" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="CK74" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171614</v>
+        <v>171618</v>
       </c>
       <c r="CU74" s="1">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="CV74" s="1">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="CW74" s="1">
-        <v>4399</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26023,7 +26023,7 @@
         <v>21</v>
       </c>
       <c r="D76" s="2">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E76" s="2">
         <v>156</v>
@@ -26053,16 +26053,16 @@
         <v>392</v>
       </c>
       <c r="N76" s="1">
-        <v>117541</v>
+        <v>117544</v>
       </c>
       <c r="O76" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P76" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="Q76" s="2">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>151013</v>
+        <v>151016</v>
       </c>
       <c r="CU76" s="1">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="CV76" s="1">
-        <v>1337</v>
+        <v>1316</v>
       </c>
       <c r="CW76" s="1">
-        <v>3740</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26430,16 +26430,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1910</v>
+        <v>1915</v>
       </c>
       <c r="AM77" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AN77" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO77" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390876</v>
+        <v>390881</v>
       </c>
       <c r="CU77" s="1">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="CV77" s="1">
-        <v>10237</v>
+        <v>10242</v>
       </c>
       <c r="CW77" s="1">
-        <v>16066</v>
+        <v>16071</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27554,16 +27554,16 @@
         <v>16</v>
       </c>
       <c r="F81" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="1">
         <v>1578</v>
@@ -27830,16 +27830,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="CU81" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CV81" s="1">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CW81" s="1">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28290,7 +28290,7 @@
         <v>0</v>
       </c>
       <c r="AV83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW83" s="2">
         <v>5</v>
@@ -28446,7 +28446,7 @@
         <v>111</v>
       </c>
       <c r="CV83" s="1">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="CW83" s="1">
         <v>5455</v>
@@ -29178,7 +29178,7 @@
         <v>205</v>
       </c>
       <c r="AM86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN86" s="2">
         <v>3</v>
@@ -29322,7 +29322,7 @@
         <v>646</v>
       </c>
       <c r="CI86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ86" s="2">
         <v>5</v>
@@ -29358,7 +29358,7 @@
         <v>2832</v>
       </c>
       <c r="CU86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV86" s="1">
         <v>34</v>
@@ -29615,7 +29615,7 @@
         <v>10</v>
       </c>
       <c r="CE87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF87" s="2">
         <v>1</v>
@@ -29663,7 +29663,7 @@
         <v>2974</v>
       </c>
       <c r="CU87" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CV87" s="1">
         <v>46</v>
@@ -30102,16 +30102,16 @@
         <v>0</v>
       </c>
       <c r="AP89" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AQ89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR89" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS89" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30234,16 +30234,16 @@
         <v>0</v>
       </c>
       <c r="CH89" s="1">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="CI89" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CJ89" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CK89" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CL89" s="1">
         <v>10</v>
@@ -30270,16 +30270,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2171</v>
+        <v>2178</v>
       </c>
       <c r="CU89" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CV89" s="1">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="CW89" s="1">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30616,16 +30616,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="K91" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L91" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M91" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30880,16 +30880,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25854</v>
+        <v>25853</v>
       </c>
       <c r="CU91" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="CV91" s="1">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="CW91" s="1">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -34874,16 +34874,16 @@
         <v>31</v>
       </c>
       <c r="F105" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G105" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H105" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I105" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J105" s="1">
         <v>997</v>
@@ -34949,7 +34949,7 @@
         <v>4469</v>
       </c>
       <c r="AE105" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF105" s="2">
         <v>375</v>
@@ -35150,16 +35150,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7978</v>
+        <v>7980</v>
       </c>
       <c r="CU105" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CV105" s="1">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="CW105" s="1">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -37619,292 +37619,292 @@
         <v>2</v>
       </c>
       <c r="F114" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G114" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I114" s="2">
+        <v>5</v>
+      </c>
+      <c r="J114" s="1">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2">
+        <v>0</v>
+      </c>
+      <c r="N114" s="1">
+        <v>0</v>
+      </c>
+      <c r="O114" s="2">
+        <v>0</v>
+      </c>
+      <c r="P114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>0</v>
+      </c>
+      <c r="R114" s="1">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2">
+        <v>0</v>
+      </c>
+      <c r="T114" s="2">
+        <v>0</v>
+      </c>
+      <c r="U114" s="2">
+        <v>0</v>
+      </c>
+      <c r="V114" s="1">
+        <v>0</v>
+      </c>
+      <c r="W114" s="2">
+        <v>0</v>
+      </c>
+      <c r="X114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY114" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV114" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY114" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP114" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS114" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT114" s="1">
+        <v>173</v>
+      </c>
+      <c r="CU114" s="1">
+        <v>2</v>
+      </c>
+      <c r="CV114" s="1">
         <v>4</v>
       </c>
-      <c r="J114" s="1">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2">
-        <v>0</v>
-      </c>
-      <c r="N114" s="1">
-        <v>0</v>
-      </c>
-      <c r="O114" s="2">
-        <v>0</v>
-      </c>
-      <c r="P114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="2">
-        <v>0</v>
-      </c>
-      <c r="R114" s="1">
-        <v>0</v>
-      </c>
-      <c r="S114" s="2">
-        <v>0</v>
-      </c>
-      <c r="T114" s="2">
-        <v>0</v>
-      </c>
-      <c r="U114" s="2">
-        <v>0</v>
-      </c>
-      <c r="V114" s="1">
-        <v>0</v>
-      </c>
-      <c r="W114" s="2">
-        <v>0</v>
-      </c>
-      <c r="X114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y114" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX114" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY114" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV114" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY114" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP114" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS114" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT114" s="1">
-        <v>172</v>
-      </c>
-      <c r="CU114" s="1">
-        <v>1</v>
-      </c>
-      <c r="CV114" s="1">
-        <v>3</v>
-      </c>
       <c r="CW114" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38642,16 +38642,16 @@
         <v>1</v>
       </c>
       <c r="AP117" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AQ117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS117" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT117" s="1">
         <v>0</v>
@@ -38774,16 +38774,16 @@
         <v>0</v>
       </c>
       <c r="CH117" s="1">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CI117" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ117" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK117" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL117" s="1">
         <v>28</v>
@@ -38810,16 +38810,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>13158</v>
+        <v>13161</v>
       </c>
       <c r="CU117" s="1">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="CV117" s="1">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="CW117" s="1">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39144,16 +39144,16 @@
         <v>1</v>
       </c>
       <c r="F119" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I119" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J119" s="1">
         <v>0</v>
@@ -39252,16 +39252,16 @@
         <v>0</v>
       </c>
       <c r="AP119" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AQ119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS119" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT119" s="1">
         <v>0</v>
@@ -39396,16 +39396,16 @@
         <v>0</v>
       </c>
       <c r="CL119" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="CM119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO119" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP119" s="1">
         <v>0</v>
@@ -39420,16 +39420,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="CU119" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CV119" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CW119" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -39548,7 +39548,7 @@
         <v>114</v>
       </c>
       <c r="AM120" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AN120" s="2">
         <v>19</v>
@@ -39692,7 +39692,7 @@
         <v>127</v>
       </c>
       <c r="CI120" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CJ120" s="2">
         <v>26</v>
@@ -39728,7 +39728,7 @@
         <v>384</v>
       </c>
       <c r="CU120" s="1">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="CV120" s="1">
         <v>47</v>
@@ -43818,7 +43818,7 @@
         <v>1328</v>
       </c>
       <c r="AM134" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN134" s="2">
         <v>6</v>
@@ -43962,7 +43962,7 @@
         <v>2741</v>
       </c>
       <c r="CI134" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CJ134" s="2">
         <v>49</v>
@@ -43998,7 +43998,7 @@
         <v>134456</v>
       </c>
       <c r="CU134" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="CV134" s="1">
         <v>2552</v>
@@ -44096,16 +44096,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11787</v>
+        <v>11788</v>
       </c>
       <c r="AE135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF135" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG135" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62641</v>
+        <v>62642</v>
       </c>
       <c r="CU135" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="CV135" s="1">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="CW135" s="1">
-        <v>2741</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -46757,16 +46757,16 @@
         <v>243</v>
       </c>
       <c r="B144" s="1">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C144" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D144" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E144" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1">
         <v>15</v>
@@ -47045,16 +47045,16 @@
         <v>0</v>
       </c>
       <c r="CT144" s="1">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="CU144" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CV144" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW144" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47792,16 +47792,16 @@
         <v>1</v>
       </c>
       <c r="AP147" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AQ147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS147" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT147" s="1">
         <v>0</v>
@@ -47924,16 +47924,16 @@
         <v>0</v>
       </c>
       <c r="CH147" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CI147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CK147" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL147" s="1">
         <v>25</v>
@@ -47960,16 +47960,16 @@
         <v>0</v>
       </c>
       <c r="CT147" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="CU147" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV147" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CW147" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -49221,16 +49221,16 @@
         <v>1</v>
       </c>
       <c r="J152" s="1">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="K152" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L152" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="M152" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="N152" s="1">
         <v>168</v>
@@ -49485,16 +49485,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>3009</v>
+        <v>3022</v>
       </c>
       <c r="CU152" s="1">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="CW152" s="1">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50444,7 +50444,7 @@
         <v>2053</v>
       </c>
       <c r="K156" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2">
         <v>56</v>
@@ -50708,7 +50708,7 @@
         <v>71484</v>
       </c>
       <c r="CU156" s="1">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="CV156" s="1">
         <v>1051</v>
@@ -52744,16 +52744,16 @@
         <v>0</v>
       </c>
       <c r="BN163" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BO163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR163" s="1">
         <v>50</v>
@@ -52840,16 +52840,16 @@
         <v>0</v>
       </c>
       <c r="CT163" s="1">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="CU163" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV163" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CW163" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -54394,16 +54394,16 @@
         <v>1</v>
       </c>
       <c r="F169" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J169" s="1">
         <v>0</v>
@@ -54670,16 +54670,16 @@
         <v>0</v>
       </c>
       <c r="CT169" s="1">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="CU169" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV169" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CW169" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54690,7 +54690,7 @@
         <v>4531</v>
       </c>
       <c r="C170" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D170" s="2">
         <v>78</v>
@@ -54978,7 +54978,7 @@
         <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
@@ -55919,16 +55919,16 @@
         <v>3</v>
       </c>
       <c r="F174" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I174" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J174" s="1">
         <v>0</v>
@@ -56195,16 +56195,16 @@
         <v>0</v>
       </c>
       <c r="CT174" s="1">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="CU174" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV174" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CW174" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -57540,16 +57540,16 @@
         <v>0</v>
       </c>
       <c r="AL179" s="1">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM179" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN179" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO179" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP179" s="1">
         <v>5</v>
@@ -57684,16 +57684,16 @@
         <v>0</v>
       </c>
       <c r="CH179" s="1">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="CI179" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ179" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CK179" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CL179" s="1">
         <v>11</v>
@@ -57720,16 +57720,16 @@
         <v>0</v>
       </c>
       <c r="CT179" s="1">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="CU179" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CV179" s="1">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CW179" s="1">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -60432,7 +60432,7 @@
         <v>64</v>
       </c>
       <c r="CI188" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="CJ188" s="2">
         <v>64</v>
@@ -60468,7 +60468,7 @@
         <v>161</v>
       </c>
       <c r="CU188" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CV188" s="1">
         <v>161</v>
@@ -62046,7 +62046,7 @@
         <v>29177</v>
       </c>
       <c r="O194" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P194" s="2">
         <v>492</v>
@@ -62298,7 +62298,7 @@
         <v>32848</v>
       </c>
       <c r="CU194" s="1">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="CV194" s="1">
         <v>572</v>
@@ -65667,16 +65667,16 @@
         <v>305</v>
       </c>
       <c r="B206" s="1">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C206" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D206" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E206" s="2">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65955,16 +65955,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="CU206" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CV206" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="CW206" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -69697,7 +69697,7 @@
         <v>583</v>
       </c>
       <c r="D64">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
         <v>715</v>
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>
@@ -70743,7 +70743,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E116" t="s">
         <v>715</v>
@@ -71835,7 +71835,7 @@
         <v>676</v>
       </c>
       <c r="D170">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E170" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3782,7 +3782,7 @@
         <v>22</v>
       </c>
       <c r="L3" s="2">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="M3" s="2">
         <v>243</v>
@@ -4046,7 +4046,7 @@
         <v>49</v>
       </c>
       <c r="CV3" s="1">
-        <v>862</v>
+        <v>825</v>
       </c>
       <c r="CW3" s="1">
         <v>2056</v>
@@ -7140,7 +7140,7 @@
         <v>21</v>
       </c>
       <c r="M14" s="2">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="N14" s="1">
         <v>128</v>
@@ -7404,7 +7404,7 @@
         <v>143</v>
       </c>
       <c r="CW14" s="1">
-        <v>364</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7750,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" s="1">
         <v>338</v>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
       <c r="CW16" s="1">
-        <v>-37</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -12409,7 +12409,7 @@
         <v>12</v>
       </c>
       <c r="AO31" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AP31" s="1">
         <v>18</v>
@@ -12553,7 +12553,7 @@
         <v>165</v>
       </c>
       <c r="CK31" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12589,7 +12589,7 @@
         <v>274</v>
       </c>
       <c r="CW31" s="1">
-        <v>456</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -14460,7 +14460,7 @@
         <v>21</v>
       </c>
       <c r="M38" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N38" s="1">
         <v>840</v>
@@ -14724,7 +14724,7 @@
         <v>43</v>
       </c>
       <c r="CW38" s="1">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14741,7 +14741,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" s="1">
         <v>31</v>
@@ -15029,7 +15029,7 @@
         <v>76</v>
       </c>
       <c r="CW39" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -16078,7 +16078,7 @@
         <v>1</v>
       </c>
       <c r="AR43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS43" s="2">
         <v>5</v>
@@ -16222,7 +16222,7 @@
         <v>1</v>
       </c>
       <c r="CN43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO43" s="2">
         <v>5</v>
@@ -16246,7 +16246,7 @@
         <v>2</v>
       </c>
       <c r="CV43" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CW43" s="1">
         <v>34</v>
@@ -16374,7 +16374,7 @@
         <v>5</v>
       </c>
       <c r="AO44" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP44" s="1">
         <v>61</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="CK44" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="CL44" s="1">
         <v>33</v>
@@ -16554,7 +16554,7 @@
         <v>1972</v>
       </c>
       <c r="CW44" s="1">
-        <v>2474</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -18096,7 +18096,7 @@
         <v>6</v>
       </c>
       <c r="E50" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F50" s="1">
         <v>53</v>
@@ -18384,7 +18384,7 @@
         <v>40</v>
       </c>
       <c r="CW50" s="1">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -22501,16 +22501,16 @@
         <v>0</v>
       </c>
       <c r="AX64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB64" s="1">
         <v>8</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8012</v>
+        <v>8013</v>
       </c>
       <c r="CU64" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CV64" s="1">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CW64" s="1">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23706,7 +23706,7 @@
         <v>2</v>
       </c>
       <c r="AS68" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -23838,7 +23838,7 @@
         <v>4</v>
       </c>
       <c r="CK68" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="CL68" s="1">
         <v>27</v>
@@ -23874,7 +23874,7 @@
         <v>8</v>
       </c>
       <c r="CW68" s="1">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24220,7 +24220,7 @@
         <v>24</v>
       </c>
       <c r="M70" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N70" s="1">
         <v>1259</v>
@@ -24484,7 +24484,7 @@
         <v>48</v>
       </c>
       <c r="CW70" s="1">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24818,7 +24818,7 @@
         <v>3</v>
       </c>
       <c r="I72" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" s="1">
         <v>78</v>
@@ -24830,7 +24830,7 @@
         <v>6</v>
       </c>
       <c r="M72" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N72" s="1">
         <v>91</v>
@@ -24926,7 +24926,7 @@
         <v>3</v>
       </c>
       <c r="AS72" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -25058,7 +25058,7 @@
         <v>12</v>
       </c>
       <c r="CK72" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CL72" s="1">
         <v>0</v>
@@ -25094,7 +25094,7 @@
         <v>55</v>
       </c>
       <c r="CW72" s="1">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25665,10 +25665,10 @@
         <v>47</v>
       </c>
       <c r="CJ74" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="CK74" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,10 +25701,10 @@
         <v>163</v>
       </c>
       <c r="CV74" s="1">
-        <v>1841</v>
+        <v>1835</v>
       </c>
       <c r="CW74" s="1">
-        <v>4403</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25835,7 +25835,7 @@
         <v>14</v>
       </c>
       <c r="AQ75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR75" s="2">
         <v>3</v>
@@ -25967,7 +25967,7 @@
         <v>97</v>
       </c>
       <c r="CI75" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ75" s="2">
         <v>8</v>
@@ -26003,7 +26003,7 @@
         <v>221</v>
       </c>
       <c r="CU75" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CV75" s="1">
         <v>15</v>
@@ -26331,7 +26331,7 @@
         <v>-6</v>
       </c>
       <c r="E77" s="2">
-        <v>-4292</v>
+        <v>-4395</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26619,7 +26619,7 @@
         <v>10242</v>
       </c>
       <c r="CW77" s="1">
-        <v>16071</v>
+        <v>15968</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26744,7 +26744,7 @@
         <v>13</v>
       </c>
       <c r="AO78" s="2">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AP78" s="1">
         <v>0</v>
@@ -26924,7 +26924,7 @@
         <v>72</v>
       </c>
       <c r="CW78" s="1">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -27064,16 +27064,16 @@
         <v>2</v>
       </c>
       <c r="AT79" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU79" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW79" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX79" s="1">
         <v>0</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90617</v>
+        <v>90618</v>
       </c>
       <c r="CU79" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CV79" s="1">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="CW79" s="1">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -28299,7 +28299,7 @@
         <v>17</v>
       </c>
       <c r="AY83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ83" s="2">
         <v>1</v>
@@ -28443,7 +28443,7 @@
         <v>423791</v>
       </c>
       <c r="CU83" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="CV83" s="1">
         <v>886</v>
@@ -28885,7 +28885,7 @@
         <v>25</v>
       </c>
       <c r="AQ85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR85" s="2">
         <v>2</v>
@@ -29053,7 +29053,7 @@
         <v>407</v>
       </c>
       <c r="CU85" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV85" s="1">
         <v>29</v>
@@ -29193,7 +29193,7 @@
         <v>0</v>
       </c>
       <c r="AR86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS86" s="2">
         <v>3</v>
@@ -29325,7 +29325,7 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK86" s="2">
         <v>16</v>
@@ -29361,7 +29361,7 @@
         <v>2</v>
       </c>
       <c r="CV86" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CW86" s="1">
         <v>74</v>
@@ -31313,7 +31313,7 @@
         <v>81</v>
       </c>
       <c r="AM93" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN93" s="2">
         <v>4</v>
@@ -31493,7 +31493,7 @@
         <v>1178</v>
       </c>
       <c r="CU93" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV93" s="1">
         <v>26</v>
@@ -33950,7 +33950,7 @@
         <v>17506</v>
       </c>
       <c r="C102" s="2">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2">
         <v>372</v>
@@ -33989,7 +33989,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q102" s="2">
         <v>534</v>
@@ -34076,7 +34076,7 @@
         <v>2</v>
       </c>
       <c r="AS102" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT102" s="1">
         <v>60</v>
@@ -34208,7 +34208,7 @@
         <v>54</v>
       </c>
       <c r="CK102" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="CL102" s="1">
         <v>9</v>
@@ -34238,13 +34238,13 @@
         <v>43024</v>
       </c>
       <c r="CU102" s="1">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="CV102" s="1">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="CW102" s="1">
-        <v>1813</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34952,7 +34952,7 @@
         <v>1</v>
       </c>
       <c r="AF105" s="2">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="AG105" s="2">
         <v>375</v>
@@ -34988,7 +34988,7 @@
         <v>0</v>
       </c>
       <c r="AR105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS105" s="2">
         <v>4</v>
@@ -35156,7 +35156,7 @@
         <v>21</v>
       </c>
       <c r="CV105" s="1">
-        <v>433</v>
+        <v>207</v>
       </c>
       <c r="CW105" s="1">
         <v>506</v>
@@ -36390,7 +36390,7 @@
         <v>2498</v>
       </c>
       <c r="C110" s="2">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D110" s="2">
         <v>49</v>
@@ -36678,7 +36678,7 @@
         <v>13336</v>
       </c>
       <c r="CU110" s="1">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="CV110" s="1">
         <v>427</v>
@@ -36707,7 +36707,7 @@
         <v>71</v>
       </c>
       <c r="G111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2">
         <v>2</v>
@@ -36983,7 +36983,7 @@
         <v>775</v>
       </c>
       <c r="CU111" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CV111" s="1">
         <v>39</v>
@@ -37030,7 +37030,7 @@
         <v>24</v>
       </c>
       <c r="M112" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="N112" s="1">
         <v>5612</v>
@@ -37294,7 +37294,7 @@
         <v>254</v>
       </c>
       <c r="CW112" s="1">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37616,7 +37616,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="1">
         <v>64</v>
@@ -37904,7 +37904,7 @@
         <v>4</v>
       </c>
       <c r="CW114" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38349,16 +38349,16 @@
         <v>2</v>
       </c>
       <c r="AT116" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AU116" s="2">
         <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW116" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX116" s="1">
         <v>3</v>
@@ -38403,7 +38403,7 @@
         <v>0</v>
       </c>
       <c r="BL116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM116" s="2">
         <v>1</v>
@@ -38505,7 +38505,7 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21741</v>
+        <v>21742</v>
       </c>
       <c r="CU116" s="1">
         <v>84</v>
@@ -38514,7 +38514,7 @@
         <v>401</v>
       </c>
       <c r="CW116" s="1">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -39452,7 +39452,7 @@
         <v>48</v>
       </c>
       <c r="G120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="2">
         <v>2</v>
@@ -39728,7 +39728,7 @@
         <v>384</v>
       </c>
       <c r="CU120" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV120" s="1">
         <v>47</v>
@@ -44054,10 +44054,10 @@
         <v>0</v>
       </c>
       <c r="P135" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q135" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="R135" s="1">
         <v>0</v>
@@ -44306,10 +44306,10 @@
         <v>150</v>
       </c>
       <c r="CV135" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="CW135" s="1">
-        <v>2742</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -46174,7 +46174,7 @@
         <v>445</v>
       </c>
       <c r="K142" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L142" s="2">
         <v>34</v>
@@ -46438,7 +46438,7 @@
         <v>1653</v>
       </c>
       <c r="CU142" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CV142" s="1">
         <v>59</v>
@@ -46766,7 +46766,7 @@
         <v>5</v>
       </c>
       <c r="E144" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F144" s="1">
         <v>15</v>
@@ -46883,7 +46883,7 @@
         <v>0</v>
       </c>
       <c r="AR144" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS144" s="2">
         <v>2</v>
@@ -47027,7 +47027,7 @@
         <v>0</v>
       </c>
       <c r="CN144" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO144" s="2">
         <v>4</v>
@@ -47051,10 +47051,10 @@
         <v>5</v>
       </c>
       <c r="CV144" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW144" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -50546,7 +50546,7 @@
         <v>1</v>
       </c>
       <c r="AS156" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT156" s="1">
         <v>2</v>
@@ -50678,7 +50678,7 @@
         <v>53</v>
       </c>
       <c r="CK156" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="CL156" s="1">
         <v>13</v>
@@ -50714,7 +50714,7 @@
         <v>1051</v>
       </c>
       <c r="CW156" s="1">
-        <v>2533</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -51945,7 +51945,7 @@
         <v>2083</v>
       </c>
       <c r="C161" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D161" s="2">
         <v>51</v>
@@ -52071,7 +52071,7 @@
         <v>1</v>
       </c>
       <c r="AS161" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT161" s="1">
         <v>6</v>
@@ -52203,7 +52203,7 @@
         <v>25</v>
       </c>
       <c r="CK161" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CL161" s="1">
         <v>14</v>
@@ -52233,13 +52233,13 @@
         <v>22379</v>
       </c>
       <c r="CU161" s="1">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="CV161" s="1">
         <v>743</v>
       </c>
       <c r="CW161" s="1">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52669,7 +52669,7 @@
         <v>1</v>
       </c>
       <c r="AO163" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP163" s="1">
         <v>128</v>
@@ -52813,7 +52813,7 @@
         <v>9</v>
       </c>
       <c r="CK163" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CL163" s="1">
         <v>49</v>
@@ -52849,7 +52849,7 @@
         <v>22</v>
       </c>
       <c r="CW163" s="1">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -53665,7 +53665,7 @@
         <v>0</v>
       </c>
       <c r="BP166" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BQ166" s="2">
         <v>186</v>
@@ -53761,7 +53761,7 @@
         <v>6</v>
       </c>
       <c r="CV166" s="1">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="CW166" s="1">
         <v>506</v>
@@ -54110,7 +54110,7 @@
         <v>48</v>
       </c>
       <c r="M168" s="2">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="N168" s="1">
         <v>419</v>
@@ -54374,7 +54374,7 @@
         <v>156</v>
       </c>
       <c r="CW168" s="1">
-        <v>602</v>
+        <v>554</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -55193,7 +55193,7 @@
         <v>2</v>
       </c>
       <c r="BQ171" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR171" s="1">
         <v>17</v>
@@ -55289,7 +55289,7 @@
         <v>45</v>
       </c>
       <c r="CW171" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -55949,7 +55949,7 @@
         <v>9</v>
       </c>
       <c r="P174" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q174" s="2">
         <v>17</v>
@@ -56201,7 +56201,7 @@
         <v>15</v>
       </c>
       <c r="CV174" s="1">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="CW174" s="1">
         <v>37</v>
@@ -57848,7 +57848,7 @@
         <v>973</v>
       </c>
       <c r="AM180" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN180" s="2">
         <v>8</v>
@@ -58028,7 +58028,7 @@
         <v>51139</v>
       </c>
       <c r="CU180" s="1">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="CV180" s="1">
         <v>1227</v>
@@ -59385,7 +59385,7 @@
         <v>29</v>
       </c>
       <c r="AQ185" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR185" s="2">
         <v>3</v>
@@ -59517,7 +59517,7 @@
         <v>5</v>
       </c>
       <c r="CI185" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ185" s="2">
         <v>1</v>
@@ -59553,7 +59553,7 @@
         <v>156</v>
       </c>
       <c r="CU185" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CV185" s="1">
         <v>9</v>
@@ -61652,7 +61652,7 @@
         <v>407</v>
       </c>
       <c r="CI192" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="CJ192" s="2">
         <v>2</v>
@@ -61688,7 +61688,7 @@
         <v>611</v>
       </c>
       <c r="CU192" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CV192" s="1">
         <v>7</v>
@@ -62118,7 +62118,7 @@
         <v>309</v>
       </c>
       <c r="AM194" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN194" s="2">
         <v>2</v>
@@ -62136,7 +62136,7 @@
         <v>2</v>
       </c>
       <c r="AS194" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT194" s="1">
         <v>2</v>
@@ -62262,13 +62262,13 @@
         <v>449</v>
       </c>
       <c r="CI194" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CJ194" s="2">
         <v>7</v>
       </c>
       <c r="CK194" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CL194" s="1">
         <v>27</v>
@@ -62298,13 +62298,13 @@
         <v>32848</v>
       </c>
       <c r="CU194" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="CV194" s="1">
         <v>572</v>
       </c>
       <c r="CW194" s="1">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -67225,7 +67225,7 @@
         <v>28</v>
       </c>
       <c r="M211" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N211" s="1">
         <v>820</v>
@@ -67489,7 +67489,7 @@
         <v>488</v>
       </c>
       <c r="CW211" s="1">
-        <v>692</v>
+        <v>685</v>
       </c>
     </row>
     <row r="212" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -12319,13 +12319,13 @@
         <v>1393</v>
       </c>
       <c r="K31" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L31" s="2">
         <v>25</v>
       </c>
       <c r="M31" s="2">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="N31" s="1">
         <v>1982</v>
@@ -12583,13 +12583,13 @@
         <v>6004</v>
       </c>
       <c r="CU31" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="CV31" s="1">
         <v>274</v>
       </c>
       <c r="CW31" s="1">
-        <v>433</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -13324,7 +13324,7 @@
         <v>2</v>
       </c>
       <c r="AO34" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP34" s="1">
         <v>49</v>
@@ -13468,7 +13468,7 @@
         <v>4</v>
       </c>
       <c r="CK34" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CL34" s="1">
         <v>26</v>
@@ -13504,7 +13504,7 @@
         <v>65</v>
       </c>
       <c r="CW34" s="1">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -15040,7 +15040,7 @@
         <v>8771</v>
       </c>
       <c r="C40" s="2">
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2">
         <v>85</v>
@@ -15130,7 +15130,7 @@
         <v>413</v>
       </c>
       <c r="AG40" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15328,13 +15328,13 @@
         <v>53430</v>
       </c>
       <c r="CU40" s="1">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="CV40" s="1">
         <v>827</v>
       </c>
       <c r="CW40" s="1">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -22827,7 +22827,7 @@
         <v>0</v>
       </c>
       <c r="BE65" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF65" s="1">
         <v>0</v>
@@ -22959,7 +22959,7 @@
         <v>1769</v>
       </c>
       <c r="CW65" s="1">
-        <v>3541</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22976,7 +22976,7 @@
         <v>9</v>
       </c>
       <c r="E66" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F66" s="1">
         <v>12</v>
@@ -23000,7 +23000,7 @@
         <v>61</v>
       </c>
       <c r="M66" s="2">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="N66" s="1">
         <v>0</v>
@@ -23264,7 +23264,7 @@
         <v>70</v>
       </c>
       <c r="CW66" s="1">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23610,7 +23610,7 @@
         <v>3</v>
       </c>
       <c r="M68" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N68" s="1">
         <v>1092</v>
@@ -23874,7 +23874,7 @@
         <v>8</v>
       </c>
       <c r="CW68" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -25111,7 +25111,7 @@
         <v>2</v>
       </c>
       <c r="E73" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73" s="1">
         <v>45</v>
@@ -25219,7 +25219,7 @@
         <v>2</v>
       </c>
       <c r="AO73" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP73" s="1">
         <v>13</v>
@@ -25363,7 +25363,7 @@
         <v>36</v>
       </c>
       <c r="CK73" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="CL73" s="1">
         <v>6</v>
@@ -25399,7 +25399,7 @@
         <v>41</v>
       </c>
       <c r="CW73" s="1">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25500,7 +25500,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25704,7 +25704,7 @@
         <v>1835</v>
       </c>
       <c r="CW74" s="1">
-        <v>4394</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26355,7 +26355,7 @@
         <v>181</v>
       </c>
       <c r="M77" s="2">
-        <v>342</v>
+        <v>280</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26403,7 +26403,7 @@
         <v>4</v>
       </c>
       <c r="AC77" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD77" s="1">
         <v>1182</v>
@@ -26469,7 +26469,7 @@
         <v>3</v>
       </c>
       <c r="AY77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ77" s="2">
         <v>1</v>
@@ -26583,7 +26583,7 @@
         <v>365</v>
       </c>
       <c r="CK77" s="2">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26613,13 +26613,13 @@
         <v>390881</v>
       </c>
       <c r="CU77" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CV77" s="1">
         <v>10242</v>
       </c>
       <c r="CW77" s="1">
-        <v>15968</v>
+        <v>15888</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26941,7 +26941,7 @@
         <v>43</v>
       </c>
       <c r="E79" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -27229,7 +27229,7 @@
         <v>656</v>
       </c>
       <c r="CW79" s="1">
-        <v>1861</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -34082,7 +34082,7 @@
         <v>60</v>
       </c>
       <c r="AU102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV102" s="2">
         <v>2</v>
@@ -34238,7 +34238,7 @@
         <v>43024</v>
       </c>
       <c r="CU102" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="CV102" s="1">
         <v>776</v>
@@ -37335,7 +37335,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="2">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="N113" s="1">
         <v>8023</v>
@@ -37599,7 +37599,7 @@
         <v>413</v>
       </c>
       <c r="CW113" s="1">
-        <v>9884</v>
+        <v>9810</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -41689,7 +41689,7 @@
         <v>19</v>
       </c>
       <c r="AO127" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AP127" s="1">
         <v>0</v>
@@ -41833,7 +41833,7 @@
         <v>17</v>
       </c>
       <c r="CK127" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CL127" s="1">
         <v>1</v>
@@ -41869,7 +41869,7 @@
         <v>66</v>
       </c>
       <c r="CW127" s="1">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -45056,7 +45056,7 @@
         <v>2</v>
       </c>
       <c r="AS138" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT138" s="1">
         <v>0</v>
@@ -45188,7 +45188,7 @@
         <v>5</v>
       </c>
       <c r="CK138" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CL138" s="1">
         <v>4</v>
@@ -45224,7 +45224,7 @@
         <v>118</v>
       </c>
       <c r="CW138" s="1">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -46276,7 +46276,7 @@
         <v>0</v>
       </c>
       <c r="AS142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT142" s="1">
         <v>14</v>
@@ -46408,7 +46408,7 @@
         <v>3</v>
       </c>
       <c r="CK142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL142" s="1">
         <v>48</v>
@@ -46444,7 +46444,7 @@
         <v>59</v>
       </c>
       <c r="CW142" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -48405,7 +48405,7 @@
         <v>81</v>
       </c>
       <c r="AQ149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR149" s="2">
         <v>3</v>
@@ -48537,7 +48537,7 @@
         <v>163</v>
       </c>
       <c r="CI149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ149" s="2">
         <v>6</v>
@@ -48573,7 +48573,7 @@
         <v>904</v>
       </c>
       <c r="CU149" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV149" s="1">
         <v>24</v>
@@ -54080,7 +54080,7 @@
         <v>175</v>
       </c>
       <c r="C168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" s="2">
         <v>2</v>
@@ -54368,7 +54368,7 @@
         <v>5948</v>
       </c>
       <c r="CU168" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CV168" s="1">
         <v>156</v>
@@ -54774,13 +54774,13 @@
         <v>3602</v>
       </c>
       <c r="AE170" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AF170" s="2">
         <v>126</v>
       </c>
       <c r="AG170" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54978,13 +54978,13 @@
         <v>19518</v>
       </c>
       <c r="CU170" s="1">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="CV170" s="1">
         <v>501</v>
       </c>
       <c r="CW170" s="1">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -66280,7 +66280,7 @@
         <v>249</v>
       </c>
       <c r="C208" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D208" s="2">
         <v>7</v>
@@ -66568,7 +66568,7 @@
         <v>267</v>
       </c>
       <c r="CU208" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV208" s="1">
         <v>7</v>
@@ -70463,7 +70463,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="E102" t="s">
         <v>715</v>
@@ -71126,7 +71126,7 @@
         <v>646</v>
       </c>
       <c r="D135">
-        <v>10251</v>
+        <v>10250</v>
       </c>
       <c r="E135" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="BE7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF7" s="1">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="CW7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:101">
@@ -7116,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
         <v>36</v>
@@ -7404,7 +7404,7 @@
         <v>143</v>
       </c>
       <c r="CW14" s="1">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -13240,7 +13240,7 @@
         <v>24</v>
       </c>
       <c r="M34" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N34" s="1">
         <v>1429</v>
@@ -13504,7 +13504,7 @@
         <v>65</v>
       </c>
       <c r="CW34" s="1">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -15046,7 +15046,7 @@
         <v>85</v>
       </c>
       <c r="E40" s="2">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15298,7 +15298,7 @@
         <v>36</v>
       </c>
       <c r="CK40" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="CL40" s="1">
         <v>13</v>
@@ -15334,7 +15334,7 @@
         <v>827</v>
       </c>
       <c r="CW40" s="1">
-        <v>2199</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16290,7 +16290,7 @@
         <v>72</v>
       </c>
       <c r="M44" s="2">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="N44" s="1">
         <v>1597</v>
@@ -16554,7 +16554,7 @@
         <v>1972</v>
       </c>
       <c r="CW44" s="1">
-        <v>2471</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -23595,7 +23595,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="2">
         <v>2</v>
@@ -23871,7 +23871,7 @@
         <v>5</v>
       </c>
       <c r="CV68" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW68" s="1">
         <v>51</v>
@@ -24815,7 +24815,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" s="2">
         <v>4</v>
@@ -24827,7 +24827,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2">
         <v>11</v>
@@ -24923,7 +24923,7 @@
         <v>1</v>
       </c>
       <c r="AR72" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS72" s="2">
         <v>5</v>
@@ -25055,7 +25055,7 @@
         <v>4</v>
       </c>
       <c r="CJ72" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CK72" s="2">
         <v>15</v>
@@ -25091,7 +25091,7 @@
         <v>10</v>
       </c>
       <c r="CV72" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="CW72" s="1">
         <v>143</v>
@@ -25581,7 +25581,7 @@
         <v>0</v>
       </c>
       <c r="BH74" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI74" s="2">
         <v>3</v>
@@ -25701,7 +25701,7 @@
         <v>163</v>
       </c>
       <c r="CV74" s="1">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="CW74" s="1">
         <v>4395</v>
@@ -25838,7 +25838,7 @@
         <v>0</v>
       </c>
       <c r="AR75" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS75" s="2">
         <v>4</v>
@@ -25982,7 +25982,7 @@
         <v>0</v>
       </c>
       <c r="CN75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO75" s="2">
         <v>2</v>
@@ -26006,7 +26006,7 @@
         <v>3</v>
       </c>
       <c r="CV75" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW75" s="1">
         <v>18</v>
@@ -26352,7 +26352,7 @@
         <v>44</v>
       </c>
       <c r="L77" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M77" s="2">
         <v>280</v>
@@ -26616,7 +26616,7 @@
         <v>198</v>
       </c>
       <c r="CV77" s="1">
-        <v>10242</v>
+        <v>10243</v>
       </c>
       <c r="CW77" s="1">
         <v>15888</v>
@@ -26885,7 +26885,7 @@
         <v>4</v>
       </c>
       <c r="CJ78" s="2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="CK78" s="2">
         <v>73</v>
@@ -26921,7 +26921,7 @@
         <v>5</v>
       </c>
       <c r="CV78" s="1">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="CW78" s="1">
         <v>111</v>
@@ -27575,7 +27575,7 @@
         <v>60</v>
       </c>
       <c r="M81" s="2">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="N81" s="1">
         <v>3606</v>
@@ -27668,7 +27668,7 @@
         <v>0</v>
       </c>
       <c r="AR81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS81" s="2">
         <v>3</v>
@@ -27800,7 +27800,7 @@
         <v>1</v>
       </c>
       <c r="CJ81" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CK81" s="2">
         <v>9</v>
@@ -27836,10 +27836,10 @@
         <v>37</v>
       </c>
       <c r="CV81" s="1">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="CW81" s="1">
-        <v>380</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27865,7 +27865,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" s="2">
         <v>5</v>
@@ -27973,7 +27973,7 @@
         <v>1</v>
       </c>
       <c r="AR82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS82" s="2">
         <v>5</v>
@@ -28105,7 +28105,7 @@
         <v>0</v>
       </c>
       <c r="CJ82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK82" s="2">
         <v>1</v>
@@ -28141,7 +28141,7 @@
         <v>3</v>
       </c>
       <c r="CV82" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW82" s="1">
         <v>18</v>
@@ -28185,7 +28185,7 @@
         <v>186</v>
       </c>
       <c r="M83" s="2">
-        <v>480</v>
+        <v>379</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28449,7 +28449,7 @@
         <v>886</v>
       </c>
       <c r="CW83" s="1">
-        <v>5455</v>
+        <v>5354</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29325,7 +29325,7 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK86" s="2">
         <v>16</v>
@@ -29361,7 +29361,7 @@
         <v>2</v>
       </c>
       <c r="CV86" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW86" s="1">
         <v>74</v>
@@ -29489,7 +29489,7 @@
         <v>-2</v>
       </c>
       <c r="AO87" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP87" s="1">
         <v>24</v>
@@ -29633,7 +29633,7 @@
         <v>44</v>
       </c>
       <c r="CK87" s="2">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29669,7 +29669,7 @@
         <v>46</v>
       </c>
       <c r="CW87" s="1">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -30622,7 +30622,7 @@
         <v>54</v>
       </c>
       <c r="L91" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M91" s="2">
         <v>380</v>
@@ -30886,7 +30886,7 @@
         <v>76</v>
       </c>
       <c r="CV91" s="1">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="CW91" s="1">
         <v>868</v>
@@ -35284,7 +35284,7 @@
         <v>9</v>
       </c>
       <c r="AO106" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AP106" s="1">
         <v>8</v>
@@ -35428,7 +35428,7 @@
         <v>181</v>
       </c>
       <c r="CK106" s="2">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="CL106" s="1">
         <v>0</v>
@@ -35464,7 +35464,7 @@
         <v>1155</v>
       </c>
       <c r="CW106" s="1">
-        <v>2570</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36806,7 +36806,7 @@
         <v>0</v>
       </c>
       <c r="AN111" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO111" s="2">
         <v>13</v>
@@ -36986,7 +36986,7 @@
         <v>8</v>
       </c>
       <c r="CV111" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CW111" s="1">
         <v>72</v>
@@ -37625,7 +37625,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I114" s="2">
         <v>5</v>
@@ -37901,7 +37901,7 @@
         <v>2</v>
       </c>
       <c r="CV114" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW114" s="1">
         <v>6</v>
@@ -39085,7 +39085,7 @@
         <v>3</v>
       </c>
       <c r="CJ118" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CK118" s="2">
         <v>27</v>
@@ -39121,7 +39121,7 @@
         <v>7</v>
       </c>
       <c r="CV118" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="CW118" s="1">
         <v>36</v>
@@ -40478,7 +40478,7 @@
         <v>1</v>
       </c>
       <c r="AR123" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS123" s="2">
         <v>6</v>
@@ -40622,7 +40622,7 @@
         <v>1</v>
       </c>
       <c r="CN123" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CO123" s="2">
         <v>6</v>
@@ -40646,7 +40646,7 @@
         <v>3</v>
       </c>
       <c r="CV123" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW123" s="1">
         <v>30</v>
@@ -43833,7 +43833,7 @@
         <v>0</v>
       </c>
       <c r="AR134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS134" s="2">
         <v>2</v>
@@ -43965,7 +43965,7 @@
         <v>0</v>
       </c>
       <c r="CJ134" s="2">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="CK134" s="2">
         <v>81</v>
@@ -44001,7 +44001,7 @@
         <v>8</v>
       </c>
       <c r="CV134" s="1">
-        <v>2552</v>
+        <v>2535</v>
       </c>
       <c r="CW134" s="1">
         <v>5809</v>
@@ -46288,7 +46288,7 @@
         <v>1</v>
       </c>
       <c r="AW142" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX142" s="1">
         <v>4</v>
@@ -46444,7 +46444,7 @@
         <v>59</v>
       </c>
       <c r="CW142" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46599,7 +46599,7 @@
         <v>6</v>
       </c>
       <c r="AY143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ143" s="2">
         <v>2</v>
@@ -46743,7 +46743,7 @@
         <v>298</v>
       </c>
       <c r="CU143" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CV143" s="1">
         <v>13</v>
@@ -50450,7 +50450,7 @@
         <v>56</v>
       </c>
       <c r="M156" s="2">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="N156" s="1">
         <v>61027</v>
@@ -50714,7 +50714,7 @@
         <v>1051</v>
       </c>
       <c r="CW156" s="1">
-        <v>2522</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -53476,7 +53476,7 @@
         <v>10</v>
       </c>
       <c r="E166" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1">
         <v>8</v>
@@ -53764,7 +53764,7 @@
         <v>133</v>
       </c>
       <c r="CW166" s="1">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54640,7 +54640,7 @@
         <v>8</v>
       </c>
       <c r="CJ169" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CK169" s="2">
         <v>36</v>
@@ -54676,7 +54676,7 @@
         <v>13</v>
       </c>
       <c r="CV169" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CW169" s="1">
         <v>60</v>
@@ -54693,7 +54693,7 @@
         <v>0</v>
       </c>
       <c r="D170" s="2">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E170" s="2">
         <v>154</v>
@@ -54981,7 +54981,7 @@
         <v>84</v>
       </c>
       <c r="CV170" s="1">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="CW170" s="1">
         <v>1254</v>
@@ -62345,7 +62345,7 @@
         <v>6</v>
       </c>
       <c r="M195" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N195" s="1">
         <v>976</v>
@@ -62609,7 +62609,7 @@
         <v>3371</v>
       </c>
       <c r="CW195" s="1">
-        <v>5335</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -62647,7 +62647,7 @@
         <v>5</v>
       </c>
       <c r="L196" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M196" s="2">
         <v>30</v>
@@ -62911,7 +62911,7 @@
         <v>9</v>
       </c>
       <c r="CV196" s="1">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="CW196" s="1">
         <v>211</v>
@@ -64151,7 +64151,7 @@
         <v>-1</v>
       </c>
       <c r="E201" s="2">
-        <v>62</v>
+        <v>-2</v>
       </c>
       <c r="F201" s="1">
         <v>0</v>
@@ -64439,7 +64439,7 @@
         <v>2006</v>
       </c>
       <c r="CW201" s="1">
-        <v>3226</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -65820,7 +65820,7 @@
         <v>0</v>
       </c>
       <c r="BA206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB206" s="1">
         <v>8</v>
@@ -65964,7 +65964,7 @@
         <v>23</v>
       </c>
       <c r="CW206" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66233,7 +66233,7 @@
         <v>35</v>
       </c>
       <c r="CK207" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CL207" s="1">
         <v>13</v>
@@ -66269,7 +66269,7 @@
         <v>354</v>
       </c>
       <c r="CW207" s="1">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -69534,7 +69534,7 @@
         <v>575</v>
       </c>
       <c r="D56">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E56" t="s">
         <v>715</v>
@@ -70077,7 +70077,7 @@
         <v>546</v>
       </c>
       <c r="D83">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E83" t="s">
         <v>715</v>
@@ -70743,7 +70743,7 @@
         <v>630</v>
       </c>
       <c r="D116">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E116" t="s">
         <v>715</v>
@@ -72355,7 +72355,7 @@
         <v>698</v>
       </c>
       <c r="D196">
-        <v>10256</v>
+        <v>10257</v>
       </c>
       <c r="E196" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3752,16 +3752,16 @@
         <v>102</v>
       </c>
       <c r="B3" s="1">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46679</v>
+        <v>46682</v>
       </c>
       <c r="CU3" s="1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="CV3" s="1">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="CW3" s="1">
-        <v>2056</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4318,7 +4318,7 @@
         <v>58</v>
       </c>
       <c r="CK4" s="2">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4354,7 +4354,7 @@
         <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1187</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -7215,16 +7215,16 @@
         <v>0</v>
       </c>
       <c r="AL14" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM14" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN14" s="2">
+        <v>12</v>
+      </c>
+      <c r="AO14" s="2">
         <v>11</v>
-      </c>
-      <c r="AO14" s="2">
-        <v>10</v>
       </c>
       <c r="AP14" s="1">
         <v>76</v>
@@ -7299,16 +7299,16 @@
         <v>0</v>
       </c>
       <c r="BN14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR14" s="1">
         <v>7</v>
@@ -7359,16 +7359,16 @@
         <v>0</v>
       </c>
       <c r="CH14" s="1">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="CI14" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="CJ14" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="CK14" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="CL14" s="1">
         <v>29</v>
@@ -7395,16 +7395,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3183</v>
+        <v>3187</v>
       </c>
       <c r="CU14" s="1">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="CV14" s="1">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="CW14" s="1">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8979,7 +8979,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q20" s="2">
         <v>607</v>
@@ -9231,7 +9231,7 @@
         <v>50</v>
       </c>
       <c r="CV20" s="1">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="CW20" s="1">
         <v>936</v>
@@ -9969,19 +9969,19 @@
         <v>0</v>
       </c>
       <c r="AO23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AQ23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -10116,13 +10116,13 @@
         <v>5</v>
       </c>
       <c r="CL23" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CM23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO23" s="2">
         <v>3</v>
@@ -10140,13 +10140,13 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="CU23" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV23" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CW23" s="1">
         <v>44</v>
@@ -12406,7 +12406,7 @@
         <v>6</v>
       </c>
       <c r="AN31" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO31" s="2">
         <v>23</v>
@@ -12550,7 +12550,7 @@
         <v>11</v>
       </c>
       <c r="CJ31" s="2">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="CK31" s="2">
         <v>182</v>
@@ -12586,7 +12586,7 @@
         <v>30</v>
       </c>
       <c r="CV31" s="1">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="CW31" s="1">
         <v>418</v>
@@ -12714,7 +12714,7 @@
         <v>4</v>
       </c>
       <c r="AO32" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP32" s="1">
         <v>45</v>
@@ -12858,7 +12858,7 @@
         <v>9</v>
       </c>
       <c r="CK32" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12894,7 +12894,7 @@
         <v>223</v>
       </c>
       <c r="CW32" s="1">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13321,7 +13321,7 @@
         <v>0</v>
       </c>
       <c r="AN34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO34" s="2">
         <v>5</v>
@@ -13465,7 +13465,7 @@
         <v>2</v>
       </c>
       <c r="CJ34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK34" s="2">
         <v>11</v>
@@ -13501,7 +13501,7 @@
         <v>13</v>
       </c>
       <c r="CV34" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="CW34" s="1">
         <v>129</v>
@@ -14457,7 +14457,7 @@
         <v>10</v>
       </c>
       <c r="L38" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M38" s="2">
         <v>30</v>
@@ -14721,7 +14721,7 @@
         <v>15</v>
       </c>
       <c r="CV38" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="CW38" s="1">
         <v>115</v>
@@ -16260,7 +16260,7 @@
         <v>235</v>
       </c>
       <c r="C44" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D44" s="2">
         <v>11</v>
@@ -16548,7 +16548,7 @@
         <v>50655</v>
       </c>
       <c r="CU44" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="CV44" s="1">
         <v>1972</v>
@@ -18392,136 +18392,136 @@
         <v>150</v>
       </c>
       <c r="B51" s="1">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C51" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E51" s="2">
+        <v>32</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="2">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="2">
+        <v>0</v>
+      </c>
+      <c r="X51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="1">
+        <v>190</v>
+      </c>
+      <c r="AM51" s="2">
+        <v>158</v>
+      </c>
+      <c r="AN51" s="2">
+        <v>158</v>
+      </c>
+      <c r="AO51" s="2">
+        <v>159</v>
+      </c>
+      <c r="AP51" s="1">
         <v>31</v>
       </c>
-      <c r="F51" s="1">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2">
-        <v>0</v>
-      </c>
-      <c r="V51" s="1">
-        <v>0</v>
-      </c>
-      <c r="W51" s="2">
-        <v>0</v>
-      </c>
-      <c r="X51" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL51" s="1">
-        <v>32</v>
-      </c>
-      <c r="AM51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AP51" s="1">
-        <v>0</v>
-      </c>
       <c r="AQ51" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AR51" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AS51" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT51" s="1">
         <v>0</v>
@@ -18644,16 +18644,16 @@
         <v>0</v>
       </c>
       <c r="CH51" s="1">
-        <v>1082</v>
+        <v>2813</v>
       </c>
       <c r="CI51" s="2">
-        <v>26</v>
+        <v>1757</v>
       </c>
       <c r="CJ51" s="2">
-        <v>91</v>
+        <v>1822</v>
       </c>
       <c r="CK51" s="2">
-        <v>199</v>
+        <v>1930</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18680,16 +18680,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>1820</v>
+        <v>3741</v>
       </c>
       <c r="CU51" s="1">
-        <v>33</v>
+        <v>1954</v>
       </c>
       <c r="CV51" s="1">
-        <v>108</v>
+        <v>2025</v>
       </c>
       <c r="CW51" s="1">
-        <v>231</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20234,16 +20234,16 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -20510,16 +20510,16 @@
         <v>0</v>
       </c>
       <c r="CT57" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CU57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW57" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -21018,7 +21018,7 @@
         <v>0</v>
       </c>
       <c r="BL59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM59" s="2">
         <v>1</v>
@@ -21126,7 +21126,7 @@
         <v>1</v>
       </c>
       <c r="CV59" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="CW59" s="1">
         <v>53</v>
@@ -21442,16 +21442,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6499</v>
+        <v>6491</v>
       </c>
       <c r="C61" s="2">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="D61" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E61" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21475,7 +21475,7 @@
         <v>30</v>
       </c>
       <c r="M61" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N61" s="1">
         <v>43316</v>
@@ -21559,7 +21559,7 @@
         <v>2</v>
       </c>
       <c r="AO61" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP61" s="1">
         <v>37</v>
@@ -21703,7 +21703,7 @@
         <v>46</v>
       </c>
       <c r="CK61" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65916</v>
+        <v>65908</v>
       </c>
       <c r="CU61" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CV61" s="1">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="CW61" s="1">
-        <v>951</v>
+        <v>914</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22052,16 +22052,16 @@
         <v>162</v>
       </c>
       <c r="B63" s="1">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C63" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E63" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22340,16 +22340,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2871</v>
+        <v>2880</v>
       </c>
       <c r="CU63" s="1">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="CV63" s="1">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="CW63" s="1">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22441,16 +22441,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="AE64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF64" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG64" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8013</v>
+        <v>8014</v>
       </c>
       <c r="CU64" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CV64" s="1">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="CW64" s="1">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22695,7 +22695,7 @@
         <v>51</v>
       </c>
       <c r="M65" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="N65" s="1">
         <v>58956</v>
@@ -22707,7 +22707,7 @@
         <v>1631</v>
       </c>
       <c r="Q65" s="2">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -22791,7 +22791,7 @@
         <v>0</v>
       </c>
       <c r="AS65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT65" s="1">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>34</v>
       </c>
       <c r="CK65" s="2">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22935,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="CO65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP65" s="1">
         <v>0</v>
@@ -22959,7 +22959,7 @@
         <v>1769</v>
       </c>
       <c r="CW65" s="1">
-        <v>3540</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23697,16 +23697,16 @@
         <v>0</v>
       </c>
       <c r="AP68" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AQ68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS68" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT68" s="1">
         <v>0</v>
@@ -23829,16 +23829,16 @@
         <v>0</v>
       </c>
       <c r="CH68" s="1">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="CI68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ68" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CK68" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CL68" s="1">
         <v>27</v>
@@ -23865,16 +23865,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="CU68" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CV68" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CW68" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16172</v>
+        <v>16194</v>
       </c>
       <c r="CI74" s="2">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="CJ74" s="2">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="CK74" s="2">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171618</v>
+        <v>171640</v>
       </c>
       <c r="CU74" s="1">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="CV74" s="1">
-        <v>1832</v>
+        <v>1854</v>
       </c>
       <c r="CW74" s="1">
-        <v>4395</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26026,7 +26026,7 @@
         <v>37</v>
       </c>
       <c r="E76" s="2">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -26050,19 +26050,19 @@
         <v>202</v>
       </c>
       <c r="M76" s="2">
-        <v>392</v>
+        <v>326</v>
       </c>
       <c r="N76" s="1">
-        <v>117544</v>
+        <v>117545</v>
       </c>
       <c r="O76" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P76" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="Q76" s="2">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>151016</v>
+        <v>151017</v>
       </c>
       <c r="CU76" s="1">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CV76" s="1">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="CW76" s="1">
-        <v>3743</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26355,7 +26355,7 @@
         <v>182</v>
       </c>
       <c r="M77" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26430,16 +26430,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="AM77" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AN77" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AO77" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7298</v>
+        <v>7303</v>
       </c>
       <c r="CI77" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="CJ77" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="CK77" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390881</v>
+        <v>390890</v>
       </c>
       <c r="CU77" s="1">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="CV77" s="1">
-        <v>10243</v>
+        <v>10252</v>
       </c>
       <c r="CW77" s="1">
-        <v>15888</v>
+        <v>15898</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26956,16 +26956,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>4545</v>
+        <v>4534</v>
       </c>
       <c r="K79" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L79" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="M79" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90618</v>
+        <v>90607</v>
       </c>
       <c r="CU79" s="1">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="CV79" s="1">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="CW79" s="1">
-        <v>1855</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27611,7 +27611,7 @@
         <v>0</v>
       </c>
       <c r="Y81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="1">
         <v>0</v>
@@ -27695,7 +27695,7 @@
         <v>1</v>
       </c>
       <c r="BA81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB81" s="1">
         <v>0</v>
@@ -27839,7 +27839,7 @@
         <v>148</v>
       </c>
       <c r="CW81" s="1">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28269,7 +28269,7 @@
         <v>13</v>
       </c>
       <c r="AO83" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28284,16 +28284,16 @@
         <v>0</v>
       </c>
       <c r="AT83" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AU83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV83" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW83" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX83" s="1">
         <v>17</v>
@@ -28413,7 +28413,7 @@
         <v>147</v>
       </c>
       <c r="CK83" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423791</v>
+        <v>423792</v>
       </c>
       <c r="CU83" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="CV83" s="1">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="CW83" s="1">
-        <v>5354</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29088,7 +29088,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" s="1">
         <v>107</v>
@@ -29364,7 +29364,7 @@
         <v>31</v>
       </c>
       <c r="CW86" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29624,16 +29624,16 @@
         <v>1</v>
       </c>
       <c r="CH87" s="1">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="CI87" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CJ87" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="CK87" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29660,16 +29660,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="CU87" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV87" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="CW87" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -29994,16 +29994,16 @@
         <v>5</v>
       </c>
       <c r="F89" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="1">
         <v>397</v>
@@ -30270,16 +30270,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="CU89" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV89" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="CW89" s="1">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30622,7 +30622,7 @@
         <v>54</v>
       </c>
       <c r="L91" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M91" s="2">
         <v>380</v>
@@ -30886,7 +30886,7 @@
         <v>76</v>
       </c>
       <c r="CV91" s="1">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="CW91" s="1">
         <v>868</v>
@@ -30903,7 +30903,7 @@
         <v>2</v>
       </c>
       <c r="D92" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
@@ -30927,7 +30927,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2">
         <v>12</v>
@@ -31191,7 +31191,7 @@
         <v>8</v>
       </c>
       <c r="CV92" s="1">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="CW92" s="1">
         <v>94</v>
@@ -32129,16 +32129,16 @@
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J96" s="1">
         <v>2</v>
@@ -32405,16 +32405,16 @@
         <v>0</v>
       </c>
       <c r="CT96" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="CU96" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW96" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -33663,7 +33663,7 @@
         <v>6</v>
       </c>
       <c r="I101" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J101" s="1">
         <v>0</v>
@@ -33939,7 +33939,7 @@
         <v>6</v>
       </c>
       <c r="CW101" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:101">
@@ -34073,7 +34073,7 @@
         <v>0</v>
       </c>
       <c r="AR102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS102" s="2">
         <v>3</v>
@@ -34205,7 +34205,7 @@
         <v>21</v>
       </c>
       <c r="CJ102" s="2">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="CK102" s="2">
         <v>85</v>
@@ -34241,7 +34241,7 @@
         <v>60</v>
       </c>
       <c r="CV102" s="1">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="CW102" s="1">
         <v>1795</v>
@@ -34360,16 +34360,16 @@
         <v>0</v>
       </c>
       <c r="AL103" s="1">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AM103" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AN103" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AO103" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AP103" s="1">
         <v>0</v>
@@ -34504,16 +34504,16 @@
         <v>0</v>
       </c>
       <c r="CH103" s="1">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="CI103" s="2">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="CJ103" s="2">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="CK103" s="2">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="CL103" s="1">
         <v>0</v>
@@ -34540,16 +34540,16 @@
         <v>0</v>
       </c>
       <c r="CT103" s="1">
-        <v>1007</v>
+        <v>1046</v>
       </c>
       <c r="CU103" s="1">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="CV103" s="1">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="CW103" s="1">
-        <v>183</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34868,7 +34868,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E105" s="2">
         <v>31</v>
@@ -34982,13 +34982,13 @@
         <v>2</v>
       </c>
       <c r="AP105" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AQ105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR105" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS105" s="2">
         <v>4</v>
@@ -35150,13 +35150,13 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7980</v>
+        <v>7981</v>
       </c>
       <c r="CU105" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CV105" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="CW105" s="1">
         <v>506</v>
@@ -35173,7 +35173,7 @@
         <v>126</v>
       </c>
       <c r="D106" s="2">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="E106" s="2">
         <v>406</v>
@@ -35461,7 +35461,7 @@
         <v>311</v>
       </c>
       <c r="CV106" s="1">
-        <v>1155</v>
+        <v>1077</v>
       </c>
       <c r="CW106" s="1">
         <v>2528</v>
@@ -36420,7 +36420,7 @@
         <v>210</v>
       </c>
       <c r="M110" s="2">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="N110" s="1">
         <v>1303</v>
@@ -36504,7 +36504,7 @@
         <v>8</v>
       </c>
       <c r="AO110" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP110" s="1">
         <v>0</v>
@@ -36648,7 +36648,7 @@
         <v>71</v>
       </c>
       <c r="CK110" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="CL110" s="1">
         <v>0</v>
@@ -36684,7 +36684,7 @@
         <v>427</v>
       </c>
       <c r="CW110" s="1">
-        <v>1011</v>
+        <v>954</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36704,16 +36704,16 @@
         <v>2</v>
       </c>
       <c r="F111" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I111" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J111" s="1">
         <v>0</v>
@@ -36806,7 +36806,7 @@
         <v>0</v>
       </c>
       <c r="AN111" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO111" s="2">
         <v>13</v>
@@ -36980,16 +36980,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="CU111" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV111" s="1">
         <v>38</v>
       </c>
       <c r="CW111" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37326,16 +37326,16 @@
         <v>0</v>
       </c>
       <c r="J113" s="1">
-        <v>4762</v>
+        <v>4800</v>
       </c>
       <c r="K113" s="2">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="L113" s="2">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="M113" s="2">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="N113" s="1">
         <v>8023</v>
@@ -37590,16 +37590,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173813</v>
+        <v>173851</v>
       </c>
       <c r="CU113" s="1">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="CV113" s="1">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="CW113" s="1">
-        <v>9810</v>
+        <v>9848</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38217,16 +38217,16 @@
         <v>215</v>
       </c>
       <c r="B116" s="1">
-        <v>4421</v>
+        <v>4427</v>
       </c>
       <c r="C116" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D116" s="2">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E116" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -38250,7 +38250,7 @@
         <v>132</v>
       </c>
       <c r="M116" s="2">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="N116" s="1">
         <v>4537</v>
@@ -38334,7 +38334,7 @@
         <v>5</v>
       </c>
       <c r="AO116" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP116" s="1">
         <v>28</v>
@@ -38349,28 +38349,28 @@
         <v>2</v>
       </c>
       <c r="AT116" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AU116" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV116" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW116" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX116" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB116" s="1">
         <v>2</v>
@@ -38478,7 +38478,7 @@
         <v>35</v>
       </c>
       <c r="CK116" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21742</v>
+        <v>21750</v>
       </c>
       <c r="CU116" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="CV116" s="1">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="CW116" s="1">
-        <v>1155</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -42487,28 +42487,28 @@
         <v>229</v>
       </c>
       <c r="B130" s="1">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C130" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D130" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E130" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F130" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J130" s="1">
         <v>0</v>
@@ -42775,16 +42775,16 @@
         <v>0</v>
       </c>
       <c r="CT130" s="1">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="CU130" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CV130" s="1">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="CW130" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43115,7 +43115,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I132" s="2">
         <v>6</v>
@@ -43391,7 +43391,7 @@
         <v>1</v>
       </c>
       <c r="CV132" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW132" s="1">
         <v>6</v>
@@ -43824,7 +43824,7 @@
         <v>6</v>
       </c>
       <c r="AO134" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP134" s="1">
         <v>36</v>
@@ -43968,7 +43968,7 @@
         <v>33</v>
       </c>
       <c r="CK134" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="CL134" s="1">
         <v>9</v>
@@ -44004,7 +44004,7 @@
         <v>2535</v>
       </c>
       <c r="CW134" s="1">
-        <v>5809</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44102,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="AF135" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG135" s="2">
         <v>750</v>
@@ -44129,7 +44129,7 @@
         <v>3</v>
       </c>
       <c r="AO135" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP135" s="1">
         <v>23</v>
@@ -44273,7 +44273,7 @@
         <v>93</v>
       </c>
       <c r="CK135" s="2">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="CL135" s="1">
         <v>13</v>
@@ -44306,10 +44306,10 @@
         <v>150</v>
       </c>
       <c r="CV135" s="1">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="CW135" s="1">
-        <v>2744</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44569,16 +44569,16 @@
         <v>0</v>
       </c>
       <c r="CH136" s="1">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="CI136" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ136" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CK136" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CL136" s="1">
         <v>13</v>
@@ -44605,16 +44605,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158871</v>
+        <v>158874</v>
       </c>
       <c r="CU136" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CV136" s="1">
-        <v>5081</v>
+        <v>5084</v>
       </c>
       <c r="CW136" s="1">
-        <v>6081</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44622,16 +44622,16 @@
         <v>236</v>
       </c>
       <c r="B137" s="1">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C137" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E137" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F137" s="1">
         <v>25</v>
@@ -44646,16 +44646,16 @@
         <v>2</v>
       </c>
       <c r="J137" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K137" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L137" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M137" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N137" s="1">
         <v>153</v>
@@ -44910,16 +44910,16 @@
         <v>0</v>
       </c>
       <c r="CT137" s="1">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="CU137" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="CV137" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="CW137" s="1">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -45041,7 +45041,7 @@
         <v>0</v>
       </c>
       <c r="AN138" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO138" s="2">
         <v>8</v>
@@ -45185,7 +45185,7 @@
         <v>0</v>
       </c>
       <c r="CJ138" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CK138" s="2">
         <v>12</v>
@@ -45221,7 +45221,7 @@
         <v>19</v>
       </c>
       <c r="CV138" s="1">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="CW138" s="1">
         <v>268</v>
@@ -45747,7 +45747,7 @@
         <v>0</v>
       </c>
       <c r="BT140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU140" s="2">
         <v>1</v>
@@ -45831,7 +45831,7 @@
         <v>3</v>
       </c>
       <c r="CV140" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW140" s="1">
         <v>24</v>
@@ -46285,7 +46285,7 @@
         <v>0</v>
       </c>
       <c r="AV142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW142" s="2">
         <v>4</v>
@@ -46441,7 +46441,7 @@
         <v>22</v>
       </c>
       <c r="CV142" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="CW142" s="1">
         <v>101</v>
@@ -46713,7 +46713,7 @@
         <v>2</v>
       </c>
       <c r="CK143" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CL143" s="1">
         <v>73</v>
@@ -46749,7 +46749,7 @@
         <v>13</v>
       </c>
       <c r="CW143" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -46877,16 +46877,16 @@
         <v>4</v>
       </c>
       <c r="AP144" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AQ144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR144" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS144" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT144" s="1">
         <v>0</v>
@@ -47021,16 +47021,16 @@
         <v>1</v>
       </c>
       <c r="CL144" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CM144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN144" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO144" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP144" s="1">
         <v>0</v>
@@ -47045,16 +47045,16 @@
         <v>0</v>
       </c>
       <c r="CT144" s="1">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="CU144" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CV144" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CW144" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47693,7 +47693,7 @@
         <v>3</v>
       </c>
       <c r="I147" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J147" s="1">
         <v>18</v>
@@ -47969,7 +47969,7 @@
         <v>13</v>
       </c>
       <c r="CW147" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48402,16 +48402,16 @@
         <v>0</v>
       </c>
       <c r="AP149" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ149" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR149" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS149" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT149" s="1">
         <v>0</v>
@@ -48534,16 +48534,16 @@
         <v>0</v>
       </c>
       <c r="CH149" s="1">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CI149" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ149" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CK149" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CL149" s="1">
         <v>37</v>
@@ -48570,16 +48570,16 @@
         <v>0</v>
       </c>
       <c r="CT149" s="1">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="CU149" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV149" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CW149" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="150" spans="1:101">
@@ -48716,7 +48716,7 @@
         <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48860,7 +48860,7 @@
         <v>2</v>
       </c>
       <c r="CO150" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP150" s="1">
         <v>0</v>
@@ -48884,7 +48884,7 @@
         <v>7</v>
       </c>
       <c r="CW150" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49021,7 +49021,7 @@
         <v>2</v>
       </c>
       <c r="AS151" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT151" s="1">
         <v>0</v>
@@ -49153,7 +49153,7 @@
         <v>8</v>
       </c>
       <c r="CK151" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CL151" s="1">
         <v>28</v>
@@ -49189,7 +49189,7 @@
         <v>22</v>
       </c>
       <c r="CW151" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49230,7 +49230,7 @@
         <v>45</v>
       </c>
       <c r="M152" s="2">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N152" s="1">
         <v>168</v>
@@ -49326,7 +49326,7 @@
         <v>2</v>
       </c>
       <c r="AS152" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT152" s="1">
         <v>0</v>
@@ -49458,7 +49458,7 @@
         <v>16</v>
       </c>
       <c r="CK152" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="CL152" s="1">
         <v>9</v>
@@ -49494,7 +49494,7 @@
         <v>101</v>
       </c>
       <c r="CW152" s="1">
-        <v>310</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50441,16 +50441,16 @@
         <v>0</v>
       </c>
       <c r="J156" s="1">
-        <v>2053</v>
+        <v>2066</v>
       </c>
       <c r="K156" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L156" s="2">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="M156" s="2">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="N156" s="1">
         <v>61027</v>
@@ -50705,16 +50705,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71484</v>
+        <v>71497</v>
       </c>
       <c r="CU156" s="1">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="CV156" s="1">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="CW156" s="1">
-        <v>2494</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -52068,7 +52068,7 @@
         <v>0</v>
       </c>
       <c r="AR161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS161" s="2">
         <v>1</v>
@@ -52200,7 +52200,7 @@
         <v>6</v>
       </c>
       <c r="CJ161" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="CK161" s="2">
         <v>40</v>
@@ -52236,7 +52236,7 @@
         <v>46</v>
       </c>
       <c r="CV161" s="1">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="CW161" s="1">
         <v>1271</v>
@@ -53497,7 +53497,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="2">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="M166" s="2">
         <v>108</v>
@@ -53761,7 +53761,7 @@
         <v>6</v>
       </c>
       <c r="CV166" s="1">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="CW166" s="1">
         <v>501</v>
@@ -54107,7 +54107,7 @@
         <v>17</v>
       </c>
       <c r="L168" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M168" s="2">
         <v>100</v>
@@ -54197,16 +54197,16 @@
         <v>2</v>
       </c>
       <c r="AP168" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AQ168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR168" s="2">
         <v>2</v>
       </c>
       <c r="AS168" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT168" s="1">
         <v>0</v>
@@ -54329,16 +54329,16 @@
         <v>0</v>
       </c>
       <c r="CH168" s="1">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="CI168" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CJ168" s="2">
         <v>24</v>
       </c>
       <c r="CK168" s="2">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54365,16 +54365,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5948</v>
+        <v>5956</v>
       </c>
       <c r="CU168" s="1">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="CV168" s="1">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="CW168" s="1">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54687,16 +54687,16 @@
         <v>269</v>
       </c>
       <c r="B170" s="1">
-        <v>4531</v>
+        <v>4549</v>
       </c>
       <c r="C170" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D170" s="2">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E170" s="2">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -54720,7 +54720,7 @@
         <v>168</v>
       </c>
       <c r="M170" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54780,7 +54780,7 @@
         <v>126</v>
       </c>
       <c r="AG170" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54975,16 +54975,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19518</v>
+        <v>19536</v>
       </c>
       <c r="CU170" s="1">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="CV170" s="1">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="CW170" s="1">
-        <v>1254</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -56634,7 +56634,7 @@
         <v>32</v>
       </c>
       <c r="AO176" s="2">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="AP176" s="1">
         <v>0</v>
@@ -56778,7 +56778,7 @@
         <v>70</v>
       </c>
       <c r="CK176" s="2">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56814,7 +56814,7 @@
         <v>105</v>
       </c>
       <c r="CW176" s="1">
-        <v>199</v>
+        <v>129</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57136,7 +57136,7 @@
         <v>83</v>
       </c>
       <c r="E178" s="2">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -57160,19 +57160,19 @@
         <v>29</v>
       </c>
       <c r="M178" s="2">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="N178" s="1">
-        <v>73475</v>
+        <v>73112</v>
       </c>
       <c r="O178" s="2">
-        <v>0</v>
+        <v>-363</v>
       </c>
       <c r="P178" s="2">
-        <v>2329</v>
+        <v>1966</v>
       </c>
       <c r="Q178" s="2">
-        <v>4477</v>
+        <v>4114</v>
       </c>
       <c r="R178" s="1">
         <v>0</v>
@@ -57244,7 +57244,7 @@
         <v>22</v>
       </c>
       <c r="AO178" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AP178" s="1">
         <v>30</v>
@@ -57388,7 +57388,7 @@
         <v>69</v>
       </c>
       <c r="CK178" s="2">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="CL178" s="1">
         <v>7</v>
@@ -57415,16 +57415,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>85227</v>
+        <v>84864</v>
       </c>
       <c r="CU178" s="1">
-        <v>75</v>
+        <v>-288</v>
       </c>
       <c r="CV178" s="1">
-        <v>2574</v>
+        <v>2211</v>
       </c>
       <c r="CW178" s="1">
-        <v>4967</v>
+        <v>4539</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57770,7 +57770,7 @@
         <v>71</v>
       </c>
       <c r="M180" s="2">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="N180" s="1">
         <v>36939</v>
@@ -57845,16 +57845,16 @@
         <v>0</v>
       </c>
       <c r="AL180" s="1">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="AM180" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN180" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO180" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP180" s="1">
         <v>9</v>
@@ -57989,16 +57989,16 @@
         <v>0</v>
       </c>
       <c r="CH180" s="1">
-        <v>2038</v>
+        <v>2049</v>
       </c>
       <c r="CI180" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ180" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="CK180" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="CL180" s="1">
         <v>3</v>
@@ -58025,16 +58025,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51139</v>
+        <v>51152</v>
       </c>
       <c r="CU180" s="1">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="CV180" s="1">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="CW180" s="1">
-        <v>2685</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -62007,16 +62007,16 @@
         <v>293</v>
       </c>
       <c r="B194" s="1">
-        <v>1602</v>
+        <v>1609</v>
       </c>
       <c r="C194" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D194" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E194" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F194" s="1">
         <v>0</v>
@@ -62295,16 +62295,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32848</v>
+        <v>32855</v>
       </c>
       <c r="CU194" s="1">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="CV194" s="1">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="CW194" s="1">
-        <v>1366</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62564,16 +62564,16 @@
         <v>0</v>
       </c>
       <c r="CH195" s="1">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="CI195" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CJ195" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CK195" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CL195" s="1">
         <v>9</v>
@@ -62600,16 +62600,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71195</v>
+        <v>71198</v>
       </c>
       <c r="CU195" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CV195" s="1">
-        <v>3371</v>
+        <v>3374</v>
       </c>
       <c r="CW195" s="1">
-        <v>5333</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -63846,7 +63846,7 @@
         <v>99</v>
       </c>
       <c r="E200" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="F200" s="1">
         <v>0</v>
@@ -63870,7 +63870,7 @@
         <v>36</v>
       </c>
       <c r="M200" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="N200" s="1">
         <v>7999</v>
@@ -64134,7 +64134,7 @@
         <v>256</v>
       </c>
       <c r="CW200" s="1">
-        <v>513</v>
+        <v>460</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64268,7 +64268,7 @@
         <v>0</v>
       </c>
       <c r="AR201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS201" s="2">
         <v>3</v>
@@ -64400,7 +64400,7 @@
         <v>21</v>
       </c>
       <c r="CJ201" s="2">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="CK201" s="2">
         <v>128</v>
@@ -64436,7 +64436,7 @@
         <v>62</v>
       </c>
       <c r="CV201" s="1">
-        <v>2006</v>
+        <v>1993</v>
       </c>
       <c r="CW201" s="1">
         <v>3162</v>
@@ -65775,16 +65775,16 @@
         <v>0</v>
       </c>
       <c r="AL206" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AM206" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN206" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO206" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP206" s="1">
         <v>80</v>
@@ -65931,16 +65931,16 @@
         <v>12</v>
       </c>
       <c r="CL206" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CM206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP206" s="1">
         <v>0</v>
@@ -65955,16 +65955,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="CU206" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CV206" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CW206" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -65981,7 +65981,7 @@
         <v>28</v>
       </c>
       <c r="E207" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -66005,7 +66005,7 @@
         <v>39</v>
       </c>
       <c r="M207" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N207" s="1">
         <v>5091</v>
@@ -66101,7 +66101,7 @@
         <v>3</v>
       </c>
       <c r="AS207" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT207" s="1">
         <v>0</v>
@@ -66233,7 +66233,7 @@
         <v>35</v>
       </c>
       <c r="CK207" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="CL207" s="1">
         <v>13</v>
@@ -66269,7 +66269,7 @@
         <v>354</v>
       </c>
       <c r="CW207" s="1">
-        <v>648</v>
+        <v>617</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66286,7 +66286,7 @@
         <v>7</v>
       </c>
       <c r="E208" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1">
         <v>18</v>
@@ -66574,7 +66574,7 @@
         <v>7</v>
       </c>
       <c r="CW208" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:101">
@@ -67201,7 +67201,7 @@
         <v>9</v>
       </c>
       <c r="E211" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F211" s="1">
         <v>15</v>
@@ -67489,7 +67489,7 @@
         <v>488</v>
       </c>
       <c r="CW211" s="1">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -7191,16 +7191,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="1">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="AE14" s="2">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AF14" s="2">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="AG14" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3187</v>
+        <v>3181</v>
       </c>
       <c r="CU14" s="1">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="CV14" s="1">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="CW14" s="1">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -9975,10 +9975,10 @@
         <v>88</v>
       </c>
       <c r="AQ23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS23" s="2">
         <v>6</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="CJ23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CK23" s="2">
         <v>5</v>
@@ -10119,7 +10119,7 @@
         <v>52</v>
       </c>
       <c r="CM23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN23" s="2">
         <v>2</v>
@@ -10143,10 +10143,10 @@
         <v>733</v>
       </c>
       <c r="CU23" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CW23" s="1">
         <v>44</v>
@@ -10720,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="CJ25" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CK25" s="2">
         <v>25</v>
@@ -10756,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="CV25" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CW25" s="1">
         <v>25</v>
@@ -14454,7 +14454,7 @@
         <v>389</v>
       </c>
       <c r="K38" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>14</v>
@@ -14718,7 +14718,7 @@
         <v>1951</v>
       </c>
       <c r="CU38" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CV38" s="1">
         <v>36</v>
@@ -15037,16 +15037,16 @@
         <v>139</v>
       </c>
       <c r="B40" s="1">
-        <v>8771</v>
+        <v>8830</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15325,16 +15325,16 @@
         <v>0</v>
       </c>
       <c r="CT40" s="1">
-        <v>53430</v>
+        <v>53489</v>
       </c>
       <c r="CU40" s="1">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="CV40" s="1">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="CW40" s="1">
-        <v>2115</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16072,16 +16072,16 @@
         <v>0</v>
       </c>
       <c r="AP43" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AQ43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -16216,16 +16216,16 @@
         <v>0</v>
       </c>
       <c r="CL43" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CM43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CP43" s="1">
         <v>0</v>
@@ -16240,16 +16240,16 @@
         <v>0</v>
       </c>
       <c r="CT43" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CU43" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV43" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CW43" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -18811,7 +18811,7 @@
         <v>3</v>
       </c>
       <c r="AN52" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO52" s="2">
         <v>20</v>
@@ -18955,7 +18955,7 @@
         <v>0</v>
       </c>
       <c r="CJ52" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="CK52" s="2">
         <v>23</v>
@@ -18991,7 +18991,7 @@
         <v>3</v>
       </c>
       <c r="CV52" s="1">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="CW52" s="1">
         <v>47</v>
@@ -20856,16 +20856,16 @@
         <v>3</v>
       </c>
       <c r="J59" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K59" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M59" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N59" s="1">
         <v>321</v>
@@ -20940,16 +20940,16 @@
         <v>0</v>
       </c>
       <c r="AL59" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AM59" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN59" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO59" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP59" s="1">
         <v>73</v>
@@ -20958,7 +20958,7 @@
         <v>0</v>
       </c>
       <c r="AR59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS59" s="2">
         <v>4</v>
@@ -21084,16 +21084,16 @@
         <v>0</v>
       </c>
       <c r="CH59" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="CI59" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ59" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CK59" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL59" s="1">
         <v>67</v>
@@ -21120,16 +21120,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="CU59" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CV59" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="CW59" s="1">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -22363,7 +22363,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E64" s="2">
         <v>21</v>
@@ -22387,7 +22387,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M64" s="2">
         <v>16</v>
@@ -22423,7 +22423,7 @@
         <v>0</v>
       </c>
       <c r="X64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="2">
         <v>1</v>
@@ -22651,7 +22651,7 @@
         <v>83</v>
       </c>
       <c r="CV64" s="1">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="CW64" s="1">
         <v>490</v>
@@ -22662,16 +22662,16 @@
         <v>164</v>
       </c>
       <c r="B65" s="1">
-        <v>3702</v>
+        <v>3716</v>
       </c>
       <c r="C65" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D65" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E65" s="2">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22692,7 +22692,7 @@
         <v>11</v>
       </c>
       <c r="L65" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M65" s="2">
         <v>95</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67186</v>
+        <v>67200</v>
       </c>
       <c r="CU65" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="CV65" s="1">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="CW65" s="1">
-        <v>3512</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22967,16 +22967,16 @@
         <v>165</v>
       </c>
       <c r="B66" s="1">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F66" s="1">
         <v>12</v>
@@ -23255,16 +23255,16 @@
         <v>0</v>
       </c>
       <c r="CT66" s="1">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="CU66" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV66" s="1">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="CW66" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23844,7 +23844,7 @@
         <v>27</v>
       </c>
       <c r="CM68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN68" s="2">
         <v>1</v>
@@ -23868,7 +23868,7 @@
         <v>2132</v>
       </c>
       <c r="CU68" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV68" s="1">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>1</v>
       </c>
       <c r="AR70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS70" s="2">
         <v>6</v>
@@ -24445,7 +24445,7 @@
         <v>1</v>
       </c>
       <c r="CJ70" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CK70" s="2">
         <v>7</v>
@@ -24481,7 +24481,7 @@
         <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="CW70" s="1">
         <v>82</v>
@@ -24800,7 +24800,7 @@
         <v>9</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -24920,7 +24920,7 @@
         <v>22</v>
       </c>
       <c r="AQ72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR72" s="2">
         <v>2</v>
@@ -25052,7 +25052,7 @@
         <v>41</v>
       </c>
       <c r="CI72" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ72" s="2">
         <v>7</v>
@@ -25088,7 +25088,7 @@
         <v>516</v>
       </c>
       <c r="CU72" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="CV72" s="1">
         <v>44</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16194</v>
+        <v>16207</v>
       </c>
       <c r="CI74" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="CJ74" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="CK74" s="2">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171640</v>
+        <v>171653</v>
       </c>
       <c r="CU74" s="1">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="CV74" s="1">
-        <v>1854</v>
+        <v>1865</v>
       </c>
       <c r="CW74" s="1">
-        <v>4417</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25832,16 +25832,16 @@
         <v>0</v>
       </c>
       <c r="AP75" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR75" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS75" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT75" s="1">
         <v>0</v>
@@ -25964,16 +25964,16 @@
         <v>0</v>
       </c>
       <c r="CH75" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="CI75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ75" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CK75" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CL75" s="1">
         <v>8</v>
@@ -26000,16 +26000,16 @@
         <v>0</v>
       </c>
       <c r="CT75" s="1">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="CU75" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV75" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW75" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -26017,16 +26017,16 @@
         <v>175</v>
       </c>
       <c r="B76" s="1">
-        <v>5094</v>
+        <v>5146</v>
       </c>
       <c r="C76" s="2">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D76" s="2">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -26158,7 +26158,7 @@
         <v>1</v>
       </c>
       <c r="AW76" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX76" s="1">
         <v>10</v>
@@ -26170,7 +26170,7 @@
         <v>0</v>
       </c>
       <c r="BA76" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB76" s="1">
         <v>4</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>151017</v>
+        <v>151069</v>
       </c>
       <c r="CU76" s="1">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="CV76" s="1">
-        <v>1317</v>
+        <v>1369</v>
       </c>
       <c r="CW76" s="1">
-        <v>3649</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26346,16 +26346,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4879</v>
+        <v>4878</v>
       </c>
       <c r="K77" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L77" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M77" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26433,10 +26433,10 @@
         <v>1919</v>
       </c>
       <c r="AM77" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AN77" s="2">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AO77" s="2">
         <v>81</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7303</v>
+        <v>7348</v>
       </c>
       <c r="CI77" s="2">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="CJ77" s="2">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="CK77" s="2">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390890</v>
+        <v>390934</v>
       </c>
       <c r="CU77" s="1">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="CV77" s="1">
-        <v>10252</v>
+        <v>10284</v>
       </c>
       <c r="CW77" s="1">
-        <v>15898</v>
+        <v>15942</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26645,7 +26645,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78" s="2">
         <v>5</v>
@@ -26921,7 +26921,7 @@
         <v>5</v>
       </c>
       <c r="CV78" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="CW78" s="1">
         <v>111</v>
@@ -26938,7 +26938,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="2">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E79" s="2">
         <v>72</v>
@@ -27226,7 +27226,7 @@
         <v>62</v>
       </c>
       <c r="CV79" s="1">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="CW79" s="1">
         <v>1844</v>
@@ -27572,7 +27572,7 @@
         <v>27</v>
       </c>
       <c r="L81" s="2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="M81" s="2">
         <v>92</v>
@@ -27836,7 +27836,7 @@
         <v>37</v>
       </c>
       <c r="CV81" s="1">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="CW81" s="1">
         <v>349</v>
@@ -27859,16 +27859,16 @@
         <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -27967,16 +27967,16 @@
         <v>0</v>
       </c>
       <c r="AP82" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AQ82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS82" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -28111,16 +28111,16 @@
         <v>1</v>
       </c>
       <c r="CL82" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CM82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO82" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP82" s="1">
         <v>0</v>
@@ -28135,16 +28135,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="CU82" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CV82" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CW82" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28152,16 +28152,16 @@
         <v>182</v>
       </c>
       <c r="B83" s="1">
-        <v>2661</v>
+        <v>2729</v>
       </c>
       <c r="C83" s="2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D83" s="2">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="E83" s="2">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423792</v>
+        <v>423860</v>
       </c>
       <c r="CU83" s="1">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="CV83" s="1">
-        <v>887</v>
+        <v>955</v>
       </c>
       <c r="CW83" s="1">
-        <v>5316</v>
+        <v>5384</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -30222,16 +30222,16 @@
         <v>0</v>
       </c>
       <c r="CD89" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CE89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH89" s="1">
         <v>95</v>
@@ -30270,16 +30270,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="CU89" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV89" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="CW89" s="1">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -32183,7 +32183,7 @@
         <v>0</v>
       </c>
       <c r="X96" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="2">
         <v>2</v>
@@ -32411,7 +32411,7 @@
         <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW96" s="1">
         <v>41</v>
@@ -33989,7 +33989,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="Q102" s="2">
         <v>534</v>
@@ -34241,7 +34241,7 @@
         <v>60</v>
       </c>
       <c r="CV102" s="1">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="CW102" s="1">
         <v>1795</v>
@@ -34363,7 +34363,7 @@
         <v>202</v>
       </c>
       <c r="AM103" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AN103" s="2">
         <v>16</v>
@@ -34507,7 +34507,7 @@
         <v>802</v>
       </c>
       <c r="CI103" s="2">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="CJ103" s="2">
         <v>130</v>
@@ -34543,7 +34543,7 @@
         <v>1046</v>
       </c>
       <c r="CU103" s="1">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="CV103" s="1">
         <v>149</v>
@@ -37341,7 +37341,7 @@
         <v>8023</v>
       </c>
       <c r="O113" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P113" s="2">
         <v>175</v>
@@ -37593,7 +37593,7 @@
         <v>173851</v>
       </c>
       <c r="CU113" s="1">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="CV113" s="1">
         <v>451</v>
@@ -38223,7 +38223,7 @@
         <v>27</v>
       </c>
       <c r="D116" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E116" s="2">
         <v>111</v>
@@ -38511,7 +38511,7 @@
         <v>92</v>
       </c>
       <c r="CV116" s="1">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="CW116" s="1">
         <v>1088</v>
@@ -38935,16 +38935,16 @@
         <v>0</v>
       </c>
       <c r="AL118" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP118" s="1">
         <v>2</v>
@@ -39079,16 +39079,16 @@
         <v>0</v>
       </c>
       <c r="CH118" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="CI118" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CJ118" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CK118" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="CL118" s="1">
         <v>0</v>
@@ -39115,16 +39115,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="CU118" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CV118" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CW118" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -39695,7 +39695,7 @@
         <v>1</v>
       </c>
       <c r="CJ120" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="CK120" s="2">
         <v>40</v>
@@ -39731,7 +39731,7 @@
         <v>6</v>
       </c>
       <c r="CV120" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="CW120" s="1">
         <v>72</v>
@@ -44096,16 +44096,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11788</v>
+        <v>11789</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF135" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG135" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62642</v>
+        <v>62643</v>
       </c>
       <c r="CU135" s="1">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CV135" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="CW135" s="1">
-        <v>2725</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44347,7 +44347,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2">
         <v>7</v>
@@ -44611,7 +44611,7 @@
         <v>7</v>
       </c>
       <c r="CV136" s="1">
-        <v>5084</v>
+        <v>5083</v>
       </c>
       <c r="CW136" s="1">
         <v>6083</v>
@@ -46258,7 +46258,7 @@
         <v>69</v>
       </c>
       <c r="AM142" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN142" s="2">
         <v>4</v>
@@ -46402,7 +46402,7 @@
         <v>114</v>
       </c>
       <c r="CI142" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ142" s="2">
         <v>3</v>
@@ -46438,7 +46438,7 @@
         <v>1653</v>
       </c>
       <c r="CU142" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CV142" s="1">
         <v>58</v>
@@ -46757,16 +46757,16 @@
         <v>243</v>
       </c>
       <c r="B144" s="1">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C144" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D144" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E144" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1">
         <v>15</v>
@@ -47045,16 +47045,16 @@
         <v>0</v>
       </c>
       <c r="CT144" s="1">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="CU144" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV144" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CW144" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -48922,7 +48922,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M151" s="2">
         <v>8</v>
@@ -49186,7 +49186,7 @@
         <v>2</v>
       </c>
       <c r="CV151" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="CW151" s="1">
         <v>39</v>
@@ -49311,7 +49311,7 @@
         <v>0</v>
       </c>
       <c r="AN152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO152" s="2">
         <v>1</v>
@@ -49455,7 +49455,7 @@
         <v>2</v>
       </c>
       <c r="CJ152" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CK152" s="2">
         <v>34</v>
@@ -49491,7 +49491,7 @@
         <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="CW152" s="1">
         <v>277</v>
@@ -50528,7 +50528,7 @@
         <v>394</v>
       </c>
       <c r="AM156" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN156" s="2">
         <v>4</v>
@@ -50672,7 +50672,7 @@
         <v>2778</v>
       </c>
       <c r="CI156" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ156" s="2">
         <v>53</v>
@@ -50708,7 +50708,7 @@
         <v>71497</v>
       </c>
       <c r="CU156" s="1">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="CV156" s="1">
         <v>1064</v>
@@ -51267,16 +51267,16 @@
         <v>0</v>
       </c>
       <c r="CD158" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CE158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH158" s="1">
         <v>5929</v>
@@ -51315,16 +51315,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25461</v>
+        <v>25462</v>
       </c>
       <c r="CU158" s="1">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="CV158" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="CW158" s="1">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -52980,7 +52980,7 @@
         <v>17</v>
       </c>
       <c r="AQ164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR164" s="2">
         <v>2</v>
@@ -53124,7 +53124,7 @@
         <v>4</v>
       </c>
       <c r="CM164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN164" s="2">
         <v>1</v>
@@ -53148,7 +53148,7 @@
         <v>1125</v>
       </c>
       <c r="CU164" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CV164" s="1">
         <v>106</v>
@@ -53593,7 +53593,7 @@
         <v>1</v>
       </c>
       <c r="AR166" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS166" s="2">
         <v>5</v>
@@ -53725,7 +53725,7 @@
         <v>4</v>
       </c>
       <c r="CJ166" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK166" s="2">
         <v>9</v>
@@ -53761,7 +53761,7 @@
         <v>6</v>
       </c>
       <c r="CV166" s="1">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="CW166" s="1">
         <v>501</v>
@@ -54774,7 +54774,7 @@
         <v>3602</v>
       </c>
       <c r="AE170" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF170" s="2">
         <v>126</v>
@@ -54978,7 +54978,7 @@
         <v>19536</v>
       </c>
       <c r="CU170" s="1">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="CV170" s="1">
         <v>497</v>
@@ -55016,16 +55016,16 @@
         <v>1</v>
       </c>
       <c r="J171" s="1">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="K171" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L171" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M171" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N171" s="1">
         <v>2698</v>
@@ -55280,16 +55280,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5829</v>
+        <v>5838</v>
       </c>
       <c r="CU171" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CV171" s="1">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="CW171" s="1">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -57761,16 +57761,16 @@
         <v>0</v>
       </c>
       <c r="J180" s="1">
-        <v>1516</v>
+        <v>1549</v>
       </c>
       <c r="K180" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L180" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="M180" s="2">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="N180" s="1">
         <v>36939</v>
@@ -58025,16 +58025,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51152</v>
+        <v>51185</v>
       </c>
       <c r="CU180" s="1">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="CV180" s="1">
-        <v>1240</v>
+        <v>1273</v>
       </c>
       <c r="CW180" s="1">
-        <v>2663</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -58602,7 +58602,7 @@
         <v>215</v>
       </c>
       <c r="CI182" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ182" s="2">
         <v>27</v>
@@ -58638,7 +58638,7 @@
         <v>330</v>
       </c>
       <c r="CU182" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV182" s="1">
         <v>29</v>
@@ -60183,7 +60183,7 @@
         <v>0</v>
       </c>
       <c r="D188" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E188" s="2">
         <v>15</v>
@@ -60195,7 +60195,7 @@
         <v>1</v>
       </c>
       <c r="H188" s="2">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="I188" s="2">
         <v>73</v>
@@ -60291,7 +60291,7 @@
         <v>1</v>
       </c>
       <c r="AN188" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO188" s="2">
         <v>5</v>
@@ -60303,7 +60303,7 @@
         <v>0</v>
       </c>
       <c r="AR188" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AS188" s="2">
         <v>4</v>
@@ -60435,7 +60435,7 @@
         <v>8</v>
       </c>
       <c r="CJ188" s="2">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="CK188" s="2">
         <v>64</v>
@@ -60471,7 +60471,7 @@
         <v>10</v>
       </c>
       <c r="CV188" s="1">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="CW188" s="1">
         <v>161</v>
@@ -62007,16 +62007,16 @@
         <v>293</v>
       </c>
       <c r="B194" s="1">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="C194" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D194" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E194" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F194" s="1">
         <v>0</v>
@@ -62295,16 +62295,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32855</v>
+        <v>32865</v>
       </c>
       <c r="CU194" s="1">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="CV194" s="1">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="CW194" s="1">
-        <v>1373</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -63840,7 +63840,7 @@
         <v>4265</v>
       </c>
       <c r="C200" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D200" s="2">
         <v>99</v>
@@ -63945,16 +63945,16 @@
         <v>0</v>
       </c>
       <c r="AL200" s="1">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AM200" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AN200" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AO200" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64089,16 +64089,16 @@
         <v>0</v>
       </c>
       <c r="CH200" s="1">
-        <v>1026</v>
+        <v>1041</v>
       </c>
       <c r="CI200" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="CJ200" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="CK200" s="2">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64125,16 +64125,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16290</v>
+        <v>16310</v>
       </c>
       <c r="CU200" s="1">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="CV200" s="1">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="CW200" s="1">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -65670,7 +65670,7 @@
         <v>239</v>
       </c>
       <c r="C206" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2">
         <v>8</v>
@@ -65790,7 +65790,7 @@
         <v>80</v>
       </c>
       <c r="AQ206" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR206" s="2">
         <v>2</v>
@@ -65922,7 +65922,7 @@
         <v>211</v>
       </c>
       <c r="CI206" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CJ206" s="2">
         <v>9</v>
@@ -65958,7 +65958,7 @@
         <v>1232</v>
       </c>
       <c r="CU206" s="1">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="CV206" s="1">
         <v>25</v>
@@ -66014,7 +66014,7 @@
         <v>0</v>
       </c>
       <c r="P207" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q207" s="2">
         <v>107</v>
@@ -66266,7 +66266,7 @@
         <v>44</v>
       </c>
       <c r="CV207" s="1">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="CW207" s="1">
         <v>617</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3827,7 +3827,7 @@
         <v>93</v>
       </c>
       <c r="AA3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="2">
         <v>2</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS3" s="2">
         <v>5</v>
@@ -4010,7 +4010,7 @@
         <v>25</v>
       </c>
       <c r="CJ3" s="2">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="CK3" s="2">
         <v>108</v>
@@ -4043,10 +4043,10 @@
         <v>46682</v>
       </c>
       <c r="CU3" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="CV3" s="1">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="CW3" s="1">
         <v>2059</v>
@@ -5708,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="AR9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS9" s="2">
         <v>5</v>
@@ -5840,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="CJ9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK9" s="2">
         <v>7</v>
@@ -5876,7 +5876,7 @@
         <v>5</v>
       </c>
       <c r="CV9" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CW9" s="1">
         <v>94</v>
@@ -7137,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2">
         <v>43</v>
@@ -7221,7 +7221,7 @@
         <v>9</v>
       </c>
       <c r="AN14" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO14" s="2">
         <v>11</v>
@@ -7401,7 +7401,7 @@
         <v>85</v>
       </c>
       <c r="CV14" s="1">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="CW14" s="1">
         <v>288</v>
@@ -8133,7 +8133,7 @@
         <v>573</v>
       </c>
       <c r="AM17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="2">
         <v>6</v>
@@ -8277,7 +8277,7 @@
         <v>1129</v>
       </c>
       <c r="CI17" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CJ17" s="2">
         <v>24</v>
@@ -8313,7 +8313,7 @@
         <v>1831</v>
       </c>
       <c r="CU17" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CV17" s="1">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>11</v>
       </c>
       <c r="L28" s="2">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M28" s="2">
         <v>83</v>
@@ -11503,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="AR28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS28" s="2">
         <v>5</v>
@@ -11635,7 +11635,7 @@
         <v>3</v>
       </c>
       <c r="CJ28" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CK28" s="2">
         <v>34</v>
@@ -11671,7 +11671,7 @@
         <v>16</v>
       </c>
       <c r="CV28" s="1">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="CW28" s="1">
         <v>780</v>
@@ -12439,7 +12439,7 @@
         <v>4</v>
       </c>
       <c r="AY31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ31" s="2">
         <v>1</v>
@@ -12583,7 +12583,7 @@
         <v>6004</v>
       </c>
       <c r="CU31" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CV31" s="1">
         <v>258</v>
@@ -13330,7 +13330,7 @@
         <v>49</v>
       </c>
       <c r="AQ34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34" s="2">
         <v>1</v>
@@ -13462,7 +13462,7 @@
         <v>222</v>
       </c>
       <c r="CI34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ34" s="2">
         <v>3</v>
@@ -13498,7 +13498,7 @@
         <v>2578</v>
       </c>
       <c r="CU34" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV34" s="1">
         <v>63</v>
@@ -18090,7 +18090,7 @@
         <v>75</v>
       </c>
       <c r="C50" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D50" s="2">
         <v>6</v>
@@ -18378,7 +18378,7 @@
         <v>396</v>
       </c>
       <c r="CU50" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CV50" s="1">
         <v>40</v>
@@ -20862,7 +20862,7 @@
         <v>2</v>
       </c>
       <c r="L59" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M59" s="2">
         <v>9</v>
@@ -21090,7 +21090,7 @@
         <v>2</v>
       </c>
       <c r="CJ59" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK59" s="2">
         <v>11</v>
@@ -21126,7 +21126,7 @@
         <v>7</v>
       </c>
       <c r="CV59" s="1">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="CW59" s="1">
         <v>59</v>
@@ -22175,7 +22175,7 @@
         <v>67</v>
       </c>
       <c r="AQ63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR63" s="2">
         <v>3</v>
@@ -22307,7 +22307,7 @@
         <v>692</v>
       </c>
       <c r="CI63" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="CJ63" s="2">
         <v>33</v>
@@ -22343,7 +22343,7 @@
         <v>2880</v>
       </c>
       <c r="CU63" s="1">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="CV63" s="1">
         <v>94</v>
@@ -22692,7 +22692,7 @@
         <v>11</v>
       </c>
       <c r="L65" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M65" s="2">
         <v>95</v>
@@ -22920,7 +22920,7 @@
         <v>7</v>
       </c>
       <c r="CJ65" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="CK65" s="2">
         <v>61</v>
@@ -22956,7 +22956,7 @@
         <v>49</v>
       </c>
       <c r="CV65" s="1">
-        <v>1767</v>
+        <v>1752</v>
       </c>
       <c r="CW65" s="1">
         <v>3526</v>
@@ -23607,7 +23607,7 @@
         <v>2</v>
       </c>
       <c r="L68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2">
         <v>7</v>
@@ -23871,7 +23871,7 @@
         <v>6</v>
       </c>
       <c r="CV68" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW68" s="1">
         <v>53</v>
@@ -25437,7 +25437,7 @@
         <v>37</v>
       </c>
       <c r="L74" s="2">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="M74" s="2">
         <v>193</v>
@@ -25524,7 +25524,7 @@
         <v>131</v>
       </c>
       <c r="AO74" s="2">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25662,13 +25662,13 @@
         <v>16207</v>
       </c>
       <c r="CI74" s="2">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="CJ74" s="2">
         <v>212</v>
       </c>
       <c r="CK74" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,13 +25698,13 @@
         <v>171653</v>
       </c>
       <c r="CU74" s="1">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="CV74" s="1">
-        <v>1865</v>
+        <v>1815</v>
       </c>
       <c r="CW74" s="1">
-        <v>4430</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26020,7 +26020,7 @@
         <v>5146</v>
       </c>
       <c r="C76" s="2">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D76" s="2">
         <v>89</v>
@@ -26308,7 +26308,7 @@
         <v>151069</v>
       </c>
       <c r="CU76" s="1">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="CV76" s="1">
         <v>1369</v>
@@ -26457,7 +26457,7 @@
         <v>26</v>
       </c>
       <c r="AU77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV77" s="2">
         <v>1</v>
@@ -26580,7 +26580,7 @@
         <v>146</v>
       </c>
       <c r="CJ77" s="2">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="CK77" s="2">
         <v>628</v>
@@ -26613,10 +26613,10 @@
         <v>390934</v>
       </c>
       <c r="CU77" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CV77" s="1">
-        <v>10284</v>
+        <v>10247</v>
       </c>
       <c r="CW77" s="1">
         <v>15942</v>
@@ -27545,7 +27545,7 @@
         <v>843</v>
       </c>
       <c r="C81" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D81" s="2">
         <v>7</v>
@@ -27833,7 +27833,7 @@
         <v>6407</v>
       </c>
       <c r="CU81" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="CV81" s="1">
         <v>130</v>
@@ -27862,7 +27862,7 @@
         <v>70</v>
       </c>
       <c r="G82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="2">
         <v>3</v>
@@ -27970,7 +27970,7 @@
         <v>78</v>
       </c>
       <c r="AQ82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR82" s="2">
         <v>3</v>
@@ -28114,7 +28114,7 @@
         <v>70</v>
       </c>
       <c r="CM82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN82" s="2">
         <v>3</v>
@@ -28138,7 +28138,7 @@
         <v>322</v>
       </c>
       <c r="CU82" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CV82" s="1">
         <v>10</v>
@@ -30009,7 +30009,7 @@
         <v>397</v>
       </c>
       <c r="K89" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2">
         <v>27</v>
@@ -30192,7 +30192,7 @@
         <v>0</v>
       </c>
       <c r="BT89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU89" s="2">
         <v>1</v>
@@ -30273,10 +30273,10 @@
         <v>2180</v>
       </c>
       <c r="CU89" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CV89" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="CW89" s="1">
         <v>223</v>
@@ -30619,13 +30619,13 @@
         <v>5418</v>
       </c>
       <c r="K91" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L91" s="2">
         <v>186</v>
       </c>
       <c r="M91" s="2">
-        <v>380</v>
+        <v>305</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30883,13 +30883,13 @@
         <v>25853</v>
       </c>
       <c r="CU91" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="CV91" s="1">
         <v>413</v>
       </c>
       <c r="CW91" s="1">
-        <v>868</v>
+        <v>793</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33977,7 +33977,7 @@
         <v>35</v>
       </c>
       <c r="L102" s="2">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="M102" s="2">
         <v>188</v>
@@ -34058,7 +34058,7 @@
         <v>235</v>
       </c>
       <c r="AM102" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN102" s="2">
         <v>4</v>
@@ -34202,7 +34202,7 @@
         <v>1800</v>
       </c>
       <c r="CI102" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CJ102" s="2">
         <v>42</v>
@@ -34238,10 +34238,10 @@
         <v>43024</v>
       </c>
       <c r="CU102" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="CV102" s="1">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="CW102" s="1">
         <v>1795</v>
@@ -36462,7 +36462,7 @@
         <v>132</v>
       </c>
       <c r="AA110" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB110" s="2">
         <v>5</v>
@@ -36678,7 +36678,7 @@
         <v>13336</v>
       </c>
       <c r="CU110" s="1">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="CV110" s="1">
         <v>427</v>
@@ -37120,7 +37120,7 @@
         <v>73</v>
       </c>
       <c r="AQ112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR112" s="2">
         <v>2</v>
@@ -37252,7 +37252,7 @@
         <v>262</v>
       </c>
       <c r="CI112" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ112" s="2">
         <v>9</v>
@@ -37288,7 +37288,7 @@
         <v>8282</v>
       </c>
       <c r="CU112" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV112" s="1">
         <v>254</v>
@@ -37329,7 +37329,7 @@
         <v>4800</v>
       </c>
       <c r="K113" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="L113" s="2">
         <v>161</v>
@@ -37593,7 +37593,7 @@
         <v>173851</v>
       </c>
       <c r="CU113" s="1">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="CV113" s="1">
         <v>451</v>
@@ -38525,7 +38525,7 @@
         <v>9353</v>
       </c>
       <c r="C117" s="2">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2">
         <v>545</v>
@@ -38813,7 +38813,7 @@
         <v>13161</v>
       </c>
       <c r="CU117" s="1">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="CV117" s="1">
         <v>592</v>
@@ -39255,7 +39255,7 @@
         <v>114</v>
       </c>
       <c r="AQ119" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR119" s="2">
         <v>3</v>
@@ -39399,7 +39399,7 @@
         <v>91</v>
       </c>
       <c r="CM119" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CN119" s="2">
         <v>3</v>
@@ -39423,7 +39423,7 @@
         <v>845</v>
       </c>
       <c r="CU119" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CV119" s="1">
         <v>16</v>
@@ -41683,10 +41683,10 @@
         <v>956</v>
       </c>
       <c r="AM127" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN127" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AO127" s="2">
         <v>28</v>
@@ -41827,10 +41827,10 @@
         <v>545</v>
       </c>
       <c r="CI127" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CJ127" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CK127" s="2">
         <v>26</v>
@@ -41863,10 +41863,10 @@
         <v>2585</v>
       </c>
       <c r="CU127" s="1">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="CV127" s="1">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="CW127" s="1">
         <v>99</v>
@@ -44042,7 +44042,7 @@
         <v>61</v>
       </c>
       <c r="L135" s="2">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="M135" s="2">
         <v>478</v>
@@ -44306,7 +44306,7 @@
         <v>151</v>
       </c>
       <c r="CV135" s="1">
-        <v>1016</v>
+        <v>941</v>
       </c>
       <c r="CW135" s="1">
         <v>2726</v>
@@ -44323,7 +44323,7 @@
         <v>2</v>
       </c>
       <c r="D136" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E136" s="2">
         <v>7</v>
@@ -44572,7 +44572,7 @@
         <v>389</v>
       </c>
       <c r="CI136" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CJ136" s="2">
         <v>16</v>
@@ -44608,10 +44608,10 @@
         <v>158874</v>
       </c>
       <c r="CU136" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CV136" s="1">
-        <v>5083</v>
+        <v>5082</v>
       </c>
       <c r="CW136" s="1">
         <v>6083</v>
@@ -44625,7 +44625,7 @@
         <v>147</v>
       </c>
       <c r="C137" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D137" s="2">
         <v>10</v>
@@ -44913,7 +44913,7 @@
         <v>646</v>
       </c>
       <c r="CU137" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CV137" s="1">
         <v>22</v>
@@ -45002,7 +45002,7 @@
         <v>86</v>
       </c>
       <c r="AA138" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB138" s="2">
         <v>3</v>
@@ -45050,7 +45050,7 @@
         <v>24</v>
       </c>
       <c r="AQ138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR138" s="2">
         <v>2</v>
@@ -45194,7 +45194,7 @@
         <v>4</v>
       </c>
       <c r="CM138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN138" s="2">
         <v>1</v>
@@ -45218,7 +45218,7 @@
         <v>4404</v>
       </c>
       <c r="CU138" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CV138" s="1">
         <v>113</v>
@@ -45848,7 +45848,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E141" s="2">
         <v>14</v>
@@ -46136,7 +46136,7 @@
         <v>5</v>
       </c>
       <c r="CV141" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CW141" s="1">
         <v>40</v>
@@ -50728,7 +50728,7 @@
         <v>32</v>
       </c>
       <c r="D157" s="2">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="E157" s="2">
         <v>191</v>
@@ -51016,7 +51016,7 @@
         <v>143</v>
       </c>
       <c r="CV157" s="1">
-        <v>5277</v>
+        <v>5248</v>
       </c>
       <c r="CW157" s="1">
         <v>9210</v>
@@ -52053,7 +52053,7 @@
         <v>160</v>
       </c>
       <c r="AM161" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN161" s="2">
         <v>8</v>
@@ -52197,7 +52197,7 @@
         <v>810</v>
       </c>
       <c r="CI161" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ161" s="2">
         <v>17</v>
@@ -52233,7 +52233,7 @@
         <v>22379</v>
       </c>
       <c r="CU161" s="1">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="CV161" s="1">
         <v>734</v>
@@ -54104,7 +54104,7 @@
         <v>1326</v>
       </c>
       <c r="K168" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L168" s="2">
         <v>34</v>
@@ -54188,7 +54188,7 @@
         <v>29</v>
       </c>
       <c r="AM168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN168" s="2">
         <v>1</v>
@@ -54368,7 +54368,7 @@
         <v>5956</v>
       </c>
       <c r="CU168" s="1">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="CV168" s="1">
         <v>142</v>
@@ -54717,7 +54717,7 @@
         <v>43</v>
       </c>
       <c r="L170" s="2">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="M170" s="2">
         <v>381</v>
@@ -54981,7 +54981,7 @@
         <v>80</v>
       </c>
       <c r="CV170" s="1">
-        <v>497</v>
+        <v>428</v>
       </c>
       <c r="CW170" s="1">
         <v>1277</v>
@@ -57241,7 +57241,7 @@
         <v>16</v>
       </c>
       <c r="AN178" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO178" s="2">
         <v>31</v>
@@ -57385,7 +57385,7 @@
         <v>25</v>
       </c>
       <c r="CJ178" s="2">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="CK178" s="2">
         <v>137</v>
@@ -57421,7 +57421,7 @@
         <v>-288</v>
       </c>
       <c r="CV178" s="1">
-        <v>2211</v>
+        <v>2182</v>
       </c>
       <c r="CW178" s="1">
         <v>4539</v>
@@ -57767,7 +57767,7 @@
         <v>33</v>
       </c>
       <c r="L180" s="2">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="M180" s="2">
         <v>187</v>
@@ -58031,7 +58031,7 @@
         <v>77</v>
       </c>
       <c r="CV180" s="1">
-        <v>1273</v>
+        <v>1229</v>
       </c>
       <c r="CW180" s="1">
         <v>2696</v>
@@ -61095,7 +61095,7 @@
         <v>13</v>
       </c>
       <c r="C191" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -61107,7 +61107,7 @@
         <v>34</v>
       </c>
       <c r="G191" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H191" s="2">
         <v>2</v>
@@ -61383,7 +61383,7 @@
         <v>670</v>
       </c>
       <c r="CU191" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV191" s="1">
         <v>13</v>
@@ -62339,7 +62339,7 @@
         <v>170</v>
       </c>
       <c r="K195" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L195" s="2">
         <v>6</v>
@@ -62567,7 +62567,7 @@
         <v>518</v>
       </c>
       <c r="CI195" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CJ195" s="2">
         <v>21</v>
@@ -62603,7 +62603,7 @@
         <v>71198</v>
       </c>
       <c r="CU195" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV195" s="1">
         <v>3374</v>
@@ -63948,7 +63948,7 @@
         <v>405</v>
       </c>
       <c r="AM200" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AN200" s="2">
         <v>13</v>
@@ -64092,7 +64092,7 @@
         <v>1041</v>
       </c>
       <c r="CI200" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="CJ200" s="2">
         <v>51</v>
@@ -64128,7 +64128,7 @@
         <v>16310</v>
       </c>
       <c r="CU200" s="1">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="CV200" s="1">
         <v>276</v>
@@ -65778,7 +65778,7 @@
         <v>39</v>
       </c>
       <c r="AM206" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN206" s="2">
         <v>4</v>
@@ -65922,7 +65922,7 @@
         <v>211</v>
       </c>
       <c r="CI206" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ206" s="2">
         <v>9</v>
@@ -65958,7 +65958,7 @@
         <v>1232</v>
       </c>
       <c r="CU206" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CV206" s="1">
         <v>25</v>
@@ -67219,7 +67219,7 @@
         <v>1262</v>
       </c>
       <c r="K211" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L211" s="2">
         <v>28</v>
@@ -67483,7 +67483,7 @@
         <v>6274</v>
       </c>
       <c r="CU211" s="1">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="CV211" s="1">
         <v>488</v>
@@ -69034,7 +69034,7 @@
         <v>558</v>
       </c>
       <c r="D31">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
         <v>715</v>
@@ -70077,7 +70077,7 @@
         <v>546</v>
       </c>
       <c r="D83">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s">
         <v>715</v>
@@ -71326,7 +71326,7 @@
         <v>656</v>
       </c>
       <c r="D145">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E145" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3785,7 +3785,7 @@
         <v>63</v>
       </c>
       <c r="M3" s="2">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="N3" s="1">
         <v>19611</v>
@@ -3881,7 +3881,7 @@
         <v>2</v>
       </c>
       <c r="AS3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT3" s="1">
         <v>0</v>
@@ -4013,7 +4013,7 @@
         <v>50</v>
       </c>
       <c r="CK3" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4049,7 +4049,7 @@
         <v>812</v>
       </c>
       <c r="CW3" s="1">
-        <v>2059</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4090,7 +4090,7 @@
         <v>200</v>
       </c>
       <c r="M4" s="2">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="N4" s="1">
         <v>9299</v>
@@ -4354,7 +4354,7 @@
         <v>443</v>
       </c>
       <c r="CW4" s="1">
-        <v>1173</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4365,13 +4365,13 @@
         <v>237</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>5</v>
       </c>
       <c r="E5" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1">
         <v>19</v>
@@ -4389,13 +4389,13 @@
         <v>1185</v>
       </c>
       <c r="K5" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>62</v>
       </c>
       <c r="M5" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="N5" s="1">
         <v>2965</v>
@@ -4653,13 +4653,13 @@
         <v>38681</v>
       </c>
       <c r="CU5" s="1">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CV5" s="1">
         <v>319</v>
       </c>
       <c r="CW5" s="1">
-        <v>832</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -7810,7 +7810,7 @@
         <v>8</v>
       </c>
       <c r="AG16" s="2">
-        <v>-98</v>
+        <v>7</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
       <c r="CW16" s="1">
-        <v>-38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -9066,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="AS20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT20" s="1">
         <v>0</v>
@@ -9234,7 +9234,7 @@
         <v>390</v>
       </c>
       <c r="CW20" s="1">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11386,13 +11386,13 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1">
         <v>31</v>
       </c>
       <c r="G28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>2</v>
       </c>
       <c r="AS28" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -11638,7 +11638,7 @@
         <v>13</v>
       </c>
       <c r="CK28" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11668,13 +11668,13 @@
         <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV28" s="1">
         <v>239</v>
       </c>
       <c r="CW28" s="1">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -16260,7 +16260,7 @@
         <v>235</v>
       </c>
       <c r="C44" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2">
         <v>11</v>
@@ -16548,7 +16548,7 @@
         <v>50655</v>
       </c>
       <c r="CU44" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="CV44" s="1">
         <v>1972</v>
@@ -19113,7 +19113,7 @@
         <v>114</v>
       </c>
       <c r="AM53" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN53" s="2">
         <v>18</v>
@@ -19257,7 +19257,7 @@
         <v>145</v>
       </c>
       <c r="CI53" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CJ53" s="2">
         <v>20</v>
@@ -19293,7 +19293,7 @@
         <v>353</v>
       </c>
       <c r="CU53" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CV53" s="1">
         <v>40</v>
@@ -20178,7 +20178,7 @@
         <v>30</v>
       </c>
       <c r="CK56" s="2">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="CL56" s="1">
         <v>2</v>
@@ -20214,7 +20214,7 @@
         <v>118</v>
       </c>
       <c r="CW56" s="1">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20853,7 +20853,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="1">
         <v>31</v>
@@ -21129,7 +21129,7 @@
         <v>35</v>
       </c>
       <c r="CW59" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -22061,7 +22061,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22349,7 +22349,7 @@
         <v>94</v>
       </c>
       <c r="CW63" s="1">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22618,7 +22618,7 @@
         <v>21</v>
       </c>
       <c r="CK64" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="CL64" s="1">
         <v>10</v>
@@ -22654,7 +22654,7 @@
         <v>175</v>
       </c>
       <c r="CW64" s="1">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23586,7 +23586,7 @@
         <v>-29</v>
       </c>
       <c r="E68" s="2">
-        <v>-24</v>
+        <v>-26</v>
       </c>
       <c r="F68" s="1">
         <v>21</v>
@@ -23874,7 +23874,7 @@
         <v>8</v>
       </c>
       <c r="CW68" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24256,7 +24256,7 @@
         <v>0</v>
       </c>
       <c r="Y70" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="1">
         <v>0</v>
@@ -24316,7 +24316,7 @@
         <v>2</v>
       </c>
       <c r="AS70" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24448,7 +24448,7 @@
         <v>1</v>
       </c>
       <c r="CK70" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CL70" s="1">
         <v>44</v>
@@ -24484,7 +24484,7 @@
         <v>45</v>
       </c>
       <c r="CW70" s="1">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25416,7 +25416,7 @@
         <v>136</v>
       </c>
       <c r="E74" s="2">
-        <v>379</v>
+        <v>305</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25434,7 +25434,7 @@
         <v>10112</v>
       </c>
       <c r="K74" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2">
         <v>77</v>
@@ -25566,7 +25566,7 @@
         <v>15</v>
       </c>
       <c r="BC74" s="2">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BD74" s="2">
         <v>-4</v>
@@ -25662,7 +25662,7 @@
         <v>16207</v>
       </c>
       <c r="CI74" s="2">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="CJ74" s="2">
         <v>212</v>
@@ -25698,13 +25698,13 @@
         <v>171653</v>
       </c>
       <c r="CU74" s="1">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="CV74" s="1">
         <v>1815</v>
       </c>
       <c r="CW74" s="1">
-        <v>4401</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26583,7 +26583,7 @@
         <v>378</v>
       </c>
       <c r="CK77" s="2">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26619,7 +26619,7 @@
         <v>10247</v>
       </c>
       <c r="CW77" s="1">
-        <v>15942</v>
+        <v>15903</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27049,7 +27049,7 @@
         <v>2</v>
       </c>
       <c r="AO79" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP79" s="1">
         <v>35</v>
@@ -27067,7 +27067,7 @@
         <v>6</v>
       </c>
       <c r="AU79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV79" s="2">
         <v>3</v>
@@ -27193,7 +27193,7 @@
         <v>51</v>
       </c>
       <c r="CK79" s="2">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="CL79" s="1">
         <v>2</v>
@@ -27223,13 +27223,13 @@
         <v>90607</v>
       </c>
       <c r="CU79" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="CV79" s="1">
         <v>631</v>
       </c>
       <c r="CW79" s="1">
-        <v>1844</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27348,7 +27348,7 @@
         <v>794</v>
       </c>
       <c r="AM80" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AN80" s="2">
         <v>70</v>
@@ -27492,7 +27492,7 @@
         <v>809</v>
       </c>
       <c r="CI80" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CJ80" s="2">
         <v>67</v>
@@ -27528,7 +27528,7 @@
         <v>1764</v>
       </c>
       <c r="CU80" s="1">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="CV80" s="1">
         <v>144</v>
@@ -27569,7 +27569,7 @@
         <v>1578</v>
       </c>
       <c r="K81" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2">
         <v>42</v>
@@ -27833,7 +27833,7 @@
         <v>6407</v>
       </c>
       <c r="CU81" s="1">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="CV81" s="1">
         <v>130</v>
@@ -29698,7 +29698,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J88" s="1">
         <v>811</v>
@@ -29710,7 +29710,7 @@
         <v>29</v>
       </c>
       <c r="M88" s="2">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="N88" s="1">
         <v>1035</v>
@@ -29806,7 +29806,7 @@
         <v>3</v>
       </c>
       <c r="AS88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29938,7 +29938,7 @@
         <v>15</v>
       </c>
       <c r="CK88" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29974,7 +29974,7 @@
         <v>129</v>
       </c>
       <c r="CW88" s="1">
-        <v>440</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -29991,7 +29991,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1">
         <v>39</v>
@@ -30015,7 +30015,7 @@
         <v>27</v>
       </c>
       <c r="M89" s="2">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="N89" s="1">
         <v>48</v>
@@ -30279,7 +30279,7 @@
         <v>89</v>
       </c>
       <c r="CW89" s="1">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30721,7 +30721,7 @@
         <v>1</v>
       </c>
       <c r="AS91" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT91" s="1">
         <v>0</v>
@@ -30853,7 +30853,7 @@
         <v>82</v>
       </c>
       <c r="CK91" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30889,7 +30889,7 @@
         <v>413</v>
       </c>
       <c r="CW91" s="1">
-        <v>793</v>
+        <v>755</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -33980,7 +33980,7 @@
         <v>35</v>
       </c>
       <c r="M102" s="2">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="N102" s="1">
         <v>14647</v>
@@ -34244,7 +34244,7 @@
         <v>724</v>
       </c>
       <c r="CW102" s="1">
-        <v>1795</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34871,7 +34871,7 @@
         <v>0</v>
       </c>
       <c r="E105" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1">
         <v>6</v>
@@ -34895,7 +34895,7 @@
         <v>33</v>
       </c>
       <c r="M105" s="2">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="N105" s="1">
         <v>1428</v>
@@ -35075,7 +35075,7 @@
         <v>0</v>
       </c>
       <c r="BU105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV105" s="1">
         <v>4</v>
@@ -35159,7 +35159,7 @@
         <v>205</v>
       </c>
       <c r="CW105" s="1">
-        <v>506</v>
+        <v>477</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35200,7 +35200,7 @@
         <v>399</v>
       </c>
       <c r="M106" s="2">
-        <v>986</v>
+        <v>747</v>
       </c>
       <c r="N106" s="1">
         <v>22916</v>
@@ -35464,7 +35464,7 @@
         <v>1077</v>
       </c>
       <c r="CW106" s="1">
-        <v>2528</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36450,7 +36450,7 @@
         <v>9</v>
       </c>
       <c r="W110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X110" s="2">
         <v>1</v>
@@ -36678,7 +36678,7 @@
         <v>13336</v>
       </c>
       <c r="CU110" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CV110" s="1">
         <v>427</v>
@@ -36815,7 +36815,7 @@
         <v>45</v>
       </c>
       <c r="AQ111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR111" s="2">
         <v>1</v>
@@ -36947,7 +36947,7 @@
         <v>483</v>
       </c>
       <c r="CI111" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CJ111" s="2">
         <v>25</v>
@@ -36983,7 +36983,7 @@
         <v>776</v>
       </c>
       <c r="CU111" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CV111" s="1">
         <v>38</v>
@@ -37126,7 +37126,7 @@
         <v>2</v>
       </c>
       <c r="AS112" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT112" s="1">
         <v>0</v>
@@ -37294,7 +37294,7 @@
         <v>254</v>
       </c>
       <c r="CW112" s="1">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37563,7 +37563,7 @@
         <v>67</v>
       </c>
       <c r="CK113" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37599,7 +37599,7 @@
         <v>451</v>
       </c>
       <c r="CW113" s="1">
-        <v>9848</v>
+        <v>9843</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38220,7 +38220,7 @@
         <v>4427</v>
       </c>
       <c r="C116" s="2">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D116" s="2">
         <v>46</v>
@@ -38340,7 +38340,7 @@
         <v>28</v>
       </c>
       <c r="AQ116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR116" s="2">
         <v>1</v>
@@ -38508,7 +38508,7 @@
         <v>21750</v>
       </c>
       <c r="CU116" s="1">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="CV116" s="1">
         <v>378</v>
@@ -38531,7 +38531,7 @@
         <v>545</v>
       </c>
       <c r="E117" s="2">
-        <v>1039</v>
+        <v>916</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -38819,7 +38819,7 @@
         <v>592</v>
       </c>
       <c r="CW117" s="1">
-        <v>1215</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -41282,7 +41282,7 @@
         <v>64</v>
       </c>
       <c r="G126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="2">
         <v>3</v>
@@ -41558,7 +41558,7 @@
         <v>834</v>
       </c>
       <c r="CU126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV126" s="1">
         <v>14</v>
@@ -42299,7 +42299,7 @@
         <v>0</v>
       </c>
       <c r="AO129" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP129" s="1">
         <v>35</v>
@@ -42455,7 +42455,7 @@
         <v>0</v>
       </c>
       <c r="CO129" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP129" s="1">
         <v>0</v>
@@ -42479,7 +42479,7 @@
         <v>105</v>
       </c>
       <c r="CW129" s="1">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -43112,7 +43112,7 @@
         <v>39</v>
       </c>
       <c r="G132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" s="2">
         <v>2</v>
@@ -43388,7 +43388,7 @@
         <v>44</v>
       </c>
       <c r="CU132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV132" s="1">
         <v>2</v>
@@ -43740,7 +43740,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" s="1">
         <v>50045</v>
@@ -44004,7 +44004,7 @@
         <v>2535</v>
       </c>
       <c r="CW134" s="1">
-        <v>5799</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44039,13 +44039,13 @@
         <v>6539</v>
       </c>
       <c r="K135" s="2">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L135" s="2">
         <v>114</v>
       </c>
       <c r="M135" s="2">
-        <v>478</v>
+        <v>381</v>
       </c>
       <c r="N135" s="1">
         <v>32057</v>
@@ -44099,7 +44099,7 @@
         <v>11789</v>
       </c>
       <c r="AE135" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF135" s="2">
         <v>159</v>
@@ -44147,7 +44147,7 @@
         <v>22</v>
       </c>
       <c r="AU135" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV135" s="2">
         <v>2</v>
@@ -44303,13 +44303,13 @@
         <v>62643</v>
       </c>
       <c r="CU135" s="1">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="CV135" s="1">
         <v>941</v>
       </c>
       <c r="CW135" s="1">
-        <v>2726</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -47065,7 +47065,7 @@
         <v>662</v>
       </c>
       <c r="C145" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D145" s="2">
         <v>10</v>
@@ -47185,7 +47185,7 @@
         <v>78</v>
       </c>
       <c r="AQ145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR145" s="2">
         <v>3</v>
@@ -47317,7 +47317,7 @@
         <v>145</v>
       </c>
       <c r="CI145" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ145" s="2">
         <v>7</v>
@@ -47353,7 +47353,7 @@
         <v>2476</v>
       </c>
       <c r="CU145" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="CV145" s="1">
         <v>51</v>
@@ -47998,7 +47998,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="1">
         <v>1218</v>
@@ -48010,7 +48010,7 @@
         <v>19</v>
       </c>
       <c r="M148" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N148" s="1">
         <v>3253</v>
@@ -48106,7 +48106,7 @@
         <v>0</v>
       </c>
       <c r="AS148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT148" s="1">
         <v>0</v>
@@ -48238,7 +48238,7 @@
         <v>34</v>
       </c>
       <c r="CK148" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="CL148" s="1">
         <v>16</v>
@@ -48274,7 +48274,7 @@
         <v>108</v>
       </c>
       <c r="CW148" s="1">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -49320,7 +49320,7 @@
         <v>49</v>
       </c>
       <c r="AQ152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR152" s="2">
         <v>2</v>
@@ -49488,7 +49488,7 @@
         <v>3022</v>
       </c>
       <c r="CU152" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV152" s="1">
         <v>93</v>
@@ -50139,7 +50139,7 @@
         <v>557</v>
       </c>
       <c r="K155" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2">
         <v>13</v>
@@ -50241,7 +50241,7 @@
         <v>4</v>
       </c>
       <c r="AS155" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT155" s="1">
         <v>1</v>
@@ -50373,7 +50373,7 @@
         <v>16</v>
       </c>
       <c r="CK155" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CL155" s="1">
         <v>1</v>
@@ -50403,13 +50403,13 @@
         <v>2660</v>
       </c>
       <c r="CU155" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CV155" s="1">
         <v>56</v>
       </c>
       <c r="CW155" s="1">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -51036,7 +51036,7 @@
         <v>219</v>
       </c>
       <c r="E158" s="2">
-        <v>408</v>
+        <v>353</v>
       </c>
       <c r="F158" s="1">
         <v>2</v>
@@ -51324,7 +51324,7 @@
         <v>841</v>
       </c>
       <c r="CW158" s="1">
-        <v>1688</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51646,7 +51646,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160" s="1">
         <v>22</v>
@@ -51658,7 +51658,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J160" s="1">
         <v>0</v>
@@ -51934,7 +51934,7 @@
         <v>0</v>
       </c>
       <c r="CW160" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:101">
@@ -52986,7 +52986,7 @@
         <v>2</v>
       </c>
       <c r="AS164" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT164" s="1">
         <v>0</v>
@@ -53118,7 +53118,7 @@
         <v>6</v>
       </c>
       <c r="CK164" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CL164" s="1">
         <v>4</v>
@@ -53154,7 +53154,7 @@
         <v>106</v>
       </c>
       <c r="CW164" s="1">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53590,7 +53590,7 @@
         <v>84</v>
       </c>
       <c r="AQ166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR166" s="2">
         <v>2</v>
@@ -53722,7 +53722,7 @@
         <v>192</v>
       </c>
       <c r="CI166" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ166" s="2">
         <v>7</v>
@@ -53758,7 +53758,7 @@
         <v>5253</v>
       </c>
       <c r="CU166" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CV166" s="1">
         <v>105</v>
@@ -54332,7 +54332,7 @@
         <v>438</v>
       </c>
       <c r="CI168" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="CJ168" s="2">
         <v>24</v>
@@ -54368,7 +54368,7 @@
         <v>5956</v>
       </c>
       <c r="CU168" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CV168" s="1">
         <v>142</v>
@@ -54804,7 +54804,7 @@
         <v>3</v>
       </c>
       <c r="AO170" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AP170" s="1">
         <v>36</v>
@@ -54948,7 +54948,7 @@
         <v>62</v>
       </c>
       <c r="CK170" s="2">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="CL170" s="1">
         <v>17</v>
@@ -54984,7 +54984,7 @@
         <v>428</v>
       </c>
       <c r="CW170" s="1">
-        <v>1277</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -59893,7 +59893,7 @@
         <v>3</v>
       </c>
       <c r="I187" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J187" s="1">
         <v>0</v>
@@ -60169,7 +60169,7 @@
         <v>3</v>
       </c>
       <c r="CW187" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:101">
@@ -61137,7 +61137,7 @@
         <v>0</v>
       </c>
       <c r="Q191" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R191" s="1">
         <v>0</v>
@@ -61209,7 +61209,7 @@
         <v>6</v>
       </c>
       <c r="AO191" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP191" s="1">
         <v>37</v>
@@ -61389,7 +61389,7 @@
         <v>13</v>
       </c>
       <c r="CW191" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192" spans="1:101">
@@ -62040,7 +62040,7 @@
         <v>43</v>
       </c>
       <c r="M194" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="N194" s="1">
         <v>29177</v>
@@ -62304,7 +62304,7 @@
         <v>581</v>
       </c>
       <c r="CW194" s="1">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62746,7 +62746,7 @@
         <v>1</v>
       </c>
       <c r="AS196" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT196" s="1">
         <v>0</v>
@@ -62890,7 +62890,7 @@
         <v>0</v>
       </c>
       <c r="CO196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP196" s="1">
         <v>0</v>
@@ -62914,7 +62914,7 @@
         <v>88</v>
       </c>
       <c r="CW196" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -64175,7 +64175,7 @@
         <v>118</v>
       </c>
       <c r="M201" s="2">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="N201" s="1">
         <v>23253</v>
@@ -64259,7 +64259,7 @@
         <v>2</v>
       </c>
       <c r="AO201" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AP201" s="1">
         <v>25</v>
@@ -64403,7 +64403,7 @@
         <v>46</v>
       </c>
       <c r="CK201" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64439,7 +64439,7 @@
         <v>1993</v>
       </c>
       <c r="CW201" s="1">
-        <v>3162</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -67913,7 +67913,7 @@
         <v>75</v>
       </c>
       <c r="AM213" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN213" s="2">
         <v>6</v>
@@ -67931,7 +67931,7 @@
         <v>0</v>
       </c>
       <c r="AS213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT213" s="1">
         <v>0</v>
@@ -68063,7 +68063,7 @@
         <v>5</v>
       </c>
       <c r="CK213" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CL213" s="1">
         <v>0</v>
@@ -68093,13 +68093,13 @@
         <v>269</v>
       </c>
       <c r="CU213" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CV213" s="1">
         <v>19</v>
       </c>
       <c r="CW213" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -69534,7 +69534,7 @@
         <v>575</v>
       </c>
       <c r="D56">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E56" t="s">
         <v>715</v>
@@ -70077,7 +70077,7 @@
         <v>546</v>
       </c>
       <c r="D83">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E83" t="s">
         <v>715</v>
@@ -70543,7 +70543,7 @@
         <v>622</v>
       </c>
       <c r="D106">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E106" t="s">
         <v>715</v>
@@ -71326,7 +71326,7 @@
         <v>656</v>
       </c>
       <c r="D145">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E145" t="s">
         <v>715</v>
@@ -71386,7 +71386,7 @@
         <v>658</v>
       </c>
       <c r="D148">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>9</v>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="CW2" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:101">
@@ -3779,7 +3779,7 @@
         <v>4242</v>
       </c>
       <c r="K3" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
         <v>63</v>
@@ -3875,7 +3875,7 @@
         <v>76</v>
       </c>
       <c r="AQ3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="2">
         <v>2</v>
@@ -4007,7 +4007,7 @@
         <v>2060</v>
       </c>
       <c r="CI3" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CJ3" s="2">
         <v>50</v>
@@ -4043,7 +4043,7 @@
         <v>46682</v>
       </c>
       <c r="CU3" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="CV3" s="1">
         <v>812</v>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2">
         <v>8</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="M5" s="2">
         <v>100</v>
@@ -4614,16 +4614,16 @@
         <v>0</v>
       </c>
       <c r="CH5" s="1">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="CI5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ5" s="2">
         <v>2</v>
       </c>
       <c r="CK5" s="2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="CL5" s="1">
         <v>0</v>
@@ -4650,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38681</v>
+        <v>38682</v>
       </c>
       <c r="CU5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV5" s="1">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="CW5" s="1">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5705,7 +5705,7 @@
         <v>43</v>
       </c>
       <c r="AQ9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" s="2">
         <v>2</v>
@@ -5837,7 +5837,7 @@
         <v>491</v>
       </c>
       <c r="CI9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ9" s="2">
         <v>3</v>
@@ -5873,7 +5873,7 @@
         <v>2862</v>
       </c>
       <c r="CU9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CV9" s="1">
         <v>48</v>
@@ -7191,16 +7191,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="1">
-        <v>2016</v>
+        <v>1998</v>
       </c>
       <c r="AE14" s="2">
-        <v>-6</v>
+        <v>-24</v>
       </c>
       <c r="AF14" s="2">
-        <v>-2</v>
+        <v>-20</v>
       </c>
       <c r="AG14" s="2">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3181</v>
+        <v>3163</v>
       </c>
       <c r="CU14" s="1">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="CV14" s="1">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="CW14" s="1">
-        <v>288</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7810,7 +7810,7 @@
         <v>8</v>
       </c>
       <c r="AG16" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         <v>2</v>
       </c>
       <c r="AS16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT16" s="1">
         <v>0</v>
@@ -7990,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="CO16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP16" s="1">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
       <c r="CW16" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -8139,7 +8139,7 @@
         <v>6</v>
       </c>
       <c r="AO17" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP17" s="1">
         <v>29</v>
@@ -8283,7 +8283,7 @@
         <v>24</v>
       </c>
       <c r="CK17" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CL17" s="1">
         <v>29</v>
@@ -8319,7 +8319,7 @@
         <v>30</v>
       </c>
       <c r="CW17" s="1">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8946,7 +8946,7 @@
         <v>106</v>
       </c>
       <c r="E20" s="2">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -8964,13 +8964,13 @@
         <v>903</v>
       </c>
       <c r="K20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2">
         <v>19</v>
       </c>
       <c r="M20" s="2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N20" s="1">
         <v>12653</v>
@@ -9195,7 +9195,7 @@
         <v>11</v>
       </c>
       <c r="CJ20" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="CK20" s="2">
         <v>52</v>
@@ -9228,13 +9228,13 @@
         <v>20687</v>
       </c>
       <c r="CU20" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CV20" s="1">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="CW20" s="1">
-        <v>935</v>
+        <v>906</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9356,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="AN21" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="2">
         <v>2</v>
@@ -9500,7 +9500,7 @@
         <v>18</v>
       </c>
       <c r="CJ21" s="2">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="CK21" s="2">
         <v>60</v>
@@ -9536,7 +9536,7 @@
         <v>19</v>
       </c>
       <c r="CV21" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="CW21" s="1">
         <v>66</v>
@@ -10723,7 +10723,7 @@
         <v>11</v>
       </c>
       <c r="CK25" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CL25" s="1">
         <v>0</v>
@@ -10759,7 +10759,7 @@
         <v>11</v>
       </c>
       <c r="CW25" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:101">
@@ -10776,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1">
         <v>41</v>
@@ -10788,7 +10788,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
         <v>0</v>
@@ -11064,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="CW26" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:101">
@@ -11198,7 +11198,7 @@
         <v>0</v>
       </c>
       <c r="AR27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS27" s="2">
         <v>1</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="CJ27" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CK27" s="2">
         <v>34</v>
@@ -11366,7 +11366,7 @@
         <v>10</v>
       </c>
       <c r="CV27" s="1">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="CW27" s="1">
         <v>61</v>
@@ -11404,13 +11404,13 @@
         <v>955</v>
       </c>
       <c r="K28" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2">
         <v>24</v>
       </c>
       <c r="M28" s="2">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="N28" s="1">
         <v>2024</v>
@@ -11500,7 +11500,7 @@
         <v>69</v>
       </c>
       <c r="AQ28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR28" s="2">
         <v>2</v>
@@ -11632,7 +11632,7 @@
         <v>3012</v>
       </c>
       <c r="CI28" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ28" s="2">
         <v>13</v>
@@ -11668,13 +11668,13 @@
         <v>24074</v>
       </c>
       <c r="CU28" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CV28" s="1">
         <v>239</v>
       </c>
       <c r="CW28" s="1">
-        <v>774</v>
+        <v>755</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
@@ -11979,7 +11979,7 @@
         <v>0</v>
       </c>
       <c r="CW29" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:101">
@@ -12008,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J30" s="1">
         <v>0</v>
@@ -12284,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="CW30" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:101">
@@ -12412,16 +12412,16 @@
         <v>23</v>
       </c>
       <c r="AP31" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT31" s="1">
         <v>1</v>
@@ -12544,16 +12544,16 @@
         <v>0</v>
       </c>
       <c r="CH31" s="1">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="CI31" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="CJ31" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="CK31" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12580,16 +12580,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>6004</v>
+        <v>6012</v>
       </c>
       <c r="CU31" s="1">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="CV31" s="1">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="CW31" s="1">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12606,7 +12606,7 @@
         <v>52</v>
       </c>
       <c r="E32" s="2">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -12744,7 +12744,7 @@
         <v>25</v>
       </c>
       <c r="AY32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ32" s="2">
         <v>1</v>
@@ -12888,13 +12888,13 @@
         <v>11125</v>
       </c>
       <c r="CU32" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CV32" s="1">
         <v>223</v>
       </c>
       <c r="CW32" s="1">
-        <v>561</v>
+        <v>537</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13234,13 +13234,13 @@
         <v>499</v>
       </c>
       <c r="K34" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2">
         <v>24</v>
       </c>
       <c r="M34" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N34" s="1">
         <v>1429</v>
@@ -13327,16 +13327,16 @@
         <v>5</v>
       </c>
       <c r="AP34" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AQ34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -13459,16 +13459,16 @@
         <v>0</v>
       </c>
       <c r="CH34" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="CI34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ34" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CK34" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CL34" s="1">
         <v>26</v>
@@ -13495,16 +13495,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="CU34" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CV34" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="CW34" s="1">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -13533,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
@@ -13809,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="CW35" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:101">
@@ -14143,7 +14143,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J37" s="1">
         <v>0</v>
@@ -14419,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="CW37" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:101">
@@ -14436,7 +14436,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14724,7 +14724,7 @@
         <v>36</v>
       </c>
       <c r="CW38" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14849,7 +14849,7 @@
         <v>11</v>
       </c>
       <c r="AO39" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP39" s="1">
         <v>14</v>
@@ -14993,7 +14993,7 @@
         <v>60</v>
       </c>
       <c r="CK39" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="CL39" s="1">
         <v>2</v>
@@ -15029,7 +15029,7 @@
         <v>76</v>
       </c>
       <c r="CW39" s="1">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15037,16 +15037,16 @@
         <v>139</v>
       </c>
       <c r="B40" s="1">
-        <v>8830</v>
+        <v>8828</v>
       </c>
       <c r="C40" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D40" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>115</v>
       </c>
       <c r="M40" s="2">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="N40" s="1">
         <v>16656</v>
@@ -15130,7 +15130,7 @@
         <v>413</v>
       </c>
       <c r="AG40" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15325,16 +15325,16 @@
         <v>0</v>
       </c>
       <c r="CT40" s="1">
-        <v>53489</v>
+        <v>53487</v>
       </c>
       <c r="CU40" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CV40" s="1">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="CW40" s="1">
-        <v>2174</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -15668,7 +15668,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
@@ -15944,7 +15944,7 @@
         <v>0</v>
       </c>
       <c r="CW42" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:101">
@@ -16075,7 +16075,7 @@
         <v>89</v>
       </c>
       <c r="AQ43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR43" s="2">
         <v>3</v>
@@ -16219,7 +16219,7 @@
         <v>80</v>
       </c>
       <c r="CM43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN43" s="2">
         <v>3</v>
@@ -16243,7 +16243,7 @@
         <v>567</v>
       </c>
       <c r="CU43" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV43" s="1">
         <v>26</v>
@@ -16365,16 +16365,16 @@
         <v>0</v>
       </c>
       <c r="AL44" s="1">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM44" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN44" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO44" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP44" s="1">
         <v>61</v>
@@ -16521,16 +16521,16 @@
         <v>33</v>
       </c>
       <c r="CL44" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CM44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP44" s="1">
         <v>0</v>
@@ -16545,16 +16545,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50655</v>
+        <v>50657</v>
       </c>
       <c r="CU44" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CV44" s="1">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="CW44" s="1">
-        <v>2454</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -16583,7 +16583,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
@@ -16859,7 +16859,7 @@
         <v>0</v>
       </c>
       <c r="CW45" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:101">
@@ -18216,7 +18216,7 @@
         <v>1</v>
       </c>
       <c r="AS50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>23</v>
       </c>
       <c r="CK50" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="CL50" s="1">
         <v>0</v>
@@ -18384,7 +18384,7 @@
         <v>40</v>
       </c>
       <c r="CW50" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -18814,7 +18814,7 @@
         <v>4</v>
       </c>
       <c r="AO52" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP52" s="1">
         <v>0</v>
@@ -18949,16 +18949,16 @@
         <v>0</v>
       </c>
       <c r="CH52" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="CI52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CK52" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CL52" s="1">
         <v>0</v>
@@ -18985,16 +18985,16 @@
         <v>0</v>
       </c>
       <c r="CT52" s="1">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CU52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV52" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CW52" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:101">
@@ -19427,16 +19427,16 @@
         <v>4</v>
       </c>
       <c r="AP54" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -19559,16 +19559,16 @@
         <v>0</v>
       </c>
       <c r="CH54" s="1">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ54" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CK54" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CL54" s="1">
         <v>8</v>
@@ -19595,16 +19595,16 @@
         <v>0</v>
       </c>
       <c r="CT54" s="1">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="CU54" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CV54" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CW54" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -19920,7 +19920,7 @@
         <v>2047</v>
       </c>
       <c r="C56" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2">
         <v>17</v>
@@ -19944,7 +19944,7 @@
         <v>1532</v>
       </c>
       <c r="K56" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2">
         <v>14</v>
@@ -20208,7 +20208,7 @@
         <v>7796</v>
       </c>
       <c r="CU56" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="CV56" s="1">
         <v>118</v>
@@ -20847,7 +20847,7 @@
         <v>33</v>
       </c>
       <c r="G59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>1</v>
@@ -21123,7 +21123,7 @@
         <v>862</v>
       </c>
       <c r="CU59" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV59" s="1">
         <v>35</v>
@@ -21472,7 +21472,7 @@
         <v>14</v>
       </c>
       <c r="L61" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M61" s="2">
         <v>51</v>
@@ -21535,7 +21535,7 @@
         <v>0</v>
       </c>
       <c r="AG61" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AH61" s="1">
         <v>23</v>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="AN61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO61" s="2">
         <v>3</v>
@@ -21565,7 +21565,7 @@
         <v>37</v>
       </c>
       <c r="AQ61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR61" s="2">
         <v>1</v>
@@ -21697,10 +21697,10 @@
         <v>5332</v>
       </c>
       <c r="CI61" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CJ61" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CK61" s="2">
         <v>86</v>
@@ -21733,13 +21733,13 @@
         <v>65908</v>
       </c>
       <c r="CU61" s="1">
-        <v>6</v>
+        <v>-9</v>
       </c>
       <c r="CV61" s="1">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="CW61" s="1">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22202,7 +22202,7 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA63" s="2">
         <v>1</v>
@@ -22346,7 +22346,7 @@
         <v>17</v>
       </c>
       <c r="CV63" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="CW63" s="1">
         <v>170</v>
@@ -22366,7 +22366,7 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1">
         <v>18</v>
@@ -22390,19 +22390,19 @@
         <v>5</v>
       </c>
       <c r="M64" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N64" s="1">
-        <v>4319</v>
+        <v>4322</v>
       </c>
       <c r="O64" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P64" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q64" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8014</v>
+        <v>8017</v>
       </c>
       <c r="CU64" s="1">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="CV64" s="1">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CW64" s="1">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22701,7 +22701,7 @@
         <v>58956</v>
       </c>
       <c r="O65" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P65" s="2">
         <v>1631</v>
@@ -22773,7 +22773,7 @@
         <v>101</v>
       </c>
       <c r="AM65" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN65" s="2">
         <v>4</v>
@@ -22914,16 +22914,16 @@
         <v>0</v>
       </c>
       <c r="CH65" s="1">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="CI65" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CJ65" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CK65" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67200</v>
+        <v>67204</v>
       </c>
       <c r="CU65" s="1">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="CV65" s="1">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="CW65" s="1">
-        <v>3526</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -24307,16 +24307,16 @@
         <v>0</v>
       </c>
       <c r="AP70" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS70" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24439,16 +24439,16 @@
         <v>0</v>
       </c>
       <c r="CH70" s="1">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="CI70" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CJ70" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CK70" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CL70" s="1">
         <v>44</v>
@@ -24475,16 +24475,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="CU70" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CV70" s="1">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="CW70" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24917,16 +24917,16 @@
         <v>0</v>
       </c>
       <c r="AP72" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR72" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS72" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT72" s="1">
         <v>0</v>
@@ -25049,16 +25049,16 @@
         <v>0</v>
       </c>
       <c r="CH72" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="CI72" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ72" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK72" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CL72" s="1">
         <v>0</v>
@@ -25085,16 +25085,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="CU72" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CV72" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="CW72" s="1">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25413,7 +25413,7 @@
         <v>35</v>
       </c>
       <c r="D74" s="2">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="E74" s="2">
         <v>305</v>
@@ -25521,7 +25521,7 @@
         <v>48</v>
       </c>
       <c r="AN74" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AO74" s="2">
         <v>383</v>
@@ -25665,10 +25665,10 @@
         <v>66</v>
       </c>
       <c r="CJ74" s="2">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="CK74" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,10 +25701,10 @@
         <v>149</v>
       </c>
       <c r="CV74" s="1">
-        <v>1815</v>
+        <v>1714</v>
       </c>
       <c r="CW74" s="1">
-        <v>4327</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26047,7 +26047,7 @@
         <v>68</v>
       </c>
       <c r="L76" s="2">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="M76" s="2">
         <v>326</v>
@@ -26311,7 +26311,7 @@
         <v>160</v>
       </c>
       <c r="CV76" s="1">
-        <v>1369</v>
+        <v>1297</v>
       </c>
       <c r="CW76" s="1">
         <v>3699</v>
@@ -26328,7 +26328,7 @@
         <v>21</v>
       </c>
       <c r="D77" s="2">
-        <v>-6</v>
+        <v>34</v>
       </c>
       <c r="E77" s="2">
         <v>-4395</v>
@@ -26349,7 +26349,7 @@
         <v>4878</v>
       </c>
       <c r="K77" s="2">
-        <v>43</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="2">
         <v>181</v>
@@ -26439,7 +26439,7 @@
         <v>47</v>
       </c>
       <c r="AO77" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26580,10 +26580,10 @@
         <v>146</v>
       </c>
       <c r="CJ77" s="2">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="CK77" s="2">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26613,13 +26613,13 @@
         <v>390934</v>
       </c>
       <c r="CU77" s="1">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="CV77" s="1">
-        <v>10247</v>
+        <v>10252</v>
       </c>
       <c r="CW77" s="1">
-        <v>15903</v>
+        <v>15875</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26642,7 +26642,7 @@
         <v>28</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
         <v>2</v>
@@ -26741,7 +26741,7 @@
         <v>0</v>
       </c>
       <c r="AN78" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AO78" s="2">
         <v>33</v>
@@ -26882,10 +26882,10 @@
         <v>144</v>
       </c>
       <c r="CI78" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ78" s="2">
         <v>4</v>
-      </c>
-      <c r="CJ78" s="2">
-        <v>46</v>
       </c>
       <c r="CK78" s="2">
         <v>73</v>
@@ -26918,10 +26918,10 @@
         <v>259</v>
       </c>
       <c r="CU78" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CV78" s="1">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="CW78" s="1">
         <v>111</v>
@@ -26932,16 +26932,16 @@
         <v>178</v>
       </c>
       <c r="B79" s="1">
-        <v>4278</v>
+        <v>4285</v>
       </c>
       <c r="C79" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D79" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E79" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -26965,7 +26965,7 @@
         <v>131</v>
       </c>
       <c r="M79" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27058,7 +27058,7 @@
         <v>0</v>
       </c>
       <c r="AR79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS79" s="2">
         <v>2</v>
@@ -27190,7 +27190,7 @@
         <v>22</v>
       </c>
       <c r="CJ79" s="2">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="CK79" s="2">
         <v>124</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90607</v>
+        <v>90614</v>
       </c>
       <c r="CU79" s="1">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="CV79" s="1">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="CW79" s="1">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27354,7 +27354,7 @@
         <v>70</v>
       </c>
       <c r="AO80" s="2">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27498,7 +27498,7 @@
         <v>67</v>
       </c>
       <c r="CK80" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27534,7 +27534,7 @@
         <v>144</v>
       </c>
       <c r="CW80" s="1">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27653,7 +27653,7 @@
         <v>45</v>
       </c>
       <c r="AM81" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN81" s="2">
         <v>4</v>
@@ -27797,7 +27797,7 @@
         <v>155</v>
       </c>
       <c r="CI81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ81" s="2">
         <v>2</v>
@@ -27833,7 +27833,7 @@
         <v>6407</v>
       </c>
       <c r="CU81" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CV81" s="1">
         <v>130</v>
@@ -28179,10 +28179,10 @@
         <v>8638</v>
       </c>
       <c r="K83" s="2">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="M83" s="2">
         <v>379</v>
@@ -28443,10 +28443,10 @@
         <v>423860</v>
       </c>
       <c r="CU83" s="1">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="CV83" s="1">
-        <v>955</v>
+        <v>881</v>
       </c>
       <c r="CW83" s="1">
         <v>5384</v>
@@ -28777,13 +28777,13 @@
         <v>72</v>
       </c>
       <c r="G85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="2">
         <v>3</v>
       </c>
       <c r="I85" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J85" s="1">
         <v>0</v>
@@ -29053,13 +29053,13 @@
         <v>407</v>
       </c>
       <c r="CU85" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV85" s="1">
         <v>29</v>
       </c>
       <c r="CW85" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29073,7 +29073,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
@@ -29361,7 +29361,7 @@
         <v>2</v>
       </c>
       <c r="CV86" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="CW86" s="1">
         <v>73</v>
@@ -29486,7 +29486,7 @@
         <v>1</v>
       </c>
       <c r="AN87" s="2">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AO87" s="2">
         <v>5</v>
@@ -29630,7 +29630,7 @@
         <v>23</v>
       </c>
       <c r="CJ87" s="2">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="CK87" s="2">
         <v>88</v>
@@ -29666,7 +29666,7 @@
         <v>24</v>
       </c>
       <c r="CV87" s="1">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="CW87" s="1">
         <v>97</v>
@@ -30601,7 +30601,7 @@
         <v>110</v>
       </c>
       <c r="E91" s="2">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -30622,7 +30622,7 @@
         <v>53</v>
       </c>
       <c r="L91" s="2">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="M91" s="2">
         <v>305</v>
@@ -30886,10 +30886,10 @@
         <v>75</v>
       </c>
       <c r="CV91" s="1">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="CW91" s="1">
-        <v>755</v>
+        <v>724</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -30900,7 +30900,7 @@
         <v>269</v>
       </c>
       <c r="C92" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2">
         <v>5</v>
@@ -30909,13 +30909,13 @@
         <v>14</v>
       </c>
       <c r="F92" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="2">
         <v>1</v>
@@ -31014,7 +31014,7 @@
         <v>4</v>
       </c>
       <c r="AO92" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP92" s="1">
         <v>33</v>
@@ -31158,7 +31158,7 @@
         <v>11</v>
       </c>
       <c r="CK92" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CL92" s="1">
         <v>25</v>
@@ -31185,16 +31185,16 @@
         <v>0</v>
       </c>
       <c r="CT92" s="1">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="CU92" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV92" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CW92" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31454,16 +31454,16 @@
         <v>0</v>
       </c>
       <c r="CH93" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CI93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ93" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CK93" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CL93" s="1">
         <v>36</v>
@@ -31490,16 +31490,16 @@
         <v>0</v>
       </c>
       <c r="CT93" s="1">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="CU93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV93" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CW93" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -32674,16 +32674,16 @@
         <v>0</v>
       </c>
       <c r="CH97" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CI97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ97" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CK97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32710,16 +32710,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="CU97" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV97" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CW97" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33454,7 +33454,7 @@
         <v>10</v>
       </c>
       <c r="AO100" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP100" s="1">
         <v>0</v>
@@ -33598,7 +33598,7 @@
         <v>9</v>
       </c>
       <c r="CK100" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CL100" s="1">
         <v>0</v>
@@ -33634,7 +33634,7 @@
         <v>22</v>
       </c>
       <c r="CW100" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33956,7 +33956,7 @@
         <v>372</v>
       </c>
       <c r="E102" s="2">
-        <v>806</v>
+        <v>665</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -34055,16 +34055,16 @@
         <v>0</v>
       </c>
       <c r="AL102" s="1">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN102" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO102" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP102" s="1">
         <v>36</v>
@@ -34199,16 +34199,16 @@
         <v>0</v>
       </c>
       <c r="CH102" s="1">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="CI102" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ102" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="CK102" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="CL102" s="1">
         <v>9</v>
@@ -34235,16 +34235,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>43024</v>
+        <v>43028</v>
       </c>
       <c r="CU102" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="CV102" s="1">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="CW102" s="1">
-        <v>1752</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -35170,7 +35170,7 @@
         <v>9449</v>
       </c>
       <c r="C106" s="2">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="D106" s="2">
         <v>192</v>
@@ -35278,10 +35278,10 @@
         <v>559</v>
       </c>
       <c r="AM106" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN106" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO106" s="2">
         <v>17</v>
@@ -35422,10 +35422,10 @@
         <v>6442</v>
       </c>
       <c r="CI106" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CJ106" s="2">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="CK106" s="2">
         <v>324</v>
@@ -35458,10 +35458,10 @@
         <v>92607</v>
       </c>
       <c r="CU106" s="1">
-        <v>311</v>
+        <v>183</v>
       </c>
       <c r="CV106" s="1">
-        <v>1077</v>
+        <v>1015</v>
       </c>
       <c r="CW106" s="1">
         <v>2289</v>
@@ -35894,7 +35894,7 @@
         <v>0</v>
       </c>
       <c r="AO108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP108" s="1">
         <v>13</v>
@@ -36038,7 +36038,7 @@
         <v>11</v>
       </c>
       <c r="CK108" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CL108" s="1">
         <v>7</v>
@@ -36074,7 +36074,7 @@
         <v>25</v>
       </c>
       <c r="CW108" s="1">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36417,22 +36417,22 @@
         <v>88</v>
       </c>
       <c r="L110" s="2">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M110" s="2">
         <v>364</v>
       </c>
       <c r="N110" s="1">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="O110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q110" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R110" s="1">
         <v>0</v>
@@ -36675,16 +36675,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13336</v>
+        <v>13337</v>
       </c>
       <c r="CU110" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CV110" s="1">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="CW110" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36806,7 +36806,7 @@
         <v>0</v>
       </c>
       <c r="AN111" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AO111" s="2">
         <v>13</v>
@@ -36950,7 +36950,7 @@
         <v>0</v>
       </c>
       <c r="CJ111" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CK111" s="2">
         <v>51</v>
@@ -36986,7 +36986,7 @@
         <v>1</v>
       </c>
       <c r="CV111" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="CW111" s="1">
         <v>73</v>
@@ -37006,7 +37006,7 @@
         <v>25</v>
       </c>
       <c r="E112" s="2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37021,16 +37021,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="1">
-        <v>1119</v>
+        <v>1131</v>
       </c>
       <c r="K112" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L112" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M112" s="2">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="N112" s="1">
         <v>5612</v>
@@ -37285,13 +37285,13 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8282</v>
+        <v>8294</v>
       </c>
       <c r="CU112" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="CV112" s="1">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="CW112" s="1">
         <v>644</v>
@@ -38244,10 +38244,10 @@
         <v>4904</v>
       </c>
       <c r="K116" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="M116" s="2">
         <v>239</v>
@@ -38508,10 +38508,10 @@
         <v>21750</v>
       </c>
       <c r="CU116" s="1">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="CV116" s="1">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="CW116" s="1">
         <v>1088</v>
@@ -38648,10 +38648,10 @@
         <v>1</v>
       </c>
       <c r="AR117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS117" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT117" s="1">
         <v>0</v>
@@ -38780,7 +38780,7 @@
         <v>2</v>
       </c>
       <c r="CJ117" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK117" s="2">
         <v>11</v>
@@ -38795,7 +38795,7 @@
         <v>1</v>
       </c>
       <c r="CO117" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP117" s="1">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>7</v>
       </c>
       <c r="CV117" s="1">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="CW117" s="1">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -40373,7 +40373,7 @@
         <v>3</v>
       </c>
       <c r="I123" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J123" s="1">
         <v>142</v>
@@ -40565,7 +40565,7 @@
         <v>1</v>
       </c>
       <c r="BU123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV123" s="1">
         <v>0</v>
@@ -40649,7 +40649,7 @@
         <v>13</v>
       </c>
       <c r="CW123" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -41279,16 +41279,16 @@
         <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2">
         <v>3</v>
       </c>
       <c r="I126" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J126" s="1">
         <v>0</v>
@@ -41513,7 +41513,7 @@
         <v>0</v>
       </c>
       <c r="CF126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG126" s="2">
         <v>1</v>
@@ -41555,16 +41555,16 @@
         <v>0</v>
       </c>
       <c r="CT126" s="1">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="CU126" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV126" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW126" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:101">
@@ -41680,16 +41680,16 @@
         <v>0</v>
       </c>
       <c r="AL127" s="1">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="AM127" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN127" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AO127" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AP127" s="1">
         <v>0</v>
@@ -41824,16 +41824,16 @@
         <v>0</v>
       </c>
       <c r="CH127" s="1">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="CI127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ127" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CK127" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CL127" s="1">
         <v>1</v>
@@ -41860,16 +41860,16 @@
         <v>0</v>
       </c>
       <c r="CT127" s="1">
-        <v>2585</v>
+        <v>2591</v>
       </c>
       <c r="CU127" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="CV127" s="1">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="CW127" s="1">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -42305,7 +42305,7 @@
         <v>35</v>
       </c>
       <c r="AQ129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR129" s="2">
         <v>3</v>
@@ -42437,7 +42437,7 @@
         <v>498</v>
       </c>
       <c r="CI129" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ129" s="2">
         <v>22</v>
@@ -42473,7 +42473,7 @@
         <v>3563</v>
       </c>
       <c r="CU129" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CV129" s="1">
         <v>105</v>
@@ -42598,10 +42598,10 @@
         <v>152</v>
       </c>
       <c r="AM130" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN130" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO130" s="2">
         <v>29</v>
@@ -42742,10 +42742,10 @@
         <v>218</v>
       </c>
       <c r="CI130" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ130" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CK130" s="2">
         <v>34</v>
@@ -42778,10 +42778,10 @@
         <v>1093</v>
       </c>
       <c r="CU130" s="1">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="CV130" s="1">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="CW130" s="1">
         <v>228</v>
@@ -43118,7 +43118,7 @@
         <v>2</v>
       </c>
       <c r="I132" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J132" s="1">
         <v>0</v>
@@ -43394,7 +43394,7 @@
         <v>2</v>
       </c>
       <c r="CW132" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:101">
@@ -43420,10 +43420,10 @@
         <v>1</v>
       </c>
       <c r="H133" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I133" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J133" s="1">
         <v>0</v>
@@ -43696,10 +43696,10 @@
         <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW133" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:101">
@@ -43791,16 +43791,16 @@
         <v>6</v>
       </c>
       <c r="AD134" s="1">
-        <v>79709</v>
+        <v>79708</v>
       </c>
       <c r="AE134" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AF134" s="2">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AG134" s="2">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="AH134" s="1">
         <v>0</v>
@@ -43995,16 +43995,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>134456</v>
+        <v>134455</v>
       </c>
       <c r="CU134" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV134" s="1">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="CW134" s="1">
-        <v>5798</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44018,10 +44018,10 @@
         <v>42</v>
       </c>
       <c r="D135" s="2">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="E135" s="2">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -44126,7 +44126,7 @@
         <v>0</v>
       </c>
       <c r="AN135" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO135" s="2">
         <v>4</v>
@@ -44267,10 +44267,10 @@
         <v>3161</v>
       </c>
       <c r="CI135" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="CJ135" s="2">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="CK135" s="2">
         <v>141</v>
@@ -44303,13 +44303,13 @@
         <v>62643</v>
       </c>
       <c r="CU135" s="1">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="CV135" s="1">
-        <v>941</v>
+        <v>868</v>
       </c>
       <c r="CW135" s="1">
-        <v>2629</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44655,7 +44655,7 @@
         <v>6</v>
       </c>
       <c r="M137" s="2">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="N137" s="1">
         <v>153</v>
@@ -44919,7 +44919,7 @@
         <v>22</v>
       </c>
       <c r="CW137" s="1">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -44960,7 +44960,7 @@
         <v>28</v>
       </c>
       <c r="M138" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N138" s="1">
         <v>2200</v>
@@ -45035,16 +45035,16 @@
         <v>0</v>
       </c>
       <c r="AL138" s="1">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AM138" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN138" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO138" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP138" s="1">
         <v>24</v>
@@ -45191,16 +45191,16 @@
         <v>12</v>
       </c>
       <c r="CL138" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN138" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO138" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP138" s="1">
         <v>0</v>
@@ -45215,16 +45215,16 @@
         <v>0</v>
       </c>
       <c r="CT138" s="1">
-        <v>4404</v>
+        <v>4407</v>
       </c>
       <c r="CU138" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CV138" s="1">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="CW138" s="1">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -45555,10 +45555,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J140" s="1">
         <v>55</v>
@@ -45663,10 +45663,10 @@
         <v>0</v>
       </c>
       <c r="AR140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS140" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT140" s="1">
         <v>0</v>
@@ -45795,7 +45795,7 @@
         <v>0</v>
       </c>
       <c r="CJ140" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CK140" s="2">
         <v>3</v>
@@ -45810,7 +45810,7 @@
         <v>2</v>
       </c>
       <c r="CO140" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP140" s="1">
         <v>0</v>
@@ -45831,10 +45831,10 @@
         <v>3</v>
       </c>
       <c r="CV140" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CW140" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -45845,13 +45845,13 @@
         <v>82</v>
       </c>
       <c r="C141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" s="2">
         <v>4</v>
       </c>
       <c r="E141" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1">
         <v>49</v>
@@ -46133,13 +46133,13 @@
         <v>585</v>
       </c>
       <c r="CU141" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV141" s="1">
         <v>15</v>
       </c>
       <c r="CW141" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46267,16 +46267,16 @@
         <v>4</v>
       </c>
       <c r="AP142" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AQ142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT142" s="1">
         <v>14</v>
@@ -46399,16 +46399,16 @@
         <v>0</v>
       </c>
       <c r="CH142" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="CI142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL142" s="1">
         <v>48</v>
@@ -46435,16 +46435,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="CU142" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CV142" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="CW142" s="1">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46470,7 +46470,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I143" s="2">
         <v>4</v>
@@ -46578,7 +46578,7 @@
         <v>0</v>
       </c>
       <c r="AR143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS143" s="2">
         <v>4</v>
@@ -46722,7 +46722,7 @@
         <v>0</v>
       </c>
       <c r="CN143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO143" s="2">
         <v>2</v>
@@ -46746,7 +46746,7 @@
         <v>4</v>
       </c>
       <c r="CV143" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CW143" s="1">
         <v>20</v>
@@ -46970,7 +46970,7 @@
         <v>0</v>
       </c>
       <c r="BU144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV144" s="1">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>21</v>
       </c>
       <c r="CW144" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47179,7 +47179,7 @@
         <v>0</v>
       </c>
       <c r="AO145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP145" s="1">
         <v>78</v>
@@ -47206,16 +47206,16 @@
         <v>0</v>
       </c>
       <c r="AX145" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AY145" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ145" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA145" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB145" s="1">
         <v>0</v>
@@ -47335,7 +47335,7 @@
         <v>1</v>
       </c>
       <c r="CO145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP145" s="1">
         <v>0</v>
@@ -47350,13 +47350,13 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="CU145" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV145" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="CW145" s="1">
         <v>129</v>
@@ -47783,7 +47783,7 @@
         <v>4</v>
       </c>
       <c r="AM147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN147" s="2">
         <v>1</v>
@@ -47963,7 +47963,7 @@
         <v>222</v>
       </c>
       <c r="CU147" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV147" s="1">
         <v>13</v>
@@ -48121,16 +48121,16 @@
         <v>0</v>
       </c>
       <c r="AX148" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB148" s="1">
         <v>15</v>
@@ -48265,16 +48265,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="CU148" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV148" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CW148" s="1">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48710,10 +48710,10 @@
         <v>86</v>
       </c>
       <c r="AQ150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR150" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS150" s="2">
         <v>5</v>
@@ -48842,7 +48842,7 @@
         <v>127</v>
       </c>
       <c r="CI150" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ150" s="2">
         <v>2</v>
@@ -48857,7 +48857,7 @@
         <v>0</v>
       </c>
       <c r="CN150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO150" s="2">
         <v>3</v>
@@ -48878,10 +48878,10 @@
         <v>308</v>
       </c>
       <c r="CU150" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV150" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CW150" s="1">
         <v>13</v>
@@ -49006,7 +49006,7 @@
         <v>0</v>
       </c>
       <c r="AN151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO151" s="2">
         <v>3</v>
@@ -49015,10 +49015,10 @@
         <v>63</v>
       </c>
       <c r="AQ151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS151" s="2">
         <v>4</v>
@@ -49147,10 +49147,10 @@
         <v>142</v>
       </c>
       <c r="CI151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ151" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK151" s="2">
         <v>13</v>
@@ -49162,7 +49162,7 @@
         <v>0</v>
       </c>
       <c r="CN151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO151" s="2">
         <v>1</v>
@@ -49183,10 +49183,10 @@
         <v>456</v>
       </c>
       <c r="CU151" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV151" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CW151" s="1">
         <v>39</v>
@@ -49452,7 +49452,7 @@
         <v>182</v>
       </c>
       <c r="CI152" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ152" s="2">
         <v>9</v>
@@ -49488,7 +49488,7 @@
         <v>3022</v>
       </c>
       <c r="CU152" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CV152" s="1">
         <v>93</v>
@@ -50133,7 +50133,7 @@
         <v>3</v>
       </c>
       <c r="I155" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J155" s="1">
         <v>557</v>
@@ -50142,10 +50142,10 @@
         <v>0</v>
       </c>
       <c r="L155" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M155" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N155" s="1">
         <v>1204</v>
@@ -50238,7 +50238,7 @@
         <v>1</v>
       </c>
       <c r="AR155" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS155" s="2">
         <v>5</v>
@@ -50370,7 +50370,7 @@
         <v>4</v>
       </c>
       <c r="CJ155" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CK155" s="2">
         <v>17</v>
@@ -50382,7 +50382,7 @@
         <v>0</v>
       </c>
       <c r="CN155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO155" s="2">
         <v>1</v>
@@ -50406,10 +50406,10 @@
         <v>6</v>
       </c>
       <c r="CV155" s="1">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="CW155" s="1">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50725,13 +50725,13 @@
         <v>4973</v>
       </c>
       <c r="C157" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D157" s="2">
         <v>71</v>
       </c>
       <c r="E157" s="2">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -50749,13 +50749,13 @@
         <v>3472</v>
       </c>
       <c r="K157" s="2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L157" s="2">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="M157" s="2">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="N157" s="1">
         <v>11983</v>
@@ -50851,7 +50851,7 @@
         <v>2</v>
       </c>
       <c r="AS157" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT157" s="1">
         <v>41</v>
@@ -50983,7 +50983,7 @@
         <v>122</v>
       </c>
       <c r="CK157" s="2">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="CL157" s="1">
         <v>9</v>
@@ -51013,13 +51013,13 @@
         <v>166337</v>
       </c>
       <c r="CU157" s="1">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="CV157" s="1">
-        <v>5248</v>
+        <v>5190</v>
       </c>
       <c r="CW157" s="1">
-        <v>9210</v>
+        <v>9102</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51033,7 +51033,7 @@
         <v>82</v>
       </c>
       <c r="D158" s="2">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="E158" s="2">
         <v>353</v>
@@ -51057,10 +51057,10 @@
         <v>68</v>
       </c>
       <c r="L158" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M158" s="2">
-        <v>456</v>
+        <v>379</v>
       </c>
       <c r="N158" s="1">
         <v>3024</v>
@@ -51144,7 +51144,7 @@
         <v>20</v>
       </c>
       <c r="AO158" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AP158" s="1">
         <v>3</v>
@@ -51288,7 +51288,7 @@
         <v>319</v>
       </c>
       <c r="CK158" s="2">
-        <v>614</v>
+        <v>546</v>
       </c>
       <c r="CL158" s="1">
         <v>0</v>
@@ -51321,10 +51321,10 @@
         <v>290</v>
       </c>
       <c r="CV158" s="1">
-        <v>841</v>
+        <v>763</v>
       </c>
       <c r="CW158" s="1">
-        <v>1633</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51951,7 +51951,7 @@
         <v>51</v>
       </c>
       <c r="E161" s="2">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F161" s="1">
         <v>2</v>
@@ -51975,7 +51975,7 @@
         <v>86</v>
       </c>
       <c r="M161" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="N161" s="1">
         <v>10033</v>
@@ -52050,16 +52050,16 @@
         <v>0</v>
       </c>
       <c r="AL161" s="1">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM161" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN161" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO161" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP161" s="1">
         <v>35</v>
@@ -52194,16 +52194,16 @@
         <v>0</v>
       </c>
       <c r="CH161" s="1">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="CI161" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ161" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CK161" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="CL161" s="1">
         <v>14</v>
@@ -52230,16 +52230,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22379</v>
+        <v>22386</v>
       </c>
       <c r="CU161" s="1">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="CV161" s="1">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="CW161" s="1">
-        <v>1271</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52887,7 +52887,7 @@
         <v>6</v>
       </c>
       <c r="L164" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M164" s="2">
         <v>24</v>
@@ -52983,7 +52983,7 @@
         <v>0</v>
       </c>
       <c r="AR164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS164" s="2">
         <v>4</v>
@@ -53115,7 +53115,7 @@
         <v>0</v>
       </c>
       <c r="CJ164" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CK164" s="2">
         <v>11</v>
@@ -53151,7 +53151,7 @@
         <v>7</v>
       </c>
       <c r="CV164" s="1">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="CW164" s="1">
         <v>199</v>
@@ -53491,16 +53491,16 @@
         <v>2</v>
       </c>
       <c r="J166" s="1">
-        <v>1698</v>
+        <v>1714</v>
       </c>
       <c r="K166" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L166" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="M166" s="2">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="N166" s="1">
         <v>2217</v>
@@ -53755,16 +53755,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5253</v>
+        <v>5269</v>
       </c>
       <c r="CU166" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="CV166" s="1">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="CW166" s="1">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54101,16 +54101,16 @@
         <v>1</v>
       </c>
       <c r="J168" s="1">
-        <v>1326</v>
+        <v>1343</v>
       </c>
       <c r="K168" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L168" s="2">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M168" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="N168" s="1">
         <v>419</v>
@@ -54365,16 +54365,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5956</v>
+        <v>5973</v>
       </c>
       <c r="CU168" s="1">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="CV168" s="1">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="CW168" s="1">
-        <v>562</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54696,7 +54696,7 @@
         <v>74</v>
       </c>
       <c r="E170" s="2">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -54720,7 +54720,7 @@
         <v>99</v>
       </c>
       <c r="M170" s="2">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54780,7 +54780,7 @@
         <v>126</v>
       </c>
       <c r="AG170" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54984,7 +54984,7 @@
         <v>428</v>
       </c>
       <c r="CW170" s="1">
-        <v>1258</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -56159,16 +56159,16 @@
         <v>0</v>
       </c>
       <c r="CH174" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CI174" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ174" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CK174" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CL174" s="1">
         <v>82</v>
@@ -56195,16 +56195,16 @@
         <v>0</v>
       </c>
       <c r="CT174" s="1">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="CU174" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CV174" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CW174" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -56631,7 +56631,7 @@
         <v>5</v>
       </c>
       <c r="AN176" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AO176" s="2">
         <v>40</v>
@@ -56775,7 +56775,7 @@
         <v>22</v>
       </c>
       <c r="CJ176" s="2">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="CK176" s="2">
         <v>81</v>
@@ -56811,7 +56811,7 @@
         <v>28</v>
       </c>
       <c r="CV176" s="1">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="CW176" s="1">
         <v>129</v>
@@ -57127,16 +57127,16 @@
         <v>277</v>
       </c>
       <c r="B178" s="1">
-        <v>7825</v>
+        <v>7840</v>
       </c>
       <c r="C178" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D178" s="2">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E178" s="2">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -57151,16 +57151,16 @@
         <v>0</v>
       </c>
       <c r="J178" s="1">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="K178" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L178" s="2">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M178" s="2">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="N178" s="1">
         <v>73112</v>
@@ -57415,16 +57415,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>84864</v>
+        <v>84894</v>
       </c>
       <c r="CU178" s="1">
-        <v>-288</v>
+        <v>-292</v>
       </c>
       <c r="CV178" s="1">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="CW178" s="1">
-        <v>4539</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57743,7 +57743,7 @@
         <v>31</v>
       </c>
       <c r="D180" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E180" s="2">
         <v>197</v>
@@ -57782,7 +57782,7 @@
         <v>948</v>
       </c>
       <c r="Q180" s="2">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="R180" s="1">
         <v>0</v>
@@ -58031,10 +58031,10 @@
         <v>77</v>
       </c>
       <c r="CV180" s="1">
-        <v>1229</v>
+        <v>1193</v>
       </c>
       <c r="CW180" s="1">
-        <v>2696</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -59277,13 +59277,13 @@
         <v>74</v>
       </c>
       <c r="G185" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="2">
         <v>3</v>
       </c>
       <c r="I185" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J185" s="1">
         <v>0</v>
@@ -59553,13 +59553,13 @@
         <v>156</v>
       </c>
       <c r="CU185" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV185" s="1">
         <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -59890,7 +59890,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187" s="2">
         <v>5</v>
@@ -60166,7 +60166,7 @@
         <v>1</v>
       </c>
       <c r="CV187" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW187" s="1">
         <v>5</v>
@@ -61649,16 +61649,16 @@
         <v>0</v>
       </c>
       <c r="CH192" s="1">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="CI192" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ192" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CK192" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61685,16 +61685,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="CU192" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CV192" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CW192" s="1">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62037,7 +62037,7 @@
         <v>19</v>
       </c>
       <c r="L194" s="2">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M194" s="2">
         <v>62</v>
@@ -62049,7 +62049,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="Q194" s="2">
         <v>1228</v>
@@ -62220,7 +62220,7 @@
         <v>1</v>
       </c>
       <c r="BU194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV194" s="1">
         <v>8</v>
@@ -62301,10 +62301,10 @@
         <v>38</v>
       </c>
       <c r="CV194" s="1">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="CW194" s="1">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62830,7 +62830,7 @@
         <v>1</v>
       </c>
       <c r="BU196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV196" s="1">
         <v>0</v>
@@ -62914,7 +62914,7 @@
         <v>88</v>
       </c>
       <c r="CW196" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63837,16 +63837,16 @@
         <v>299</v>
       </c>
       <c r="B200" s="1">
-        <v>4265</v>
+        <v>4289</v>
       </c>
       <c r="C200" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D200" s="2">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E200" s="2">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="F200" s="1">
         <v>0</v>
@@ -63867,7 +63867,7 @@
         <v>10</v>
       </c>
       <c r="L200" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M200" s="2">
         <v>76</v>
@@ -64125,16 +64125,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16310</v>
+        <v>16334</v>
       </c>
       <c r="CU200" s="1">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="CV200" s="1">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="CW200" s="1">
-        <v>480</v>
+        <v>504</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64253,7 +64253,7 @@
         <v>333</v>
       </c>
       <c r="AM201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN201" s="2">
         <v>2</v>
@@ -64397,7 +64397,7 @@
         <v>3590</v>
       </c>
       <c r="CI201" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CJ201" s="2">
         <v>46</v>
@@ -64433,7 +64433,7 @@
         <v>88076</v>
       </c>
       <c r="CU201" s="1">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="CV201" s="1">
         <v>1993</v>
@@ -64555,16 +64555,16 @@
         <v>0</v>
       </c>
       <c r="AL202" s="1">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AM202" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AN202" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AO202" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AP202" s="1">
         <v>0</v>
@@ -64699,16 +64699,16 @@
         <v>0</v>
       </c>
       <c r="CH202" s="1">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="CI202" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CJ202" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CK202" s="2">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="CL202" s="1">
         <v>0</v>
@@ -64735,16 +64735,16 @@
         <v>0</v>
       </c>
       <c r="CT202" s="1">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="CU202" s="1">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="CV202" s="1">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="CW202" s="1">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65078,7 +65078,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J204" s="1">
         <v>0</v>
@@ -65354,7 +65354,7 @@
         <v>0</v>
       </c>
       <c r="CW204" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:101">
@@ -66095,10 +66095,10 @@
         <v>66</v>
       </c>
       <c r="AQ207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR207" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS207" s="2">
         <v>5</v>
@@ -66227,10 +66227,10 @@
         <v>3204</v>
       </c>
       <c r="CI207" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CJ207" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="CK207" s="2">
         <v>55</v>
@@ -66242,7 +66242,7 @@
         <v>0</v>
       </c>
       <c r="CN207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO207" s="2">
         <v>1</v>
@@ -66263,10 +66263,10 @@
         <v>14059</v>
       </c>
       <c r="CU207" s="1">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="CV207" s="1">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="CW207" s="1">
         <v>617</v>
@@ -66690,196 +66690,196 @@
         <v>0</v>
       </c>
       <c r="AL209" s="1">
+        <v>32</v>
+      </c>
+      <c r="AM209" s="2">
+        <v>6</v>
+      </c>
+      <c r="AN209" s="2">
+        <v>7</v>
+      </c>
+      <c r="AO209" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY209" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV209" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY209" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH209" s="1">
+        <v>245</v>
+      </c>
+      <c r="CI209" s="2">
+        <v>24</v>
+      </c>
+      <c r="CJ209" s="2">
+        <v>39</v>
+      </c>
+      <c r="CK209" s="2">
+        <v>85</v>
+      </c>
+      <c r="CL209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP209" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS209" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT209" s="1">
+        <v>735</v>
+      </c>
+      <c r="CU209" s="1">
         <v>30</v>
       </c>
-      <c r="AM209" s="2">
-        <v>4</v>
-      </c>
-      <c r="AN209" s="2">
-        <v>5</v>
-      </c>
-      <c r="AO209" s="2">
-        <v>16</v>
-      </c>
-      <c r="AP209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX209" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY209" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV209" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY209" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH209" s="1">
-        <v>238</v>
-      </c>
-      <c r="CI209" s="2">
-        <v>17</v>
-      </c>
-      <c r="CJ209" s="2">
-        <v>32</v>
-      </c>
-      <c r="CK209" s="2">
-        <v>78</v>
-      </c>
-      <c r="CL209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP209" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS209" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT209" s="1">
-        <v>726</v>
-      </c>
-      <c r="CU209" s="1">
-        <v>21</v>
-      </c>
       <c r="CV209" s="1">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="CW209" s="1">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -67198,7 +67198,7 @@
         <v>6</v>
       </c>
       <c r="D211" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E211" s="2">
         <v>13</v>
@@ -67453,7 +67453,7 @@
         <v>45</v>
       </c>
       <c r="CK211" s="2">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="CL211" s="1">
         <v>15</v>
@@ -67486,10 +67486,10 @@
         <v>7</v>
       </c>
       <c r="CV211" s="1">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="CW211" s="1">
-        <v>683</v>
+        <v>671</v>
       </c>
     </row>
     <row r="212" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -9048,7 +9048,7 @@
         <v>309</v>
       </c>
       <c r="AM20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" s="2">
         <v>1</v>
@@ -9192,7 +9192,7 @@
         <v>1068</v>
       </c>
       <c r="CI20" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ20" s="2">
         <v>25</v>
@@ -9228,7 +9228,7 @@
         <v>20687</v>
       </c>
       <c r="CU20" s="1">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="CV20" s="1">
         <v>385</v>
@@ -11183,7 +11183,7 @@
         <v>87</v>
       </c>
       <c r="AM27" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="2">
         <v>12</v>
@@ -11327,7 +11327,7 @@
         <v>334</v>
       </c>
       <c r="CI27" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CJ27" s="2">
         <v>15</v>
@@ -11363,7 +11363,7 @@
         <v>552</v>
       </c>
       <c r="CU27" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CV27" s="1">
         <v>31</v>
@@ -12708,7 +12708,7 @@
         <v>306</v>
       </c>
       <c r="AM32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="2">
         <v>4</v>
@@ -12852,7 +12852,7 @@
         <v>470</v>
       </c>
       <c r="CI32" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ32" s="2">
         <v>9</v>
@@ -12888,7 +12888,7 @@
         <v>11125</v>
       </c>
       <c r="CU32" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="CV32" s="1">
         <v>223</v>
@@ -18395,7 +18395,7 @@
         <v>706</v>
       </c>
       <c r="C51" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2">
         <v>14</v>
@@ -18683,7 +18683,7 @@
         <v>3741</v>
       </c>
       <c r="CU51" s="1">
-        <v>1954</v>
+        <v>1947</v>
       </c>
       <c r="CV51" s="1">
         <v>2025</v>
@@ -21469,7 +21469,7 @@
         <v>1993</v>
       </c>
       <c r="K61" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2">
         <v>20</v>
@@ -21733,7 +21733,7 @@
         <v>65908</v>
       </c>
       <c r="CU61" s="1">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="CV61" s="1">
         <v>419</v>
@@ -22689,7 +22689,7 @@
         <v>1784</v>
       </c>
       <c r="K65" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2">
         <v>32</v>
@@ -22953,7 +22953,7 @@
         <v>67204</v>
       </c>
       <c r="CU65" s="1">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="CV65" s="1">
         <v>1756</v>
@@ -23580,7 +23580,7 @@
         <v>225</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="2">
         <v>-29</v>
@@ -23604,7 +23604,7 @@
         <v>308</v>
       </c>
       <c r="K68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2">
         <v>2</v>
@@ -23868,7 +23868,7 @@
         <v>2132</v>
       </c>
       <c r="CU68" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CV68" s="1">
         <v>8</v>
@@ -24310,7 +24310,7 @@
         <v>82</v>
       </c>
       <c r="AQ70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR70" s="2">
         <v>3</v>
@@ -24442,7 +24442,7 @@
         <v>165</v>
       </c>
       <c r="CI70" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CJ70" s="2">
         <v>4</v>
@@ -24478,7 +24478,7 @@
         <v>2266</v>
       </c>
       <c r="CU70" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CV70" s="1">
         <v>49</v>
@@ -24956,7 +24956,7 @@
         <v>3</v>
       </c>
       <c r="BC72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD72" s="2">
         <v>2</v>
@@ -25088,7 +25088,7 @@
         <v>519</v>
       </c>
       <c r="CU72" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV72" s="1">
         <v>47</v>
@@ -25105,7 +25105,7 @@
         <v>51</v>
       </c>
       <c r="C73" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -25213,7 +25213,7 @@
         <v>98</v>
       </c>
       <c r="AM73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN73" s="2">
         <v>2</v>
@@ -25357,7 +25357,7 @@
         <v>517</v>
       </c>
       <c r="CI73" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CJ73" s="2">
         <v>36</v>
@@ -25393,7 +25393,7 @@
         <v>735</v>
       </c>
       <c r="CU73" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CV73" s="1">
         <v>41</v>
@@ -25518,7 +25518,7 @@
         <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AN74" s="2">
         <v>112</v>
@@ -25662,7 +25662,7 @@
         <v>16207</v>
       </c>
       <c r="CI74" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="CJ74" s="2">
         <v>193</v>
@@ -25698,7 +25698,7 @@
         <v>171653</v>
       </c>
       <c r="CU74" s="1">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="CV74" s="1">
         <v>1714</v>
@@ -26056,7 +26056,7 @@
         <v>117545</v>
       </c>
       <c r="O76" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P76" s="2">
         <v>913</v>
@@ -26308,7 +26308,7 @@
         <v>151069</v>
       </c>
       <c r="CU76" s="1">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="CV76" s="1">
         <v>1297</v>
@@ -26959,7 +26959,7 @@
         <v>4534</v>
       </c>
       <c r="K79" s="2">
-        <v>37</v>
+        <v>-11</v>
       </c>
       <c r="L79" s="2">
         <v>131</v>
@@ -27223,7 +27223,7 @@
         <v>90614</v>
       </c>
       <c r="CU79" s="1">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="CV79" s="1">
         <v>620</v>
@@ -28263,7 +28263,7 @@
         <v>3399</v>
       </c>
       <c r="AM83" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AN83" s="2">
         <v>13</v>
@@ -28407,7 +28407,7 @@
         <v>13773</v>
       </c>
       <c r="CI83" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CJ83" s="2">
         <v>147</v>
@@ -28443,7 +28443,7 @@
         <v>423860</v>
       </c>
       <c r="CU83" s="1">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="CV83" s="1">
         <v>881</v>
@@ -29483,7 +29483,7 @@
         <v>504</v>
       </c>
       <c r="AM87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN87" s="2">
         <v>-8</v>
@@ -29627,7 +29627,7 @@
         <v>2391</v>
       </c>
       <c r="CI87" s="2">
-        <v>23</v>
+        <v>-1</v>
       </c>
       <c r="CJ87" s="2">
         <v>15</v>
@@ -29663,7 +29663,7 @@
         <v>2973</v>
       </c>
       <c r="CU87" s="1">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="CV87" s="1">
         <v>11</v>
@@ -29680,7 +29680,7 @@
         <v>270</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88" s="2">
         <v>4</v>
@@ -29704,7 +29704,7 @@
         <v>811</v>
       </c>
       <c r="K88" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2">
         <v>29</v>
@@ -29800,7 +29800,7 @@
         <v>60</v>
       </c>
       <c r="AQ88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR88" s="2">
         <v>3</v>
@@ -29932,7 +29932,7 @@
         <v>2011</v>
       </c>
       <c r="CI88" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CJ88" s="2">
         <v>15</v>
@@ -29968,7 +29968,7 @@
         <v>9583</v>
       </c>
       <c r="CU88" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CV88" s="1">
         <v>129</v>
@@ -30703,7 +30703,7 @@
         <v>762</v>
       </c>
       <c r="AM91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN91" s="2">
         <v>4</v>
@@ -30847,7 +30847,7 @@
         <v>7747</v>
       </c>
       <c r="CI91" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CJ91" s="2">
         <v>82</v>
@@ -30883,7 +30883,7 @@
         <v>25853</v>
       </c>
       <c r="CU91" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="CV91" s="1">
         <v>342</v>
@@ -33448,7 +33448,7 @@
         <v>62</v>
       </c>
       <c r="AM100" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN100" s="2">
         <v>10</v>
@@ -33592,7 +33592,7 @@
         <v>38</v>
       </c>
       <c r="CI100" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ100" s="2">
         <v>9</v>
@@ -33628,7 +33628,7 @@
         <v>160</v>
       </c>
       <c r="CU100" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CV100" s="1">
         <v>22</v>
@@ -33974,7 +33974,7 @@
         <v>5096</v>
       </c>
       <c r="K102" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2">
         <v>35</v>
@@ -34238,7 +34238,7 @@
         <v>43028</v>
       </c>
       <c r="CU102" s="1">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="CV102" s="1">
         <v>728</v>
@@ -35194,7 +35194,7 @@
         <v>10792</v>
       </c>
       <c r="K106" s="2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2">
         <v>399</v>
@@ -35458,7 +35458,7 @@
         <v>92607</v>
       </c>
       <c r="CU106" s="1">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="CV106" s="1">
         <v>1015</v>
@@ -36414,7 +36414,7 @@
         <v>4913</v>
       </c>
       <c r="K110" s="2">
-        <v>88</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="2">
         <v>156</v>
@@ -36498,7 +36498,7 @@
         <v>152</v>
       </c>
       <c r="AM110" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN110" s="2">
         <v>8</v>
@@ -36642,7 +36642,7 @@
         <v>1881</v>
       </c>
       <c r="CI110" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CJ110" s="2">
         <v>71</v>
@@ -36678,7 +36678,7 @@
         <v>13337</v>
       </c>
       <c r="CU110" s="1">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="CV110" s="1">
         <v>374</v>
@@ -37622,7 +37622,7 @@
         <v>64</v>
       </c>
       <c r="G114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="2">
         <v>3</v>
@@ -37898,7 +37898,7 @@
         <v>173</v>
       </c>
       <c r="CU114" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV114" s="1">
         <v>3</v>
@@ -38472,7 +38472,7 @@
         <v>1199</v>
       </c>
       <c r="CI116" s="2">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="CJ116" s="2">
         <v>35</v>
@@ -38508,7 +38508,7 @@
         <v>21750</v>
       </c>
       <c r="CU116" s="1">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CV116" s="1">
         <v>337</v>
@@ -38669,7 +38669,7 @@
         <v>2</v>
       </c>
       <c r="AY117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ117" s="2">
         <v>2</v>
@@ -38813,7 +38813,7 @@
         <v>13161</v>
       </c>
       <c r="CU117" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV117" s="1">
         <v>588</v>
@@ -43417,7 +43417,7 @@
         <v>72</v>
       </c>
       <c r="G133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="2">
         <v>2</v>
@@ -43693,7 +43693,7 @@
         <v>96</v>
       </c>
       <c r="CU133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV133" s="1">
         <v>2</v>
@@ -44015,7 +44015,7 @@
         <v>7667</v>
       </c>
       <c r="C135" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D135" s="2">
         <v>92</v>
@@ -44303,7 +44303,7 @@
         <v>62643</v>
       </c>
       <c r="CU135" s="1">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="CV135" s="1">
         <v>868</v>
@@ -45540,7 +45540,7 @@
         <v>119</v>
       </c>
       <c r="C140" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D140" s="2">
         <v>3</v>
@@ -45804,7 +45804,7 @@
         <v>11</v>
       </c>
       <c r="CM140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN140" s="2">
         <v>2</v>
@@ -45828,7 +45828,7 @@
         <v>570</v>
       </c>
       <c r="CU140" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV140" s="1">
         <v>7</v>
@@ -46085,7 +46085,7 @@
         <v>9</v>
       </c>
       <c r="CE141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF141" s="2">
         <v>1</v>
@@ -46109,7 +46109,7 @@
         <v>74</v>
       </c>
       <c r="CM141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN141" s="2">
         <v>2</v>
@@ -46133,7 +46133,7 @@
         <v>585</v>
       </c>
       <c r="CU141" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV141" s="1">
         <v>15</v>
@@ -46467,7 +46467,7 @@
         <v>72</v>
       </c>
       <c r="G143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
         <v>2</v>
@@ -46563,7 +46563,7 @@
         <v>4</v>
       </c>
       <c r="AM143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN143" s="2">
         <v>1</v>
@@ -46707,7 +46707,7 @@
         <v>16</v>
       </c>
       <c r="CI143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ143" s="2">
         <v>2</v>
@@ -46743,7 +46743,7 @@
         <v>298</v>
       </c>
       <c r="CU143" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV143" s="1">
         <v>10</v>
@@ -48004,7 +48004,7 @@
         <v>1218</v>
       </c>
       <c r="K148" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L148" s="2">
         <v>19</v>
@@ -48088,7 +48088,7 @@
         <v>124</v>
       </c>
       <c r="AM148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN148" s="2">
         <v>4</v>
@@ -48232,7 +48232,7 @@
         <v>433</v>
       </c>
       <c r="CI148" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ148" s="2">
         <v>34</v>
@@ -48268,7 +48268,7 @@
         <v>5591</v>
       </c>
       <c r="CU148" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="CV148" s="1">
         <v>109</v>
@@ -50504,7 +50504,7 @@
         <v>3095</v>
       </c>
       <c r="AE156" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF156" s="2">
         <v>72</v>
@@ -50708,7 +50708,7 @@
         <v>71497</v>
       </c>
       <c r="CU156" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CV156" s="1">
         <v>1064</v>
@@ -51030,7 +51030,7 @@
         <v>8243</v>
       </c>
       <c r="C158" s="2">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D158" s="2">
         <v>142</v>
@@ -51054,7 +51054,7 @@
         <v>7081</v>
       </c>
       <c r="K158" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2">
         <v>217</v>
@@ -51318,7 +51318,7 @@
         <v>25462</v>
       </c>
       <c r="CU158" s="1">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="CV158" s="1">
         <v>763</v>
@@ -54798,7 +54798,7 @@
         <v>229</v>
       </c>
       <c r="AM170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN170" s="2">
         <v>3</v>
@@ -54942,7 +54942,7 @@
         <v>1451</v>
       </c>
       <c r="CI170" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ170" s="2">
         <v>62</v>
@@ -54978,7 +54978,7 @@
         <v>19536</v>
       </c>
       <c r="CU170" s="1">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="CV170" s="1">
         <v>428</v>
@@ -56628,7 +56628,7 @@
         <v>399</v>
       </c>
       <c r="AM176" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN176" s="2">
         <v>17</v>
@@ -56772,7 +56772,7 @@
         <v>748</v>
       </c>
       <c r="CI176" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CJ176" s="2">
         <v>51</v>
@@ -56808,7 +56808,7 @@
         <v>1314</v>
       </c>
       <c r="CU176" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="CV176" s="1">
         <v>71</v>
@@ -57238,7 +57238,7 @@
         <v>171</v>
       </c>
       <c r="AM178" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AN178" s="2">
         <v>19</v>
@@ -57382,7 +57382,7 @@
         <v>1152</v>
       </c>
       <c r="CI178" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CJ178" s="2">
         <v>43</v>
@@ -57418,7 +57418,7 @@
         <v>84894</v>
       </c>
       <c r="CU178" s="1">
-        <v>-292</v>
+        <v>-333</v>
       </c>
       <c r="CV178" s="1">
         <v>2181</v>
@@ -62644,7 +62644,7 @@
         <v>719</v>
       </c>
       <c r="K196" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L196" s="2">
         <v>11</v>
@@ -62728,7 +62728,7 @@
         <v>105</v>
       </c>
       <c r="AM196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN196" s="2">
         <v>5</v>
@@ -62872,7 +62872,7 @@
         <v>411</v>
       </c>
       <c r="CI196" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ196" s="2">
         <v>15</v>
@@ -62908,7 +62908,7 @@
         <v>5481</v>
       </c>
       <c r="CU196" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CV196" s="1">
         <v>88</v>
@@ -63864,7 +63864,7 @@
         <v>2036</v>
       </c>
       <c r="K200" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L200" s="2">
         <v>23</v>
@@ -64128,7 +64128,7 @@
         <v>16334</v>
       </c>
       <c r="CU200" s="1">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="CV200" s="1">
         <v>287</v>
@@ -64169,7 +64169,7 @@
         <v>3540</v>
       </c>
       <c r="K201" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L201" s="2">
         <v>118</v>
@@ -64433,7 +64433,7 @@
         <v>88076</v>
       </c>
       <c r="CU201" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CV201" s="1">
         <v>1993</v>
@@ -65975,7 +65975,7 @@
         <v>1378</v>
       </c>
       <c r="C207" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D207" s="2">
         <v>28</v>
@@ -65999,7 +65999,7 @@
         <v>620</v>
       </c>
       <c r="K207" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L207" s="2">
         <v>39</v>
@@ -66263,7 +66263,7 @@
         <v>14059</v>
       </c>
       <c r="CU207" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CV207" s="1">
         <v>341</v>
@@ -67195,7 +67195,7 @@
         <v>222</v>
       </c>
       <c r="C211" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D211" s="2">
         <v>8</v>
@@ -67483,7 +67483,7 @@
         <v>6274</v>
       </c>
       <c r="CU211" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CV211" s="1">
         <v>487</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3758,7 +3758,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2">
         <v>33</v>
@@ -3776,16 +3776,16 @@
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>4242</v>
+        <v>4286</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3" s="2">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="M3" s="2">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="N3" s="1">
         <v>19611</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46682</v>
+        <v>46726</v>
       </c>
       <c r="CU3" s="1">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="CV3" s="1">
-        <v>812</v>
+        <v>850</v>
       </c>
       <c r="CW3" s="1">
-        <v>1989</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4087,7 +4087,7 @@
         <v>67</v>
       </c>
       <c r="L4" s="2">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="M4" s="2">
         <v>354</v>
@@ -4351,7 +4351,7 @@
         <v>82</v>
       </c>
       <c r="CV4" s="1">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="CW4" s="1">
         <v>1105</v>
@@ -7753,16 +7753,16 @@
         <v>6</v>
       </c>
       <c r="N16" s="1">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="O16" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P16" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q16" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>
@@ -7837,16 +7837,16 @@
         <v>0</v>
       </c>
       <c r="AP16" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AQ16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT16" s="1">
         <v>0</v>
@@ -7981,16 +7981,16 @@
         <v>5</v>
       </c>
       <c r="CL16" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CM16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP16" s="1">
         <v>0</v>
@@ -8005,16 +8005,16 @@
         <v>0</v>
       </c>
       <c r="CT16" s="1">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="CU16" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CV16" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CW16" s="1">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -8130,16 +8130,16 @@
         <v>0</v>
       </c>
       <c r="AL17" s="1">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AM17" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO17" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP17" s="1">
         <v>29</v>
@@ -8274,16 +8274,16 @@
         <v>0</v>
       </c>
       <c r="CH17" s="1">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="CI17" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ17" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CK17" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CL17" s="1">
         <v>29</v>
@@ -8310,16 +8310,16 @@
         <v>0</v>
       </c>
       <c r="CT17" s="1">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="CU17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CV17" s="1">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="CW17" s="1">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8943,7 +8943,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="2">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>173</v>
@@ -8967,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M20" s="2">
         <v>53</v>
@@ -9231,7 +9231,7 @@
         <v>39</v>
       </c>
       <c r="CV20" s="1">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="CW20" s="1">
         <v>906</v>
@@ -9362,16 +9362,16 @@
         <v>2</v>
       </c>
       <c r="AP21" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS21" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -9494,16 +9494,16 @@
         <v>0</v>
       </c>
       <c r="CH21" s="1">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="CI21" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CJ21" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CK21" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="CL21" s="1">
         <v>1</v>
@@ -9530,16 +9530,16 @@
         <v>0</v>
       </c>
       <c r="CT21" s="1">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="CU21" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CV21" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CW21" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -11180,16 +11180,16 @@
         <v>0</v>
       </c>
       <c r="AL27" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AM27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO27" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP27" s="1">
         <v>12</v>
@@ -11360,16 +11360,16 @@
         <v>0</v>
       </c>
       <c r="CT27" s="1">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="CU27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV27" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CW27" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="BU28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV28" s="1">
         <v>5</v>
@@ -11674,7 +11674,7 @@
         <v>239</v>
       </c>
       <c r="CW28" s="1">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12597,16 +12597,16 @@
         <v>131</v>
       </c>
       <c r="B32" s="1">
-        <v>2618</v>
+        <v>2635</v>
       </c>
       <c r="C32" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D32" s="2">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -12711,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO32" s="2">
         <v>4</v>
@@ -12855,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="CJ32" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK32" s="2">
         <v>15</v>
@@ -12885,16 +12885,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11125</v>
+        <v>11142</v>
       </c>
       <c r="CU32" s="1">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="CV32" s="1">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="CW32" s="1">
-        <v>537</v>
+        <v>554</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -15067,7 +15067,7 @@
         <v>39</v>
       </c>
       <c r="L40" s="2">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M40" s="2">
         <v>196</v>
@@ -15295,7 +15295,7 @@
         <v>16</v>
       </c>
       <c r="CJ40" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="CK40" s="2">
         <v>76</v>
@@ -15331,7 +15331,7 @@
         <v>112</v>
       </c>
       <c r="CV40" s="1">
-        <v>821</v>
+        <v>776</v>
       </c>
       <c r="CW40" s="1">
         <v>2114</v>
@@ -18093,7 +18093,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2">
         <v>6</v>
@@ -18201,7 +18201,7 @@
         <v>0</v>
       </c>
       <c r="AN50" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AO50" s="2">
         <v>11</v>
@@ -18345,7 +18345,7 @@
         <v>4</v>
       </c>
       <c r="CJ50" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CK50" s="2">
         <v>49</v>
@@ -18381,7 +18381,7 @@
         <v>6</v>
       </c>
       <c r="CV50" s="1">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="CW50" s="1">
         <v>71</v>
@@ -20031,7 +20031,7 @@
         <v>0</v>
       </c>
       <c r="AN56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO56" s="2">
         <v>2</v>
@@ -20175,7 +20175,7 @@
         <v>12</v>
       </c>
       <c r="CJ56" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="CK56" s="2">
         <v>45</v>
@@ -20211,7 +20211,7 @@
         <v>12</v>
       </c>
       <c r="CV56" s="1">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="CW56" s="1">
         <v>372</v>
@@ -20243,7 +20243,7 @@
         <v>3</v>
       </c>
       <c r="I57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -20519,7 +20519,7 @@
         <v>3</v>
       </c>
       <c r="CW57" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -20838,7 +20838,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="2">
         <v>7</v>
@@ -21126,7 +21126,7 @@
         <v>6</v>
       </c>
       <c r="CV59" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CW59" s="1">
         <v>58</v>
@@ -21562,16 +21562,16 @@
         <v>3</v>
       </c>
       <c r="AP61" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AQ61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS61" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -21694,16 +21694,16 @@
         <v>0</v>
       </c>
       <c r="CH61" s="1">
-        <v>5332</v>
+        <v>5342</v>
       </c>
       <c r="CI61" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ61" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CK61" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65908</v>
+        <v>65919</v>
       </c>
       <c r="CU61" s="1">
-        <v>-23</v>
+        <v>-12</v>
       </c>
       <c r="CV61" s="1">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="CW61" s="1">
-        <v>910</v>
+        <v>921</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22441,16 +22441,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="AE64" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF64" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG64" s="2">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22615,7 +22615,7 @@
         <v>3</v>
       </c>
       <c r="CJ64" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="CK64" s="2">
         <v>29</v>
@@ -22645,16 +22645,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8017</v>
+        <v>8018</v>
       </c>
       <c r="CU64" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="CV64" s="1">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="CW64" s="1">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22686,16 +22686,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>1784</v>
+        <v>1800</v>
       </c>
       <c r="K65" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L65" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M65" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="N65" s="1">
         <v>58956</v>
@@ -22950,16 +22950,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67204</v>
+        <v>67220</v>
       </c>
       <c r="CU65" s="1">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="CV65" s="1">
-        <v>1756</v>
+        <v>1772</v>
       </c>
       <c r="CW65" s="1">
-        <v>3530</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -22997,7 +22997,7 @@
         <v>14</v>
       </c>
       <c r="L66" s="2">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="M66" s="2">
         <v>90</v>
@@ -23261,7 +23261,7 @@
         <v>15</v>
       </c>
       <c r="CV66" s="1">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="CW66" s="1">
         <v>113</v>
@@ -23703,7 +23703,7 @@
         <v>1</v>
       </c>
       <c r="AR68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS68" s="2">
         <v>6</v>
@@ -23835,7 +23835,7 @@
         <v>1</v>
       </c>
       <c r="CJ68" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CK68" s="2">
         <v>17</v>
@@ -23871,7 +23871,7 @@
         <v>4</v>
       </c>
       <c r="CV68" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CW68" s="1">
         <v>51</v>
@@ -25102,16 +25102,16 @@
         <v>172</v>
       </c>
       <c r="B73" s="1">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C73" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D73" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1">
         <v>45</v>
@@ -25354,16 +25354,16 @@
         <v>0</v>
       </c>
       <c r="CH73" s="1">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="CI73" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CJ73" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CK73" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="CL73" s="1">
         <v>6</v>
@@ -25390,16 +25390,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="CU73" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CV73" s="1">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="CW73" s="1">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25431,16 +25431,16 @@
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>10112</v>
+        <v>10153</v>
       </c>
       <c r="K74" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L74" s="2">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="M74" s="2">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="N74" s="1">
         <v>79173</v>
@@ -25518,13 +25518,13 @@
         <v>36271</v>
       </c>
       <c r="AM74" s="2">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AN74" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AO74" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>16207</v>
       </c>
       <c r="CI74" s="2">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="CJ74" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="CK74" s="2">
         <v>419</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171653</v>
+        <v>171694</v>
       </c>
       <c r="CU74" s="1">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="CV74" s="1">
-        <v>1714</v>
+        <v>1744</v>
       </c>
       <c r="CW74" s="1">
-        <v>4325</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26044,7 +26044,7 @@
         <v>5809</v>
       </c>
       <c r="K76" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2">
         <v>130</v>
@@ -26143,7 +26143,7 @@
         <v>0</v>
       </c>
       <c r="AR76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS76" s="2">
         <v>3</v>
@@ -26275,7 +26275,7 @@
         <v>25</v>
       </c>
       <c r="CJ76" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="CK76" s="2">
         <v>86</v>
@@ -26308,10 +26308,10 @@
         <v>151069</v>
       </c>
       <c r="CU76" s="1">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="CV76" s="1">
-        <v>1297</v>
+        <v>1280</v>
       </c>
       <c r="CW76" s="1">
         <v>3699</v>
@@ -26346,16 +26346,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4878</v>
+        <v>4922</v>
       </c>
       <c r="K77" s="2">
-        <v>-2</v>
+        <v>42</v>
       </c>
       <c r="L77" s="2">
         <v>181</v>
       </c>
       <c r="M77" s="2">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26580,10 +26580,10 @@
         <v>146</v>
       </c>
       <c r="CJ77" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="CK77" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390934</v>
+        <v>390978</v>
       </c>
       <c r="CU77" s="1">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="CV77" s="1">
-        <v>10252</v>
+        <v>10234</v>
       </c>
       <c r="CW77" s="1">
-        <v>15875</v>
+        <v>15925</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26639,16 +26639,16 @@
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -26915,16 +26915,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV78" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CW78" s="1">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26962,7 +26962,7 @@
         <v>-11</v>
       </c>
       <c r="L79" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="M79" s="2">
         <v>228</v>
@@ -27043,7 +27043,7 @@
         <v>296</v>
       </c>
       <c r="AM79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN79" s="2">
         <v>2</v>
@@ -27187,7 +27187,7 @@
         <v>2036</v>
       </c>
       <c r="CI79" s="2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="CJ79" s="2">
         <v>34</v>
@@ -27223,10 +27223,10 @@
         <v>90614</v>
       </c>
       <c r="CU79" s="1">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="CV79" s="1">
-        <v>620</v>
+        <v>568</v>
       </c>
       <c r="CW79" s="1">
         <v>1826</v>
@@ -27345,16 +27345,16 @@
         <v>0</v>
       </c>
       <c r="AL80" s="1">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="AM80" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AN80" s="2">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="AO80" s="2">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27489,16 +27489,16 @@
         <v>1</v>
       </c>
       <c r="CH80" s="1">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="CI80" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CJ80" s="2">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="CK80" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27525,16 +27525,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1764</v>
+        <v>1798</v>
       </c>
       <c r="CU80" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="CV80" s="1">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="CW80" s="1">
-        <v>224</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27566,16 +27566,16 @@
         <v>1</v>
       </c>
       <c r="J81" s="1">
-        <v>1578</v>
+        <v>1589</v>
       </c>
       <c r="K81" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L81" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="M81" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N81" s="1">
         <v>3606</v>
@@ -27650,16 +27650,16 @@
         <v>0</v>
       </c>
       <c r="AL81" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AM81" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN81" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO81" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP81" s="1">
         <v>58</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="CH81" s="1">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CI81" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ81" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK81" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL81" s="1">
         <v>30</v>
@@ -27830,16 +27830,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6407</v>
+        <v>6422</v>
       </c>
       <c r="CU81" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="CV81" s="1">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="CW81" s="1">
-        <v>349</v>
+        <v>364</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28260,16 +28260,16 @@
         <v>0</v>
       </c>
       <c r="AL83" s="1">
-        <v>3399</v>
+        <v>3401</v>
       </c>
       <c r="AM83" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN83" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO83" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28404,16 +28404,16 @@
         <v>0</v>
       </c>
       <c r="CH83" s="1">
-        <v>13773</v>
+        <v>13813</v>
       </c>
       <c r="CI83" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CJ83" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="CK83" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423860</v>
+        <v>423902</v>
       </c>
       <c r="CU83" s="1">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="CV83" s="1">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="CW83" s="1">
-        <v>5384</v>
+        <v>5426</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28780,7 +28780,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" s="2">
         <v>4</v>
@@ -29056,7 +29056,7 @@
         <v>10</v>
       </c>
       <c r="CV85" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CW85" s="1">
         <v>56</v>
@@ -29480,16 +29480,16 @@
         <v>0</v>
       </c>
       <c r="AL87" s="1">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM87" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN87" s="2">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="AO87" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP87" s="1">
         <v>24</v>
@@ -29624,16 +29624,16 @@
         <v>1</v>
       </c>
       <c r="CH87" s="1">
-        <v>2391</v>
+        <v>2402</v>
       </c>
       <c r="CI87" s="2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CJ87" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="CK87" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29660,16 +29660,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2973</v>
+        <v>2985</v>
       </c>
       <c r="CU87" s="1">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CV87" s="1">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="CW87" s="1">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -29695,7 +29695,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="2">
         <v>2</v>
@@ -29707,7 +29707,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M88" s="2">
         <v>69</v>
@@ -29803,7 +29803,7 @@
         <v>0</v>
       </c>
       <c r="AR88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS88" s="2">
         <v>5</v>
@@ -29935,7 +29935,7 @@
         <v>0</v>
       </c>
       <c r="CJ88" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CK88" s="2">
         <v>33</v>
@@ -29971,7 +29971,7 @@
         <v>0</v>
       </c>
       <c r="CV88" s="1">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="CW88" s="1">
         <v>418</v>
@@ -30619,7 +30619,7 @@
         <v>5418</v>
       </c>
       <c r="K91" s="2">
-        <v>53</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="2">
         <v>115</v>
@@ -30718,7 +30718,7 @@
         <v>0</v>
       </c>
       <c r="AR91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS91" s="2">
         <v>1</v>
@@ -30850,7 +30850,7 @@
         <v>1</v>
       </c>
       <c r="CJ91" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="CK91" s="2">
         <v>153</v>
@@ -30883,10 +30883,10 @@
         <v>25853</v>
       </c>
       <c r="CU91" s="1">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="CV91" s="1">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="CW91" s="1">
         <v>724</v>
@@ -31155,7 +31155,7 @@
         <v>6</v>
       </c>
       <c r="CJ92" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CK92" s="2">
         <v>17</v>
@@ -31191,7 +31191,7 @@
         <v>7</v>
       </c>
       <c r="CV92" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CW92" s="1">
         <v>92</v>
@@ -32135,7 +32135,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" s="2">
         <v>6</v>
@@ -32243,7 +32243,7 @@
         <v>0</v>
       </c>
       <c r="AR96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS96" s="2">
         <v>2</v>
@@ -32327,7 +32327,7 @@
         <v>0</v>
       </c>
       <c r="BT96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU96" s="2">
         <v>2</v>
@@ -32411,7 +32411,7 @@
         <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="CW96" s="1">
         <v>41</v>
@@ -32443,7 +32443,7 @@
         <v>3</v>
       </c>
       <c r="I97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J97" s="1">
         <v>0</v>
@@ -32719,7 +32719,7 @@
         <v>8</v>
       </c>
       <c r="CW97" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -33358,7 +33358,7 @@
         <v>3</v>
       </c>
       <c r="I100" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -33451,7 +33451,7 @@
         <v>0</v>
       </c>
       <c r="AN100" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO100" s="2">
         <v>16</v>
@@ -33595,7 +33595,7 @@
         <v>0</v>
       </c>
       <c r="CJ100" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CK100" s="2">
         <v>12</v>
@@ -33631,10 +33631,10 @@
         <v>1</v>
       </c>
       <c r="CV100" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="CW100" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33953,7 +33953,7 @@
         <v>0</v>
       </c>
       <c r="D102" s="2">
-        <v>372</v>
+        <v>279</v>
       </c>
       <c r="E102" s="2">
         <v>665</v>
@@ -33971,16 +33971,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="1">
-        <v>5096</v>
+        <v>5122</v>
       </c>
       <c r="K102" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L102" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="M102" s="2">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="N102" s="1">
         <v>14647</v>
@@ -34235,16 +34235,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>43028</v>
+        <v>43054</v>
       </c>
       <c r="CU102" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="CV102" s="1">
-        <v>728</v>
+        <v>661</v>
       </c>
       <c r="CW102" s="1">
-        <v>1615</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34261,7 +34261,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F103" s="1">
         <v>12</v>
@@ -34549,7 +34549,7 @@
         <v>149</v>
       </c>
       <c r="CW103" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34862,16 +34862,16 @@
         <v>204</v>
       </c>
       <c r="B105" s="1">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C105" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D105" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E105" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1">
         <v>6</v>
@@ -35120,7 +35120,7 @@
         <v>4</v>
       </c>
       <c r="CJ105" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CK105" s="2">
         <v>22</v>
@@ -35150,16 +35150,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7981</v>
+        <v>7988</v>
       </c>
       <c r="CU105" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CV105" s="1">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="CW105" s="1">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35197,7 +35197,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="2">
-        <v>399</v>
+        <v>221</v>
       </c>
       <c r="M106" s="2">
         <v>747</v>
@@ -35419,16 +35419,16 @@
         <v>0</v>
       </c>
       <c r="CH106" s="1">
-        <v>6442</v>
+        <v>6493</v>
       </c>
       <c r="CI106" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="CJ106" s="2">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="CK106" s="2">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="CL106" s="1">
         <v>0</v>
@@ -35455,16 +35455,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92607</v>
+        <v>92658</v>
       </c>
       <c r="CU106" s="1">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="CV106" s="1">
-        <v>1015</v>
+        <v>888</v>
       </c>
       <c r="CW106" s="1">
-        <v>2289</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36501,7 +36501,7 @@
         <v>0</v>
       </c>
       <c r="AN110" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO110" s="2">
         <v>9</v>
@@ -36645,7 +36645,7 @@
         <v>0</v>
       </c>
       <c r="CJ110" s="2">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="CK110" s="2">
         <v>154</v>
@@ -36681,7 +36681,7 @@
         <v>7</v>
       </c>
       <c r="CV110" s="1">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="CW110" s="1">
         <v>955</v>
@@ -37117,16 +37117,16 @@
         <v>0</v>
       </c>
       <c r="AP112" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR112" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS112" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT112" s="1">
         <v>0</v>
@@ -37249,16 +37249,16 @@
         <v>0</v>
       </c>
       <c r="CH112" s="1">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="CI112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ112" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CK112" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CL112" s="1">
         <v>26</v>
@@ -37285,16 +37285,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8294</v>
+        <v>8297</v>
       </c>
       <c r="CU112" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CV112" s="1">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="CW112" s="1">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37560,7 +37560,7 @@
         <v>40</v>
       </c>
       <c r="CJ113" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="CK113" s="2">
         <v>147</v>
@@ -37596,7 +37596,7 @@
         <v>78</v>
       </c>
       <c r="CV113" s="1">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="CW113" s="1">
         <v>9843</v>
@@ -38331,7 +38331,7 @@
         <v>0</v>
       </c>
       <c r="AN116" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO116" s="2">
         <v>13</v>
@@ -38475,7 +38475,7 @@
         <v>-1</v>
       </c>
       <c r="CJ116" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="CK116" s="2">
         <v>58</v>
@@ -38511,7 +38511,7 @@
         <v>9</v>
       </c>
       <c r="CV116" s="1">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="CW116" s="1">
         <v>1088</v>
@@ -38522,16 +38522,16 @@
         <v>216</v>
       </c>
       <c r="B117" s="1">
-        <v>9353</v>
+        <v>9560</v>
       </c>
       <c r="C117" s="2">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="D117" s="2">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="E117" s="2">
-        <v>916</v>
+        <v>1123</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -38810,16 +38810,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>13161</v>
+        <v>13368</v>
       </c>
       <c r="CU117" s="1">
-        <v>6</v>
+        <v>213</v>
       </c>
       <c r="CV117" s="1">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="CW117" s="1">
-        <v>1090</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39138,7 +39138,7 @@
         <v>0</v>
       </c>
       <c r="D119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="2">
         <v>1</v>
@@ -39150,7 +39150,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I119" s="2">
         <v>5</v>
@@ -42191,7 +42191,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="1">
         <v>44</v>
@@ -42290,16 +42290,16 @@
         <v>0</v>
       </c>
       <c r="AL129" s="1">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AM129" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN129" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO129" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AP129" s="1">
         <v>35</v>
@@ -42308,7 +42308,7 @@
         <v>0</v>
       </c>
       <c r="AR129" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS129" s="2">
         <v>4</v>
@@ -42434,16 +42434,16 @@
         <v>0</v>
       </c>
       <c r="CH129" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="CI129" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ129" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CK129" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="CL129" s="1">
         <v>37</v>
@@ -42470,16 +42470,16 @@
         <v>0</v>
       </c>
       <c r="CT129" s="1">
-        <v>3563</v>
+        <v>3571</v>
       </c>
       <c r="CU129" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CV129" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CW129" s="1">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -42595,16 +42595,16 @@
         <v>0</v>
       </c>
       <c r="AL130" s="1">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AM130" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN130" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AO130" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP130" s="1">
         <v>0</v>
@@ -42739,16 +42739,16 @@
         <v>0</v>
       </c>
       <c r="CH130" s="1">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="CI130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ130" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CK130" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CL130" s="1">
         <v>0</v>
@@ -42775,16 +42775,16 @@
         <v>0</v>
       </c>
       <c r="CT130" s="1">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="CU130" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CV130" s="1">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="CW130" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43414,16 +43414,16 @@
         <v>4</v>
       </c>
       <c r="F133" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I133" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J133" s="1">
         <v>0</v>
@@ -43690,16 +43690,16 @@
         <v>0</v>
       </c>
       <c r="CT133" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="CU133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW133" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:101">
@@ -43815,16 +43815,16 @@
         <v>0</v>
       </c>
       <c r="AL134" s="1">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="AM134" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN134" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO134" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP134" s="1">
         <v>36</v>
@@ -43959,16 +43959,16 @@
         <v>0</v>
       </c>
       <c r="CH134" s="1">
-        <v>2741</v>
+        <v>2747</v>
       </c>
       <c r="CI134" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CJ134" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="CK134" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="CL134" s="1">
         <v>9</v>
@@ -43995,16 +43995,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>134455</v>
+        <v>134463</v>
       </c>
       <c r="CU134" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="CV134" s="1">
-        <v>2534</v>
+        <v>2542</v>
       </c>
       <c r="CW134" s="1">
-        <v>5797</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44012,16 +44012,16 @@
         <v>234</v>
       </c>
       <c r="B135" s="1">
-        <v>7667</v>
+        <v>7706</v>
       </c>
       <c r="C135" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D135" s="2">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="E135" s="2">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -44036,16 +44036,16 @@
         <v>0</v>
       </c>
       <c r="J135" s="1">
-        <v>6539</v>
+        <v>6596</v>
       </c>
       <c r="K135" s="2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L135" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="M135" s="2">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="N135" s="1">
         <v>32057</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62643</v>
+        <v>62739</v>
       </c>
       <c r="CU135" s="1">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="CV135" s="1">
-        <v>868</v>
+        <v>964</v>
       </c>
       <c r="CW135" s="1">
-        <v>2572</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44575,7 +44575,7 @@
         <v>3</v>
       </c>
       <c r="CJ136" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CK136" s="2">
         <v>25</v>
@@ -44611,7 +44611,7 @@
         <v>5</v>
       </c>
       <c r="CV136" s="1">
-        <v>5082</v>
+        <v>5079</v>
       </c>
       <c r="CW136" s="1">
         <v>6083</v>
@@ -46153,7 +46153,7 @@
         <v>0</v>
       </c>
       <c r="D142" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E142" s="2">
         <v>4</v>
@@ -46441,7 +46441,7 @@
         <v>19</v>
       </c>
       <c r="CV142" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="CW142" s="1">
         <v>103</v>
@@ -46464,16 +46464,16 @@
         <v>1</v>
       </c>
       <c r="F143" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I143" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J143" s="1">
         <v>0</v>
@@ -46572,16 +46572,16 @@
         <v>1</v>
       </c>
       <c r="AP143" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS143" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT143" s="1">
         <v>0</v>
@@ -46716,16 +46716,16 @@
         <v>4</v>
       </c>
       <c r="CL143" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="CM143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP143" s="1">
         <v>0</v>
@@ -46740,16 +46740,16 @@
         <v>0</v>
       </c>
       <c r="CT143" s="1">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="CU143" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV143" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CW143" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47068,7 +47068,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E145" s="2">
         <v>38</v>
@@ -47092,7 +47092,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M145" s="2">
         <v>19</v>
@@ -47188,7 +47188,7 @@
         <v>0</v>
       </c>
       <c r="AR145" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS145" s="2">
         <v>4</v>
@@ -47320,7 +47320,7 @@
         <v>0</v>
       </c>
       <c r="CJ145" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CK145" s="2">
         <v>11</v>
@@ -47356,7 +47356,7 @@
         <v>3</v>
       </c>
       <c r="CV145" s="1">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="CW145" s="1">
         <v>129</v>
@@ -47983,7 +47983,7 @@
         <v>0</v>
       </c>
       <c r="D148" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E148" s="2">
         <v>7</v>
@@ -48007,7 +48007,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M148" s="2">
         <v>28</v>
@@ -48091,7 +48091,7 @@
         <v>0</v>
       </c>
       <c r="AN148" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO148" s="2">
         <v>12</v>
@@ -48235,7 +48235,7 @@
         <v>0</v>
       </c>
       <c r="CJ148" s="2">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="CK148" s="2">
         <v>49</v>
@@ -48271,7 +48271,7 @@
         <v>1</v>
       </c>
       <c r="CV148" s="1">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="CW148" s="1">
         <v>232</v>
@@ -48408,7 +48408,7 @@
         <v>1</v>
       </c>
       <c r="AR149" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS149" s="2">
         <v>7</v>
@@ -48540,7 +48540,7 @@
         <v>3</v>
       </c>
       <c r="CJ149" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK149" s="2">
         <v>15</v>
@@ -48576,7 +48576,7 @@
         <v>4</v>
       </c>
       <c r="CV149" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CW149" s="1">
         <v>68</v>
@@ -48707,16 +48707,16 @@
         <v>0</v>
       </c>
       <c r="AP150" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AQ150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR150" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48851,16 +48851,16 @@
         <v>5</v>
       </c>
       <c r="CL150" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CM150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN150" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO150" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP150" s="1">
         <v>0</v>
@@ -48875,16 +48875,16 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="CU150" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV150" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CW150" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49206,7 +49206,7 @@
         <v>2</v>
       </c>
       <c r="E152" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F152" s="1">
         <v>22</v>
@@ -49494,7 +49494,7 @@
         <v>93</v>
       </c>
       <c r="CW152" s="1">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50136,16 +50136,16 @@
         <v>4</v>
       </c>
       <c r="J155" s="1">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="K155" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L155" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M155" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="N155" s="1">
         <v>1204</v>
@@ -50400,16 +50400,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2660</v>
+        <v>2666</v>
       </c>
       <c r="CU155" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV155" s="1">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="CW155" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50447,7 +50447,7 @@
         <v>13</v>
       </c>
       <c r="L156" s="2">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M156" s="2">
         <v>123</v>
@@ -50531,22 +50531,22 @@
         <v>0</v>
       </c>
       <c r="AN156" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO156" s="2">
         <v>6</v>
       </c>
       <c r="AP156" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AQ156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR156" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS156" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT156" s="1">
         <v>2</v>
@@ -50669,16 +50669,16 @@
         <v>0</v>
       </c>
       <c r="CH156" s="1">
-        <v>2778</v>
+        <v>2789</v>
       </c>
       <c r="CI156" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ156" s="2">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="CK156" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="CL156" s="1">
         <v>13</v>
@@ -50705,16 +50705,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71497</v>
+        <v>71509</v>
       </c>
       <c r="CU156" s="1">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="CV156" s="1">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="CW156" s="1">
-        <v>2507</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50848,7 +50848,7 @@
         <v>0</v>
       </c>
       <c r="AR157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS157" s="2">
         <v>3</v>
@@ -50980,7 +50980,7 @@
         <v>53</v>
       </c>
       <c r="CJ157" s="2">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="CK157" s="2">
         <v>208</v>
@@ -51016,7 +51016,7 @@
         <v>56</v>
       </c>
       <c r="CV157" s="1">
-        <v>5190</v>
+        <v>5156</v>
       </c>
       <c r="CW157" s="1">
         <v>9102</v>
@@ -51141,7 +51141,7 @@
         <v>12</v>
       </c>
       <c r="AN158" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AO158" s="2">
         <v>37</v>
@@ -51285,7 +51285,7 @@
         <v>127</v>
       </c>
       <c r="CJ158" s="2">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="CK158" s="2">
         <v>546</v>
@@ -51321,7 +51321,7 @@
         <v>140</v>
       </c>
       <c r="CV158" s="1">
-        <v>763</v>
+        <v>677</v>
       </c>
       <c r="CW158" s="1">
         <v>1476</v>
@@ -51948,7 +51948,7 @@
         <v>0</v>
       </c>
       <c r="D161" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E161" s="2">
         <v>86</v>
@@ -51972,7 +51972,7 @@
         <v>34</v>
       </c>
       <c r="L161" s="2">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="M161" s="2">
         <v>136</v>
@@ -52236,7 +52236,7 @@
         <v>41</v>
       </c>
       <c r="CV161" s="1">
-        <v>741</v>
+        <v>700</v>
       </c>
       <c r="CW161" s="1">
         <v>1229</v>
@@ -52810,7 +52810,7 @@
         <v>2</v>
       </c>
       <c r="CJ163" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CK163" s="2">
         <v>15</v>
@@ -52846,7 +52846,7 @@
         <v>3</v>
       </c>
       <c r="CV163" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CW163" s="1">
         <v>46</v>
@@ -52977,16 +52977,16 @@
         <v>1</v>
       </c>
       <c r="AP164" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR164" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS164" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT164" s="1">
         <v>0</v>
@@ -53109,16 +53109,16 @@
         <v>0</v>
       </c>
       <c r="CH164" s="1">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="CI164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ164" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK164" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL164" s="1">
         <v>4</v>
@@ -53145,16 +53145,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="CU164" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV164" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="CW164" s="1">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53473,7 +53473,7 @@
         <v>0</v>
       </c>
       <c r="D166" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E166" s="2">
         <v>14</v>
@@ -53761,7 +53761,7 @@
         <v>17</v>
       </c>
       <c r="CV166" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="CW166" s="1">
         <v>517</v>
@@ -54813,7 +54813,7 @@
         <v>0</v>
       </c>
       <c r="AR170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS170" s="2">
         <v>1</v>
@@ -54945,7 +54945,7 @@
         <v>0</v>
       </c>
       <c r="CJ170" s="2">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="CK170" s="2">
         <v>138</v>
@@ -54981,7 +54981,7 @@
         <v>63</v>
       </c>
       <c r="CV170" s="1">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="CW170" s="1">
         <v>1162</v>
@@ -55100,16 +55100,16 @@
         <v>0</v>
       </c>
       <c r="AL171" s="1">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="AM171" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN171" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO171" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP171" s="1">
         <v>6</v>
@@ -55280,16 +55280,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5838</v>
+        <v>5840</v>
       </c>
       <c r="CU171" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CV171" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="CW171" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -55928,7 +55928,7 @@
         <v>2</v>
       </c>
       <c r="I174" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J174" s="1">
         <v>0</v>
@@ -56036,7 +56036,7 @@
         <v>2</v>
       </c>
       <c r="AS174" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT174" s="1">
         <v>0</v>
@@ -56180,7 +56180,7 @@
         <v>4</v>
       </c>
       <c r="CO174" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CP174" s="1">
         <v>0</v>
@@ -56204,7 +56204,7 @@
         <v>23</v>
       </c>
       <c r="CW174" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -57157,7 +57157,7 @@
         <v>15</v>
       </c>
       <c r="L178" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M178" s="2">
         <v>81</v>
@@ -57235,16 +57235,16 @@
         <v>2</v>
       </c>
       <c r="AL178" s="1">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN178" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO178" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AP178" s="1">
         <v>30</v>
@@ -57379,16 +57379,16 @@
         <v>0</v>
       </c>
       <c r="CH178" s="1">
-        <v>1152</v>
+        <v>1176</v>
       </c>
       <c r="CI178" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CJ178" s="2">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="CK178" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="CL178" s="1">
         <v>7</v>
@@ -57415,16 +57415,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>84894</v>
+        <v>84919</v>
       </c>
       <c r="CU178" s="1">
-        <v>-333</v>
+        <v>-308</v>
       </c>
       <c r="CV178" s="1">
-        <v>2181</v>
+        <v>2198</v>
       </c>
       <c r="CW178" s="1">
-        <v>4569</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -58063,7 +58063,7 @@
         <v>3</v>
       </c>
       <c r="I181" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J181" s="1">
         <v>0</v>
@@ -58339,7 +58339,7 @@
         <v>3</v>
       </c>
       <c r="CW181" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -59280,7 +59280,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I185" s="2">
         <v>5</v>
@@ -59556,7 +59556,7 @@
         <v>2</v>
       </c>
       <c r="CV185" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW185" s="1">
         <v>17</v>
@@ -61418,7 +61418,7 @@
         <v>3</v>
       </c>
       <c r="I192" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J192" s="1">
         <v>0</v>
@@ -61694,7 +61694,7 @@
         <v>10</v>
       </c>
       <c r="CW192" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62318,7 +62318,7 @@
         <v>2</v>
       </c>
       <c r="D195" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E195" s="2">
         <v>10</v>
@@ -62570,7 +62570,7 @@
         <v>3</v>
       </c>
       <c r="CJ195" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CK195" s="2">
         <v>31</v>
@@ -62606,7 +62606,7 @@
         <v>12</v>
       </c>
       <c r="CV195" s="1">
-        <v>3374</v>
+        <v>3368</v>
       </c>
       <c r="CW195" s="1">
         <v>5335</v>
@@ -62743,7 +62743,7 @@
         <v>0</v>
       </c>
       <c r="AR196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS196" s="2">
         <v>2</v>
@@ -62875,7 +62875,7 @@
         <v>0</v>
       </c>
       <c r="CJ196" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CK196" s="2">
         <v>28</v>
@@ -62911,7 +62911,7 @@
         <v>0</v>
       </c>
       <c r="CV196" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="CW196" s="1">
         <v>208</v>
@@ -63843,7 +63843,7 @@
         <v>24</v>
       </c>
       <c r="D200" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E200" s="2">
         <v>181</v>
@@ -64131,7 +64131,7 @@
         <v>45</v>
       </c>
       <c r="CV200" s="1">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="CW200" s="1">
         <v>504</v>
@@ -64172,7 +64172,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="M201" s="2">
         <v>230</v>
@@ -64184,7 +64184,7 @@
         <v>0</v>
       </c>
       <c r="P201" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q201" s="2">
         <v>701</v>
@@ -64223,7 +64223,7 @@
         <v>3</v>
       </c>
       <c r="AC201" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AD201" s="1">
         <v>48204</v>
@@ -64250,16 +64250,16 @@
         <v>0</v>
       </c>
       <c r="AL201" s="1">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN201" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO201" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP201" s="1">
         <v>25</v>
@@ -64394,16 +64394,16 @@
         <v>0</v>
       </c>
       <c r="CH201" s="1">
-        <v>3590</v>
+        <v>3616</v>
       </c>
       <c r="CI201" s="2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CJ201" s="2">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="CK201" s="2">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64430,16 +64430,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88076</v>
+        <v>88103</v>
       </c>
       <c r="CU201" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CV201" s="1">
-        <v>1993</v>
+        <v>1977</v>
       </c>
       <c r="CW201" s="1">
-        <v>3114</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64561,7 +64561,7 @@
         <v>19</v>
       </c>
       <c r="AN202" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AO202" s="2">
         <v>90</v>
@@ -64705,7 +64705,7 @@
         <v>10</v>
       </c>
       <c r="CJ202" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CK202" s="2">
         <v>48</v>
@@ -64741,7 +64741,7 @@
         <v>31</v>
       </c>
       <c r="CV202" s="1">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="CW202" s="1">
         <v>139</v>
@@ -65978,7 +65978,7 @@
         <v>0</v>
       </c>
       <c r="D207" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E207" s="2">
         <v>46</v>
@@ -66002,7 +66002,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="2">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M207" s="2">
         <v>60</v>
@@ -66266,7 +66266,7 @@
         <v>0</v>
       </c>
       <c r="CV207" s="1">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="CW207" s="1">
         <v>617</v>
@@ -66699,7 +66699,7 @@
         <v>7</v>
       </c>
       <c r="AO209" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AP209" s="1">
         <v>0</v>
@@ -66843,7 +66843,7 @@
         <v>39</v>
       </c>
       <c r="CK209" s="2">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="CL209" s="1">
         <v>0</v>
@@ -66879,7 +66879,7 @@
         <v>65</v>
       </c>
       <c r="CW209" s="1">
-        <v>122</v>
+        <v>89</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -66932,7 +66932,7 @@
         <v>7</v>
       </c>
       <c r="Q210" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R210" s="1">
         <v>8</v>
@@ -67100,7 +67100,7 @@
         <v>1</v>
       </c>
       <c r="BU210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV210" s="1">
         <v>1</v>
@@ -67184,7 +67184,7 @@
         <v>18</v>
       </c>
       <c r="CW210" s="1">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67318,7 +67318,7 @@
         <v>0</v>
       </c>
       <c r="AR211" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS211" s="2">
         <v>4</v>
@@ -67450,7 +67450,7 @@
         <v>0</v>
       </c>
       <c r="CJ211" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="CK211" s="2">
         <v>104</v>
@@ -67486,7 +67486,7 @@
         <v>1</v>
       </c>
       <c r="CV211" s="1">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="CW211" s="1">
         <v>671</v>
@@ -70463,7 +70463,7 @@
         <v>618</v>
       </c>
       <c r="D102">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="E102" t="s">
         <v>715</v>
@@ -71126,7 +71126,7 @@
         <v>646</v>
       </c>
       <c r="D135">
-        <v>10250</v>
+        <v>10251</v>
       </c>
       <c r="E135" t="s">
         <v>715</v>
@@ -72035,7 +72035,7 @@
         <v>686</v>
       </c>
       <c r="D180">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E180" t="s">
         <v>715</v>
@@ -72561,7 +72561,7 @@
         <v>706</v>
       </c>
       <c r="D206">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E206" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3872,16 +3872,16 @@
         <v>0</v>
       </c>
       <c r="AP3" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AQ3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" s="1">
         <v>0</v>
@@ -4004,16 +4004,16 @@
         <v>0</v>
       </c>
       <c r="CH3" s="1">
-        <v>2060</v>
+        <v>2076</v>
       </c>
       <c r="CI3" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CJ3" s="2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="CK3" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4040,16 +4040,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46726</v>
+        <v>46743</v>
       </c>
       <c r="CU3" s="1">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="CV3" s="1">
-        <v>850</v>
+        <v>867</v>
       </c>
       <c r="CW3" s="1">
-        <v>2033</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>7007</v>
+        <v>7059</v>
       </c>
       <c r="K4" s="2">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="L4" s="2">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="M4" s="2">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="N4" s="1">
         <v>9299</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM4" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO4" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP4" s="1">
         <v>0</v>
@@ -4309,16 +4309,16 @@
         <v>0</v>
       </c>
       <c r="CH4" s="1">
-        <v>2156</v>
+        <v>2175</v>
       </c>
       <c r="CI4" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="CJ4" s="2">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="CK4" s="2">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4345,16 +4345,16 @@
         <v>0</v>
       </c>
       <c r="CT4" s="1">
-        <v>42911</v>
+        <v>42984</v>
       </c>
       <c r="CU4" s="1">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="CV4" s="1">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="CW4" s="1">
-        <v>1105</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4362,16 +4362,16 @@
         <v>104</v>
       </c>
       <c r="B5" s="1">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1">
         <v>19</v>
@@ -4386,16 +4386,16 @@
         <v>2</v>
       </c>
       <c r="J5" s="1">
-        <v>1185</v>
+        <v>1205</v>
       </c>
       <c r="K5" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M5" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N5" s="1">
         <v>2965</v>
@@ -4650,16 +4650,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38682</v>
+        <v>38703</v>
       </c>
       <c r="CU5" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="CV5" s="1">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="CW5" s="1">
-        <v>794</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5582,16 +5582,16 @@
         <v>108</v>
       </c>
       <c r="B9" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1">
         <v>36</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AP9" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AQ9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -5822,28 +5822,28 @@
         <v>0</v>
       </c>
       <c r="CD9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CE9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH9" s="1">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="CI9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ9" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CK9" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CL9" s="1">
         <v>8</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2862</v>
+        <v>2867</v>
       </c>
       <c r="CU9" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CV9" s="1">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="CW9" s="1">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7520,16 +7520,16 @@
         <v>0</v>
       </c>
       <c r="AL15" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" s="1">
         <v>21</v>
@@ -7664,16 +7664,16 @@
         <v>0</v>
       </c>
       <c r="CH15" s="1">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="CI15" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CJ15" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK15" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL15" s="1">
         <v>2</v>
@@ -7700,16 +7700,16 @@
         <v>0</v>
       </c>
       <c r="CT15" s="1">
-        <v>3415</v>
+        <v>3417</v>
       </c>
       <c r="CU15" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CV15" s="1">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CW15" s="1">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -8937,16 +8937,16 @@
         <v>119</v>
       </c>
       <c r="B20" s="1">
-        <v>5082</v>
+        <v>5114</v>
       </c>
       <c r="C20" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="CH20" s="1">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="CI20" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ20" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="CK20" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9225,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20687</v>
+        <v>20729</v>
       </c>
       <c r="CU20" s="1">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="CV20" s="1">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="CW20" s="1">
-        <v>906</v>
+        <v>948</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11234,7 +11234,7 @@
         <v>0</v>
       </c>
       <c r="BD27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE27" s="2">
         <v>1</v>
@@ -11366,7 +11366,7 @@
         <v>2</v>
       </c>
       <c r="CV27" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW27" s="1">
         <v>62</v>
@@ -11389,28 +11389,28 @@
         <v>7</v>
       </c>
       <c r="F28" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="1">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="K28" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L28" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="M28" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="N28" s="1">
         <v>2024</v>
@@ -11485,28 +11485,28 @@
         <v>0</v>
       </c>
       <c r="AL28" s="1">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AM28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP28" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AQ28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS28" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" s="1">
         <v>0</v>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="CH28" s="1">
-        <v>3012</v>
+        <v>3015</v>
       </c>
       <c r="CI28" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ28" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CK28" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11665,16 +11665,16 @@
         <v>0</v>
       </c>
       <c r="CT28" s="1">
-        <v>24074</v>
+        <v>24090</v>
       </c>
       <c r="CU28" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CV28" s="1">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="CW28" s="1">
-        <v>754</v>
+        <v>770</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12717,16 +12717,16 @@
         <v>4</v>
       </c>
       <c r="AP32" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AQ32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -12750,7 +12750,7 @@
         <v>1</v>
       </c>
       <c r="BA32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB32" s="1">
         <v>3</v>
@@ -12849,16 +12849,16 @@
         <v>0</v>
       </c>
       <c r="CH32" s="1">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="CI32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ32" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CK32" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12885,16 +12885,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11142</v>
+        <v>11144</v>
       </c>
       <c r="CU32" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CV32" s="1">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="CW32" s="1">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -14427,16 +14427,16 @@
         <v>137</v>
       </c>
       <c r="B38" s="1">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" s="1">
         <v>21</v>
@@ -14451,16 +14451,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="K38" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M38" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N38" s="1">
         <v>840</v>
@@ -14715,16 +14715,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1951</v>
+        <v>1958</v>
       </c>
       <c r="CU38" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CV38" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="CW38" s="1">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14732,16 +14732,16 @@
         <v>138</v>
       </c>
       <c r="B39" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C39" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1">
         <v>31</v>
@@ -15020,16 +15020,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="CU39" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CV39" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CW39" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15061,16 +15061,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>4194</v>
+        <v>4215</v>
       </c>
       <c r="K40" s="2">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="L40" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="M40" s="2">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="N40" s="1">
         <v>16656</v>
@@ -15289,16 +15289,16 @@
         <v>0</v>
       </c>
       <c r="CH40" s="1">
-        <v>2351</v>
+        <v>2367</v>
       </c>
       <c r="CI40" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="CJ40" s="2">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="CK40" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="CL40" s="1">
         <v>13</v>
@@ -15325,16 +15325,16 @@
         <v>0</v>
       </c>
       <c r="CT40" s="1">
-        <v>53487</v>
+        <v>53524</v>
       </c>
       <c r="CU40" s="1">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="CV40" s="1">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="CW40" s="1">
-        <v>2114</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -20169,16 +20169,16 @@
         <v>0</v>
       </c>
       <c r="CH56" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="CI56" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CJ56" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CK56" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CL56" s="1">
         <v>2</v>
@@ -20205,16 +20205,16 @@
         <v>0</v>
       </c>
       <c r="CT56" s="1">
-        <v>7796</v>
+        <v>7797</v>
       </c>
       <c r="CU56" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV56" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CW56" s="1">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -21466,16 +21466,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="K61" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L61" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M61" s="2">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N61" s="1">
         <v>43316</v>
@@ -21730,16 +21730,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65919</v>
+        <v>65926</v>
       </c>
       <c r="CU61" s="1">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="CV61" s="1">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="CW61" s="1">
-        <v>921</v>
+        <v>928</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -24187,16 +24187,16 @@
         <v>169</v>
       </c>
       <c r="B70" s="1">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="1">
         <v>15</v>
@@ -24475,16 +24475,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="CU70" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV70" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="CW70" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25515,16 +25515,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36271</v>
+        <v>36284</v>
       </c>
       <c r="AM74" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AN74" s="2">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="AO74" s="2">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25659,16 +25659,16 @@
         <v>0</v>
       </c>
       <c r="CH74" s="1">
-        <v>16207</v>
+        <v>16216</v>
       </c>
       <c r="CI74" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="CJ74" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="CK74" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25695,16 +25695,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171694</v>
+        <v>171716</v>
       </c>
       <c r="CU74" s="1">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="CV74" s="1">
-        <v>1744</v>
+        <v>1766</v>
       </c>
       <c r="CW74" s="1">
-        <v>4363</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26041,16 +26041,16 @@
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>5809</v>
+        <v>5857</v>
       </c>
       <c r="K76" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L76" s="2">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="M76" s="2">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="N76" s="1">
         <v>117545</v>
@@ -26137,16 +26137,16 @@
         <v>3</v>
       </c>
       <c r="AP76" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AQ76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS76" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT76" s="1">
         <v>26</v>
@@ -26269,16 +26269,16 @@
         <v>1</v>
       </c>
       <c r="CH76" s="1">
-        <v>2251</v>
+        <v>2260</v>
       </c>
       <c r="CI76" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="CJ76" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="CK76" s="2">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="CL76" s="1">
         <v>7</v>
@@ -26305,16 +26305,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>151069</v>
+        <v>151127</v>
       </c>
       <c r="CU76" s="1">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="CV76" s="1">
-        <v>1280</v>
+        <v>1338</v>
       </c>
       <c r="CW76" s="1">
-        <v>3699</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26322,16 +26322,16 @@
         <v>176</v>
       </c>
       <c r="B77" s="1">
-        <v>10858</v>
+        <v>10919</v>
       </c>
       <c r="C77" s="2">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D77" s="2">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="E77" s="2">
-        <v>-4395</v>
+        <v>-4334</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26430,16 +26430,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="AM77" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN77" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AO77" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26487,7 +26487,7 @@
         <v>0</v>
       </c>
       <c r="BE77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF77" s="1">
         <v>127</v>
@@ -26574,16 +26574,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7348</v>
+        <v>7356</v>
       </c>
       <c r="CI77" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="CJ77" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="CK77" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26610,16 +26610,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390978</v>
+        <v>391048</v>
       </c>
       <c r="CU77" s="1">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="CV77" s="1">
-        <v>10234</v>
+        <v>10304</v>
       </c>
       <c r="CW77" s="1">
-        <v>15925</v>
+        <v>15994</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26735,16 +26735,16 @@
         <v>0</v>
       </c>
       <c r="AL78" s="1">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="AM78" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN78" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AO78" s="2">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AP78" s="1">
         <v>0</v>
@@ -26879,16 +26879,16 @@
         <v>0</v>
       </c>
       <c r="CH78" s="1">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="CI78" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CJ78" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CK78" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="CL78" s="1">
         <v>0</v>
@@ -26915,16 +26915,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="CU78" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="CV78" s="1">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="CW78" s="1">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -27052,16 +27052,16 @@
         <v>3</v>
       </c>
       <c r="AP79" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT79" s="1">
         <v>6</v>
@@ -27073,7 +27073,7 @@
         <v>3</v>
       </c>
       <c r="AW79" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX79" s="1">
         <v>0</v>
@@ -27184,16 +27184,16 @@
         <v>0</v>
       </c>
       <c r="CH79" s="1">
-        <v>2036</v>
+        <v>2051</v>
       </c>
       <c r="CI79" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="CJ79" s="2">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="CK79" s="2">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="CL79" s="1">
         <v>2</v>
@@ -27220,16 +27220,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90614</v>
+        <v>90630</v>
       </c>
       <c r="CU79" s="1">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="CV79" s="1">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="CW79" s="1">
-        <v>1826</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -28176,16 +28176,16 @@
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8638</v>
+        <v>8710</v>
       </c>
       <c r="K83" s="2">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L83" s="2">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="M83" s="2">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28440,16 +28440,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423902</v>
+        <v>423974</v>
       </c>
       <c r="CU83" s="1">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="CV83" s="1">
-        <v>886</v>
+        <v>958</v>
       </c>
       <c r="CW83" s="1">
-        <v>5426</v>
+        <v>5498</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29689,28 +29689,28 @@
         <v>5</v>
       </c>
       <c r="F88" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J88" s="1">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="K88" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L88" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M88" s="2">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N88" s="1">
         <v>1035</v>
@@ -29965,16 +29965,16 @@
         <v>0</v>
       </c>
       <c r="CT88" s="1">
-        <v>9583</v>
+        <v>9590</v>
       </c>
       <c r="CU88" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CV88" s="1">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="CW88" s="1">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -30616,16 +30616,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>5418</v>
+        <v>5472</v>
       </c>
       <c r="K91" s="2">
-        <v>-1</v>
+        <v>53</v>
       </c>
       <c r="L91" s="2">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="M91" s="2">
-        <v>305</v>
+        <v>359</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30700,16 +30700,16 @@
         <v>0</v>
       </c>
       <c r="AL91" s="1">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="AM91" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN91" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AO91" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AP91" s="1">
         <v>26</v>
@@ -30844,16 +30844,16 @@
         <v>0</v>
       </c>
       <c r="CH91" s="1">
-        <v>7747</v>
+        <v>7789</v>
       </c>
       <c r="CI91" s="2">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="CJ91" s="2">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="CK91" s="2">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30880,16 +30880,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25853</v>
+        <v>25955</v>
       </c>
       <c r="CU91" s="1">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="CV91" s="1">
-        <v>334</v>
+        <v>436</v>
       </c>
       <c r="CW91" s="1">
-        <v>724</v>
+        <v>826</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -31149,16 +31149,16 @@
         <v>0</v>
       </c>
       <c r="CH92" s="1">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="CI92" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CJ92" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CK92" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL92" s="1">
         <v>25</v>
@@ -31185,16 +31185,16 @@
         <v>0</v>
       </c>
       <c r="CT92" s="1">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="CU92" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV92" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CW92" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -33457,16 +33457,16 @@
         <v>16</v>
       </c>
       <c r="AP100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT100" s="1">
         <v>0</v>
@@ -33601,16 +33601,16 @@
         <v>12</v>
       </c>
       <c r="CL100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP100" s="1">
         <v>0</v>
@@ -33625,16 +33625,16 @@
         <v>0</v>
       </c>
       <c r="CT100" s="1">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="CU100" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV100" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW100" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33947,16 +33947,16 @@
         <v>201</v>
       </c>
       <c r="B102" s="1">
-        <v>17506</v>
+        <v>17591</v>
       </c>
       <c r="C102" s="2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D102" s="2">
-        <v>279</v>
+        <v>364</v>
       </c>
       <c r="E102" s="2">
-        <v>665</v>
+        <v>750</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -34079,16 +34079,16 @@
         <v>3</v>
       </c>
       <c r="AT102" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AU102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV102" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW102" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX102" s="1">
         <v>17</v>
@@ -34235,16 +34235,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>43054</v>
+        <v>43140</v>
       </c>
       <c r="CU102" s="1">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="CV102" s="1">
-        <v>661</v>
+        <v>747</v>
       </c>
       <c r="CW102" s="1">
-        <v>1641</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34886,16 +34886,16 @@
         <v>2</v>
       </c>
       <c r="J105" s="1">
-        <v>997</v>
+        <v>1011</v>
       </c>
       <c r="K105" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L105" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M105" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="N105" s="1">
         <v>1428</v>
@@ -35054,16 +35054,16 @@
         <v>0</v>
       </c>
       <c r="BN105" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BO105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR105" s="1">
         <v>66</v>
@@ -35114,16 +35114,16 @@
         <v>0</v>
       </c>
       <c r="CH105" s="1">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="CI105" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CJ105" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CK105" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CL105" s="1">
         <v>26</v>
@@ -35150,16 +35150,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>7988</v>
+        <v>8004</v>
       </c>
       <c r="CU105" s="1">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="CV105" s="1">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="CW105" s="1">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35191,16 +35191,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="1">
-        <v>10792</v>
+        <v>10918</v>
       </c>
       <c r="K106" s="2">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L106" s="2">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="M106" s="2">
-        <v>747</v>
+        <v>873</v>
       </c>
       <c r="N106" s="1">
         <v>22916</v>
@@ -35287,16 +35287,16 @@
         <v>17</v>
       </c>
       <c r="AP106" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT106" s="1">
         <v>0</v>
@@ -35455,16 +35455,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92658</v>
+        <v>92785</v>
       </c>
       <c r="CU106" s="1">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="CV106" s="1">
-        <v>888</v>
+        <v>1015</v>
       </c>
       <c r="CW106" s="1">
-        <v>2340</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36029,16 +36029,16 @@
         <v>0</v>
       </c>
       <c r="CH108" s="1">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CI108" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CJ108" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CK108" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL108" s="1">
         <v>7</v>
@@ -36065,16 +36065,16 @@
         <v>0</v>
       </c>
       <c r="CT108" s="1">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="CU108" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV108" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CW108" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36411,16 +36411,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="1">
-        <v>4913</v>
+        <v>4995</v>
       </c>
       <c r="K110" s="2">
-        <v>-1</v>
+        <v>81</v>
       </c>
       <c r="L110" s="2">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="M110" s="2">
-        <v>364</v>
+        <v>446</v>
       </c>
       <c r="N110" s="1">
         <v>1304</v>
@@ -36495,16 +36495,16 @@
         <v>0</v>
       </c>
       <c r="AL110" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM110" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN110" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO110" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP110" s="1">
         <v>0</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="CH110" s="1">
-        <v>1881</v>
+        <v>1897</v>
       </c>
       <c r="CI110" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CJ110" s="2">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="CK110" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="CL110" s="1">
         <v>0</v>
@@ -36675,16 +36675,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13337</v>
+        <v>13437</v>
       </c>
       <c r="CU110" s="1">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="CV110" s="1">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="CW110" s="1">
-        <v>955</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36800,28 +36800,28 @@
         <v>0</v>
       </c>
       <c r="AL111" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN111" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO111" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP111" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AQ111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR111" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT111" s="1">
         <v>0</v>
@@ -36944,16 +36944,16 @@
         <v>0</v>
       </c>
       <c r="CH111" s="1">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="CI111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ111" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CK111" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36980,16 +36980,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="CU111" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CV111" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="CW111" s="1">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37410,16 +37410,16 @@
         <v>0</v>
       </c>
       <c r="AL113" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AM113" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN113" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO113" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP113" s="1">
         <v>0</v>
@@ -37554,16 +37554,16 @@
         <v>0</v>
       </c>
       <c r="CH113" s="1">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="CI113" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CJ113" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="CK113" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37590,16 +37590,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173851</v>
+        <v>173855</v>
       </c>
       <c r="CU113" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="CV113" s="1">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="CW113" s="1">
-        <v>9843</v>
+        <v>9847</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38241,16 +38241,16 @@
         <v>0</v>
       </c>
       <c r="J116" s="1">
-        <v>4904</v>
+        <v>4940</v>
       </c>
       <c r="K116" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L116" s="2">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="M116" s="2">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="N116" s="1">
         <v>4537</v>
@@ -38325,16 +38325,16 @@
         <v>0</v>
       </c>
       <c r="AL116" s="1">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM116" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN116" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO116" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP116" s="1">
         <v>28</v>
@@ -38469,16 +38469,16 @@
         <v>0</v>
       </c>
       <c r="CH116" s="1">
-        <v>1199</v>
+        <v>1228</v>
       </c>
       <c r="CI116" s="2">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CJ116" s="2">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="CK116" s="2">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38505,16 +38505,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21750</v>
+        <v>21818</v>
       </c>
       <c r="CU116" s="1">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="CV116" s="1">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="CW116" s="1">
-        <v>1088</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -44120,16 +44120,16 @@
         <v>0</v>
       </c>
       <c r="AL135" s="1">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="AM135" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN135" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO135" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AP135" s="1">
         <v>23</v>
@@ -44264,16 +44264,16 @@
         <v>0</v>
       </c>
       <c r="CH135" s="1">
-        <v>3161</v>
+        <v>3179</v>
       </c>
       <c r="CI135" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CJ135" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="CK135" s="2">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="CL135" s="1">
         <v>13</v>
@@ -44300,16 +44300,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62739</v>
+        <v>62761</v>
       </c>
       <c r="CU135" s="1">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="CV135" s="1">
-        <v>964</v>
+        <v>986</v>
       </c>
       <c r="CW135" s="1">
-        <v>2668</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -45077,7 +45077,7 @@
         <v>0</v>
       </c>
       <c r="AZ138" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA138" s="2">
         <v>24</v>
@@ -45221,7 +45221,7 @@
         <v>17</v>
       </c>
       <c r="CV138" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="CW138" s="1">
         <v>264</v>
@@ -45537,16 +45537,16 @@
         <v>239</v>
       </c>
       <c r="B140" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1">
         <v>47</v>
@@ -45789,16 +45789,16 @@
         <v>0</v>
       </c>
       <c r="CH140" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="CI140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL140" s="1">
         <v>11</v>
@@ -45825,16 +45825,16 @@
         <v>0</v>
       </c>
       <c r="CT140" s="1">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CU140" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV140" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CW140" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -45854,16 +45854,16 @@
         <v>12</v>
       </c>
       <c r="F141" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="1">
         <v>26</v>
@@ -46130,16 +46130,16 @@
         <v>0</v>
       </c>
       <c r="CT141" s="1">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="CU141" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV141" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW141" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -47062,16 +47062,16 @@
         <v>244</v>
       </c>
       <c r="B145" s="1">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C145" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D145" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E145" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -47182,16 +47182,16 @@
         <v>0</v>
       </c>
       <c r="AP145" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR145" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS145" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT145" s="1">
         <v>0</v>
@@ -47215,7 +47215,7 @@
         <v>4</v>
       </c>
       <c r="BA145" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB145" s="1">
         <v>0</v>
@@ -47326,16 +47326,16 @@
         <v>11</v>
       </c>
       <c r="CL145" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CM145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN145" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO145" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP145" s="1">
         <v>0</v>
@@ -47350,16 +47350,16 @@
         <v>0</v>
       </c>
       <c r="CT145" s="1">
-        <v>2478</v>
+        <v>2483</v>
       </c>
       <c r="CU145" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CV145" s="1">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="CW145" s="1">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -49012,16 +49012,16 @@
         <v>3</v>
       </c>
       <c r="AP151" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS151" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT151" s="1">
         <v>0</v>
@@ -49144,28 +49144,28 @@
         <v>0</v>
       </c>
       <c r="CH151" s="1">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CI151" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ151" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CK151" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CL151" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CM151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP151" s="1">
         <v>0</v>
@@ -49180,16 +49180,16 @@
         <v>0</v>
       </c>
       <c r="CT151" s="1">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="CU151" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV151" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CW151" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -50232,16 +50232,16 @@
         <v>0</v>
       </c>
       <c r="AP155" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AQ155" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR155" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS155" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT155" s="1">
         <v>1</v>
@@ -50364,16 +50364,16 @@
         <v>0</v>
       </c>
       <c r="CH155" s="1">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CI155" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CJ155" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CK155" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CL155" s="1">
         <v>1</v>
@@ -50400,16 +50400,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="CU155" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CV155" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CW155" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50722,16 +50722,16 @@
         <v>256</v>
       </c>
       <c r="B157" s="1">
-        <v>4973</v>
+        <v>5004</v>
       </c>
       <c r="C157" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D157" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="E157" s="2">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -50746,16 +50746,16 @@
         <v>0</v>
       </c>
       <c r="J157" s="1">
-        <v>3472</v>
+        <v>3516</v>
       </c>
       <c r="K157" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L157" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="M157" s="2">
-        <v>263</v>
+        <v>307</v>
       </c>
       <c r="N157" s="1">
         <v>11983</v>
@@ -51010,16 +51010,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166337</v>
+        <v>166412</v>
       </c>
       <c r="CU157" s="1">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="CV157" s="1">
-        <v>5156</v>
+        <v>5231</v>
       </c>
       <c r="CW157" s="1">
-        <v>9102</v>
+        <v>9177</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51027,16 +51027,16 @@
         <v>257</v>
       </c>
       <c r="B158" s="1">
-        <v>8243</v>
+        <v>8297</v>
       </c>
       <c r="C158" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D158" s="2">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="E158" s="2">
-        <v>353</v>
+        <v>407</v>
       </c>
       <c r="F158" s="1">
         <v>2</v>
@@ -51051,16 +51051,16 @@
         <v>0</v>
       </c>
       <c r="J158" s="1">
-        <v>7081</v>
+        <v>7116</v>
       </c>
       <c r="K158" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L158" s="2">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="M158" s="2">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="N158" s="1">
         <v>3024</v>
@@ -51135,16 +51135,16 @@
         <v>0</v>
       </c>
       <c r="AL158" s="1">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="AM158" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AN158" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AO158" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AP158" s="1">
         <v>3</v>
@@ -51279,16 +51279,16 @@
         <v>1</v>
       </c>
       <c r="CH158" s="1">
-        <v>5929</v>
+        <v>6072</v>
       </c>
       <c r="CI158" s="2">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="CJ158" s="2">
-        <v>237</v>
+        <v>380</v>
       </c>
       <c r="CK158" s="2">
-        <v>546</v>
+        <v>689</v>
       </c>
       <c r="CL158" s="1">
         <v>0</v>
@@ -51315,16 +51315,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25462</v>
+        <v>25700</v>
       </c>
       <c r="CU158" s="1">
-        <v>140</v>
+        <v>378</v>
       </c>
       <c r="CV158" s="1">
-        <v>677</v>
+        <v>915</v>
       </c>
       <c r="CW158" s="1">
-        <v>1476</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51942,16 +51942,16 @@
         <v>260</v>
       </c>
       <c r="B161" s="1">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="C161" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D161" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E161" s="2">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F161" s="1">
         <v>2</v>
@@ -51966,16 +51966,16 @@
         <v>0</v>
       </c>
       <c r="J161" s="1">
-        <v>3318</v>
+        <v>3333</v>
       </c>
       <c r="K161" s="2">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L161" s="2">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="M161" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N161" s="1">
         <v>10033</v>
@@ -52230,16 +52230,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22386</v>
+        <v>22410</v>
       </c>
       <c r="CU161" s="1">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="CV161" s="1">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="CW161" s="1">
-        <v>1229</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -54711,16 +54711,16 @@
         <v>0</v>
       </c>
       <c r="J170" s="1">
-        <v>6367</v>
+        <v>6413</v>
       </c>
       <c r="K170" s="2">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="L170" s="2">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="M170" s="2">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54795,16 +54795,16 @@
         <v>0</v>
       </c>
       <c r="AL170" s="1">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM170" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN170" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO170" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP170" s="1">
         <v>36</v>
@@ -54939,16 +54939,16 @@
         <v>0</v>
       </c>
       <c r="CH170" s="1">
-        <v>1451</v>
+        <v>1492</v>
       </c>
       <c r="CI170" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="CJ170" s="2">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="CK170" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="CL170" s="1">
         <v>17</v>
@@ -54975,16 +54975,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19536</v>
+        <v>19624</v>
       </c>
       <c r="CU170" s="1">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="CV170" s="1">
-        <v>392</v>
+        <v>480</v>
       </c>
       <c r="CW170" s="1">
-        <v>1162</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55244,16 +55244,16 @@
         <v>0</v>
       </c>
       <c r="CH171" s="1">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="CI171" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CJ171" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CK171" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CL171" s="1">
         <v>6</v>
@@ -55280,16 +55280,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5840</v>
+        <v>5846</v>
       </c>
       <c r="CU171" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV171" s="1">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="CW171" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -56625,16 +56625,16 @@
         <v>0</v>
       </c>
       <c r="AL176" s="1">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN176" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO176" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP176" s="1">
         <v>0</v>
@@ -56769,16 +56769,16 @@
         <v>0</v>
       </c>
       <c r="CH176" s="1">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="CI176" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ176" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="CK176" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56805,16 +56805,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1314</v>
+        <v>1326</v>
       </c>
       <c r="CU176" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="CV176" s="1">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="CW176" s="1">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57737,16 +57737,16 @@
         <v>279</v>
       </c>
       <c r="B180" s="1">
-        <v>8072</v>
+        <v>8113</v>
       </c>
       <c r="C180" s="2">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D180" s="2">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="E180" s="2">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -58025,16 +58025,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51185</v>
+        <v>51226</v>
       </c>
       <c r="CU180" s="1">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="CV180" s="1">
-        <v>1193</v>
+        <v>1234</v>
       </c>
       <c r="CW180" s="1">
-        <v>2698</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -59884,292 +59884,292 @@
         <v>0</v>
       </c>
       <c r="F187" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G187" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" s="2">
+        <v>3</v>
+      </c>
+      <c r="I187" s="2">
+        <v>6</v>
+      </c>
+      <c r="J187" s="1">
+        <v>0</v>
+      </c>
+      <c r="K187" s="2">
+        <v>0</v>
+      </c>
+      <c r="L187" s="2">
+        <v>0</v>
+      </c>
+      <c r="M187" s="2">
+        <v>0</v>
+      </c>
+      <c r="N187" s="1">
+        <v>0</v>
+      </c>
+      <c r="O187" s="2">
+        <v>0</v>
+      </c>
+      <c r="P187" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="2">
+        <v>0</v>
+      </c>
+      <c r="R187" s="1">
+        <v>0</v>
+      </c>
+      <c r="S187" s="2">
+        <v>0</v>
+      </c>
+      <c r="T187" s="2">
+        <v>0</v>
+      </c>
+      <c r="U187" s="2">
+        <v>0</v>
+      </c>
+      <c r="V187" s="1">
+        <v>0</v>
+      </c>
+      <c r="W187" s="2">
+        <v>0</v>
+      </c>
+      <c r="X187" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP187" s="1">
+        <v>1</v>
+      </c>
+      <c r="AQ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX187" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY187" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV187" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY187" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ187" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD187" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH187" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL187" s="1">
+        <v>1</v>
+      </c>
+      <c r="CM187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP187" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS187" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT187" s="1">
+        <v>82</v>
+      </c>
+      <c r="CU187" s="1">
         <v>2</v>
       </c>
-      <c r="I187" s="2">
-        <v>5</v>
-      </c>
-      <c r="J187" s="1">
-        <v>0</v>
-      </c>
-      <c r="K187" s="2">
-        <v>0</v>
-      </c>
-      <c r="L187" s="2">
-        <v>0</v>
-      </c>
-      <c r="M187" s="2">
-        <v>0</v>
-      </c>
-      <c r="N187" s="1">
-        <v>0</v>
-      </c>
-      <c r="O187" s="2">
-        <v>0</v>
-      </c>
-      <c r="P187" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q187" s="2">
-        <v>0</v>
-      </c>
-      <c r="R187" s="1">
-        <v>0</v>
-      </c>
-      <c r="S187" s="2">
-        <v>0</v>
-      </c>
-      <c r="T187" s="2">
-        <v>0</v>
-      </c>
-      <c r="U187" s="2">
-        <v>0</v>
-      </c>
-      <c r="V187" s="1">
-        <v>0</v>
-      </c>
-      <c r="W187" s="2">
-        <v>0</v>
-      </c>
-      <c r="X187" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y187" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP187" s="1">
-        <v>1</v>
-      </c>
-      <c r="AQ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX187" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY187" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV187" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY187" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ187" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD187" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH187" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL187" s="1">
-        <v>1</v>
-      </c>
-      <c r="CM187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP187" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS187" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT187" s="1">
-        <v>81</v>
-      </c>
-      <c r="CU187" s="1">
-        <v>1</v>
-      </c>
       <c r="CV187" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW187" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:101">
@@ -62031,16 +62031,16 @@
         <v>0</v>
       </c>
       <c r="J194" s="1">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="K194" s="2">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L194" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M194" s="2">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="N194" s="1">
         <v>29177</v>
@@ -62295,16 +62295,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32865</v>
+        <v>32879</v>
       </c>
       <c r="CU194" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="CV194" s="1">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="CW194" s="1">
-        <v>1372</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62725,16 +62725,16 @@
         <v>0</v>
       </c>
       <c r="AL196" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AM196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN196" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO196" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP196" s="1">
         <v>15</v>
@@ -62869,16 +62869,16 @@
         <v>0</v>
       </c>
       <c r="CH196" s="1">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="CI196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ196" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CK196" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CL196" s="1">
         <v>3</v>
@@ -62905,16 +62905,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5481</v>
+        <v>5483</v>
       </c>
       <c r="CU196" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV196" s="1">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="CW196" s="1">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63861,16 +63861,16 @@
         <v>0</v>
       </c>
       <c r="J200" s="1">
-        <v>2036</v>
+        <v>2058</v>
       </c>
       <c r="K200" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L200" s="2">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="M200" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="N200" s="1">
         <v>7999</v>
@@ -64125,16 +64125,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16334</v>
+        <v>16356</v>
       </c>
       <c r="CU200" s="1">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="CV200" s="1">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="CW200" s="1">
-        <v>504</v>
+        <v>526</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64166,16 +64166,16 @@
         <v>0</v>
       </c>
       <c r="J201" s="1">
-        <v>3540</v>
+        <v>3569</v>
       </c>
       <c r="K201" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L201" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="M201" s="2">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="N201" s="1">
         <v>23253</v>
@@ -64430,16 +64430,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88103</v>
+        <v>88132</v>
       </c>
       <c r="CU201" s="1">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="CV201" s="1">
-        <v>1977</v>
+        <v>2006</v>
       </c>
       <c r="CW201" s="1">
-        <v>3138</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64462,7 +64462,7 @@
         <v>20</v>
       </c>
       <c r="G202" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H202" s="2">
         <v>2</v>
@@ -64738,7 +64738,7 @@
         <v>909</v>
       </c>
       <c r="CU202" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="CV202" s="1">
         <v>58</v>
@@ -65972,16 +65972,16 @@
         <v>306</v>
       </c>
       <c r="B207" s="1">
-        <v>1378</v>
+        <v>1397</v>
       </c>
       <c r="C207" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D207" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E207" s="2">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -65996,16 +65996,16 @@
         <v>0</v>
       </c>
       <c r="J207" s="1">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K207" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L207" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M207" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N207" s="1">
         <v>5091</v>
@@ -66092,16 +66092,16 @@
         <v>0</v>
       </c>
       <c r="AP207" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AQ207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR207" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS207" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT207" s="1">
         <v>0</v>
@@ -66224,28 +66224,28 @@
         <v>0</v>
       </c>
       <c r="CH207" s="1">
-        <v>3204</v>
+        <v>3212</v>
       </c>
       <c r="CI207" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CJ207" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="CK207" s="2">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="CL207" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CM207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO207" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP207" s="1">
         <v>2</v>
@@ -66260,16 +66260,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>14059</v>
+        <v>14091</v>
       </c>
       <c r="CU207" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CV207" s="1">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="CW207" s="1">
-        <v>617</v>
+        <v>649</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -67216,16 +67216,16 @@
         <v>1</v>
       </c>
       <c r="J211" s="1">
-        <v>1262</v>
+        <v>1277</v>
       </c>
       <c r="K211" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L211" s="2">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M211" s="2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N211" s="1">
         <v>820</v>
@@ -67480,16 +67480,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>6274</v>
+        <v>6289</v>
       </c>
       <c r="CU211" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="CV211" s="1">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="CW211" s="1">
-        <v>671</v>
+        <v>686</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69054,7 +69054,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E32" t="s">
         <v>715</v>
@@ -69997,7 +69997,7 @@
         <v>598</v>
       </c>
       <c r="D79">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E79" t="s">
         <v>715</v>
@@ -72561,7 +72561,7 @@
         <v>706</v>
       </c>
       <c r="D206">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E206" t="s">
         <v>715</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4084,7 +4084,7 @@
         <v>7059</v>
       </c>
       <c r="K4" s="2">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="L4" s="2">
         <v>183</v>
@@ -4168,10 +4168,10 @@
         <v>190</v>
       </c>
       <c r="AM4" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN4" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO4" s="2">
         <v>9</v>
@@ -4312,10 +4312,10 @@
         <v>2175</v>
       </c>
       <c r="CI4" s="2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="CJ4" s="2">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="CK4" s="2">
         <v>141</v>
@@ -4348,10 +4348,10 @@
         <v>42984</v>
       </c>
       <c r="CU4" s="1">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="CV4" s="1">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="CW4" s="1">
         <v>1178</v>
@@ -7667,7 +7667,7 @@
         <v>374</v>
       </c>
       <c r="CI15" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CJ15" s="2">
         <v>21</v>
@@ -7703,7 +7703,7 @@
         <v>3417</v>
       </c>
       <c r="CU15" s="1">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="CV15" s="1">
         <v>181</v>
@@ -8345,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -8621,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="CV18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW18" s="1">
         <v>6</v>
@@ -8940,7 +8940,7 @@
         <v>5114</v>
       </c>
       <c r="C20" s="2">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2">
         <v>100</v>
@@ -9228,7 +9228,7 @@
         <v>20729</v>
       </c>
       <c r="CU20" s="1">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="CV20" s="1">
         <v>375</v>
@@ -9365,7 +9365,7 @@
         <v>18</v>
       </c>
       <c r="AQ21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR21" s="2">
         <v>3</v>
@@ -9497,7 +9497,7 @@
         <v>237</v>
       </c>
       <c r="CI21" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="CJ21" s="2">
         <v>30</v>
@@ -9533,7 +9533,7 @@
         <v>375</v>
       </c>
       <c r="CU21" s="1">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="CV21" s="1">
         <v>33</v>
@@ -12403,7 +12403,7 @@
         <v>340</v>
       </c>
       <c r="AM31" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="2">
         <v>9</v>
@@ -12547,7 +12547,7 @@
         <v>713</v>
       </c>
       <c r="CI31" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="CJ31" s="2">
         <v>159</v>
@@ -12583,7 +12583,7 @@
         <v>6012</v>
       </c>
       <c r="CU31" s="1">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="CV31" s="1">
         <v>266</v>
@@ -12603,7 +12603,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="2">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2">
         <v>102</v>
@@ -12891,7 +12891,7 @@
         <v>52</v>
       </c>
       <c r="CV32" s="1">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="CW32" s="1">
         <v>555</v>
@@ -13832,13 +13832,13 @@
         <v>36</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>3</v>
       </c>
       <c r="I36" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -14108,13 +14108,13 @@
         <v>38</v>
       </c>
       <c r="CU36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV36" s="1">
         <v>3</v>
       </c>
       <c r="CW36" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:101">
@@ -14846,7 +14846,7 @@
         <v>5</v>
       </c>
       <c r="AN39" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AO39" s="2">
         <v>12</v>
@@ -14990,7 +14990,7 @@
         <v>31</v>
       </c>
       <c r="CJ39" s="2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="CK39" s="2">
         <v>77</v>
@@ -15026,7 +15026,7 @@
         <v>39</v>
       </c>
       <c r="CV39" s="1">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="CW39" s="1">
         <v>100</v>
@@ -15064,7 +15064,7 @@
         <v>4215</v>
       </c>
       <c r="K40" s="2">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L40" s="2">
         <v>94</v>
@@ -15292,7 +15292,7 @@
         <v>2367</v>
       </c>
       <c r="CI40" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="CJ40" s="2">
         <v>49</v>
@@ -15328,7 +15328,7 @@
         <v>53524</v>
       </c>
       <c r="CU40" s="1">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="CV40" s="1">
         <v>813</v>
@@ -18808,7 +18808,7 @@
         <v>131</v>
       </c>
       <c r="AM52" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN52" s="2">
         <v>4</v>
@@ -18988,7 +18988,7 @@
         <v>318</v>
       </c>
       <c r="CU52" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CV52" s="1">
         <v>6</v>
@@ -20172,7 +20172,7 @@
         <v>562</v>
       </c>
       <c r="CI56" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CJ56" s="2">
         <v>13</v>
@@ -20208,7 +20208,7 @@
         <v>7797</v>
       </c>
       <c r="CU56" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CV56" s="1">
         <v>100</v>
@@ -22447,7 +22447,7 @@
         <v>4</v>
       </c>
       <c r="AF64" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AG64" s="2">
         <v>160</v>
@@ -22651,7 +22651,7 @@
         <v>87</v>
       </c>
       <c r="CV64" s="1">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="CW64" s="1">
         <v>461</v>
@@ -22665,7 +22665,7 @@
         <v>3716</v>
       </c>
       <c r="C65" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D65" s="2">
         <v>47</v>
@@ -22689,7 +22689,7 @@
         <v>1800</v>
       </c>
       <c r="K65" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L65" s="2">
         <v>48</v>
@@ -22953,7 +22953,7 @@
         <v>67220</v>
       </c>
       <c r="CU65" s="1">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="CV65" s="1">
         <v>1772</v>
@@ -22994,7 +22994,7 @@
         <v>976</v>
       </c>
       <c r="K66" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2">
         <v>40</v>
@@ -23258,7 +23258,7 @@
         <v>1659</v>
       </c>
       <c r="CU66" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="CV66" s="1">
         <v>46</v>
@@ -23604,7 +23604,7 @@
         <v>308</v>
       </c>
       <c r="K68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2">
         <v>2</v>
@@ -23868,7 +23868,7 @@
         <v>2132</v>
       </c>
       <c r="CU68" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV68" s="1">
         <v>5</v>
@@ -23897,7 +23897,7 @@
         <v>70</v>
       </c>
       <c r="G69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2">
         <v>6</v>
@@ -24173,7 +24173,7 @@
         <v>108</v>
       </c>
       <c r="CU69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV69" s="1">
         <v>9</v>
@@ -25410,7 +25410,7 @@
         <v>12604</v>
       </c>
       <c r="C74" s="2">
-        <v>35</v>
+        <v>-1</v>
       </c>
       <c r="D74" s="2">
         <v>73</v>
@@ -25518,10 +25518,10 @@
         <v>36284</v>
       </c>
       <c r="AM74" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AN74" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AO74" s="2">
         <v>393</v>
@@ -25665,7 +25665,7 @@
         <v>49</v>
       </c>
       <c r="CJ74" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="CK74" s="2">
         <v>428</v>
@@ -25698,10 +25698,10 @@
         <v>171716</v>
       </c>
       <c r="CU74" s="1">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="CV74" s="1">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="CW74" s="1">
         <v>4385</v>
@@ -26128,7 +26128,7 @@
         <v>309</v>
       </c>
       <c r="AM76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN76" s="2">
         <v>1</v>
@@ -26272,7 +26272,7 @@
         <v>2260</v>
       </c>
       <c r="CI76" s="2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="CJ76" s="2">
         <v>34</v>
@@ -26308,7 +26308,7 @@
         <v>151127</v>
       </c>
       <c r="CU76" s="1">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="CV76" s="1">
         <v>1338</v>
@@ -26325,7 +26325,7 @@
         <v>10919</v>
       </c>
       <c r="C77" s="2">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D77" s="2">
         <v>95</v>
@@ -26577,7 +26577,7 @@
         <v>7356</v>
       </c>
       <c r="CI77" s="2">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="CJ77" s="2">
         <v>333</v>
@@ -26613,7 +26613,7 @@
         <v>391048</v>
       </c>
       <c r="CU77" s="1">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="CV77" s="1">
         <v>10304</v>
@@ -28263,7 +28263,7 @@
         <v>3401</v>
       </c>
       <c r="AM83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN83" s="2">
         <v>14</v>
@@ -28443,7 +28443,7 @@
         <v>423974</v>
       </c>
       <c r="CU83" s="1">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="CV83" s="1">
         <v>958</v>
@@ -30598,7 +30598,7 @@
         <v>16</v>
       </c>
       <c r="D91" s="2">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E91" s="2">
         <v>177</v>
@@ -30847,7 +30847,7 @@
         <v>7789</v>
       </c>
       <c r="CI91" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="CJ91" s="2">
         <v>117</v>
@@ -30883,10 +30883,10 @@
         <v>25955</v>
       </c>
       <c r="CU91" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="CV91" s="1">
-        <v>436</v>
+        <v>379</v>
       </c>
       <c r="CW91" s="1">
         <v>826</v>
@@ -31152,7 +31152,7 @@
         <v>685</v>
       </c>
       <c r="CI92" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CJ92" s="2">
         <v>8</v>
@@ -31188,7 +31188,7 @@
         <v>3796</v>
       </c>
       <c r="CU92" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CV92" s="1">
         <v>35</v>
@@ -32437,10 +32437,10 @@
         <v>78</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I97" s="2">
         <v>5</v>
@@ -32713,10 +32713,10 @@
         <v>223</v>
       </c>
       <c r="CU97" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV97" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW97" s="1">
         <v>16</v>
@@ -33355,7 +33355,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I100" s="2">
         <v>5</v>
@@ -33631,7 +33631,7 @@
         <v>3</v>
       </c>
       <c r="CV100" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW100" s="1">
         <v>35</v>
@@ -34889,7 +34889,7 @@
         <v>1011</v>
       </c>
       <c r="K105" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L105" s="2">
         <v>47</v>
@@ -35153,7 +35153,7 @@
         <v>8004</v>
       </c>
       <c r="CU105" s="1">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="CV105" s="1">
         <v>225</v>
@@ -37000,10 +37000,10 @@
         <v>990</v>
       </c>
       <c r="C112" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E112" s="2">
         <v>48</v>
@@ -37288,10 +37288,10 @@
         <v>8297</v>
       </c>
       <c r="CU112" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="CV112" s="1">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="CW112" s="1">
         <v>647</v>
@@ -37557,10 +37557,10 @@
         <v>1488</v>
       </c>
       <c r="CI113" s="2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="CJ113" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="CK113" s="2">
         <v>149</v>
@@ -37593,10 +37593,10 @@
         <v>173855</v>
       </c>
       <c r="CU113" s="1">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="CV113" s="1">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="CW113" s="1">
         <v>9847</v>
@@ -38472,7 +38472,7 @@
         <v>1228</v>
       </c>
       <c r="CI116" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CJ116" s="2">
         <v>51</v>
@@ -38508,7 +38508,7 @@
         <v>21818</v>
       </c>
       <c r="CU116" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CV116" s="1">
         <v>390</v>
@@ -38938,7 +38938,7 @@
         <v>2</v>
       </c>
       <c r="AM118" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN118" s="2">
         <v>2</v>
@@ -38950,7 +38950,7 @@
         <v>2</v>
       </c>
       <c r="AQ118" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR118" s="2">
         <v>2</v>
@@ -39082,7 +39082,7 @@
         <v>31</v>
       </c>
       <c r="CI118" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CJ118" s="2">
         <v>18</v>
@@ -39118,7 +39118,7 @@
         <v>139</v>
       </c>
       <c r="CU118" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="CV118" s="1">
         <v>25</v>
@@ -44954,7 +44954,7 @@
         <v>1208</v>
       </c>
       <c r="K138" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L138" s="2">
         <v>28</v>
@@ -45218,7 +45218,7 @@
         <v>4407</v>
       </c>
       <c r="CU138" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="CV138" s="1">
         <v>115</v>
@@ -46162,7 +46162,7 @@
         <v>15</v>
       </c>
       <c r="G142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2">
         <v>2</v>
@@ -46438,7 +46438,7 @@
         <v>1655</v>
       </c>
       <c r="CU142" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CV142" s="1">
         <v>58</v>
@@ -49203,7 +49203,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="2">
         <v>6</v>
@@ -49491,7 +49491,7 @@
         <v>14</v>
       </c>
       <c r="CV152" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="CW152" s="1">
         <v>275</v>
@@ -50833,7 +50833,7 @@
         <v>1050</v>
       </c>
       <c r="AM157" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN157" s="2">
         <v>3</v>
@@ -50977,10 +50977,10 @@
         <v>4861</v>
       </c>
       <c r="CI157" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="CJ157" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="CK157" s="2">
         <v>208</v>
@@ -51013,10 +51013,10 @@
         <v>166412</v>
       </c>
       <c r="CU157" s="1">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="CV157" s="1">
-        <v>5231</v>
+        <v>5229</v>
       </c>
       <c r="CW157" s="1">
         <v>9177</v>
@@ -51057,7 +51057,7 @@
         <v>35</v>
       </c>
       <c r="L158" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M158" s="2">
         <v>414</v>
@@ -51138,7 +51138,7 @@
         <v>530</v>
       </c>
       <c r="AM158" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AN158" s="2">
         <v>22</v>
@@ -51282,7 +51282,7 @@
         <v>6072</v>
       </c>
       <c r="CI158" s="2">
-        <v>270</v>
+        <v>143</v>
       </c>
       <c r="CJ158" s="2">
         <v>380</v>
@@ -51318,10 +51318,10 @@
         <v>25700</v>
       </c>
       <c r="CU158" s="1">
-        <v>378</v>
+        <v>239</v>
       </c>
       <c r="CV158" s="1">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="CW158" s="1">
         <v>1714</v>
@@ -51969,7 +51969,7 @@
         <v>3333</v>
       </c>
       <c r="K161" s="2">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="L161" s="2">
         <v>74</v>
@@ -52233,7 +52233,7 @@
         <v>22410</v>
       </c>
       <c r="CU161" s="1">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="CV161" s="1">
         <v>724</v>
@@ -52807,7 +52807,7 @@
         <v>163</v>
       </c>
       <c r="CI163" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ163" s="2">
         <v>5</v>
@@ -52843,7 +52843,7 @@
         <v>1131</v>
       </c>
       <c r="CU163" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV163" s="1">
         <v>18</v>
@@ -54714,7 +54714,7 @@
         <v>6413</v>
       </c>
       <c r="K170" s="2">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="L170" s="2">
         <v>145</v>
@@ -54978,7 +54978,7 @@
         <v>19624</v>
       </c>
       <c r="CU170" s="1">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="CV170" s="1">
         <v>480</v>
@@ -55910,7 +55910,7 @@
         <v>25</v>
       </c>
       <c r="C174" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D174" s="2">
         <v>3</v>
@@ -56030,7 +56030,7 @@
         <v>109</v>
       </c>
       <c r="AQ174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR174" s="2">
         <v>2</v>
@@ -56174,7 +56174,7 @@
         <v>82</v>
       </c>
       <c r="CM174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN174" s="2">
         <v>4</v>
@@ -56198,7 +56198,7 @@
         <v>488</v>
       </c>
       <c r="CU174" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CV174" s="1">
         <v>23</v>
@@ -56532,13 +56532,13 @@
         <v>52</v>
       </c>
       <c r="G176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="2">
         <v>1</v>
       </c>
       <c r="I176" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J176" s="1">
         <v>0</v>
@@ -56808,13 +56808,13 @@
         <v>1326</v>
       </c>
       <c r="CU176" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV176" s="1">
         <v>83</v>
       </c>
       <c r="CW176" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -58060,7 +58060,7 @@
         <v>1</v>
       </c>
       <c r="H181" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I181" s="2">
         <v>5</v>
@@ -58336,7 +58336,7 @@
         <v>1</v>
       </c>
       <c r="CV181" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW181" s="1">
         <v>5</v>
@@ -59887,7 +59887,7 @@
         <v>74</v>
       </c>
       <c r="G187" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="2">
         <v>3</v>
@@ -60163,7 +60163,7 @@
         <v>82</v>
       </c>
       <c r="CU187" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV187" s="1">
         <v>3</v>
@@ -61338,7 +61338,7 @@
         <v>0</v>
       </c>
       <c r="CF191" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG191" s="2">
         <v>1</v>
@@ -61386,7 +61386,7 @@
         <v>0</v>
       </c>
       <c r="CV191" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW191" s="1">
         <v>36</v>
@@ -61412,10 +61412,10 @@
         <v>76</v>
       </c>
       <c r="G192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I192" s="2">
         <v>5</v>
@@ -61688,10 +61688,10 @@
         <v>614</v>
       </c>
       <c r="CU192" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV192" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW192" s="1">
         <v>25</v>
@@ -62034,7 +62034,7 @@
         <v>974</v>
       </c>
       <c r="K194" s="2">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="L194" s="2">
         <v>47</v>
@@ -62298,7 +62298,7 @@
         <v>32879</v>
       </c>
       <c r="CU194" s="1">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="CV194" s="1">
         <v>592</v>
@@ -62315,7 +62315,7 @@
         <v>232</v>
       </c>
       <c r="C195" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D195" s="2">
         <v>2</v>
@@ -62603,7 +62603,7 @@
         <v>71198</v>
       </c>
       <c r="CU195" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV195" s="1">
         <v>3368</v>
@@ -64558,7 +64558,7 @@
         <v>445</v>
       </c>
       <c r="AM202" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AN202" s="2">
         <v>35</v>
@@ -64702,7 +64702,7 @@
         <v>428</v>
       </c>
       <c r="CI202" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CJ202" s="2">
         <v>20</v>
@@ -64738,7 +64738,7 @@
         <v>909</v>
       </c>
       <c r="CU202" s="1">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="CV202" s="1">
         <v>58</v>
@@ -66693,7 +66693,7 @@
         <v>32</v>
       </c>
       <c r="AM209" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN209" s="2">
         <v>7</v>
@@ -66837,7 +66837,7 @@
         <v>245</v>
       </c>
       <c r="CI209" s="2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="CJ209" s="2">
         <v>39</v>
@@ -66873,7 +66873,7 @@
         <v>735</v>
       </c>
       <c r="CU209" s="1">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="CV209" s="1">
         <v>65</v>
@@ -66905,7 +66905,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="2">
         <v>4</v>
@@ -67097,7 +67097,7 @@
         <v>0</v>
       </c>
       <c r="BT210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU210" s="2">
         <v>1</v>
@@ -67181,7 +67181,7 @@
         <v>3</v>
       </c>
       <c r="CV210" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CW210" s="1">
         <v>32</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="842">
   <si>
     <t>ati_all</t>
   </si>
@@ -1719,6 +1719,9 @@
   </si>
   <si>
     <t>ATIPCoordinator@cihr-irsc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@bch-mc.ca</t>
   </si>
   <si>
     <t>atip-aiprp@clc-sic.ca</t>
@@ -3142,292 +3145,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -8979,7 +8982,7 @@
         <v>3</v>
       </c>
       <c r="P20" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q20" s="2">
         <v>607</v>
@@ -9231,7 +9234,7 @@
         <v>46</v>
       </c>
       <c r="CV20" s="1">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="CW20" s="1">
         <v>948</v>
@@ -13835,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -14111,7 +14114,7 @@
         <v>0</v>
       </c>
       <c r="CV36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW36" s="1">
         <v>5</v>
@@ -14550,7 +14553,7 @@
         <v>42</v>
       </c>
       <c r="AQ38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR38" s="2">
         <v>3</v>
@@ -14694,7 +14697,7 @@
         <v>30</v>
       </c>
       <c r="CM38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN38" s="2">
         <v>3</v>
@@ -14718,7 +14721,7 @@
         <v>1958</v>
       </c>
       <c r="CU38" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV38" s="1">
         <v>43</v>
@@ -18650,7 +18653,7 @@
         <v>1757</v>
       </c>
       <c r="CJ51" s="2">
-        <v>1822</v>
+        <v>1795</v>
       </c>
       <c r="CK51" s="2">
         <v>1930</v>
@@ -18686,7 +18689,7 @@
         <v>1947</v>
       </c>
       <c r="CV51" s="1">
-        <v>2025</v>
+        <v>1998</v>
       </c>
       <c r="CW51" s="1">
         <v>2152</v>
@@ -23275,7 +23278,7 @@
         <v>2481</v>
       </c>
       <c r="C67" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2">
         <v>44</v>
@@ -23563,7 +23566,7 @@
         <v>3358</v>
       </c>
       <c r="CU67" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CV67" s="1">
         <v>44</v>
@@ -25665,7 +25668,7 @@
         <v>49</v>
       </c>
       <c r="CJ74" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="CK74" s="2">
         <v>428</v>
@@ -25701,7 +25704,7 @@
         <v>106</v>
       </c>
       <c r="CV74" s="1">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="CW74" s="1">
         <v>4385</v>
@@ -26577,7 +26580,7 @@
         <v>7356</v>
       </c>
       <c r="CI77" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="CJ77" s="2">
         <v>333</v>
@@ -26613,7 +26616,7 @@
         <v>391048</v>
       </c>
       <c r="CU77" s="1">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="CV77" s="1">
         <v>10304</v>
@@ -27187,7 +27190,7 @@
         <v>2051</v>
       </c>
       <c r="CI79" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CJ79" s="2">
         <v>49</v>
@@ -27223,7 +27226,7 @@
         <v>90630</v>
       </c>
       <c r="CU79" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV79" s="1">
         <v>584</v>
@@ -27351,7 +27354,7 @@
         <v>19</v>
       </c>
       <c r="AN80" s="2">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="AO80" s="2">
         <v>128</v>
@@ -27495,7 +27498,7 @@
         <v>15</v>
       </c>
       <c r="CJ80" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="CK80" s="2">
         <v>116</v>
@@ -27531,7 +27534,7 @@
         <v>40</v>
       </c>
       <c r="CV80" s="1">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="CW80" s="1">
         <v>258</v>
@@ -29325,7 +29328,7 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CK86" s="2">
         <v>16</v>
@@ -29361,7 +29364,7 @@
         <v>2</v>
       </c>
       <c r="CV86" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CW86" s="1">
         <v>73</v>
@@ -29390,7 +29393,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" s="2">
         <v>3</v>
@@ -29666,7 +29669,7 @@
         <v>11</v>
       </c>
       <c r="CV87" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CW87" s="1">
         <v>109</v>
@@ -30595,7 +30598,7 @@
         <v>7101</v>
       </c>
       <c r="C91" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D91" s="2">
         <v>53</v>
@@ -30850,7 +30853,7 @@
         <v>42</v>
       </c>
       <c r="CJ91" s="2">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="CK91" s="2">
         <v>195</v>
@@ -30883,10 +30886,10 @@
         <v>25955</v>
       </c>
       <c r="CU91" s="1">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="CV91" s="1">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="CW91" s="1">
         <v>826</v>
@@ -33047,7 +33050,7 @@
         <v>80</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="2">
         <v>3</v>
@@ -33323,7 +33326,7 @@
         <v>80</v>
       </c>
       <c r="CU99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV99" s="1">
         <v>3</v>
@@ -33352,7 +33355,7 @@
         <v>48</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2">
         <v>2</v>
@@ -33628,7 +33631,7 @@
         <v>162</v>
       </c>
       <c r="CU100" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV100" s="1">
         <v>13</v>
@@ -34569,16 +34572,16 @@
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I104" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J104" s="1">
         <v>0</v>
@@ -34845,16 +34848,16 @@
         <v>0</v>
       </c>
       <c r="CT104" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CU104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV104" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW104" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:101">
@@ -34949,7 +34952,7 @@
         <v>4469</v>
       </c>
       <c r="AE105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF105" s="2">
         <v>150</v>
@@ -35153,7 +35156,7 @@
         <v>8004</v>
       </c>
       <c r="CU105" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CV105" s="1">
         <v>225</v>
@@ -39757,7 +39760,7 @@
         <v>78</v>
       </c>
       <c r="G121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="2">
         <v>2</v>
@@ -40033,7 +40036,7 @@
         <v>80</v>
       </c>
       <c r="CU121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV121" s="1">
         <v>3</v>
@@ -40367,7 +40370,7 @@
         <v>49</v>
       </c>
       <c r="G123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="2">
         <v>3</v>
@@ -40643,7 +40646,7 @@
         <v>936</v>
       </c>
       <c r="CU123" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV123" s="1">
         <v>13</v>
@@ -44320,7 +44323,7 @@
         <v>148</v>
       </c>
       <c r="C136" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D136" s="2">
         <v>3</v>
@@ -44356,7 +44359,7 @@
         <v>1439</v>
       </c>
       <c r="O136" s="2">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="P136" s="2">
         <v>13</v>
@@ -44608,7 +44611,7 @@
         <v>158874</v>
       </c>
       <c r="CU136" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CV136" s="1">
         <v>5079</v>
@@ -46177,7 +46180,7 @@
         <v>16</v>
       </c>
       <c r="L142" s="2">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M142" s="2">
         <v>54</v>
@@ -46345,7 +46348,7 @@
         <v>0</v>
       </c>
       <c r="BP142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ142" s="2">
         <v>3</v>
@@ -46441,7 +46444,7 @@
         <v>18</v>
       </c>
       <c r="CV142" s="1">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="CW142" s="1">
         <v>103</v>
@@ -49200,7 +49203,7 @@
         <v>188</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -49488,7 +49491,7 @@
         <v>3022</v>
       </c>
       <c r="CU152" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV152" s="1">
         <v>92</v>
@@ -50130,7 +50133,7 @@
         <v>1</v>
       </c>
       <c r="H155" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I155" s="2">
         <v>4</v>
@@ -50406,7 +50409,7 @@
         <v>15</v>
       </c>
       <c r="CV155" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CW155" s="1">
         <v>91</v>
@@ -50417,16 +50420,16 @@
         <v>255</v>
       </c>
       <c r="B156" s="1">
-        <v>2026</v>
+        <v>2046</v>
       </c>
       <c r="C156" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D156" s="2">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E156" s="2">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -50705,16 +50708,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71509</v>
+        <v>71529</v>
       </c>
       <c r="CU156" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="CV156" s="1">
-        <v>1039</v>
+        <v>1059</v>
       </c>
       <c r="CW156" s="1">
-        <v>2519</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -51057,7 +51060,7 @@
         <v>35</v>
       </c>
       <c r="L158" s="2">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="M158" s="2">
         <v>414</v>
@@ -51321,7 +51324,7 @@
         <v>239</v>
       </c>
       <c r="CV158" s="1">
-        <v>916</v>
+        <v>837</v>
       </c>
       <c r="CW158" s="1">
         <v>1714</v>
@@ -54858,7 +54861,7 @@
         <v>362</v>
       </c>
       <c r="BG170" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH170" s="2">
         <v>11</v>
@@ -54978,7 +54981,7 @@
         <v>19624</v>
       </c>
       <c r="CU170" s="1">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="CV170" s="1">
         <v>480</v>
@@ -56523,7 +56526,7 @@
         <v>0</v>
       </c>
       <c r="D176" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" s="2">
         <v>6</v>
@@ -56811,7 +56814,7 @@
         <v>12</v>
       </c>
       <c r="CV176" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="CW176" s="1">
         <v>140</v>
@@ -60802,7 +60805,7 @@
         <v>79</v>
       </c>
       <c r="G190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" s="2">
         <v>3</v>
@@ -61078,7 +61081,7 @@
         <v>80</v>
       </c>
       <c r="CU190" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV190" s="1">
         <v>3</v>
@@ -62351,7 +62354,7 @@
         <v>976</v>
       </c>
       <c r="O195" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P195" s="2">
         <v>12</v>
@@ -62603,7 +62606,7 @@
         <v>71198</v>
       </c>
       <c r="CU195" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CV195" s="1">
         <v>3368</v>
@@ -67805,7 +67808,7 @@
         <v>31</v>
       </c>
       <c r="C213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D213" s="2">
         <v>5</v>
@@ -68093,7 +68096,7 @@
         <v>269</v>
       </c>
       <c r="CU213" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV213" s="1">
         <v>19</v>
@@ -68122,7 +68125,7 @@
         <v>70</v>
       </c>
       <c r="G214" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214" s="2">
         <v>3</v>
@@ -68398,7 +68401,7 @@
         <v>165</v>
       </c>
       <c r="CU214" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV214" s="1">
         <v>3</v>
@@ -68454,10 +68457,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -68474,10 +68477,10 @@
         <v>399</v>
       </c>
       <c r="E3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -68494,10 +68497,10 @@
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -68514,10 +68517,10 @@
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F5" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -68534,10 +68537,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G6" t="s">
         <v>537</v>
@@ -68557,10 +68560,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -68577,10 +68580,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -68597,10 +68600,10 @@
         <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F9" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -68617,10 +68620,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F10" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -68637,10 +68640,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F11" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -68657,10 +68660,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -68677,10 +68680,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F13" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -68697,10 +68700,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F14" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -68714,10 +68717,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F15" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -68734,10 +68737,10 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F16" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -68754,10 +68757,10 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F17" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -68774,10 +68777,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F18" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -68794,10 +68797,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F19" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -68814,10 +68817,10 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F20" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -68834,10 +68837,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F21" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -68854,10 +68857,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F22" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -68874,10 +68877,10 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F23" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -68894,10 +68897,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F24" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -68914,10 +68917,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F25" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -68934,10 +68937,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F26" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -68954,10 +68957,10 @@
         <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F27" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -68974,10 +68977,10 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F28" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -68994,10 +68997,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F29" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G29" t="s">
         <v>533</v>
@@ -69017,10 +69020,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F30" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -69037,10 +69040,10 @@
         <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F31" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -69057,10 +69060,10 @@
         <v>268</v>
       </c>
       <c r="E32" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F32" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -69077,10 +69080,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F33" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -69097,10 +69100,10 @@
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F34" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -69117,10 +69120,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F35" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -69137,10 +69140,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F36" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -69157,10 +69160,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F37" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -69177,10 +69180,10 @@
         <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F38" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -69197,10 +69200,10 @@
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F39" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -69217,13 +69220,13 @@
         <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F40" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G40" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -69240,10 +69243,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F41" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -69260,10 +69263,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F42" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -69277,10 +69280,10 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F43" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -69297,10 +69300,10 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F44" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -69317,10 +69320,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F45" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -69337,10 +69340,10 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F46" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -69357,10 +69360,10 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F47" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -69377,10 +69380,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F48" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -69391,16 +69394,16 @@
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F49" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -69411,16 +69414,16 @@
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D50">
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F50" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -69431,16 +69434,16 @@
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D51">
         <v>37</v>
       </c>
       <c r="E51" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F51" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -69451,16 +69454,16 @@
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F52" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -69471,16 +69474,16 @@
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D53">
         <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F53" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -69491,16 +69494,16 @@
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F54" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -69511,16 +69514,16 @@
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F55" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -69531,16 +69534,16 @@
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D56">
         <v>197</v>
       </c>
       <c r="E56" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F56" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -69551,16 +69554,16 @@
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F57" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -69571,19 +69574,19 @@
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F58" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G58" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -69594,16 +69597,16 @@
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D59">
         <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F59" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -69614,16 +69617,16 @@
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F60" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -69634,16 +69637,16 @@
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D61">
         <v>333</v>
       </c>
       <c r="E61" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F61" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -69654,16 +69657,16 @@
         <v>380</v>
       </c>
       <c r="C62" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F62" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -69674,16 +69677,16 @@
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D63">
         <v>95</v>
       </c>
       <c r="E63" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F63" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -69694,16 +69697,16 @@
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D64">
         <v>134</v>
       </c>
       <c r="E64" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F64" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -69714,16 +69717,16 @@
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D65">
         <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F65" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -69734,16 +69737,16 @@
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D66">
         <v>341</v>
       </c>
       <c r="E66" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F66" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -69754,16 +69757,16 @@
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D67">
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F67" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -69774,16 +69777,16 @@
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D68">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F68" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -69794,16 +69797,16 @@
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D69">
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F69" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -69814,16 +69817,16 @@
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D70">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F70" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -69834,16 +69837,16 @@
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F71" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -69854,16 +69857,16 @@
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D72">
         <v>6</v>
       </c>
       <c r="E72" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F72" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -69874,16 +69877,16 @@
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D73">
         <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F73" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -69894,16 +69897,16 @@
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D74">
         <v>2229</v>
       </c>
       <c r="E74" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F74" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -69914,16 +69917,16 @@
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
       <c r="E75" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F75" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -69934,16 +69937,16 @@
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D76">
         <v>920</v>
       </c>
       <c r="E76" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F76" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -69954,16 +69957,16 @@
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D77">
         <v>175</v>
       </c>
       <c r="E77" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F77" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -69974,16 +69977,16 @@
         <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F78" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -69994,16 +69997,16 @@
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D79">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E79" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F79" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -70014,16 +70017,16 @@
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D80">
         <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F80" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -70034,16 +70037,16 @@
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D81">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E81" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F81" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -70054,16 +70057,16 @@
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F82" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -70080,10 +70083,10 @@
         <v>268</v>
       </c>
       <c r="E83" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F83" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -70094,16 +70097,16 @@
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F84" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -70114,16 +70117,16 @@
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D85">
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F85" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -70134,16 +70137,16 @@
         <v>404</v>
       </c>
       <c r="C86" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D86">
         <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F86" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -70154,16 +70157,16 @@
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F87" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -70174,19 +70177,19 @@
         <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D88">
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F88" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G88" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -70197,19 +70200,19 @@
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D89">
         <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F89" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G89" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -70220,16 +70223,16 @@
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F90" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -70240,16 +70243,16 @@
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D91">
         <v>109</v>
       </c>
       <c r="E91" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F91" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -70260,16 +70263,16 @@
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D92">
         <v>28</v>
       </c>
       <c r="E92" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F92" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -70283,10 +70286,10 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F93" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -70297,16 +70300,16 @@
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F94" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -70317,16 +70320,16 @@
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F95" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -70337,16 +70340,16 @@
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F96" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -70357,16 +70360,16 @@
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D97">
         <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F97" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -70377,16 +70380,16 @@
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F98" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -70397,16 +70400,16 @@
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F99" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -70417,19 +70420,19 @@
         <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F100" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G100" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -70440,16 +70443,16 @@
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F101" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -70460,16 +70463,16 @@
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D102">
         <v>2984</v>
       </c>
       <c r="E102" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F102" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -70480,16 +70483,16 @@
         <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F103" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -70500,16 +70503,16 @@
         <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F104" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -70520,16 +70523,16 @@
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D105">
         <v>131</v>
       </c>
       <c r="E105" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F105" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -70540,16 +70543,16 @@
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D106">
         <v>98</v>
       </c>
       <c r="E106" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F106" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -70560,16 +70563,16 @@
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D107">
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F107" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -70580,16 +70583,16 @@
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D108">
         <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F108" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -70600,16 +70603,16 @@
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F109" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -70620,16 +70623,16 @@
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D110">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F110" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -70640,16 +70643,16 @@
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F111" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -70660,16 +70663,16 @@
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D112">
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F112" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -70686,10 +70689,10 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F113" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -70700,16 +70703,16 @@
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F114" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -70720,16 +70723,16 @@
         <v>433</v>
       </c>
       <c r="C115" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F115" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -70740,16 +70743,16 @@
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D116">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E116" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F116" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -70760,16 +70763,16 @@
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D117">
         <v>65</v>
       </c>
       <c r="E117" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F117" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -70780,16 +70783,16 @@
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F118" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -70800,16 +70803,16 @@
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D119">
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F119" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -70820,16 +70823,16 @@
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D120">
         <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F120" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -70840,16 +70843,16 @@
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F121" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -70860,16 +70863,16 @@
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F122" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -70880,16 +70883,16 @@
         <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F123" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -70900,16 +70903,16 @@
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F124" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -70920,16 +70923,16 @@
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F125" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -70940,16 +70943,16 @@
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F126" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -70960,19 +70963,19 @@
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D127">
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F127" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G127" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -70983,16 +70986,16 @@
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F128" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -71003,16 +71006,16 @@
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D129">
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F129" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -71023,16 +71026,16 @@
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F130" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -71043,16 +71046,16 @@
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F131" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -71063,16 +71066,16 @@
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F132" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -71083,16 +71086,16 @@
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F133" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -71103,16 +71106,16 @@
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D134">
         <v>54</v>
       </c>
       <c r="E134" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F134" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -71123,16 +71126,16 @@
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D135">
         <v>10251</v>
       </c>
       <c r="E135" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F135" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -71143,16 +71146,16 @@
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D136">
         <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F136" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -71163,16 +71166,16 @@
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F137" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -71183,16 +71186,16 @@
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D138">
         <v>374</v>
       </c>
       <c r="E138" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F138" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -71203,16 +71206,16 @@
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D139">
         <v>5</v>
       </c>
       <c r="E139" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F139" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -71223,16 +71226,16 @@
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F140" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -71243,16 +71246,16 @@
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D141">
         <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F141" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -71263,16 +71266,16 @@
         <v>460</v>
       </c>
       <c r="C142" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D142">
         <v>22</v>
       </c>
       <c r="E142" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F142" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -71283,16 +71286,16 @@
         <v>461</v>
       </c>
       <c r="C143" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D143">
         <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F143" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -71303,16 +71306,16 @@
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D144">
         <v>4</v>
       </c>
       <c r="E144" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F144" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -71323,16 +71326,16 @@
         <v>463</v>
       </c>
       <c r="C145" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D145">
         <v>51</v>
       </c>
       <c r="E145" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F145" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -71343,16 +71346,16 @@
         <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F146" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -71363,16 +71366,16 @@
         <v>465</v>
       </c>
       <c r="C147" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F147" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -71383,16 +71386,16 @@
         <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D148">
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F148" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -71406,10 +71409,10 @@
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F149" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -71420,19 +71423,19 @@
         <v>468</v>
       </c>
       <c r="C150" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F150" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G150" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -71443,19 +71446,19 @@
         <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F151" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G151" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -71466,16 +71469,16 @@
         <v>470</v>
       </c>
       <c r="C152" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D152">
         <v>5</v>
       </c>
       <c r="E152" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F152" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -71486,16 +71489,16 @@
         <v>471</v>
       </c>
       <c r="C153" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F153" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -71512,10 +71515,10 @@
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F154" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -71526,16 +71529,16 @@
         <v>473</v>
       </c>
       <c r="C155" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D155">
         <v>19</v>
       </c>
       <c r="E155" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F155" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -71546,16 +71549,16 @@
         <v>474</v>
       </c>
       <c r="C156" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D156">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E156" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F156" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -71566,16 +71569,16 @@
         <v>475</v>
       </c>
       <c r="C157" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D157">
         <v>135</v>
       </c>
       <c r="E157" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F157" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -71586,16 +71589,16 @@
         <v>476</v>
       </c>
       <c r="C158" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D158">
         <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F158" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -71612,10 +71615,10 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F159" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -71626,16 +71629,16 @@
         <v>478</v>
       </c>
       <c r="C160" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F160" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -71646,16 +71649,16 @@
         <v>479</v>
       </c>
       <c r="C161" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D161">
         <v>761</v>
       </c>
       <c r="E161" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F161" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -71666,16 +71669,16 @@
         <v>480</v>
       </c>
       <c r="C162" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F162" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -71686,19 +71689,19 @@
         <v>481</v>
       </c>
       <c r="C163" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D163">
         <v>16</v>
       </c>
       <c r="E163" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F163" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G163" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -71709,16 +71712,16 @@
         <v>482</v>
       </c>
       <c r="C164" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D164">
         <v>3</v>
       </c>
       <c r="E164" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F164" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -71729,16 +71732,16 @@
         <v>483</v>
       </c>
       <c r="C165" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D165">
         <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F165" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -71749,16 +71752,16 @@
         <v>484</v>
       </c>
       <c r="C166" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D166">
         <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F166" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -71769,16 +71772,16 @@
         <v>485</v>
       </c>
       <c r="C167" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F167" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -71789,16 +71792,16 @@
         <v>486</v>
       </c>
       <c r="C168" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D168">
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F168" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -71809,19 +71812,19 @@
         <v>487</v>
       </c>
       <c r="C169" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F169" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G169" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -71832,16 +71835,16 @@
         <v>488</v>
       </c>
       <c r="C170" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D170">
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F170" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -71852,16 +71855,16 @@
         <v>489</v>
       </c>
       <c r="C171" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D171">
         <v>134</v>
       </c>
       <c r="E171" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F171" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -71872,16 +71875,16 @@
         <v>490</v>
       </c>
       <c r="C172" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D172">
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F172" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -71892,16 +71895,16 @@
         <v>491</v>
       </c>
       <c r="C173" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F173" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -71912,16 +71915,16 @@
         <v>492</v>
       </c>
       <c r="C174" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F174" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -71932,16 +71935,16 @@
         <v>493</v>
       </c>
       <c r="C175" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D175">
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F175" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -71952,16 +71955,16 @@
         <v>494</v>
       </c>
       <c r="C176" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D176">
         <v>0</v>
       </c>
       <c r="E176" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F176" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -71972,16 +71975,16 @@
         <v>495</v>
       </c>
       <c r="C177" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F177" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -71992,16 +71995,16 @@
         <v>496</v>
       </c>
       <c r="C178" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D178">
         <v>242</v>
       </c>
       <c r="E178" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F178" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -72012,16 +72015,16 @@
         <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D179">
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F179" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -72032,16 +72035,16 @@
         <v>498</v>
       </c>
       <c r="C180" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D180">
         <v>101</v>
       </c>
       <c r="E180" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F180" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -72052,16 +72055,16 @@
         <v>499</v>
       </c>
       <c r="C181" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F181" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -72072,16 +72075,16 @@
         <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D182">
         <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F182" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -72095,10 +72098,10 @@
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F183" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -72109,16 +72112,16 @@
         <v>502</v>
       </c>
       <c r="C184" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F184" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -72129,16 +72132,16 @@
         <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D185">
         <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F185" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -72149,16 +72152,16 @@
         <v>504</v>
       </c>
       <c r="C186" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F186" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -72169,16 +72172,16 @@
         <v>505</v>
       </c>
       <c r="C187" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F187" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -72189,16 +72192,16 @@
         <v>506</v>
       </c>
       <c r="C188" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F188" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -72209,16 +72212,16 @@
         <v>507</v>
       </c>
       <c r="C189" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F189" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -72229,16 +72232,16 @@
         <v>508</v>
       </c>
       <c r="C190" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F190" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -72249,19 +72252,19 @@
         <v>509</v>
       </c>
       <c r="C191" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D191">
         <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F191" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G191" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -72272,16 +72275,16 @@
         <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D192">
         <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F192" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -72292,16 +72295,16 @@
         <v>511</v>
       </c>
       <c r="C193" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F193" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -72312,16 +72315,16 @@
         <v>512</v>
       </c>
       <c r="C194" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D194">
         <v>116</v>
       </c>
       <c r="E194" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F194" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -72332,16 +72335,16 @@
         <v>513</v>
       </c>
       <c r="C195" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D195">
         <v>10</v>
       </c>
       <c r="E195" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F195" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -72352,16 +72355,16 @@
         <v>514</v>
       </c>
       <c r="C196" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D196">
         <v>10257</v>
       </c>
       <c r="E196" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F196" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -72372,16 +72375,16 @@
         <v>515</v>
       </c>
       <c r="C197" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F197" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -72392,19 +72395,19 @@
         <v>516</v>
       </c>
       <c r="C198" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F198" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G198" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -72415,16 +72418,16 @@
         <v>517</v>
       </c>
       <c r="C199" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F199" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -72435,19 +72438,19 @@
         <v>518</v>
       </c>
       <c r="C200" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D200">
         <v>314</v>
       </c>
       <c r="E200" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F200" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G200" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -72458,16 +72461,16 @@
         <v>519</v>
       </c>
       <c r="C201" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D201">
         <v>49</v>
       </c>
       <c r="E201" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F201" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -72478,16 +72481,16 @@
         <v>520</v>
       </c>
       <c r="C202" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D202">
         <v>7</v>
       </c>
       <c r="E202" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F202" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -72504,10 +72507,10 @@
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F203" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -72524,10 +72527,10 @@
         <v>0</v>
       </c>
       <c r="E204" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F204" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -72538,16 +72541,16 @@
         <v>523</v>
       </c>
       <c r="C205" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D205">
         <v>0</v>
       </c>
       <c r="E205" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F205" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -72558,16 +72561,16 @@
         <v>524</v>
       </c>
       <c r="C206" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D206">
         <v>442</v>
       </c>
       <c r="E206" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F206" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -72578,16 +72581,16 @@
         <v>525</v>
       </c>
       <c r="C207" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D207">
         <v>126</v>
       </c>
       <c r="E207" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F207" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -72598,16 +72601,16 @@
         <v>526</v>
       </c>
       <c r="C208" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F208" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -72618,16 +72621,16 @@
         <v>527</v>
       </c>
       <c r="C209" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D209">
         <v>0</v>
       </c>
       <c r="E209" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F209" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -72638,16 +72641,16 @@
         <v>528</v>
       </c>
       <c r="C210" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D210">
         <v>23</v>
       </c>
       <c r="E210" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F210" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -72658,16 +72661,16 @@
         <v>529</v>
       </c>
       <c r="C211" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D211">
         <v>26</v>
       </c>
       <c r="E211" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F211" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -72678,16 +72681,16 @@
         <v>530</v>
       </c>
       <c r="C212" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D212">
         <v>18</v>
       </c>
       <c r="E212" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F212" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -72698,16 +72701,16 @@
         <v>531</v>
       </c>
       <c r="C213" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D213">
         <v>2</v>
       </c>
       <c r="E213" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F213" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -72718,16 +72721,16 @@
         <v>532</v>
       </c>
       <c r="C214" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D214">
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F214" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4778,16 +4778,16 @@
         <v>0</v>
       </c>
       <c r="AL6" s="1">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AM6" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN6" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AO6" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AP6" s="1">
         <v>1</v>
@@ -4922,16 +4922,16 @@
         <v>0</v>
       </c>
       <c r="CH6" s="1">
-        <v>1566</v>
+        <v>1595</v>
       </c>
       <c r="CI6" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CJ6" s="2">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="CK6" s="2">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="CL6" s="1">
         <v>1</v>
@@ -4958,16 +4958,16 @@
         <v>0</v>
       </c>
       <c r="CT6" s="1">
-        <v>2245</v>
+        <v>2278</v>
       </c>
       <c r="CU6" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="CV6" s="1">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="CW6" s="1">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -6515,7 +6515,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -6743,7 +6743,7 @@
         <v>4</v>
       </c>
       <c r="CE12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF12" s="2">
         <v>1</v>
@@ -6791,7 +6791,7 @@
         <v>431</v>
       </c>
       <c r="CU12" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CV12" s="1">
         <v>202</v>
@@ -7173,7 +7173,7 @@
         <v>5</v>
       </c>
       <c r="W14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="2">
         <v>1</v>
@@ -7401,7 +7401,7 @@
         <v>3163</v>
       </c>
       <c r="CU14" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CV14" s="1">
         <v>108</v>
@@ -8345,7 +8345,7 @@
         <v>75</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2">
         <v>2</v>
@@ -8621,7 +8621,7 @@
         <v>172</v>
       </c>
       <c r="CU18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV18" s="1">
         <v>2</v>
@@ -8979,7 +8979,7 @@
         <v>12653</v>
       </c>
       <c r="O20" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2">
         <v>226</v>
@@ -9231,7 +9231,7 @@
         <v>20729</v>
       </c>
       <c r="CU20" s="1">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="CV20" s="1">
         <v>374</v>
@@ -9870,7 +9870,7 @@
         <v>64</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>3</v>
@@ -10146,7 +10146,7 @@
         <v>733</v>
       </c>
       <c r="CU23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV23" s="1">
         <v>26</v>
@@ -11087,16 +11087,16 @@
         <v>6</v>
       </c>
       <c r="F27" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
@@ -11363,16 +11363,16 @@
         <v>0</v>
       </c>
       <c r="CT27" s="1">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="CU27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV27" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CW27" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -12298,7 +12298,7 @@
         <v>709</v>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
         <v>10</v>
@@ -12307,16 +12307,16 @@
         <v>13</v>
       </c>
       <c r="F31" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="1">
         <v>1393</v>
@@ -12583,16 +12583,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="CU31" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CV31" s="1">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="CW31" s="1">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12840,16 +12840,16 @@
         <v>0</v>
       </c>
       <c r="CD32" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CE32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH32" s="1">
         <v>471</v>
@@ -12888,16 +12888,16 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11144</v>
+        <v>11145</v>
       </c>
       <c r="CU32" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CV32" s="1">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="CW32" s="1">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13282,16 +13282,16 @@
         <v>1</v>
       </c>
       <c r="Z34" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD34" s="1">
         <v>0</v>
@@ -13498,16 +13498,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="CU34" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV34" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CW34" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14433,7 +14433,7 @@
         <v>240</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2">
         <v>6</v>
@@ -14721,7 +14721,7 @@
         <v>1958</v>
       </c>
       <c r="CU38" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV38" s="1">
         <v>43</v>
@@ -14738,7 +14738,7 @@
         <v>113</v>
       </c>
       <c r="C39" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2">
         <v>3</v>
@@ -14843,16 +14843,16 @@
         <v>0</v>
       </c>
       <c r="AL39" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AM39" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN39" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO39" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP39" s="1">
         <v>14</v>
@@ -14990,7 +14990,7 @@
         <v>406</v>
       </c>
       <c r="CI39" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="CJ39" s="2">
         <v>42</v>
@@ -15023,16 +15023,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="CU39" s="1">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="CV39" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="CW39" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -16371,7 +16371,7 @@
         <v>384</v>
       </c>
       <c r="AM44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN44" s="2">
         <v>6</v>
@@ -16515,7 +16515,7 @@
         <v>889</v>
       </c>
       <c r="CI44" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ44" s="2">
         <v>27</v>
@@ -16551,7 +16551,7 @@
         <v>50657</v>
       </c>
       <c r="CU44" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="CV44" s="1">
         <v>1974</v>
@@ -18105,7 +18105,7 @@
         <v>53</v>
       </c>
       <c r="G50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>2</v>
@@ -18210,16 +18210,16 @@
         <v>11</v>
       </c>
       <c r="AP50" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ50" s="2">
         <v>1</v>
       </c>
       <c r="AR50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT50" s="1">
         <v>0</v>
@@ -18342,16 +18342,16 @@
         <v>0</v>
       </c>
       <c r="CH50" s="1">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="CI50" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CJ50" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK50" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="CL50" s="1">
         <v>0</v>
@@ -18378,16 +18378,16 @@
         <v>0</v>
       </c>
       <c r="CT50" s="1">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="CU50" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CV50" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="CW50" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -19421,7 +19421,7 @@
         <v>41</v>
       </c>
       <c r="AM54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN54" s="2">
         <v>4</v>
@@ -19565,7 +19565,7 @@
         <v>130</v>
       </c>
       <c r="CI54" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CJ54" s="2">
         <v>18</v>
@@ -19601,7 +19601,7 @@
         <v>258</v>
       </c>
       <c r="CU54" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CV54" s="1">
         <v>23</v>
@@ -22360,16 +22360,16 @@
         <v>163</v>
       </c>
       <c r="B64" s="1">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1">
         <v>18</v>
@@ -22384,16 +22384,16 @@
         <v>2</v>
       </c>
       <c r="J64" s="1">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K64" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L64" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M64" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N64" s="1">
         <v>4322</v>
@@ -22468,16 +22468,16 @@
         <v>0</v>
       </c>
       <c r="AL64" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM64" s="2">
         <v>1</v>
       </c>
       <c r="AN64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP64" s="1">
         <v>51</v>
@@ -22612,16 +22612,16 @@
         <v>0</v>
       </c>
       <c r="CH64" s="1">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="CI64" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CJ64" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CK64" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CL64" s="1">
         <v>10</v>
@@ -22648,16 +22648,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8018</v>
+        <v>8029</v>
       </c>
       <c r="CU64" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="CV64" s="1">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="CW64" s="1">
-        <v>461</v>
+        <v>472</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22701,16 +22701,16 @@
         <v>111</v>
       </c>
       <c r="N65" s="1">
-        <v>58956</v>
+        <v>58955</v>
       </c>
       <c r="O65" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P65" s="2">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q65" s="2">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -22812,7 +22812,7 @@
         <v>18</v>
       </c>
       <c r="AY65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ65" s="2">
         <v>2</v>
@@ -22953,16 +22953,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67220</v>
+        <v>67219</v>
       </c>
       <c r="CU65" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="CV65" s="1">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="CW65" s="1">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -24815,7 +24815,7 @@
         <v>18</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="2">
         <v>2</v>
@@ -25091,7 +25091,7 @@
         <v>519</v>
       </c>
       <c r="CU72" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV72" s="1">
         <v>47</v>
@@ -25410,16 +25410,16 @@
         <v>173</v>
       </c>
       <c r="B74" s="1">
-        <v>12604</v>
+        <v>12674</v>
       </c>
       <c r="C74" s="2">
-        <v>-1</v>
+        <v>69</v>
       </c>
       <c r="D74" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="E74" s="2">
-        <v>305</v>
+        <v>375</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25521,7 +25521,7 @@
         <v>36284</v>
       </c>
       <c r="AM74" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AN74" s="2">
         <v>112</v>
@@ -25665,7 +25665,7 @@
         <v>16216</v>
       </c>
       <c r="CI74" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="CJ74" s="2">
         <v>194</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171716</v>
+        <v>171786</v>
       </c>
       <c r="CU74" s="1">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="CV74" s="1">
-        <v>1756</v>
+        <v>1826</v>
       </c>
       <c r="CW74" s="1">
-        <v>4385</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25718,7 +25718,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -25730,7 +25730,7 @@
         <v>35</v>
       </c>
       <c r="G75" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="2">
         <v>2</v>
@@ -26006,7 +26006,7 @@
         <v>223</v>
       </c>
       <c r="CU75" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CV75" s="1">
         <v>15</v>
@@ -26325,16 +26325,16 @@
         <v>176</v>
       </c>
       <c r="B77" s="1">
-        <v>10919</v>
+        <v>10827</v>
       </c>
       <c r="C77" s="2">
-        <v>61</v>
+        <v>-31</v>
       </c>
       <c r="D77" s="2">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="E77" s="2">
-        <v>-4334</v>
+        <v>-4426</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26436,7 +26436,7 @@
         <v>1920</v>
       </c>
       <c r="AM77" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AN77" s="2">
         <v>48</v>
@@ -26517,16 +26517,16 @@
         <v>0</v>
       </c>
       <c r="BN77" s="1">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="BO77" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BP77" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BQ77" s="2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="BR77" s="1">
         <v>0</v>
@@ -26580,7 +26580,7 @@
         <v>7356</v>
       </c>
       <c r="CI77" s="2">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="CJ77" s="2">
         <v>333</v>
@@ -26613,16 +26613,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>391048</v>
+        <v>390969</v>
       </c>
       <c r="CU77" s="1">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="CV77" s="1">
-        <v>10304</v>
+        <v>10225</v>
       </c>
       <c r="CW77" s="1">
-        <v>15994</v>
+        <v>15915</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26959,16 +26959,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>4534</v>
+        <v>4583</v>
       </c>
       <c r="K79" s="2">
-        <v>-11</v>
+        <v>38</v>
       </c>
       <c r="L79" s="2">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="M79" s="2">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27223,16 +27223,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90630</v>
+        <v>90679</v>
       </c>
       <c r="CU79" s="1">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="CV79" s="1">
-        <v>584</v>
+        <v>633</v>
       </c>
       <c r="CW79" s="1">
-        <v>1840</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27243,7 +27243,7 @@
         <v>139</v>
       </c>
       <c r="C80" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D80" s="2">
         <v>5</v>
@@ -27255,7 +27255,7 @@
         <v>17</v>
       </c>
       <c r="G80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2">
         <v>1</v>
@@ -27531,7 +27531,7 @@
         <v>1798</v>
       </c>
       <c r="CU80" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CV80" s="1">
         <v>142</v>
@@ -27689,16 +27689,16 @@
         <v>0</v>
       </c>
       <c r="AX81" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB81" s="1">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6422</v>
+        <v>6423</v>
       </c>
       <c r="CU81" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CV81" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="CW81" s="1">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28329,7 +28329,7 @@
         <v>0</v>
       </c>
       <c r="BH83" s="2">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="BI83" s="2">
         <v>59</v>
@@ -28449,7 +28449,7 @@
         <v>183</v>
       </c>
       <c r="CV83" s="1">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="CW83" s="1">
         <v>5498</v>
@@ -28475,7 +28475,7 @@
         <v>37</v>
       </c>
       <c r="G84" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
         <v>3</v>
@@ -28751,7 +28751,7 @@
         <v>37</v>
       </c>
       <c r="CU84" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV84" s="1">
         <v>3</v>
@@ -29181,7 +29181,7 @@
         <v>205</v>
       </c>
       <c r="AM86" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN86" s="2">
         <v>3</v>
@@ -29361,7 +29361,7 @@
         <v>2832</v>
       </c>
       <c r="CU86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV86" s="1">
         <v>28</v>
@@ -29800,16 +29800,16 @@
         <v>0</v>
       </c>
       <c r="AP88" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AQ88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR88" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS88" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29932,16 +29932,16 @@
         <v>0</v>
       </c>
       <c r="CH88" s="1">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="CI88" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ88" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CK88" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29968,16 +29968,16 @@
         <v>0</v>
       </c>
       <c r="CT88" s="1">
-        <v>9590</v>
+        <v>9593</v>
       </c>
       <c r="CU88" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CV88" s="1">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CW88" s="1">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -30595,16 +30595,16 @@
         <v>190</v>
       </c>
       <c r="B91" s="1">
-        <v>7101</v>
+        <v>7166</v>
       </c>
       <c r="C91" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D91" s="2">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="E91" s="2">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -30619,16 +30619,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>5472</v>
+        <v>5471</v>
       </c>
       <c r="K91" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L91" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M91" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30883,16 +30883,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>25955</v>
+        <v>26019</v>
       </c>
       <c r="CU91" s="1">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="CV91" s="1">
-        <v>352</v>
+        <v>416</v>
       </c>
       <c r="CW91" s="1">
-        <v>826</v>
+        <v>890</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -31313,16 +31313,16 @@
         <v>0</v>
       </c>
       <c r="AL93" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN93" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO93" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP93" s="1">
         <v>37</v>
@@ -31493,16 +31493,16 @@
         <v>0</v>
       </c>
       <c r="CT93" s="1">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="CU93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV93" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CW93" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -33352,16 +33352,16 @@
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I100" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -33628,16 +33628,16 @@
         <v>0</v>
       </c>
       <c r="CT100" s="1">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="CU100" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV100" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW100" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -35242,16 +35242,16 @@
         <v>0</v>
       </c>
       <c r="Z106" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AA106" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB106" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC106" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD106" s="1">
         <v>41783</v>
@@ -35458,16 +35458,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92785</v>
+        <v>92789</v>
       </c>
       <c r="CU106" s="1">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="CV106" s="1">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="CW106" s="1">
-        <v>2467</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36035,7 +36035,7 @@
         <v>278</v>
       </c>
       <c r="CI108" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CJ108" s="2">
         <v>12</v>
@@ -36071,7 +36071,7 @@
         <v>944</v>
       </c>
       <c r="CU108" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CV108" s="1">
         <v>26</v>
@@ -36522,16 +36522,16 @@
         <v>0</v>
       </c>
       <c r="AT110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX110" s="1">
         <v>0</v>
@@ -36678,16 +36678,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13437</v>
+        <v>13438</v>
       </c>
       <c r="CU110" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="CV110" s="1">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="CW110" s="1">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37389,16 +37389,16 @@
         <v>7</v>
       </c>
       <c r="AD113" s="1">
-        <v>156896</v>
+        <v>158197</v>
       </c>
       <c r="AE113" s="2">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="AF113" s="2">
-        <v>0</v>
+        <v>1301</v>
       </c>
       <c r="AG113" s="2">
-        <v>8812</v>
+        <v>10113</v>
       </c>
       <c r="AH113" s="1">
         <v>1</v>
@@ -37593,16 +37593,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>173855</v>
+        <v>175156</v>
       </c>
       <c r="CU113" s="1">
-        <v>54</v>
+        <v>1355</v>
       </c>
       <c r="CV113" s="1">
-        <v>446</v>
+        <v>1747</v>
       </c>
       <c r="CW113" s="1">
-        <v>9847</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38355,7 +38355,7 @@
         <v>64</v>
       </c>
       <c r="AU116" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV116" s="2">
         <v>6</v>
@@ -38511,7 +38511,7 @@
         <v>21818</v>
       </c>
       <c r="CU116" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="CV116" s="1">
         <v>390</v>
@@ -38845,7 +38845,7 @@
         <v>40</v>
       </c>
       <c r="G118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="2">
         <v>2</v>
@@ -39121,7 +39121,7 @@
         <v>139</v>
       </c>
       <c r="CU118" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV118" s="1">
         <v>25</v>
@@ -40559,16 +40559,16 @@
         <v>0</v>
       </c>
       <c r="BR123" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BS123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU123" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV123" s="1">
         <v>0</v>
@@ -40643,16 +40643,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="CU123" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV123" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW123" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -41578,7 +41578,7 @@
         <v>1080</v>
       </c>
       <c r="C127" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2">
         <v>30</v>
@@ -41866,7 +41866,7 @@
         <v>2591</v>
       </c>
       <c r="CU127" s="1">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="CV127" s="1">
         <v>59</v>
@@ -42185,22 +42185,22 @@
         <v>228</v>
       </c>
       <c r="B129" s="1">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C129" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F129" s="1">
         <v>44</v>
       </c>
       <c r="G129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="2">
         <v>2</v>
@@ -42473,16 +42473,16 @@
         <v>0</v>
       </c>
       <c r="CT129" s="1">
-        <v>3571</v>
+        <v>3573</v>
       </c>
       <c r="CU129" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV129" s="1">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="CW129" s="1">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -44099,16 +44099,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11789</v>
+        <v>11790</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF135" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG135" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44303,16 +44303,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62761</v>
+        <v>62762</v>
       </c>
       <c r="CU135" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="CW135" s="1">
-        <v>2690</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44954,16 +44954,16 @@
         <v>1</v>
       </c>
       <c r="J138" s="1">
-        <v>1208</v>
+        <v>1226</v>
       </c>
       <c r="K138" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L138" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="M138" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="N138" s="1">
         <v>2200</v>
@@ -45218,16 +45218,16 @@
         <v>0</v>
       </c>
       <c r="CT138" s="1">
-        <v>4407</v>
+        <v>4425</v>
       </c>
       <c r="CU138" s="1">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="CV138" s="1">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="CW138" s="1">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -47980,40 +47980,40 @@
         <v>247</v>
       </c>
       <c r="B148" s="1">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C148" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D148" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E148" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F148" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" s="1">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="K148" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L148" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M148" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="N148" s="1">
         <v>3253</v>
@@ -48100,16 +48100,16 @@
         <v>12</v>
       </c>
       <c r="AP148" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT148" s="1">
         <v>0</v>
@@ -48232,16 +48232,16 @@
         <v>0</v>
       </c>
       <c r="CH148" s="1">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="CI148" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ148" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="CK148" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="CL148" s="1">
         <v>16</v>
@@ -48268,16 +48268,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>5591</v>
+        <v>5611</v>
       </c>
       <c r="CU148" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="CV148" s="1">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="CW148" s="1">
-        <v>232</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -49212,16 +49212,16 @@
         <v>6</v>
       </c>
       <c r="F152" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J152" s="1">
         <v>870</v>
@@ -49320,16 +49320,16 @@
         <v>1</v>
       </c>
       <c r="AP152" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AQ152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR152" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS152" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT152" s="1">
         <v>0</v>
@@ -49452,16 +49452,16 @@
         <v>0</v>
       </c>
       <c r="CH152" s="1">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CI152" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ152" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CK152" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CL152" s="1">
         <v>9</v>
@@ -49488,16 +49488,16 @@
         <v>0</v>
       </c>
       <c r="CT152" s="1">
-        <v>3022</v>
+        <v>3026</v>
       </c>
       <c r="CU152" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="CW152" s="1">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50130,7 +50130,7 @@
         <v>29</v>
       </c>
       <c r="G155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="2">
         <v>2</v>
@@ -50238,7 +50238,7 @@
         <v>35</v>
       </c>
       <c r="AQ155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR155" s="2">
         <v>3</v>
@@ -50370,7 +50370,7 @@
         <v>413</v>
       </c>
       <c r="CI155" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CJ155" s="2">
         <v>10</v>
@@ -50406,7 +50406,7 @@
         <v>2669</v>
       </c>
       <c r="CU155" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CV155" s="1">
         <v>50</v>
@@ -50567,7 +50567,7 @@
         <v>8</v>
       </c>
       <c r="AY156" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ156" s="2">
         <v>4</v>
@@ -50639,7 +50639,7 @@
         <v>1</v>
       </c>
       <c r="BW156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX156" s="2">
         <v>1</v>
@@ -50711,7 +50711,7 @@
         <v>71529</v>
       </c>
       <c r="CU156" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="CV156" s="1">
         <v>1059</v>
@@ -50833,16 +50833,16 @@
         <v>0</v>
       </c>
       <c r="AL157" s="1">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="AM157" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN157" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AO157" s="2">
-        <v>-34</v>
+        <v>-28</v>
       </c>
       <c r="AP157" s="1">
         <v>49</v>
@@ -50977,16 +50977,16 @@
         <v>0</v>
       </c>
       <c r="CH157" s="1">
-        <v>4861</v>
+        <v>4874</v>
       </c>
       <c r="CI157" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CJ157" s="2">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="CK157" s="2">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="CL157" s="1">
         <v>9</v>
@@ -51013,16 +51013,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166412</v>
+        <v>166431</v>
       </c>
       <c r="CU157" s="1">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="CV157" s="1">
-        <v>5229</v>
+        <v>5248</v>
       </c>
       <c r="CW157" s="1">
-        <v>9177</v>
+        <v>9196</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -52555,28 +52555,28 @@
         <v>262</v>
       </c>
       <c r="B163" s="1">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E163" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F163" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="1">
         <v>110</v>
@@ -52843,16 +52843,16 @@
         <v>0</v>
       </c>
       <c r="CT163" s="1">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="CU163" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV163" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CW163" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -53180,7 +53180,7 @@
         <v>58</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="2">
         <v>3</v>
@@ -53456,7 +53456,7 @@
         <v>79</v>
       </c>
       <c r="CU165" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV165" s="1">
         <v>3</v>
@@ -53485,7 +53485,7 @@
         <v>8</v>
       </c>
       <c r="G166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2">
         <v>1</v>
@@ -53761,7 +53761,7 @@
         <v>5269</v>
       </c>
       <c r="CU166" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV166" s="1">
         <v>115</v>
@@ -54095,7 +54095,7 @@
         <v>16</v>
       </c>
       <c r="G168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="2">
         <v>1</v>
@@ -54371,7 +54371,7 @@
         <v>5973</v>
       </c>
       <c r="CU168" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CV168" s="1">
         <v>159</v>
@@ -54717,7 +54717,7 @@
         <v>6413</v>
       </c>
       <c r="K170" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L170" s="2">
         <v>145</v>
@@ -54774,16 +54774,16 @@
         <v>7</v>
       </c>
       <c r="AD170" s="1">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="AE170" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF170" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG170" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54978,16 +54978,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19624</v>
+        <v>19625</v>
       </c>
       <c r="CU170" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="CV170" s="1">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="CW170" s="1">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -57166,16 +57166,16 @@
         <v>81</v>
       </c>
       <c r="N178" s="1">
-        <v>73112</v>
+        <v>73111</v>
       </c>
       <c r="O178" s="2">
-        <v>-363</v>
+        <v>-364</v>
       </c>
       <c r="P178" s="2">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="Q178" s="2">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="R178" s="1">
         <v>0</v>
@@ -57418,16 +57418,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>84919</v>
+        <v>84918</v>
       </c>
       <c r="CU178" s="1">
-        <v>-308</v>
+        <v>-309</v>
       </c>
       <c r="CV178" s="1">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="CW178" s="1">
-        <v>4594</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57435,22 +57435,22 @@
         <v>278</v>
       </c>
       <c r="B179" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C179" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E179" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F179" s="1">
         <v>27</v>
       </c>
       <c r="G179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="2">
         <v>3</v>
@@ -57723,16 +57723,16 @@
         <v>0</v>
       </c>
       <c r="CT179" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="CU179" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV179" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CW179" s="1">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -58057,292 +58057,292 @@
         <v>0</v>
       </c>
       <c r="F181" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G181" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="2">
+        <v>3</v>
+      </c>
+      <c r="I181" s="2">
+        <v>6</v>
+      </c>
+      <c r="J181" s="1">
+        <v>0</v>
+      </c>
+      <c r="K181" s="2">
+        <v>0</v>
+      </c>
+      <c r="L181" s="2">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2">
+        <v>0</v>
+      </c>
+      <c r="N181" s="1">
+        <v>0</v>
+      </c>
+      <c r="O181" s="2">
+        <v>0</v>
+      </c>
+      <c r="P181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="2">
+        <v>0</v>
+      </c>
+      <c r="R181" s="1">
+        <v>0</v>
+      </c>
+      <c r="S181" s="2">
+        <v>0</v>
+      </c>
+      <c r="T181" s="2">
+        <v>0</v>
+      </c>
+      <c r="U181" s="2">
+        <v>0</v>
+      </c>
+      <c r="V181" s="1">
+        <v>0</v>
+      </c>
+      <c r="W181" s="2">
+        <v>0</v>
+      </c>
+      <c r="X181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX181" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY181" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV181" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY181" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP181" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS181" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT181" s="1">
+        <v>80</v>
+      </c>
+      <c r="CU181" s="1">
         <v>2</v>
       </c>
-      <c r="I181" s="2">
-        <v>5</v>
-      </c>
-      <c r="J181" s="1">
-        <v>0</v>
-      </c>
-      <c r="K181" s="2">
-        <v>0</v>
-      </c>
-      <c r="L181" s="2">
-        <v>0</v>
-      </c>
-      <c r="M181" s="2">
-        <v>0</v>
-      </c>
-      <c r="N181" s="1">
-        <v>0</v>
-      </c>
-      <c r="O181" s="2">
-        <v>0</v>
-      </c>
-      <c r="P181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q181" s="2">
-        <v>0</v>
-      </c>
-      <c r="R181" s="1">
-        <v>0</v>
-      </c>
-      <c r="S181" s="2">
-        <v>0</v>
-      </c>
-      <c r="T181" s="2">
-        <v>0</v>
-      </c>
-      <c r="U181" s="2">
-        <v>0</v>
-      </c>
-      <c r="V181" s="1">
-        <v>0</v>
-      </c>
-      <c r="W181" s="2">
-        <v>0</v>
-      </c>
-      <c r="X181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y181" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX181" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY181" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV181" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY181" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP181" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS181" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT181" s="1">
-        <v>79</v>
-      </c>
-      <c r="CU181" s="1">
-        <v>1</v>
-      </c>
       <c r="CV181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW181" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -58602,16 +58602,16 @@
         <v>1</v>
       </c>
       <c r="CH182" s="1">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="CI182" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ182" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="CK182" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="CL182" s="1">
         <v>0</v>
@@ -58638,16 +58638,16 @@
         <v>0</v>
       </c>
       <c r="CT182" s="1">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="CU182" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV182" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="CW182" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="183" spans="1:101">
@@ -60195,7 +60195,7 @@
         <v>73</v>
       </c>
       <c r="G188" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="2">
         <v>2</v>
@@ -60471,7 +60471,7 @@
         <v>161</v>
       </c>
       <c r="CU188" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV188" s="1">
         <v>27</v>
@@ -62202,28 +62202,28 @@
         <v>0</v>
       </c>
       <c r="BN194" s="1">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="BO194" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BP194" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BQ194" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BR194" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BS194" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BT194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV194" s="1">
         <v>8</v>
@@ -62298,16 +62298,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32879</v>
+        <v>32887</v>
       </c>
       <c r="CU194" s="1">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="CV194" s="1">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="CW194" s="1">
-        <v>1386</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62315,16 +62315,16 @@
         <v>294</v>
       </c>
       <c r="B195" s="1">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C195" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D195" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E195" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F195" s="1">
         <v>19</v>
@@ -62603,16 +62603,16 @@
         <v>0</v>
       </c>
       <c r="CT195" s="1">
-        <v>71198</v>
+        <v>71201</v>
       </c>
       <c r="CU195" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CV195" s="1">
-        <v>3368</v>
+        <v>3371</v>
       </c>
       <c r="CW195" s="1">
-        <v>5335</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -62824,16 +62824,16 @@
         <v>0</v>
       </c>
       <c r="BR196" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BS196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT196" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU196" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV196" s="1">
         <v>0</v>
@@ -62908,16 +62908,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5483</v>
+        <v>5484</v>
       </c>
       <c r="CU196" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV196" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CW196" s="1">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -65874,16 +65874,16 @@
         <v>0</v>
       </c>
       <c r="BR206" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT206" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU206" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV206" s="1">
         <v>3</v>
@@ -65958,16 +65958,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="CU206" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV206" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CW206" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66280,16 +66280,16 @@
         <v>307</v>
       </c>
       <c r="B208" s="1">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C208" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D208" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E208" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F208" s="1">
         <v>18</v>
@@ -66568,16 +66568,16 @@
         <v>0</v>
       </c>
       <c r="CT208" s="1">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="CU208" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV208" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CW208" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:101">
@@ -66902,16 +66902,16 @@
         <v>0</v>
       </c>
       <c r="F210" s="1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G210" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H210" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I210" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J210" s="1">
         <v>2</v>
@@ -67013,7 +67013,7 @@
         <v>52</v>
       </c>
       <c r="AQ210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR210" s="2">
         <v>2</v>
@@ -67145,7 +67145,7 @@
         <v>391</v>
       </c>
       <c r="CI210" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ210" s="2">
         <v>6</v>
@@ -67178,16 +67178,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="CU210" s="1">
         <v>3</v>
       </c>
       <c r="CV210" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="CW210" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67195,16 +67195,16 @@
         <v>310</v>
       </c>
       <c r="B211" s="1">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C211" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D211" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E211" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F211" s="1">
         <v>15</v>
@@ -67315,16 +67315,16 @@
         <v>0</v>
       </c>
       <c r="AP211" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AQ211" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR211" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS211" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT211" s="1">
         <v>9</v>
@@ -67447,16 +67447,16 @@
         <v>0</v>
       </c>
       <c r="CH211" s="1">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="CI211" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CJ211" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="CK211" s="2">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="CL211" s="1">
         <v>15</v>
@@ -67483,16 +67483,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>6289</v>
+        <v>6305</v>
       </c>
       <c r="CU211" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="CV211" s="1">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="CW211" s="1">
-        <v>686</v>
+        <v>702</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69900,7 +69900,7 @@
         <v>594</v>
       </c>
       <c r="D74">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="E74" t="s">
         <v>716</v>
@@ -70000,7 +70000,7 @@
         <v>599</v>
       </c>
       <c r="D79">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5615,7 +5615,7 @@
         <v>3</v>
       </c>
       <c r="L9" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="CV9" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CW9" s="1">
         <v>99</v>
@@ -12304,7 +12304,7 @@
         <v>10</v>
       </c>
       <c r="E31" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1">
         <v>22</v>
@@ -12592,7 +12592,7 @@
         <v>267</v>
       </c>
       <c r="CW31" s="1">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -13240,7 +13240,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M34" s="2">
         <v>41</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -13504,7 +13504,7 @@
         <v>6</v>
       </c>
       <c r="CV34" s="1">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="CW34" s="1">
         <v>132</v>
@@ -16461,7 +16461,7 @@
         <v>0</v>
       </c>
       <c r="BQ44" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR44" s="1">
         <v>14</v>
@@ -16557,7 +16557,7 @@
         <v>1974</v>
       </c>
       <c r="CW44" s="1">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -19026,7 +19026,7 @@
         <v>2</v>
       </c>
       <c r="I53" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -19302,7 +19302,7 @@
         <v>40</v>
       </c>
       <c r="CW53" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:101">
@@ -22453,7 +22453,7 @@
         <v>66</v>
       </c>
       <c r="AG64" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>177</v>
       </c>
       <c r="CW64" s="1">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22866,7 +22866,7 @@
         <v>0</v>
       </c>
       <c r="BQ65" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR65" s="1">
         <v>5</v>
@@ -22962,7 +22962,7 @@
         <v>1771</v>
       </c>
       <c r="CW65" s="1">
-        <v>3545</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23284,7 +23284,7 @@
         <v>44</v>
       </c>
       <c r="E67" s="2">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -23572,7 +23572,7 @@
         <v>44</v>
       </c>
       <c r="CW67" s="1">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:101">
@@ -25527,7 +25527,7 @@
         <v>112</v>
       </c>
       <c r="AO74" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="CK74" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25704,10 +25704,10 @@
         <v>171</v>
       </c>
       <c r="CV74" s="1">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="CW74" s="1">
-        <v>4455</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -30015,7 +30015,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M89" s="2">
         <v>42</v>
@@ -30279,7 +30279,7 @@
         <v>9</v>
       </c>
       <c r="CV89" s="1">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="CW89" s="1">
         <v>207</v>
@@ -31531,7 +31531,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J94" s="1">
         <v>0</v>
@@ -31807,7 +31807,7 @@
         <v>3</v>
       </c>
       <c r="CW94" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:101">
@@ -33056,7 +33056,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J99" s="1">
         <v>0</v>
@@ -33332,7 +33332,7 @@
         <v>3</v>
       </c>
       <c r="CW99" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:101">
@@ -36420,7 +36420,7 @@
         <v>81</v>
       </c>
       <c r="L110" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M110" s="2">
         <v>446</v>
@@ -36684,7 +36684,7 @@
         <v>108</v>
       </c>
       <c r="CV110" s="1">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="CW110" s="1">
         <v>1056</v>
@@ -38352,16 +38352,16 @@
         <v>2</v>
       </c>
       <c r="AT116" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AU116" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV116" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW116" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX116" s="1">
         <v>4</v>
@@ -38508,16 +38508,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21818</v>
+        <v>21819</v>
       </c>
       <c r="CU116" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CV116" s="1">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="CW116" s="1">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -39177,7 +39177,7 @@
         <v>0</v>
       </c>
       <c r="P119" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q119" s="2">
         <v>5</v>
@@ -39429,7 +39429,7 @@
         <v>3</v>
       </c>
       <c r="CV119" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW119" s="1">
         <v>27</v>
@@ -39766,7 +39766,7 @@
         <v>2</v>
       </c>
       <c r="I121" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J121" s="1">
         <v>0</v>
@@ -40042,7 +40042,7 @@
         <v>3</v>
       </c>
       <c r="CW121" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:101">
@@ -40373,7 +40373,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I123" s="2">
         <v>5</v>
@@ -40649,7 +40649,7 @@
         <v>3</v>
       </c>
       <c r="CV123" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW123" s="1">
         <v>29</v>
@@ -40681,7 +40681,7 @@
         <v>2</v>
       </c>
       <c r="I124" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" s="1">
         <v>0</v>
@@ -40957,7 +40957,7 @@
         <v>2</v>
       </c>
       <c r="CW124" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:101">
@@ -41581,7 +41581,7 @@
         <v>2</v>
       </c>
       <c r="D127" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E127" s="2">
         <v>44</v>
@@ -41869,7 +41869,7 @@
         <v>8</v>
       </c>
       <c r="CV127" s="1">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="CW127" s="1">
         <v>105</v>
@@ -42009,7 +42009,7 @@
         <v>1</v>
       </c>
       <c r="AS128" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT128" s="1">
         <v>0</v>
@@ -42141,7 +42141,7 @@
         <v>1</v>
       </c>
       <c r="CK128" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CL128" s="1">
         <v>59</v>
@@ -42177,7 +42177,7 @@
         <v>7</v>
       </c>
       <c r="CW128" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:101">
@@ -43716,7 +43716,7 @@
         <v>8</v>
       </c>
       <c r="D134" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E134" s="2">
         <v>27</v>
@@ -44004,7 +44004,7 @@
         <v>15</v>
       </c>
       <c r="CV134" s="1">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="CW134" s="1">
         <v>5805</v>
@@ -44341,7 +44341,7 @@
         <v>1</v>
       </c>
       <c r="I136" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J136" s="1">
         <v>164</v>
@@ -44617,7 +44617,7 @@
         <v>5079</v>
       </c>
       <c r="CW136" s="1">
-        <v>6083</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -51240,7 +51240,7 @@
         <v>0</v>
       </c>
       <c r="BT158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU158" s="2">
         <v>2</v>
@@ -51324,7 +51324,7 @@
         <v>239</v>
       </c>
       <c r="CV158" s="1">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="CW158" s="1">
         <v>1714</v>
@@ -51990,7 +51990,7 @@
         <v>254</v>
       </c>
       <c r="Q161" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="R161" s="1">
         <v>0</v>
@@ -52242,7 +52242,7 @@
         <v>724</v>
       </c>
       <c r="CW161" s="1">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -57331,7 +57331,7 @@
         <v>0</v>
       </c>
       <c r="BQ178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR178" s="1">
         <v>7</v>
@@ -57427,7 +57427,7 @@
         <v>2197</v>
       </c>
       <c r="CW178" s="1">
-        <v>4593</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -60811,7 +60811,7 @@
         <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J190" s="1">
         <v>0</v>
@@ -61087,7 +61087,7 @@
         <v>3</v>
       </c>
       <c r="CW190" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:101">
@@ -62184,7 +62184,7 @@
         <v>0</v>
       </c>
       <c r="BH194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI194" s="2">
         <v>2</v>
@@ -62304,7 +62304,7 @@
         <v>41</v>
       </c>
       <c r="CV194" s="1">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="CW194" s="1">
         <v>1394</v>
@@ -62345,7 +62345,7 @@
         <v>4</v>
       </c>
       <c r="L195" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M195" s="2">
         <v>13</v>
@@ -62609,7 +62609,7 @@
         <v>16</v>
       </c>
       <c r="CV195" s="1">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="CW195" s="1">
         <v>5338</v>
@@ -62830,7 +62830,7 @@
         <v>1</v>
       </c>
       <c r="BT196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU196" s="2">
         <v>2</v>
@@ -62914,7 +62914,7 @@
         <v>3</v>
       </c>
       <c r="CV196" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="CW196" s="1">
         <v>211</v>
@@ -64456,7 +64456,7 @@
         <v>0</v>
       </c>
       <c r="D202" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202" s="2">
         <v>0</v>
@@ -64744,7 +64744,7 @@
         <v>5</v>
       </c>
       <c r="CV202" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CW202" s="1">
         <v>139</v>
@@ -65676,10 +65676,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E206" s="2">
-        <v>-21</v>
+        <v>19</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65799,7 +65799,7 @@
         <v>2</v>
       </c>
       <c r="AS206" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT206" s="1">
         <v>0</v>
@@ -65931,7 +65931,7 @@
         <v>9</v>
       </c>
       <c r="CK206" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CL206" s="1">
         <v>35</v>
@@ -65964,10 +65964,10 @@
         <v>6</v>
       </c>
       <c r="CV206" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW206" s="1">
-        <v>27</v>
+        <v>65</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66020,7 +66020,7 @@
         <v>48</v>
       </c>
       <c r="Q207" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R207" s="1">
         <v>0</v>
@@ -66272,7 +66272,7 @@
         <v>350</v>
       </c>
       <c r="CW207" s="1">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66932,7 +66932,7 @@
         <v>0</v>
       </c>
       <c r="P210" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q210" s="2">
         <v>7</v>
@@ -67019,7 +67019,7 @@
         <v>2</v>
       </c>
       <c r="AS210" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT210" s="1">
         <v>0</v>
@@ -67151,7 +67151,7 @@
         <v>6</v>
       </c>
       <c r="CK210" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CL210" s="1">
         <v>23</v>
@@ -67184,10 +67184,10 @@
         <v>3</v>
       </c>
       <c r="CV210" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW210" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="211" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5594,7 +5594,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1">
         <v>36</v>
@@ -5882,7 +5882,7 @@
         <v>52</v>
       </c>
       <c r="CW9" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7155,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="R14" s="1">
         <v>2</v>
@@ -7167,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="U14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="1">
         <v>5</v>
@@ -7407,7 +7407,7 @@
         <v>108</v>
       </c>
       <c r="CW14" s="1">
-        <v>270</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8985,7 +8985,7 @@
         <v>226</v>
       </c>
       <c r="Q20" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>374</v>
       </c>
       <c r="CW20" s="1">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -15241,7 +15241,7 @@
         <v>2</v>
       </c>
       <c r="BQ40" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR40" s="1">
         <v>7</v>
@@ -15337,7 +15337,7 @@
         <v>813</v>
       </c>
       <c r="CW40" s="1">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -17489,7 +17489,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1">
         <v>44</v>
@@ -17501,7 +17501,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
@@ -17777,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="CW48" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:101">
@@ -17806,7 +17806,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>1</v>
       </c>
       <c r="CW49" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:101">
@@ -24199,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="1">
         <v>15</v>
@@ -24487,7 +24487,7 @@
         <v>50</v>
       </c>
       <c r="CW70" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25527,7 +25527,7 @@
         <v>112</v>
       </c>
       <c r="AO74" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,7 +25671,7 @@
         <v>192</v>
       </c>
       <c r="CK74" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>1824</v>
       </c>
       <c r="CW74" s="1">
-        <v>4451</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -28248,7 +28248,7 @@
         <v>176</v>
       </c>
       <c r="AG83" s="2">
-        <v>3521</v>
+        <v>3518</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>3</v>
       </c>
       <c r="AW83" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX83" s="1">
         <v>17</v>
@@ -28452,7 +28452,7 @@
         <v>945</v>
       </c>
       <c r="CW83" s="1">
-        <v>5498</v>
+        <v>5494</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -30030,7 +30030,7 @@
         <v>5</v>
       </c>
       <c r="Q89" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R89" s="1">
         <v>0</v>
@@ -30282,7 +30282,7 @@
         <v>80</v>
       </c>
       <c r="CW89" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -38851,7 +38851,7 @@
         <v>2</v>
       </c>
       <c r="I118" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -39127,7 +39127,7 @@
         <v>25</v>
       </c>
       <c r="CW118" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -44754,7 +44754,7 @@
         <v>3</v>
       </c>
       <c r="AS137" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT137" s="1">
         <v>0</v>
@@ -44898,7 +44898,7 @@
         <v>2</v>
       </c>
       <c r="CO137" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP137" s="1">
         <v>0</v>
@@ -44922,7 +44922,7 @@
         <v>22</v>
       </c>
       <c r="CW137" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -47379,7 +47379,7 @@
         <v>0</v>
       </c>
       <c r="E146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" s="1">
         <v>60</v>
@@ -47391,7 +47391,7 @@
         <v>4</v>
       </c>
       <c r="I146" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J146" s="1">
         <v>0</v>
@@ -47667,7 +47667,7 @@
         <v>4</v>
       </c>
       <c r="CW146" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147" spans="1:101">
@@ -51356,7 +51356,7 @@
         <v>4</v>
       </c>
       <c r="I159" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J159" s="1">
         <v>0</v>
@@ -51632,7 +51632,7 @@
         <v>4</v>
       </c>
       <c r="CW159" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:101">
@@ -52098,7 +52098,7 @@
         <v>0</v>
       </c>
       <c r="BA161" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB161" s="1">
         <v>3</v>
@@ -52242,7 +52242,7 @@
         <v>724</v>
       </c>
       <c r="CW161" s="1">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -54293,7 +54293,7 @@
         <v>1</v>
       </c>
       <c r="BU168" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV168" s="1">
         <v>2</v>
@@ -54377,7 +54377,7 @@
         <v>159</v>
       </c>
       <c r="CW168" s="1">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54735,7 +54735,7 @@
         <v>49</v>
       </c>
       <c r="Q170" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R170" s="1">
         <v>0</v>
@@ -54987,7 +54987,7 @@
         <v>481</v>
       </c>
       <c r="CW170" s="1">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -72664,7 +72664,7 @@
         <v>712</v>
       </c>
       <c r="D211">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E211" t="s">
         <v>744</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2">
         <v>17</v>
@@ -6794,7 +6794,7 @@
         <v>21</v>
       </c>
       <c r="CV12" s="1">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="CW12" s="1">
         <v>206</v>
@@ -7155,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R14" s="1">
         <v>2</v>
@@ -7407,7 +7407,7 @@
         <v>108</v>
       </c>
       <c r="CW14" s="1">
-        <v>247</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8351,7 +8351,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v>2</v>
       </c>
       <c r="CW18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -8967,7 +8967,7 @@
         <v>903</v>
       </c>
       <c r="K20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2">
         <v>5</v>
@@ -9231,7 +9231,7 @@
         <v>20729</v>
       </c>
       <c r="CU20" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CV20" s="1">
         <v>374</v>
@@ -12301,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
@@ -12589,7 +12589,7 @@
         <v>18</v>
       </c>
       <c r="CV31" s="1">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="CW31" s="1">
         <v>425</v>
@@ -14753,7 +14753,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2">
         <v>2</v>
@@ -15029,7 +15029,7 @@
         <v>3</v>
       </c>
       <c r="CV39" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CW39" s="1">
         <v>102</v>
@@ -19929,7 +19929,7 @@
         <v>17</v>
       </c>
       <c r="E56" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>14</v>
       </c>
       <c r="M56" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N56" s="1">
         <v>2310</v>
@@ -20217,7 +20217,7 @@
         <v>100</v>
       </c>
       <c r="CW56" s="1">
-        <v>373</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -20243,7 +20243,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" s="2">
         <v>5</v>
@@ -20519,7 +20519,7 @@
         <v>1</v>
       </c>
       <c r="CV57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW57" s="1">
         <v>5</v>
@@ -20545,7 +20545,7 @@
         <v>40</v>
       </c>
       <c r="G58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2">
         <v>3</v>
@@ -20653,7 +20653,7 @@
         <v>22</v>
       </c>
       <c r="AQ58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR58" s="2">
         <v>2</v>
@@ -20797,7 +20797,7 @@
         <v>19</v>
       </c>
       <c r="CM58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN58" s="2">
         <v>2</v>
@@ -20821,7 +20821,7 @@
         <v>181</v>
       </c>
       <c r="CU58" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CV58" s="1">
         <v>18</v>
@@ -22447,13 +22447,13 @@
         <v>1999</v>
       </c>
       <c r="AE64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF64" s="2">
         <v>66</v>
       </c>
       <c r="AG64" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22651,13 +22651,13 @@
         <v>8029</v>
       </c>
       <c r="CU64" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="CV64" s="1">
         <v>177</v>
       </c>
       <c r="CW64" s="1">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -24205,7 +24205,7 @@
         <v>15</v>
       </c>
       <c r="G70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2">
         <v>3</v>
@@ -24481,7 +24481,7 @@
         <v>2267</v>
       </c>
       <c r="CU70" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV70" s="1">
         <v>50</v>
@@ -25123,7 +25123,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="2">
         <v>2</v>
@@ -25399,7 +25399,7 @@
         <v>11</v>
       </c>
       <c r="CV73" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CW73" s="1">
         <v>96</v>
@@ -25524,7 +25524,7 @@
         <v>13</v>
       </c>
       <c r="AN74" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="AO74" s="2">
         <v>367</v>
@@ -25668,7 +25668,7 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="CK74" s="2">
         <v>422</v>
@@ -25704,7 +25704,7 @@
         <v>171</v>
       </c>
       <c r="CV74" s="1">
-        <v>1824</v>
+        <v>1817</v>
       </c>
       <c r="CW74" s="1">
         <v>4423</v>
@@ -26442,7 +26442,7 @@
         <v>48</v>
       </c>
       <c r="AO77" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26622,7 +26622,7 @@
         <v>10225</v>
       </c>
       <c r="CW77" s="1">
-        <v>15915</v>
+        <v>15913</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26651,7 +26651,7 @@
         <v>3</v>
       </c>
       <c r="I78" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -26927,7 +26927,7 @@
         <v>28</v>
       </c>
       <c r="CW78" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -28200,7 +28200,7 @@
         <v>269</v>
       </c>
       <c r="Q83" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="R83" s="1">
         <v>0</v>
@@ -28452,7 +28452,7 @@
         <v>945</v>
       </c>
       <c r="CW83" s="1">
-        <v>5494</v>
+        <v>5495</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29854,7 +29854,7 @@
         <v>0</v>
       </c>
       <c r="BH88" s="2">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="BI88" s="2">
         <v>-7</v>
@@ -29974,7 +29974,7 @@
         <v>10</v>
       </c>
       <c r="CV88" s="1">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="CW88" s="1">
         <v>428</v>
@@ -31528,7 +31528,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
         <v>2</v>
@@ -31804,7 +31804,7 @@
         <v>0</v>
       </c>
       <c r="CV94" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW94" s="1">
         <v>5</v>
@@ -32551,7 +32551,7 @@
         <v>0</v>
       </c>
       <c r="AR97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS97" s="2">
         <v>5</v>
@@ -32683,7 +32683,7 @@
         <v>1</v>
       </c>
       <c r="CJ97" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CK97" s="2">
         <v>6</v>
@@ -32719,7 +32719,7 @@
         <v>1</v>
       </c>
       <c r="CV97" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CW97" s="1">
         <v>16</v>
@@ -33047,16 +33047,16 @@
         <v>0</v>
       </c>
       <c r="F99" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="2">
         <v>3</v>
       </c>
       <c r="I99" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J99" s="1">
         <v>0</v>
@@ -33323,16 +33323,16 @@
         <v>0</v>
       </c>
       <c r="CT99" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CU99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV99" s="1">
         <v>3</v>
       </c>
       <c r="CW99" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:101">
@@ -34091,7 +34091,7 @@
         <v>3</v>
       </c>
       <c r="AW102" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX102" s="1">
         <v>17</v>
@@ -34103,7 +34103,7 @@
         <v>0</v>
       </c>
       <c r="BA102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB102" s="1">
         <v>5</v>
@@ -34247,7 +34247,7 @@
         <v>747</v>
       </c>
       <c r="CW102" s="1">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -36124,7 +36124,7 @@
         <v>311</v>
       </c>
       <c r="O109" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P109" s="2">
         <v>8</v>
@@ -36196,7 +36196,7 @@
         <v>96</v>
       </c>
       <c r="AM109" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN109" s="2">
         <v>3</v>
@@ -36340,7 +36340,7 @@
         <v>347</v>
       </c>
       <c r="CI109" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CJ109" s="2">
         <v>14</v>
@@ -36376,7 +36376,7 @@
         <v>757</v>
       </c>
       <c r="CU109" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CV109" s="1">
         <v>25</v>
@@ -36713,7 +36713,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I111" s="2">
         <v>5</v>
@@ -36989,7 +36989,7 @@
         <v>4</v>
       </c>
       <c r="CV111" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CW111" s="1">
         <v>76</v>
@@ -37560,7 +37560,7 @@
         <v>1488</v>
       </c>
       <c r="CI113" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="CJ113" s="2">
         <v>60</v>
@@ -37596,7 +37596,7 @@
         <v>175156</v>
       </c>
       <c r="CU113" s="1">
-        <v>1355</v>
+        <v>1343</v>
       </c>
       <c r="CV113" s="1">
         <v>1747</v>
@@ -38639,7 +38639,7 @@
         <v>0</v>
       </c>
       <c r="AN117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO117" s="2">
         <v>1</v>
@@ -38795,7 +38795,7 @@
         <v>0</v>
       </c>
       <c r="CN117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO117" s="2">
         <v>1</v>
@@ -38819,7 +38819,7 @@
         <v>213</v>
       </c>
       <c r="CV117" s="1">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="CW117" s="1">
         <v>1297</v>
@@ -39757,16 +39757,16 @@
         <v>1</v>
       </c>
       <c r="F121" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="2">
         <v>2</v>
       </c>
       <c r="I121" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J121" s="1">
         <v>0</v>
@@ -40033,16 +40033,16 @@
         <v>0</v>
       </c>
       <c r="CT121" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CU121" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV121" s="1">
         <v>3</v>
       </c>
       <c r="CW121" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:101">
@@ -40678,7 +40678,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I124" s="2">
         <v>4</v>
@@ -40954,7 +40954,7 @@
         <v>0</v>
       </c>
       <c r="CV124" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CW124" s="1">
         <v>4</v>
@@ -41384,7 +41384,7 @@
         <v>0</v>
       </c>
       <c r="AN126" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO126" s="2">
         <v>6</v>
@@ -41564,7 +41564,7 @@
         <v>1</v>
       </c>
       <c r="CV126" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW126" s="1">
         <v>17</v>
@@ -41581,7 +41581,7 @@
         <v>2</v>
       </c>
       <c r="D127" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E127" s="2">
         <v>44</v>
@@ -41869,7 +41869,7 @@
         <v>8</v>
       </c>
       <c r="CV127" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="CW127" s="1">
         <v>105</v>
@@ -42535,7 +42535,7 @@
         <v>85</v>
       </c>
       <c r="Q130" s="2">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="R130" s="1">
         <v>0</v>
@@ -42787,7 +42787,7 @@
         <v>135</v>
       </c>
       <c r="CW130" s="1">
-        <v>234</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -46351,7 +46351,7 @@
         <v>0</v>
       </c>
       <c r="BQ142" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR142" s="1">
         <v>27</v>
@@ -46447,7 +46447,7 @@
         <v>43</v>
       </c>
       <c r="CW142" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47212,7 +47212,7 @@
         <v>41</v>
       </c>
       <c r="AY145" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ145" s="2">
         <v>4</v>
@@ -47356,7 +47356,7 @@
         <v>2483</v>
       </c>
       <c r="CU145" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV145" s="1">
         <v>48</v>
@@ -50923,7 +50923,7 @@
         <v>0</v>
       </c>
       <c r="BP157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ157" s="2">
         <v>1</v>
@@ -51019,7 +51019,7 @@
         <v>94</v>
       </c>
       <c r="CV157" s="1">
-        <v>5248</v>
+        <v>5247</v>
       </c>
       <c r="CW157" s="1">
         <v>9196</v>
@@ -52890,7 +52890,7 @@
         <v>6</v>
       </c>
       <c r="L164" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M164" s="2">
         <v>24</v>
@@ -53154,7 +53154,7 @@
         <v>9</v>
       </c>
       <c r="CV164" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="CW164" s="1">
         <v>201</v>
@@ -53183,7 +53183,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I165" s="2">
         <v>7</v>
@@ -53459,7 +53459,7 @@
         <v>0</v>
       </c>
       <c r="CV165" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW165" s="1">
         <v>7</v>
@@ -53671,7 +53671,7 @@
         <v>0</v>
       </c>
       <c r="BQ166" s="2">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="BR166" s="1">
         <v>13</v>
@@ -53767,7 +53767,7 @@
         <v>115</v>
       </c>
       <c r="CW166" s="1">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54089,7 +54089,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F168" s="1">
         <v>16</v>
@@ -54290,7 +54290,7 @@
         <v>0</v>
       </c>
       <c r="BT168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU168" s="2">
         <v>1</v>
@@ -54374,10 +54374,10 @@
         <v>25</v>
       </c>
       <c r="CV168" s="1">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="CW168" s="1">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -55193,7 +55193,7 @@
         <v>0</v>
       </c>
       <c r="BP171" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ171" s="2">
         <v>2</v>
@@ -55289,7 +55289,7 @@
         <v>17</v>
       </c>
       <c r="CV171" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="CW171" s="1">
         <v>98</v>
@@ -58060,7 +58060,7 @@
         <v>72</v>
       </c>
       <c r="G181" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181" s="2">
         <v>3</v>
@@ -58336,7 +58336,7 @@
         <v>80</v>
       </c>
       <c r="CU181" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV181" s="1">
         <v>3</v>
@@ -58464,7 +58464,7 @@
         <v>0</v>
       </c>
       <c r="AN182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO182" s="2">
         <v>1</v>
@@ -58596,7 +58596,7 @@
         <v>0</v>
       </c>
       <c r="CF182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG182" s="2">
         <v>1</v>
@@ -58608,7 +58608,7 @@
         <v>4</v>
       </c>
       <c r="CJ182" s="2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="CK182" s="2">
         <v>46</v>
@@ -58644,7 +58644,7 @@
         <v>4</v>
       </c>
       <c r="CV182" s="1">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="CW182" s="1">
         <v>48</v>
@@ -60802,16 +60802,16 @@
         <v>0</v>
       </c>
       <c r="F190" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G190" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" s="2">
         <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J190" s="1">
         <v>0</v>
@@ -61078,16 +61078,16 @@
         <v>0</v>
       </c>
       <c r="CT190" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CU190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV190" s="1">
         <v>3</v>
       </c>
       <c r="CW190" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:101">
@@ -61526,7 +61526,7 @@
         <v>0</v>
       </c>
       <c r="AR192" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS192" s="2">
         <v>4</v>
@@ -61658,7 +61658,7 @@
         <v>3</v>
       </c>
       <c r="CJ192" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CK192" s="2">
         <v>15</v>
@@ -61694,7 +61694,7 @@
         <v>3</v>
       </c>
       <c r="CV192" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CW192" s="1">
         <v>25</v>
@@ -62184,7 +62184,7 @@
         <v>0</v>
       </c>
       <c r="BH194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI194" s="2">
         <v>2</v>
@@ -62304,7 +62304,7 @@
         <v>41</v>
       </c>
       <c r="CV194" s="1">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="CW194" s="1">
         <v>1394</v>
@@ -63987,7 +63987,7 @@
         <v>17</v>
       </c>
       <c r="AY200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ200" s="2">
         <v>6</v>
@@ -64131,7 +64131,7 @@
         <v>16356</v>
       </c>
       <c r="CU200" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CV200" s="1">
         <v>266</v>
@@ -65784,7 +65784,7 @@
         <v>1</v>
       </c>
       <c r="AN206" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO206" s="2">
         <v>7</v>
@@ -65928,7 +65928,7 @@
         <v>0</v>
       </c>
       <c r="CJ206" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CK206" s="2">
         <v>11</v>
@@ -65964,7 +65964,7 @@
         <v>6</v>
       </c>
       <c r="CV206" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CW206" s="1">
         <v>65</v>
@@ -67396,7 +67396,7 @@
         <v>0</v>
       </c>
       <c r="BQ211" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR211" s="1">
         <v>15</v>
@@ -67492,7 +67492,7 @@
         <v>508</v>
       </c>
       <c r="CW211" s="1">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -67811,7 +67811,7 @@
         <v>0</v>
       </c>
       <c r="D213" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E213" s="2">
         <v>5</v>
@@ -67823,7 +67823,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I213" s="2">
         <v>3</v>
@@ -68099,7 +68099,7 @@
         <v>0</v>
       </c>
       <c r="CV213" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CW213" s="1">
         <v>33</v>
@@ -69057,7 +69057,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E32" t="s">
         <v>716</v>
@@ -69960,7 +69960,7 @@
         <v>597</v>
       </c>
       <c r="D77">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E77" t="s">
         <v>716</v>
@@ -70746,7 +70746,7 @@
         <v>631</v>
       </c>
       <c r="D116">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="E116" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5618,7 +5618,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N9" s="1">
         <v>1558</v>
@@ -5882,7 +5882,7 @@
         <v>52</v>
       </c>
       <c r="CW9" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -6509,7 +6509,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1">
         <v>18</v>
@@ -6797,7 +6797,7 @@
         <v>197</v>
       </c>
       <c r="CW12" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -9873,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -10149,7 +10149,7 @@
         <v>2</v>
       </c>
       <c r="CV23" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW23" s="1">
         <v>44</v>
@@ -11093,7 +11093,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="2">
         <v>5</v>
@@ -11369,7 +11369,7 @@
         <v>3</v>
       </c>
       <c r="CV27" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW27" s="1">
         <v>63</v>
@@ -11425,7 +11425,7 @@
         <v>10</v>
       </c>
       <c r="Q28" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -11677,7 +11677,7 @@
         <v>255</v>
       </c>
       <c r="CW28" s="1">
-        <v>770</v>
+        <v>755</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -16374,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="AN44" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO44" s="2">
         <v>8</v>
@@ -16518,7 +16518,7 @@
         <v>0</v>
       </c>
       <c r="CJ44" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="CK44" s="2">
         <v>33</v>
@@ -16554,7 +16554,7 @@
         <v>22</v>
       </c>
       <c r="CV44" s="1">
-        <v>1974</v>
+        <v>1961</v>
       </c>
       <c r="CW44" s="1">
         <v>2450</v>
@@ -18108,7 +18108,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2">
         <v>3</v>
@@ -18384,7 +18384,7 @@
         <v>2</v>
       </c>
       <c r="CV50" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CW50" s="1">
         <v>73</v>
@@ -19926,7 +19926,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E56" s="2">
         <v>37</v>
@@ -19950,7 +19950,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M56" s="2">
         <v>16</v>
@@ -20214,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="CV56" s="1">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="CW56" s="1">
         <v>354</v>
@@ -21487,7 +21487,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q61" s="2">
         <v>399</v>
@@ -21739,7 +21739,7 @@
         <v>-5</v>
       </c>
       <c r="CV61" s="1">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="CW61" s="1">
         <v>928</v>
@@ -22453,7 +22453,7 @@
         <v>66</v>
       </c>
       <c r="AG64" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>177</v>
       </c>
       <c r="CW64" s="1">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25527,7 +25527,7 @@
         <v>106</v>
       </c>
       <c r="AO74" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CK74" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25704,10 +25704,10 @@
         <v>171</v>
       </c>
       <c r="CV74" s="1">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="CW74" s="1">
-        <v>4423</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26218,10 +26218,10 @@
         <v>0</v>
       </c>
       <c r="BP76" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ76" s="2">
         <v>2</v>
-      </c>
-      <c r="BQ76" s="2">
-        <v>17</v>
       </c>
       <c r="BR76" s="1">
         <v>3</v>
@@ -26314,10 +26314,10 @@
         <v>114</v>
       </c>
       <c r="CV76" s="1">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="CW76" s="1">
-        <v>3757</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26586,7 +26586,7 @@
         <v>333</v>
       </c>
       <c r="CK77" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26607,7 +26607,7 @@
         <v>0</v>
       </c>
       <c r="CR77" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CS77" s="2">
         <v>1</v>
@@ -26619,10 +26619,10 @@
         <v>96</v>
       </c>
       <c r="CV77" s="1">
-        <v>10225</v>
+        <v>10223</v>
       </c>
       <c r="CW77" s="1">
-        <v>15913</v>
+        <v>15910</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -28356,7 +28356,7 @@
         <v>1</v>
       </c>
       <c r="BQ83" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR83" s="1">
         <v>8</v>
@@ -28452,7 +28452,7 @@
         <v>945</v>
       </c>
       <c r="CW83" s="1">
-        <v>5495</v>
+        <v>5494</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29076,7 +29076,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
@@ -29364,7 +29364,7 @@
         <v>0</v>
       </c>
       <c r="CV86" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CW86" s="1">
         <v>73</v>
@@ -35027,7 +35027,7 @@
         <v>0</v>
       </c>
       <c r="BD105" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE105" s="2">
         <v>2</v>
@@ -35159,7 +35159,7 @@
         <v>31</v>
       </c>
       <c r="CV105" s="1">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="CW105" s="1">
         <v>500</v>
@@ -38836,7 +38836,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" s="2">
         <v>2</v>
@@ -39124,7 +39124,7 @@
         <v>5</v>
       </c>
       <c r="CV118" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CW118" s="1">
         <v>40</v>
@@ -39201,7 +39201,7 @@
         <v>0</v>
       </c>
       <c r="X119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y119" s="2">
         <v>1</v>
@@ -39429,7 +39429,7 @@
         <v>3</v>
       </c>
       <c r="CV119" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW119" s="1">
         <v>27</v>
@@ -39458,7 +39458,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I120" s="2">
         <v>5</v>
@@ -39734,7 +39734,7 @@
         <v>6</v>
       </c>
       <c r="CV120" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CW120" s="1">
         <v>72</v>
@@ -41528,7 +41528,7 @@
         <v>0</v>
       </c>
       <c r="CJ126" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CK126" s="2">
         <v>4</v>
@@ -41564,7 +41564,7 @@
         <v>1</v>
       </c>
       <c r="CV126" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CW126" s="1">
         <v>17</v>
@@ -44105,7 +44105,7 @@
         <v>2</v>
       </c>
       <c r="AF135" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG135" s="2">
         <v>752</v>
@@ -44309,7 +44309,7 @@
         <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="CW135" s="1">
         <v>2691</v>
@@ -44631,7 +44631,7 @@
         <v>4</v>
       </c>
       <c r="D137" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E137" s="2">
         <v>16</v>
@@ -44646,7 +44646,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J137" s="1">
         <v>43</v>
@@ -44655,7 +44655,7 @@
         <v>4</v>
       </c>
       <c r="L137" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M137" s="2">
         <v>8</v>
@@ -44919,10 +44919,10 @@
         <v>10</v>
       </c>
       <c r="CV137" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CW137" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -49230,7 +49230,7 @@
         <v>13</v>
       </c>
       <c r="L152" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M152" s="2">
         <v>67</v>
@@ -49494,7 +49494,7 @@
         <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="CW152" s="1">
         <v>279</v>
@@ -51204,7 +51204,7 @@
         <v>0</v>
       </c>
       <c r="BH158" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BI158" s="2">
         <v>5</v>
@@ -51324,7 +51324,7 @@
         <v>239</v>
       </c>
       <c r="CV158" s="1">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="CW158" s="1">
         <v>1714</v>
@@ -57268,7 +57268,7 @@
         <v>0</v>
       </c>
       <c r="AV178" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW178" s="2">
         <v>2</v>
@@ -57424,7 +57424,7 @@
         <v>-309</v>
       </c>
       <c r="CV178" s="1">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="CW178" s="1">
         <v>4592</v>
@@ -57453,7 +57453,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I179" s="2">
         <v>5</v>
@@ -57729,7 +57729,7 @@
         <v>8</v>
       </c>
       <c r="CV179" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="CW179" s="1">
         <v>75</v>
@@ -63978,7 +63978,7 @@
         <v>0</v>
       </c>
       <c r="AV200" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW200" s="2">
         <v>5</v>
@@ -63990,7 +63990,7 @@
         <v>0</v>
       </c>
       <c r="AZ200" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA200" s="2">
         <v>7</v>
@@ -64134,7 +64134,7 @@
         <v>66</v>
       </c>
       <c r="CV200" s="1">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="CW200" s="1">
         <v>526</v>
@@ -64226,7 +64226,7 @@
         <v>3</v>
       </c>
       <c r="AC201" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD201" s="1">
         <v>48204</v>
@@ -64442,7 +64442,7 @@
         <v>2006</v>
       </c>
       <c r="CW201" s="1">
-        <v>3167</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -69057,7 +69057,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E32" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4144,16 +4144,16 @@
         <v>7</v>
       </c>
       <c r="AD4" s="1">
-        <v>21444</v>
+        <v>21644</v>
       </c>
       <c r="AE4" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF4" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG4" s="2">
-        <v>339</v>
+        <v>539</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -4348,16 +4348,16 @@
         <v>0</v>
       </c>
       <c r="CT4" s="1">
-        <v>42984</v>
+        <v>43184</v>
       </c>
       <c r="CU4" s="1">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="CV4" s="1">
-        <v>436</v>
+        <v>636</v>
       </c>
       <c r="CW4" s="1">
-        <v>1178</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
@@ -4964,7 +4964,7 @@
         <v>34</v>
       </c>
       <c r="CV6" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="CW6" s="1">
         <v>136</v>
@@ -5609,16 +5609,16 @@
         <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K9" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L9" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N9" s="1">
         <v>1558</v>
@@ -5873,16 +5873,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2867</v>
+        <v>2872</v>
       </c>
       <c r="CU9" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV9" s="1">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="CW9" s="1">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -6500,16 +6500,16 @@
         <v>111</v>
       </c>
       <c r="B12" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1">
         <v>18</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="CT12" s="1">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="CU12" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CV12" s="1">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="CW12" s="1">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="1">
         <v>3</v>
@@ -10143,16 +10143,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="CU23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CW23" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -13234,16 +13234,16 @@
         <v>6</v>
       </c>
       <c r="J34" s="1">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="K34" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L34" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M34" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N34" s="1">
         <v>1429</v>
@@ -13498,16 +13498,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2582</v>
+        <v>2588</v>
       </c>
       <c r="CU34" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV34" s="1">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="CW34" s="1">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14550,16 +14550,16 @@
         <v>0</v>
       </c>
       <c r="AP38" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AQ38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="2">
         <v>3</v>
       </c>
       <c r="AS38" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -14694,16 +14694,16 @@
         <v>3</v>
       </c>
       <c r="CL38" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CM38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN38" s="2">
         <v>3</v>
       </c>
       <c r="CO38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP38" s="1">
         <v>0</v>
@@ -14718,16 +14718,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="CU38" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV38" s="1">
         <v>43</v>
       </c>
       <c r="CW38" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -14987,16 +14987,16 @@
         <v>0</v>
       </c>
       <c r="CH39" s="1">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="CI39" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ39" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="CK39" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="CL39" s="1">
         <v>2</v>
@@ -15023,16 +15023,16 @@
         <v>0</v>
       </c>
       <c r="CT39" s="1">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="CU39" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="CV39" s="1">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="CW39" s="1">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15363,7 +15363,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="2">
         <v>4</v>
@@ -15459,7 +15459,7 @@
         <v>7</v>
       </c>
       <c r="AN41" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO41" s="2">
         <v>23</v>
@@ -15603,7 +15603,7 @@
         <v>25</v>
       </c>
       <c r="CJ41" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CK41" s="2">
         <v>45</v>
@@ -15639,7 +15639,7 @@
         <v>34</v>
       </c>
       <c r="CV41" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CW41" s="1">
         <v>79</v>
@@ -17492,16 +17492,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="1">
         <v>0</v>
@@ -17768,16 +17768,16 @@
         <v>0</v>
       </c>
       <c r="CT48" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="CU48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:101">
@@ -18395,16 +18395,16 @@
         <v>150</v>
       </c>
       <c r="B51" s="1">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E51" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18683,16 +18683,16 @@
         <v>0</v>
       </c>
       <c r="CT51" s="1">
-        <v>3741</v>
+        <v>3745</v>
       </c>
       <c r="CU51" s="1">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="CV51" s="1">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="CW51" s="1">
-        <v>2152</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -19920,40 +19920,40 @@
         <v>155</v>
       </c>
       <c r="B56" s="1">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2">
+        <v>16</v>
+      </c>
+      <c r="E56" s="2">
+        <v>38</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1547</v>
+      </c>
+      <c r="K56" s="2">
         <v>15</v>
       </c>
-      <c r="E56" s="2">
-        <v>37</v>
-      </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>1532</v>
-      </c>
-      <c r="K56" s="2">
-        <v>0</v>
-      </c>
       <c r="L56" s="2">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M56" s="2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="N56" s="1">
         <v>2310</v>
@@ -20208,16 +20208,16 @@
         <v>0</v>
       </c>
       <c r="CT56" s="1">
-        <v>7797</v>
+        <v>7813</v>
       </c>
       <c r="CU56" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="CV56" s="1">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="CW56" s="1">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -21448,7 +21448,7 @@
         <v>6491</v>
       </c>
       <c r="C61" s="2">
-        <v>-23</v>
+        <v>-40</v>
       </c>
       <c r="D61" s="2">
         <v>191</v>
@@ -21736,7 +21736,7 @@
         <v>65926</v>
       </c>
       <c r="CU61" s="1">
-        <v>-5</v>
+        <v>-22</v>
       </c>
       <c r="CV61" s="1">
         <v>438</v>
@@ -22082,7 +22082,7 @@
         <v>330</v>
       </c>
       <c r="K63" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2">
         <v>11</v>
@@ -22178,7 +22178,7 @@
         <v>67</v>
       </c>
       <c r="AQ63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR63" s="2">
         <v>3</v>
@@ -22310,7 +22310,7 @@
         <v>692</v>
       </c>
       <c r="CI63" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ63" s="2">
         <v>33</v>
@@ -22346,7 +22346,7 @@
         <v>2880</v>
       </c>
       <c r="CU63" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CV63" s="1">
         <v>93</v>
@@ -22399,7 +22399,7 @@
         <v>4322</v>
       </c>
       <c r="O64" s="2">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="P64" s="2">
         <v>73</v>
@@ -22444,16 +22444,16 @@
         <v>5</v>
       </c>
       <c r="AD64" s="1">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="AE64" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AF64" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AG64" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22648,16 +22648,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8029</v>
+        <v>8032</v>
       </c>
       <c r="CU64" s="1">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="CV64" s="1">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="CW64" s="1">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23275,16 +23275,16 @@
         <v>166</v>
       </c>
       <c r="B67" s="1">
-        <v>2481</v>
+        <v>2500</v>
       </c>
       <c r="C67" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D67" s="2">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E67" s="2">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -23563,16 +23563,16 @@
         <v>0</v>
       </c>
       <c r="CT67" s="1">
-        <v>3358</v>
+        <v>3377</v>
       </c>
       <c r="CU67" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CV67" s="1">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="CW67" s="1">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:101">
@@ -23784,16 +23784,16 @@
         <v>0</v>
       </c>
       <c r="BR68" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV68" s="1">
         <v>0</v>
@@ -23868,16 +23868,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="CU68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV68" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CW68" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -25518,16 +25518,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36284</v>
+        <v>36288</v>
       </c>
       <c r="AM74" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AN74" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AO74" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25650,16 +25650,16 @@
         <v>0</v>
       </c>
       <c r="CD74" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CE74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH74" s="1">
         <v>16216</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171786</v>
+        <v>171791</v>
       </c>
       <c r="CU74" s="1">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="CV74" s="1">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="CW74" s="1">
-        <v>4420</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26212,16 +26212,16 @@
         <v>0</v>
       </c>
       <c r="BN76" s="1">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="BO76" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BP76" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ76" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="BR76" s="1">
         <v>3</v>
@@ -26308,16 +26308,16 @@
         <v>0</v>
       </c>
       <c r="CT76" s="1">
-        <v>151127</v>
+        <v>151140</v>
       </c>
       <c r="CU76" s="1">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="CV76" s="1">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="CW76" s="1">
-        <v>3742</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26367,7 +26367,7 @@
         <v>0</v>
       </c>
       <c r="P77" s="2">
-        <v>9555</v>
+        <v>9556</v>
       </c>
       <c r="Q77" s="2">
         <v>19095</v>
@@ -26433,16 +26433,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="AM77" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AN77" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO77" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26523,7 +26523,7 @@
         <v>13</v>
       </c>
       <c r="BP77" s="2">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BQ77" s="2">
         <v>66</v>
@@ -26577,16 +26577,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7356</v>
+        <v>7365</v>
       </c>
       <c r="CI77" s="2">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="CJ77" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="CK77" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26607,22 +26607,22 @@
         <v>0</v>
       </c>
       <c r="CR77" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CS77" s="2">
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390969</v>
+        <v>390977</v>
       </c>
       <c r="CU77" s="1">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="CV77" s="1">
-        <v>10223</v>
+        <v>10183</v>
       </c>
       <c r="CW77" s="1">
-        <v>15910</v>
+        <v>15918</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27187,16 +27187,16 @@
         <v>0</v>
       </c>
       <c r="CH79" s="1">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="CI79" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="CJ79" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="CK79" s="2">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="CL79" s="1">
         <v>2</v>
@@ -27223,16 +27223,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90679</v>
+        <v>90689</v>
       </c>
       <c r="CU79" s="1">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="CV79" s="1">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="CW79" s="1">
-        <v>1889</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27692,7 +27692,7 @@
         <v>11</v>
       </c>
       <c r="AY81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ81" s="2">
         <v>2</v>
@@ -27836,7 +27836,7 @@
         <v>6423</v>
       </c>
       <c r="CU81" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV81" s="1">
         <v>146</v>
@@ -28179,16 +28179,16 @@
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8710</v>
+        <v>8700</v>
       </c>
       <c r="K83" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L83" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="M83" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28293,10 +28293,10 @@
         <v>1</v>
       </c>
       <c r="AV83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW83" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX83" s="1">
         <v>17</v>
@@ -28308,7 +28308,7 @@
         <v>1</v>
       </c>
       <c r="BA83" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB83" s="1">
         <v>14</v>
@@ -28347,16 +28347,16 @@
         <v>0</v>
       </c>
       <c r="BN83" s="1">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="BO83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP83" s="2">
         <v>1</v>
       </c>
       <c r="BQ83" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR83" s="1">
         <v>8</v>
@@ -28443,16 +28443,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423974</v>
+        <v>423965</v>
       </c>
       <c r="CU83" s="1">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="CV83" s="1">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="CW83" s="1">
-        <v>5494</v>
+        <v>5483</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28777,16 +28777,16 @@
         <v>1</v>
       </c>
       <c r="F85" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J85" s="1">
         <v>0</v>
@@ -29053,16 +29053,16 @@
         <v>0</v>
       </c>
       <c r="CT85" s="1">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="CU85" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV85" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CW85" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29094,16 +29094,16 @@
         <v>1</v>
       </c>
       <c r="J86" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="1">
         <v>1593</v>
@@ -29196,7 +29196,7 @@
         <v>0</v>
       </c>
       <c r="AR86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS86" s="2">
         <v>3</v>
@@ -29328,7 +29328,7 @@
         <v>0</v>
       </c>
       <c r="CJ86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK86" s="2">
         <v>16</v>
@@ -29358,16 +29358,16 @@
         <v>0</v>
       </c>
       <c r="CT86" s="1">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="CU86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV86" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CW86" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -29375,16 +29375,16 @@
         <v>186</v>
       </c>
       <c r="B87" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F87" s="1">
         <v>21</v>
@@ -29489,7 +29489,7 @@
         <v>1</v>
       </c>
       <c r="AN87" s="2">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="AO87" s="2">
         <v>6</v>
@@ -29633,7 +29633,7 @@
         <v>10</v>
       </c>
       <c r="CJ87" s="2">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="CK87" s="2">
         <v>99</v>
@@ -29663,16 +29663,16 @@
         <v>0</v>
       </c>
       <c r="CT87" s="1">
-        <v>2985</v>
+        <v>2988</v>
       </c>
       <c r="CU87" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CV87" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="CW87" s="1">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -30069,16 +30069,16 @@
         <v>0</v>
       </c>
       <c r="AD89" s="1">
-        <v>1481</v>
+        <v>1532</v>
       </c>
       <c r="AE89" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AF89" s="2">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="AG89" s="2">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AH89" s="1">
         <v>0</v>
@@ -30273,16 +30273,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2180</v>
+        <v>2231</v>
       </c>
       <c r="CU89" s="1">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="CV89" s="1">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="CW89" s="1">
-        <v>205</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30787,16 +30787,16 @@
         <v>0</v>
       </c>
       <c r="BN91" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BO91" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP91" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BQ91" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BR91" s="1">
         <v>14</v>
@@ -30883,16 +30883,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>26019</v>
+        <v>26024</v>
       </c>
       <c r="CU91" s="1">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="CV91" s="1">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="CW91" s="1">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -31522,292 +31522,292 @@
         <v>3</v>
       </c>
       <c r="F94" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G94" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" s="2">
+        <v>4</v>
+      </c>
+      <c r="J94" s="1">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1">
+        <v>0</v>
+      </c>
+      <c r="O94" s="2">
+        <v>0</v>
+      </c>
+      <c r="P94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>0</v>
+      </c>
+      <c r="R94" s="1">
+        <v>0</v>
+      </c>
+      <c r="S94" s="2">
+        <v>0</v>
+      </c>
+      <c r="T94" s="2">
+        <v>0</v>
+      </c>
+      <c r="U94" s="2">
+        <v>0</v>
+      </c>
+      <c r="V94" s="1">
+        <v>0</v>
+      </c>
+      <c r="W94" s="2">
+        <v>0</v>
+      </c>
+      <c r="X94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY94" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV94" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY94" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP94" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS94" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT94" s="1">
+        <v>63</v>
+      </c>
+      <c r="CU94" s="1">
         <v>2</v>
       </c>
-      <c r="J94" s="1">
-        <v>0</v>
-      </c>
-      <c r="K94" s="2">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2">
-        <v>0</v>
-      </c>
-      <c r="N94" s="1">
-        <v>0</v>
-      </c>
-      <c r="O94" s="2">
-        <v>0</v>
-      </c>
-      <c r="P94" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="2">
-        <v>0</v>
-      </c>
-      <c r="R94" s="1">
-        <v>0</v>
-      </c>
-      <c r="S94" s="2">
-        <v>0</v>
-      </c>
-      <c r="T94" s="2">
-        <v>0</v>
-      </c>
-      <c r="U94" s="2">
-        <v>0</v>
-      </c>
-      <c r="V94" s="1">
-        <v>0</v>
-      </c>
-      <c r="W94" s="2">
-        <v>0</v>
-      </c>
-      <c r="X94" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY94" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV94" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY94" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP94" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS94" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT94" s="1">
-        <v>61</v>
-      </c>
-      <c r="CU94" s="1">
-        <v>0</v>
-      </c>
       <c r="CV94" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CW94" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:101">
@@ -32378,7 +32378,7 @@
         <v>0</v>
       </c>
       <c r="CJ96" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CK96" s="2">
         <v>24</v>
@@ -32414,7 +32414,7 @@
         <v>1</v>
       </c>
       <c r="CV96" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="CW96" s="1">
         <v>41</v>
@@ -32745,7 +32745,7 @@
         <v>76</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="2">
         <v>7</v>
@@ -33021,7 +33021,7 @@
         <v>81</v>
       </c>
       <c r="CU98" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV98" s="1">
         <v>7</v>
@@ -33660,7 +33660,7 @@
         <v>74</v>
       </c>
       <c r="G101" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2">
         <v>6</v>
@@ -33936,7 +33936,7 @@
         <v>94</v>
       </c>
       <c r="CU101" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CV101" s="1">
         <v>6</v>
@@ -35173,7 +35173,7 @@
         <v>9449</v>
       </c>
       <c r="C106" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D106" s="2">
         <v>192</v>
@@ -35206,16 +35206,16 @@
         <v>873</v>
       </c>
       <c r="N106" s="1">
-        <v>22916</v>
+        <v>22919</v>
       </c>
       <c r="O106" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P106" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q106" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R106" s="1">
         <v>0</v>
@@ -35458,16 +35458,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92789</v>
+        <v>92792</v>
       </c>
       <c r="CU106" s="1">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="CV106" s="1">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="CW106" s="1">
-        <v>2471</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35798,7 +35798,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I108" s="2">
         <v>3</v>
@@ -36074,7 +36074,7 @@
         <v>2</v>
       </c>
       <c r="CV108" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW108" s="1">
         <v>52</v>
@@ -38361,7 +38361,7 @@
         <v>7</v>
       </c>
       <c r="AW116" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX116" s="1">
         <v>4</v>
@@ -38517,7 +38517,7 @@
         <v>391</v>
       </c>
       <c r="CW116" s="1">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38842,16 +38842,16 @@
         <v>2</v>
       </c>
       <c r="F118" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="1">
         <v>0</v>
@@ -39118,16 +39118,16 @@
         <v>0</v>
       </c>
       <c r="CT118" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="CU118" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV118" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CW118" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:101">
@@ -40355,16 +40355,16 @@
         <v>222</v>
       </c>
       <c r="B123" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="1">
         <v>49</v>
@@ -40478,7 +40478,7 @@
         <v>171</v>
       </c>
       <c r="AQ123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR123" s="2">
         <v>3</v>
@@ -40622,7 +40622,7 @@
         <v>96</v>
       </c>
       <c r="CM123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN123" s="2">
         <v>3</v>
@@ -40643,16 +40643,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="CU123" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV123" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW123" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -44093,7 +44093,7 @@
         <v>0</v>
       </c>
       <c r="AB135" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC135" s="2">
         <v>8</v>
@@ -44201,7 +44201,7 @@
         <v>0</v>
       </c>
       <c r="BL135" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM135" s="2">
         <v>2</v>
@@ -44309,7 +44309,7 @@
         <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="CW135" s="1">
         <v>2691</v>
@@ -44320,16 +44320,16 @@
         <v>235</v>
       </c>
       <c r="B136" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E136" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1">
         <v>17</v>
@@ -44608,16 +44608,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158874</v>
+        <v>158875</v>
       </c>
       <c r="CU136" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV136" s="1">
-        <v>5079</v>
+        <v>5080</v>
       </c>
       <c r="CW136" s="1">
-        <v>6082</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44751,7 +44751,7 @@
         <v>1</v>
       </c>
       <c r="AR137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS137" s="2">
         <v>5</v>
@@ -44883,7 +44883,7 @@
         <v>0</v>
       </c>
       <c r="CJ137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK137" s="2">
         <v>1</v>
@@ -44919,7 +44919,7 @@
         <v>10</v>
       </c>
       <c r="CV137" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW137" s="1">
         <v>36</v>
@@ -44960,7 +44960,7 @@
         <v>18</v>
       </c>
       <c r="L138" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M138" s="2">
         <v>76</v>
@@ -45224,7 +45224,7 @@
         <v>21</v>
       </c>
       <c r="CV138" s="1">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="CW138" s="1">
         <v>282</v>
@@ -45744,16 +45744,16 @@
         <v>0</v>
       </c>
       <c r="BR140" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU140" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV140" s="1">
         <v>0</v>
@@ -45828,16 +45828,16 @@
         <v>0</v>
       </c>
       <c r="CT140" s="1">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="CU140" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV140" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW140" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -45875,7 +45875,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2">
         <v>1</v>
@@ -46139,7 +46139,7 @@
         <v>3</v>
       </c>
       <c r="CV141" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW141" s="1">
         <v>39</v>
@@ -46354,16 +46354,16 @@
         <v>1</v>
       </c>
       <c r="BR142" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV142" s="1">
         <v>0</v>
@@ -46438,16 +46438,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="CU142" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CV142" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CW142" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47687,16 +47687,16 @@
         <v>0</v>
       </c>
       <c r="F147" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I147" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J147" s="1">
         <v>18</v>
@@ -47723,16 +47723,16 @@
         <v>6</v>
       </c>
       <c r="R147" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V147" s="1">
         <v>0</v>
@@ -47963,16 +47963,16 @@
         <v>0</v>
       </c>
       <c r="CT147" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="CU147" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CV147" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CW147" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -49233,7 +49233,7 @@
         <v>38</v>
       </c>
       <c r="M152" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N152" s="1">
         <v>168</v>
@@ -49497,7 +49497,7 @@
         <v>89</v>
       </c>
       <c r="CW152" s="1">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50115,16 +50115,16 @@
         <v>254</v>
       </c>
       <c r="B155" s="1">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" s="1">
         <v>29</v>
@@ -50403,16 +50403,16 @@
         <v>0</v>
       </c>
       <c r="CT155" s="1">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="CU155" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CW155" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -51066,16 +51066,16 @@
         <v>414</v>
       </c>
       <c r="N158" s="1">
-        <v>3024</v>
+        <v>3027</v>
       </c>
       <c r="O158" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P158" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Q158" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51144,7 +51144,7 @@
         <v>6</v>
       </c>
       <c r="AN158" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO158" s="2">
         <v>43</v>
@@ -51318,16 +51318,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25700</v>
+        <v>25703</v>
       </c>
       <c r="CU158" s="1">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="CV158" s="1">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="CW158" s="1">
-        <v>1714</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -53177,16 +53177,16 @@
         <v>0</v>
       </c>
       <c r="F165" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I165" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J165" s="1">
         <v>0</v>
@@ -53453,16 +53453,16 @@
         <v>0</v>
       </c>
       <c r="CT165" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CU165" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV165" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW165" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:101">
@@ -54080,16 +54080,16 @@
         <v>267</v>
       </c>
       <c r="B168" s="1">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C168" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D168" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1">
         <v>16</v>
@@ -54368,16 +54368,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5973</v>
+        <v>5975</v>
       </c>
       <c r="CU168" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CV168" s="1">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CW168" s="1">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54496,7 +54496,7 @@
         <v>120</v>
       </c>
       <c r="AM169" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN169" s="2">
         <v>3</v>
@@ -54508,7 +54508,7 @@
         <v>1</v>
       </c>
       <c r="AQ169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR169" s="2">
         <v>1</v>
@@ -54640,7 +54640,7 @@
         <v>183</v>
       </c>
       <c r="CI169" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ169" s="2">
         <v>8</v>
@@ -54676,7 +54676,7 @@
         <v>365</v>
       </c>
       <c r="CU169" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CV169" s="1">
         <v>15</v>
@@ -54690,16 +54690,16 @@
         <v>269</v>
       </c>
       <c r="B170" s="1">
-        <v>4549</v>
+        <v>4574</v>
       </c>
       <c r="C170" s="2">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D170" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E170" s="2">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -54768,7 +54768,7 @@
         <v>0</v>
       </c>
       <c r="AB170" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC170" s="2">
         <v>7</v>
@@ -54978,16 +54978,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19625</v>
+        <v>19650</v>
       </c>
       <c r="CU170" s="1">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="CV170" s="1">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="CW170" s="1">
-        <v>1250</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -57549,7 +57549,7 @@
         <v>2</v>
       </c>
       <c r="AN179" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AO179" s="2">
         <v>40</v>
@@ -57693,7 +57693,7 @@
         <v>4</v>
       </c>
       <c r="CJ179" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CK179" s="2">
         <v>28</v>
@@ -57729,7 +57729,7 @@
         <v>8</v>
       </c>
       <c r="CV179" s="1">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="CW179" s="1">
         <v>75</v>
@@ -57743,7 +57743,7 @@
         <v>8113</v>
       </c>
       <c r="C180" s="2">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="D180" s="2">
         <v>118</v>
@@ -58031,7 +58031,7 @@
         <v>51226</v>
       </c>
       <c r="CU180" s="1">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="CV180" s="1">
         <v>1234</v>
@@ -59277,16 +59277,16 @@
         <v>0</v>
       </c>
       <c r="F185" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J185" s="1">
         <v>0</v>
@@ -59553,16 +59553,16 @@
         <v>0</v>
       </c>
       <c r="CT185" s="1">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="CU185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV185" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -61717,16 +61717,16 @@
         <v>0</v>
       </c>
       <c r="F193" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G193" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="1">
         <v>0</v>
@@ -61993,16 +61993,16 @@
         <v>0</v>
       </c>
       <c r="CT193" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CU193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:101">
@@ -63936,16 +63936,16 @@
         <v>21</v>
       </c>
       <c r="AH200" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL200" s="1">
         <v>405</v>
@@ -63990,7 +63990,7 @@
         <v>0</v>
       </c>
       <c r="AZ200" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA200" s="2">
         <v>7</v>
@@ -64128,16 +64128,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16356</v>
+        <v>16357</v>
       </c>
       <c r="CU200" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CV200" s="1">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CW200" s="1">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64169,16 +64169,16 @@
         <v>0</v>
       </c>
       <c r="J201" s="1">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="K201" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L201" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M201" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N201" s="1">
         <v>23253</v>
@@ -64433,16 +64433,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88132</v>
+        <v>88131</v>
       </c>
       <c r="CU201" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="CV201" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="CW201" s="1">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64462,16 +64462,16 @@
         <v>0</v>
       </c>
       <c r="F202" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G202" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" s="2">
+        <v>3</v>
+      </c>
+      <c r="I202" s="2">
         <v>2</v>
-      </c>
-      <c r="I202" s="2">
-        <v>1</v>
       </c>
       <c r="J202" s="1">
         <v>0</v>
@@ -64738,16 +64738,16 @@
         <v>0</v>
       </c>
       <c r="CT202" s="1">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="CU202" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CV202" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CW202" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65670,16 +65670,16 @@
         <v>305</v>
       </c>
       <c r="B206" s="1">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C206" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D206" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E206" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65958,16 +65958,16 @@
         <v>0</v>
       </c>
       <c r="CT206" s="1">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="CU206" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CV206" s="1">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="CW206" s="1">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66926,16 +66926,16 @@
         <v>0</v>
       </c>
       <c r="N210" s="1">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O210" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P210" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q210" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R210" s="1">
         <v>8</v>
@@ -67004,7 +67004,7 @@
         <v>0</v>
       </c>
       <c r="AN210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO210" s="2">
         <v>1</v>
@@ -67094,16 +67094,16 @@
         <v>0</v>
       </c>
       <c r="BR210" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BS210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU210" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV210" s="1">
         <v>1</v>
@@ -67178,16 +67178,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="CU210" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CV210" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="CW210" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="AO6" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AP6" s="1">
         <v>1</v>
@@ -4931,7 +4931,7 @@
         <v>68</v>
       </c>
       <c r="CK6" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="CL6" s="1">
         <v>1</v>
@@ -4967,7 +4967,7 @@
         <v>81</v>
       </c>
       <c r="CW6" s="1">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -6608,16 +6608,16 @@
         <v>0</v>
       </c>
       <c r="AL12" s="1">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AM12" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AN12" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AO12" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AP12" s="1">
         <v>0</v>
@@ -6752,16 +6752,16 @@
         <v>1</v>
       </c>
       <c r="CH12" s="1">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="CI12" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="CJ12" s="2">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CK12" s="2">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="CL12" s="1">
         <v>0</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="CT12" s="1">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="CU12" s="1">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="CV12" s="1">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="CW12" s="1">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7230,16 +7230,16 @@
         <v>11</v>
       </c>
       <c r="AP14" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AQ14" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR14" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS14" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT14" s="1">
         <v>0</v>
@@ -7398,16 +7398,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="CU14" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CV14" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CW14" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7744,16 +7744,16 @@
         <v>3</v>
       </c>
       <c r="J16" s="1">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N16" s="1">
         <v>345</v>
@@ -8008,16 +8008,16 @@
         <v>0</v>
       </c>
       <c r="CT16" s="1">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="CU16" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV16" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CW16" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L20" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="N20" s="1">
         <v>12653</v>
@@ -9228,16 +9228,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20729</v>
+        <v>20738</v>
       </c>
       <c r="CU20" s="1">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="CW20" s="1">
-        <v>947</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -14670,16 +14670,16 @@
         <v>0</v>
       </c>
       <c r="CD38" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CE38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH38" s="1">
         <v>301</v>
@@ -14718,16 +14718,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="CU38" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV38" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CW38" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -15366,7 +15366,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
@@ -15462,7 +15462,7 @@
         <v>7</v>
       </c>
       <c r="AO41" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AP41" s="1">
         <v>11</v>
@@ -15606,7 +15606,7 @@
         <v>25</v>
       </c>
       <c r="CK41" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="CL41" s="1">
         <v>6</v>
@@ -15642,7 +15642,7 @@
         <v>34</v>
       </c>
       <c r="CW41" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:101">
@@ -16260,16 +16260,16 @@
         <v>143</v>
       </c>
       <c r="B44" s="1">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D44" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E44" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F44" s="1">
         <v>13</v>
@@ -16464,16 +16464,16 @@
         <v>0</v>
       </c>
       <c r="BR44" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BS44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV44" s="1">
         <v>0</v>
@@ -16548,16 +16548,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50657</v>
+        <v>50664</v>
       </c>
       <c r="CU44" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CV44" s="1">
-        <v>1961</v>
+        <v>1968</v>
       </c>
       <c r="CW44" s="1">
-        <v>2450</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -17797,16 +17797,16 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G49" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I49" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
@@ -18073,16 +18073,16 @@
         <v>0</v>
       </c>
       <c r="CT49" s="1">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="CU49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV49" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CW49" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:101">
@@ -20237,292 +20237,292 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2">
+        <v>3</v>
+      </c>
+      <c r="I57" s="2">
+        <v>6</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="2">
+        <v>0</v>
+      </c>
+      <c r="X57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV57" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY57" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CP57" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS57" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT57" s="1">
+        <v>66</v>
+      </c>
+      <c r="CU57" s="1">
         <v>2</v>
       </c>
-      <c r="I57" s="2">
-        <v>5</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="2">
-        <v>0</v>
-      </c>
-      <c r="X57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP57" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT57" s="1">
-        <v>65</v>
-      </c>
-      <c r="CU57" s="1">
-        <v>1</v>
-      </c>
       <c r="CV57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW57" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:101">
@@ -20991,16 +20991,16 @@
         <v>0</v>
       </c>
       <c r="BB59" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC59" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD59" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE59" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BF59" s="1">
         <v>0</v>
@@ -21039,16 +21039,16 @@
         <v>0</v>
       </c>
       <c r="BR59" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV59" s="1">
         <v>0</v>
@@ -21123,16 +21123,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="CU59" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV59" s="1">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="CW59" s="1">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21619,7 +21619,7 @@
         <v>0</v>
       </c>
       <c r="BH61" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI61" s="2">
         <v>2</v>
@@ -21739,7 +21739,7 @@
         <v>-22</v>
       </c>
       <c r="CV61" s="1">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="CW61" s="1">
         <v>928</v>
@@ -22573,7 +22573,7 @@
         <v>2</v>
       </c>
       <c r="BU64" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>180</v>
       </c>
       <c r="CW64" s="1">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25668,7 +25668,7 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="CK74" s="2">
         <v>421</v>
@@ -25704,7 +25704,7 @@
         <v>176</v>
       </c>
       <c r="CV74" s="1">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="CW74" s="1">
         <v>4425</v>
@@ -26439,7 +26439,7 @@
         <v>9</v>
       </c>
       <c r="AN77" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AO77" s="2">
         <v>74</v>
@@ -26619,7 +26619,7 @@
         <v>103</v>
       </c>
       <c r="CV77" s="1">
-        <v>10183</v>
+        <v>10182</v>
       </c>
       <c r="CW77" s="1">
         <v>15918</v>
@@ -27240,28 +27240,28 @@
         <v>179</v>
       </c>
       <c r="B80" s="1">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C80" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80" s="2">
+        <v>10</v>
+      </c>
+      <c r="E80" s="2">
+        <v>15</v>
+      </c>
+      <c r="F80" s="1">
+        <v>21</v>
+      </c>
+      <c r="G80" s="2">
+        <v>4</v>
+      </c>
+      <c r="H80" s="2">
         <v>5</v>
       </c>
-      <c r="E80" s="2">
-        <v>10</v>
-      </c>
-      <c r="F80" s="1">
-        <v>17</v>
-      </c>
-      <c r="G80" s="2">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2">
-        <v>1</v>
-      </c>
       <c r="I80" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -27528,16 +27528,16 @@
         <v>0</v>
       </c>
       <c r="CT80" s="1">
-        <v>1798</v>
+        <v>1807</v>
       </c>
       <c r="CU80" s="1">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="CV80" s="1">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="CW80" s="1">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27755,7 +27755,7 @@
         <v>0</v>
       </c>
       <c r="BT81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU81" s="2">
         <v>1</v>
@@ -27839,7 +27839,7 @@
         <v>17</v>
       </c>
       <c r="CV81" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="CW81" s="1">
         <v>365</v>
@@ -30799,16 +30799,16 @@
         <v>5</v>
       </c>
       <c r="BR91" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BS91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91" s="1">
         <v>2</v>
@@ -30883,16 +30883,16 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>26024</v>
+        <v>26025</v>
       </c>
       <c r="CU91" s="1">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CV91" s="1">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="CW91" s="1">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -34895,7 +34895,7 @@
         <v>14</v>
       </c>
       <c r="L105" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M105" s="2">
         <v>66</v>
@@ -35159,7 +35159,7 @@
         <v>31</v>
       </c>
       <c r="CV105" s="1">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="CW105" s="1">
         <v>500</v>
@@ -35786,10 +35786,10 @@
         <v>0</v>
       </c>
       <c r="D108" s="2">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2">
         <v>4</v>
-      </c>
-      <c r="E108" s="2">
-        <v>6</v>
       </c>
       <c r="F108" s="1">
         <v>37</v>
@@ -35798,7 +35798,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I108" s="2">
         <v>3</v>
@@ -36074,10 +36074,10 @@
         <v>2</v>
       </c>
       <c r="CV108" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CW108" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36435,7 +36435,7 @@
         <v>21</v>
       </c>
       <c r="Q110" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R110" s="1">
         <v>0</v>
@@ -36687,7 +36687,7 @@
         <v>452</v>
       </c>
       <c r="CW110" s="1">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -38352,16 +38352,16 @@
         <v>2</v>
       </c>
       <c r="AT116" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AU116" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV116" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW116" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX116" s="1">
         <v>4</v>
@@ -38508,16 +38508,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21819</v>
+        <v>21820</v>
       </c>
       <c r="CU116" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CV116" s="1">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="CW116" s="1">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38555,7 +38555,7 @@
         <v>3</v>
       </c>
       <c r="L117" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M117" s="2">
         <v>22</v>
@@ -38819,7 +38819,7 @@
         <v>213</v>
       </c>
       <c r="CV117" s="1">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="CW117" s="1">
         <v>1297</v>
@@ -39177,7 +39177,7 @@
         <v>0</v>
       </c>
       <c r="P119" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q119" s="2">
         <v>5</v>
@@ -39429,7 +39429,7 @@
         <v>3</v>
       </c>
       <c r="CV119" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CW119" s="1">
         <v>27</v>
@@ -41575,16 +41575,16 @@
         <v>226</v>
       </c>
       <c r="B127" s="1">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C127" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D127" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E127" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -41863,16 +41863,16 @@
         <v>0</v>
       </c>
       <c r="CT127" s="1">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="CU127" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV127" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CW127" s="1">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -45974,7 +45974,7 @@
         <v>2</v>
       </c>
       <c r="AS141" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT141" s="1">
         <v>0</v>
@@ -46118,7 +46118,7 @@
         <v>2</v>
       </c>
       <c r="CO141" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP141" s="1">
         <v>0</v>
@@ -46142,7 +46142,7 @@
         <v>15</v>
       </c>
       <c r="CW141" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -50938,7 +50938,7 @@
         <v>0</v>
       </c>
       <c r="BU157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV157" s="1">
         <v>5</v>
@@ -51022,7 +51022,7 @@
         <v>5247</v>
       </c>
       <c r="CW157" s="1">
-        <v>9196</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51204,7 +51204,7 @@
         <v>0</v>
       </c>
       <c r="BH158" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI158" s="2">
         <v>5</v>
@@ -51324,7 +51324,7 @@
         <v>242</v>
       </c>
       <c r="CV158" s="1">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="CW158" s="1">
         <v>1717</v>
@@ -52881,7 +52881,7 @@
         <v>3</v>
       </c>
       <c r="I164" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J164" s="1">
         <v>100</v>
@@ -52893,7 +52893,7 @@
         <v>12</v>
       </c>
       <c r="M164" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N164" s="1">
         <v>249</v>
@@ -53157,7 +53157,7 @@
         <v>100</v>
       </c>
       <c r="CW164" s="1">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -57322,16 +57322,16 @@
         <v>0</v>
       </c>
       <c r="BN178" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BO178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR178" s="1">
         <v>7</v>
@@ -57418,16 +57418,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>84918</v>
+        <v>84919</v>
       </c>
       <c r="CU178" s="1">
-        <v>-309</v>
+        <v>-308</v>
       </c>
       <c r="CV178" s="1">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="CW178" s="1">
-        <v>4592</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57998,7 +57998,7 @@
         <v>11</v>
       </c>
       <c r="CJ180" s="2">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="CK180" s="2">
         <v>103</v>
@@ -58034,7 +58034,7 @@
         <v>87</v>
       </c>
       <c r="CV180" s="1">
-        <v>1234</v>
+        <v>1219</v>
       </c>
       <c r="CW180" s="1">
         <v>2739</v>
@@ -63876,16 +63876,16 @@
         <v>98</v>
       </c>
       <c r="N200" s="1">
-        <v>7999</v>
+        <v>7998</v>
       </c>
       <c r="O200" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P200" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q200" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R200" s="1">
         <v>0</v>
@@ -63933,7 +63933,7 @@
         <v>14</v>
       </c>
       <c r="AG200" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AH200" s="1">
         <v>17</v>
@@ -64128,16 +64128,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16357</v>
+        <v>16356</v>
       </c>
       <c r="CU200" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CV200" s="1">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="CW200" s="1">
-        <v>527</v>
+        <v>519</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64145,16 +64145,16 @@
         <v>300</v>
       </c>
       <c r="B201" s="1">
-        <v>8407</v>
+        <v>8573</v>
       </c>
       <c r="C201" s="2">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D201" s="2">
-        <v>-1</v>
+        <v>165</v>
       </c>
       <c r="E201" s="2">
-        <v>-2</v>
+        <v>164</v>
       </c>
       <c r="F201" s="1">
         <v>0</v>
@@ -64433,16 +64433,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88131</v>
+        <v>88297</v>
       </c>
       <c r="CU201" s="1">
-        <v>55</v>
+        <v>221</v>
       </c>
       <c r="CV201" s="1">
-        <v>2005</v>
+        <v>2171</v>
       </c>
       <c r="CW201" s="1">
-        <v>3163</v>
+        <v>3329</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -65883,7 +65883,7 @@
         <v>2</v>
       </c>
       <c r="BU206" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV206" s="1">
         <v>3</v>
@@ -65967,7 +65967,7 @@
         <v>28</v>
       </c>
       <c r="CW206" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66047,16 +66047,16 @@
         <v>1</v>
       </c>
       <c r="Z207" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AA207" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB207" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC207" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD207" s="1">
         <v>2320</v>
@@ -66263,16 +66263,16 @@
         <v>0</v>
       </c>
       <c r="CT207" s="1">
-        <v>14091</v>
+        <v>14094</v>
       </c>
       <c r="CU207" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="CV207" s="1">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="CW207" s="1">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -67010,16 +67010,16 @@
         <v>1</v>
       </c>
       <c r="AP210" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AQ210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR210" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS210" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT210" s="1">
         <v>0</v>
@@ -67178,16 +67178,16 @@
         <v>0</v>
       </c>
       <c r="CT210" s="1">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="CU210" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV210" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW210" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67321,7 +67321,7 @@
         <v>1</v>
       </c>
       <c r="AR211" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS211" s="2">
         <v>5</v>
@@ -67453,7 +67453,7 @@
         <v>12</v>
       </c>
       <c r="CJ211" s="2">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="CK211" s="2">
         <v>116</v>
@@ -67489,7 +67489,7 @@
         <v>32</v>
       </c>
       <c r="CV211" s="1">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="CW211" s="1">
         <v>700</v>
@@ -69057,7 +69057,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E32" t="s">
         <v>716</v>
@@ -69537,7 +69537,7 @@
         <v>576</v>
       </c>
       <c r="D56">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
         <v>716</v>
@@ -69600,7 +69600,7 @@
         <v>579</v>
       </c>
       <c r="D59">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
         <v>716</v>
@@ -69900,7 +69900,7 @@
         <v>594</v>
       </c>
       <c r="D74">
-        <v>2232</v>
+        <v>2237</v>
       </c>
       <c r="E74" t="s">
         <v>716</v>
@@ -70746,7 +70746,7 @@
         <v>631</v>
       </c>
       <c r="D116">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E116" t="s">
         <v>716</v>
@@ -72358,7 +72358,7 @@
         <v>699</v>
       </c>
       <c r="D196">
-        <v>10257</v>
+        <v>10258</v>
       </c>
       <c r="E196" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4975,16 +4975,16 @@
         <v>106</v>
       </c>
       <c r="B7" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <v>29</v>
@@ -5263,16 +5263,16 @@
         <v>0</v>
       </c>
       <c r="CT7" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CU7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CV7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CW7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:101">
@@ -7747,7 +7747,7 @@
         <v>116</v>
       </c>
       <c r="K16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2">
         <v>2</v>
@@ -8011,7 +8011,7 @@
         <v>974</v>
       </c>
       <c r="CU16" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV16" s="1">
         <v>23</v>
@@ -12603,7 +12603,7 @@
         <v>2635</v>
       </c>
       <c r="C32" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D32" s="2">
         <v>54</v>
@@ -12891,7 +12891,7 @@
         <v>11145</v>
       </c>
       <c r="CU32" s="1">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="CV32" s="1">
         <v>224</v>
@@ -12908,7 +12908,7 @@
         <v>79</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="2">
         <v>11</v>
@@ -13196,7 +13196,7 @@
         <v>116</v>
       </c>
       <c r="CU33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV33" s="1">
         <v>15</v>
@@ -16266,7 +16266,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E44" s="2">
         <v>19</v>
@@ -16290,7 +16290,7 @@
         <v>18</v>
       </c>
       <c r="L44" s="2">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="M44" s="2">
         <v>107</v>
@@ -16470,7 +16470,7 @@
         <v>1</v>
       </c>
       <c r="BT44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU44" s="2">
         <v>2</v>
@@ -16554,7 +16554,7 @@
         <v>29</v>
       </c>
       <c r="CV44" s="1">
-        <v>1968</v>
+        <v>1948</v>
       </c>
       <c r="CW44" s="1">
         <v>2457</v>
@@ -18252,7 +18252,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE50" s="2">
         <v>1</v>
@@ -18384,7 +18384,7 @@
         <v>2</v>
       </c>
       <c r="CV50" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CW50" s="1">
         <v>73</v>
@@ -23595,7 +23595,7 @@
         <v>21</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
         <v>1</v>
@@ -23871,7 +23871,7 @@
         <v>2133</v>
       </c>
       <c r="CU68" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV68" s="1">
         <v>6</v>
@@ -26580,7 +26580,7 @@
         <v>7365</v>
       </c>
       <c r="CI77" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="CJ77" s="2">
         <v>334</v>
@@ -26616,7 +26616,7 @@
         <v>390977</v>
       </c>
       <c r="CU77" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="CV77" s="1">
         <v>10182</v>
@@ -27073,7 +27073,7 @@
         <v>1</v>
       </c>
       <c r="AV79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW79" s="2">
         <v>4</v>
@@ -27229,7 +27229,7 @@
         <v>72</v>
       </c>
       <c r="CV79" s="1">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="CW79" s="1">
         <v>1899</v>
@@ -27785,16 +27785,16 @@
         <v>0</v>
       </c>
       <c r="CD81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH81" s="1">
         <v>157</v>
@@ -27833,16 +27833,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6423</v>
+        <v>6424</v>
       </c>
       <c r="CU81" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CV81" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="CW81" s="1">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -34976,7 +34976,7 @@
         <v>41</v>
       </c>
       <c r="AM105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN105" s="2">
         <v>1</v>
@@ -35015,7 +35015,7 @@
         <v>0</v>
       </c>
       <c r="AZ105" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA105" s="2">
         <v>2</v>
@@ -35120,7 +35120,7 @@
         <v>281</v>
       </c>
       <c r="CI105" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CJ105" s="2">
         <v>10</v>
@@ -35156,10 +35156,10 @@
         <v>8004</v>
       </c>
       <c r="CU105" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="CV105" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="CW105" s="1">
         <v>500</v>
@@ -36417,7 +36417,7 @@
         <v>4995</v>
       </c>
       <c r="K110" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L110" s="2">
         <v>239</v>
@@ -36681,7 +36681,7 @@
         <v>13438</v>
       </c>
       <c r="CU110" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CV110" s="1">
         <v>452</v>
@@ -41578,7 +41578,7 @@
         <v>1083</v>
       </c>
       <c r="C127" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D127" s="2">
         <v>22</v>
@@ -41866,7 +41866,7 @@
         <v>2594</v>
       </c>
       <c r="CU127" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CV127" s="1">
         <v>51</v>
@@ -41895,7 +41895,7 @@
         <v>40</v>
       </c>
       <c r="G128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="2">
         <v>3</v>
@@ -42000,16 +42000,16 @@
         <v>2</v>
       </c>
       <c r="AP128" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AQ128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS128" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT128" s="1">
         <v>0</v>
@@ -42144,16 +42144,16 @@
         <v>2</v>
       </c>
       <c r="CL128" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="CM128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP128" s="1">
         <v>0</v>
@@ -42168,16 +42168,16 @@
         <v>0</v>
       </c>
       <c r="CT128" s="1">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="CU128" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV128" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CW128" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:101">
@@ -44572,16 +44572,16 @@
         <v>0</v>
       </c>
       <c r="CH136" s="1">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="CI136" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CJ136" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CK136" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL136" s="1">
         <v>13</v>
@@ -44608,16 +44608,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158875</v>
+        <v>158876</v>
       </c>
       <c r="CU136" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV136" s="1">
-        <v>5080</v>
+        <v>5081</v>
       </c>
       <c r="CW136" s="1">
-        <v>6083</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -52872,28 +52872,28 @@
         <v>0</v>
       </c>
       <c r="F164" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G164" s="2">
         <v>1</v>
       </c>
       <c r="H164" s="2">
+        <v>4</v>
+      </c>
+      <c r="I164" s="2">
+        <v>6</v>
+      </c>
+      <c r="J164" s="1">
+        <v>103</v>
+      </c>
+      <c r="K164" s="2">
         <v>3</v>
       </c>
-      <c r="I164" s="2">
-        <v>5</v>
-      </c>
-      <c r="J164" s="1">
-        <v>100</v>
-      </c>
-      <c r="K164" s="2">
-        <v>6</v>
-      </c>
       <c r="L164" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M164" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N164" s="1">
         <v>249</v>
@@ -53148,16 +53148,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="CU164" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CV164" s="1">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CW164" s="1">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53710,16 +53710,16 @@
         <v>0</v>
       </c>
       <c r="CD166" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CE166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH166" s="1">
         <v>192</v>
@@ -53758,16 +53758,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="CU166" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV166" s="1">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="CW166" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -57740,16 +57740,16 @@
         <v>279</v>
       </c>
       <c r="B180" s="1">
-        <v>8113</v>
+        <v>8175</v>
       </c>
       <c r="C180" s="2">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D180" s="2">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="E180" s="2">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -58028,16 +58028,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51226</v>
+        <v>51288</v>
       </c>
       <c r="CU180" s="1">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="CV180" s="1">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="CW180" s="1">
-        <v>2739</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -61203,16 +61203,16 @@
         <v>0</v>
       </c>
       <c r="AL191" s="1">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN191" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO191" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP191" s="1">
         <v>37</v>
@@ -61383,16 +61383,16 @@
         <v>0</v>
       </c>
       <c r="CT191" s="1">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="CU191" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV191" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW191" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="192" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4685,13 +4685,13 @@
         <v>42</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -4961,13 +4961,13 @@
         <v>2278</v>
       </c>
       <c r="CU6" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="CV6" s="1">
         <v>81</v>
       </c>
       <c r="CW6" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -5879,7 +5879,7 @@
         <v>13</v>
       </c>
       <c r="CV9" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CW9" s="1">
         <v>101</v>
@@ -7155,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14" s="1">
         <v>2</v>
@@ -7407,7 +7407,7 @@
         <v>109</v>
       </c>
       <c r="CW14" s="1">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7496,7 +7496,7 @@
         <v>3</v>
       </c>
       <c r="AC15" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -7712,7 +7712,7 @@
         <v>181</v>
       </c>
       <c r="CW15" s="1">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -7810,7 +7810,7 @@
         <v>0</v>
       </c>
       <c r="AF16" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="2">
         <v>8</v>
@@ -8014,7 +8014,7 @@
         <v>10</v>
       </c>
       <c r="CV16" s="1">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="CW16" s="1">
         <v>76</v>
@@ -8985,7 +8985,7 @@
         <v>226</v>
       </c>
       <c r="Q20" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>383</v>
       </c>
       <c r="CW20" s="1">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="2">
         <v>23</v>
@@ -10149,7 +10149,7 @@
         <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CW23" s="1">
         <v>45</v>
@@ -11090,7 +11090,7 @@
         <v>67</v>
       </c>
       <c r="G27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2">
         <v>3</v>
@@ -11366,7 +11366,7 @@
         <v>554</v>
       </c>
       <c r="CU27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV27" s="1">
         <v>31</v>
@@ -13417,7 +13417,7 @@
         <v>17</v>
       </c>
       <c r="BS34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT34" s="2">
         <v>1</v>
@@ -13501,7 +13501,7 @@
         <v>2588</v>
       </c>
       <c r="CU34" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV34" s="1">
         <v>59</v>
@@ -14559,7 +14559,7 @@
         <v>3</v>
       </c>
       <c r="AS38" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT38" s="1">
         <v>0</v>
@@ -14703,7 +14703,7 @@
         <v>3</v>
       </c>
       <c r="CO38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP38" s="1">
         <v>0</v>
@@ -14727,7 +14727,7 @@
         <v>44</v>
       </c>
       <c r="CW38" s="1">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -16395,7 +16395,7 @@
         <v>32</v>
       </c>
       <c r="AU44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV44" s="2">
         <v>1</v>
@@ -16551,7 +16551,7 @@
         <v>50664</v>
       </c>
       <c r="CU44" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CV44" s="1">
         <v>1948</v>
@@ -20880,7 +20880,7 @@
         <v>8</v>
       </c>
       <c r="Q59" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -20964,7 +20964,7 @@
         <v>1</v>
       </c>
       <c r="AS59" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -21048,7 +21048,7 @@
         <v>2</v>
       </c>
       <c r="BU59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV59" s="1">
         <v>0</v>
@@ -21108,7 +21108,7 @@
         <v>0</v>
       </c>
       <c r="CO59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP59" s="1">
         <v>0</v>
@@ -21132,7 +21132,7 @@
         <v>40</v>
       </c>
       <c r="CW59" s="1">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -21448,13 +21448,13 @@
         <v>6491</v>
       </c>
       <c r="C61" s="2">
-        <v>-40</v>
+        <v>-21</v>
       </c>
       <c r="D61" s="2">
         <v>191</v>
       </c>
       <c r="E61" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21736,13 +21736,13 @@
         <v>65926</v>
       </c>
       <c r="CU61" s="1">
-        <v>-22</v>
+        <v>-3</v>
       </c>
       <c r="CV61" s="1">
         <v>436</v>
       </c>
       <c r="CW61" s="1">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="AR63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS63" s="2">
         <v>6</v>
@@ -22313,7 +22313,7 @@
         <v>0</v>
       </c>
       <c r="CJ63" s="2">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="CK63" s="2">
         <v>45</v>
@@ -22349,7 +22349,7 @@
         <v>9</v>
       </c>
       <c r="CV63" s="1">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="CW63" s="1">
         <v>170</v>
@@ -22447,13 +22447,13 @@
         <v>2002</v>
       </c>
       <c r="AE64" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF64" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AG64" s="2">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22651,13 +22651,13 @@
         <v>8032</v>
       </c>
       <c r="CU64" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV64" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CW64" s="1">
-        <v>471</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -25671,7 +25671,7 @@
         <v>188</v>
       </c>
       <c r="CK74" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>1818</v>
       </c>
       <c r="CW74" s="1">
-        <v>4425</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26062,7 +26062,7 @@
         <v>4</v>
       </c>
       <c r="P76" s="2">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="Q76" s="2">
         <v>2419</v>
@@ -26194,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="BH76" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BI76" s="2">
         <v>36</v>
@@ -26314,7 +26314,7 @@
         <v>127</v>
       </c>
       <c r="CV76" s="1">
-        <v>1349</v>
+        <v>1308</v>
       </c>
       <c r="CW76" s="1">
         <v>3755</v>
@@ -26583,7 +26583,7 @@
         <v>68</v>
       </c>
       <c r="CJ77" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="CK77" s="2">
         <v>586</v>
@@ -26619,7 +26619,7 @@
         <v>101</v>
       </c>
       <c r="CV77" s="1">
-        <v>10182</v>
+        <v>10180</v>
       </c>
       <c r="CW77" s="1">
         <v>15918</v>
@@ -28894,7 +28894,7 @@
         <v>2</v>
       </c>
       <c r="AS85" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT85" s="1">
         <v>0</v>
@@ -29026,7 +29026,7 @@
         <v>24</v>
       </c>
       <c r="CK85" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="CL85" s="1">
         <v>0</v>
@@ -29062,7 +29062,7 @@
         <v>29</v>
       </c>
       <c r="CW85" s="1">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -30111,7 +30111,7 @@
         <v>1</v>
       </c>
       <c r="AR89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS89" s="2">
         <v>6</v>
@@ -30243,7 +30243,7 @@
         <v>6</v>
       </c>
       <c r="CJ89" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CK89" s="2">
         <v>16</v>
@@ -30279,7 +30279,7 @@
         <v>60</v>
       </c>
       <c r="CV89" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="CW89" s="1">
         <v>256</v>
@@ -32141,7 +32141,7 @@
         <v>2</v>
       </c>
       <c r="I96" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J96" s="1">
         <v>2</v>
@@ -32417,7 +32417,7 @@
         <v>2</v>
       </c>
       <c r="CW96" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -34160,7 +34160,7 @@
         <v>0</v>
       </c>
       <c r="BT102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU102" s="2">
         <v>1</v>
@@ -34244,7 +34244,7 @@
         <v>116</v>
       </c>
       <c r="CV102" s="1">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="CW102" s="1">
         <v>1725</v>
@@ -35371,7 +35371,7 @@
         <v>0</v>
       </c>
       <c r="BQ106" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BR106" s="1">
         <v>4</v>
@@ -35467,7 +35467,7 @@
         <v>1022</v>
       </c>
       <c r="CW106" s="1">
-        <v>2474</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36393,7 +36393,7 @@
         <v>2498</v>
       </c>
       <c r="C110" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D110" s="2">
         <v>49</v>
@@ -36681,7 +36681,7 @@
         <v>13438</v>
       </c>
       <c r="CU110" s="1">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="CV110" s="1">
         <v>452</v>
@@ -37195,7 +37195,7 @@
         <v>153</v>
       </c>
       <c r="BO112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP112" s="2">
         <v>2</v>
@@ -37291,7 +37291,7 @@
         <v>8297</v>
       </c>
       <c r="CU112" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV112" s="1">
         <v>263</v>
@@ -38226,7 +38226,7 @@
         <v>6</v>
       </c>
       <c r="D116" s="2">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E116" s="2">
         <v>111</v>
@@ -38514,7 +38514,7 @@
         <v>79</v>
       </c>
       <c r="CV116" s="1">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="CW116" s="1">
         <v>1157</v>
@@ -39551,7 +39551,7 @@
         <v>114</v>
       </c>
       <c r="AM120" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN120" s="2">
         <v>19</v>
@@ -39695,7 +39695,7 @@
         <v>127</v>
       </c>
       <c r="CI120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ120" s="2">
         <v>16</v>
@@ -39731,7 +39731,7 @@
         <v>384</v>
       </c>
       <c r="CU120" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CV120" s="1">
         <v>36</v>
@@ -40481,7 +40481,7 @@
         <v>0</v>
       </c>
       <c r="AR123" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS123" s="2">
         <v>6</v>
@@ -40625,7 +40625,7 @@
         <v>0</v>
       </c>
       <c r="CN123" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO123" s="2">
         <v>6</v>
@@ -40649,7 +40649,7 @@
         <v>2</v>
       </c>
       <c r="CV123" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW123" s="1">
         <v>30</v>
@@ -43713,7 +43713,7 @@
         <v>321</v>
       </c>
       <c r="C134" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D134" s="2">
         <v>8</v>
@@ -44001,7 +44001,7 @@
         <v>134463</v>
       </c>
       <c r="CU134" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="CV134" s="1">
         <v>2538</v>
@@ -44045,7 +44045,7 @@
         <v>57</v>
       </c>
       <c r="L135" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M135" s="2">
         <v>438</v>
@@ -44309,7 +44309,7 @@
         <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="CW135" s="1">
         <v>2691</v>
@@ -44395,7 +44395,7 @@
         <v>52</v>
       </c>
       <c r="AA136" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB136" s="2">
         <v>6</v>
@@ -44611,7 +44611,7 @@
         <v>158876</v>
       </c>
       <c r="CU136" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CV136" s="1">
         <v>5081</v>
@@ -44748,7 +44748,7 @@
         <v>64</v>
       </c>
       <c r="AQ137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR137" s="2">
         <v>2</v>
@@ -44892,7 +44892,7 @@
         <v>43</v>
       </c>
       <c r="CM137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN137" s="2">
         <v>2</v>
@@ -44916,7 +44916,7 @@
         <v>646</v>
       </c>
       <c r="CU137" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV137" s="1">
         <v>17</v>
@@ -46159,7 +46159,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F142" s="1">
         <v>15</v>
@@ -46447,7 +46447,7 @@
         <v>44</v>
       </c>
       <c r="CW142" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -52143,7 +52143,7 @@
         <v>0</v>
       </c>
       <c r="BP161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ161" s="2">
         <v>1</v>
@@ -52239,7 +52239,7 @@
         <v>31</v>
       </c>
       <c r="CV161" s="1">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CW161" s="1">
         <v>1252</v>
@@ -54254,7 +54254,7 @@
         <v>0</v>
       </c>
       <c r="BH168" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI168" s="2">
         <v>5</v>
@@ -54374,7 +54374,7 @@
         <v>27</v>
       </c>
       <c r="CV168" s="1">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="CW168" s="1">
         <v>579</v>
@@ -57340,7 +57340,7 @@
         <v>0</v>
       </c>
       <c r="BT178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU178" s="2">
         <v>1</v>
@@ -57424,7 +57424,7 @@
         <v>-308</v>
       </c>
       <c r="CV178" s="1">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="CW178" s="1">
         <v>4593</v>
@@ -58611,7 +58611,7 @@
         <v>18</v>
       </c>
       <c r="CK182" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="CL182" s="1">
         <v>0</v>
@@ -58647,7 +58647,7 @@
         <v>18</v>
       </c>
       <c r="CW182" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="183" spans="1:101">
@@ -59394,7 +59394,7 @@
         <v>3</v>
       </c>
       <c r="AS185" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT185" s="1">
         <v>0</v>
@@ -59538,7 +59538,7 @@
         <v>2</v>
       </c>
       <c r="CO185" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP185" s="1">
         <v>0</v>
@@ -59562,7 +59562,7 @@
         <v>9</v>
       </c>
       <c r="CW185" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -60291,7 +60291,7 @@
         <v>5</v>
       </c>
       <c r="AM188" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN188" s="2">
         <v>1</v>
@@ -60435,7 +60435,7 @@
         <v>64</v>
       </c>
       <c r="CI188" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ188" s="2">
         <v>24</v>
@@ -60471,7 +60471,7 @@
         <v>161</v>
       </c>
       <c r="CU188" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CV188" s="1">
         <v>27</v>
@@ -62133,7 +62133,7 @@
         <v>65</v>
       </c>
       <c r="AQ194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR194" s="2">
         <v>2</v>
@@ -62265,7 +62265,7 @@
         <v>449</v>
       </c>
       <c r="CI194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ194" s="2">
         <v>7</v>
@@ -62301,7 +62301,7 @@
         <v>32887</v>
       </c>
       <c r="CU194" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="CV194" s="1">
         <v>598</v>
@@ -62390,7 +62390,7 @@
         <v>45</v>
       </c>
       <c r="AA195" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB195" s="2">
         <v>6</v>
@@ -62606,7 +62606,7 @@
         <v>71201</v>
       </c>
       <c r="CU195" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CV195" s="1">
         <v>3370</v>
@@ -65679,7 +65679,7 @@
         <v>14</v>
       </c>
       <c r="E206" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F206" s="1">
         <v>9</v>
@@ -65967,7 +65967,7 @@
         <v>28</v>
       </c>
       <c r="CW206" s="1">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="1:101">
@@ -66236,7 +66236,7 @@
         <v>33</v>
       </c>
       <c r="CK207" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="CL207" s="1">
         <v>14</v>
@@ -66272,7 +66272,7 @@
         <v>353</v>
       </c>
       <c r="CW207" s="1">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="208" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -5612,7 +5612,7 @@
         <v>231</v>
       </c>
       <c r="K9" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2">
         <v>10</v>
@@ -5876,7 +5876,7 @@
         <v>2872</v>
       </c>
       <c r="CU9" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV9" s="1">
         <v>56</v>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="CW13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:101">
@@ -8985,7 +8985,7 @@
         <v>226</v>
       </c>
       <c r="Q20" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         <v>383</v>
       </c>
       <c r="CW20" s="1">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11084,7 +11084,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1">
         <v>67</v>
@@ -11372,7 +11372,7 @@
         <v>31</v>
       </c>
       <c r="CW27" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -12627,7 +12627,7 @@
         <v>842</v>
       </c>
       <c r="K32" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2">
         <v>53</v>
@@ -12891,7 +12891,7 @@
         <v>11145</v>
       </c>
       <c r="CU32" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="CV32" s="1">
         <v>224</v>
@@ -16353,7 +16353,7 @@
         <v>1836</v>
       </c>
       <c r="AG44" s="2">
-        <v>2219</v>
+        <v>1836</v>
       </c>
       <c r="AH44" s="1">
         <v>0</v>
@@ -16389,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="AS44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT44" s="1">
         <v>32</v>
@@ -16521,7 +16521,7 @@
         <v>16</v>
       </c>
       <c r="CK44" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CL44" s="1">
         <v>34</v>
@@ -16557,7 +16557,7 @@
         <v>1948</v>
       </c>
       <c r="CW44" s="1">
-        <v>2457</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -22453,7 +22453,7 @@
         <v>68</v>
       </c>
       <c r="AG64" s="2">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>179</v>
       </c>
       <c r="CW64" s="1">
-        <v>451</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22674,7 +22674,7 @@
         <v>47</v>
       </c>
       <c r="E65" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22830,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="BE65" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BF65" s="1">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>1771</v>
       </c>
       <c r="CW65" s="1">
-        <v>3535</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25413,7 +25413,7 @@
         <v>12674</v>
       </c>
       <c r="C74" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D74" s="2">
         <v>143</v>
@@ -25527,7 +25527,7 @@
         <v>109</v>
       </c>
       <c r="AO74" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,7 +25671,7 @@
         <v>188</v>
       </c>
       <c r="CK74" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,13 +25701,13 @@
         <v>171791</v>
       </c>
       <c r="CU74" s="1">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CV74" s="1">
         <v>1818</v>
       </c>
       <c r="CW74" s="1">
-        <v>4421</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26352,7 +26352,7 @@
         <v>4922</v>
       </c>
       <c r="K77" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L77" s="2">
         <v>181</v>
@@ -26406,7 +26406,7 @@
         <v>4</v>
       </c>
       <c r="AC77" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD77" s="1">
         <v>1182</v>
@@ -26586,7 +26586,7 @@
         <v>332</v>
       </c>
       <c r="CK77" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26616,13 +26616,13 @@
         <v>390977</v>
       </c>
       <c r="CU77" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="CV77" s="1">
         <v>10180</v>
       </c>
       <c r="CW77" s="1">
-        <v>15918</v>
+        <v>15912</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -28188,7 +28188,7 @@
         <v>174</v>
       </c>
       <c r="M83" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28452,7 +28452,7 @@
         <v>933</v>
       </c>
       <c r="CW83" s="1">
-        <v>5483</v>
+        <v>5484</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29749,7 +29749,7 @@
         <v>0</v>
       </c>
       <c r="Y88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="1">
         <v>0</v>
@@ -29977,7 +29977,7 @@
         <v>137</v>
       </c>
       <c r="CW88" s="1">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -32554,7 +32554,7 @@
         <v>1</v>
       </c>
       <c r="AS97" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT97" s="1">
         <v>0</v>
@@ -32686,7 +32686,7 @@
         <v>2</v>
       </c>
       <c r="CK97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32722,7 +32722,7 @@
         <v>5</v>
       </c>
       <c r="CW97" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -36399,7 +36399,7 @@
         <v>49</v>
       </c>
       <c r="E110" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36687,7 +36687,7 @@
         <v>452</v>
       </c>
       <c r="CW110" s="1">
-        <v>1055</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -38361,7 +38361,7 @@
         <v>8</v>
       </c>
       <c r="AW116" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX116" s="1">
         <v>4</v>
@@ -38517,7 +38517,7 @@
         <v>373</v>
       </c>
       <c r="CW116" s="1">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -46177,7 +46177,7 @@
         <v>445</v>
       </c>
       <c r="K142" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2">
         <v>20</v>
@@ -46441,7 +46441,7 @@
         <v>1656</v>
       </c>
       <c r="CU142" s="1">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="CV142" s="1">
         <v>44</v>
@@ -47804,7 +47804,7 @@
         <v>2</v>
       </c>
       <c r="AS147" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT147" s="1">
         <v>0</v>
@@ -47888,7 +47888,7 @@
         <v>1</v>
       </c>
       <c r="BU147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV147" s="1">
         <v>0</v>
@@ -47972,7 +47972,7 @@
         <v>15</v>
       </c>
       <c r="CW147" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -51111,7 +51111,7 @@
         <v>3</v>
       </c>
       <c r="AC158" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD158" s="1">
         <v>157</v>
@@ -51327,7 +51327,7 @@
         <v>835</v>
       </c>
       <c r="CW158" s="1">
-        <v>1717</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -54406,7 +54406,7 @@
         <v>3</v>
       </c>
       <c r="I169" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169" s="1">
         <v>0</v>
@@ -54682,7 +54682,7 @@
         <v>15</v>
       </c>
       <c r="CW169" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -61517,7 +61517,7 @@
         <v>0</v>
       </c>
       <c r="AO192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP192" s="1">
         <v>56</v>
@@ -61661,7 +61661,7 @@
         <v>2</v>
       </c>
       <c r="CK192" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61697,7 +61697,7 @@
         <v>5</v>
       </c>
       <c r="CW192" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62324,7 +62324,7 @@
         <v>5</v>
       </c>
       <c r="E195" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F195" s="1">
         <v>19</v>
@@ -62612,7 +62612,7 @@
         <v>3370</v>
       </c>
       <c r="CW195" s="1">
-        <v>5338</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="196" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -18656,7 +18656,7 @@
         <v>1795</v>
       </c>
       <c r="CK51" s="2">
-        <v>1930</v>
+        <v>1891</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18692,7 +18692,7 @@
         <v>2002</v>
       </c>
       <c r="CW51" s="1">
-        <v>2156</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -19424,7 +19424,7 @@
         <v>0</v>
       </c>
       <c r="AN54" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO54" s="2">
         <v>4</v>
@@ -19568,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="CJ54" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CK54" s="2">
         <v>22</v>
@@ -19604,7 +19604,7 @@
         <v>2</v>
       </c>
       <c r="CV54" s="1">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="CW54" s="1">
         <v>28</v>
@@ -21451,7 +21451,7 @@
         <v>-21</v>
       </c>
       <c r="D61" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E61" s="2">
         <v>240</v>
@@ -21739,7 +21739,7 @@
         <v>-3</v>
       </c>
       <c r="CV61" s="1">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="CW61" s="1">
         <v>916</v>
@@ -22453,7 +22453,7 @@
         <v>68</v>
       </c>
       <c r="AG64" s="2">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>179</v>
       </c>
       <c r="CW64" s="1">
-        <v>420</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22830,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="BE65" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BF65" s="1">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>1771</v>
       </c>
       <c r="CW65" s="1">
-        <v>3506</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23790,7 +23790,7 @@
         <v>1</v>
       </c>
       <c r="BT68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU68" s="2">
         <v>3</v>
@@ -23874,7 +23874,7 @@
         <v>3</v>
       </c>
       <c r="CV68" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CW68" s="1">
         <v>52</v>
@@ -26053,7 +26053,7 @@
         <v>178</v>
       </c>
       <c r="M76" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N76" s="1">
         <v>117545</v>
@@ -26317,7 +26317,7 @@
         <v>1308</v>
       </c>
       <c r="CW76" s="1">
-        <v>3755</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26355,7 +26355,7 @@
         <v>43</v>
       </c>
       <c r="L77" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M77" s="2">
         <v>324</v>
@@ -26370,7 +26370,7 @@
         <v>9556</v>
       </c>
       <c r="Q77" s="2">
-        <v>19095</v>
+        <v>19106</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>
@@ -26619,10 +26619,10 @@
         <v>102</v>
       </c>
       <c r="CV77" s="1">
-        <v>10180</v>
+        <v>10181</v>
       </c>
       <c r="CW77" s="1">
-        <v>15912</v>
+        <v>15923</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -28329,7 +28329,7 @@
         <v>0</v>
       </c>
       <c r="BH83" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BI83" s="2">
         <v>59</v>
@@ -28449,7 +28449,7 @@
         <v>174</v>
       </c>
       <c r="CV83" s="1">
-        <v>933</v>
+        <v>887</v>
       </c>
       <c r="CW83" s="1">
         <v>5484</v>
@@ -34088,7 +34088,7 @@
         <v>1</v>
       </c>
       <c r="AV102" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW102" s="2">
         <v>4</v>
@@ -34244,7 +34244,7 @@
         <v>116</v>
       </c>
       <c r="CV102" s="1">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="CW102" s="1">
         <v>1725</v>
@@ -34931,7 +34931,7 @@
         <v>0</v>
       </c>
       <c r="X105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y105" s="2">
         <v>1</v>
@@ -35159,7 +35159,7 @@
         <v>26</v>
       </c>
       <c r="CV105" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CW105" s="1">
         <v>500</v>
@@ -36396,7 +36396,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="2">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E110" s="2">
         <v>80</v>
@@ -36684,7 +36684,7 @@
         <v>102</v>
       </c>
       <c r="CV110" s="1">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="CW110" s="1">
         <v>1046</v>
@@ -37563,7 +37563,7 @@
         <v>2</v>
       </c>
       <c r="CJ113" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="CK113" s="2">
         <v>149</v>
@@ -37599,7 +37599,7 @@
         <v>1343</v>
       </c>
       <c r="CV113" s="1">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="CW113" s="1">
         <v>11148</v>
@@ -38418,7 +38418,7 @@
         <v>0</v>
       </c>
       <c r="BP116" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ116" s="2">
         <v>2</v>
@@ -38514,7 +38514,7 @@
         <v>79</v>
       </c>
       <c r="CV116" s="1">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="CW116" s="1">
         <v>1158</v>
@@ -39156,7 +39156,7 @@
         <v>3</v>
       </c>
       <c r="I119" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J119" s="1">
         <v>0</v>
@@ -39432,7 +39432,7 @@
         <v>10</v>
       </c>
       <c r="CW119" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -41901,7 +41901,7 @@
         <v>3</v>
       </c>
       <c r="I128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J128" s="1">
         <v>0</v>
@@ -42006,7 +42006,7 @@
         <v>1</v>
       </c>
       <c r="AR128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS128" s="2">
         <v>3</v>
@@ -42138,7 +42138,7 @@
         <v>0</v>
       </c>
       <c r="CJ128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK128" s="2">
         <v>2</v>
@@ -42174,10 +42174,10 @@
         <v>2</v>
       </c>
       <c r="CV128" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CW128" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:101">
@@ -47693,7 +47693,7 @@
         <v>2</v>
       </c>
       <c r="H147" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I147" s="2">
         <v>7</v>
@@ -47705,7 +47705,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="2">
         <v>2</v>
@@ -47717,7 +47717,7 @@
         <v>0</v>
       </c>
       <c r="P147" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="2">
         <v>6</v>
@@ -47885,7 +47885,7 @@
         <v>0</v>
       </c>
       <c r="BT147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU147" s="2">
         <v>1</v>
@@ -47936,7 +47936,7 @@
         <v>2</v>
       </c>
       <c r="CK147" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CL147" s="1">
         <v>25</v>
@@ -47969,10 +47969,10 @@
         <v>5</v>
       </c>
       <c r="CV147" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW147" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -49245,7 +49245,7 @@
         <v>15</v>
       </c>
       <c r="Q152" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R152" s="1">
         <v>1</v>
@@ -49269,7 +49269,7 @@
         <v>0</v>
       </c>
       <c r="Y152" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z152" s="1">
         <v>0</v>
@@ -49497,7 +49497,7 @@
         <v>89</v>
       </c>
       <c r="CW152" s="1">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50450,7 +50450,7 @@
         <v>13</v>
       </c>
       <c r="L156" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M156" s="2">
         <v>123</v>
@@ -50714,7 +50714,7 @@
         <v>45</v>
       </c>
       <c r="CV156" s="1">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="CW156" s="1">
         <v>2539</v>
@@ -50806,7 +50806,7 @@
         <v>3</v>
       </c>
       <c r="AC157" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD157" s="1">
         <v>138904</v>
@@ -50866,7 +50866,7 @@
         <v>1</v>
       </c>
       <c r="AW157" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX157" s="1">
         <v>4</v>
@@ -51022,7 +51022,7 @@
         <v>5247</v>
       </c>
       <c r="CW157" s="1">
-        <v>9195</v>
+        <v>9190</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -54125,7 +54125,7 @@
         <v>23</v>
       </c>
       <c r="Q168" s="2">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="R168" s="1">
         <v>0</v>
@@ -54149,7 +54149,7 @@
         <v>0</v>
       </c>
       <c r="Y168" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z168" s="1">
         <v>0</v>
@@ -54377,7 +54377,7 @@
         <v>154</v>
       </c>
       <c r="CW168" s="1">
-        <v>579</v>
+        <v>556</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54403,7 +54403,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2">
         <v>4</v>
@@ -54679,7 +54679,7 @@
         <v>1</v>
       </c>
       <c r="CV169" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW169" s="1">
         <v>59</v>
@@ -57830,7 +57830,7 @@
         <v>0</v>
       </c>
       <c r="AF180" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG180" s="2">
         <v>17</v>
@@ -58034,7 +58034,7 @@
         <v>149</v>
       </c>
       <c r="CV180" s="1">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="CW180" s="1">
         <v>2801</v>
@@ -62139,7 +62139,7 @@
         <v>2</v>
       </c>
       <c r="AS194" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT194" s="1">
         <v>2</v>
@@ -62271,7 +62271,7 @@
         <v>7</v>
       </c>
       <c r="CK194" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CL194" s="1">
         <v>27</v>
@@ -62307,7 +62307,7 @@
         <v>598</v>
       </c>
       <c r="CW194" s="1">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -63978,7 +63978,7 @@
         <v>0</v>
       </c>
       <c r="AV200" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW200" s="2">
         <v>5</v>
@@ -63990,7 +63990,7 @@
         <v>0</v>
       </c>
       <c r="AZ200" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA200" s="2">
         <v>7</v>
@@ -64134,7 +64134,7 @@
         <v>66</v>
       </c>
       <c r="CV200" s="1">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="CW200" s="1">
         <v>519</v>
@@ -66702,7 +66702,7 @@
         <v>7</v>
       </c>
       <c r="AO209" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP209" s="1">
         <v>0</v>
@@ -66846,7 +66846,7 @@
         <v>39</v>
       </c>
       <c r="CK209" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="CL209" s="1">
         <v>0</v>
@@ -66882,7 +66882,7 @@
         <v>65</v>
       </c>
       <c r="CW209" s="1">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="210" spans="1:101">
@@ -69880,7 +69880,7 @@
         <v>593</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" t="s">
         <v>716</v>
@@ -69900,7 +69900,7 @@
         <v>594</v>
       </c>
       <c r="D74">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="E74" t="s">
         <v>716</v>
@@ -69940,7 +69940,7 @@
         <v>596</v>
       </c>
       <c r="D76">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="E76" t="s">
         <v>716</v>
@@ -70000,7 +70000,7 @@
         <v>599</v>
       </c>
       <c r="D79">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -1409,7 +1409,7 @@
     <t>Office of the Privacy Commissioner of Canada | Commissariat à la protection de la vie privée du Canada</t>
   </si>
   <si>
-    <t>Old Port of Montreal Corporation Inc. | Société du Vieux-Port de Montréal Inc.</t>
+    <t xml:space="preserve">SITES Canada Inc.  | SITES Canada Inc. </t>
   </si>
   <si>
     <t>Law Commission of Canada | Commission du droit du Canada</t>
@@ -3842,7 +3842,7 @@
         <v>18286</v>
       </c>
       <c r="AE3" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="2">
         <v>293</v>
@@ -4046,7 +4046,7 @@
         <v>46743</v>
       </c>
       <c r="CU3" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="CV3" s="1">
         <v>867</v>
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="BT5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU5" s="2">
         <v>2</v>
@@ -4659,7 +4659,7 @@
         <v>22</v>
       </c>
       <c r="CV5" s="1">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="CW5" s="1">
         <v>815</v>
@@ -7221,7 +7221,7 @@
         <v>34</v>
       </c>
       <c r="AM14" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="2">
         <v>9</v>
@@ -7233,7 +7233,7 @@
         <v>77</v>
       </c>
       <c r="AQ14" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AR14" s="2">
         <v>20</v>
@@ -7365,7 +7365,7 @@
         <v>194</v>
       </c>
       <c r="CI14" s="2">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="CJ14" s="2">
         <v>74</v>
@@ -7401,7 +7401,7 @@
         <v>3164</v>
       </c>
       <c r="CU14" s="1">
-        <v>67</v>
+        <v>-19</v>
       </c>
       <c r="CV14" s="1">
         <v>109</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="BP20" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ20" s="2">
         <v>2</v>
-      </c>
-      <c r="BQ20" s="2">
-        <v>8</v>
       </c>
       <c r="BR20" s="1">
         <v>13</v>
@@ -9234,10 +9234,10 @@
         <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="CW20" s="1">
-        <v>956</v>
+        <v>950</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -10720,7 +10720,7 @@
         <v>48</v>
       </c>
       <c r="CI25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ25" s="2">
         <v>11</v>
@@ -10756,7 +10756,7 @@
         <v>110</v>
       </c>
       <c r="CU25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV25" s="1">
         <v>11</v>
@@ -11416,16 +11416,16 @@
         <v>74</v>
       </c>
       <c r="N28" s="1">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="O28" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P28" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q28" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="CT28" s="1">
-        <v>24090</v>
+        <v>24098</v>
       </c>
       <c r="CU28" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="CV28" s="1">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="CW28" s="1">
-        <v>755</v>
+        <v>763</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12328,7 +12328,7 @@
         <v>25</v>
       </c>
       <c r="M31" s="2">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="N31" s="1">
         <v>1982</v>
@@ -12592,7 +12592,7 @@
         <v>265</v>
       </c>
       <c r="CW31" s="1">
-        <v>425</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12630,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="2">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M32" s="2">
         <v>100</v>
@@ -12894,7 +12894,7 @@
         <v>20</v>
       </c>
       <c r="CV32" s="1">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="CW32" s="1">
         <v>556</v>
@@ -13225,7 +13225,7 @@
         <v>64</v>
       </c>
       <c r="G34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>4</v>
@@ -13501,7 +13501,7 @@
         <v>2588</v>
       </c>
       <c r="CU34" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV34" s="1">
         <v>59</v>
@@ -14436,7 +14436,7 @@
         <v>2</v>
       </c>
       <c r="D38" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="2">
         <v>9</v>
@@ -14724,7 +14724,7 @@
         <v>10</v>
       </c>
       <c r="CV38" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="CW38" s="1">
         <v>119</v>
@@ -15360,7 +15360,7 @@
         <v>47</v>
       </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
@@ -15456,7 +15456,7 @@
         <v>76</v>
       </c>
       <c r="AM41" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AN41" s="2">
         <v>7</v>
@@ -15600,7 +15600,7 @@
         <v>528</v>
       </c>
       <c r="CI41" s="2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="CJ41" s="2">
         <v>25</v>
@@ -15636,7 +15636,7 @@
         <v>692</v>
       </c>
       <c r="CU41" s="1">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="CV41" s="1">
         <v>34</v>
@@ -18090,16 +18090,16 @@
         <v>149</v>
       </c>
       <c r="B50" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="1">
         <v>53</v>
@@ -18378,16 +18378,16 @@
         <v>0</v>
       </c>
       <c r="CT50" s="1">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="CU50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV50" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CW50" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -20551,7 +20551,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20659,7 +20659,7 @@
         <v>2</v>
       </c>
       <c r="AS58" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT58" s="1">
         <v>0</v>
@@ -20791,7 +20791,7 @@
         <v>6</v>
       </c>
       <c r="CK58" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CL58" s="1">
         <v>19</v>
@@ -20827,7 +20827,7 @@
         <v>18</v>
       </c>
       <c r="CW58" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -21448,7 +21448,7 @@
         <v>6491</v>
       </c>
       <c r="C61" s="2">
-        <v>-21</v>
+        <v>-11</v>
       </c>
       <c r="D61" s="2">
         <v>171</v>
@@ -21736,7 +21736,7 @@
         <v>65926</v>
       </c>
       <c r="CU61" s="1">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="CV61" s="1">
         <v>416</v>
@@ -22453,7 +22453,7 @@
         <v>68</v>
       </c>
       <c r="AG64" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>179</v>
       </c>
       <c r="CW64" s="1">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22671,7 +22671,7 @@
         <v>14</v>
       </c>
       <c r="D65" s="2">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E65" s="2">
         <v>79</v>
@@ -22959,7 +22959,7 @@
         <v>33</v>
       </c>
       <c r="CV65" s="1">
-        <v>1771</v>
+        <v>1753</v>
       </c>
       <c r="CW65" s="1">
         <v>3500</v>
@@ -24959,7 +24959,7 @@
         <v>3</v>
       </c>
       <c r="BC72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD72" s="2">
         <v>2</v>
@@ -25091,7 +25091,7 @@
         <v>519</v>
       </c>
       <c r="CU72" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CV72" s="1">
         <v>47</v>
@@ -25261,16 +25261,16 @@
         <v>0</v>
       </c>
       <c r="BB73" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF73" s="1">
         <v>0</v>
@@ -25393,16 +25393,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="CU73" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV73" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CW73" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25668,7 +25668,7 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="CK74" s="2">
         <v>414</v>
@@ -25704,7 +25704,7 @@
         <v>177</v>
       </c>
       <c r="CV74" s="1">
-        <v>1818</v>
+        <v>1804</v>
       </c>
       <c r="CW74" s="1">
         <v>4417</v>
@@ -26065,7 +26065,7 @@
         <v>908</v>
       </c>
       <c r="Q76" s="2">
-        <v>2419</v>
+        <v>2401</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26317,7 +26317,7 @@
         <v>1308</v>
       </c>
       <c r="CW76" s="1">
-        <v>3754</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26526,7 +26526,7 @@
         <v>13</v>
       </c>
       <c r="BQ77" s="2">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="BR77" s="1">
         <v>0</v>
@@ -26580,10 +26580,10 @@
         <v>7365</v>
       </c>
       <c r="CI77" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="CJ77" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="CK77" s="2">
         <v>584</v>
@@ -26616,13 +26616,13 @@
         <v>390977</v>
       </c>
       <c r="CU77" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="CV77" s="1">
-        <v>10181</v>
+        <v>10177</v>
       </c>
       <c r="CW77" s="1">
-        <v>15923</v>
+        <v>15912</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26648,7 +26648,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78" s="2">
         <v>5</v>
@@ -26924,7 +26924,7 @@
         <v>14</v>
       </c>
       <c r="CV78" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CW78" s="1">
         <v>124</v>
@@ -27019,16 +27019,16 @@
         <v>7</v>
       </c>
       <c r="AD79" s="1">
-        <v>8587</v>
+        <v>8588</v>
       </c>
       <c r="AE79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF79" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG79" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH79" s="1">
         <v>0</v>
@@ -27223,16 +27223,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90689</v>
+        <v>90690</v>
       </c>
       <c r="CU79" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CV79" s="1">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="CW79" s="1">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27785,16 +27785,16 @@
         <v>0</v>
       </c>
       <c r="CD81" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CE81" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CF81" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CG81" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CH81" s="1">
         <v>157</v>
@@ -27833,16 +27833,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6424</v>
+        <v>6432</v>
       </c>
       <c r="CU81" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="CV81" s="1">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="CW81" s="1">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28888,7 +28888,7 @@
         <v>25</v>
       </c>
       <c r="AQ85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR85" s="2">
         <v>2</v>
@@ -29020,7 +29020,7 @@
         <v>272</v>
       </c>
       <c r="CI85" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CJ85" s="2">
         <v>24</v>
@@ -29056,7 +29056,7 @@
         <v>408</v>
       </c>
       <c r="CU85" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="CV85" s="1">
         <v>29</v>
@@ -30078,7 +30078,7 @@
         <v>51</v>
       </c>
       <c r="AG89" s="2">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="AH89" s="1">
         <v>0</v>
@@ -30282,7 +30282,7 @@
         <v>89</v>
       </c>
       <c r="CW89" s="1">
-        <v>256</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -31247,7 +31247,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q93" s="2">
         <v>44</v>
@@ -31499,7 +31499,7 @@
         <v>2</v>
       </c>
       <c r="CV93" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CW93" s="1">
         <v>67</v>
@@ -34124,7 +34124,7 @@
         <v>0</v>
       </c>
       <c r="BH102" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BI102" s="2">
         <v>15</v>
@@ -34142,16 +34142,16 @@
         <v>0</v>
       </c>
       <c r="BN102" s="1">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="BO102" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BP102" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BQ102" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BR102" s="1">
         <v>2</v>
@@ -34238,16 +34238,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>43140</v>
+        <v>43148</v>
       </c>
       <c r="CU102" s="1">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="CV102" s="1">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="CW102" s="1">
-        <v>1725</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -35478,7 +35478,7 @@
         <v>35</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="2">
         <v>1</v>
@@ -35490,7 +35490,7 @@
         <v>69</v>
       </c>
       <c r="G107" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H107" s="2">
         <v>3</v>
@@ -35766,7 +35766,7 @@
         <v>104</v>
       </c>
       <c r="CU107" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV107" s="1">
         <v>4</v>
@@ -35795,7 +35795,7 @@
         <v>37</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2">
         <v>2</v>
@@ -36071,7 +36071,7 @@
         <v>944</v>
       </c>
       <c r="CU108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV108" s="1">
         <v>22</v>
@@ -36716,7 +36716,7 @@
         <v>2</v>
       </c>
       <c r="I111" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J111" s="1">
         <v>0</v>
@@ -36992,7 +36992,7 @@
         <v>30</v>
       </c>
       <c r="CW111" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37566,7 +37566,7 @@
         <v>61</v>
       </c>
       <c r="CK113" s="2">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37602,7 +37602,7 @@
         <v>1748</v>
       </c>
       <c r="CW113" s="1">
-        <v>11148</v>
+        <v>11124</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38361,7 +38361,7 @@
         <v>8</v>
       </c>
       <c r="AW116" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX116" s="1">
         <v>4</v>
@@ -38517,7 +38517,7 @@
         <v>371</v>
       </c>
       <c r="CW116" s="1">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38552,7 +38552,7 @@
         <v>335</v>
       </c>
       <c r="K117" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2">
         <v>4</v>
@@ -38567,7 +38567,7 @@
         <v>0</v>
       </c>
       <c r="P117" s="2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="2">
         <v>113</v>
@@ -38816,10 +38816,10 @@
         <v>13368</v>
       </c>
       <c r="CU117" s="1">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="CV117" s="1">
-        <v>607</v>
+        <v>581</v>
       </c>
       <c r="CW117" s="1">
         <v>1297</v>
@@ -39153,7 +39153,7 @@
         <v>1</v>
       </c>
       <c r="H119" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I119" s="2">
         <v>4</v>
@@ -39429,7 +39429,7 @@
         <v>3</v>
       </c>
       <c r="CV119" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW119" s="1">
         <v>26</v>
@@ -40475,16 +40475,16 @@
         <v>0</v>
       </c>
       <c r="AP123" s="1">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AQ123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR123" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS123" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT123" s="1">
         <v>0</v>
@@ -40565,7 +40565,7 @@
         <v>1</v>
       </c>
       <c r="BT123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU123" s="2">
         <v>2</v>
@@ -40619,16 +40619,16 @@
         <v>0</v>
       </c>
       <c r="CL123" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="CM123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN123" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO123" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CP123" s="1">
         <v>0</v>
@@ -40643,16 +40643,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="CU123" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV123" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW123" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -41689,7 +41689,7 @@
         <v>5</v>
       </c>
       <c r="AN127" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AO127" s="2">
         <v>33</v>
@@ -41833,7 +41833,7 @@
         <v>1</v>
       </c>
       <c r="CJ127" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CK127" s="2">
         <v>27</v>
@@ -41869,7 +41869,7 @@
         <v>9</v>
       </c>
       <c r="CV127" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="CW127" s="1">
         <v>108</v>
@@ -44102,7 +44102,7 @@
         <v>11790</v>
       </c>
       <c r="AE135" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF135" s="2">
         <v>159</v>
@@ -44306,7 +44306,7 @@
         <v>62762</v>
       </c>
       <c r="CU135" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="CV135" s="1">
         <v>981</v>
@@ -45582,7 +45582,7 @@
         <v>0</v>
       </c>
       <c r="P140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="2">
         <v>4</v>
@@ -45834,7 +45834,7 @@
         <v>3</v>
       </c>
       <c r="CV140" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW140" s="1">
         <v>24</v>
@@ -45887,7 +45887,7 @@
         <v>0</v>
       </c>
       <c r="P141" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="2">
         <v>8</v>
@@ -45968,10 +45968,10 @@
         <v>66</v>
       </c>
       <c r="AQ141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS141" s="2">
         <v>3</v>
@@ -46103,7 +46103,7 @@
         <v>0</v>
       </c>
       <c r="CJ141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK141" s="2">
         <v>2</v>
@@ -46112,7 +46112,7 @@
         <v>74</v>
       </c>
       <c r="CM141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN141" s="2">
         <v>2</v>
@@ -46136,10 +46136,10 @@
         <v>586</v>
       </c>
       <c r="CU141" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV141" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW141" s="1">
         <v>37</v>
@@ -46279,7 +46279,7 @@
         <v>1</v>
       </c>
       <c r="AS142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT142" s="1">
         <v>14</v>
@@ -46423,7 +46423,7 @@
         <v>0</v>
       </c>
       <c r="CO142" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP142" s="1">
         <v>0</v>
@@ -46447,7 +46447,7 @@
         <v>44</v>
       </c>
       <c r="CW142" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47690,7 +47690,7 @@
         <v>49</v>
       </c>
       <c r="G147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H147" s="2">
         <v>3</v>
@@ -47699,16 +47699,16 @@
         <v>7</v>
       </c>
       <c r="J147" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K147" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M147" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N147" s="1">
         <v>18</v>
@@ -47795,16 +47795,16 @@
         <v>1</v>
       </c>
       <c r="AP147" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AQ147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR147" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS147" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT147" s="1">
         <v>0</v>
@@ -47879,16 +47879,16 @@
         <v>0</v>
       </c>
       <c r="BR147" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV147" s="1">
         <v>0</v>
@@ -47915,16 +47915,16 @@
         <v>0</v>
       </c>
       <c r="CD147" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CE147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH147" s="1">
         <v>31</v>
@@ -47939,16 +47939,16 @@
         <v>2</v>
       </c>
       <c r="CL147" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CM147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN147" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO147" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP147" s="1">
         <v>0</v>
@@ -47963,16 +47963,16 @@
         <v>0</v>
       </c>
       <c r="CT147" s="1">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="CU147" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CV147" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW147" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48016,16 +48016,16 @@
         <v>34</v>
       </c>
       <c r="N148" s="1">
-        <v>3253</v>
+        <v>3255</v>
       </c>
       <c r="O148" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P148" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q148" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R148" s="1">
         <v>0</v>
@@ -48268,16 +48268,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>5611</v>
+        <v>5613</v>
       </c>
       <c r="CU148" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CV148" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CW148" s="1">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -49242,7 +49242,7 @@
         <v>0</v>
       </c>
       <c r="P152" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q152" s="2">
         <v>15</v>
@@ -49494,7 +49494,7 @@
         <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="CW152" s="1">
         <v>273</v>
@@ -51234,16 +51234,16 @@
         <v>0</v>
       </c>
       <c r="BR158" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BS158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU158" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV158" s="1">
         <v>0</v>
@@ -51318,16 +51318,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25703</v>
+        <v>25704</v>
       </c>
       <c r="CU158" s="1">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="CV158" s="1">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="CW158" s="1">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -52149,16 +52149,16 @@
         <v>1</v>
       </c>
       <c r="BR161" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BS161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU161" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV161" s="1">
         <v>0</v>
@@ -52233,16 +52233,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22410</v>
+        <v>22411</v>
       </c>
       <c r="CU161" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CV161" s="1">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="CW161" s="1">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52720,7 +52720,7 @@
         <v>0</v>
       </c>
       <c r="BE163" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BF163" s="1">
         <v>0</v>
@@ -52852,7 +52852,7 @@
         <v>20</v>
       </c>
       <c r="CW163" s="1">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -52878,7 +52878,7 @@
         <v>1</v>
       </c>
       <c r="H164" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I164" s="2">
         <v>6</v>
@@ -53154,7 +53154,7 @@
         <v>6</v>
       </c>
       <c r="CV164" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="CW164" s="1">
         <v>203</v>
@@ -54122,7 +54122,7 @@
         <v>0</v>
       </c>
       <c r="P168" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q168" s="2">
         <v>23</v>
@@ -54374,7 +54374,7 @@
         <v>27</v>
       </c>
       <c r="CV168" s="1">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="CW168" s="1">
         <v>556</v>
@@ -55013,7 +55013,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171" s="2">
         <v>1</v>
@@ -55025,7 +55025,7 @@
         <v>9</v>
       </c>
       <c r="L171" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M171" s="2">
         <v>26</v>
@@ -55037,7 +55037,7 @@
         <v>0</v>
       </c>
       <c r="P171" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q171" s="2">
         <v>40</v>
@@ -55289,7 +55289,7 @@
         <v>17</v>
       </c>
       <c r="CV171" s="1">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="CW171" s="1">
         <v>98</v>
@@ -55949,7 +55949,7 @@
         <v>202</v>
       </c>
       <c r="O174" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P174" s="2">
         <v>9</v>
@@ -56021,7 +56021,7 @@
         <v>9</v>
       </c>
       <c r="AM174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN174" s="2">
         <v>1</v>
@@ -56201,7 +56201,7 @@
         <v>488</v>
       </c>
       <c r="CU174" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="CV174" s="1">
         <v>23</v>
@@ -59388,7 +59388,7 @@
         <v>29</v>
       </c>
       <c r="AQ185" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR185" s="2">
         <v>3</v>
@@ -59532,7 +59532,7 @@
         <v>25</v>
       </c>
       <c r="CM185" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN185" s="2">
         <v>2</v>
@@ -59556,7 +59556,7 @@
         <v>157</v>
       </c>
       <c r="CU185" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV185" s="1">
         <v>9</v>
@@ -62342,7 +62342,7 @@
         <v>170</v>
       </c>
       <c r="K195" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L195" s="2">
         <v>5</v>
@@ -62606,7 +62606,7 @@
         <v>71201</v>
       </c>
       <c r="CU195" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CV195" s="1">
         <v>3370</v>
@@ -64050,7 +64050,7 @@
         <v>0</v>
       </c>
       <c r="BT200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU200" s="2">
         <v>2</v>
@@ -64134,7 +64134,7 @@
         <v>66</v>
       </c>
       <c r="CV200" s="1">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="CW200" s="1">
         <v>519</v>
@@ -64319,7 +64319,7 @@
         <v>0</v>
       </c>
       <c r="BH201" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BI201" s="2">
         <v>6</v>
@@ -64403,7 +64403,7 @@
         <v>26</v>
       </c>
       <c r="CJ201" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="CK201" s="2">
         <v>138</v>
@@ -64439,7 +64439,7 @@
         <v>221</v>
       </c>
       <c r="CV201" s="1">
-        <v>2171</v>
+        <v>2157</v>
       </c>
       <c r="CW201" s="1">
         <v>3329</v>
@@ -66911,7 +66911,7 @@
         <v>3</v>
       </c>
       <c r="I210" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J210" s="1">
         <v>2</v>
@@ -67187,7 +67187,7 @@
         <v>16</v>
       </c>
       <c r="CW210" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:101">
@@ -67234,7 +67234,7 @@
         <v>820</v>
       </c>
       <c r="O211" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P211" s="2">
         <v>19</v>
@@ -67486,7 +67486,7 @@
         <v>6305</v>
       </c>
       <c r="CU211" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CV211" s="1">
         <v>499</v>
@@ -68057,16 +68057,16 @@
         <v>0</v>
       </c>
       <c r="CH213" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="CI213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ213" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CK213" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CL213" s="1">
         <v>0</v>
@@ -68093,16 +68093,16 @@
         <v>0</v>
       </c>
       <c r="CT213" s="1">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CU213" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV213" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CW213" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -68128,7 +68128,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I214" s="2">
         <v>5</v>
@@ -68404,7 +68404,7 @@
         <v>0</v>
       </c>
       <c r="CV214" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW214" s="1">
         <v>6</v>
@@ -69720,7 +69720,7 @@
         <v>585</v>
       </c>
       <c r="D65">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E65" t="s">
         <v>716</v>
@@ -72358,7 +72358,7 @@
         <v>699</v>
       </c>
       <c r="D196">
-        <v>10258</v>
+        <v>10265</v>
       </c>
       <c r="E196" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="BH3" s="2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="BI3" s="2">
         <v>59</v>
@@ -4049,7 +4049,7 @@
         <v>64</v>
       </c>
       <c r="CV3" s="1">
-        <v>867</v>
+        <v>808</v>
       </c>
       <c r="CW3" s="1">
         <v>2050</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="BH4" s="2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="2">
         <v>55</v>
@@ -4354,7 +4354,7 @@
         <v>273</v>
       </c>
       <c r="CV4" s="1">
-        <v>636</v>
+        <v>581</v>
       </c>
       <c r="CW4" s="1">
         <v>1378</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="BH14" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BI14" s="2">
         <v>12</v>
@@ -7404,7 +7404,7 @@
         <v>-19</v>
       </c>
       <c r="CV14" s="1">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="CW14" s="1">
         <v>233</v>
@@ -8139,7 +8139,7 @@
         <v>2</v>
       </c>
       <c r="AN17" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO17" s="2">
         <v>18</v>
@@ -8283,7 +8283,7 @@
         <v>3</v>
       </c>
       <c r="CJ17" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CK17" s="2">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>5</v>
       </c>
       <c r="CV17" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CW17" s="1">
         <v>51</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
@@ -9844,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="CV22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CW22" s="1">
         <v>5</v>
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2">
         <v>23</v>
@@ -10149,7 +10149,7 @@
         <v>3</v>
       </c>
       <c r="CV23" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CW23" s="1">
         <v>45</v>
@@ -11554,7 +11554,7 @@
         <v>0</v>
       </c>
       <c r="BH28" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BI28" s="2">
         <v>13</v>
@@ -11674,7 +11674,7 @@
         <v>24</v>
       </c>
       <c r="CV28" s="1">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="CW28" s="1">
         <v>763</v>
@@ -12325,7 +12325,7 @@
         <v>9</v>
       </c>
       <c r="L31" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M31" s="2">
         <v>46</v>
@@ -12589,7 +12589,7 @@
         <v>18</v>
       </c>
       <c r="CV31" s="1">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="CW31" s="1">
         <v>409</v>
@@ -16350,7 +16350,7 @@
         <v>0</v>
       </c>
       <c r="AF44" s="2">
-        <v>1836</v>
+        <v>0</v>
       </c>
       <c r="AG44" s="2">
         <v>1836</v>
@@ -16554,7 +16554,7 @@
         <v>28</v>
       </c>
       <c r="CV44" s="1">
-        <v>1948</v>
+        <v>112</v>
       </c>
       <c r="CW44" s="1">
         <v>2072</v>
@@ -22097,7 +22097,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="2">
         <v>69</v>
@@ -22349,7 +22349,7 @@
         <v>9</v>
       </c>
       <c r="CV63" s="1">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="CW63" s="1">
         <v>170</v>
@@ -22450,7 +22450,7 @@
         <v>5</v>
       </c>
       <c r="AF64" s="2">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="AG64" s="2">
         <v>90</v>
@@ -22654,7 +22654,7 @@
         <v>20</v>
       </c>
       <c r="CV64" s="1">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="CW64" s="1">
         <v>401</v>
@@ -22830,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="BE65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF65" s="1">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>1753</v>
       </c>
       <c r="CW65" s="1">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23622,7 +23622,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="2">
         <v>41</v>
@@ -23874,7 +23874,7 @@
         <v>3</v>
       </c>
       <c r="CV68" s="1">
-        <v>5</v>
+        <v>-19</v>
       </c>
       <c r="CW68" s="1">
         <v>52</v>
@@ -23891,7 +23891,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E69" s="2">
         <v>3</v>
@@ -23903,7 +23903,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I69" s="2">
         <v>6</v>
@@ -24179,7 +24179,7 @@
         <v>0</v>
       </c>
       <c r="CV69" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CW69" s="1">
         <v>9</v>
@@ -25668,7 +25668,7 @@
         <v>48</v>
       </c>
       <c r="CJ74" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="CK74" s="2">
         <v>414</v>
@@ -25704,7 +25704,7 @@
         <v>177</v>
       </c>
       <c r="CV74" s="1">
-        <v>1804</v>
+        <v>1799</v>
       </c>
       <c r="CW74" s="1">
         <v>4417</v>
@@ -26026,7 +26026,7 @@
         <v>52</v>
       </c>
       <c r="D76" s="2">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="E76" s="2">
         <v>179</v>
@@ -26062,7 +26062,7 @@
         <v>4</v>
       </c>
       <c r="P76" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Q76" s="2">
         <v>2401</v>
@@ -26110,7 +26110,7 @@
         <v>0</v>
       </c>
       <c r="AF76" s="2">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AG76" s="2">
         <v>614</v>
@@ -26146,7 +26146,7 @@
         <v>1</v>
       </c>
       <c r="AR76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS76" s="2">
         <v>4</v>
@@ -26158,7 +26158,7 @@
         <v>0</v>
       </c>
       <c r="AV76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" s="2">
         <v>3</v>
@@ -26314,7 +26314,7 @@
         <v>127</v>
       </c>
       <c r="CV76" s="1">
-        <v>1308</v>
+        <v>1196</v>
       </c>
       <c r="CW76" s="1">
         <v>3736</v>
@@ -26550,7 +26550,7 @@
         <v>0</v>
       </c>
       <c r="BY77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ77" s="1">
         <v>3</v>
@@ -26583,7 +26583,7 @@
         <v>67</v>
       </c>
       <c r="CJ77" s="2">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="CK77" s="2">
         <v>584</v>
@@ -26619,10 +26619,10 @@
         <v>101</v>
       </c>
       <c r="CV77" s="1">
-        <v>10177</v>
+        <v>10151</v>
       </c>
       <c r="CW77" s="1">
-        <v>15912</v>
+        <v>15911</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27587,7 +27587,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q81" s="2">
         <v>218</v>
@@ -27839,7 +27839,7 @@
         <v>26</v>
       </c>
       <c r="CV81" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="CW81" s="1">
         <v>374</v>
@@ -27868,7 +27868,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I82" s="2">
         <v>6</v>
@@ -27976,7 +27976,7 @@
         <v>1</v>
       </c>
       <c r="AR82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS82" s="2">
         <v>6</v>
@@ -28120,7 +28120,7 @@
         <v>1</v>
       </c>
       <c r="CN82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CO82" s="2">
         <v>5</v>
@@ -28144,7 +28144,7 @@
         <v>3</v>
       </c>
       <c r="CV82" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW82" s="1">
         <v>21</v>
@@ -29854,7 +29854,7 @@
         <v>0</v>
       </c>
       <c r="BH88" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI88" s="2">
         <v>-7</v>
@@ -29974,7 +29974,7 @@
         <v>10</v>
       </c>
       <c r="CV88" s="1">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="CW88" s="1">
         <v>427</v>
@@ -30769,7 +30769,7 @@
         <v>0</v>
       </c>
       <c r="BH91" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI91" s="2">
         <v>5</v>
@@ -30889,7 +30889,7 @@
         <v>171</v>
       </c>
       <c r="CV91" s="1">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="CW91" s="1">
         <v>896</v>
@@ -36564,7 +36564,7 @@
         <v>0</v>
       </c>
       <c r="BH110" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BI110" s="2">
         <v>13</v>
@@ -36684,7 +36684,7 @@
         <v>102</v>
       </c>
       <c r="CV110" s="1">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="CW110" s="1">
         <v>1046</v>
@@ -36701,7 +36701,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E111" s="2">
         <v>2</v>
@@ -36989,7 +36989,7 @@
         <v>4</v>
       </c>
       <c r="CV111" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="CW111" s="1">
         <v>75</v>
@@ -37479,7 +37479,7 @@
         <v>0</v>
       </c>
       <c r="BH113" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="BI113" s="2">
         <v>37</v>
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="BP113" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BQ113" s="2">
         <v>7</v>
@@ -37599,7 +37599,7 @@
         <v>1343</v>
       </c>
       <c r="CV113" s="1">
-        <v>1748</v>
+        <v>1705</v>
       </c>
       <c r="CW113" s="1">
         <v>11124</v>
@@ -43800,7 +43800,7 @@
         <v>-1</v>
       </c>
       <c r="AF134" s="2">
-        <v>1762</v>
+        <v>1745</v>
       </c>
       <c r="AG134" s="2">
         <v>3914</v>
@@ -44004,7 +44004,7 @@
         <v>7</v>
       </c>
       <c r="CV134" s="1">
-        <v>2538</v>
+        <v>2521</v>
       </c>
       <c r="CW134" s="1">
         <v>5805</v>
@@ -45080,7 +45080,7 @@
         <v>0</v>
       </c>
       <c r="AZ138" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA138" s="2">
         <v>24</v>
@@ -45224,7 +45224,7 @@
         <v>21</v>
       </c>
       <c r="CV138" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="CW138" s="1">
         <v>282</v>
@@ -46473,7 +46473,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I143" s="2">
         <v>5</v>
@@ -46509,7 +46509,7 @@
         <v>0</v>
       </c>
       <c r="T143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U143" s="2">
         <v>1</v>
@@ -46749,7 +46749,7 @@
         <v>3</v>
       </c>
       <c r="CV143" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW143" s="1">
         <v>23</v>
@@ -49230,7 +49230,7 @@
         <v>13</v>
       </c>
       <c r="L152" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M152" s="2">
         <v>70</v>
@@ -49494,7 +49494,7 @@
         <v>17</v>
       </c>
       <c r="CV152" s="1">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="CW152" s="1">
         <v>273</v>
@@ -50145,7 +50145,7 @@
         <v>6</v>
       </c>
       <c r="L155" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M155" s="2">
         <v>35</v>
@@ -50409,7 +50409,7 @@
         <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="CW155" s="1">
         <v>92</v>
@@ -50803,7 +50803,7 @@
         <v>0</v>
       </c>
       <c r="AB157" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC157" s="2">
         <v>3</v>
@@ -50899,7 +50899,7 @@
         <v>0</v>
       </c>
       <c r="BH157" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BI157" s="2">
         <v>17</v>
@@ -51019,7 +51019,7 @@
         <v>94</v>
       </c>
       <c r="CV157" s="1">
-        <v>5247</v>
+        <v>5227</v>
       </c>
       <c r="CW157" s="1">
         <v>9190</v>
@@ -51108,7 +51108,7 @@
         <v>0</v>
       </c>
       <c r="AB158" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC158" s="2">
         <v>3</v>
@@ -51324,7 +51324,7 @@
         <v>243</v>
       </c>
       <c r="CV158" s="1">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="CW158" s="1">
         <v>1715</v>
@@ -52890,7 +52890,7 @@
         <v>3</v>
       </c>
       <c r="L164" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M164" s="2">
         <v>26</v>
@@ -53154,7 +53154,7 @@
         <v>6</v>
       </c>
       <c r="CV164" s="1">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="CW164" s="1">
         <v>203</v>
@@ -54864,7 +54864,7 @@
         <v>0</v>
       </c>
       <c r="BH170" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="BI170" s="2">
         <v>11</v>
@@ -54984,7 +54984,7 @@
         <v>132</v>
       </c>
       <c r="CV170" s="1">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="CW170" s="1">
         <v>1275</v>
@@ -57136,7 +57136,7 @@
         <v>15</v>
       </c>
       <c r="D178" s="2">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E178" s="2">
         <v>158</v>
@@ -57304,7 +57304,7 @@
         <v>0</v>
       </c>
       <c r="BH178" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BI178" s="2">
         <v>38</v>
@@ -57424,7 +57424,7 @@
         <v>-308</v>
       </c>
       <c r="CV178" s="1">
-        <v>2195</v>
+        <v>2163</v>
       </c>
       <c r="CW178" s="1">
         <v>4593</v>
@@ -57854,7 +57854,7 @@
         <v>2</v>
       </c>
       <c r="AN180" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO180" s="2">
         <v>15</v>
@@ -58034,7 +58034,7 @@
         <v>149</v>
       </c>
       <c r="CV180" s="1">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="CW180" s="1">
         <v>2801</v>
@@ -63954,7 +63954,7 @@
         <v>5</v>
       </c>
       <c r="AN200" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AO200" s="2">
         <v>20</v>
@@ -64014,7 +64014,7 @@
         <v>0</v>
       </c>
       <c r="BH200" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BI200" s="2">
         <v>19</v>
@@ -64098,7 +64098,7 @@
         <v>15</v>
       </c>
       <c r="CJ200" s="2">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="CK200" s="2">
         <v>87</v>
@@ -64134,7 +64134,7 @@
         <v>66</v>
       </c>
       <c r="CV200" s="1">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="CW200" s="1">
         <v>519</v>
@@ -65880,7 +65880,7 @@
         <v>1</v>
       </c>
       <c r="BT206" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU206" s="2">
         <v>2</v>
@@ -65964,7 +65964,7 @@
         <v>13</v>
       </c>
       <c r="CV206" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CW206" s="1">
         <v>67</v>
@@ -66149,7 +66149,7 @@
         <v>0</v>
       </c>
       <c r="BH207" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BI207" s="2">
         <v>38</v>
@@ -66269,7 +66269,7 @@
         <v>35</v>
       </c>
       <c r="CV207" s="1">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="CW207" s="1">
         <v>650</v>
@@ -67369,7 +67369,7 @@
         <v>0</v>
       </c>
       <c r="BH211" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI211" s="2">
         <v>2</v>
@@ -67489,7 +67489,7 @@
         <v>31</v>
       </c>
       <c r="CV211" s="1">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="CW211" s="1">
         <v>700</v>
@@ -68597,7 +68597,7 @@
         <v>540</v>
       </c>
       <c r="D9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>716</v>
@@ -70000,7 +70000,7 @@
         <v>599</v>
       </c>
       <c r="D79">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3764,7 +3764,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>808</v>
       </c>
       <c r="CW3" s="1">
-        <v>2050</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="AO6" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP6" s="1">
         <v>1</v>
@@ -4931,7 +4931,7 @@
         <v>68</v>
       </c>
       <c r="CK6" s="2">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="CL6" s="1">
         <v>1</v>
@@ -4967,7 +4967,7 @@
         <v>81</v>
       </c>
       <c r="CW6" s="1">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -13231,7 +13231,7 @@
         <v>4</v>
       </c>
       <c r="I34" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34" s="1">
         <v>505</v>
@@ -13507,7 +13507,7 @@
         <v>59</v>
       </c>
       <c r="CW34" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -16293,7 +16293,7 @@
         <v>55</v>
       </c>
       <c r="M44" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="N44" s="1">
         <v>1597</v>
@@ -16557,7 +16557,7 @@
         <v>112</v>
       </c>
       <c r="CW44" s="1">
-        <v>2072</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -18404,7 +18404,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -18692,7 +18692,7 @@
         <v>2002</v>
       </c>
       <c r="CW51" s="1">
-        <v>2117</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -25491,7 +25491,7 @@
         <v>3</v>
       </c>
       <c r="AC74" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD74" s="1">
         <v>16215</v>
@@ -25611,7 +25611,7 @@
         <v>10</v>
       </c>
       <c r="BQ74" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BR74" s="1">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>1799</v>
       </c>
       <c r="CW74" s="1">
-        <v>4417</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -27554,7 +27554,7 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F81" s="1">
         <v>6</v>
@@ -27842,7 +27842,7 @@
         <v>155</v>
       </c>
       <c r="CW81" s="1">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27871,7 +27871,7 @@
         <v>2</v>
       </c>
       <c r="I82" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -27979,7 +27979,7 @@
         <v>2</v>
       </c>
       <c r="AS82" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -28123,7 +28123,7 @@
         <v>2</v>
       </c>
       <c r="CO82" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP82" s="1">
         <v>0</v>
@@ -28147,7 +28147,7 @@
         <v>7</v>
       </c>
       <c r="CW82" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -29187,7 +29187,7 @@
         <v>3</v>
       </c>
       <c r="AO86" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP86" s="1">
         <v>52</v>
@@ -29367,7 +29367,7 @@
         <v>26</v>
       </c>
       <c r="CW86" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -34581,7 +34581,7 @@
         <v>3</v>
       </c>
       <c r="I104" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J104" s="1">
         <v>0</v>
@@ -34857,7 +34857,7 @@
         <v>3</v>
       </c>
       <c r="CW104" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:101">
@@ -39461,7 +39461,7 @@
         <v>1</v>
       </c>
       <c r="I120" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J120" s="1">
         <v>0</v>
@@ -39737,7 +39737,7 @@
         <v>36</v>
       </c>
       <c r="CW120" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -40484,7 +40484,7 @@
         <v>3</v>
       </c>
       <c r="AS123" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT123" s="1">
         <v>0</v>
@@ -40628,7 +40628,7 @@
         <v>3</v>
       </c>
       <c r="CO123" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CP123" s="1">
         <v>0</v>
@@ -40652,7 +40652,7 @@
         <v>13</v>
       </c>
       <c r="CW123" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -46195,7 +46195,7 @@
         <v>12</v>
       </c>
       <c r="Q142" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R142" s="1">
         <v>0</v>
@@ -46447,7 +46447,7 @@
         <v>44</v>
       </c>
       <c r="CW142" s="1">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47989,7 +47989,7 @@
         <v>5</v>
       </c>
       <c r="E148" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F148" s="1">
         <v>12</v>
@@ -48277,7 +48277,7 @@
         <v>98</v>
       </c>
       <c r="CW148" s="1">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -50429,7 +50429,7 @@
         <v>43</v>
       </c>
       <c r="E156" s="2">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -50717,7 +50717,7 @@
         <v>1058</v>
       </c>
       <c r="CW156" s="1">
-        <v>2539</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -52816,7 +52816,7 @@
         <v>5</v>
       </c>
       <c r="CK163" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CL163" s="1">
         <v>49</v>
@@ -52852,7 +52852,7 @@
         <v>20</v>
       </c>
       <c r="CW163" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -57552,7 +57552,7 @@
         <v>14</v>
       </c>
       <c r="AO179" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AP179" s="1">
         <v>5</v>
@@ -57696,7 +57696,7 @@
         <v>10</v>
       </c>
       <c r="CK179" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CL179" s="1">
         <v>11</v>
@@ -57732,7 +57732,7 @@
         <v>28</v>
       </c>
       <c r="CW179" s="1">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -57857,7 +57857,7 @@
         <v>6</v>
       </c>
       <c r="AO180" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP180" s="1">
         <v>9</v>
@@ -58037,7 +58037,7 @@
         <v>1271</v>
       </c>
       <c r="CW180" s="1">
-        <v>2801</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -64346,7 +64346,7 @@
         <v>2</v>
       </c>
       <c r="BQ201" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR201" s="1">
         <v>5</v>
@@ -64442,7 +64442,7 @@
         <v>2157</v>
       </c>
       <c r="CW201" s="1">
-        <v>3329</v>
+        <v>3327</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -69177,7 +69177,7 @@
         <v>563</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
         <v>716</v>
@@ -69537,7 +69537,7 @@
         <v>576</v>
       </c>
       <c r="D56">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E56" t="s">
         <v>716</v>
@@ -69640,7 +69640,7 @@
         <v>581</v>
       </c>
       <c r="D61">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E61" t="s">
         <v>716</v>
@@ -69720,7 +69720,7 @@
         <v>585</v>
       </c>
       <c r="D65">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s">
         <v>716</v>
@@ -70000,7 +70000,7 @@
         <v>599</v>
       </c>
       <c r="D79">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>
@@ -70080,7 +70080,7 @@
         <v>546</v>
       </c>
       <c r="D83">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E83" t="s">
         <v>716</v>
@@ -70466,7 +70466,7 @@
         <v>619</v>
       </c>
       <c r="D102">
-        <v>2984</v>
+        <v>2986</v>
       </c>
       <c r="E102" t="s">
         <v>716</v>
@@ -72038,7 +72038,7 @@
         <v>687</v>
       </c>
       <c r="D180">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E180" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3839,16 +3839,16 @@
         <v>4</v>
       </c>
       <c r="AD3" s="1">
-        <v>18286</v>
+        <v>18288</v>
       </c>
       <c r="AE3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG3" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -4043,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46743</v>
+        <v>46745</v>
       </c>
       <c r="CU3" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="CV3" s="1">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="CW3" s="1">
-        <v>2040</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4569,16 +4569,16 @@
         <v>0</v>
       </c>
       <c r="BR5" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BS5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV5" s="1">
         <v>1</v>
@@ -4653,16 +4653,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38703</v>
+        <v>38704</v>
       </c>
       <c r="CU5" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CV5" s="1">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="CW5" s="1">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -4778,16 +4778,16 @@
         <v>0</v>
       </c>
       <c r="AL6" s="1">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM6" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AN6" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AO6" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AP6" s="1">
         <v>1</v>
@@ -4922,16 +4922,16 @@
         <v>0</v>
       </c>
       <c r="CH6" s="1">
-        <v>1595</v>
+        <v>1625</v>
       </c>
       <c r="CI6" s="2">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="CJ6" s="2">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="CK6" s="2">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="CL6" s="1">
         <v>1</v>
@@ -4958,16 +4958,16 @@
         <v>0</v>
       </c>
       <c r="CT6" s="1">
-        <v>2278</v>
+        <v>2314</v>
       </c>
       <c r="CU6" s="1">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="CV6" s="1">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="CW6" s="1">
-        <v>85</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:101">
@@ -9891,16 +9891,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P23" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -10143,16 +10143,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="CU23" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CV23" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="CW23" s="1">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -10717,16 +10717,16 @@
         <v>0</v>
       </c>
       <c r="CH25" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="CI25" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ25" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CK25" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CL25" s="1">
         <v>0</v>
@@ -10753,16 +10753,16 @@
         <v>0</v>
       </c>
       <c r="CT25" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="CU25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV25" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CW25" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:101">
@@ -12905,16 +12905,16 @@
         <v>132</v>
       </c>
       <c r="B33" s="1">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E33" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1">
         <v>37</v>
@@ -13193,16 +13193,16 @@
         <v>0</v>
       </c>
       <c r="CT33" s="1">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="CU33" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CV33" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CW33" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:101">
@@ -15076,16 +15076,16 @@
         <v>217</v>
       </c>
       <c r="N40" s="1">
-        <v>16656</v>
+        <v>16664</v>
       </c>
       <c r="O40" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P40" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="Q40" s="2">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -15328,16 +15328,16 @@
         <v>0</v>
       </c>
       <c r="CT40" s="1">
-        <v>53524</v>
+        <v>53532</v>
       </c>
       <c r="CU40" s="1">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="CV40" s="1">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="CW40" s="1">
-        <v>2150</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -15991,16 +15991,16 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="O43" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P43" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="Q43" s="2">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -16243,16 +16243,16 @@
         <v>0</v>
       </c>
       <c r="CT43" s="1">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="CU43" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="CV43" s="1">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="CW43" s="1">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -16344,16 +16344,16 @@
         <v>6</v>
       </c>
       <c r="AD44" s="1">
-        <v>45887</v>
+        <v>46913</v>
       </c>
       <c r="AE44" s="2">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="AF44" s="2">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="AG44" s="2">
-        <v>1836</v>
+        <v>2862</v>
       </c>
       <c r="AH44" s="1">
         <v>0</v>
@@ -16548,16 +16548,16 @@
         <v>0</v>
       </c>
       <c r="CT44" s="1">
-        <v>50664</v>
+        <v>51690</v>
       </c>
       <c r="CU44" s="1">
-        <v>28</v>
+        <v>1054</v>
       </c>
       <c r="CV44" s="1">
-        <v>112</v>
+        <v>1138</v>
       </c>
       <c r="CW44" s="1">
-        <v>2056</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -19615,16 +19615,16 @@
         <v>154</v>
       </c>
       <c r="B55" s="1">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" s="1">
         <v>54</v>
@@ -19903,16 +19903,16 @@
         <v>0</v>
       </c>
       <c r="CT55" s="1">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="CU55" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV55" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CW55" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:101">
@@ -21445,16 +21445,16 @@
         <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>6491</v>
+        <v>6432</v>
       </c>
       <c r="C61" s="2">
-        <v>-11</v>
+        <v>-70</v>
       </c>
       <c r="D61" s="2">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="E61" s="2">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -21733,16 +21733,16 @@
         <v>0</v>
       </c>
       <c r="CT61" s="1">
-        <v>65926</v>
+        <v>65867</v>
       </c>
       <c r="CU61" s="1">
-        <v>7</v>
+        <v>-52</v>
       </c>
       <c r="CV61" s="1">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="CW61" s="1">
-        <v>916</v>
+        <v>857</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22821,16 +22821,16 @@
         <v>2</v>
       </c>
       <c r="BB65" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC65" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD65" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE65" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF65" s="1">
         <v>0</v>
@@ -22953,16 +22953,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67219</v>
+        <v>67221</v>
       </c>
       <c r="CU65" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="CV65" s="1">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="CW65" s="1">
-        <v>3499</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25117,16 +25117,16 @@
         <v>9</v>
       </c>
       <c r="F73" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J73" s="1">
         <v>0</v>
@@ -25393,16 +25393,16 @@
         <v>0</v>
       </c>
       <c r="CT73" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="CU73" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV73" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CW73" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25662,16 +25662,16 @@
         <v>1</v>
       </c>
       <c r="CH74" s="1">
-        <v>16216</v>
+        <v>16225</v>
       </c>
       <c r="CI74" s="2">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="CJ74" s="2">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="CK74" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171791</v>
+        <v>171800</v>
       </c>
       <c r="CU74" s="1">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="CV74" s="1">
-        <v>1799</v>
+        <v>1808</v>
       </c>
       <c r="CW74" s="1">
-        <v>4406</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -25823,16 +25823,16 @@
         <v>0</v>
       </c>
       <c r="AL75" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP75" s="1">
         <v>15</v>
@@ -25967,16 +25967,16 @@
         <v>0</v>
       </c>
       <c r="CH75" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="CI75" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CJ75" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CK75" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CL75" s="1">
         <v>8</v>
@@ -26003,16 +26003,16 @@
         <v>0</v>
       </c>
       <c r="CT75" s="1">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="CU75" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CV75" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CW75" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:101">
@@ -27898,16 +27898,16 @@
         <v>1</v>
       </c>
       <c r="R82" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" s="1">
         <v>4</v>
@@ -28138,16 +28138,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="CU82" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV82" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CW82" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28239,16 +28239,16 @@
         <v>6</v>
       </c>
       <c r="AD83" s="1">
-        <v>352902</v>
+        <v>352903</v>
       </c>
       <c r="AE83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF83" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG83" s="2">
-        <v>3518</v>
+        <v>3519</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28443,16 +28443,16 @@
         <v>0</v>
       </c>
       <c r="CT83" s="1">
-        <v>423965</v>
+        <v>423966</v>
       </c>
       <c r="CU83" s="1">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CV83" s="1">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="CW83" s="1">
-        <v>5484</v>
+        <v>5485</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -30105,16 +30105,16 @@
         <v>0</v>
       </c>
       <c r="AP89" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AQ89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR89" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS89" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30237,16 +30237,16 @@
         <v>1</v>
       </c>
       <c r="CH89" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CI89" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CJ89" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CK89" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CL89" s="1">
         <v>10</v>
@@ -30273,16 +30273,16 @@
         <v>0</v>
       </c>
       <c r="CT89" s="1">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="CU89" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="CV89" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="CW89" s="1">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -32132,16 +32132,16 @@
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J96" s="1">
         <v>2</v>
@@ -32408,16 +32408,16 @@
         <v>0</v>
       </c>
       <c r="CT96" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="CU96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV96" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW96" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -32437,16 +32437,16 @@
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J97" s="1">
         <v>0</v>
@@ -32713,16 +32713,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="CU97" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV97" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CW97" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -34363,16 +34363,16 @@
         <v>0</v>
       </c>
       <c r="AL103" s="1">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AM103" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AN103" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AO103" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AP103" s="1">
         <v>0</v>
@@ -34507,16 +34507,16 @@
         <v>0</v>
       </c>
       <c r="CH103" s="1">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="CI103" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="CJ103" s="2">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="CK103" s="2">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="CL103" s="1">
         <v>0</v>
@@ -34543,16 +34543,16 @@
         <v>0</v>
       </c>
       <c r="CT103" s="1">
-        <v>1046</v>
+        <v>1087</v>
       </c>
       <c r="CU103" s="1">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="CV103" s="1">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="CW103" s="1">
-        <v>220</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -35069,16 +35069,16 @@
         <v>1</v>
       </c>
       <c r="BR105" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BS105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV105" s="1">
         <v>4</v>
@@ -35153,16 +35153,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>8004</v>
+        <v>8005</v>
       </c>
       <c r="CU105" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CV105" s="1">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="CW105" s="1">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -35206,16 +35206,16 @@
         <v>873</v>
       </c>
       <c r="N106" s="1">
-        <v>22919</v>
+        <v>22918</v>
       </c>
       <c r="O106" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P106" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q106" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="R106" s="1">
         <v>0</v>
@@ -35458,16 +35458,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92792</v>
+        <v>92791</v>
       </c>
       <c r="CU106" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="CV106" s="1">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="CW106" s="1">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -37000,16 +37000,16 @@
         <v>211</v>
       </c>
       <c r="B112" s="1">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D112" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E112" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37288,16 +37288,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8297</v>
+        <v>8305</v>
       </c>
       <c r="CU112" s="1">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="CV112" s="1">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="CW112" s="1">
-        <v>647</v>
+        <v>655</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -38549,16 +38549,16 @@
         <v>0</v>
       </c>
       <c r="J117" s="1">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M117" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N117" s="1">
         <v>2543</v>
@@ -38633,16 +38633,16 @@
         <v>0</v>
       </c>
       <c r="AL117" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO117" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP117" s="1">
         <v>62</v>
@@ -38777,16 +38777,16 @@
         <v>0</v>
       </c>
       <c r="CH117" s="1">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CI117" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ117" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CK117" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL117" s="1">
         <v>28</v>
@@ -38813,16 +38813,16 @@
         <v>0</v>
       </c>
       <c r="CT117" s="1">
-        <v>13368</v>
+        <v>13371</v>
       </c>
       <c r="CU117" s="1">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="CV117" s="1">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="CW117" s="1">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39147,16 +39147,16 @@
         <v>1</v>
       </c>
       <c r="F119" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G119" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H119" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I119" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J119" s="1">
         <v>0</v>
@@ -39423,16 +39423,16 @@
         <v>0</v>
       </c>
       <c r="CT119" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="CU119" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV119" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW119" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -46174,16 +46174,16 @@
         <v>4</v>
       </c>
       <c r="J142" s="1">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="K142" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L142" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="M142" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="N142" s="1">
         <v>565</v>
@@ -46270,16 +46270,16 @@
         <v>4</v>
       </c>
       <c r="AP142" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AQ142" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR142" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT142" s="1">
         <v>14</v>
@@ -46414,16 +46414,16 @@
         <v>4</v>
       </c>
       <c r="CL142" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="CM142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP142" s="1">
         <v>0</v>
@@ -46438,16 +46438,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1656</v>
+        <v>1674</v>
       </c>
       <c r="CU142" s="1">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="CV142" s="1">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="CW142" s="1">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -48052,16 +48052,16 @@
         <v>1</v>
       </c>
       <c r="Z148" s="1">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AA148" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB148" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC148" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD148" s="1">
         <v>0</v>
@@ -48268,16 +48268,16 @@
         <v>0</v>
       </c>
       <c r="CT148" s="1">
-        <v>5613</v>
+        <v>5615</v>
       </c>
       <c r="CU148" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CV148" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="CW148" s="1">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -51066,16 +51066,16 @@
         <v>414</v>
       </c>
       <c r="N158" s="1">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="O158" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P158" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q158" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51318,16 +51318,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25704</v>
+        <v>25705</v>
       </c>
       <c r="CU158" s="1">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="CV158" s="1">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="CW158" s="1">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -54397,16 +54397,16 @@
         <v>1</v>
       </c>
       <c r="F169" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H169" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J169" s="1">
         <v>0</v>
@@ -54673,16 +54673,16 @@
         <v>0</v>
       </c>
       <c r="CT169" s="1">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="CU169" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV169" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CW169" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -57860,16 +57860,16 @@
         <v>12</v>
       </c>
       <c r="AP180" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT180" s="1">
         <v>0</v>
@@ -58028,16 +58028,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51288</v>
+        <v>51289</v>
       </c>
       <c r="CU180" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="CV180" s="1">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="CW180" s="1">
-        <v>2798</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -60192,16 +60192,16 @@
         <v>15</v>
       </c>
       <c r="F188" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G188" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I188" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J188" s="1">
         <v>0</v>
@@ -60468,16 +60468,16 @@
         <v>0</v>
       </c>
       <c r="CT188" s="1">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CU188" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV188" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CW188" s="1">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="189" spans="1:101">
@@ -61412,16 +61412,16 @@
         <v>0</v>
       </c>
       <c r="F192" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I192" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" s="1">
         <v>0</v>
@@ -61688,16 +61688,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="CU192" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV192" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CW192" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -64044,16 +64044,16 @@
         <v>0</v>
       </c>
       <c r="BR200" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BS200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU200" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV200" s="1">
         <v>5</v>
@@ -64128,16 +64128,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16356</v>
+        <v>16357</v>
       </c>
       <c r="CU200" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="CV200" s="1">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="CW200" s="1">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4273,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="BU4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV4" s="1">
         <v>5</v>
@@ -4357,7 +4357,7 @@
         <v>581</v>
       </c>
       <c r="CW4" s="1">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="BU5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV5" s="1">
         <v>1</v>
@@ -4662,7 +4662,7 @@
         <v>318</v>
       </c>
       <c r="CW5" s="1">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="BE9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9" s="1">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>56</v>
       </c>
       <c r="CW9" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -6611,7 +6611,7 @@
         <v>139</v>
       </c>
       <c r="AM12" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AN12" s="2">
         <v>86</v>
@@ -6755,7 +6755,7 @@
         <v>166</v>
       </c>
       <c r="CI12" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CJ12" s="2">
         <v>114</v>
@@ -6791,7 +6791,7 @@
         <v>447</v>
       </c>
       <c r="CU12" s="1">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="CV12" s="1">
         <v>213</v>
@@ -8967,7 +8967,7 @@
         <v>912</v>
       </c>
       <c r="K20" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L20" s="2">
         <v>14</v>
@@ -9231,7 +9231,7 @@
         <v>20738</v>
       </c>
       <c r="CU20" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="CV20" s="1">
         <v>381</v>
@@ -9371,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="AR21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS21" s="2">
         <v>5</v>
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="CJ21" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="CK21" s="2">
         <v>61</v>
@@ -9539,7 +9539,7 @@
         <v>2</v>
       </c>
       <c r="CV21" s="1">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="CW21" s="1">
         <v>68</v>
@@ -12322,7 +12322,7 @@
         <v>1393</v>
       </c>
       <c r="K31" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2">
         <v>17</v>
@@ -12586,7 +12586,7 @@
         <v>6013</v>
       </c>
       <c r="CU31" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CV31" s="1">
         <v>257</v>
@@ -14586,16 +14586,16 @@
         <v>0</v>
       </c>
       <c r="BB38" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE38" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BF38" s="1">
         <v>0</v>
@@ -14718,16 +14718,16 @@
         <v>0</v>
       </c>
       <c r="CT38" s="1">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="CU38" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV38" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CW38" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -15133,7 +15133,7 @@
         <v>413</v>
       </c>
       <c r="AG40" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15337,7 +15337,7 @@
         <v>821</v>
       </c>
       <c r="CW40" s="1">
-        <v>2158</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -15348,7 +15348,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -15456,7 +15456,7 @@
         <v>76</v>
       </c>
       <c r="AM41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" s="2">
         <v>7</v>
@@ -15600,7 +15600,7 @@
         <v>528</v>
       </c>
       <c r="CI41" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ41" s="2">
         <v>25</v>
@@ -15636,7 +15636,7 @@
         <v>692</v>
       </c>
       <c r="CU41" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CV41" s="1">
         <v>34</v>
@@ -16263,7 +16263,7 @@
         <v>241</v>
       </c>
       <c r="C44" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" s="2">
         <v>15</v>
@@ -16287,7 +16287,7 @@
         <v>1365</v>
       </c>
       <c r="K44" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>55</v>
@@ -16551,7 +16551,7 @@
         <v>51690</v>
       </c>
       <c r="CU44" s="1">
-        <v>1054</v>
+        <v>1035</v>
       </c>
       <c r="CV44" s="1">
         <v>1138</v>
@@ -18650,7 +18650,7 @@
         <v>2813</v>
       </c>
       <c r="CI51" s="2">
-        <v>1757</v>
+        <v>1731</v>
       </c>
       <c r="CJ51" s="2">
         <v>1795</v>
@@ -18686,7 +18686,7 @@
         <v>3745</v>
       </c>
       <c r="CU51" s="1">
-        <v>1951</v>
+        <v>1925</v>
       </c>
       <c r="CV51" s="1">
         <v>2002</v>
@@ -19119,7 +19119,7 @@
         <v>0</v>
       </c>
       <c r="AN53" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AO53" s="2">
         <v>21</v>
@@ -19263,7 +19263,7 @@
         <v>0</v>
       </c>
       <c r="CJ53" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="CK53" s="2">
         <v>23</v>
@@ -19299,7 +19299,7 @@
         <v>0</v>
       </c>
       <c r="CV53" s="1">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="CW53" s="1">
         <v>49</v>
@@ -20545,7 +20545,7 @@
         <v>40</v>
       </c>
       <c r="G58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>3</v>
@@ -20653,7 +20653,7 @@
         <v>22</v>
       </c>
       <c r="AQ58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR58" s="2">
         <v>2</v>
@@ -20797,7 +20797,7 @@
         <v>19</v>
       </c>
       <c r="CM58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN58" s="2">
         <v>2</v>
@@ -20821,7 +20821,7 @@
         <v>181</v>
       </c>
       <c r="CU58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV58" s="1">
         <v>18</v>
@@ -21448,7 +21448,7 @@
         <v>6432</v>
       </c>
       <c r="C61" s="2">
-        <v>-70</v>
+        <v>-67</v>
       </c>
       <c r="D61" s="2">
         <v>112</v>
@@ -21736,7 +21736,7 @@
         <v>65867</v>
       </c>
       <c r="CU61" s="1">
-        <v>-52</v>
+        <v>-49</v>
       </c>
       <c r="CV61" s="1">
         <v>357</v>
@@ -22088,7 +22088,7 @@
         <v>11</v>
       </c>
       <c r="M63" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N63" s="1">
         <v>1118</v>
@@ -22184,7 +22184,7 @@
         <v>2</v>
       </c>
       <c r="AS63" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22268,7 +22268,7 @@
         <v>1</v>
       </c>
       <c r="BU63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV63" s="1">
         <v>0</v>
@@ -22352,7 +22352,7 @@
         <v>50</v>
       </c>
       <c r="CW63" s="1">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22453,7 +22453,7 @@
         <v>10</v>
       </c>
       <c r="AG64" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>121</v>
       </c>
       <c r="CW64" s="1">
-        <v>401</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23281,7 +23281,7 @@
         <v>19</v>
       </c>
       <c r="D67" s="2">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E67" s="2">
         <v>107</v>
@@ -23569,7 +23569,7 @@
         <v>19</v>
       </c>
       <c r="CV67" s="1">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="CW67" s="1">
         <v>107</v>
@@ -23586,7 +23586,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="E68" s="2">
         <v>-26</v>
@@ -23874,7 +23874,7 @@
         <v>3</v>
       </c>
       <c r="CV68" s="1">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="CW68" s="1">
         <v>52</v>
@@ -24217,7 +24217,7 @@
         <v>285</v>
       </c>
       <c r="K70" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2">
         <v>24</v>
@@ -24481,7 +24481,7 @@
         <v>2267</v>
       </c>
       <c r="CU70" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CV70" s="1">
         <v>50</v>
@@ -25503,7 +25503,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25527,7 +25527,7 @@
         <v>109</v>
       </c>
       <c r="AO74" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25665,10 +25665,10 @@
         <v>16225</v>
       </c>
       <c r="CI74" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="CJ74" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="CK74" s="2">
         <v>423</v>
@@ -25701,13 +25701,13 @@
         <v>171800</v>
       </c>
       <c r="CU74" s="1">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="CV74" s="1">
-        <v>1808</v>
+        <v>1802</v>
       </c>
       <c r="CW74" s="1">
-        <v>4415</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26059,13 +26059,13 @@
         <v>117545</v>
       </c>
       <c r="O76" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P76" s="2">
         <v>907</v>
       </c>
       <c r="Q76" s="2">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26311,13 +26311,13 @@
         <v>151140</v>
       </c>
       <c r="CU76" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="CV76" s="1">
         <v>1196</v>
       </c>
       <c r="CW76" s="1">
-        <v>3736</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26355,10 +26355,10 @@
         <v>43</v>
       </c>
       <c r="L77" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M77" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26436,13 +26436,13 @@
         <v>1919</v>
       </c>
       <c r="AM77" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AN77" s="2">
         <v>45</v>
       </c>
       <c r="AO77" s="2">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26583,7 +26583,7 @@
         <v>67</v>
       </c>
       <c r="CJ77" s="2">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="CK77" s="2">
         <v>584</v>
@@ -26616,13 +26616,13 @@
         <v>390977</v>
       </c>
       <c r="CU77" s="1">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="CV77" s="1">
-        <v>10151</v>
+        <v>10131</v>
       </c>
       <c r="CW77" s="1">
-        <v>15911</v>
+        <v>15905</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27560,7 +27560,7 @@
         <v>6</v>
       </c>
       <c r="G81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2">
         <v>1</v>
@@ -27836,7 +27836,7 @@
         <v>6432</v>
       </c>
       <c r="CU81" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CV81" s="1">
         <v>155</v>
@@ -27895,7 +27895,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" s="1">
         <v>11</v>
@@ -28147,7 +28147,7 @@
         <v>8</v>
       </c>
       <c r="CW82" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -30027,7 +30027,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="2">
         <v>5</v>
@@ -30108,7 +30108,7 @@
         <v>44</v>
       </c>
       <c r="AQ89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR89" s="2">
         <v>3</v>
@@ -30240,7 +30240,7 @@
         <v>96</v>
       </c>
       <c r="CI89" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CJ89" s="2">
         <v>7</v>
@@ -30276,10 +30276,10 @@
         <v>2233</v>
       </c>
       <c r="CU89" s="1">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="CV89" s="1">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="CW89" s="1">
         <v>172</v>
@@ -30622,7 +30622,7 @@
         <v>5471</v>
       </c>
       <c r="K91" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L91" s="2">
         <v>168</v>
@@ -30886,7 +30886,7 @@
         <v>26025</v>
       </c>
       <c r="CU91" s="1">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CV91" s="1">
         <v>417</v>
@@ -34151,7 +34151,7 @@
         <v>8</v>
       </c>
       <c r="BQ102" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BR102" s="1">
         <v>2</v>
@@ -34247,7 +34247,7 @@
         <v>738</v>
       </c>
       <c r="CW102" s="1">
-        <v>1733</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34880,7 +34880,7 @@
         <v>6</v>
       </c>
       <c r="G105" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H105" s="2">
         <v>2</v>
@@ -35156,7 +35156,7 @@
         <v>8005</v>
       </c>
       <c r="CU105" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CV105" s="1">
         <v>216</v>
@@ -37625,7 +37625,7 @@
         <v>64</v>
       </c>
       <c r="G114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="2">
         <v>3</v>
@@ -37901,7 +37901,7 @@
         <v>173</v>
       </c>
       <c r="CU114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV114" s="1">
         <v>3</v>
@@ -38648,7 +38648,7 @@
         <v>62</v>
       </c>
       <c r="AQ117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR117" s="2">
         <v>1</v>
@@ -38780,7 +38780,7 @@
         <v>168</v>
       </c>
       <c r="CI117" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ117" s="2">
         <v>7</v>
@@ -38816,7 +38816,7 @@
         <v>13371</v>
       </c>
       <c r="CU117" s="1">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="CV117" s="1">
         <v>584</v>
@@ -39150,7 +39150,7 @@
         <v>64</v>
       </c>
       <c r="G119" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119" s="2">
         <v>3</v>
@@ -39258,7 +39258,7 @@
         <v>114</v>
       </c>
       <c r="AQ119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR119" s="2">
         <v>3</v>
@@ -39402,7 +39402,7 @@
         <v>91</v>
       </c>
       <c r="CM119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN119" s="2">
         <v>3</v>
@@ -39426,7 +39426,7 @@
         <v>846</v>
       </c>
       <c r="CU119" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CV119" s="1">
         <v>10</v>
@@ -41584,7 +41584,7 @@
         <v>22</v>
       </c>
       <c r="E127" s="2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -41872,7 +41872,7 @@
         <v>45</v>
       </c>
       <c r="CW127" s="1">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -42496,7 +42496,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E130" s="2">
         <v>7</v>
@@ -42784,7 +42784,7 @@
         <v>10</v>
       </c>
       <c r="CV130" s="1">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="CW130" s="1">
         <v>164</v>
@@ -43719,7 +43719,7 @@
         <v>8</v>
       </c>
       <c r="E134" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -44007,7 +44007,7 @@
         <v>2521</v>
       </c>
       <c r="CW134" s="1">
-        <v>5805</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44102,7 +44102,7 @@
         <v>11790</v>
       </c>
       <c r="AE135" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF135" s="2">
         <v>159</v>
@@ -44216,7 +44216,7 @@
         <v>42</v>
       </c>
       <c r="BQ135" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BR135" s="1">
         <v>0</v>
@@ -44306,13 +44306,13 @@
         <v>62762</v>
       </c>
       <c r="CU135" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="CV135" s="1">
         <v>981</v>
       </c>
       <c r="CW135" s="1">
-        <v>2691</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -46763,7 +46763,7 @@
         <v>499</v>
       </c>
       <c r="C144" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2">
         <v>7</v>
@@ -47051,7 +47051,7 @@
         <v>1191</v>
       </c>
       <c r="CU144" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CV144" s="1">
         <v>21</v>
@@ -47798,7 +47798,7 @@
         <v>45</v>
       </c>
       <c r="AQ147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR147" s="2">
         <v>3</v>
@@ -47930,7 +47930,7 @@
         <v>31</v>
       </c>
       <c r="CI147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ147" s="2">
         <v>2</v>
@@ -47966,7 +47966,7 @@
         <v>230</v>
       </c>
       <c r="CU147" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV147" s="1">
         <v>16</v>
@@ -49108,7 +49108,7 @@
         <v>1</v>
       </c>
       <c r="BU151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV151" s="1">
         <v>0</v>
@@ -49192,7 +49192,7 @@
         <v>14</v>
       </c>
       <c r="CW151" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49227,7 +49227,7 @@
         <v>870</v>
       </c>
       <c r="K152" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L152" s="2">
         <v>28</v>
@@ -49491,7 +49491,7 @@
         <v>3026</v>
       </c>
       <c r="CU152" s="1">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CV152" s="1">
         <v>64</v>
@@ -52158,7 +52158,7 @@
         <v>1</v>
       </c>
       <c r="BU161" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV161" s="1">
         <v>0</v>
@@ -52242,7 +52242,7 @@
         <v>724</v>
       </c>
       <c r="CW161" s="1">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52750,7 +52750,7 @@
         <v>20</v>
       </c>
       <c r="BO163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP163" s="2">
         <v>1</v>
@@ -52846,7 +52846,7 @@
         <v>1133</v>
       </c>
       <c r="CU163" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV163" s="1">
         <v>20</v>
@@ -53500,7 +53500,7 @@
         <v>16</v>
       </c>
       <c r="L166" s="2">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="M166" s="2">
         <v>124</v>
@@ -53764,7 +53764,7 @@
         <v>17</v>
       </c>
       <c r="CV166" s="1">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="CW166" s="1">
         <v>506</v>
@@ -54197,7 +54197,7 @@
         <v>1</v>
       </c>
       <c r="AO168" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP168" s="1">
         <v>35</v>
@@ -54341,7 +54341,7 @@
         <v>24</v>
       </c>
       <c r="CK168" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54377,7 +54377,7 @@
         <v>131</v>
       </c>
       <c r="CW168" s="1">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54400,7 +54400,7 @@
         <v>48</v>
       </c>
       <c r="G169" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H169" s="2">
         <v>3</v>
@@ -54493,28 +54493,28 @@
         <v>0</v>
       </c>
       <c r="AL169" s="1">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="AM169" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AN169" s="2">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AO169" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AP169" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR169" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS169" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT169" s="1">
         <v>0</v>
@@ -54673,16 +54673,16 @@
         <v>0</v>
       </c>
       <c r="CT169" s="1">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="CU169" s="1">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="CV169" s="1">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="CW169" s="1">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -55925,7 +55925,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" s="2">
         <v>2</v>
@@ -56201,7 +56201,7 @@
         <v>488</v>
       </c>
       <c r="CU174" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV174" s="1">
         <v>23</v>
@@ -57546,13 +57546,13 @@
         <v>536</v>
       </c>
       <c r="AM179" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN179" s="2">
         <v>14</v>
       </c>
       <c r="AO179" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AP179" s="1">
         <v>5</v>
@@ -57690,7 +57690,7 @@
         <v>230</v>
       </c>
       <c r="CI179" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ179" s="2">
         <v>10</v>
@@ -57726,13 +57726,13 @@
         <v>852</v>
       </c>
       <c r="CU179" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CV179" s="1">
         <v>28</v>
       </c>
       <c r="CW179" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="1:101">
@@ -57749,7 +57749,7 @@
         <v>180</v>
       </c>
       <c r="E180" s="2">
-        <v>300</v>
+        <v>242</v>
       </c>
       <c r="F180" s="1">
         <v>1</v>
@@ -58037,7 +58037,7 @@
         <v>1272</v>
       </c>
       <c r="CW180" s="1">
-        <v>2799</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -63930,7 +63930,7 @@
         <v>0</v>
       </c>
       <c r="AF200" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG200" s="2">
         <v>14</v>
@@ -64134,7 +64134,7 @@
         <v>67</v>
       </c>
       <c r="CV200" s="1">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="CW200" s="1">
         <v>520</v>
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>2046</v>
+        <v>2079</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64343,7 +64343,7 @@
         <v>0</v>
       </c>
       <c r="BP201" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ201" s="2">
         <v>2</v>
@@ -64439,10 +64439,10 @@
         <v>221</v>
       </c>
       <c r="CV201" s="1">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="CW201" s="1">
-        <v>3327</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -65673,7 +65673,7 @@
         <v>246</v>
       </c>
       <c r="C206" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D206" s="2">
         <v>14</v>
@@ -65961,7 +65961,7 @@
         <v>1240</v>
       </c>
       <c r="CU206" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV206" s="1">
         <v>27</v>
@@ -66188,7 +66188,7 @@
         <v>1</v>
       </c>
       <c r="BU207" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV207" s="1">
         <v>0</v>
@@ -66272,7 +66272,7 @@
         <v>315</v>
       </c>
       <c r="CW207" s="1">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="208" spans="1:101">

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15049,7 +15049,7 @@
         <v>79</v>
       </c>
       <c r="E40" s="2">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -15337,7 +15337,7 @@
         <v>821</v>
       </c>
       <c r="CW40" s="1">
-        <v>2160</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16305,7 +16305,7 @@
         <v>19</v>
       </c>
       <c r="Q44" s="2">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -16557,7 +16557,7 @@
         <v>1138</v>
       </c>
       <c r="CW44" s="1">
-        <v>3082</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="45" spans="1:101">
@@ -22064,7 +22064,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22352,7 +22352,7 @@
         <v>50</v>
       </c>
       <c r="CW63" s="1">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22794,7 +22794,7 @@
         <v>0</v>
       </c>
       <c r="AS65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT65" s="1">
         <v>1</v>
@@ -22926,7 +22926,7 @@
         <v>26</v>
       </c>
       <c r="CK65" s="2">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22938,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="CO65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP65" s="1">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>1755</v>
       </c>
       <c r="CW65" s="1">
-        <v>3501</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25503,7 +25503,7 @@
         <v>214</v>
       </c>
       <c r="AG74" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25527,7 +25527,7 @@
         <v>109</v>
       </c>
       <c r="AO74" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,7 +25671,7 @@
         <v>172</v>
       </c>
       <c r="CK74" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>1802</v>
       </c>
       <c r="CW74" s="1">
-        <v>4418</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26065,7 +26065,7 @@
         <v>907</v>
       </c>
       <c r="Q76" s="2">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="R76" s="1">
         <v>1</v>
@@ -26317,7 +26317,7 @@
         <v>1196</v>
       </c>
       <c r="CW76" s="1">
-        <v>3737</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26747,7 +26747,7 @@
         <v>16</v>
       </c>
       <c r="AO78" s="2">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="AP78" s="1">
         <v>0</v>
@@ -26927,7 +26927,7 @@
         <v>27</v>
       </c>
       <c r="CW78" s="1">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -27662,7 +27662,7 @@
         <v>6</v>
       </c>
       <c r="AO81" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP81" s="1">
         <v>58</v>
@@ -27806,7 +27806,7 @@
         <v>4</v>
       </c>
       <c r="CK81" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CL81" s="1">
         <v>30</v>
@@ -27842,7 +27842,7 @@
         <v>155</v>
       </c>
       <c r="CW81" s="1">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -30114,7 +30114,7 @@
         <v>3</v>
       </c>
       <c r="AS89" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT89" s="1">
         <v>0</v>
@@ -30246,7 +30246,7 @@
         <v>7</v>
       </c>
       <c r="CK89" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CL89" s="1">
         <v>10</v>
@@ -30282,7 +30282,7 @@
         <v>86</v>
       </c>
       <c r="CW89" s="1">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -35496,7 +35496,7 @@
         <v>3</v>
       </c>
       <c r="I107" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J107" s="1">
         <v>0</v>
@@ -35772,7 +35772,7 @@
         <v>4</v>
       </c>
       <c r="CW107" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:101">
@@ -37631,7 +37631,7 @@
         <v>3</v>
       </c>
       <c r="I114" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J114" s="1">
         <v>0</v>
@@ -37907,7 +37907,7 @@
         <v>3</v>
       </c>
       <c r="CW114" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -46793,7 +46793,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N144" s="1">
         <v>322</v>
@@ -47057,7 +47057,7 @@
         <v>21</v>
       </c>
       <c r="CW144" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -51649,7 +51649,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F160" s="1">
         <v>22</v>
@@ -51661,7 +51661,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J160" s="1">
         <v>0</v>
@@ -51937,7 +51937,7 @@
         <v>0</v>
       </c>
       <c r="CW160" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:101">
@@ -53186,7 +53186,7 @@
         <v>3</v>
       </c>
       <c r="I165" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J165" s="1">
         <v>0</v>
@@ -53462,7 +53462,7 @@
         <v>3</v>
       </c>
       <c r="CW165" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:101">
@@ -58001,7 +58001,7 @@
         <v>32</v>
       </c>
       <c r="CK180" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="CL180" s="1">
         <v>3</v>
@@ -58037,7 +58037,7 @@
         <v>1272</v>
       </c>
       <c r="CW180" s="1">
-        <v>2741</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -63957,7 +63957,7 @@
         <v>9</v>
       </c>
       <c r="AO200" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64101,7 +64101,7 @@
         <v>32</v>
       </c>
       <c r="CK200" s="2">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64137,7 +64137,7 @@
         <v>201</v>
       </c>
       <c r="CW200" s="1">
-        <v>520</v>
+        <v>498</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64190,7 +64190,7 @@
         <v>209</v>
       </c>
       <c r="Q201" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="R201" s="1">
         <v>0</v>
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>2079</v>
+        <v>2091</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64442,7 +64442,7 @@
         <v>2155</v>
       </c>
       <c r="CW201" s="1">
-        <v>3360</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -71129,7 +71129,7 @@
         <v>647</v>
       </c>
       <c r="D135">
-        <v>10251</v>
+        <v>10254</v>
       </c>
       <c r="E135" t="s">
         <v>716</v>
@@ -72358,7 +72358,7 @@
         <v>699</v>
       </c>
       <c r="D196">
-        <v>10265</v>
+        <v>10267</v>
       </c>
       <c r="E196" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="BP3" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ3" s="2">
         <v>25</v>
@@ -4049,7 +4049,7 @@
         <v>66</v>
       </c>
       <c r="CV3" s="1">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="CW3" s="1">
         <v>2042</v>
@@ -4401,16 +4401,16 @@
         <v>120</v>
       </c>
       <c r="N5" s="1">
-        <v>2965</v>
+        <v>2980</v>
       </c>
       <c r="O5" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P5" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="2">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
@@ -4653,16 +4653,16 @@
         <v>0</v>
       </c>
       <c r="CT5" s="1">
-        <v>38704</v>
+        <v>38719</v>
       </c>
       <c r="CU5" s="1">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="CV5" s="1">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="CW5" s="1">
-        <v>815</v>
+        <v>830</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -7311,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="BQ14" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR14" s="1">
         <v>7</v>
@@ -7368,7 +7368,7 @@
         <v>2</v>
       </c>
       <c r="CJ14" s="2">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="CK14" s="2">
         <v>74</v>
@@ -7404,10 +7404,10 @@
         <v>-19</v>
       </c>
       <c r="CV14" s="1">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="CW14" s="1">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -7804,16 +7804,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="1">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AE16" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF16" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG16" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -8008,16 +8008,16 @@
         <v>0</v>
       </c>
       <c r="CT16" s="1">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="CU16" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="CV16" s="1">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="CW16" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:101">
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="CR20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS20" s="2">
         <v>1</v>
@@ -9234,7 +9234,7 @@
         <v>51</v>
       </c>
       <c r="CV20" s="1">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="CW20" s="1">
         <v>950</v>
@@ -11192,7 +11192,7 @@
         <v>13</v>
       </c>
       <c r="AO27" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP27" s="1">
         <v>12</v>
@@ -11336,7 +11336,7 @@
         <v>15</v>
       </c>
       <c r="CK27" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="CL27" s="1">
         <v>1</v>
@@ -11372,7 +11372,7 @@
         <v>31</v>
       </c>
       <c r="CW27" s="1">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:101">
@@ -13228,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="2">
         <v>5</v>
@@ -13255,7 +13255,7 @@
         <v>23</v>
       </c>
       <c r="Q34" s="2">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="R34" s="1">
         <v>1</v>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="BP34" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BQ34" s="2">
         <v>4</v>
@@ -13504,10 +13504,10 @@
         <v>10</v>
       </c>
       <c r="CV34" s="1">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="CW34" s="1">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -16084,7 +16084,7 @@
         <v>3</v>
       </c>
       <c r="AS43" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT43" s="1">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>3</v>
       </c>
       <c r="CO43" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CP43" s="1">
         <v>0</v>
@@ -16252,7 +16252,7 @@
         <v>40</v>
       </c>
       <c r="CW43" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -19929,7 +19929,7 @@
         <v>16</v>
       </c>
       <c r="E56" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -20217,7 +20217,7 @@
         <v>108</v>
       </c>
       <c r="CW56" s="1">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -22175,16 +22175,16 @@
         <v>0</v>
       </c>
       <c r="AP63" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AQ63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR63" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS63" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT63" s="1">
         <v>0</v>
@@ -22307,16 +22307,16 @@
         <v>0</v>
       </c>
       <c r="CH63" s="1">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="CI63" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ63" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CK63" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="CL63" s="1">
         <v>22</v>
@@ -22343,16 +22343,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2880</v>
+        <v>2883</v>
       </c>
       <c r="CU63" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CV63" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="CW63" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22507,7 +22507,7 @@
         <v>2</v>
       </c>
       <c r="AY64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" s="2">
         <v>1</v>
@@ -22651,7 +22651,7 @@
         <v>8032</v>
       </c>
       <c r="CU64" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CV64" s="1">
         <v>121</v>
@@ -22737,16 +22737,16 @@
         <v>1</v>
       </c>
       <c r="Z65" s="1">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AA65" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB65" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC65" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD65" s="1">
         <v>338</v>
@@ -22953,16 +22953,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67221</v>
+        <v>67225</v>
       </c>
       <c r="CU65" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="CV65" s="1">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="CW65" s="1">
-        <v>3488</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23586,7 +23586,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <v>-30</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2">
         <v>-26</v>
@@ -23874,7 +23874,7 @@
         <v>3</v>
       </c>
       <c r="CV68" s="1">
-        <v>-20</v>
+        <v>11</v>
       </c>
       <c r="CW68" s="1">
         <v>52</v>
@@ -24310,16 +24310,16 @@
         <v>0</v>
       </c>
       <c r="AP70" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AQ70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR70" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24454,16 +24454,16 @@
         <v>8</v>
       </c>
       <c r="CL70" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CM70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP70" s="1">
         <v>0</v>
@@ -24478,16 +24478,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="CU70" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CW70" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24821,7 +24821,7 @@
         <v>2</v>
       </c>
       <c r="I72" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" s="1">
         <v>78</v>
@@ -24833,7 +24833,7 @@
         <v>2</v>
       </c>
       <c r="M72" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N72" s="1">
         <v>91</v>
@@ -24893,7 +24893,7 @@
         <v>9</v>
       </c>
       <c r="AG72" s="2">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="AH72" s="1">
         <v>1</v>
@@ -25013,7 +25013,7 @@
         <v>1</v>
       </c>
       <c r="BU72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV72" s="1">
         <v>2</v>
@@ -25097,7 +25097,7 @@
         <v>47</v>
       </c>
       <c r="CW72" s="1">
-        <v>146</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25518,16 +25518,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36288</v>
+        <v>36302</v>
       </c>
       <c r="AM74" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="AN74" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AO74" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25662,16 +25662,16 @@
         <v>1</v>
       </c>
       <c r="CH74" s="1">
-        <v>16225</v>
+        <v>16228</v>
       </c>
       <c r="CI74" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="CJ74" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="CK74" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171800</v>
+        <v>171817</v>
       </c>
       <c r="CU74" s="1">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="CV74" s="1">
-        <v>1802</v>
+        <v>1815</v>
       </c>
       <c r="CW74" s="1">
-        <v>4393</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26433,16 +26433,16 @@
         <v>0</v>
       </c>
       <c r="AL77" s="1">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="AM77" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN77" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO77" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26577,16 +26577,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7365</v>
+        <v>7368</v>
       </c>
       <c r="CI77" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="CJ77" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="CK77" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26613,16 +26613,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390977</v>
+        <v>390982</v>
       </c>
       <c r="CU77" s="1">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="CV77" s="1">
-        <v>10131</v>
+        <v>10135</v>
       </c>
       <c r="CW77" s="1">
-        <v>15905</v>
+        <v>15901</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -27070,7 +27070,7 @@
         <v>6</v>
       </c>
       <c r="AU79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV79" s="2">
         <v>2</v>
@@ -27226,7 +27226,7 @@
         <v>90690</v>
       </c>
       <c r="CU79" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="CV79" s="1">
         <v>643</v>
@@ -27746,7 +27746,7 @@
         <v>0</v>
       </c>
       <c r="BQ81" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR81" s="1">
         <v>19</v>
@@ -27842,7 +27842,7 @@
         <v>155</v>
       </c>
       <c r="CW81" s="1">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -27862,16 +27862,16 @@
         <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -27970,16 +27970,16 @@
         <v>0</v>
       </c>
       <c r="AP82" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AQ82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS82" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT82" s="1">
         <v>0</v>
@@ -28114,16 +28114,16 @@
         <v>1</v>
       </c>
       <c r="CL82" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CM82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO82" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CP82" s="1">
         <v>0</v>
@@ -28138,16 +28138,16 @@
         <v>0</v>
       </c>
       <c r="CT82" s="1">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="CU82" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CV82" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW82" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:101">
@@ -28200,7 +28200,7 @@
         <v>269</v>
       </c>
       <c r="Q83" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="R83" s="1">
         <v>0</v>
@@ -28452,7 +28452,7 @@
         <v>888</v>
       </c>
       <c r="CW83" s="1">
-        <v>5485</v>
+        <v>5484</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29223,7 +29223,7 @@
         <v>1</v>
       </c>
       <c r="BA86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB86" s="1">
         <v>20</v>
@@ -29331,7 +29331,7 @@
         <v>1</v>
       </c>
       <c r="CK86" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CL86" s="1">
         <v>35</v>
@@ -29367,7 +29367,7 @@
         <v>26</v>
       </c>
       <c r="CW86" s="1">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:101">
@@ -31418,7 +31418,7 @@
         <v>1</v>
       </c>
       <c r="BU93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV93" s="1">
         <v>0</v>
@@ -31502,7 +31502,7 @@
         <v>27</v>
       </c>
       <c r="CW93" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -32677,16 +32677,16 @@
         <v>0</v>
       </c>
       <c r="CH97" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CI97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ97" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CK97" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CL97" s="1">
         <v>33</v>
@@ -32713,16 +32713,16 @@
         <v>0</v>
       </c>
       <c r="CT97" s="1">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="CU97" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV97" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW97" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:101">
@@ -35215,7 +35215,7 @@
         <v>184</v>
       </c>
       <c r="Q106" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="R106" s="1">
         <v>0</v>
@@ -35344,7 +35344,7 @@
         <v>0</v>
       </c>
       <c r="BH106" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI106" s="2">
         <v>4</v>
@@ -35464,10 +35464,10 @@
         <v>184</v>
       </c>
       <c r="CV106" s="1">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="CW106" s="1">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -37030,7 +37030,7 @@
         <v>12</v>
       </c>
       <c r="L112" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M112" s="2">
         <v>84</v>
@@ -37294,7 +37294,7 @@
         <v>23</v>
       </c>
       <c r="CV112" s="1">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="CW112" s="1">
         <v>655</v>
@@ -38355,7 +38355,7 @@
         <v>66</v>
       </c>
       <c r="AU116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV116" s="2">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>21820</v>
       </c>
       <c r="CU116" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="CV116" s="1">
         <v>371</v>
@@ -39384,7 +39384,7 @@
         <v>0</v>
       </c>
       <c r="CG119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH119" s="1">
         <v>148</v>
@@ -39432,7 +39432,7 @@
         <v>10</v>
       </c>
       <c r="CW119" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:101">
@@ -39452,16 +39452,16 @@
         <v>0</v>
       </c>
       <c r="F120" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G120" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I120" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J120" s="1">
         <v>0</v>
@@ -39728,16 +39728,16 @@
         <v>0</v>
       </c>
       <c r="CT120" s="1">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="CU120" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV120" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CW120" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -41306,16 +41306,16 @@
         <v>0</v>
       </c>
       <c r="N126" s="1">
-        <v>554</v>
+        <v>603</v>
       </c>
       <c r="O126" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="P126" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q126" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R126" s="1">
         <v>0</v>
@@ -41558,16 +41558,16 @@
         <v>0</v>
       </c>
       <c r="CT126" s="1">
-        <v>835</v>
+        <v>884</v>
       </c>
       <c r="CU126" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="CV126" s="1">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="CW126" s="1">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="127" spans="1:101">
@@ -44326,7 +44326,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E136" s="2">
         <v>8</v>
@@ -44614,7 +44614,7 @@
         <v>5</v>
       </c>
       <c r="CV136" s="1">
-        <v>5081</v>
+        <v>5080</v>
       </c>
       <c r="CW136" s="1">
         <v>6084</v>
@@ -44625,16 +44625,16 @@
         <v>236</v>
       </c>
       <c r="B137" s="1">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C137" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D137" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E137" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F137" s="1">
         <v>25</v>
@@ -44649,16 +44649,16 @@
         <v>1</v>
       </c>
       <c r="J137" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K137" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L137" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M137" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N137" s="1">
         <v>153</v>
@@ -44913,16 +44913,16 @@
         <v>0</v>
       </c>
       <c r="CT137" s="1">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="CU137" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="CV137" s="1">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="CW137" s="1">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -45080,7 +45080,7 @@
         <v>0</v>
       </c>
       <c r="AZ138" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA138" s="2">
         <v>24</v>
@@ -45224,7 +45224,7 @@
         <v>21</v>
       </c>
       <c r="CV138" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="CW138" s="1">
         <v>282</v>
@@ -45998,7 +45998,7 @@
         <v>0</v>
       </c>
       <c r="BA141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB141" s="1">
         <v>11</v>
@@ -46142,7 +46142,7 @@
         <v>10</v>
       </c>
       <c r="CW141" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46291,7 +46291,7 @@
         <v>0</v>
       </c>
       <c r="AW142" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX142" s="1">
         <v>4</v>
@@ -46447,7 +46447,7 @@
         <v>62</v>
       </c>
       <c r="CW142" s="1">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -47801,7 +47801,7 @@
         <v>1</v>
       </c>
       <c r="AR147" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS147" s="2">
         <v>5</v>
@@ -47969,7 +47969,7 @@
         <v>8</v>
       </c>
       <c r="CV147" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW147" s="1">
         <v>33</v>
@@ -51640,28 +51640,28 @@
         <v>259</v>
       </c>
       <c r="B160" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C160" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D160" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E160" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F160" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G160" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H160" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I160" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J160" s="1">
         <v>0</v>
@@ -51928,16 +51928,16 @@
         <v>0</v>
       </c>
       <c r="CT160" s="1">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="CU160" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV160" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CW160" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:101">
@@ -52561,7 +52561,7 @@
         <v>1</v>
       </c>
       <c r="D163" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E163" s="2">
         <v>6</v>
@@ -52849,7 +52849,7 @@
         <v>2</v>
       </c>
       <c r="CV163" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CW163" s="1">
         <v>32</v>
@@ -54502,7 +54502,7 @@
         <v>24</v>
       </c>
       <c r="AO169" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="AP169" s="1">
         <v>2</v>
@@ -54637,16 +54637,16 @@
         <v>0</v>
       </c>
       <c r="CH169" s="1">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="CI169" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CJ169" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="CK169" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CL169" s="1">
         <v>0</v>
@@ -54673,16 +54673,16 @@
         <v>0</v>
       </c>
       <c r="CT169" s="1">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="CU169" s="1">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="CV169" s="1">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="CW169" s="1">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="170" spans="1:101">
@@ -54995,16 +54995,16 @@
         <v>270</v>
       </c>
       <c r="B171" s="1">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C171" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D171" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E171" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F171" s="1">
         <v>16</v>
@@ -55283,16 +55283,16 @@
         <v>0</v>
       </c>
       <c r="CT171" s="1">
-        <v>5846</v>
+        <v>5854</v>
       </c>
       <c r="CU171" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="CV171" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CW171" s="1">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="172" spans="1:101">
@@ -57764,16 +57764,16 @@
         <v>0</v>
       </c>
       <c r="J180" s="1">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="K180" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L180" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M180" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N180" s="1">
         <v>36939</v>
@@ -58028,16 +58028,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51289</v>
+        <v>51287</v>
       </c>
       <c r="CU180" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="CV180" s="1">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="CW180" s="1">
-        <v>2720</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -61652,16 +61652,16 @@
         <v>0</v>
       </c>
       <c r="CH192" s="1">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="CI192" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CJ192" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CK192" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CL192" s="1">
         <v>37</v>
@@ -61688,16 +61688,16 @@
         <v>0</v>
       </c>
       <c r="CT192" s="1">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="CU192" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="CV192" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CW192" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="193" spans="1:101">
@@ -62010,16 +62010,16 @@
         <v>293</v>
       </c>
       <c r="B194" s="1">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="C194" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D194" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E194" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F194" s="1">
         <v>0</v>
@@ -62118,16 +62118,16 @@
         <v>0</v>
       </c>
       <c r="AL194" s="1">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AM194" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN194" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AO194" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AP194" s="1">
         <v>65</v>
@@ -62274,16 +62274,16 @@
         <v>8</v>
       </c>
       <c r="CL194" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CM194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO194" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CP194" s="1">
         <v>0</v>
@@ -62298,16 +62298,16 @@
         <v>0</v>
       </c>
       <c r="CT194" s="1">
-        <v>32887</v>
+        <v>32902</v>
       </c>
       <c r="CU194" s="1">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="CV194" s="1">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="CW194" s="1">
-        <v>1391</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -64053,7 +64053,7 @@
         <v>1</v>
       </c>
       <c r="BU200" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV200" s="1">
         <v>5</v>
@@ -64137,7 +64137,7 @@
         <v>201</v>
       </c>
       <c r="CW200" s="1">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64442,7 +64442,7 @@
         <v>2155</v>
       </c>
       <c r="CW201" s="1">
-        <v>3374</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -66301,7 +66301,7 @@
         <v>0</v>
       </c>
       <c r="I208" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J208" s="1">
         <v>0</v>
@@ -66577,7 +66577,7 @@
         <v>9</v>
       </c>
       <c r="CW208" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:101">
@@ -68474,7 +68474,7 @@
         <v>534</v>
       </c>
       <c r="D3">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>716</v>
@@ -69537,7 +69537,7 @@
         <v>576</v>
       </c>
       <c r="D56">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E56" t="s">
         <v>716</v>
@@ -70000,7 +70000,7 @@
         <v>599</v>
       </c>
       <c r="D79">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E79" t="s">
         <v>716</v>
@@ -70466,7 +70466,7 @@
         <v>619</v>
       </c>
       <c r="D102">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="E102" t="s">
         <v>716</v>
@@ -71129,7 +71129,7 @@
         <v>647</v>
       </c>
       <c r="D135">
-        <v>10254</v>
+        <v>10256</v>
       </c>
       <c r="E135" t="s">
         <v>716</v>
@@ -72441,7 +72441,7 @@
         <v>703</v>
       </c>
       <c r="D200">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E200" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4132,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AA4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC4" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD4" s="1">
         <v>21644</v>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="BT4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU4" s="2">
         <v>1</v>
@@ -4348,16 +4348,16 @@
         <v>0</v>
       </c>
       <c r="CT4" s="1">
-        <v>43184</v>
+        <v>43187</v>
       </c>
       <c r="CU4" s="1">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="CV4" s="1">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="CW4" s="1">
-        <v>1377</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="AF5" s="2">
-        <v>237</v>
+        <v>898</v>
       </c>
       <c r="AG5" s="2">
         <v>608</v>
@@ -4659,7 +4659,7 @@
         <v>38</v>
       </c>
       <c r="CV5" s="1">
-        <v>322</v>
+        <v>983</v>
       </c>
       <c r="CW5" s="1">
         <v>830</v>
@@ -8976,16 +8976,16 @@
         <v>62</v>
       </c>
       <c r="N20" s="1">
-        <v>12653</v>
+        <v>12655</v>
       </c>
       <c r="O20" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q20" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9228,16 +9228,16 @@
         <v>1</v>
       </c>
       <c r="CT20" s="1">
-        <v>20738</v>
+        <v>20740</v>
       </c>
       <c r="CU20" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="CW20" s="1">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9245,28 +9245,28 @@
         <v>120</v>
       </c>
       <c r="B21" s="1">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C21" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="1">
         <v>0</v>
@@ -9533,16 +9533,16 @@
         <v>0</v>
       </c>
       <c r="CT21" s="1">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="CU21" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="CV21" s="1">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="CW21" s="1">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -9981,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="AR23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" s="2">
         <v>6</v>
@@ -10113,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="CJ23" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CK23" s="2">
         <v>5</v>
@@ -10149,7 +10149,7 @@
         <v>9</v>
       </c>
       <c r="CV23" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="CW23" s="1">
         <v>51</v>
@@ -10726,7 +10726,7 @@
         <v>14</v>
       </c>
       <c r="CK25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CL25" s="1">
         <v>0</v>
@@ -10762,7 +10762,7 @@
         <v>14</v>
       </c>
       <c r="CW25" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:101">
@@ -12319,16 +12319,16 @@
         <v>2</v>
       </c>
       <c r="J31" s="1">
-        <v>1393</v>
+        <v>1416</v>
       </c>
       <c r="K31" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L31" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="M31" s="2">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="N31" s="1">
         <v>1982</v>
@@ -12583,16 +12583,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>6013</v>
+        <v>6036</v>
       </c>
       <c r="CU31" s="1">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="CV31" s="1">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="CW31" s="1">
-        <v>409</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -12624,13 +12624,13 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>842</v>
+        <v>865</v>
       </c>
       <c r="K32" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L32" s="2">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="M32" s="2">
         <v>100</v>
@@ -12888,13 +12888,13 @@
         <v>0</v>
       </c>
       <c r="CT32" s="1">
-        <v>11145</v>
+        <v>11168</v>
       </c>
       <c r="CU32" s="1">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="CV32" s="1">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="CW32" s="1">
         <v>556</v>
@@ -14460,7 +14460,7 @@
         <v>5</v>
       </c>
       <c r="L38" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M38" s="2">
         <v>35</v>
@@ -14595,7 +14595,7 @@
         <v>1</v>
       </c>
       <c r="BE38" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BF38" s="1">
         <v>0</v>
@@ -14724,10 +14724,10 @@
         <v>11</v>
       </c>
       <c r="CV38" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CW38" s="1">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -15130,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="AF40" s="2">
-        <v>413</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="2">
         <v>766</v>
@@ -15334,7 +15334,7 @@
         <v>102</v>
       </c>
       <c r="CV40" s="1">
-        <v>821</v>
+        <v>409</v>
       </c>
       <c r="CW40" s="1">
         <v>2075</v>
@@ -20859,16 +20859,16 @@
         <v>2</v>
       </c>
       <c r="J59" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K59" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M59" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N59" s="1">
         <v>321</v>
@@ -20955,16 +20955,16 @@
         <v>3</v>
       </c>
       <c r="AP59" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AQ59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS59" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT59" s="1">
         <v>0</v>
@@ -21087,16 +21087,16 @@
         <v>0</v>
       </c>
       <c r="CH59" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CI59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CJ59" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CK59" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CL59" s="1">
         <v>67</v>
@@ -21123,16 +21123,16 @@
         <v>0</v>
       </c>
       <c r="CT59" s="1">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="CU59" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CV59" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="CW59" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:101">
@@ -22055,16 +22055,16 @@
         <v>162</v>
       </c>
       <c r="B63" s="1">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D63" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E63" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -22091,16 +22091,16 @@
         <v>17</v>
       </c>
       <c r="N63" s="1">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="O63" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P63" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q63" s="2">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="R63" s="1">
         <v>0</v>
@@ -22343,16 +22343,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2883</v>
+        <v>2911</v>
       </c>
       <c r="CU63" s="1">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="CV63" s="1">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="CW63" s="1">
-        <v>168</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22453,7 +22453,7 @@
         <v>10</v>
       </c>
       <c r="AG64" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>121</v>
       </c>
       <c r="CW64" s="1">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -23897,16 +23897,16 @@
         <v>3</v>
       </c>
       <c r="F69" s="1">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G69" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I69" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J69" s="1">
         <v>0</v>
@@ -24173,16 +24173,16 @@
         <v>0</v>
       </c>
       <c r="CT69" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="CU69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV69" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CW69" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:101">
@@ -24316,7 +24316,7 @@
         <v>2</v>
       </c>
       <c r="AR70" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS70" s="2">
         <v>7</v>
@@ -24460,7 +24460,7 @@
         <v>1</v>
       </c>
       <c r="CN70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO70" s="2">
         <v>3</v>
@@ -24484,7 +24484,7 @@
         <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="CW70" s="1">
         <v>80</v>
@@ -25440,7 +25440,7 @@
         <v>41</v>
       </c>
       <c r="L74" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="M74" s="2">
         <v>234</v>
@@ -25527,7 +25527,7 @@
         <v>119</v>
       </c>
       <c r="AO74" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,7 +25671,7 @@
         <v>175</v>
       </c>
       <c r="CK74" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25704,10 +25704,10 @@
         <v>199</v>
       </c>
       <c r="CV74" s="1">
-        <v>1815</v>
+        <v>1775</v>
       </c>
       <c r="CW74" s="1">
-        <v>4397</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26349,16 +26349,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4922</v>
+        <v>4921</v>
       </c>
       <c r="K77" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L77" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M77" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26577,16 +26577,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7368</v>
+        <v>7369</v>
       </c>
       <c r="CI77" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="CJ77" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="CK77" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -27665,16 +27665,16 @@
         <v>6</v>
       </c>
       <c r="AP81" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AQ81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS81" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT81" s="1">
         <v>5</v>
@@ -27809,16 +27809,16 @@
         <v>10</v>
       </c>
       <c r="CL81" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CM81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP81" s="1">
         <v>0</v>
@@ -27833,16 +27833,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6432</v>
+        <v>6434</v>
       </c>
       <c r="CU81" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="CV81" s="1">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CW81" s="1">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -30673,7 +30673,7 @@
         <v>0</v>
       </c>
       <c r="AB91" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="2">
         <v>6</v>
@@ -30889,7 +30889,7 @@
         <v>172</v>
       </c>
       <c r="CV91" s="1">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="CW91" s="1">
         <v>896</v>
@@ -34040,7 +34040,7 @@
         <v>0</v>
       </c>
       <c r="AF102" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AG102" s="2">
         <v>139</v>
@@ -34244,7 +34244,7 @@
         <v>124</v>
       </c>
       <c r="CV102" s="1">
-        <v>738</v>
+        <v>690</v>
       </c>
       <c r="CW102" s="1">
         <v>1728</v>
@@ -35206,16 +35206,16 @@
         <v>873</v>
       </c>
       <c r="N106" s="1">
-        <v>22918</v>
+        <v>22915</v>
       </c>
       <c r="O106" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="P106" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q106" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="R106" s="1">
         <v>0</v>
@@ -35410,16 +35410,16 @@
         <v>0</v>
       </c>
       <c r="CD106" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CE106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH106" s="1">
         <v>6493</v>
@@ -35458,16 +35458,16 @@
         <v>0</v>
       </c>
       <c r="CT106" s="1">
-        <v>92791</v>
+        <v>92789</v>
       </c>
       <c r="CU106" s="1">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="CV106" s="1">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="CW106" s="1">
-        <v>2467</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -35780,16 +35780,16 @@
         <v>207</v>
       </c>
       <c r="B108" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F108" s="1">
         <v>37</v>
@@ -36068,16 +36068,16 @@
         <v>0</v>
       </c>
       <c r="CT108" s="1">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="CU108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV108" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CW108" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:101">
@@ -36420,7 +36420,7 @@
         <v>82</v>
       </c>
       <c r="L110" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M110" s="2">
         <v>446</v>
@@ -36684,7 +36684,7 @@
         <v>102</v>
       </c>
       <c r="CV110" s="1">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="CW110" s="1">
         <v>1046</v>
@@ -36695,16 +36695,16 @@
         <v>210</v>
       </c>
       <c r="B111" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="1">
         <v>72</v>
@@ -36983,16 +36983,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="CU111" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CV111" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CW111" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37006,7 +37006,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E112" s="2">
         <v>56</v>
@@ -37294,7 +37294,7 @@
         <v>23</v>
       </c>
       <c r="CV112" s="1">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="CW112" s="1">
         <v>655</v>
@@ -37557,16 +37557,16 @@
         <v>0</v>
       </c>
       <c r="CH113" s="1">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="CI113" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CJ113" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="CK113" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37593,16 +37593,16 @@
         <v>0</v>
       </c>
       <c r="CT113" s="1">
-        <v>175156</v>
+        <v>175161</v>
       </c>
       <c r="CU113" s="1">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="CV113" s="1">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="CW113" s="1">
-        <v>11124</v>
+        <v>11129</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38531,7 +38531,7 @@
         <v>207</v>
       </c>
       <c r="D117" s="2">
-        <v>568</v>
+        <v>372</v>
       </c>
       <c r="E117" s="2">
         <v>1123</v>
@@ -38819,7 +38819,7 @@
         <v>210</v>
       </c>
       <c r="CV117" s="1">
-        <v>584</v>
+        <v>388</v>
       </c>
       <c r="CW117" s="1">
         <v>1300</v>
@@ -39557,7 +39557,7 @@
         <v>19</v>
       </c>
       <c r="AO120" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AP120" s="1">
         <v>0</v>
@@ -39701,7 +39701,7 @@
         <v>16</v>
       </c>
       <c r="CK120" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="CL120" s="1">
         <v>0</v>
@@ -39737,7 +39737,7 @@
         <v>38</v>
       </c>
       <c r="CW120" s="1">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -44213,7 +44213,7 @@
         <v>0</v>
       </c>
       <c r="BP135" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BQ135" s="2">
         <v>42</v>
@@ -44309,7 +44309,7 @@
         <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>981</v>
+        <v>939</v>
       </c>
       <c r="CW135" s="1">
         <v>2690</v>
@@ -44404,16 +44404,16 @@
         <v>6</v>
       </c>
       <c r="AD136" s="1">
-        <v>156594</v>
+        <v>156588</v>
       </c>
       <c r="AE136" s="2">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AF136" s="2">
-        <v>5042</v>
+        <v>5036</v>
       </c>
       <c r="AG136" s="2">
-        <v>5983</v>
+        <v>5977</v>
       </c>
       <c r="AH136" s="1">
         <v>0</v>
@@ -44608,16 +44608,16 @@
         <v>0</v>
       </c>
       <c r="CT136" s="1">
-        <v>158876</v>
+        <v>158870</v>
       </c>
       <c r="CU136" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="CV136" s="1">
-        <v>5080</v>
+        <v>5074</v>
       </c>
       <c r="CW136" s="1">
-        <v>6084</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -45576,16 +45576,16 @@
         <v>0</v>
       </c>
       <c r="N140" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R140" s="1">
         <v>3</v>
@@ -45828,16 +45828,16 @@
         <v>0</v>
       </c>
       <c r="CT140" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CU140" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV140" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW140" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -47933,7 +47933,7 @@
         <v>0</v>
       </c>
       <c r="CJ147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK147" s="2">
         <v>2</v>
@@ -47969,7 +47969,7 @@
         <v>8</v>
       </c>
       <c r="CV147" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW147" s="1">
         <v>33</v>
@@ -49410,7 +49410,7 @@
         <v>0</v>
       </c>
       <c r="BT152" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU152" s="2">
         <v>9</v>
@@ -49494,7 +49494,7 @@
         <v>4</v>
       </c>
       <c r="CV152" s="1">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="CW152" s="1">
         <v>273</v>
@@ -49517,16 +49517,16 @@
         <v>1</v>
       </c>
       <c r="F153" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G153" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I153" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J153" s="1">
         <v>0</v>
@@ -49793,16 +49793,16 @@
         <v>0</v>
       </c>
       <c r="CT153" s="1">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="CU153" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CV153" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CW153" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:101">
@@ -50797,16 +50797,16 @@
         <v>1</v>
       </c>
       <c r="Z157" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AA157" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB157" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC157" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD157" s="1">
         <v>138904</v>
@@ -50929,16 +50929,16 @@
         <v>1</v>
       </c>
       <c r="BR157" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV157" s="1">
         <v>5</v>
@@ -51013,16 +51013,16 @@
         <v>0</v>
       </c>
       <c r="CT157" s="1">
-        <v>166431</v>
+        <v>166435</v>
       </c>
       <c r="CU157" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="CV157" s="1">
-        <v>5227</v>
+        <v>5231</v>
       </c>
       <c r="CW157" s="1">
-        <v>9190</v>
+        <v>9194</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51039,7 +51039,7 @@
         <v>196</v>
       </c>
       <c r="E158" s="2">
-        <v>407</v>
+        <v>325</v>
       </c>
       <c r="F158" s="1">
         <v>2</v>
@@ -51102,16 +51102,16 @@
         <v>0</v>
       </c>
       <c r="Z158" s="1">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AA158" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB158" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC158" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD158" s="1">
         <v>157</v>
@@ -51144,7 +51144,7 @@
         <v>6</v>
       </c>
       <c r="AN158" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO158" s="2">
         <v>43</v>
@@ -51318,16 +51318,16 @@
         <v>0</v>
       </c>
       <c r="CT158" s="1">
-        <v>25705</v>
+        <v>25708</v>
       </c>
       <c r="CU158" s="1">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="CV158" s="1">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="CW158" s="1">
-        <v>1716</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -52807,16 +52807,16 @@
         <v>0</v>
       </c>
       <c r="CH163" s="1">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="CI163" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CJ163" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CK163" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CL163" s="1">
         <v>49</v>
@@ -52843,16 +52843,16 @@
         <v>0</v>
       </c>
       <c r="CT163" s="1">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="CU163" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV163" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CW163" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -53494,16 +53494,16 @@
         <v>2</v>
       </c>
       <c r="J166" s="1">
-        <v>1714</v>
+        <v>1731</v>
       </c>
       <c r="K166" s="2">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="L166" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="M166" s="2">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="N166" s="1">
         <v>2217</v>
@@ -53542,16 +53542,16 @@
         <v>1</v>
       </c>
       <c r="Z166" s="1">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AA166" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB166" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC166" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD166" s="1">
         <v>0</v>
@@ -53758,16 +53758,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5270</v>
+        <v>5290</v>
       </c>
       <c r="CU166" s="1">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="CV166" s="1">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="CW166" s="1">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54110,7 +54110,7 @@
         <v>17</v>
       </c>
       <c r="L168" s="2">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="M168" s="2">
         <v>117</v>
@@ -54374,7 +54374,7 @@
         <v>27</v>
       </c>
       <c r="CV168" s="1">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="CW168" s="1">
         <v>547</v>
@@ -54699,7 +54699,7 @@
         <v>99</v>
       </c>
       <c r="E170" s="2">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -54987,7 +54987,7 @@
         <v>495</v>
       </c>
       <c r="CW170" s="1">
-        <v>1275</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -60438,7 +60438,7 @@
         <v>0</v>
       </c>
       <c r="CJ188" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CK188" s="2">
         <v>64</v>
@@ -60474,7 +60474,7 @@
         <v>1</v>
       </c>
       <c r="CV188" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CW188" s="1">
         <v>162</v>
@@ -62019,7 +62019,7 @@
         <v>26</v>
       </c>
       <c r="E194" s="2">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F194" s="1">
         <v>0</v>
@@ -62307,7 +62307,7 @@
         <v>602</v>
       </c>
       <c r="CW194" s="1">
-        <v>1406</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -62644,16 +62644,16 @@
         <v>0</v>
       </c>
       <c r="J196" s="1">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="K196" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L196" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M196" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N196" s="1">
         <v>3415</v>
@@ -62908,16 +62908,16 @@
         <v>0</v>
       </c>
       <c r="CT196" s="1">
-        <v>5484</v>
+        <v>5491</v>
       </c>
       <c r="CU196" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="CV196" s="1">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="CW196" s="1">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -63840,16 +63840,16 @@
         <v>299</v>
       </c>
       <c r="B200" s="1">
-        <v>4289</v>
+        <v>4308</v>
       </c>
       <c r="C200" s="2">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D200" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E200" s="2">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="F200" s="1">
         <v>0</v>
@@ -64128,16 +64128,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16357</v>
+        <v>16376</v>
       </c>
       <c r="CU200" s="1">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="CV200" s="1">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="CW200" s="1">
-        <v>497</v>
+        <v>516</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -67324,7 +67324,7 @@
         <v>1</v>
       </c>
       <c r="AS211" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT211" s="1">
         <v>9</v>
@@ -67456,7 +67456,7 @@
         <v>41</v>
       </c>
       <c r="CK211" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="CL211" s="1">
         <v>15</v>
@@ -67492,7 +67492,7 @@
         <v>497</v>
       </c>
       <c r="CW211" s="1">
-        <v>700</v>
+        <v>671</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -72358,7 +72358,7 @@
         <v>699</v>
       </c>
       <c r="D196">
-        <v>10267</v>
+        <v>10268</v>
       </c>
       <c r="E196" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="832">
   <si>
     <t>ati_all</t>
   </si>
@@ -977,21 +977,6 @@
     <t>opengov_email</t>
   </si>
   <si>
-    <t>16342451 Canada Inc.  | 16342451 Canada Inc</t>
-  </si>
-  <si>
-    <t>Agriculture and Agri-Food Canada | Agriculture et Agroalimentaire Canada</t>
-  </si>
-  <si>
-    <t>Crown-Indigenous Relations and Northern Affairs Canada | Relations Couronne-Autochtones et Affaires du Nord Canada</t>
-  </si>
-  <si>
-    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
-  </si>
-  <si>
-    <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
-  </si>
-  <si>
     <t>Atlantic Pilotage Authority Canada | Administration de pilotage de l'Atlantique Canada</t>
   </si>
   <si>
@@ -1394,9 +1379,6 @@
     <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
   </si>
   <si>
-    <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
-  </si>
-  <si>
     <t>Office of the Commissioner of Official Languages | Commissariat aux langues officielles</t>
   </si>
   <si>
@@ -1616,297 +1598,288 @@
     <t>Yukon Environmental and Socio-economic Assessment Board | Office d’évaluation environnementale et socio-économique du Yukon</t>
   </si>
   <si>
+    <t>bbradley@atlanticpilotage.com</t>
+  </si>
+  <si>
+    <t>atip.coordinator@asiapacific.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@tribunal.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@bankofcanada.ca</t>
+  </si>
+  <si>
+    <t>sgustin@bctreaty.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@bdc.ca</t>
+  </si>
+  <si>
+    <t>moffitt@portofbelledune.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@cannor.gc.ca</t>
+  </si>
+  <si>
+    <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip@catsa.gc.ca</t>
+  </si>
+  <si>
+    <t>nancy.laframboise@cb-cda.gc.ca</t>
+  </si>
+  <si>
+    <t>Peter.Hull@cbc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@canadacouncil.ca</t>
+  </si>
+  <si>
+    <t>atip.aiprp@ccc.ca</t>
+  </si>
+  <si>
+    <t>atip_aiprp@ccohs.ca</t>
+  </si>
+  <si>
+    <t>priscilla.revolus@cdc-ccl.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@cdev.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@agr.gc.ca</t>
+    <t>ATIP-AIPRP@cdic.ca</t>
+  </si>
+  <si>
+    <t>dec.aiprp-atip.ced@canada.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@cdev.ca</t>
+  </si>
+  <si>
+    <t>ATIPOffice-BureauAIPRP@neb-one.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-CFIA-AIPRP@inspection.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP.AIPRP@cfmws.com</t>
+  </si>
+  <si>
+    <t>atip-aiprp@grainscanada.gc.ca</t>
+  </si>
+  <si>
+    <t>atipcgf@cgf-fcc.ca</t>
+  </si>
+  <si>
+    <t>atip.aiprp@chrc-ccdp.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@cib-bic.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cic.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@college-ic.ca</t>
+  </si>
+  <si>
+    <t>ATIPCoordinator@cihr-irsc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@bch-mc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@clc-sic.ca</t>
+  </si>
+  <si>
+    <t>AIPRP-ATIP@museedelhistoire.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cmhc.ca</t>
+  </si>
+  <si>
+    <t>atip@humanrights.ca</t>
+  </si>
+  <si>
+    <t>ablack@pier21.ca</t>
+  </si>
+  <si>
+    <t>kdoucette@nature.ca</t>
+  </si>
+  <si>
+    <t>TBennett@cnlopb.nl.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cnsc-ccsn.gc.ca</t>
+  </si>
+  <si>
+    <t>atip@cnsoer.ca</t>
+  </si>
+  <si>
+    <t>adiaz@cpata-cabamc.ca</t>
+  </si>
+  <si>
+    <t>ATIP.AIPRP@crcc-ccetp.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
+  </si>
+  <si>
+    <t>INT-REC-G@cra-arc.gc.ca</t>
+  </si>
+  <si>
+    <t>atavassoli@crrf-fcrr.ca</t>
+  </si>
+  <si>
+    <t>AIPRP-ATIP@crtc.gc.ca</t>
+  </si>
+  <si>
+    <t>AIPRP-ATIP@asc-csa.gc.ca</t>
+  </si>
+  <si>
+    <t>CSC.ATIP-AIPRP.SCC@csc-scc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@cse-cst.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@smtp.gc.ca</t>
+  </si>
+  <si>
+    <t>atipaiprp@csps-efpc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@ingeniumcanada.org</t>
+  </si>
+  <si>
+    <t>OTC.AIPRP-ATIP.CTA@otc-cta.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@destinationcanada.com</t>
+  </si>
+  <si>
+    <t>atip-aiprp@cwa-aec.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@DCC-CDC.gc.ca</t>
+  </si>
+  <si>
+    <t>dcp@international.gc.ca</t>
+  </si>
+  <si>
+    <t>atipteam@edc.ca</t>
+  </si>
+  <si>
+    <t>atip-laiprp@dfo-mpo.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@forces.gc.ca</t>
+  </si>
+  <si>
+    <t>atip@northcrestdev.ca</t>
+  </si>
+  <si>
+    <t>ecatip-ecaiprp@ec.gc.ca</t>
+  </si>
+  <si>
+    <t>aiprp-atip@elections.ca</t>
+  </si>
+  <si>
+    <t>corporateandhrservices-servicesgenerauxetrh@erc-cee.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIPteam@edc.ca</t>
+  </si>
+  <si>
+    <t>info@federalbridge.ca</t>
+  </si>
+  <si>
+    <t>Nathalie.forester@fcac-acfc.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP_AIPRP@fcc-fac.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@feddevontario.gc.ca</t>
+  </si>
+  <si>
+    <t>fednor-atipinbox@ised-isde.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIPcontrol@freshwaterfish.com</t>
+  </si>
+  <si>
+    <t>fin.atip-aiprp.fin@canada.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@fintrac-canafe.gc.ca</t>
+  </si>
+  <si>
+    <t>mail@fnfmb.com</t>
+  </si>
+  <si>
+    <t>atip@fntc.ca</t>
+  </si>
+  <si>
+    <t>FPCATIP-AIPRPCPAC.CPAC@canada.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@sr-nr.gc.ca</t>
+  </si>
+  <si>
+    <t>mpoirier@glpa-apgl.com</t>
+  </si>
+  <si>
+    <t>snorrish@wlwb.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@porthalifax.ca</t>
+  </si>
+  <si>
+    <t>atip@hopaports.ca</t>
+  </si>
+  <si>
+    <t>access.informal-demandes.informelles@hc-sc.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@hfr-tgf.ca</t>
+  </si>
+  <si>
+    <t>pc.clmhc-hsmbc.pc@canada.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@iaac-aeic.gc.ca</t>
+  </si>
+  <si>
+    <t>ic.atip-aiprpa.ic@ised-isde.gc.ca</t>
+  </si>
+  <si>
+    <t>llahaie@idrc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@invcanada.ca</t>
+  </si>
+  <si>
+    <t>PortalSupport-Soutienportail@tbs-sct.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@infc.gc.ca</t>
+  </si>
+  <si>
+    <t>isabelle.henrie@innovation.ca</t>
+  </si>
+  <si>
+    <t>atip@irb-cisr.gc.ca</t>
   </si>
   <si>
     <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@acoa-apeca.gc.ca</t>
-  </si>
-  <si>
-    <t>igaudreault@aecl.ca</t>
-  </si>
-  <si>
-    <t>bbradley@atlanticpilotage.com</t>
-  </si>
-  <si>
-    <t>atip.coordinator@asiapacific.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@tribunal.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@bankofcanada.ca</t>
-  </si>
-  <si>
-    <t>sgustin@bctreaty.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@bdc.ca</t>
-  </si>
-  <si>
-    <t>moffitt@portofbelledune.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@cannor.gc.ca</t>
-  </si>
-  <si>
-    <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip@catsa.gc.ca</t>
-  </si>
-  <si>
-    <t>nancy.laframboise@cb-cda.gc.ca</t>
-  </si>
-  <si>
-    <t>Peter.Hull@cbc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@canadacouncil.ca</t>
-  </si>
-  <si>
-    <t>atip.aiprp@ccc.ca</t>
-  </si>
-  <si>
-    <t>atip_aiprp@ccohs.ca</t>
-  </si>
-  <si>
-    <t>priscilla.revolus@cdc-ccl.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cdic.ca</t>
-  </si>
-  <si>
-    <t>dec.aiprp-atip.ced@canada.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@cdev.ca</t>
-  </si>
-  <si>
-    <t>ATIPOffice-BureauAIPRP@neb-one.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-CFIA-AIPRP@inspection.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP.AIPRP@cfmws.com</t>
-  </si>
-  <si>
-    <t>atip-aiprp@grainscanada.gc.ca</t>
-  </si>
-  <si>
-    <t>atipcgf@cgf-fcc.ca</t>
-  </si>
-  <si>
-    <t>atip.aiprp@chrc-ccdp.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@cib-bic.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cic.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@college-ic.ca</t>
-  </si>
-  <si>
-    <t>ATIPCoordinator@cihr-irsc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@bch-mc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@clc-sic.ca</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@museedelhistoire.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cmhc.ca</t>
-  </si>
-  <si>
-    <t>atip@humanrights.ca</t>
-  </si>
-  <si>
-    <t>ablack@pier21.ca</t>
-  </si>
-  <si>
-    <t>kdoucette@nature.ca</t>
-  </si>
-  <si>
-    <t>TBennett@cnlopb.nl.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@cnsc-ccsn.gc.ca</t>
-  </si>
-  <si>
-    <t>atip@cnsoer.ca</t>
-  </si>
-  <si>
-    <t>adiaz@cpata-cabamc.ca</t>
-  </si>
-  <si>
-    <t>ATIP.AIPRP@crcc-ccetp.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
-  </si>
-  <si>
-    <t>INT-REC-G@cra-arc.gc.ca</t>
-  </si>
-  <si>
-    <t>atavassoli@crrf-fcrr.ca</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@crtc.gc.ca</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@asc-csa.gc.ca</t>
-  </si>
-  <si>
-    <t>CSC.ATIP-AIPRP.SCC@csc-scc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@cse-cst.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@smtp.gc.ca</t>
-  </si>
-  <si>
-    <t>atipaiprp@csps-efpc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@ingeniumcanada.org</t>
-  </si>
-  <si>
-    <t>OTC.AIPRP-ATIP.CTA@otc-cta.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@destinationcanada.com</t>
-  </si>
-  <si>
-    <t>atip-aiprp@cwa-aec.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@DCC-CDC.gc.ca</t>
-  </si>
-  <si>
-    <t>dcp@international.gc.ca</t>
-  </si>
-  <si>
-    <t>atipteam@edc.ca</t>
-  </si>
-  <si>
-    <t>atip-laiprp@dfo-mpo.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@forces.gc.ca</t>
-  </si>
-  <si>
-    <t>atip@northcrestdev.ca</t>
-  </si>
-  <si>
-    <t>ecatip-ecaiprp@ec.gc.ca</t>
-  </si>
-  <si>
-    <t>aiprp-atip@elections.ca</t>
-  </si>
-  <si>
-    <t>corporateandhrservices-servicesgenerauxetrh@erc-cee.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIPteam@edc.ca</t>
-  </si>
-  <si>
-    <t>info@federalbridge.ca</t>
-  </si>
-  <si>
-    <t>Nathalie.forester@fcac-acfc.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP_AIPRP@fcc-fac.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@feddevontario.gc.ca</t>
-  </si>
-  <si>
-    <t>fednor-atipinbox@ised-isde.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIPcontrol@freshwaterfish.com</t>
-  </si>
-  <si>
-    <t>fin.atip-aiprp.fin@canada.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@fintrac-canafe.gc.ca</t>
-  </si>
-  <si>
-    <t>mail@fnfmb.com</t>
-  </si>
-  <si>
-    <t>atip@fntc.ca</t>
-  </si>
-  <si>
-    <t>FPCATIP-AIPRPCPAC.CPAC@canada.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@sr-nr.gc.ca</t>
-  </si>
-  <si>
-    <t>mpoirier@glpa-apgl.com</t>
-  </si>
-  <si>
-    <t>snorrish@wlwb.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@porthalifax.ca</t>
-  </si>
-  <si>
-    <t>atip@hopaports.ca</t>
-  </si>
-  <si>
-    <t>access.informal-demandes.informelles@hc-sc.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@hfr-tgf.ca</t>
-  </si>
-  <si>
-    <t>pc.clmhc-hsmbc.pc@canada.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@iaac-aeic.gc.ca</t>
-  </si>
-  <si>
-    <t>ic.atip-aiprpa.ic@ised-isde.gc.ca</t>
-  </si>
-  <si>
-    <t>llahaie@idrc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@invcanada.ca</t>
-  </si>
-  <si>
-    <t>PortalSupport-Soutienportail@tbs-sct.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@infc.gc.ca</t>
-  </si>
-  <si>
-    <t>isabelle.henrie@innovation.ca</t>
-  </si>
-  <si>
-    <t>atip@irb-cisr.gc.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@pjcci.ca</t>
   </si>
   <si>
@@ -1976,9 +1949,6 @@
     <t>jean-frederic.boulais@oci-bec.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@ocl-cal.gc.ca</t>
-  </si>
-  <si>
     <t>AIPRP-ATIP@clo-ocol.gc.ca</t>
   </si>
   <si>
@@ -2162,42 +2132,42 @@
     <t>atip@yesab.ca</t>
   </si>
   <si>
+    <t>2016-09-23</t>
+  </si>
+  <si>
+    <t>2018-08-21</t>
+  </si>
+  <si>
+    <t>2023-09-16</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2021-01-09</t>
+  </si>
+  <si>
+    <t>2018-07-27</t>
+  </si>
+  <si>
+    <t>2019-07-13</t>
+  </si>
+  <si>
+    <t>2024-08-17</t>
+  </si>
+  <si>
+    <t>2023-11-09</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2023-03-28</t>
+  </si>
+  <si>
     <t>2025-09-09</t>
   </si>
   <si>
-    <t>2016-09-23</t>
-  </si>
-  <si>
-    <t>2018-08-21</t>
-  </si>
-  <si>
-    <t>2023-09-16</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2021-01-09</t>
-  </si>
-  <si>
-    <t>2018-07-27</t>
-  </si>
-  <si>
-    <t>2019-07-13</t>
-  </si>
-  <si>
-    <t>2024-08-17</t>
-  </si>
-  <si>
-    <t>2023-11-09</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2023-03-28</t>
-  </si>
-  <si>
     <t>2024-11-21</t>
   </si>
   <si>
@@ -2252,19 +2222,19 @@
     <t>2019-03-30</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>IRCC.Open-Ouvert.IRCC@cic.gc.ca</t>
@@ -3140,297 +3110,297 @@
     <col min="98" max="101" width="6.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" s="3" customFormat="1" ht="80" customHeight="1">
+    <row r="1" spans="1:101" s="3" customFormat="1" ht="80.25" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="AU1" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="AV1" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="AW1" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="AV1" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="AW1" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="AX1" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="AY1" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="AZ1" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="BA1" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="BB1" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="BC1" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="BD1" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="BE1" s="3" t="s">
-        <v>807</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -3758,7 +3728,7 @@
         <v>1516</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <v>12</v>
@@ -3956,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="BQ3" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BR3" s="1">
         <v>3</v>
@@ -4046,13 +4016,13 @@
         <v>46745</v>
       </c>
       <c r="CU3" s="1">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="CV3" s="1">
         <v>787</v>
       </c>
       <c r="CW3" s="1">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4455,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="AF5" s="2">
-        <v>898</v>
+        <v>291</v>
       </c>
       <c r="AG5" s="2">
         <v>608</v>
@@ -4659,7 +4629,7 @@
         <v>38</v>
       </c>
       <c r="CV5" s="1">
-        <v>983</v>
+        <v>376</v>
       </c>
       <c r="CW5" s="1">
         <v>830</v>
@@ -5786,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="BQ9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR9" s="1">
         <v>3</v>
@@ -5882,7 +5852,7 @@
         <v>56</v>
       </c>
       <c r="CW9" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7164,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U14" s="2">
         <v>0</v>
@@ -7221,7 +7191,7 @@
         <v>34</v>
       </c>
       <c r="AM14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="2">
         <v>9</v>
@@ -7305,7 +7275,7 @@
         <v>5</v>
       </c>
       <c r="BO14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP14" s="2">
         <v>1</v>
@@ -7365,7 +7335,7 @@
         <v>194</v>
       </c>
       <c r="CI14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ14" s="2">
         <v>63</v>
@@ -7401,10 +7371,10 @@
         <v>3164</v>
       </c>
       <c r="CU14" s="1">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="CV14" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="CW14" s="1">
         <v>231</v>
@@ -9978,13 +9948,13 @@
         <v>88</v>
       </c>
       <c r="AQ23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR23" s="2">
         <v>2</v>
       </c>
       <c r="AS23" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -10122,13 +10092,13 @@
         <v>52</v>
       </c>
       <c r="CM23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN23" s="2">
         <v>2</v>
       </c>
       <c r="CO23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP23" s="1">
         <v>0</v>
@@ -10146,13 +10116,13 @@
         <v>740</v>
       </c>
       <c r="CU23" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CV23" s="1">
         <v>27</v>
       </c>
       <c r="CW23" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -10723,7 +10693,7 @@
         <v>3</v>
       </c>
       <c r="CJ25" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CK25" s="2">
         <v>23</v>
@@ -10759,7 +10729,7 @@
         <v>3</v>
       </c>
       <c r="CV25" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW25" s="1">
         <v>23</v>
@@ -15133,7 +15103,7 @@
         <v>1</v>
       </c>
       <c r="AG40" s="2">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15337,7 +15307,7 @@
         <v>409</v>
       </c>
       <c r="CW40" s="1">
-        <v>2075</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16302,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="2">
         <v>19</v>
@@ -16554,7 +16524,7 @@
         <v>1035</v>
       </c>
       <c r="CV44" s="1">
-        <v>1138</v>
+        <v>1119</v>
       </c>
       <c r="CW44" s="1">
         <v>3043</v>
@@ -18398,7 +18368,7 @@
         <v>710</v>
       </c>
       <c r="C51" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2">
         <v>18</v>
@@ -18506,7 +18476,7 @@
         <v>190</v>
       </c>
       <c r="AM51" s="2">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="AN51" s="2">
         <v>158</v>
@@ -18518,7 +18488,7 @@
         <v>31</v>
       </c>
       <c r="AQ51" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AR51" s="2">
         <v>31</v>
@@ -18650,7 +18620,7 @@
         <v>2813</v>
       </c>
       <c r="CI51" s="2">
-        <v>1731</v>
+        <v>0</v>
       </c>
       <c r="CJ51" s="2">
         <v>1795</v>
@@ -18686,7 +18656,7 @@
         <v>3745</v>
       </c>
       <c r="CU51" s="1">
-        <v>1925</v>
+        <v>4</v>
       </c>
       <c r="CV51" s="1">
         <v>2002</v>
@@ -20240,7 +20210,7 @@
         <v>61</v>
       </c>
       <c r="G57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
         <v>3</v>
@@ -20516,7 +20486,7 @@
         <v>66</v>
       </c>
       <c r="CU57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV57" s="1">
         <v>3</v>
@@ -20548,7 +20518,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
@@ -20644,7 +20614,7 @@
         <v>0</v>
       </c>
       <c r="AN58" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO58" s="2">
         <v>9</v>
@@ -20788,7 +20758,7 @@
         <v>0</v>
       </c>
       <c r="CJ58" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CK58" s="2">
         <v>11</v>
@@ -20824,7 +20794,7 @@
         <v>0</v>
       </c>
       <c r="CV58" s="1">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="CW58" s="1">
         <v>31</v>
@@ -21448,7 +21418,7 @@
         <v>6432</v>
       </c>
       <c r="C61" s="2">
-        <v>-67</v>
+        <v>-59</v>
       </c>
       <c r="D61" s="2">
         <v>112</v>
@@ -21736,7 +21706,7 @@
         <v>65867</v>
       </c>
       <c r="CU61" s="1">
-        <v>-49</v>
+        <v>-41</v>
       </c>
       <c r="CV61" s="1">
         <v>357</v>
@@ -22058,7 +22028,7 @@
         <v>531</v>
       </c>
       <c r="C63" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2">
         <v>26</v>
@@ -22346,7 +22316,7 @@
         <v>2911</v>
       </c>
       <c r="CU63" s="1">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="CV63" s="1">
         <v>81</v>
@@ -22447,7 +22417,7 @@
         <v>2002</v>
       </c>
       <c r="AE64" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF64" s="2">
         <v>10</v>
@@ -22651,7 +22621,7 @@
         <v>8032</v>
       </c>
       <c r="CU64" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CV64" s="1">
         <v>121</v>
@@ -22815,7 +22785,7 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA65" s="2">
         <v>2</v>
@@ -22899,7 +22869,7 @@
         <v>0</v>
       </c>
       <c r="CB65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC65" s="2">
         <v>1</v>
@@ -22959,7 +22929,7 @@
         <v>39</v>
       </c>
       <c r="CV65" s="1">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CW65" s="1">
         <v>3492</v>
@@ -22979,7 +22949,7 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1">
         <v>12</v>
@@ -23003,7 +22973,7 @@
         <v>40</v>
       </c>
       <c r="M66" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="N66" s="1">
         <v>0</v>
@@ -23267,7 +23237,7 @@
         <v>46</v>
       </c>
       <c r="CW66" s="1">
-        <v>113</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:101">
@@ -23613,7 +23583,7 @@
         <v>2</v>
       </c>
       <c r="M68" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N68" s="1">
         <v>1092</v>
@@ -23703,7 +23673,7 @@
         <v>63</v>
       </c>
       <c r="AQ68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR68" s="2">
         <v>2</v>
@@ -23793,7 +23763,7 @@
         <v>1</v>
       </c>
       <c r="BU68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BV68" s="1">
         <v>0</v>
@@ -23835,7 +23805,7 @@
         <v>215</v>
       </c>
       <c r="CI68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ68" s="2">
         <v>3</v>
@@ -23871,13 +23841,13 @@
         <v>2133</v>
       </c>
       <c r="CU68" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV68" s="1">
         <v>11</v>
       </c>
       <c r="CW68" s="1">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24208,7 +24178,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" s="2">
         <v>3</v>
@@ -24319,7 +24289,7 @@
         <v>3</v>
       </c>
       <c r="AS70" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT70" s="1">
         <v>0</v>
@@ -24463,7 +24433,7 @@
         <v>1</v>
       </c>
       <c r="CO70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP70" s="1">
         <v>0</v>
@@ -24484,10 +24454,10 @@
         <v>7</v>
       </c>
       <c r="CV70" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="CW70" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -25443,7 +25413,7 @@
         <v>78</v>
       </c>
       <c r="M74" s="2">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="N74" s="1">
         <v>79173</v>
@@ -25452,7 +25422,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="2">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="2">
         <v>2444</v>
@@ -25665,13 +25635,13 @@
         <v>16228</v>
       </c>
       <c r="CI74" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="CJ74" s="2">
         <v>175</v>
       </c>
       <c r="CK74" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,13 +25671,13 @@
         <v>171817</v>
       </c>
       <c r="CU74" s="1">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="CV74" s="1">
-        <v>1775</v>
+        <v>743</v>
       </c>
       <c r="CW74" s="1">
-        <v>4374</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26059,7 +26029,7 @@
         <v>117545</v>
       </c>
       <c r="O76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" s="2">
         <v>907</v>
@@ -26254,7 +26224,7 @@
         <v>0</v>
       </c>
       <c r="CB76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC76" s="2">
         <v>1</v>
@@ -26311,10 +26281,10 @@
         <v>151140</v>
       </c>
       <c r="CU76" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="CV76" s="1">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="CW76" s="1">
         <v>3738</v>
@@ -26436,10 +26406,10 @@
         <v>1921</v>
       </c>
       <c r="AM77" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN77" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AO77" s="2">
         <v>69</v>
@@ -26559,7 +26529,7 @@
         <v>0</v>
       </c>
       <c r="CB77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC77" s="2">
         <v>2</v>
@@ -26580,7 +26550,7 @@
         <v>7369</v>
       </c>
       <c r="CI77" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="CJ77" s="2">
         <v>285</v>
@@ -26616,10 +26586,10 @@
         <v>390982</v>
       </c>
       <c r="CU77" s="1">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="CV77" s="1">
-        <v>10135</v>
+        <v>10131</v>
       </c>
       <c r="CW77" s="1">
         <v>15901</v>
@@ -26962,7 +26932,7 @@
         <v>4583</v>
       </c>
       <c r="K79" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L79" s="2">
         <v>128</v>
@@ -27025,7 +26995,7 @@
         <v>1</v>
       </c>
       <c r="AF79" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG79" s="2">
         <v>187</v>
@@ -27226,10 +27196,10 @@
         <v>90690</v>
       </c>
       <c r="CU79" s="1">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="CV79" s="1">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="CW79" s="1">
         <v>1900</v>
@@ -28164,7 +28134,7 @@
         <v>97</v>
       </c>
       <c r="E83" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -28185,7 +28155,7 @@
         <v>62</v>
       </c>
       <c r="L83" s="2">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="M83" s="2">
         <v>442</v>
@@ -28290,7 +28260,7 @@
         <v>71</v>
       </c>
       <c r="AU83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV83" s="2">
         <v>1</v>
@@ -28446,13 +28416,13 @@
         <v>423966</v>
       </c>
       <c r="CU83" s="1">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="CV83" s="1">
-        <v>888</v>
+        <v>837</v>
       </c>
       <c r="CW83" s="1">
-        <v>5484</v>
+        <v>5464</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29023,7 +28993,7 @@
         <v>0</v>
       </c>
       <c r="CJ85" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CK85" s="2">
         <v>38</v>
@@ -29059,7 +29029,7 @@
         <v>1</v>
       </c>
       <c r="CV85" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="CW85" s="1">
         <v>49</v>
@@ -29630,7 +29600,7 @@
         <v>2402</v>
       </c>
       <c r="CI87" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CJ87" s="2">
         <v>45</v>
@@ -29666,7 +29636,7 @@
         <v>2988</v>
       </c>
       <c r="CU87" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV87" s="1">
         <v>50</v>
@@ -29991,7 +29961,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="2">
         <v>4</v>
@@ -30000,7 +29970,7 @@
         <v>39</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="2">
         <v>2</v>
@@ -30015,7 +29985,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M89" s="2">
         <v>42</v>
@@ -30276,10 +30246,10 @@
         <v>2233</v>
       </c>
       <c r="CU89" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CV89" s="1">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="CW89" s="1">
         <v>170</v>
@@ -30712,7 +30682,7 @@
         <v>10</v>
       </c>
       <c r="AO91" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AP91" s="1">
         <v>26</v>
@@ -30856,7 +30826,7 @@
         <v>90</v>
       </c>
       <c r="CK91" s="2">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="CL91" s="1">
         <v>5</v>
@@ -30892,7 +30862,7 @@
         <v>414</v>
       </c>
       <c r="CW91" s="1">
-        <v>896</v>
+        <v>860</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -30906,7 +30876,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
@@ -30930,7 +30900,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2">
         <v>12</v>
@@ -31194,7 +31164,7 @@
         <v>2</v>
       </c>
       <c r="CV92" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="CW92" s="1">
         <v>93</v>
@@ -31415,7 +31385,7 @@
         <v>0</v>
       </c>
       <c r="BT93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU93" s="2">
         <v>1</v>
@@ -31499,7 +31469,7 @@
         <v>2</v>
       </c>
       <c r="CV93" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CW93" s="1">
         <v>66</v>
@@ -32135,7 +32105,7 @@
         <v>50</v>
       </c>
       <c r="G96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
         <v>3</v>
@@ -32411,7 +32381,7 @@
         <v>966</v>
       </c>
       <c r="CU96" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV96" s="1">
         <v>3</v>
@@ -33956,7 +33926,7 @@
         <v>85</v>
       </c>
       <c r="D102" s="2">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="E102" s="2">
         <v>750</v>
@@ -34043,7 +34013,7 @@
         <v>0</v>
       </c>
       <c r="AG102" s="2">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="AH102" s="1">
         <v>0</v>
@@ -34067,7 +34037,7 @@
         <v>5</v>
       </c>
       <c r="AO102" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP102" s="1">
         <v>36</v>
@@ -34211,7 +34181,7 @@
         <v>45</v>
       </c>
       <c r="CK102" s="2">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="CL102" s="1">
         <v>9</v>
@@ -34244,10 +34214,10 @@
         <v>124</v>
       </c>
       <c r="CV102" s="1">
-        <v>690</v>
+        <v>536</v>
       </c>
       <c r="CW102" s="1">
-        <v>1728</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -34366,7 +34336,7 @@
         <v>211</v>
       </c>
       <c r="AM103" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AN103" s="2">
         <v>25</v>
@@ -34510,7 +34480,7 @@
         <v>834</v>
       </c>
       <c r="CI103" s="2">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="CJ103" s="2">
         <v>162</v>
@@ -34546,7 +34516,7 @@
         <v>1087</v>
       </c>
       <c r="CU103" s="1">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="CV103" s="1">
         <v>190</v>
@@ -34988,7 +34958,7 @@
         <v>61</v>
       </c>
       <c r="AQ105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR105" s="2">
         <v>2</v>
@@ -35156,7 +35126,7 @@
         <v>8005</v>
       </c>
       <c r="CU105" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV105" s="1">
         <v>216</v>
@@ -35179,7 +35149,7 @@
         <v>192</v>
       </c>
       <c r="E106" s="2">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -35467,7 +35437,7 @@
         <v>1015</v>
       </c>
       <c r="CW106" s="1">
-        <v>2465</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36038,7 +36008,7 @@
         <v>1</v>
       </c>
       <c r="CJ108" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CK108" s="2">
         <v>18</v>
@@ -36074,7 +36044,7 @@
         <v>2</v>
       </c>
       <c r="CV108" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CW108" s="1">
         <v>51</v>
@@ -36432,7 +36402,7 @@
         <v>1</v>
       </c>
       <c r="P110" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="2">
         <v>62</v>
@@ -36684,7 +36654,7 @@
         <v>102</v>
       </c>
       <c r="CV110" s="1">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="CW110" s="1">
         <v>1046</v>
@@ -36710,7 +36680,7 @@
         <v>72</v>
       </c>
       <c r="G111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2">
         <v>2</v>
@@ -36986,7 +36956,7 @@
         <v>780</v>
       </c>
       <c r="CU111" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CV111" s="1">
         <v>29</v>
@@ -37332,7 +37302,7 @@
         <v>4800</v>
       </c>
       <c r="K113" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2">
         <v>161</v>
@@ -37596,7 +37566,7 @@
         <v>175161</v>
       </c>
       <c r="CU113" s="1">
-        <v>1348</v>
+        <v>1310</v>
       </c>
       <c r="CV113" s="1">
         <v>1710</v>
@@ -38223,7 +38193,7 @@
         <v>4427</v>
       </c>
       <c r="C116" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D116" s="2">
         <v>27</v>
@@ -38337,7 +38307,7 @@
         <v>6</v>
       </c>
       <c r="AO116" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AP116" s="1">
         <v>28</v>
@@ -38355,10 +38325,10 @@
         <v>66</v>
       </c>
       <c r="AU116" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW116" s="2">
         <v>12</v>
@@ -38367,7 +38337,7 @@
         <v>4</v>
       </c>
       <c r="AY116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" s="2">
         <v>1</v>
@@ -38481,7 +38451,7 @@
         <v>51</v>
       </c>
       <c r="CK116" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="CL116" s="1">
         <v>12</v>
@@ -38511,13 +38481,13 @@
         <v>21820</v>
       </c>
       <c r="CU116" s="1">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="CV116" s="1">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="CW116" s="1">
-        <v>1157</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38570,7 +38540,7 @@
         <v>0</v>
       </c>
       <c r="Q117" s="2">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="R117" s="1">
         <v>0</v>
@@ -38822,7 +38792,7 @@
         <v>388</v>
       </c>
       <c r="CW117" s="1">
-        <v>1300</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -42493,7 +42463,7 @@
         <v>79</v>
       </c>
       <c r="C130" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D130" s="2">
         <v>4</v>
@@ -42505,7 +42475,7 @@
         <v>55</v>
       </c>
       <c r="G130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="2">
         <v>1</v>
@@ -42781,7 +42751,7 @@
         <v>1099</v>
       </c>
       <c r="CU130" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CV130" s="1">
         <v>132</v>
@@ -44057,7 +44027,7 @@
         <v>0</v>
       </c>
       <c r="P135" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q135" s="2">
         <v>973</v>
@@ -44309,7 +44279,7 @@
         <v>120</v>
       </c>
       <c r="CV135" s="1">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="CW135" s="1">
         <v>2690</v>
@@ -44575,7 +44545,7 @@
         <v>390</v>
       </c>
       <c r="CI136" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CJ136" s="2">
         <v>14</v>
@@ -44611,7 +44581,7 @@
         <v>158870</v>
       </c>
       <c r="CU136" s="1">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="CV136" s="1">
         <v>5074</v>
@@ -44628,7 +44598,7 @@
         <v>163</v>
       </c>
       <c r="C137" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D137" s="2">
         <v>25</v>
@@ -44652,7 +44622,7 @@
         <v>44</v>
       </c>
       <c r="K137" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L137" s="2">
         <v>5</v>
@@ -44916,7 +44886,7 @@
         <v>663</v>
       </c>
       <c r="CU137" s="1">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="CV137" s="1">
         <v>34</v>
@@ -45609,7 +45579,7 @@
         <v>0</v>
       </c>
       <c r="Y140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z140" s="1">
         <v>0</v>
@@ -45837,7 +45807,7 @@
         <v>10</v>
       </c>
       <c r="CW140" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -46778,7 +46748,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" s="2">
         <v>3</v>
@@ -46883,7 +46853,7 @@
         <v>61</v>
       </c>
       <c r="AQ144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR144" s="2">
         <v>2</v>
@@ -47027,7 +46997,7 @@
         <v>70</v>
       </c>
       <c r="CM144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN144" s="2">
         <v>2</v>
@@ -47051,10 +47021,10 @@
         <v>1191</v>
       </c>
       <c r="CU144" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV144" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CW144" s="1">
         <v>41</v>
@@ -48408,7 +48378,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR149" s="2">
         <v>3</v>
@@ -48540,7 +48510,7 @@
         <v>166</v>
       </c>
       <c r="CI149" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ149" s="2">
         <v>6</v>
@@ -48576,7 +48546,7 @@
         <v>908</v>
       </c>
       <c r="CU149" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV149" s="1">
         <v>24</v>
@@ -50328,7 +50298,7 @@
         <v>1</v>
       </c>
       <c r="BU155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV155" s="1">
         <v>2</v>
@@ -50412,7 +50382,7 @@
         <v>45</v>
       </c>
       <c r="CW155" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50447,13 +50417,13 @@
         <v>2066</v>
       </c>
       <c r="K156" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2">
         <v>50</v>
       </c>
       <c r="M156" s="2">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="N156" s="1">
         <v>61027</v>
@@ -50711,13 +50681,13 @@
         <v>71529</v>
       </c>
       <c r="CU156" s="1">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="CV156" s="1">
         <v>1058</v>
       </c>
       <c r="CW156" s="1">
-        <v>2528</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -51951,7 +51921,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="2">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E161" s="2">
         <v>95</v>
@@ -52062,7 +52032,7 @@
         <v>11</v>
       </c>
       <c r="AO161" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP161" s="1">
         <v>35</v>
@@ -52206,7 +52176,7 @@
         <v>21</v>
       </c>
       <c r="CK161" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="CL161" s="1">
         <v>14</v>
@@ -52239,10 +52209,10 @@
         <v>32</v>
       </c>
       <c r="CV161" s="1">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="CW161" s="1">
-        <v>1252</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -53599,7 +53569,7 @@
         <v>2</v>
       </c>
       <c r="AS166" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT166" s="1">
         <v>0</v>
@@ -53731,7 +53701,7 @@
         <v>7</v>
       </c>
       <c r="CK166" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CL166" s="1">
         <v>32</v>
@@ -53767,7 +53737,7 @@
         <v>114</v>
       </c>
       <c r="CW166" s="1">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54113,7 +54083,7 @@
         <v>34</v>
       </c>
       <c r="M168" s="2">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="N168" s="1">
         <v>419</v>
@@ -54203,7 +54173,7 @@
         <v>35</v>
       </c>
       <c r="AQ168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR168" s="2">
         <v>2</v>
@@ -54335,7 +54305,7 @@
         <v>438</v>
       </c>
       <c r="CI168" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CJ168" s="2">
         <v>24</v>
@@ -54371,13 +54341,13 @@
         <v>5975</v>
       </c>
       <c r="CU168" s="1">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="CV168" s="1">
         <v>114</v>
       </c>
       <c r="CW168" s="1">
-        <v>547</v>
+        <v>516</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54693,7 +54663,7 @@
         <v>4574</v>
       </c>
       <c r="C170" s="2">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D170" s="2">
         <v>99</v>
@@ -54981,7 +54951,7 @@
         <v>19650</v>
       </c>
       <c r="CU170" s="1">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="CV170" s="1">
         <v>495</v>
@@ -57169,13 +57139,13 @@
         <v>73111</v>
       </c>
       <c r="O178" s="2">
-        <v>-364</v>
+        <v>-1</v>
       </c>
       <c r="P178" s="2">
         <v>1965</v>
       </c>
       <c r="Q178" s="2">
-        <v>4113</v>
+        <v>4114</v>
       </c>
       <c r="R178" s="1">
         <v>0</v>
@@ -57421,13 +57391,13 @@
         <v>84919</v>
       </c>
       <c r="CU178" s="1">
-        <v>-308</v>
+        <v>55</v>
       </c>
       <c r="CV178" s="1">
         <v>2163</v>
       </c>
       <c r="CW178" s="1">
-        <v>4593</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57833,7 +57803,7 @@
         <v>0</v>
       </c>
       <c r="AG180" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AH180" s="1">
         <v>1</v>
@@ -57851,7 +57821,7 @@
         <v>975</v>
       </c>
       <c r="AM180" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN180" s="2">
         <v>6</v>
@@ -57941,7 +57911,7 @@
         <v>44</v>
       </c>
       <c r="BQ180" s="2">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="BR180" s="1">
         <v>34</v>
@@ -57953,7 +57923,7 @@
         <v>1</v>
       </c>
       <c r="BU180" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV180" s="1">
         <v>0</v>
@@ -57995,7 +57965,7 @@
         <v>2049</v>
       </c>
       <c r="CI180" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ180" s="2">
         <v>32</v>
@@ -58031,13 +58001,13 @@
         <v>51287</v>
       </c>
       <c r="CU180" s="1">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="CV180" s="1">
         <v>1270</v>
       </c>
       <c r="CW180" s="1">
-        <v>2718</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -59535,7 +59505,7 @@
         <v>0</v>
       </c>
       <c r="CN185" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO185" s="2">
         <v>4</v>
@@ -59559,7 +59529,7 @@
         <v>1</v>
       </c>
       <c r="CV185" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW185" s="1">
         <v>16</v>
@@ -62013,7 +61983,7 @@
         <v>1628</v>
       </c>
       <c r="C194" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D194" s="2">
         <v>26</v>
@@ -62301,7 +62271,7 @@
         <v>32902</v>
       </c>
       <c r="CU194" s="1">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="CV194" s="1">
         <v>602</v>
@@ -62570,7 +62540,7 @@
         <v>518</v>
       </c>
       <c r="CI195" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ195" s="2">
         <v>16</v>
@@ -62606,7 +62576,7 @@
         <v>71201</v>
       </c>
       <c r="CU195" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CV195" s="1">
         <v>3370</v>
@@ -62653,7 +62623,7 @@
         <v>18</v>
       </c>
       <c r="M196" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N196" s="1">
         <v>3415</v>
@@ -62917,7 +62887,7 @@
         <v>94</v>
       </c>
       <c r="CW196" s="1">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -65781,7 +65751,7 @@
         <v>39</v>
       </c>
       <c r="AM206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN206" s="2">
         <v>2</v>
@@ -65937,7 +65907,7 @@
         <v>35</v>
       </c>
       <c r="CM206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN206" s="2">
         <v>1</v>
@@ -65961,7 +65931,7 @@
         <v>1240</v>
       </c>
       <c r="CU206" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CV206" s="1">
         <v>27</v>
@@ -67922,7 +67892,7 @@
         <v>6</v>
       </c>
       <c r="AO213" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP213" s="1">
         <v>3</v>
@@ -68066,7 +68036,7 @@
         <v>6</v>
       </c>
       <c r="CK213" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CL213" s="1">
         <v>0</v>
@@ -68102,7 +68072,7 @@
         <v>16</v>
       </c>
       <c r="CW213" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="214" spans="1:101">
@@ -68417,7 +68387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -68445,2279 +68415,2276 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="F2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F3" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D4">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F4" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F5" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F6" t="s">
-        <v>748</v>
-      </c>
-      <c r="G6" t="s">
-        <v>537</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F7" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="F8" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F9" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
-      <c r="C10" t="s">
-        <v>541</v>
-      </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F10" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="F11" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F12" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="F13" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F14" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
+      <c r="C15" t="s">
+        <v>539</v>
+      </c>
       <c r="D15">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F15" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="F16" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F17" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F18" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F19" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F20" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F21" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F22" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F23" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="F24" t="s">
-        <v>749</v>
+        <v>736</v>
+      </c>
+      <c r="G24" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F25" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F26" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>281</v>
       </c>
       <c r="E27" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F27" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="F28" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="F29" t="s">
-        <v>749</v>
-      </c>
-      <c r="G29" t="s">
-        <v>533</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="F30" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D31">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F31" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D32">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F32" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B33" t="s">
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="F33" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F34" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
         <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="F35" t="s">
-        <v>748</v>
+        <v>739</v>
+      </c>
+      <c r="G35" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
         <v>354</v>
       </c>
       <c r="C36" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="F36" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B37" t="s">
         <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="F37" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B38" t="s">
         <v>356</v>
       </c>
-      <c r="C38" t="s">
-        <v>563</v>
-      </c>
       <c r="D38">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F38" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="F39" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
         <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="D40">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E40" t="s">
         <v>716</v>
       </c>
       <c r="F40" t="s">
-        <v>746</v>
-      </c>
-      <c r="G40" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="F41" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
         <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="F42" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
         <v>361</v>
       </c>
+      <c r="C43" t="s">
+        <v>558</v>
+      </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F43" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="D44">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F44" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
         <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="F45" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B46" t="s">
         <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E46" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F46" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s">
         <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F47" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
         <v>366</v>
       </c>
       <c r="C48" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F48" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B49" t="s">
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F49" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B50" t="s">
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F50" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s">
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D51">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="E51" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F51" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s">
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F52" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="F53" t="s">
-        <v>748</v>
+        <v>736</v>
+      </c>
+      <c r="G53" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E54" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F54" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B55" t="s">
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F55" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D56">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="E56" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F56" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F57" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="F58" t="s">
-        <v>749</v>
-      </c>
-      <c r="G58" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B59" t="s">
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D59">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="E59" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F59" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B60" t="s">
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="E60" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F60" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B61" t="s">
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D61">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E61" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F61" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B62" t="s">
         <v>380</v>
       </c>
       <c r="C62" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="F62" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B63" t="s">
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D63">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F63" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B64" t="s">
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="D64">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F64" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D65">
-        <v>284</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F65" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="D66">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F66" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B67" t="s">
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F67" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B68" t="s">
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F68" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B69" t="s">
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>2240</v>
       </c>
       <c r="E69" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F69" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B70" t="s">
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F70" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B71" t="s">
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="E71" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F71" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
       <c r="F72" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B73" t="s">
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="F73" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B74" t="s">
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D74">
-        <v>2240</v>
+        <v>1216</v>
       </c>
       <c r="E74" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F74" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B75" t="s">
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>728</v>
+        <v>705</v>
       </c>
       <c r="F75" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B76" t="s">
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D76">
-        <v>927</v>
+        <v>55</v>
       </c>
       <c r="E76" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F76" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B77" t="s">
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D77">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F77" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B78" t="s">
         <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>598</v>
+        <v>535</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="E78" t="s">
-        <v>729</v>
+        <v>705</v>
       </c>
       <c r="F78" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B79" t="s">
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="D79">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F79" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B80" t="s">
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D80">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F80" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B81" t="s">
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D81">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E81" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F81" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B82" t="s">
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F82" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B83" t="s">
         <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>546</v>
+        <v>596</v>
       </c>
       <c r="D83">
-        <v>269</v>
+        <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F83" t="s">
-        <v>749</v>
+        <v>737</v>
+      </c>
+      <c r="G83" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B84" t="s">
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E84" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F84" t="s">
-        <v>749</v>
+        <v>737</v>
+      </c>
+      <c r="G84" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B85" t="s">
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D85">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F85" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
       </c>
       <c r="C86" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D86">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="E86" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F86" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B87" t="s">
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E87" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F87" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B88" t="s">
         <v>406</v>
       </c>
-      <c r="C88" t="s">
-        <v>606</v>
-      </c>
       <c r="D88">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F88" t="s">
-        <v>747</v>
-      </c>
-      <c r="G88" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B89" t="s">
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D89">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="F89" t="s">
-        <v>747</v>
-      </c>
-      <c r="G89" t="s">
-        <v>607</v>
+        <v>736</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B90" t="s">
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F90" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s">
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D91">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F91" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D92">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F92" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B93" t="s">
         <v>411</v>
       </c>
+      <c r="C93" t="s">
+        <v>605</v>
+      </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F93" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B94" t="s">
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="F94" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B95" t="s">
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F95" t="s">
-        <v>749</v>
+        <v>736</v>
+      </c>
+      <c r="G95" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F96" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s">
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>2987</v>
       </c>
       <c r="E97" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F97" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B98" t="s">
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="F98" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B99" t="s">
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="F99" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B100" t="s">
         <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E100" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F100" t="s">
-        <v>749</v>
-      </c>
-      <c r="G100" t="s">
-        <v>617</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B101" t="s">
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E101" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F101" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B102" t="s">
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D102">
-        <v>2987</v>
+        <v>2</v>
       </c>
       <c r="E102" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F102" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B103" t="s">
         <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="F103" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B104" t="s">
         <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="F104" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B105" t="s">
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D105">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F105" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B106" t="s">
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D106">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F106" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B107" t="s">
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D107">
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F107" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E108" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="F108" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s">
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>733</v>
+        <v>705</v>
       </c>
       <c r="F109" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B110" t="s">
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="D110">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="F110" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B111" t="s">
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="E111" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F111" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B112" t="s">
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="E112" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F112" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B113" t="s">
         <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>535</v>
+        <v>624</v>
       </c>
       <c r="D113">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>734</v>
+        <v>705</v>
       </c>
       <c r="F113" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F114" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B115" t="s">
         <v>433</v>
@@ -70726,2011 +70693,1891 @@
         <v>626</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
+        <v>705</v>
+      </c>
+      <c r="F115" t="s">
         <v>735</v>
-      </c>
-      <c r="F115" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B116" t="s">
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>631</v>
+        <v>606</v>
       </c>
       <c r="D116">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F116" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B117" t="s">
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D117">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F117" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B118" t="s">
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F118" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B119" t="s">
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F119" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B120" t="s">
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D120">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F120" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B121" t="s">
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F121" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B122" t="s">
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F122" t="s">
-        <v>749</v>
+        <v>735</v>
+      </c>
+      <c r="G122" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B123" t="s">
         <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F123" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B124" t="s">
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F124" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B125" t="s">
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F125" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F126" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B127" t="s">
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D127">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F127" t="s">
-        <v>748</v>
-      </c>
-      <c r="G127" t="s">
-        <v>641</v>
+        <v>736</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B128" t="s">
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F128" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B129" t="s">
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D129">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E129" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F129" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B130" t="s">
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>10256</v>
       </c>
       <c r="E130" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F130" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B131" t="s">
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E131" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F131" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B132" t="s">
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="F132" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B133" t="s">
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="E133" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F133" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B134" t="s">
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>648</v>
+        <v>590</v>
       </c>
       <c r="D134">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E134" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="F134" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B135" t="s">
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D135">
-        <v>10256</v>
+        <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F135" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B136" t="s">
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E136" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F136" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B137" t="s">
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E137" t="s">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="F137" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B138" t="s">
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D138">
-        <v>374</v>
+        <v>4</v>
       </c>
       <c r="E138" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F138" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B139" t="s">
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E139" t="s">
+        <v>705</v>
+      </c>
+      <c r="F139" t="s">
         <v>737</v>
       </c>
-      <c r="F139" t="s">
-        <v>749</v>
-      </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B140" t="s">
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>652</v>
+        <v>559</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F140" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B141" t="s">
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D141">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F141" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B142" t="s">
         <v>460</v>
       </c>
       <c r="C142" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D142">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F142" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B143" t="s">
         <v>461</v>
       </c>
-      <c r="C143" t="s">
-        <v>655</v>
-      </c>
       <c r="D143">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F143" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B144" t="s">
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F144" t="s">
-        <v>749</v>
+        <v>736</v>
+      </c>
+      <c r="G144" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B145" t="s">
         <v>463</v>
       </c>
       <c r="C145" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D145">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="F145" t="s">
-        <v>747</v>
+        <v>736</v>
+      </c>
+      <c r="G145" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B146" t="s">
         <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>569</v>
+        <v>652</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="F146" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B147" t="s">
         <v>465</v>
       </c>
       <c r="C147" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F147" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B148" t="s">
         <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>659</v>
+        <v>533</v>
       </c>
       <c r="D148">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F148" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B149" t="s">
         <v>467</v>
       </c>
+      <c r="C149" t="s">
+        <v>654</v>
+      </c>
       <c r="D149">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F149" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s">
         <v>468</v>
       </c>
       <c r="C150" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="E150" t="s">
+        <v>705</v>
+      </c>
+      <c r="F150" t="s">
         <v>738</v>
-      </c>
-      <c r="F150" t="s">
-        <v>749</v>
-      </c>
-      <c r="G150" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B151" t="s">
         <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="E151" t="s">
+        <v>705</v>
+      </c>
+      <c r="F151" t="s">
         <v>739</v>
-      </c>
-      <c r="F151" t="s">
-        <v>749</v>
-      </c>
-      <c r="G151" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
         <v>470</v>
       </c>
       <c r="C152" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D152">
         <v>5</v>
       </c>
       <c r="E152" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="F152" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
         <v>471</v>
       </c>
       <c r="C153" t="s">
-        <v>663</v>
+        <v>558</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F153" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
         <v>472</v>
       </c>
       <c r="C154" t="s">
-        <v>544</v>
+        <v>658</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F154" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B155" t="s">
         <v>473</v>
       </c>
       <c r="C155" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D155">
-        <v>19</v>
+        <v>761</v>
       </c>
       <c r="E155" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F155" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B156" t="s">
         <v>474</v>
       </c>
       <c r="C156" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D156">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="E156" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="F156" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B157" t="s">
         <v>475</v>
       </c>
       <c r="C157" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D157">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="E157" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F157" t="s">
-        <v>746</v>
+        <v>737</v>
+      </c>
+      <c r="G157" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B158" t="s">
         <v>476</v>
       </c>
       <c r="C158" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F158" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B159" t="s">
         <v>477</v>
       </c>
       <c r="C159" t="s">
-        <v>568</v>
+        <v>662</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F159" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B160" t="s">
         <v>478</v>
       </c>
       <c r="C160" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F160" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B161" t="s">
         <v>479</v>
       </c>
       <c r="C161" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="D161">
-        <v>761</v>
+        <v>0</v>
       </c>
       <c r="E161" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F161" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B162" t="s">
         <v>480</v>
       </c>
       <c r="C162" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="F162" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B163" t="s">
         <v>481</v>
       </c>
       <c r="C163" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D163">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E163" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="F163" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="G163" t="s">
-        <v>755</v>
+        <v>666</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B164" t="s">
         <v>482</v>
       </c>
       <c r="C164" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F164" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B165" t="s">
         <v>483</v>
       </c>
       <c r="C165" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="E165" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F165" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B166" t="s">
         <v>484</v>
       </c>
       <c r="C166" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F166" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B167" t="s">
         <v>485</v>
       </c>
       <c r="C167" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F167" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B168" t="s">
         <v>486</v>
       </c>
       <c r="C168" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D168">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E168" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="F168" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B169" t="s">
         <v>487</v>
       </c>
       <c r="C169" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>742</v>
+        <v>705</v>
       </c>
       <c r="F169" t="s">
-        <v>749</v>
-      </c>
-      <c r="G169" t="s">
-        <v>676</v>
+        <v>736</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B170" t="s">
         <v>488</v>
       </c>
       <c r="C170" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D170">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F170" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B171" t="s">
         <v>489</v>
       </c>
       <c r="C171" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D171">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F171" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B172" t="s">
         <v>490</v>
       </c>
       <c r="C172" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="E172" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F172" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B173" t="s">
         <v>491</v>
       </c>
       <c r="C173" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F173" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B174" t="s">
         <v>492</v>
       </c>
       <c r="C174" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="E174" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F174" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B175" t="s">
         <v>493</v>
       </c>
       <c r="C175" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D175">
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F175" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B176" t="s">
         <v>494</v>
       </c>
       <c r="C176" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E176" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F176" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B177" t="s">
         <v>495</v>
       </c>
-      <c r="C177" t="s">
-        <v>684</v>
-      </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F177" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B178" t="s">
         <v>496</v>
       </c>
       <c r="C178" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="D178">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F178" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B179" t="s">
         <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>686</v>
+        <v>593</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F179" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B180" t="s">
         <v>498</v>
       </c>
       <c r="C180" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D180">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F180" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B181" t="s">
         <v>499</v>
       </c>
       <c r="C181" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F181" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B182" t="s">
         <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D182">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F182" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B183" t="s">
         <v>501</v>
       </c>
+      <c r="C183" t="s">
+        <v>684</v>
+      </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F183" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B184" t="s">
         <v>502</v>
       </c>
       <c r="C184" t="s">
-        <v>690</v>
+        <v>606</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="F184" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B185" t="s">
         <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>603</v>
+        <v>685</v>
       </c>
       <c r="D185">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E185" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F185" t="s">
-        <v>749</v>
+        <v>737</v>
+      </c>
+      <c r="G185" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B186" t="s">
         <v>504</v>
       </c>
       <c r="C186" t="s">
-        <v>691</v>
+        <v>604</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E186" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F186" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B187" t="s">
         <v>505</v>
       </c>
       <c r="C187" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F187" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B188" t="s">
         <v>506</v>
       </c>
       <c r="C188" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="E188" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F188" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B189" t="s">
         <v>507</v>
       </c>
       <c r="C189" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E189" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F189" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B190" t="s">
         <v>508</v>
       </c>
       <c r="C190" t="s">
-        <v>616</v>
+        <v>689</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>10268</v>
       </c>
       <c r="E190" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="F190" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B191" t="s">
         <v>509</v>
       </c>
       <c r="C191" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E191" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="F191" t="s">
-        <v>747</v>
-      </c>
-      <c r="G191" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B192" t="s">
         <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>614</v>
+        <v>691</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F192" t="s">
-        <v>749</v>
+        <v>736</v>
+      </c>
+      <c r="G192" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B193" t="s">
         <v>511</v>
       </c>
       <c r="C193" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F193" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B194" t="s">
         <v>512</v>
       </c>
       <c r="C194" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D194">
-        <v>116</v>
+        <v>315</v>
       </c>
       <c r="E194" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F194" t="s">
-        <v>747</v>
+        <v>736</v>
+      </c>
+      <c r="G194" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B195" t="s">
         <v>513</v>
       </c>
       <c r="C195" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E195" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F195" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B196" t="s">
         <v>514</v>
       </c>
       <c r="C196" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D196">
-        <v>10268</v>
+        <v>7</v>
       </c>
       <c r="E196" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F196" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B197" t="s">
         <v>515</v>
       </c>
       <c r="C197" t="s">
-        <v>700</v>
+        <v>544</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="F197" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B198" t="s">
         <v>516</v>
       </c>
       <c r="C198" t="s">
-        <v>701</v>
+        <v>544</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="F198" t="s">
-        <v>749</v>
-      </c>
-      <c r="G198" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B199" t="s">
         <v>517</v>
       </c>
       <c r="C199" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F199" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B200" t="s">
         <v>518</v>
       </c>
       <c r="C200" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D200">
-        <v>315</v>
+        <v>442</v>
       </c>
       <c r="E200" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F200" t="s">
-        <v>749</v>
-      </c>
-      <c r="G200" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B201" t="s">
         <v>519</v>
       </c>
       <c r="C201" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D201">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E201" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F201" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B202" t="s">
         <v>520</v>
       </c>
       <c r="C202" t="s">
+        <v>699</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
         <v>705</v>
       </c>
-      <c r="D202">
-        <v>7</v>
-      </c>
-      <c r="E202" t="s">
-        <v>716</v>
-      </c>
       <c r="F202" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B203" t="s">
         <v>521</v>
       </c>
       <c r="C203" t="s">
-        <v>533</v>
+        <v>700</v>
       </c>
       <c r="D203">
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>743</v>
+        <v>705</v>
       </c>
       <c r="F203" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B204" t="s">
         <v>522</v>
       </c>
       <c r="C204" t="s">
-        <v>533</v>
+        <v>701</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E204" t="s">
-        <v>743</v>
+        <v>705</v>
       </c>
       <c r="F204" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B205" t="s">
         <v>523</v>
       </c>
       <c r="C205" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E205" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="F205" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B206" t="s">
         <v>524</v>
       </c>
       <c r="C206" t="s">
-        <v>707</v>
+        <v>665</v>
       </c>
       <c r="D206">
-        <v>442</v>
+        <v>18</v>
       </c>
       <c r="E206" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F206" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B207" t="s">
         <v>525</v>
       </c>
       <c r="C207" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D207">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F207" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B208" t="s">
         <v>526</v>
       </c>
       <c r="C208" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F208" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
-        <v>308</v>
-      </c>
-      <c r="B209" t="s">
-        <v>527</v>
-      </c>
-      <c r="C209" t="s">
-        <v>710</v>
-      </c>
-      <c r="D209">
-        <v>0</v>
-      </c>
-      <c r="E209" t="s">
-        <v>716</v>
-      </c>
-      <c r="F209" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
-        <v>309</v>
-      </c>
-      <c r="B210" t="s">
-        <v>528</v>
-      </c>
-      <c r="C210" t="s">
-        <v>711</v>
-      </c>
-      <c r="D210">
-        <v>23</v>
-      </c>
-      <c r="E210" t="s">
-        <v>716</v>
-      </c>
-      <c r="F210" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
-        <v>310</v>
-      </c>
-      <c r="B211" t="s">
-        <v>529</v>
-      </c>
-      <c r="C211" t="s">
-        <v>712</v>
-      </c>
-      <c r="D211">
-        <v>27</v>
-      </c>
-      <c r="E211" t="s">
-        <v>744</v>
-      </c>
-      <c r="F211" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
-        <v>311</v>
-      </c>
-      <c r="B212" t="s">
-        <v>530</v>
-      </c>
-      <c r="C212" t="s">
-        <v>675</v>
-      </c>
-      <c r="D212">
-        <v>18</v>
-      </c>
-      <c r="E212" t="s">
-        <v>716</v>
-      </c>
-      <c r="F212" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
-        <v>312</v>
-      </c>
-      <c r="B213" t="s">
-        <v>531</v>
-      </c>
-      <c r="C213" t="s">
-        <v>713</v>
-      </c>
-      <c r="D213">
-        <v>2</v>
-      </c>
-      <c r="E213" t="s">
-        <v>716</v>
-      </c>
-      <c r="F213" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
-        <v>313</v>
-      </c>
-      <c r="B214" t="s">
-        <v>532</v>
-      </c>
-      <c r="C214" t="s">
-        <v>714</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="E214" t="s">
-        <v>716</v>
-      </c>
-      <c r="F214" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="842">
   <si>
     <t>ati_all</t>
   </si>
@@ -977,6 +977,21 @@
     <t>opengov_email</t>
   </si>
   <si>
+    <t>16342451 Canada Inc.  | 16342451 Canada Inc</t>
+  </si>
+  <si>
+    <t>Agriculture and Agri-Food Canada | Agriculture et Agroalimentaire Canada</t>
+  </si>
+  <si>
+    <t>Crown-Indigenous Relations and Northern Affairs Canada | Relations Couronne-Autochtones et Affaires du Nord Canada</t>
+  </si>
+  <si>
+    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
+  </si>
+  <si>
+    <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
+  </si>
+  <si>
     <t>Atlantic Pilotage Authority Canada | Administration de pilotage de l'Atlantique Canada</t>
   </si>
   <si>
@@ -1379,6 +1394,9 @@
     <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
   </si>
   <si>
+    <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
+  </si>
+  <si>
     <t>Office of the Commissioner of Official Languages | Commissariat aux langues officielles</t>
   </si>
   <si>
@@ -1598,6 +1616,21 @@
     <t>Yukon Environmental and Socio-economic Assessment Board | Office d’évaluation environnementale et socio-économique du Yukon</t>
   </si>
   <si>
+    <t>atip-aiprp@cdev.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@agr.gc.ca</t>
+  </si>
+  <si>
+    <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@acoa-apeca.gc.ca</t>
+  </si>
+  <si>
+    <t>igaudreault@aecl.ca</t>
+  </si>
+  <si>
     <t>bbradley@atlanticpilotage.com</t>
   </si>
   <si>
@@ -1649,9 +1682,6 @@
     <t>priscilla.revolus@cdc-ccl.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@cdev.gc.ca</t>
-  </si>
-  <si>
     <t>ATIP-AIPRP@cdic.ca</t>
   </si>
   <si>
@@ -1877,9 +1907,6 @@
     <t>atip@irb-cisr.gc.ca</t>
   </si>
   <si>
-    <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
-  </si>
-  <si>
     <t>atip-aiprp@pjcci.ca</t>
   </si>
   <si>
@@ -1949,6 +1976,9 @@
     <t>jean-frederic.boulais@oci-bec.gc.ca</t>
   </si>
   <si>
+    <t>atip-aiprp@ocl-cal.gc.ca</t>
+  </si>
+  <si>
     <t>AIPRP-ATIP@clo-ocol.gc.ca</t>
   </si>
   <si>
@@ -2132,6 +2162,9 @@
     <t>atip@yesab.ca</t>
   </si>
   <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
     <t>2016-09-23</t>
   </si>
   <si>
@@ -2165,9 +2198,6 @@
     <t>2023-03-28</t>
   </si>
   <si>
-    <t>2025-09-09</t>
-  </si>
-  <si>
     <t>2024-11-21</t>
   </si>
   <si>
@@ -2222,19 +2252,19 @@
     <t>2019-03-30</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>IRCC.Open-Ouvert.IRCC@cic.gc.ca</t>
@@ -3115,292 +3145,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>777</v>
+        <v>787</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -3815,7 +3845,7 @@
         <v>2</v>
       </c>
       <c r="AF3" s="2">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="AG3" s="2">
         <v>727</v>
@@ -4019,7 +4049,7 @@
         <v>63</v>
       </c>
       <c r="CV3" s="1">
-        <v>787</v>
+        <v>495</v>
       </c>
       <c r="CW3" s="1">
         <v>2040</v>
@@ -12379,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="AN31" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AO31" s="2">
         <v>23</v>
@@ -12523,7 +12553,7 @@
         <v>7</v>
       </c>
       <c r="CJ31" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="CK31" s="2">
         <v>189</v>
@@ -12559,7 +12589,7 @@
         <v>32</v>
       </c>
       <c r="CV31" s="1">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="CW31" s="1">
         <v>432</v>
@@ -22420,7 +22450,7 @@
         <v>4</v>
       </c>
       <c r="AF64" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG64" s="2">
         <v>73</v>
@@ -22624,7 +22654,7 @@
         <v>18</v>
       </c>
       <c r="CV64" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="CW64" s="1">
         <v>384</v>
@@ -22893,7 +22923,7 @@
         <v>4</v>
       </c>
       <c r="CJ65" s="2">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="CK65" s="2">
         <v>54</v>
@@ -22929,7 +22959,7 @@
         <v>39</v>
       </c>
       <c r="CV65" s="1">
-        <v>1757</v>
+        <v>1742</v>
       </c>
       <c r="CW65" s="1">
         <v>3492</v>
@@ -23676,7 +23706,7 @@
         <v>0</v>
       </c>
       <c r="AR68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS68" s="2">
         <v>6</v>
@@ -23808,7 +23838,7 @@
         <v>0</v>
       </c>
       <c r="CJ68" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CK68" s="2">
         <v>17</v>
@@ -23844,7 +23874,7 @@
         <v>1</v>
       </c>
       <c r="CV68" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CW68" s="1">
         <v>49</v>
@@ -24788,7 +24818,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="2">
         <v>3</v>
@@ -24800,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2">
         <v>7</v>
@@ -24860,7 +24890,7 @@
         <v>0</v>
       </c>
       <c r="AF72" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AG72" s="2">
         <v>9</v>
@@ -24980,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="BT72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU72" s="2">
         <v>1</v>
@@ -25064,7 +25094,7 @@
         <v>3</v>
       </c>
       <c r="CV72" s="1">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="CW72" s="1">
         <v>75</v>
@@ -26032,7 +26062,7 @@
         <v>0</v>
       </c>
       <c r="P76" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q76" s="2">
         <v>2403</v>
@@ -26284,7 +26314,7 @@
         <v>123</v>
       </c>
       <c r="CV76" s="1">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="CW76" s="1">
         <v>3738</v>
@@ -26911,7 +26941,7 @@
         <v>7</v>
       </c>
       <c r="D79" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E79" s="2">
         <v>79</v>
@@ -27199,7 +27229,7 @@
         <v>83</v>
       </c>
       <c r="CV79" s="1">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="CW79" s="1">
         <v>1900</v>
@@ -27372,7 +27402,7 @@
         <v>0</v>
       </c>
       <c r="BD80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE80" s="2">
         <v>1</v>
@@ -27504,7 +27534,7 @@
         <v>43</v>
       </c>
       <c r="CV80" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="CW80" s="1">
         <v>267</v>
@@ -27545,7 +27575,7 @@
         <v>11</v>
       </c>
       <c r="L81" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M81" s="2">
         <v>103</v>
@@ -27809,7 +27839,7 @@
         <v>27</v>
       </c>
       <c r="CV81" s="1">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="CW81" s="1">
         <v>369</v>
@@ -28131,7 +28161,7 @@
         <v>68</v>
       </c>
       <c r="D83" s="2">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="E83" s="2">
         <v>137</v>
@@ -28419,7 +28449,7 @@
         <v>174</v>
       </c>
       <c r="CV83" s="1">
-        <v>837</v>
+        <v>808</v>
       </c>
       <c r="CW83" s="1">
         <v>5464</v>
@@ -36008,7 +36038,7 @@
         <v>1</v>
       </c>
       <c r="CJ108" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CK108" s="2">
         <v>18</v>
@@ -36044,7 +36074,7 @@
         <v>2</v>
       </c>
       <c r="CV108" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CW108" s="1">
         <v>51</v>
@@ -38328,7 +38358,7 @@
         <v>2</v>
       </c>
       <c r="AV116" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW116" s="2">
         <v>12</v>
@@ -38484,7 +38514,7 @@
         <v>70</v>
       </c>
       <c r="CV116" s="1">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="CW116" s="1">
         <v>1137</v>
@@ -39524,7 +39554,7 @@
         <v>0</v>
       </c>
       <c r="AN120" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AO120" s="2">
         <v>22</v>
@@ -39668,7 +39698,7 @@
         <v>0</v>
       </c>
       <c r="CJ120" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CK120" s="2">
         <v>29</v>
@@ -39704,7 +39734,7 @@
         <v>2</v>
       </c>
       <c r="CV120" s="1">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="CW120" s="1">
         <v>57</v>
@@ -44380,7 +44410,7 @@
         <v>-6</v>
       </c>
       <c r="AF136" s="2">
-        <v>5036</v>
+        <v>-6</v>
       </c>
       <c r="AG136" s="2">
         <v>5977</v>
@@ -44584,7 +44614,7 @@
         <v>-4</v>
       </c>
       <c r="CV136" s="1">
-        <v>5074</v>
+        <v>32</v>
       </c>
       <c r="CW136" s="1">
         <v>6078</v>
@@ -46138,7 +46168,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I142" s="2">
         <v>4</v>
@@ -46414,7 +46444,7 @@
         <v>21</v>
       </c>
       <c r="CV142" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="CW142" s="1">
         <v>108</v>
@@ -57740,7 +57770,7 @@
         <v>31</v>
       </c>
       <c r="L180" s="2">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="M180" s="2">
         <v>185</v>
@@ -58004,7 +58034,7 @@
         <v>135</v>
       </c>
       <c r="CV180" s="1">
-        <v>1270</v>
+        <v>1243</v>
       </c>
       <c r="CW180" s="1">
         <v>2644</v>
@@ -62375,7 +62405,7 @@
         <v>0</v>
       </c>
       <c r="AF195" s="2">
-        <v>3325</v>
+        <v>0</v>
       </c>
       <c r="AG195" s="2">
         <v>5225</v>
@@ -62579,7 +62609,7 @@
         <v>3</v>
       </c>
       <c r="CV195" s="1">
-        <v>3370</v>
+        <v>45</v>
       </c>
       <c r="CW195" s="1">
         <v>5334</v>
@@ -62668,7 +62698,7 @@
         <v>0</v>
       </c>
       <c r="AB196" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC196" s="2">
         <v>7</v>
@@ -62884,7 +62914,7 @@
         <v>10</v>
       </c>
       <c r="CV196" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="CW196" s="1">
         <v>214</v>
@@ -68387,7 +68417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -68415,2276 +68445,2279 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="F2" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F3" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D4">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F4" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F5" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
       <c r="C6" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F6" t="s">
-        <v>736</v>
+        <v>748</v>
+      </c>
+      <c r="G6" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F7" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="F8" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F9" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
+      <c r="C10" t="s">
+        <v>541</v>
+      </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F10" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="F11" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F12" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="F13" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F14" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
-      <c r="C15" t="s">
-        <v>539</v>
-      </c>
       <c r="D15">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F15" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="F16" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F17" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F18" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F19" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F20" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F21" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F22" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F23" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="F24" t="s">
-        <v>736</v>
-      </c>
-      <c r="G24" t="s">
-        <v>544</v>
+        <v>749</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F25" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="D26">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F26" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D27">
-        <v>281</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F27" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="F28" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
       <c r="F29" t="s">
-        <v>737</v>
+        <v>749</v>
+      </c>
+      <c r="G29" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="F30" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F31" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="E32" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F32" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D33">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="F33" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s">
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F34" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
         <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="D35">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="F35" t="s">
-        <v>739</v>
-      </c>
-      <c r="G35" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
         <v>354</v>
       </c>
       <c r="C36" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="F36" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
         <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="F37" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
         <v>356</v>
       </c>
+      <c r="C38" t="s">
+        <v>563</v>
+      </c>
       <c r="D38">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F38" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="D39">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="F39" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
         <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
         <v>716</v>
       </c>
       <c r="F40" t="s">
-        <v>738</v>
+        <v>746</v>
+      </c>
+      <c r="G40" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
         <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="F41" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
         <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="F42" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
         <v>361</v>
       </c>
-      <c r="C43" t="s">
-        <v>558</v>
-      </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F43" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F44" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
         <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="F45" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
         <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="D46">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F46" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
         <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F47" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
         <v>366</v>
       </c>
       <c r="C48" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F48" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s">
         <v>367</v>
       </c>
       <c r="C49" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F49" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
         <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F50" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
         <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D51">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="E51" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F51" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
         <v>370</v>
       </c>
       <c r="C52" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F52" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="F53" t="s">
-        <v>736</v>
-      </c>
-      <c r="G53" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s">
         <v>372</v>
       </c>
       <c r="C54" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D54">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F54" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
         <v>373</v>
       </c>
       <c r="C55" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F55" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B56" t="s">
         <v>374</v>
       </c>
       <c r="C56" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D56">
-        <v>336</v>
+        <v>200</v>
       </c>
       <c r="E56" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F56" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B57" t="s">
         <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F57" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D58">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="F58" t="s">
-        <v>737</v>
+        <v>749</v>
+      </c>
+      <c r="G58" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
         <v>377</v>
       </c>
       <c r="C59" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D59">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F59" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B60" t="s">
         <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D60">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F60" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
         <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D61">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E61" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F61" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B62" t="s">
         <v>380</v>
       </c>
       <c r="C62" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D62">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="F62" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B63" t="s">
         <v>381</v>
       </c>
       <c r="C63" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D63">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="E63" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F63" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
         <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D64">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F64" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F65" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B66" t="s">
         <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="E66" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F66" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B67" t="s">
         <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F67" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
         <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F68" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B69" t="s">
         <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D69">
-        <v>2240</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F69" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
         <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F70" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B71" t="s">
         <v>389</v>
       </c>
       <c r="C71" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D71">
-        <v>927</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F71" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B72" t="s">
         <v>390</v>
       </c>
       <c r="C72" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D72">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="E72" t="s">
-        <v>705</v>
+        <v>727</v>
       </c>
       <c r="F72" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B73" t="s">
         <v>391</v>
       </c>
       <c r="C73" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F73" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B74" t="s">
         <v>392</v>
       </c>
       <c r="C74" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D74">
-        <v>1216</v>
+        <v>2240</v>
       </c>
       <c r="E74" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F74" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B75" t="s">
         <v>393</v>
       </c>
       <c r="C75" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="D75">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E75" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
       <c r="F75" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B76" t="s">
         <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D76">
-        <v>55</v>
+        <v>927</v>
       </c>
       <c r="E76" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F76" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B77" t="s">
         <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="E77" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F77" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B78" t="s">
         <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>535</v>
+        <v>598</v>
       </c>
       <c r="D78">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="F78" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B79" t="s">
         <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1216</v>
       </c>
       <c r="E79" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F79" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
         <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F80" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B81" t="s">
         <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D81">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E81" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F81" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B82" t="s">
         <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F82" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B83" t="s">
         <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>596</v>
+        <v>546</v>
       </c>
       <c r="D83">
-        <v>13</v>
+        <v>269</v>
       </c>
       <c r="E83" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F83" t="s">
-        <v>737</v>
-      </c>
-      <c r="G83" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B84" t="s">
         <v>402</v>
       </c>
       <c r="C84" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D84">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F84" t="s">
-        <v>737</v>
-      </c>
-      <c r="G84" t="s">
-        <v>597</v>
+        <v>749</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B85" t="s">
         <v>403</v>
       </c>
       <c r="C85" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F85" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
       </c>
       <c r="C86" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D86">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F86" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
         <v>405</v>
       </c>
       <c r="C87" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D87">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F87" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B88" t="s">
         <v>406</v>
       </c>
+      <c r="C88" t="s">
+        <v>606</v>
+      </c>
       <c r="D88">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F88" t="s">
-        <v>736</v>
+        <v>747</v>
+      </c>
+      <c r="G88" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B89" t="s">
         <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F89" t="s">
-        <v>736</v>
+        <v>747</v>
+      </c>
+      <c r="G89" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
         <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F90" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
         <v>409</v>
       </c>
       <c r="C91" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E91" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F91" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B92" t="s">
         <v>410</v>
       </c>
       <c r="C92" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E92" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F92" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s">
         <v>411</v>
       </c>
-      <c r="C93" t="s">
-        <v>605</v>
-      </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F93" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B94" t="s">
         <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="F94" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B95" t="s">
         <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F95" t="s">
-        <v>736</v>
-      </c>
-      <c r="G95" t="s">
-        <v>607</v>
+        <v>749</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B96" t="s">
         <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F96" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
         <v>415</v>
       </c>
       <c r="C97" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D97">
-        <v>2987</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F97" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B98" t="s">
         <v>416</v>
       </c>
       <c r="C98" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="F98" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B99" t="s">
         <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="F99" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
         <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D100">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F100" t="s">
-        <v>737</v>
+        <v>749</v>
+      </c>
+      <c r="G100" t="s">
+        <v>617</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B101" t="s">
         <v>419</v>
       </c>
       <c r="C101" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D101">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F101" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B102" t="s">
         <v>420</v>
       </c>
       <c r="C102" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>2987</v>
       </c>
       <c r="E102" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F102" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B103" t="s">
         <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D103">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="F103" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B104" t="s">
         <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="F104" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B105" t="s">
         <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D105">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E105" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F105" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B106" t="s">
         <v>424</v>
       </c>
       <c r="C106" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E106" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F106" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B107" t="s">
         <v>425</v>
       </c>
       <c r="C107" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D107">
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F107" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D108">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F108" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B109" t="s">
         <v>427</v>
       </c>
       <c r="C109" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>705</v>
+        <v>733</v>
       </c>
       <c r="F109" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B110" t="s">
         <v>428</v>
       </c>
       <c r="C110" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="F110" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B111" t="s">
         <v>429</v>
       </c>
       <c r="C111" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D111">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F111" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B112" t="s">
         <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D112">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F112" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B113" t="s">
         <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>624</v>
+        <v>535</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>705</v>
+        <v>734</v>
       </c>
       <c r="F113" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
         <v>432</v>
       </c>
       <c r="C114" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F114" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B115" t="s">
         <v>433</v>
@@ -70693,1891 +70726,2011 @@
         <v>626</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>705</v>
+        <v>735</v>
       </c>
       <c r="F115" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B116" t="s">
         <v>434</v>
       </c>
       <c r="C116" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="E116" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F116" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B117" t="s">
         <v>435</v>
       </c>
       <c r="C117" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E117" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F117" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B118" t="s">
         <v>436</v>
       </c>
       <c r="C118" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F118" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B119" t="s">
         <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F119" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B120" t="s">
         <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F120" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B121" t="s">
         <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F121" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B122" t="s">
         <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D122">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F122" t="s">
-        <v>735</v>
-      </c>
-      <c r="G122" t="s">
-        <v>632</v>
+        <v>749</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B123" t="s">
         <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F123" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B124" t="s">
         <v>442</v>
       </c>
       <c r="C124" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D124">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F124" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B125" t="s">
         <v>443</v>
       </c>
       <c r="C125" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F125" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B126" t="s">
         <v>444</v>
       </c>
       <c r="C126" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F126" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
         <v>445</v>
       </c>
       <c r="C127" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F127" t="s">
-        <v>736</v>
+        <v>748</v>
+      </c>
+      <c r="G127" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B128" t="s">
         <v>446</v>
       </c>
       <c r="C128" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F128" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B129" t="s">
         <v>447</v>
       </c>
       <c r="C129" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D129">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F129" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B130" t="s">
         <v>448</v>
       </c>
       <c r="C130" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D130">
-        <v>10256</v>
+        <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F130" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B131" t="s">
         <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F131" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B132" t="s">
         <v>450</v>
       </c>
       <c r="C132" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="F132" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B133" t="s">
         <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D133">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F133" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B134" t="s">
         <v>452</v>
       </c>
       <c r="C134" t="s">
-        <v>590</v>
+        <v>648</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="E134" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="F134" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B135" t="s">
         <v>453</v>
       </c>
       <c r="C135" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>10256</v>
       </c>
       <c r="E135" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F135" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B136" t="s">
         <v>454</v>
       </c>
       <c r="C136" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D136">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F136" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B137" t="s">
         <v>455</v>
       </c>
       <c r="C137" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D137">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="F137" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
         <v>456</v>
       </c>
       <c r="C138" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D138">
-        <v>4</v>
+        <v>374</v>
       </c>
       <c r="E138" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F138" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
         <v>457</v>
       </c>
       <c r="C139" t="s">
-        <v>647</v>
+        <v>600</v>
       </c>
       <c r="D139">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E139" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="F139" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B140" t="s">
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>559</v>
+        <v>652</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F140" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
         <v>459</v>
       </c>
       <c r="C141" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F141" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
         <v>460</v>
       </c>
       <c r="C142" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D142">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E142" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F142" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
         <v>461</v>
       </c>
+      <c r="C143" t="s">
+        <v>655</v>
+      </c>
       <c r="D143">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F143" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
         <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E144" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="F144" t="s">
-        <v>736</v>
-      </c>
-      <c r="G144" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
         <v>463</v>
       </c>
       <c r="C145" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E145" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="F145" t="s">
-        <v>736</v>
-      </c>
-      <c r="G145" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B146" t="s">
         <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>652</v>
+        <v>569</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="F146" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B147" t="s">
         <v>465</v>
       </c>
       <c r="C147" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F147" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
         <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>533</v>
+        <v>659</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F148" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B149" t="s">
         <v>467</v>
       </c>
-      <c r="C149" t="s">
-        <v>654</v>
-      </c>
       <c r="D149">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F149" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B150" t="s">
         <v>468</v>
       </c>
       <c r="C150" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D150">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>705</v>
+        <v>738</v>
       </c>
       <c r="F150" t="s">
-        <v>738</v>
+        <v>749</v>
+      </c>
+      <c r="G150" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B151" t="s">
         <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D151">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>705</v>
+        <v>739</v>
       </c>
       <c r="F151" t="s">
-        <v>739</v>
+        <v>749</v>
+      </c>
+      <c r="G151" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B152" t="s">
         <v>470</v>
       </c>
       <c r="C152" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D152">
         <v>5</v>
       </c>
       <c r="E152" t="s">
-        <v>705</v>
+        <v>740</v>
       </c>
       <c r="F152" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B153" t="s">
         <v>471</v>
       </c>
       <c r="C153" t="s">
-        <v>558</v>
+        <v>663</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F153" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B154" t="s">
         <v>472</v>
       </c>
       <c r="C154" t="s">
-        <v>658</v>
+        <v>544</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F154" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B155" t="s">
         <v>473</v>
       </c>
       <c r="C155" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D155">
-        <v>761</v>
+        <v>19</v>
       </c>
       <c r="E155" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F155" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B156" t="s">
         <v>474</v>
       </c>
       <c r="C156" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="E156" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="F156" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B157" t="s">
         <v>475</v>
       </c>
       <c r="C157" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D157">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="E157" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F157" t="s">
-        <v>737</v>
-      </c>
-      <c r="G157" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B158" t="s">
         <v>476</v>
       </c>
       <c r="C158" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D158">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F158" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B159" t="s">
         <v>477</v>
       </c>
       <c r="C159" t="s">
-        <v>662</v>
+        <v>568</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F159" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B160" t="s">
         <v>478</v>
       </c>
       <c r="C160" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D160">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F160" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B161" t="s">
         <v>479</v>
       </c>
       <c r="C161" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="E161" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F161" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B162" t="s">
         <v>480</v>
       </c>
       <c r="C162" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D162">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E162" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="F162" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B163" t="s">
         <v>481</v>
       </c>
       <c r="C163" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E163" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="F163" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="G163" t="s">
-        <v>666</v>
+        <v>755</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B164" t="s">
         <v>482</v>
       </c>
       <c r="C164" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D164">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E164" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F164" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B165" t="s">
         <v>483</v>
       </c>
       <c r="C165" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D165">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="E165" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F165" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B166" t="s">
         <v>484</v>
       </c>
       <c r="C166" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F166" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B167" t="s">
         <v>485</v>
       </c>
       <c r="C167" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F167" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B168" t="s">
         <v>486</v>
       </c>
       <c r="C168" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>705</v>
+        <v>740</v>
       </c>
       <c r="F168" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B169" t="s">
         <v>487</v>
       </c>
       <c r="C169" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169" t="s">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="F169" t="s">
-        <v>736</v>
+        <v>749</v>
+      </c>
+      <c r="G169" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B170" t="s">
         <v>488</v>
       </c>
       <c r="C170" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F170" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B171" t="s">
         <v>489</v>
       </c>
       <c r="C171" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E171" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F171" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B172" t="s">
         <v>490</v>
       </c>
       <c r="C172" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D172">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F172" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B173" t="s">
         <v>491</v>
       </c>
       <c r="C173" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F173" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B174" t="s">
         <v>492</v>
       </c>
       <c r="C174" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D174">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E174" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F174" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B175" t="s">
         <v>493</v>
       </c>
       <c r="C175" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D175">
         <v>0</v>
       </c>
       <c r="E175" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F175" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B176" t="s">
         <v>494</v>
       </c>
       <c r="C176" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D176">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E176" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F176" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B177" t="s">
         <v>495</v>
       </c>
+      <c r="C177" t="s">
+        <v>684</v>
+      </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F177" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B178" t="s">
         <v>496</v>
       </c>
       <c r="C178" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="E178" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F178" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B179" t="s">
         <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>593</v>
+        <v>686</v>
       </c>
       <c r="D179">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F179" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B180" t="s">
         <v>498</v>
       </c>
       <c r="C180" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="E180" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F180" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B181" t="s">
         <v>499</v>
       </c>
       <c r="C181" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F181" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B182" t="s">
         <v>500</v>
       </c>
       <c r="C182" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F182" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B183" t="s">
         <v>501</v>
       </c>
-      <c r="C183" t="s">
-        <v>684</v>
-      </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F183" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B184" t="s">
         <v>502</v>
       </c>
       <c r="C184" t="s">
-        <v>606</v>
+        <v>690</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F184" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B185" t="s">
         <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>685</v>
+        <v>603</v>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F185" t="s">
-        <v>737</v>
-      </c>
-      <c r="G185" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B186" t="s">
         <v>504</v>
       </c>
       <c r="C186" t="s">
-        <v>604</v>
+        <v>691</v>
       </c>
       <c r="D186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F186" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B187" t="s">
         <v>505</v>
       </c>
       <c r="C187" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F187" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B188" t="s">
         <v>506</v>
       </c>
       <c r="C188" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D188">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F188" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B189" t="s">
         <v>507</v>
       </c>
       <c r="C189" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D189">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E189" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F189" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B190" t="s">
         <v>508</v>
       </c>
       <c r="C190" t="s">
-        <v>689</v>
+        <v>616</v>
       </c>
       <c r="D190">
-        <v>10268</v>
+        <v>0</v>
       </c>
       <c r="E190" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F190" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B191" t="s">
         <v>509</v>
       </c>
       <c r="C191" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="F191" t="s">
-        <v>736</v>
+        <v>747</v>
+      </c>
+      <c r="G191" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B192" t="s">
         <v>510</v>
       </c>
       <c r="C192" t="s">
-        <v>691</v>
+        <v>614</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F192" t="s">
-        <v>736</v>
-      </c>
-      <c r="G192" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B193" t="s">
         <v>511</v>
       </c>
       <c r="C193" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F193" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B194" t="s">
         <v>512</v>
       </c>
       <c r="C194" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D194">
-        <v>315</v>
+        <v>116</v>
       </c>
       <c r="E194" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F194" t="s">
-        <v>736</v>
-      </c>
-      <c r="G194" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B195" t="s">
         <v>513</v>
       </c>
       <c r="C195" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D195">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E195" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F195" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B196" t="s">
         <v>514</v>
       </c>
       <c r="C196" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D196">
-        <v>7</v>
+        <v>10268</v>
       </c>
       <c r="E196" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F196" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B197" t="s">
         <v>515</v>
       </c>
       <c r="C197" t="s">
-        <v>544</v>
+        <v>700</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="F197" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B198" t="s">
         <v>516</v>
       </c>
       <c r="C198" t="s">
-        <v>544</v>
+        <v>701</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="F198" t="s">
-        <v>736</v>
+        <v>749</v>
+      </c>
+      <c r="G198" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B199" t="s">
         <v>517</v>
       </c>
       <c r="C199" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F199" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B200" t="s">
         <v>518</v>
       </c>
       <c r="C200" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D200">
-        <v>442</v>
+        <v>315</v>
       </c>
       <c r="E200" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F200" t="s">
-        <v>736</v>
+        <v>749</v>
+      </c>
+      <c r="G200" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B201" t="s">
         <v>519</v>
       </c>
       <c r="C201" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D201">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="E201" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F201" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B202" t="s">
         <v>520</v>
       </c>
       <c r="C202" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E202" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F202" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B203" t="s">
         <v>521</v>
       </c>
       <c r="C203" t="s">
-        <v>700</v>
+        <v>533</v>
       </c>
       <c r="D203">
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="F203" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B204" t="s">
         <v>522</v>
       </c>
       <c r="C204" t="s">
-        <v>701</v>
+        <v>533</v>
       </c>
       <c r="D204">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E204" t="s">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="F204" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B205" t="s">
         <v>523</v>
       </c>
       <c r="C205" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D205">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E205" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="F205" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B206" t="s">
         <v>524</v>
       </c>
       <c r="C206" t="s">
-        <v>665</v>
+        <v>707</v>
       </c>
       <c r="D206">
-        <v>18</v>
+        <v>442</v>
       </c>
       <c r="E206" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F206" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B207" t="s">
         <v>525</v>
       </c>
       <c r="C207" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="E207" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F207" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B208" t="s">
         <v>526</v>
       </c>
       <c r="C208" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F208" t="s">
-        <v>736</v>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>308</v>
+      </c>
+      <c r="B209" t="s">
+        <v>527</v>
+      </c>
+      <c r="C209" t="s">
+        <v>710</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209" t="s">
+        <v>716</v>
+      </c>
+      <c r="F209" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>309</v>
+      </c>
+      <c r="B210" t="s">
+        <v>528</v>
+      </c>
+      <c r="C210" t="s">
+        <v>711</v>
+      </c>
+      <c r="D210">
+        <v>23</v>
+      </c>
+      <c r="E210" t="s">
+        <v>716</v>
+      </c>
+      <c r="F210" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>310</v>
+      </c>
+      <c r="B211" t="s">
+        <v>529</v>
+      </c>
+      <c r="C211" t="s">
+        <v>712</v>
+      </c>
+      <c r="D211">
+        <v>27</v>
+      </c>
+      <c r="E211" t="s">
+        <v>744</v>
+      </c>
+      <c r="F211" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>311</v>
+      </c>
+      <c r="B212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C212" t="s">
+        <v>675</v>
+      </c>
+      <c r="D212">
+        <v>18</v>
+      </c>
+      <c r="E212" t="s">
+        <v>716</v>
+      </c>
+      <c r="F212" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>312</v>
+      </c>
+      <c r="B213" t="s">
+        <v>531</v>
+      </c>
+      <c r="C213" t="s">
+        <v>713</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+      <c r="E213" t="s">
+        <v>716</v>
+      </c>
+      <c r="F213" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>313</v>
+      </c>
+      <c r="B214" t="s">
+        <v>532</v>
+      </c>
+      <c r="C214" t="s">
+        <v>714</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214" t="s">
+        <v>716</v>
+      </c>
+      <c r="F214" t="s">
+        <v>749</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -7197,7 +7197,7 @@
         <v>1998</v>
       </c>
       <c r="AE14" s="2">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="AF14" s="2">
         <v>-20</v>
@@ -7401,7 +7401,7 @@
         <v>3164</v>
       </c>
       <c r="CU14" s="1">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="CV14" s="1">
         <v>85</v>
@@ -15043,7 +15043,7 @@
         <v>8828</v>
       </c>
       <c r="C40" s="2">
-        <v>57</v>
+        <v>-2</v>
       </c>
       <c r="D40" s="2">
         <v>79</v>
@@ -15331,7 +15331,7 @@
         <v>53532</v>
       </c>
       <c r="CU40" s="1">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="CV40" s="1">
         <v>409</v>
@@ -16078,7 +16078,7 @@
         <v>89</v>
       </c>
       <c r="AQ43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR43" s="2">
         <v>3</v>
@@ -16222,7 +16222,7 @@
         <v>80</v>
       </c>
       <c r="CM43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN43" s="2">
         <v>3</v>
@@ -16246,7 +16246,7 @@
         <v>581</v>
       </c>
       <c r="CU43" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CV43" s="1">
         <v>40</v>
@@ -20862,7 +20862,7 @@
         <v>33</v>
       </c>
       <c r="K59" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2">
         <v>9</v>
@@ -20946,7 +20946,7 @@
         <v>66</v>
       </c>
       <c r="AM59" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN59" s="2">
         <v>3</v>
@@ -21090,7 +21090,7 @@
         <v>82</v>
       </c>
       <c r="CI59" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CJ59" s="2">
         <v>10</v>
@@ -21126,7 +21126,7 @@
         <v>872</v>
       </c>
       <c r="CU59" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CV59" s="1">
         <v>44</v>
@@ -22668,7 +22668,7 @@
         <v>3716</v>
       </c>
       <c r="C65" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D65" s="2">
         <v>29</v>
@@ -22956,7 +22956,7 @@
         <v>67225</v>
       </c>
       <c r="CU65" s="1">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="CV65" s="1">
         <v>1742</v>
@@ -22973,7 +22973,7 @@
         <v>671</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" s="2">
         <v>6</v>
@@ -23261,7 +23261,7 @@
         <v>1659</v>
       </c>
       <c r="CU66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV66" s="1">
         <v>46</v>
@@ -25665,7 +25665,7 @@
         <v>16228</v>
       </c>
       <c r="CI74" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="CJ74" s="2">
         <v>175</v>
@@ -25701,7 +25701,7 @@
         <v>171817</v>
       </c>
       <c r="CU74" s="1">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="CV74" s="1">
         <v>743</v>
@@ -25838,7 +25838,7 @@
         <v>15</v>
       </c>
       <c r="AQ75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR75" s="2">
         <v>3</v>
@@ -25970,7 +25970,7 @@
         <v>100</v>
       </c>
       <c r="CI75" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CJ75" s="2">
         <v>11</v>
@@ -26006,7 +26006,7 @@
         <v>226</v>
       </c>
       <c r="CU75" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CV75" s="1">
         <v>18</v>
@@ -26023,7 +26023,7 @@
         <v>5146</v>
       </c>
       <c r="C76" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D76" s="2">
         <v>56</v>
@@ -26311,7 +26311,7 @@
         <v>151140</v>
       </c>
       <c r="CU76" s="1">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="CV76" s="1">
         <v>1194</v>
@@ -26352,7 +26352,7 @@
         <v>4921</v>
       </c>
       <c r="K77" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L77" s="2">
         <v>182</v>
@@ -26580,7 +26580,7 @@
         <v>7369</v>
       </c>
       <c r="CI77" s="2">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="CJ77" s="2">
         <v>285</v>
@@ -26616,7 +26616,7 @@
         <v>390982</v>
       </c>
       <c r="CU77" s="1">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="CV77" s="1">
         <v>10131</v>
@@ -27865,7 +27865,7 @@
         <v>71</v>
       </c>
       <c r="G82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="2">
         <v>3</v>
@@ -27973,7 +27973,7 @@
         <v>79</v>
       </c>
       <c r="AQ82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR82" s="2">
         <v>3</v>
@@ -28117,7 +28117,7 @@
         <v>71</v>
       </c>
       <c r="CM82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN82" s="2">
         <v>3</v>
@@ -28141,7 +28141,7 @@
         <v>326</v>
       </c>
       <c r="CU82" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CV82" s="1">
         <v>11</v>
@@ -28158,7 +28158,7 @@
         <v>2729</v>
       </c>
       <c r="C83" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2">
         <v>68</v>
@@ -28446,7 +28446,7 @@
         <v>423966</v>
       </c>
       <c r="CU83" s="1">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="CV83" s="1">
         <v>808</v>
@@ -30228,7 +30228,7 @@
         <v>5</v>
       </c>
       <c r="CE89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF89" s="2">
         <v>1</v>
@@ -30276,7 +30276,7 @@
         <v>2233</v>
       </c>
       <c r="CU89" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CV89" s="1">
         <v>75</v>
@@ -38941,7 +38941,7 @@
         <v>2</v>
       </c>
       <c r="AM118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN118" s="2">
         <v>2</v>
@@ -39085,7 +39085,7 @@
         <v>31</v>
       </c>
       <c r="CI118" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ118" s="2">
         <v>18</v>
@@ -39121,7 +39121,7 @@
         <v>140</v>
       </c>
       <c r="CU118" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CV118" s="1">
         <v>25</v>
@@ -44102,7 +44102,7 @@
         <v>11790</v>
       </c>
       <c r="AE135" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF135" s="2">
         <v>159</v>
@@ -44306,7 +44306,7 @@
         <v>62762</v>
       </c>
       <c r="CU135" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="CV135" s="1">
         <v>941</v>
@@ -46763,7 +46763,7 @@
         <v>499</v>
       </c>
       <c r="C144" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D144" s="2">
         <v>7</v>
@@ -47051,7 +47051,7 @@
         <v>1191</v>
       </c>
       <c r="CU144" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV144" s="1">
         <v>20</v>
@@ -51273,7 +51273,7 @@
         <v>7</v>
       </c>
       <c r="CE158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF158" s="2">
         <v>1</v>
@@ -51321,7 +51321,7 @@
         <v>25708</v>
       </c>
       <c r="CU158" s="1">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CV158" s="1">
         <v>836</v>
@@ -55022,7 +55022,7 @@
         <v>293</v>
       </c>
       <c r="K171" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L171" s="2">
         <v>22</v>
@@ -55286,7 +55286,7 @@
         <v>5854</v>
       </c>
       <c r="CU171" s="1">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CV171" s="1">
         <v>44</v>
@@ -57767,7 +57767,7 @@
         <v>1547</v>
       </c>
       <c r="K180" s="2">
-        <v>31</v>
+        <v>-2</v>
       </c>
       <c r="L180" s="2">
         <v>31</v>
@@ -58031,7 +58031,7 @@
         <v>51287</v>
       </c>
       <c r="CU180" s="1">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="CV180" s="1">
         <v>1243</v>
@@ -62013,7 +62013,7 @@
         <v>1628</v>
       </c>
       <c r="C194" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D194" s="2">
         <v>26</v>
@@ -62301,7 +62301,7 @@
         <v>32902</v>
       </c>
       <c r="CU194" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="CV194" s="1">
         <v>602</v>
@@ -63951,7 +63951,7 @@
         <v>405</v>
       </c>
       <c r="AM200" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN200" s="2">
         <v>9</v>
@@ -64095,7 +64095,7 @@
         <v>1041</v>
       </c>
       <c r="CI200" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CJ200" s="2">
         <v>32</v>
@@ -64131,7 +64131,7 @@
         <v>16376</v>
       </c>
       <c r="CU200" s="1">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="CV200" s="1">
         <v>220</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3755,16 +3755,16 @@
         <v>102</v>
       </c>
       <c r="B3" s="1">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -4043,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46745</v>
+        <v>46754</v>
       </c>
       <c r="CU3" s="1">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="CV3" s="1">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="CW3" s="1">
-        <v>2040</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
         <v>58</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="BN9" s="1">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BO9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR9" s="1">
         <v>3</v>
@@ -5795,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="BT9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU9" s="2">
         <v>1</v>
@@ -5873,16 +5873,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="CU9" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV9" s="1">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="CW9" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7451,16 +7451,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>2786</v>
+        <v>2835</v>
       </c>
       <c r="O15" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="P15" s="2">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="Q15" s="2">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -7667,16 +7667,16 @@
         <v>0</v>
       </c>
       <c r="CH15" s="1">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="CI15" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CJ15" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="CK15" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="CL15" s="1">
         <v>2</v>
@@ -7703,16 +7703,16 @@
         <v>0</v>
       </c>
       <c r="CT15" s="1">
-        <v>3417</v>
+        <v>3470</v>
       </c>
       <c r="CU15" s="1">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="CV15" s="1">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="CW15" s="1">
-        <v>182</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:101">
@@ -8976,16 +8976,16 @@
         <v>62</v>
       </c>
       <c r="N20" s="1">
-        <v>12655</v>
+        <v>12654</v>
       </c>
       <c r="O20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20" s="2">
-        <v>228</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="2">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -9180,16 +9180,16 @@
         <v>0</v>
       </c>
       <c r="CD20" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CE20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH20" s="1">
         <v>1078</v>
@@ -9234,10 +9234,10 @@
         <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="CW20" s="1">
-        <v>952</v>
+        <v>935</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9897,7 +9897,7 @@
         <v>6</v>
       </c>
       <c r="P23" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="2">
         <v>29</v>
@@ -9975,16 +9975,16 @@
         <v>0</v>
       </c>
       <c r="AP23" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AQ23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" s="1">
         <v>0</v>
@@ -10119,16 +10119,16 @@
         <v>5</v>
       </c>
       <c r="CL23" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CM23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP23" s="1">
         <v>0</v>
@@ -10143,16 +10143,16 @@
         <v>0</v>
       </c>
       <c r="CT23" s="1">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="CU23" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV23" s="1">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="CW23" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:101">
@@ -11422,7 +11422,7 @@
         <v>8</v>
       </c>
       <c r="P28" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q28" s="2">
         <v>18</v>
@@ -11674,7 +11674,7 @@
         <v>24</v>
       </c>
       <c r="CV28" s="1">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="CW28" s="1">
         <v>763</v>
@@ -12388,7 +12388,7 @@
         <v>34</v>
       </c>
       <c r="AG31" s="2">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="AH31" s="1">
         <v>2</v>
@@ -12403,16 +12403,16 @@
         <v>0</v>
       </c>
       <c r="AL31" s="1">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM31" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN31" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO31" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP31" s="1">
         <v>19</v>
@@ -12547,16 +12547,16 @@
         <v>0</v>
       </c>
       <c r="CH31" s="1">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="CI31" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CJ31" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="CK31" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12583,16 +12583,16 @@
         <v>0</v>
       </c>
       <c r="CT31" s="1">
-        <v>6036</v>
+        <v>6044</v>
       </c>
       <c r="CU31" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="CV31" s="1">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="CW31" s="1">
-        <v>432</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -13252,7 +13252,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2">
         <v>25</v>
@@ -13327,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="AO34" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AP34" s="1">
         <v>50</v>
@@ -13471,7 +13471,7 @@
         <v>5</v>
       </c>
       <c r="CK34" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="CL34" s="1">
         <v>26</v>
@@ -13504,10 +13504,10 @@
         <v>10</v>
       </c>
       <c r="CV34" s="1">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="CW34" s="1">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -13832,16 +13832,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -14108,16 +14108,16 @@
         <v>0</v>
       </c>
       <c r="CT36" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CU36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW36" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:101">
@@ -14744,7 +14744,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1">
         <v>31</v>
@@ -15032,7 +15032,7 @@
         <v>65</v>
       </c>
       <c r="CW39" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15133,7 +15133,7 @@
         <v>1</v>
       </c>
       <c r="AG40" s="2">
-        <v>806</v>
+        <v>461</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -15157,7 +15157,7 @@
         <v>0</v>
       </c>
       <c r="AO40" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AP40" s="1">
         <v>27</v>
@@ -15238,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="BP40" s="2">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BQ40" s="2">
         <v>2</v>
@@ -15301,7 +15301,7 @@
         <v>49</v>
       </c>
       <c r="CK40" s="2">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="CL40" s="1">
         <v>13</v>
@@ -15334,10 +15334,10 @@
         <v>43</v>
       </c>
       <c r="CV40" s="1">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="CW40" s="1">
-        <v>2115</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="41" spans="1:101">
@@ -16000,7 +16000,7 @@
         <v>34</v>
       </c>
       <c r="Q43" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -16252,7 +16252,7 @@
         <v>40</v>
       </c>
       <c r="CW43" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:101">
@@ -19424,22 +19424,22 @@
         <v>0</v>
       </c>
       <c r="AN54" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO54" s="2">
         <v>4</v>
       </c>
       <c r="AP54" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS54" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -19562,16 +19562,16 @@
         <v>0</v>
       </c>
       <c r="CH54" s="1">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CI54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CJ54" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CK54" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CL54" s="1">
         <v>8</v>
@@ -19598,16 +19598,16 @@
         <v>0</v>
       </c>
       <c r="CT54" s="1">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="CU54" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV54" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW54" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -20542,16 +20542,16 @@
         <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" s="1">
         <v>0</v>
@@ -20638,16 +20638,16 @@
         <v>0</v>
       </c>
       <c r="AL58" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO58" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP58" s="1">
         <v>22</v>
@@ -20782,28 +20782,28 @@
         <v>0</v>
       </c>
       <c r="CH58" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="CI58" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ58" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CK58" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CL58" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CM58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CO58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CP58" s="1">
         <v>0</v>
@@ -20818,16 +20818,16 @@
         <v>0</v>
       </c>
       <c r="CT58" s="1">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="CU58" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CV58" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CW58" s="1">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:101">
@@ -20865,7 +20865,7 @@
         <v>2</v>
       </c>
       <c r="L59" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M59" s="2">
         <v>11</v>
@@ -21045,7 +21045,7 @@
         <v>1</v>
       </c>
       <c r="BT59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU59" s="2">
         <v>2</v>
@@ -21129,7 +21129,7 @@
         <v>10</v>
       </c>
       <c r="CV59" s="1">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="CW59" s="1">
         <v>58</v>
@@ -21487,7 +21487,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="2">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="2">
         <v>399</v>
@@ -21739,7 +21739,7 @@
         <v>-41</v>
       </c>
       <c r="CV61" s="1">
-        <v>357</v>
+        <v>194</v>
       </c>
       <c r="CW61" s="1">
         <v>857</v>
@@ -22259,16 +22259,16 @@
         <v>0</v>
       </c>
       <c r="BR63" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BS63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV63" s="1">
         <v>0</v>
@@ -22343,16 +22343,16 @@
         <v>0</v>
       </c>
       <c r="CT63" s="1">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="CU63" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CV63" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CW63" s="1">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:101">
@@ -22441,19 +22441,19 @@
         <v>3</v>
       </c>
       <c r="AC64" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD64" s="1">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="AE64" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AF64" s="2">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AG64" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22480,16 +22480,16 @@
         <v>2</v>
       </c>
       <c r="AP64" s="1">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="AQ64" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR64" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS64" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT64" s="1">
         <v>0</v>
@@ -22564,16 +22564,16 @@
         <v>0</v>
       </c>
       <c r="BR64" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BV64" s="1">
         <v>0</v>
@@ -22621,7 +22621,7 @@
         <v>11</v>
       </c>
       <c r="CK64" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="CL64" s="1">
         <v>10</v>
@@ -22648,16 +22648,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8032</v>
+        <v>8065</v>
       </c>
       <c r="CU64" s="1">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="CV64" s="1">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="CW64" s="1">
-        <v>384</v>
+        <v>413</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22665,16 +22665,16 @@
         <v>164</v>
       </c>
       <c r="B65" s="1">
-        <v>3716</v>
+        <v>3741</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D65" s="2">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E65" s="2">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -22698,7 +22698,7 @@
         <v>48</v>
       </c>
       <c r="M65" s="2">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="N65" s="1">
         <v>58955</v>
@@ -22746,7 +22746,7 @@
         <v>8</v>
       </c>
       <c r="AC65" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD65" s="1">
         <v>338</v>
@@ -22917,16 +22917,16 @@
         <v>0</v>
       </c>
       <c r="CH65" s="1">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="CI65" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="CJ65" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="CK65" s="2">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="CL65" s="1">
         <v>34</v>
@@ -22953,16 +22953,16 @@
         <v>0</v>
       </c>
       <c r="CT65" s="1">
-        <v>67225</v>
+        <v>67260</v>
       </c>
       <c r="CU65" s="1">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="CV65" s="1">
-        <v>1742</v>
+        <v>1777</v>
       </c>
       <c r="CW65" s="1">
-        <v>3492</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -23589,7 +23589,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="2">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="F68" s="1">
         <v>21</v>
@@ -23700,13 +23700,13 @@
         <v>0</v>
       </c>
       <c r="AP68" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS68" s="2">
         <v>6</v>
@@ -23832,16 +23832,16 @@
         <v>0</v>
       </c>
       <c r="CH68" s="1">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="CI68" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ68" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CK68" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CL68" s="1">
         <v>27</v>
@@ -23868,16 +23868,16 @@
         <v>0</v>
       </c>
       <c r="CT68" s="1">
-        <v>2133</v>
+        <v>2137</v>
       </c>
       <c r="CU68" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CV68" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW68" s="1">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:101">
@@ -24214,16 +24214,16 @@
         <v>3</v>
       </c>
       <c r="J70" s="1">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K70" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L70" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M70" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N70" s="1">
         <v>1259</v>
@@ -24478,16 +24478,16 @@
         <v>0</v>
       </c>
       <c r="CT70" s="1">
-        <v>2269</v>
+        <v>2274</v>
       </c>
       <c r="CU70" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CV70" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="CW70" s="1">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:101">
@@ -24812,40 +24812,40 @@
         <v>4</v>
       </c>
       <c r="F72" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K72" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N72" s="1">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="O72" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P72" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q72" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -24920,10 +24920,10 @@
         <v>0</v>
       </c>
       <c r="AP72" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR72" s="2">
         <v>3</v>
@@ -25004,16 +25004,16 @@
         <v>0</v>
       </c>
       <c r="BR72" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BS72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV72" s="1">
         <v>2</v>
@@ -25052,16 +25052,16 @@
         <v>0</v>
       </c>
       <c r="CH72" s="1">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="CI72" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ72" s="2">
         <v>9</v>
       </c>
       <c r="CK72" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CL72" s="1">
         <v>0</v>
@@ -25088,16 +25088,16 @@
         <v>0</v>
       </c>
       <c r="CT72" s="1">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="CU72" s="1">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="CV72" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="CW72" s="1">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:101">
@@ -25114,7 +25114,7 @@
         <v>5</v>
       </c>
       <c r="E73" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1">
         <v>46</v>
@@ -25222,7 +25222,7 @@
         <v>2</v>
       </c>
       <c r="AO73" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP73" s="1">
         <v>13</v>
@@ -25366,7 +25366,7 @@
         <v>44</v>
       </c>
       <c r="CK73" s="2">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="CL73" s="1">
         <v>6</v>
@@ -25402,7 +25402,7 @@
         <v>53</v>
       </c>
       <c r="CW73" s="1">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:101">
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="2">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="AG74" s="2">
         <v>550</v>
@@ -25518,16 +25518,16 @@
         <v>0</v>
       </c>
       <c r="AL74" s="1">
-        <v>36302</v>
+        <v>36308</v>
       </c>
       <c r="AM74" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AN74" s="2">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AO74" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25662,16 +25662,16 @@
         <v>1</v>
       </c>
       <c r="CH74" s="1">
-        <v>16228</v>
+        <v>16239</v>
       </c>
       <c r="CI74" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="CJ74" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="CK74" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171817</v>
+        <v>171834</v>
       </c>
       <c r="CU74" s="1">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="CV74" s="1">
-        <v>743</v>
+        <v>542</v>
       </c>
       <c r="CW74" s="1">
-        <v>4325</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26349,16 +26349,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>4921</v>
+        <v>4920</v>
       </c>
       <c r="K77" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L77" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M77" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26418,7 +26418,7 @@
         <v>42</v>
       </c>
       <c r="AG77" s="2">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="AH77" s="1">
         <v>4</v>
@@ -26442,7 +26442,7 @@
         <v>43</v>
       </c>
       <c r="AO77" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AP77" s="1">
         <v>74</v>
@@ -26577,16 +26577,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7369</v>
+        <v>7392</v>
       </c>
       <c r="CI77" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="CJ77" s="2">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="CK77" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26613,16 +26613,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>390982</v>
+        <v>391004</v>
       </c>
       <c r="CU77" s="1">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="CV77" s="1">
-        <v>10131</v>
+        <v>10153</v>
       </c>
       <c r="CW77" s="1">
-        <v>15901</v>
+        <v>15766</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26738,16 +26738,16 @@
         <v>0</v>
       </c>
       <c r="AL78" s="1">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AM78" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AN78" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AO78" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AP78" s="1">
         <v>0</v>
@@ -26882,16 +26882,16 @@
         <v>0</v>
       </c>
       <c r="CH78" s="1">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="CI78" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CJ78" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CK78" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="CL78" s="1">
         <v>0</v>
@@ -26918,16 +26918,16 @@
         <v>0</v>
       </c>
       <c r="CT78" s="1">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="CU78" s="1">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="CV78" s="1">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="CW78" s="1">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:101">
@@ -26944,7 +26944,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="2">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -27232,7 +27232,7 @@
         <v>622</v>
       </c>
       <c r="CW79" s="1">
-        <v>1900</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27545,16 +27545,16 @@
         <v>180</v>
       </c>
       <c r="B81" s="1">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C81" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D81" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1">
         <v>6</v>
@@ -27569,16 +27569,16 @@
         <v>1</v>
       </c>
       <c r="J81" s="1">
-        <v>1589</v>
+        <v>1604</v>
       </c>
       <c r="K81" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L81" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M81" s="2">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N81" s="1">
         <v>3606</v>
@@ -27833,16 +27833,16 @@
         <v>0</v>
       </c>
       <c r="CT81" s="1">
-        <v>6434</v>
+        <v>6451</v>
       </c>
       <c r="CU81" s="1">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="CV81" s="1">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="CW81" s="1">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:101">
@@ -28248,7 +28248,7 @@
         <v>177</v>
       </c>
       <c r="AG83" s="2">
-        <v>3519</v>
+        <v>177</v>
       </c>
       <c r="AH83" s="1">
         <v>0</v>
@@ -28272,7 +28272,7 @@
         <v>14</v>
       </c>
       <c r="AO83" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AP83" s="1">
         <v>0</v>
@@ -28416,7 +28416,7 @@
         <v>151</v>
       </c>
       <c r="CK83" s="2">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="CL83" s="1">
         <v>0</v>
@@ -28452,7 +28452,7 @@
         <v>808</v>
       </c>
       <c r="CW83" s="1">
-        <v>5464</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -28885,16 +28885,16 @@
         <v>1</v>
       </c>
       <c r="AP85" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR85" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS85" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT85" s="1">
         <v>0</v>
@@ -28921,16 +28921,16 @@
         <v>0</v>
       </c>
       <c r="BB85" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF85" s="1">
         <v>0</v>
@@ -29017,16 +29017,16 @@
         <v>0</v>
       </c>
       <c r="CH85" s="1">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="CI85" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CJ85" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="CK85" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="CL85" s="1">
         <v>0</v>
@@ -29053,16 +29053,16 @@
         <v>0</v>
       </c>
       <c r="CT85" s="1">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="CU85" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="CV85" s="1">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="CW85" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29112,7 +29112,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="2">
         <v>39</v>
@@ -29364,7 +29364,7 @@
         <v>1</v>
       </c>
       <c r="CV86" s="1">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="CW86" s="1">
         <v>68</v>
@@ -30667,13 +30667,13 @@
         <v>1</v>
       </c>
       <c r="Z91" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AA91" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB91" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC91" s="2">
         <v>6</v>
@@ -30883,13 +30883,13 @@
         <v>0</v>
       </c>
       <c r="CT91" s="1">
-        <v>26025</v>
+        <v>26028</v>
       </c>
       <c r="CU91" s="1">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="CV91" s="1">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="CW91" s="1">
         <v>860</v>
@@ -31409,16 +31409,16 @@
         <v>0</v>
       </c>
       <c r="BR93" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV93" s="1">
         <v>0</v>
@@ -31493,16 +31493,16 @@
         <v>0</v>
       </c>
       <c r="CT93" s="1">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="CU93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV93" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CW93" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -32177,7 +32177,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V96" s="1">
         <v>9</v>
@@ -32225,7 +32225,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL96" s="1">
         <v>96</v>
@@ -32333,7 +32333,7 @@
         <v>0</v>
       </c>
       <c r="BU96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV96" s="1">
         <v>0</v>
@@ -32417,7 +32417,7 @@
         <v>3</v>
       </c>
       <c r="CW96" s="1">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:101">
@@ -34363,16 +34363,16 @@
         <v>0</v>
       </c>
       <c r="AL103" s="1">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM103" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN103" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO103" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP103" s="1">
         <v>0</v>
@@ -34507,16 +34507,16 @@
         <v>0</v>
       </c>
       <c r="CH103" s="1">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="CI103" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="CJ103" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="CK103" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="CL103" s="1">
         <v>0</v>
@@ -34543,16 +34543,16 @@
         <v>0</v>
       </c>
       <c r="CT103" s="1">
-        <v>1087</v>
+        <v>1110</v>
       </c>
       <c r="CU103" s="1">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="CV103" s="1">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="CW103" s="1">
-        <v>261</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34572,16 +34572,16 @@
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G104" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I104" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J104" s="1">
         <v>0</v>
@@ -34848,16 +34848,16 @@
         <v>0</v>
       </c>
       <c r="CT104" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CU104" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV104" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CW104" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:101">
@@ -34889,28 +34889,28 @@
         <v>2</v>
       </c>
       <c r="J105" s="1">
-        <v>1011</v>
+        <v>1026</v>
       </c>
       <c r="K105" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L105" s="2">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M105" s="2">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="N105" s="1">
-        <v>1428</v>
+        <v>1461</v>
       </c>
       <c r="O105" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P105" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q105" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R105" s="1">
         <v>0</v>
@@ -34991,7 +34991,7 @@
         <v>0</v>
       </c>
       <c r="AR105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS105" s="2">
         <v>4</v>
@@ -35153,16 +35153,16 @@
         <v>0</v>
       </c>
       <c r="CT105" s="1">
-        <v>8005</v>
+        <v>8053</v>
       </c>
       <c r="CU105" s="1">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="CV105" s="1">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="CW105" s="1">
-        <v>501</v>
+        <v>549</v>
       </c>
     </row>
     <row r="106" spans="1:101">
@@ -36390,16 +36390,16 @@
         <v>209</v>
       </c>
       <c r="B110" s="1">
-        <v>2498</v>
+        <v>2509</v>
       </c>
       <c r="C110" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D110" s="2">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E110" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -36426,16 +36426,16 @@
         <v>446</v>
       </c>
       <c r="N110" s="1">
-        <v>1304</v>
+        <v>1344</v>
       </c>
       <c r="O110" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="P110" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="Q110" s="2">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="R110" s="1">
         <v>0</v>
@@ -36678,16 +36678,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13438</v>
+        <v>13489</v>
       </c>
       <c r="CU110" s="1">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="CV110" s="1">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="CW110" s="1">
-        <v>1046</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -37024,16 +37024,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="1">
-        <v>1131</v>
+        <v>1145</v>
       </c>
       <c r="K112" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L112" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M112" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="N112" s="1">
         <v>5612</v>
@@ -37288,16 +37288,16 @@
         <v>0</v>
       </c>
       <c r="CT112" s="1">
-        <v>8305</v>
+        <v>8319</v>
       </c>
       <c r="CU112" s="1">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="CV112" s="1">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="CW112" s="1">
-        <v>655</v>
+        <v>669</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37622,16 +37622,16 @@
         <v>1</v>
       </c>
       <c r="F114" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="2">
         <v>3</v>
       </c>
       <c r="I114" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114" s="1">
         <v>0</v>
@@ -37898,16 +37898,16 @@
         <v>0</v>
       </c>
       <c r="CT114" s="1">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CU114" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV114" s="1">
         <v>3</v>
       </c>
       <c r="CW114" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:101">
@@ -38412,16 +38412,16 @@
         <v>1</v>
       </c>
       <c r="BN116" s="1">
-        <v>929</v>
+        <v>1101</v>
       </c>
       <c r="BO116" s="2">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="BP116" s="2">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="BQ116" s="2">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="BR116" s="1">
         <v>1</v>
@@ -38508,16 +38508,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21820</v>
+        <v>21992</v>
       </c>
       <c r="CU116" s="1">
-        <v>70</v>
+        <v>242</v>
       </c>
       <c r="CV116" s="1">
-        <v>369</v>
+        <v>541</v>
       </c>
       <c r="CW116" s="1">
-        <v>1137</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38558,7 +38558,7 @@
         <v>5</v>
       </c>
       <c r="M117" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N117" s="1">
         <v>2543</v>
@@ -38726,7 +38726,7 @@
         <v>0</v>
       </c>
       <c r="BQ117" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BR117" s="1">
         <v>0</v>
@@ -38822,7 +38822,7 @@
         <v>388</v>
       </c>
       <c r="CW117" s="1">
-        <v>1213</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39548,16 +39548,16 @@
         <v>0</v>
       </c>
       <c r="AL120" s="1">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AM120" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AN120" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AO120" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AP120" s="1">
         <v>0</v>
@@ -39692,16 +39692,16 @@
         <v>0</v>
       </c>
       <c r="CH120" s="1">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="CI120" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CJ120" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="CK120" s="2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="CL120" s="1">
         <v>0</v>
@@ -39728,16 +39728,16 @@
         <v>0</v>
       </c>
       <c r="CT120" s="1">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="CU120" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="CV120" s="1">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="CW120" s="1">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:101">
@@ -40397,7 +40397,7 @@
         <v>0</v>
       </c>
       <c r="P123" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="2">
         <v>9</v>
@@ -40649,7 +40649,7 @@
         <v>4</v>
       </c>
       <c r="CV123" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CW123" s="1">
         <v>30</v>
@@ -41282,13 +41282,13 @@
         <v>0</v>
       </c>
       <c r="F126" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G126" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I126" s="2">
         <v>6</v>
@@ -41558,13 +41558,13 @@
         <v>0</v>
       </c>
       <c r="CT126" s="1">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="CU126" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="CV126" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CW126" s="1">
         <v>66</v>
@@ -41692,7 +41692,7 @@
         <v>12</v>
       </c>
       <c r="AO127" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="AP127" s="1">
         <v>0</v>
@@ -41848,7 +41848,7 @@
         <v>0</v>
       </c>
       <c r="CO127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP127" s="1">
         <v>0</v>
@@ -41872,7 +41872,7 @@
         <v>45</v>
       </c>
       <c r="CW127" s="1">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:101">
@@ -42532,7 +42532,7 @@
         <v>0</v>
       </c>
       <c r="P130" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="2">
         <v>85</v>
@@ -42604,10 +42604,10 @@
         <v>5</v>
       </c>
       <c r="AN130" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AO130" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AP130" s="1">
         <v>0</v>
@@ -42748,10 +42748,10 @@
         <v>1</v>
       </c>
       <c r="CJ130" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="CK130" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="CL130" s="1">
         <v>0</v>
@@ -42784,10 +42784,10 @@
         <v>6</v>
       </c>
       <c r="CV130" s="1">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="CW130" s="1">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43423,7 +43423,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I133" s="2">
         <v>5</v>
@@ -43699,7 +43699,7 @@
         <v>1</v>
       </c>
       <c r="CV133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW133" s="1">
         <v>9</v>
@@ -43752,7 +43752,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="2">
-        <v>718</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="2">
         <v>1759</v>
@@ -43830,16 +43830,16 @@
         <v>15</v>
       </c>
       <c r="AP134" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AQ134" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR134" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS134" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT134" s="1">
         <v>0</v>
@@ -43962,16 +43962,16 @@
         <v>0</v>
       </c>
       <c r="CH134" s="1">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="CI134" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CJ134" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="CK134" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="CL134" s="1">
         <v>9</v>
@@ -43998,16 +43998,16 @@
         <v>0</v>
       </c>
       <c r="CT134" s="1">
-        <v>134463</v>
+        <v>134467</v>
       </c>
       <c r="CU134" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CV134" s="1">
-        <v>2521</v>
+        <v>1808</v>
       </c>
       <c r="CW134" s="1">
-        <v>5801</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="135" spans="1:101">
@@ -44021,7 +44021,7 @@
         <v>39</v>
       </c>
       <c r="D135" s="2">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="E135" s="2">
         <v>305</v>
@@ -44045,7 +44045,7 @@
         <v>57</v>
       </c>
       <c r="L135" s="2">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="M135" s="2">
         <v>438</v>
@@ -44099,16 +44099,16 @@
         <v>8</v>
       </c>
       <c r="AD135" s="1">
-        <v>11790</v>
+        <v>11840</v>
       </c>
       <c r="AE135" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AF135" s="2">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="AG135" s="2">
-        <v>752</v>
+        <v>802</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44207,16 +44207,16 @@
         <v>2</v>
       </c>
       <c r="BN135" s="1">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="BO135" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP135" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ135" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BR135" s="1">
         <v>0</v>
@@ -44303,16 +44303,16 @@
         <v>0</v>
       </c>
       <c r="CT135" s="1">
-        <v>62762</v>
+        <v>62814</v>
       </c>
       <c r="CU135" s="1">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="CV135" s="1">
-        <v>941</v>
+        <v>889</v>
       </c>
       <c r="CW135" s="1">
-        <v>2690</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44745,16 +44745,16 @@
         <v>0</v>
       </c>
       <c r="AP137" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AQ137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR137" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS137" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT137" s="1">
         <v>0</v>
@@ -44877,16 +44877,16 @@
         <v>0</v>
       </c>
       <c r="CH137" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="CI137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK137" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL137" s="1">
         <v>43</v>
@@ -44913,16 +44913,16 @@
         <v>0</v>
       </c>
       <c r="CT137" s="1">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="CU137" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CV137" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CW137" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:101">
@@ -44954,16 +44954,16 @@
         <v>1</v>
       </c>
       <c r="J138" s="1">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="K138" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L138" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M138" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N138" s="1">
         <v>2200</v>
@@ -44972,7 +44972,7 @@
         <v>0</v>
       </c>
       <c r="P138" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q138" s="2">
         <v>135</v>
@@ -45047,7 +45047,7 @@
         <v>2</v>
       </c>
       <c r="AO138" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AP138" s="1">
         <v>24</v>
@@ -45056,7 +45056,7 @@
         <v>0</v>
       </c>
       <c r="AR138" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS138" s="2">
         <v>3</v>
@@ -45188,10 +45188,10 @@
         <v>0</v>
       </c>
       <c r="CJ138" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CK138" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CL138" s="1">
         <v>5</v>
@@ -45218,16 +45218,16 @@
         <v>0</v>
       </c>
       <c r="CT138" s="1">
-        <v>4425</v>
+        <v>4437</v>
       </c>
       <c r="CU138" s="1">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="CV138" s="1">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="CW138" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -46150,16 +46150,16 @@
         <v>241</v>
       </c>
       <c r="B142" s="1">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C142" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E142" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1">
         <v>15</v>
@@ -46186,16 +46186,16 @@
         <v>70</v>
       </c>
       <c r="N142" s="1">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O142" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P142" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q142" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R142" s="1">
         <v>0</v>
@@ -46264,7 +46264,7 @@
         <v>0</v>
       </c>
       <c r="AN142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO142" s="2">
         <v>4</v>
@@ -46408,7 +46408,7 @@
         <v>1</v>
       </c>
       <c r="CJ142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CK142" s="2">
         <v>4</v>
@@ -46438,16 +46438,16 @@
         <v>0</v>
       </c>
       <c r="CT142" s="1">
-        <v>1674</v>
+        <v>1688</v>
       </c>
       <c r="CU142" s="1">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="CV142" s="1">
         <v>61</v>
       </c>
       <c r="CW142" s="1">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46760,16 +46760,16 @@
         <v>243</v>
       </c>
       <c r="B144" s="1">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E144" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F144" s="1">
         <v>15</v>
@@ -46877,7 +46877,7 @@
         <v>2</v>
       </c>
       <c r="AO144" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP144" s="1">
         <v>61</v>
@@ -47033,7 +47033,7 @@
         <v>2</v>
       </c>
       <c r="CO144" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CP144" s="1">
         <v>0</v>
@@ -47048,16 +47048,16 @@
         <v>0</v>
       </c>
       <c r="CT144" s="1">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="CU144" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV144" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CW144" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:101">
@@ -47095,7 +47095,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M145" s="2">
         <v>19</v>
@@ -47275,7 +47275,7 @@
         <v>0</v>
       </c>
       <c r="BT145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU145" s="2">
         <v>2</v>
@@ -47359,7 +47359,7 @@
         <v>7</v>
       </c>
       <c r="CV145" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="CW145" s="1">
         <v>133</v>
@@ -50148,7 +50148,7 @@
         <v>10</v>
       </c>
       <c r="M155" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N155" s="1">
         <v>1204</v>
@@ -50325,7 +50325,7 @@
         <v>0</v>
       </c>
       <c r="BT155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU155" s="2">
         <v>1</v>
@@ -50409,10 +50409,10 @@
         <v>10</v>
       </c>
       <c r="CV155" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="CW155" s="1">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50420,16 +50420,16 @@
         <v>255</v>
       </c>
       <c r="B156" s="1">
-        <v>2046</v>
+        <v>2061</v>
       </c>
       <c r="C156" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D156" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E156" s="2">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -50537,7 +50537,7 @@
         <v>2</v>
       </c>
       <c r="AO156" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP156" s="1">
         <v>55</v>
@@ -50681,7 +50681,7 @@
         <v>47</v>
       </c>
       <c r="CK156" s="2">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="CL156" s="1">
         <v>13</v>
@@ -50708,16 +50708,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71529</v>
+        <v>71544</v>
       </c>
       <c r="CU156" s="1">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="CV156" s="1">
-        <v>1058</v>
+        <v>1073</v>
       </c>
       <c r="CW156" s="1">
-        <v>2490</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50734,7 +50734,7 @@
         <v>102</v>
       </c>
       <c r="E157" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -51022,7 +51022,7 @@
         <v>5231</v>
       </c>
       <c r="CW157" s="1">
-        <v>9194</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -52035,7 +52035,7 @@
         <v>0</v>
       </c>
       <c r="AF161" s="2">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="AG161" s="2">
         <v>457</v>
@@ -52185,16 +52185,16 @@
         <v>0</v>
       </c>
       <c r="CD161" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CE161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CH161" s="1">
         <v>814</v>
@@ -52233,16 +52233,16 @@
         <v>0</v>
       </c>
       <c r="CT161" s="1">
-        <v>22411</v>
+        <v>22412</v>
       </c>
       <c r="CU161" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CV161" s="1">
-        <v>702</v>
+        <v>390</v>
       </c>
       <c r="CW161" s="1">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -54284,16 +54284,16 @@
         <v>0</v>
       </c>
       <c r="BR168" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BS168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU168" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BV168" s="1">
         <v>2</v>
@@ -54368,16 +54368,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="CU168" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CV168" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="CW168" s="1">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54762,16 +54762,16 @@
         <v>0</v>
       </c>
       <c r="Z170" s="1">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AA170" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB170" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC170" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AD170" s="1">
         <v>3603</v>
@@ -54978,16 +54978,16 @@
         <v>0</v>
       </c>
       <c r="CT170" s="1">
-        <v>19650</v>
+        <v>19654</v>
       </c>
       <c r="CU170" s="1">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="CV170" s="1">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="CW170" s="1">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -56532,16 +56532,16 @@
         <v>6</v>
       </c>
       <c r="F176" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I176" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J176" s="1">
         <v>0</v>
@@ -56808,16 +56808,16 @@
         <v>0</v>
       </c>
       <c r="CT176" s="1">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="CU176" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CV176" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CW176" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57175,7 +57175,7 @@
         <v>1965</v>
       </c>
       <c r="Q178" s="2">
-        <v>4114</v>
+        <v>4116</v>
       </c>
       <c r="R178" s="1">
         <v>0</v>
@@ -57202,16 +57202,16 @@
         <v>1</v>
       </c>
       <c r="Z178" s="1">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AA178" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB178" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC178" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD178" s="1">
         <v>0</v>
@@ -57226,13 +57226,13 @@
         <v>0</v>
       </c>
       <c r="AH178" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ178" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK178" s="2">
         <v>2</v>
@@ -57247,19 +57247,19 @@
         <v>20</v>
       </c>
       <c r="AO178" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP178" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AQ178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT178" s="1">
         <v>10</v>
@@ -57391,7 +57391,7 @@
         <v>67</v>
       </c>
       <c r="CK178" s="2">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="CL178" s="1">
         <v>7</v>
@@ -57418,16 +57418,16 @@
         <v>0</v>
       </c>
       <c r="CT178" s="1">
-        <v>84919</v>
+        <v>84925</v>
       </c>
       <c r="CU178" s="1">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="CV178" s="1">
-        <v>2163</v>
+        <v>2169</v>
       </c>
       <c r="CW178" s="1">
-        <v>4594</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57824,16 +57824,16 @@
         <v>0</v>
       </c>
       <c r="AD180" s="1">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="AE180" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AF180" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AG180" s="2">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="AH180" s="1">
         <v>1</v>
@@ -57944,16 +57944,16 @@
         <v>44</v>
       </c>
       <c r="BR180" s="1">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BS180" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="BT180" s="2">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="BU180" s="2">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="BV180" s="1">
         <v>0</v>
@@ -58028,16 +58028,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51287</v>
+        <v>51316</v>
       </c>
       <c r="CU180" s="1">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="CV180" s="1">
-        <v>1243</v>
+        <v>1272</v>
       </c>
       <c r="CW180" s="1">
-        <v>2644</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -59385,16 +59385,16 @@
         <v>0</v>
       </c>
       <c r="AP185" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR185" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS185" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT185" s="1">
         <v>0</v>
@@ -59517,16 +59517,16 @@
         <v>0</v>
       </c>
       <c r="CH185" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CI185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ185" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CK185" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL185" s="1">
         <v>25</v>
@@ -59553,16 +59553,16 @@
         <v>0</v>
       </c>
       <c r="CT185" s="1">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CU185" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV185" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW185" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -61203,16 +61203,16 @@
         <v>0</v>
       </c>
       <c r="AL191" s="1">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM191" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN191" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO191" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP191" s="1">
         <v>37</v>
@@ -61383,16 +61383,16 @@
         <v>0</v>
       </c>
       <c r="CT191" s="1">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="CU191" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CV191" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW191" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:101">
@@ -62136,7 +62136,7 @@
         <v>0</v>
       </c>
       <c r="AR194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS194" s="2">
         <v>4</v>
@@ -62268,7 +62268,7 @@
         <v>0</v>
       </c>
       <c r="CJ194" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CK194" s="2">
         <v>8</v>
@@ -62304,7 +62304,7 @@
         <v>37</v>
       </c>
       <c r="CV194" s="1">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="CW194" s="1">
         <v>1392</v>
@@ -62662,7 +62662,7 @@
         <v>0</v>
       </c>
       <c r="P196" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q196" s="2">
         <v>133</v>
@@ -62914,7 +62914,7 @@
         <v>10</v>
       </c>
       <c r="CV196" s="1">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="CW196" s="1">
         <v>214</v>
@@ -63948,16 +63948,16 @@
         <v>1</v>
       </c>
       <c r="AL200" s="1">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM200" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN200" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO200" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP200" s="1">
         <v>24</v>
@@ -64092,16 +64092,16 @@
         <v>0</v>
       </c>
       <c r="CH200" s="1">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="CI200" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CJ200" s="2">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="CK200" s="2">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="CL200" s="1">
         <v>9</v>
@@ -64128,16 +64128,16 @@
         <v>0</v>
       </c>
       <c r="CT200" s="1">
-        <v>16376</v>
+        <v>16393</v>
       </c>
       <c r="CU200" s="1">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="CV200" s="1">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="CW200" s="1">
-        <v>516</v>
+        <v>533</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64181,16 +64181,16 @@
         <v>258</v>
       </c>
       <c r="N201" s="1">
-        <v>23253</v>
+        <v>23255</v>
       </c>
       <c r="O201" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P201" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q201" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="R201" s="1">
         <v>0</v>
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64406,7 +64406,7 @@
         <v>64</v>
       </c>
       <c r="CK201" s="2">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="CL201" s="1">
         <v>5</v>
@@ -64433,16 +64433,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88297</v>
+        <v>88299</v>
       </c>
       <c r="CU201" s="1">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="CV201" s="1">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="CW201" s="1">
-        <v>3372</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64564,7 +64564,7 @@
         <v>3</v>
       </c>
       <c r="AN202" s="2">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="AO202" s="2">
         <v>90</v>
@@ -64708,7 +64708,7 @@
         <v>2</v>
       </c>
       <c r="CJ202" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CK202" s="2">
         <v>48</v>
@@ -64744,7 +64744,7 @@
         <v>6</v>
       </c>
       <c r="CV202" s="1">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="CW202" s="1">
         <v>140</v>
@@ -66292,16 +66292,16 @@
         <v>10</v>
       </c>
       <c r="F208" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G208" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H208" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" s="1">
         <v>0</v>
@@ -66568,16 +66568,16 @@
         <v>0</v>
       </c>
       <c r="CT208" s="1">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CU208" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV208" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CW208" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:101">
@@ -67919,7 +67919,7 @@
         <v>0</v>
       </c>
       <c r="AN213" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO213" s="2">
         <v>8</v>
@@ -68063,7 +68063,7 @@
         <v>1</v>
       </c>
       <c r="CJ213" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CK213" s="2">
         <v>12</v>
@@ -68099,7 +68099,7 @@
         <v>1</v>
       </c>
       <c r="CV213" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CW213" s="1">
         <v>28</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -4153,7 +4153,7 @@
         <v>200</v>
       </c>
       <c r="AG4" s="2">
-        <v>539</v>
+        <v>200</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>583</v>
       </c>
       <c r="CW4" s="1">
-        <v>1380</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4374,7 +4374,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1">
         <v>19</v>
@@ -4398,7 +4398,7 @@
         <v>61</v>
       </c>
       <c r="M5" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="N5" s="1">
         <v>2980</v>
@@ -4620,13 +4620,13 @@
         <v>3185</v>
       </c>
       <c r="CI5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ5" s="2">
         <v>2</v>
       </c>
       <c r="CK5" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="CL5" s="1">
         <v>0</v>
@@ -4656,13 +4656,13 @@
         <v>38719</v>
       </c>
       <c r="CU5" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="CV5" s="1">
         <v>376</v>
       </c>
       <c r="CW5" s="1">
-        <v>830</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5714,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="AS9" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT9" s="1">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="CK9" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CL9" s="1">
         <v>8</v>
@@ -5882,7 +5882,7 @@
         <v>22</v>
       </c>
       <c r="CW9" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7197,7 +7197,7 @@
         <v>1998</v>
       </c>
       <c r="AE14" s="2">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="2">
         <v>-20</v>
@@ -7401,7 +7401,7 @@
         <v>3164</v>
       </c>
       <c r="CU14" s="1">
-        <v>-17</v>
+        <v>1</v>
       </c>
       <c r="CV14" s="1">
         <v>85</v>
@@ -9057,7 +9057,7 @@
         <v>1</v>
       </c>
       <c r="AO20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP20" s="1">
         <v>79</v>
@@ -9201,7 +9201,7 @@
         <v>35</v>
       </c>
       <c r="CK20" s="2">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="CL20" s="1">
         <v>23</v>
@@ -9237,7 +9237,7 @@
         <v>159</v>
       </c>
       <c r="CW20" s="1">
-        <v>935</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -9374,7 +9374,7 @@
         <v>2</v>
       </c>
       <c r="AS21" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT21" s="1">
         <v>0</v>
@@ -9506,7 +9506,7 @@
         <v>19</v>
       </c>
       <c r="CK21" s="2">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="CL21" s="1">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         <v>30</v>
       </c>
       <c r="CW21" s="1">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:101">
@@ -11389,7 +11389,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1">
         <v>32</v>
@@ -11413,7 +11413,7 @@
         <v>34</v>
       </c>
       <c r="M28" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="N28" s="1">
         <v>2032</v>
@@ -11497,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="AO28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP28" s="1">
         <v>70</v>
@@ -11641,7 +11641,7 @@
         <v>16</v>
       </c>
       <c r="CK28" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="CL28" s="1">
         <v>20</v>
@@ -11677,7 +11677,7 @@
         <v>240</v>
       </c>
       <c r="CW28" s="1">
-        <v>763</v>
+        <v>738</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12412,13 +12412,13 @@
         <v>9</v>
       </c>
       <c r="AO31" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AP31" s="1">
         <v>19</v>
       </c>
       <c r="AQ31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR31" s="2">
         <v>1</v>
@@ -12550,13 +12550,13 @@
         <v>718</v>
       </c>
       <c r="CI31" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="CJ31" s="2">
         <v>151</v>
       </c>
       <c r="CK31" s="2">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="CL31" s="1">
         <v>19</v>
@@ -12586,13 +12586,13 @@
         <v>6044</v>
       </c>
       <c r="CU31" s="1">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CV31" s="1">
         <v>272</v>
       </c>
       <c r="CW31" s="1">
-        <v>413</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:101">
@@ -13333,7 +13333,7 @@
         <v>50</v>
       </c>
       <c r="AQ34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34" s="2">
         <v>2</v>
@@ -13465,7 +13465,7 @@
         <v>224</v>
       </c>
       <c r="CI34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ34" s="2">
         <v>5</v>
@@ -13501,7 +13501,7 @@
         <v>2588</v>
       </c>
       <c r="CU34" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV34" s="1">
         <v>30</v>
@@ -15043,7 +15043,7 @@
         <v>8828</v>
       </c>
       <c r="C40" s="2">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2">
         <v>79</v>
@@ -15331,7 +15331,7 @@
         <v>53532</v>
       </c>
       <c r="CU40" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="CV40" s="1">
         <v>406</v>
@@ -16371,7 +16371,7 @@
         <v>384</v>
       </c>
       <c r="AM44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" s="2">
         <v>4</v>
@@ -16527,7 +16527,7 @@
         <v>34</v>
       </c>
       <c r="CM44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN44" s="2">
         <v>1</v>
@@ -16551,7 +16551,7 @@
         <v>51690</v>
       </c>
       <c r="CU44" s="1">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="CV44" s="1">
         <v>1119</v>
@@ -18351,7 +18351,7 @@
         <v>21</v>
       </c>
       <c r="CK50" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CL50" s="1">
         <v>0</v>
@@ -18387,7 +18387,7 @@
         <v>32</v>
       </c>
       <c r="CW50" s="1">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:101">
@@ -18955,7 +18955,7 @@
         <v>119</v>
       </c>
       <c r="CI52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ52" s="2">
         <v>2</v>
@@ -18991,7 +18991,7 @@
         <v>318</v>
       </c>
       <c r="CU52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV52" s="1">
         <v>6</v>
@@ -19433,13 +19433,13 @@
         <v>16</v>
       </c>
       <c r="AQ54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR54" s="2">
         <v>2</v>
       </c>
       <c r="AS54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT54" s="1">
         <v>0</v>
@@ -19565,13 +19565,13 @@
         <v>131</v>
       </c>
       <c r="CI54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ54" s="2">
         <v>5</v>
       </c>
       <c r="CK54" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CL54" s="1">
         <v>8</v>
@@ -19601,13 +19601,13 @@
         <v>260</v>
       </c>
       <c r="CU54" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV54" s="1">
         <v>8</v>
       </c>
       <c r="CW54" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:101">
@@ -20037,7 +20037,7 @@
         <v>0</v>
       </c>
       <c r="AO56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP56" s="1">
         <v>4</v>
@@ -20181,7 +20181,7 @@
         <v>13</v>
       </c>
       <c r="CK56" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="CL56" s="1">
         <v>2</v>
@@ -20217,7 +20217,7 @@
         <v>108</v>
       </c>
       <c r="CW56" s="1">
-        <v>361</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -21478,7 +21478,7 @@
         <v>27</v>
       </c>
       <c r="M61" s="2">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N61" s="1">
         <v>43316</v>
@@ -21574,7 +21574,7 @@
         <v>2</v>
       </c>
       <c r="AS61" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT61" s="1">
         <v>0</v>
@@ -21706,7 +21706,7 @@
         <v>50</v>
       </c>
       <c r="CK61" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="CL61" s="1">
         <v>7</v>
@@ -21742,7 +21742,7 @@
         <v>194</v>
       </c>
       <c r="CW61" s="1">
-        <v>857</v>
+        <v>833</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22399,7 +22399,7 @@
         <v>4322</v>
       </c>
       <c r="O64" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P64" s="2">
         <v>73</v>
@@ -22453,7 +22453,7 @@
         <v>30</v>
       </c>
       <c r="AG64" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22651,13 +22651,13 @@
         <v>8065</v>
       </c>
       <c r="CU64" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="CV64" s="1">
         <v>153</v>
       </c>
       <c r="CW64" s="1">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22920,7 +22920,7 @@
         <v>1892</v>
       </c>
       <c r="CI65" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CJ65" s="2">
         <v>21</v>
@@ -22956,7 +22956,7 @@
         <v>67260</v>
       </c>
       <c r="CU65" s="1">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="CV65" s="1">
         <v>1777</v>
@@ -24313,7 +24313,7 @@
         <v>83</v>
       </c>
       <c r="AQ70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR70" s="2">
         <v>3</v>
@@ -24445,7 +24445,7 @@
         <v>165</v>
       </c>
       <c r="CI70" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ70" s="2">
         <v>4</v>
@@ -24481,7 +24481,7 @@
         <v>2274</v>
       </c>
       <c r="CU70" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CV70" s="1">
         <v>54</v>
@@ -24923,7 +24923,7 @@
         <v>24</v>
       </c>
       <c r="AQ72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR72" s="2">
         <v>3</v>
@@ -25055,7 +25055,7 @@
         <v>46</v>
       </c>
       <c r="CI72" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CJ72" s="2">
         <v>9</v>
@@ -25091,7 +25091,7 @@
         <v>543</v>
       </c>
       <c r="CU72" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CV72" s="1">
         <v>37</v>
@@ -25503,7 +25503,7 @@
         <v>0</v>
       </c>
       <c r="AG74" s="2">
-        <v>550</v>
+        <v>214</v>
       </c>
       <c r="AH74" s="1">
         <v>0</v>
@@ -25527,7 +25527,7 @@
         <v>125</v>
       </c>
       <c r="AO74" s="2">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25671,7 +25671,7 @@
         <v>182</v>
       </c>
       <c r="CK74" s="2">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25707,7 +25707,7 @@
         <v>542</v>
       </c>
       <c r="CW74" s="1">
-        <v>4342</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26586,7 +26586,7 @@
         <v>308</v>
       </c>
       <c r="CK77" s="2">
-        <v>587</v>
+        <v>545</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26598,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="CO77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP77" s="1">
         <v>14</v>
@@ -26622,7 +26622,7 @@
         <v>10153</v>
       </c>
       <c r="CW77" s="1">
-        <v>15766</v>
+        <v>15723</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26938,7 +26938,7 @@
         <v>4285</v>
       </c>
       <c r="C79" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D79" s="2">
         <v>20</v>
@@ -27226,7 +27226,7 @@
         <v>90690</v>
       </c>
       <c r="CU79" s="1">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="CV79" s="1">
         <v>622</v>
@@ -28188,7 +28188,7 @@
         <v>123</v>
       </c>
       <c r="M83" s="2">
-        <v>442</v>
+        <v>327</v>
       </c>
       <c r="N83" s="1">
         <v>40131</v>
@@ -28392,7 +28392,7 @@
         <v>0</v>
       </c>
       <c r="CC83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD83" s="1">
         <v>15</v>
@@ -28452,7 +28452,7 @@
         <v>808</v>
       </c>
       <c r="CW83" s="1">
-        <v>2074</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="84" spans="1:101">
@@ -29492,7 +29492,7 @@
         <v>1</v>
       </c>
       <c r="AO87" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AP87" s="1">
         <v>24</v>
@@ -29636,7 +29636,7 @@
         <v>45</v>
       </c>
       <c r="CK87" s="2">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="CL87" s="1">
         <v>15</v>
@@ -29672,7 +29672,7 @@
         <v>50</v>
       </c>
       <c r="CW87" s="1">
-        <v>112</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:101">
@@ -30628,7 +30628,7 @@
         <v>168</v>
       </c>
       <c r="M91" s="2">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="N91" s="1">
         <v>4418</v>
@@ -30892,7 +30892,7 @@
         <v>417</v>
       </c>
       <c r="CW91" s="1">
-        <v>860</v>
+        <v>809</v>
       </c>
     </row>
     <row r="92" spans="1:101">
@@ -30909,13 +30909,13 @@
         <v>2</v>
       </c>
       <c r="E92" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F92" s="1">
         <v>14</v>
       </c>
       <c r="G92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="2">
         <v>1</v>
@@ -31191,13 +31191,13 @@
         <v>3796</v>
       </c>
       <c r="CU92" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV92" s="1">
         <v>30</v>
       </c>
       <c r="CW92" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31334,7 +31334,7 @@
         <v>0</v>
       </c>
       <c r="AS93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT93" s="1">
         <v>0</v>
@@ -31460,13 +31460,13 @@
         <v>100</v>
       </c>
       <c r="CI93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ93" s="2">
         <v>5</v>
       </c>
       <c r="CK93" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CL93" s="1">
         <v>36</v>
@@ -31496,13 +31496,13 @@
         <v>1181</v>
       </c>
       <c r="CU93" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV93" s="1">
         <v>27</v>
       </c>
       <c r="CW93" s="1">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -32680,7 +32680,7 @@
         <v>42</v>
       </c>
       <c r="CI97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ97" s="2">
         <v>3</v>
@@ -32716,7 +32716,7 @@
         <v>225</v>
       </c>
       <c r="CU97" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CV97" s="1">
         <v>7</v>
@@ -34061,7 +34061,7 @@
         <v>236</v>
       </c>
       <c r="AM102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN102" s="2">
         <v>5</v>
@@ -34205,7 +34205,7 @@
         <v>1803</v>
       </c>
       <c r="CI102" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ102" s="2">
         <v>45</v>
@@ -34241,7 +34241,7 @@
         <v>43148</v>
       </c>
       <c r="CU102" s="1">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="CV102" s="1">
         <v>536</v>
@@ -35287,7 +35287,7 @@
         <v>7</v>
       </c>
       <c r="AO106" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP106" s="1">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>172</v>
       </c>
       <c r="CK106" s="2">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="CL106" s="1">
         <v>0</v>
@@ -35467,7 +35467,7 @@
         <v>1015</v>
       </c>
       <c r="CW106" s="1">
-        <v>2386</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36423,13 +36423,13 @@
         <v>240</v>
       </c>
       <c r="M110" s="2">
-        <v>446</v>
+        <v>381</v>
       </c>
       <c r="N110" s="1">
         <v>1344</v>
       </c>
       <c r="O110" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P110" s="2">
         <v>41</v>
@@ -36681,13 +36681,13 @@
         <v>13489</v>
       </c>
       <c r="CU110" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="CV110" s="1">
         <v>450</v>
       </c>
       <c r="CW110" s="1">
-        <v>1097</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36812,7 +36812,7 @@
         <v>5</v>
       </c>
       <c r="AO111" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AP111" s="1">
         <v>46</v>
@@ -36956,7 +36956,7 @@
         <v>19</v>
       </c>
       <c r="CK111" s="2">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36992,7 +36992,7 @@
         <v>29</v>
       </c>
       <c r="CW111" s="1">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37027,13 +37027,13 @@
         <v>1145</v>
       </c>
       <c r="K112" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L112" s="2">
         <v>41</v>
       </c>
       <c r="M112" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="N112" s="1">
         <v>5612</v>
@@ -37291,13 +37291,13 @@
         <v>8319</v>
       </c>
       <c r="CU112" s="1">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="CV112" s="1">
         <v>267</v>
       </c>
       <c r="CW112" s="1">
-        <v>669</v>
+        <v>649</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37338,7 +37338,7 @@
         <v>161</v>
       </c>
       <c r="M113" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="N113" s="1">
         <v>8023</v>
@@ -37602,7 +37602,7 @@
         <v>1710</v>
       </c>
       <c r="CW113" s="1">
-        <v>11129</v>
+        <v>11053</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38253,7 +38253,7 @@
         <v>127</v>
       </c>
       <c r="M116" s="2">
-        <v>275</v>
+        <v>207</v>
       </c>
       <c r="N116" s="1">
         <v>4537</v>
@@ -38517,7 +38517,7 @@
         <v>541</v>
       </c>
       <c r="CW116" s="1">
-        <v>1309</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38726,7 +38726,7 @@
         <v>0</v>
       </c>
       <c r="BQ117" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BR117" s="1">
         <v>0</v>
@@ -38822,7 +38822,7 @@
         <v>388</v>
       </c>
       <c r="CW117" s="1">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -41285,7 +41285,7 @@
         <v>66</v>
       </c>
       <c r="G126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2">
         <v>4</v>
@@ -41561,7 +41561,7 @@
         <v>885</v>
       </c>
       <c r="CU126" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CV126" s="1">
         <v>53</v>
@@ -41686,7 +41686,7 @@
         <v>961</v>
       </c>
       <c r="AM127" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN127" s="2">
         <v>12</v>
@@ -41830,7 +41830,7 @@
         <v>546</v>
       </c>
       <c r="CI127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ127" s="2">
         <v>11</v>
@@ -41866,7 +41866,7 @@
         <v>2594</v>
       </c>
       <c r="CU127" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CV127" s="1">
         <v>45</v>
@@ -42511,7 +42511,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J130" s="1">
         <v>0</v>
@@ -42787,7 +42787,7 @@
         <v>18</v>
       </c>
       <c r="CW130" s="1">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="131" spans="1:101">
@@ -43121,7 +43121,7 @@
         <v>2</v>
       </c>
       <c r="I132" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J132" s="1">
         <v>0</v>
@@ -43397,7 +43397,7 @@
         <v>2</v>
       </c>
       <c r="CW132" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:101">
@@ -43797,7 +43797,7 @@
         <v>79708</v>
       </c>
       <c r="AE134" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AF134" s="2">
         <v>1745</v>
@@ -44001,7 +44001,7 @@
         <v>134467</v>
       </c>
       <c r="CU134" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV134" s="1">
         <v>1808</v>
@@ -44024,7 +44024,7 @@
         <v>81</v>
       </c>
       <c r="E135" s="2">
-        <v>305</v>
+        <v>224</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -44048,7 +44048,7 @@
         <v>118</v>
       </c>
       <c r="M135" s="2">
-        <v>438</v>
+        <v>347</v>
       </c>
       <c r="N135" s="1">
         <v>32057</v>
@@ -44276,7 +44276,7 @@
         <v>93</v>
       </c>
       <c r="CK135" s="2">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="CL135" s="1">
         <v>13</v>
@@ -44312,7 +44312,7 @@
         <v>889</v>
       </c>
       <c r="CW135" s="1">
-        <v>2742</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -45041,7 +45041,7 @@
         <v>215</v>
       </c>
       <c r="AM138" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN138" s="2">
         <v>2</v>
@@ -45197,7 +45197,7 @@
         <v>5</v>
       </c>
       <c r="CM138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN138" s="2">
         <v>2</v>
@@ -45221,7 +45221,7 @@
         <v>4437</v>
       </c>
       <c r="CU138" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="CV138" s="1">
         <v>75</v>
@@ -45854,7 +45854,7 @@
         <v>4</v>
       </c>
       <c r="E141" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F141" s="1">
         <v>50</v>
@@ -45890,7 +45890,7 @@
         <v>0</v>
       </c>
       <c r="Q141" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R141" s="1">
         <v>1</v>
@@ -46058,7 +46058,7 @@
         <v>1</v>
       </c>
       <c r="BU141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV141" s="1">
         <v>0</v>
@@ -46142,7 +46142,7 @@
         <v>10</v>
       </c>
       <c r="CW141" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:101">
@@ -46171,7 +46171,7 @@
         <v>1</v>
       </c>
       <c r="I142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J142" s="1">
         <v>461</v>
@@ -46273,7 +46273,7 @@
         <v>53</v>
       </c>
       <c r="AQ142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR142" s="2">
         <v>2</v>
@@ -46405,7 +46405,7 @@
         <v>115</v>
       </c>
       <c r="CI142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ142" s="2">
         <v>3</v>
@@ -46441,13 +46441,13 @@
         <v>1688</v>
       </c>
       <c r="CU142" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="CV142" s="1">
         <v>61</v>
       </c>
       <c r="CW142" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143" spans="1:101">
@@ -46476,7 +46476,7 @@
         <v>2</v>
       </c>
       <c r="I143" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J143" s="1">
         <v>0</v>
@@ -46584,7 +46584,7 @@
         <v>2</v>
       </c>
       <c r="AS143" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT143" s="1">
         <v>0</v>
@@ -46728,7 +46728,7 @@
         <v>2</v>
       </c>
       <c r="CO143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP143" s="1">
         <v>0</v>
@@ -46752,7 +46752,7 @@
         <v>11</v>
       </c>
       <c r="CW143" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:101">
@@ -47074,7 +47074,7 @@
         <v>11</v>
       </c>
       <c r="E145" s="2">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -47098,7 +47098,7 @@
         <v>5</v>
       </c>
       <c r="M145" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N145" s="1">
         <v>815</v>
@@ -47170,7 +47170,7 @@
         <v>0</v>
       </c>
       <c r="AK145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL145" s="1">
         <v>30</v>
@@ -47212,7 +47212,7 @@
         <v>41</v>
       </c>
       <c r="AY145" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ145" s="2">
         <v>4</v>
@@ -47278,7 +47278,7 @@
         <v>0</v>
       </c>
       <c r="BU145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BV145" s="1">
         <v>0</v>
@@ -47326,7 +47326,7 @@
         <v>2</v>
       </c>
       <c r="CK145" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CL145" s="1">
         <v>41</v>
@@ -47356,13 +47356,13 @@
         <v>2483</v>
       </c>
       <c r="CU145" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CV145" s="1">
         <v>44</v>
       </c>
       <c r="CW145" s="1">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="146" spans="1:101">
@@ -48127,7 +48127,7 @@
         <v>12</v>
       </c>
       <c r="AY148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ148" s="2">
         <v>1</v>
@@ -48271,7 +48271,7 @@
         <v>5615</v>
       </c>
       <c r="CU148" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV148" s="1">
         <v>100</v>
@@ -48719,7 +48719,7 @@
         <v>3</v>
       </c>
       <c r="AS150" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT150" s="1">
         <v>0</v>
@@ -48863,7 +48863,7 @@
         <v>2</v>
       </c>
       <c r="CO150" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CP150" s="1">
         <v>0</v>
@@ -48887,7 +48887,7 @@
         <v>7</v>
       </c>
       <c r="CW150" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:101">
@@ -49233,7 +49233,7 @@
         <v>28</v>
       </c>
       <c r="M152" s="2">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="N152" s="1">
         <v>168</v>
@@ -49329,7 +49329,7 @@
         <v>3</v>
       </c>
       <c r="AS152" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT152" s="1">
         <v>0</v>
@@ -49461,7 +49461,7 @@
         <v>11</v>
       </c>
       <c r="CK152" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CL152" s="1">
         <v>9</v>
@@ -49497,7 +49497,7 @@
         <v>55</v>
       </c>
       <c r="CW152" s="1">
-        <v>273</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50244,7 +50244,7 @@
         <v>3</v>
       </c>
       <c r="AS155" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT155" s="1">
         <v>1</v>
@@ -50376,7 +50376,7 @@
         <v>10</v>
       </c>
       <c r="CK155" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CL155" s="1">
         <v>1</v>
@@ -50412,7 +50412,7 @@
         <v>44</v>
       </c>
       <c r="CW155" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50818,7 +50818,7 @@
         <v>4692</v>
       </c>
       <c r="AG157" s="2">
-        <v>8205</v>
+        <v>4692</v>
       </c>
       <c r="AH157" s="1">
         <v>0</v>
@@ -51022,7 +51022,7 @@
         <v>5231</v>
       </c>
       <c r="CW157" s="1">
-        <v>9150</v>
+        <v>5637</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -52038,7 +52038,7 @@
         <v>0</v>
       </c>
       <c r="AG161" s="2">
-        <v>457</v>
+        <v>313</v>
       </c>
       <c r="AH161" s="1">
         <v>7</v>
@@ -52056,7 +52056,7 @@
         <v>163</v>
       </c>
       <c r="AM161" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN161" s="2">
         <v>11</v>
@@ -52200,7 +52200,7 @@
         <v>814</v>
       </c>
       <c r="CI161" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ161" s="2">
         <v>21</v>
@@ -52236,13 +52236,13 @@
         <v>22412</v>
       </c>
       <c r="CU161" s="1">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="CV161" s="1">
         <v>390</v>
       </c>
       <c r="CW161" s="1">
-        <v>1243</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52989,7 +52989,7 @@
         <v>2</v>
       </c>
       <c r="AS164" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT164" s="1">
         <v>0</v>
@@ -53121,7 +53121,7 @@
         <v>4</v>
       </c>
       <c r="CK164" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CL164" s="1">
         <v>4</v>
@@ -53157,7 +53157,7 @@
         <v>100</v>
       </c>
       <c r="CW164" s="1">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53479,7 +53479,7 @@
         <v>4</v>
       </c>
       <c r="E166" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F166" s="1">
         <v>8</v>
@@ -53497,7 +53497,7 @@
         <v>1731</v>
       </c>
       <c r="K166" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L166" s="2">
         <v>47</v>
@@ -53761,13 +53761,13 @@
         <v>5290</v>
       </c>
       <c r="CU166" s="1">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="CV166" s="1">
         <v>114</v>
       </c>
       <c r="CW166" s="1">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54107,7 +54107,7 @@
         <v>1343</v>
       </c>
       <c r="K168" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L168" s="2">
         <v>34</v>
@@ -54371,7 +54371,7 @@
         <v>5976</v>
       </c>
       <c r="CU168" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="CV168" s="1">
         <v>115</v>
@@ -56165,7 +56165,7 @@
         <v>24</v>
       </c>
       <c r="CI174" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ174" s="2">
         <v>2</v>
@@ -56201,7 +56201,7 @@
         <v>488</v>
       </c>
       <c r="CU174" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV174" s="1">
         <v>23</v>
@@ -56637,7 +56637,7 @@
         <v>18</v>
       </c>
       <c r="AO176" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP176" s="1">
         <v>0</v>
@@ -56781,7 +56781,7 @@
         <v>62</v>
       </c>
       <c r="CK176" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="CL176" s="1">
         <v>0</v>
@@ -56817,7 +56817,7 @@
         <v>83</v>
       </c>
       <c r="CW176" s="1">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57133,13 +57133,13 @@
         <v>7840</v>
       </c>
       <c r="C178" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D178" s="2">
         <v>73</v>
       </c>
       <c r="E178" s="2">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -57157,13 +57157,13 @@
         <v>1805</v>
       </c>
       <c r="K178" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L178" s="2">
         <v>36</v>
       </c>
       <c r="M178" s="2">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="N178" s="1">
         <v>73111</v>
@@ -57421,13 +57421,13 @@
         <v>84925</v>
       </c>
       <c r="CU178" s="1">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="CV178" s="1">
         <v>2169</v>
       </c>
       <c r="CW178" s="1">
-        <v>4567</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="179" spans="1:101">
@@ -57773,7 +57773,7 @@
         <v>31</v>
       </c>
       <c r="M180" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="N180" s="1">
         <v>36939</v>
@@ -58037,7 +58037,7 @@
         <v>1272</v>
       </c>
       <c r="CW180" s="1">
-        <v>2673</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -61655,7 +61655,7 @@
         <v>414</v>
       </c>
       <c r="CI192" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CJ192" s="2">
         <v>6</v>
@@ -61691,7 +61691,7 @@
         <v>619</v>
       </c>
       <c r="CU192" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CV192" s="1">
         <v>10</v>
@@ -62043,7 +62043,7 @@
         <v>47</v>
       </c>
       <c r="M194" s="2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N194" s="1">
         <v>29177</v>
@@ -62307,7 +62307,7 @@
         <v>598</v>
       </c>
       <c r="CW194" s="1">
-        <v>1392</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="195" spans="1:101">
@@ -63843,13 +63843,13 @@
         <v>4308</v>
       </c>
       <c r="C200" s="2">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D200" s="2">
         <v>99</v>
       </c>
       <c r="E200" s="2">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="F200" s="1">
         <v>0</v>
@@ -63873,7 +63873,7 @@
         <v>45</v>
       </c>
       <c r="M200" s="2">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="N200" s="1">
         <v>7998</v>
@@ -64131,13 +64131,13 @@
         <v>16393</v>
       </c>
       <c r="CU200" s="1">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="CV200" s="1">
         <v>237</v>
       </c>
       <c r="CW200" s="1">
-        <v>533</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:101">
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>2083</v>
+        <v>1649</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64442,7 +64442,7 @@
         <v>2157</v>
       </c>
       <c r="CW201" s="1">
-        <v>3352</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64561,7 +64561,7 @@
         <v>445</v>
       </c>
       <c r="AM202" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN202" s="2">
         <v>19</v>
@@ -64705,7 +64705,7 @@
         <v>428</v>
       </c>
       <c r="CI202" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ202" s="2">
         <v>10</v>
@@ -64741,7 +64741,7 @@
         <v>910</v>
       </c>
       <c r="CU202" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CV202" s="1">
         <v>32</v>
@@ -66068,7 +66068,7 @@
         <v>157</v>
       </c>
       <c r="AG207" s="2">
-        <v>296</v>
+        <v>195</v>
       </c>
       <c r="AH207" s="1">
         <v>0</v>
@@ -66272,7 +66272,7 @@
         <v>315</v>
       </c>
       <c r="CW207" s="1">
-        <v>649</v>
+        <v>548</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -66696,7 +66696,7 @@
         <v>32</v>
       </c>
       <c r="AM209" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN209" s="2">
         <v>7</v>
@@ -66840,7 +66840,7 @@
         <v>245</v>
       </c>
       <c r="CI209" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CJ209" s="2">
         <v>39</v>
@@ -66876,7 +66876,7 @@
         <v>735</v>
       </c>
       <c r="CU209" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CV209" s="1">
         <v>65</v>
@@ -67204,7 +67204,7 @@
         <v>11</v>
       </c>
       <c r="E211" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F211" s="1">
         <v>15</v>
@@ -67288,7 +67288,7 @@
         <v>382</v>
       </c>
       <c r="AG211" s="2">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="AH211" s="1">
         <v>3</v>
@@ -67492,7 +67492,7 @@
         <v>497</v>
       </c>
       <c r="CW211" s="1">
-        <v>671</v>
+        <v>608</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69900,7 +69900,7 @@
         <v>594</v>
       </c>
       <c r="D74">
-        <v>2240</v>
+        <v>2253</v>
       </c>
       <c r="E74" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3761,7 +3761,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2">
         <v>32</v>
@@ -3785,10 +3785,10 @@
         <v>44</v>
       </c>
       <c r="L3" s="2">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="M3" s="2">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="N3" s="1">
         <v>19611</v>
@@ -3845,10 +3845,10 @@
         <v>2</v>
       </c>
       <c r="AF3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG3" s="2">
-        <v>727</v>
+        <v>295</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="AR3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS3" s="2">
         <v>5</v>
@@ -3947,16 +3947,16 @@
         <v>0</v>
       </c>
       <c r="BN3" s="1">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="BO3" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP3" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BQ3" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BR3" s="1">
         <v>3</v>
@@ -4013,7 +4013,7 @@
         <v>16</v>
       </c>
       <c r="CJ3" s="2">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="CK3" s="2">
         <v>117</v>
@@ -4043,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="CT3" s="1">
-        <v>46754</v>
+        <v>46759</v>
       </c>
       <c r="CU3" s="1">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="CV3" s="1">
-        <v>504</v>
+        <v>434</v>
       </c>
       <c r="CW3" s="1">
-        <v>2049</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4093,7 +4093,7 @@
         <v>183</v>
       </c>
       <c r="M4" s="2">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="N4" s="1">
         <v>9299</v>
@@ -4357,7 +4357,7 @@
         <v>583</v>
       </c>
       <c r="CW4" s="1">
-        <v>1041</v>
+        <v>976</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
@@ -4395,7 +4395,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2">
         <v>99</v>
@@ -4458,7 +4458,7 @@
         <v>291</v>
       </c>
       <c r="AG5" s="2">
-        <v>608</v>
+        <v>237</v>
       </c>
       <c r="AH5" s="1">
         <v>0</v>
@@ -4659,10 +4659,10 @@
         <v>37</v>
       </c>
       <c r="CV5" s="1">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="CW5" s="1">
-        <v>794</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:101">
@@ -5131,16 +5131,16 @@
         <v>0</v>
       </c>
       <c r="BB7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BF7" s="1">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>0</v>
       </c>
       <c r="CT7" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="CU7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CV7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CW7" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:101">
@@ -5630,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="AL9" s="1">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AM9" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN9" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO9" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP9" s="1">
         <v>44</v>
@@ -5837,16 +5837,16 @@
         <v>1</v>
       </c>
       <c r="CH9" s="1">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="CI9" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CJ9" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CK9" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CL9" s="1">
         <v>8</v>
@@ -5873,16 +5873,16 @@
         <v>0</v>
       </c>
       <c r="CT9" s="1">
-        <v>2873</v>
+        <v>2879</v>
       </c>
       <c r="CU9" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV9" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="CW9" s="1">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:101">
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AF14" s="2">
+        <v>-11</v>
+      </c>
+      <c r="AG14" s="2">
         <v>-20</v>
-      </c>
-      <c r="AG14" s="2">
-        <v>65</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -7362,16 +7362,16 @@
         <v>0</v>
       </c>
       <c r="CH14" s="1">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="CI14" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ14" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="CK14" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="CL14" s="1">
         <v>29</v>
@@ -7398,16 +7398,16 @@
         <v>0</v>
       </c>
       <c r="CT14" s="1">
-        <v>3164</v>
+        <v>3167</v>
       </c>
       <c r="CU14" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CV14" s="1">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="CW14" s="1">
-        <v>231</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:101">
@@ -8142,7 +8142,7 @@
         <v>3</v>
       </c>
       <c r="AO17" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AP17" s="1">
         <v>29</v>
@@ -8286,7 +8286,7 @@
         <v>12</v>
       </c>
       <c r="CK17" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CL17" s="1">
         <v>29</v>
@@ -8322,7 +8322,7 @@
         <v>15</v>
       </c>
       <c r="CW17" s="1">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8342,16 +8342,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -8618,16 +8618,16 @@
         <v>0</v>
       </c>
       <c r="CT18" s="1">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CU18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CW18" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -8949,7 +8949,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="2">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -8973,7 +8973,7 @@
         <v>14</v>
       </c>
       <c r="M20" s="2">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="N20" s="1">
         <v>12654</v>
@@ -9198,7 +9198,7 @@
         <v>10</v>
       </c>
       <c r="CJ20" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="CK20" s="2">
         <v>45</v>
@@ -9234,10 +9234,10 @@
         <v>53</v>
       </c>
       <c r="CV20" s="1">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="CW20" s="1">
-        <v>916</v>
+        <v>859</v>
       </c>
     </row>
     <row r="21" spans="1:101">
@@ -11473,7 +11473,7 @@
         <v>173</v>
       </c>
       <c r="AG28" s="2">
-        <v>608</v>
+        <v>173</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -11677,7 +11677,7 @@
         <v>240</v>
       </c>
       <c r="CW28" s="1">
-        <v>738</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" spans="1:101">
@@ -12337,7 +12337,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="2">
         <v>73</v>
@@ -12589,7 +12589,7 @@
         <v>32</v>
       </c>
       <c r="CV31" s="1">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="CW31" s="1">
         <v>391</v>
@@ -12609,7 +12609,7 @@
         <v>54</v>
       </c>
       <c r="E32" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -12642,7 +12642,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="2">
         <v>319</v>
@@ -12729,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="AS32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT32" s="1">
         <v>0</v>
@@ -12861,7 +12861,7 @@
         <v>7</v>
       </c>
       <c r="CK32" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CL32" s="1">
         <v>25</v>
@@ -12894,10 +12894,10 @@
         <v>43</v>
       </c>
       <c r="CV32" s="1">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="CW32" s="1">
-        <v>556</v>
+        <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:101">
@@ -13234,28 +13234,28 @@
         <v>5</v>
       </c>
       <c r="J34" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K34" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M34" s="2">
+        <v>41</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1451</v>
+      </c>
+      <c r="O34" s="2">
+        <v>22</v>
+      </c>
+      <c r="P34" s="2">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="2">
         <v>47</v>
-      </c>
-      <c r="N34" s="1">
-        <v>1429</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>25</v>
       </c>
       <c r="R34" s="1">
         <v>1</v>
@@ -13330,16 +13330,16 @@
         <v>3</v>
       </c>
       <c r="AP34" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AQ34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT34" s="1">
         <v>0</v>
@@ -13474,16 +13474,16 @@
         <v>8</v>
       </c>
       <c r="CL34" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CM34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP34" s="1">
         <v>0</v>
@@ -13498,16 +13498,16 @@
         <v>0</v>
       </c>
       <c r="CT34" s="1">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="CU34" s="1">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="CV34" s="1">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="CW34" s="1">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:101">
@@ -14595,7 +14595,7 @@
         <v>1</v>
       </c>
       <c r="BE38" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BF38" s="1">
         <v>0</v>
@@ -14643,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="BU38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV38" s="1">
         <v>0</v>
@@ -14727,7 +14727,7 @@
         <v>40</v>
       </c>
       <c r="CW38" s="1">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:101">
@@ -15046,7 +15046,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E40" s="2">
         <v>204</v>
@@ -15334,7 +15334,7 @@
         <v>45</v>
       </c>
       <c r="CV40" s="1">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="CW40" s="1">
         <v>1739</v>
@@ -18817,7 +18817,7 @@
         <v>4</v>
       </c>
       <c r="AO52" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AP52" s="1">
         <v>0</v>
@@ -18961,7 +18961,7 @@
         <v>2</v>
       </c>
       <c r="CK52" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CL52" s="1">
         <v>0</v>
@@ -18997,7 +18997,7 @@
         <v>6</v>
       </c>
       <c r="CW52" s="1">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:101">
@@ -19962,7 +19962,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="2">
         <v>178</v>
@@ -20010,10 +20010,10 @@
         <v>0</v>
       </c>
       <c r="AF56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="2">
         <v>21</v>
-      </c>
-      <c r="AG56" s="2">
-        <v>73</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -20214,10 +20214,10 @@
         <v>17</v>
       </c>
       <c r="CV56" s="1">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="CW56" s="1">
-        <v>346</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:101">
@@ -21538,7 +21538,7 @@
         <v>0</v>
       </c>
       <c r="AG61" s="2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AH61" s="1">
         <v>23</v>
@@ -21559,7 +21559,7 @@
         <v>0</v>
       </c>
       <c r="AN61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO61" s="2">
         <v>3</v>
@@ -21646,7 +21646,7 @@
         <v>1</v>
       </c>
       <c r="BQ61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR61" s="1">
         <v>7</v>
@@ -21703,7 +21703,7 @@
         <v>10</v>
       </c>
       <c r="CJ61" s="2">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="CK61" s="2">
         <v>85</v>
@@ -21739,10 +21739,10 @@
         <v>-41</v>
       </c>
       <c r="CV61" s="1">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="CW61" s="1">
-        <v>833</v>
+        <v>721</v>
       </c>
     </row>
     <row r="62" spans="1:101">
@@ -22381,7 +22381,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="1">
         <v>282</v>
@@ -22396,16 +22396,16 @@
         <v>20</v>
       </c>
       <c r="N64" s="1">
-        <v>4322</v>
+        <v>4387</v>
       </c>
       <c r="O64" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P64" s="2">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="Q64" s="2">
-        <v>233</v>
+        <v>298</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -22444,16 +22444,16 @@
         <v>3</v>
       </c>
       <c r="AD64" s="1">
-        <v>2023</v>
+        <v>2041</v>
       </c>
       <c r="AE64" s="2">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="AF64" s="2">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AG64" s="2">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="AH64" s="1">
         <v>0</v>
@@ -22648,16 +22648,16 @@
         <v>0</v>
       </c>
       <c r="CT64" s="1">
-        <v>8065</v>
+        <v>8148</v>
       </c>
       <c r="CU64" s="1">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="CV64" s="1">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="CW64" s="1">
-        <v>412</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:101">
@@ -22743,7 +22743,7 @@
         <v>4</v>
       </c>
       <c r="AB65" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC65" s="2">
         <v>8</v>
@@ -22959,7 +22959,7 @@
         <v>56</v>
       </c>
       <c r="CV65" s="1">
-        <v>1777</v>
+        <v>1773</v>
       </c>
       <c r="CW65" s="1">
         <v>3500</v>
@@ -24220,7 +24220,7 @@
         <v>5</v>
       </c>
       <c r="L70" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M70" s="2">
         <v>33</v>
@@ -24232,7 +24232,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="2">
         <v>30</v>
@@ -24484,7 +24484,7 @@
         <v>8</v>
       </c>
       <c r="CV70" s="1">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="CW70" s="1">
         <v>83</v>
@@ -24504,7 +24504,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="1">
         <v>67</v>
@@ -24516,7 +24516,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="1">
         <v>0</v>
@@ -24792,7 +24792,7 @@
         <v>0</v>
       </c>
       <c r="CW71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:101">
@@ -25419,7 +25419,7 @@
         <v>143</v>
       </c>
       <c r="E74" s="2">
-        <v>375</v>
+        <v>232</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -25434,16 +25434,16 @@
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>10153</v>
+        <v>10199</v>
       </c>
       <c r="K74" s="2">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="L74" s="2">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="M74" s="2">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="N74" s="1">
         <v>79173</v>
@@ -25527,7 +25527,7 @@
         <v>125</v>
       </c>
       <c r="AO74" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>32</v>
       </c>
       <c r="CJ74" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="CK74" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25698,16 +25698,16 @@
         <v>0</v>
       </c>
       <c r="CT74" s="1">
-        <v>171834</v>
+        <v>171880</v>
       </c>
       <c r="CU74" s="1">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="CV74" s="1">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="CW74" s="1">
-        <v>3936</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26029,7 +26029,7 @@
         <v>56</v>
       </c>
       <c r="E76" s="2">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -26053,7 +26053,7 @@
         <v>178</v>
       </c>
       <c r="M76" s="2">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="N76" s="1">
         <v>117545</v>
@@ -26113,7 +26113,7 @@
         <v>0</v>
       </c>
       <c r="AG76" s="2">
-        <v>614</v>
+        <v>76</v>
       </c>
       <c r="AH76" s="1">
         <v>0</v>
@@ -26137,7 +26137,7 @@
         <v>1</v>
       </c>
       <c r="AO76" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP76" s="1">
         <v>50</v>
@@ -26281,7 +26281,7 @@
         <v>34</v>
       </c>
       <c r="CK76" s="2">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="CL76" s="1">
         <v>7</v>
@@ -26317,7 +26317,7 @@
         <v>1194</v>
       </c>
       <c r="CW76" s="1">
-        <v>3738</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="77" spans="1:101">
@@ -26334,7 +26334,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="2">
-        <v>-4426</v>
+        <v>-1298</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26358,7 +26358,7 @@
         <v>181</v>
       </c>
       <c r="M77" s="2">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="N77" s="1">
         <v>362845</v>
@@ -26577,16 +26577,16 @@
         <v>0</v>
       </c>
       <c r="CH77" s="1">
-        <v>7392</v>
+        <v>7398</v>
       </c>
       <c r="CI77" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="CJ77" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="CK77" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="CL77" s="1">
         <v>104</v>
@@ -26613,16 +26613,16 @@
         <v>1</v>
       </c>
       <c r="CT77" s="1">
-        <v>391004</v>
+        <v>391010</v>
       </c>
       <c r="CU77" s="1">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="CV77" s="1">
-        <v>10153</v>
+        <v>10159</v>
       </c>
       <c r="CW77" s="1">
-        <v>15723</v>
+        <v>18783</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26744,7 +26744,7 @@
         <v>12</v>
       </c>
       <c r="AN78" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AO78" s="2">
         <v>33</v>
@@ -26924,7 +26924,7 @@
         <v>27</v>
       </c>
       <c r="CV78" s="1">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CW78" s="1">
         <v>125</v>
@@ -26935,16 +26935,16 @@
         <v>178</v>
       </c>
       <c r="B79" s="1">
-        <v>4285</v>
+        <v>4299</v>
       </c>
       <c r="C79" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D79" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E79" s="2">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -26965,10 +26965,10 @@
         <v>49</v>
       </c>
       <c r="L79" s="2">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="M79" s="2">
-        <v>277</v>
+        <v>180</v>
       </c>
       <c r="N79" s="1">
         <v>69222</v>
@@ -27028,7 +27028,7 @@
         <v>1</v>
       </c>
       <c r="AG79" s="2">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="AH79" s="1">
         <v>0</v>
@@ -27052,7 +27052,7 @@
         <v>2</v>
       </c>
       <c r="AO79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP79" s="1">
         <v>36</v>
@@ -27136,7 +27136,7 @@
         <v>15</v>
       </c>
       <c r="BQ79" s="2">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="BR79" s="1">
         <v>0</v>
@@ -27196,7 +27196,7 @@
         <v>59</v>
       </c>
       <c r="CK79" s="2">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="CL79" s="1">
         <v>2</v>
@@ -27223,16 +27223,16 @@
         <v>0</v>
       </c>
       <c r="CT79" s="1">
-        <v>90690</v>
+        <v>90704</v>
       </c>
       <c r="CU79" s="1">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="CV79" s="1">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="CW79" s="1">
-        <v>1885</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="80" spans="1:101">
@@ -27354,10 +27354,10 @@
         <v>19</v>
       </c>
       <c r="AN80" s="2">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="AO80" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="AP80" s="1">
         <v>0</v>
@@ -27489,7 +27489,7 @@
         <v>0</v>
       </c>
       <c r="CG80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH80" s="1">
         <v>824</v>
@@ -27498,10 +27498,10 @@
         <v>15</v>
       </c>
       <c r="CJ80" s="2">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="CK80" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="CL80" s="1">
         <v>0</v>
@@ -27534,10 +27534,10 @@
         <v>43</v>
       </c>
       <c r="CV80" s="1">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="CW80" s="1">
-        <v>267</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:101">
@@ -27904,7 +27904,7 @@
         <v>1</v>
       </c>
       <c r="T82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U82" s="2">
         <v>2</v>
@@ -28144,7 +28144,7 @@
         <v>4</v>
       </c>
       <c r="CV82" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CW82" s="1">
         <v>21</v>
@@ -28245,7 +28245,7 @@
         <v>1</v>
       </c>
       <c r="AF83" s="2">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="AG83" s="2">
         <v>177</v>
@@ -28449,7 +28449,7 @@
         <v>106</v>
       </c>
       <c r="CV83" s="1">
-        <v>808</v>
+        <v>632</v>
       </c>
       <c r="CW83" s="1">
         <v>1958</v>
@@ -28774,7 +28774,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1">
         <v>73</v>
@@ -29062,7 +29062,7 @@
         <v>28</v>
       </c>
       <c r="CW85" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:101">
@@ -29689,7 +29689,7 @@
         <v>4</v>
       </c>
       <c r="E88" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1">
         <v>19</v>
@@ -29713,7 +29713,7 @@
         <v>27</v>
       </c>
       <c r="M88" s="2">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="N88" s="1">
         <v>1035</v>
@@ -29725,7 +29725,7 @@
         <v>10</v>
       </c>
       <c r="Q88" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R88" s="1">
         <v>0</v>
@@ -29773,7 +29773,7 @@
         <v>74</v>
       </c>
       <c r="AG88" s="2">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="AH88" s="1">
         <v>0</v>
@@ -29809,7 +29809,7 @@
         <v>3</v>
       </c>
       <c r="AS88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT88" s="1">
         <v>0</v>
@@ -29941,7 +29941,7 @@
         <v>14</v>
       </c>
       <c r="CK88" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="CL88" s="1">
         <v>22</v>
@@ -29977,7 +29977,7 @@
         <v>133</v>
       </c>
       <c r="CW88" s="1">
-        <v>427</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:101">
@@ -29994,7 +29994,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" s="1">
         <v>39</v>
@@ -30018,7 +30018,7 @@
         <v>8</v>
       </c>
       <c r="M89" s="2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N89" s="1">
         <v>48</v>
@@ -30282,7 +30282,7 @@
         <v>75</v>
       </c>
       <c r="CW89" s="1">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" spans="1:101">
@@ -30924,16 +30924,16 @@
         <v>1</v>
       </c>
       <c r="J92" s="1">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K92" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N92" s="1">
         <v>1776</v>
@@ -31017,7 +31017,7 @@
         <v>4</v>
       </c>
       <c r="AO92" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP92" s="1">
         <v>33</v>
@@ -31161,7 +31161,7 @@
         <v>8</v>
       </c>
       <c r="CK92" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CL92" s="1">
         <v>25</v>
@@ -31188,16 +31188,16 @@
         <v>0</v>
       </c>
       <c r="CT92" s="1">
-        <v>3796</v>
+        <v>3798</v>
       </c>
       <c r="CU92" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CV92" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CW92" s="1">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93" spans="1:101">
@@ -31313,16 +31313,16 @@
         <v>0</v>
       </c>
       <c r="AL93" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM93" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN93" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO93" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP93" s="1">
         <v>37</v>
@@ -31493,16 +31493,16 @@
         <v>0</v>
       </c>
       <c r="CT93" s="1">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="CU93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV93" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CW93" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:101">
@@ -33457,7 +33457,7 @@
         <v>5</v>
       </c>
       <c r="AO100" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AP100" s="1">
         <v>1</v>
@@ -33601,7 +33601,7 @@
         <v>4</v>
       </c>
       <c r="CK100" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CL100" s="1">
         <v>1</v>
@@ -33637,7 +33637,7 @@
         <v>14</v>
       </c>
       <c r="CW100" s="1">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33974,16 +33974,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="1">
-        <v>5122</v>
+        <v>5162</v>
       </c>
       <c r="K102" s="2">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="L102" s="2">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="M102" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N102" s="1">
         <v>14647</v>
@@ -34034,16 +34034,16 @@
         <v>8</v>
       </c>
       <c r="AD102" s="1">
-        <v>2300</v>
+        <v>2329</v>
       </c>
       <c r="AE102" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF102" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG102" s="2">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="AH102" s="1">
         <v>0</v>
@@ -34076,7 +34076,7 @@
         <v>0</v>
       </c>
       <c r="AR102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS102" s="2">
         <v>3</v>
@@ -34208,7 +34208,7 @@
         <v>0</v>
       </c>
       <c r="CJ102" s="2">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="CK102" s="2">
         <v>73</v>
@@ -34238,16 +34238,16 @@
         <v>0</v>
       </c>
       <c r="CT102" s="1">
-        <v>43148</v>
+        <v>43217</v>
       </c>
       <c r="CU102" s="1">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="CV102" s="1">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="CW102" s="1">
-        <v>1621</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="103" spans="1:101">
@@ -35203,7 +35203,7 @@
         <v>347</v>
       </c>
       <c r="M106" s="2">
-        <v>873</v>
+        <v>728</v>
       </c>
       <c r="N106" s="1">
         <v>22915</v>
@@ -35263,7 +35263,7 @@
         <v>110</v>
       </c>
       <c r="AG106" s="2">
-        <v>296</v>
+        <v>153</v>
       </c>
       <c r="AH106" s="1">
         <v>1</v>
@@ -35467,7 +35467,7 @@
         <v>1015</v>
       </c>
       <c r="CW106" s="1">
-        <v>2301</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="107" spans="1:101">
@@ -36483,7 +36483,7 @@
         <v>50</v>
       </c>
       <c r="AG110" s="2">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="AH110" s="1">
         <v>0</v>
@@ -36522,16 +36522,16 @@
         <v>0</v>
       </c>
       <c r="AT110" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU110" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV110" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW110" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX110" s="1">
         <v>0</v>
@@ -36651,7 +36651,7 @@
         <v>64</v>
       </c>
       <c r="CK110" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="CL110" s="1">
         <v>0</v>
@@ -36678,16 +36678,16 @@
         <v>0</v>
       </c>
       <c r="CT110" s="1">
-        <v>13489</v>
+        <v>13491</v>
       </c>
       <c r="CU110" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="CV110" s="1">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="CW110" s="1">
-        <v>1032</v>
+        <v>765</v>
       </c>
     </row>
     <row r="111" spans="1:101">
@@ -36803,16 +36803,16 @@
         <v>0</v>
       </c>
       <c r="AL111" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AM111" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN111" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO111" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP111" s="1">
         <v>46</v>
@@ -36947,16 +36947,16 @@
         <v>0</v>
       </c>
       <c r="CH111" s="1">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="CI111" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CJ111" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CK111" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="CL111" s="1">
         <v>27</v>
@@ -36983,16 +36983,16 @@
         <v>0</v>
       </c>
       <c r="CT111" s="1">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="CU111" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CV111" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="CW111" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:101">
@@ -37009,7 +37009,7 @@
         <v>18</v>
       </c>
       <c r="E112" s="2">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -37129,7 +37129,7 @@
         <v>3</v>
       </c>
       <c r="AS112" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT112" s="1">
         <v>0</v>
@@ -37297,7 +37297,7 @@
         <v>267</v>
       </c>
       <c r="CW112" s="1">
-        <v>649</v>
+        <v>630</v>
       </c>
     </row>
     <row r="113" spans="1:101">
@@ -37398,7 +37398,7 @@
         <v>1301</v>
       </c>
       <c r="AG113" s="2">
-        <v>10113</v>
+        <v>1301</v>
       </c>
       <c r="AH113" s="1">
         <v>1</v>
@@ -37506,7 +37506,7 @@
         <v>0</v>
       </c>
       <c r="BQ113" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BR113" s="1">
         <v>16</v>
@@ -37566,7 +37566,7 @@
         <v>66</v>
       </c>
       <c r="CK113" s="2">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37602,7 +37602,7 @@
         <v>1710</v>
       </c>
       <c r="CW113" s="1">
-        <v>11053</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38220,16 +38220,16 @@
         <v>215</v>
       </c>
       <c r="B116" s="1">
-        <v>4427</v>
+        <v>4440</v>
       </c>
       <c r="C116" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D116" s="2">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E116" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -38256,16 +38256,16 @@
         <v>207</v>
       </c>
       <c r="N116" s="1">
-        <v>4537</v>
+        <v>4536</v>
       </c>
       <c r="O116" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P116" s="2">
-        <v>106</v>
+        <v>-1</v>
       </c>
       <c r="Q116" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R116" s="1">
         <v>0</v>
@@ -38313,7 +38313,7 @@
         <v>40</v>
       </c>
       <c r="AG116" s="2">
-        <v>401</v>
+        <v>40</v>
       </c>
       <c r="AH116" s="1">
         <v>1</v>
@@ -38478,7 +38478,7 @@
         <v>29</v>
       </c>
       <c r="CJ116" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CK116" s="2">
         <v>75</v>
@@ -38508,16 +38508,16 @@
         <v>1</v>
       </c>
       <c r="CT116" s="1">
-        <v>21992</v>
+        <v>22004</v>
       </c>
       <c r="CU116" s="1">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="CV116" s="1">
-        <v>541</v>
+        <v>448</v>
       </c>
       <c r="CW116" s="1">
-        <v>1241</v>
+        <v>869</v>
       </c>
     </row>
     <row r="117" spans="1:101">
@@ -38534,7 +38534,7 @@
         <v>372</v>
       </c>
       <c r="E117" s="2">
-        <v>1123</v>
+        <v>926</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -38822,7 +38822,7 @@
         <v>388</v>
       </c>
       <c r="CW117" s="1">
-        <v>1187</v>
+        <v>990</v>
       </c>
     </row>
     <row r="118" spans="1:101">
@@ -39345,7 +39345,7 @@
         <v>0</v>
       </c>
       <c r="BT119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU119" s="2">
         <v>2</v>
@@ -39429,7 +39429,7 @@
         <v>1</v>
       </c>
       <c r="CV119" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW119" s="1">
         <v>26</v>
@@ -40391,16 +40391,16 @@
         <v>0</v>
       </c>
       <c r="N123" s="1">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="O123" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P123" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R123" s="1">
         <v>0</v>
@@ -40643,16 +40643,16 @@
         <v>0</v>
       </c>
       <c r="CT123" s="1">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="CU123" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CV123" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CW123" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:101">
@@ -42230,7 +42230,7 @@
         <v>78</v>
       </c>
       <c r="Q129" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="R129" s="1">
         <v>0</v>
@@ -42254,7 +42254,7 @@
         <v>0</v>
       </c>
       <c r="Y129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z129" s="1">
         <v>0</v>
@@ -42302,7 +42302,7 @@
         <v>4</v>
       </c>
       <c r="AO129" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AP129" s="1">
         <v>35</v>
@@ -42446,7 +42446,7 @@
         <v>20</v>
       </c>
       <c r="CK129" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="CL129" s="1">
         <v>37</v>
@@ -42482,7 +42482,7 @@
         <v>108</v>
       </c>
       <c r="CW129" s="1">
-        <v>297</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -43414,7 +43414,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F133" s="1">
         <v>73</v>
@@ -43702,7 +43702,7 @@
         <v>2</v>
       </c>
       <c r="CW133" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:101">
@@ -43824,7 +43824,7 @@
         <v>2</v>
       </c>
       <c r="AN134" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO134" s="2">
         <v>15</v>
@@ -43968,7 +43968,7 @@
         <v>9</v>
       </c>
       <c r="CJ134" s="2">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="CK134" s="2">
         <v>84</v>
@@ -44004,7 +44004,7 @@
         <v>12</v>
       </c>
       <c r="CV134" s="1">
-        <v>1808</v>
+        <v>1789</v>
       </c>
       <c r="CW134" s="1">
         <v>5805</v>
@@ -44105,7 +44105,7 @@
         <v>51</v>
       </c>
       <c r="AF135" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG135" s="2">
         <v>802</v>
@@ -44309,7 +44309,7 @@
         <v>171</v>
       </c>
       <c r="CV135" s="1">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="CW135" s="1">
         <v>2537</v>
@@ -44413,7 +44413,7 @@
         <v>-6</v>
       </c>
       <c r="AG136" s="2">
-        <v>5977</v>
+        <v>5036</v>
       </c>
       <c r="AH136" s="1">
         <v>0</v>
@@ -44581,7 +44581,7 @@
         <v>14</v>
       </c>
       <c r="CK136" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="CL136" s="1">
         <v>13</v>
@@ -44617,7 +44617,7 @@
         <v>32</v>
       </c>
       <c r="CW136" s="1">
-        <v>6078</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -44963,7 +44963,7 @@
         <v>44</v>
       </c>
       <c r="M138" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="N138" s="1">
         <v>2200</v>
@@ -45227,7 +45227,7 @@
         <v>75</v>
       </c>
       <c r="CW138" s="1">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:101">
@@ -45561,7 +45561,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J140" s="1">
         <v>55</v>
@@ -45669,7 +45669,7 @@
         <v>1</v>
       </c>
       <c r="AS140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT140" s="1">
         <v>0</v>
@@ -45801,7 +45801,7 @@
         <v>1</v>
       </c>
       <c r="CK140" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL140" s="1">
         <v>11</v>
@@ -45837,7 +45837,7 @@
         <v>10</v>
       </c>
       <c r="CW140" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:101">
@@ -46716,7 +46716,7 @@
         <v>2</v>
       </c>
       <c r="CK143" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CL143" s="1">
         <v>74</v>
@@ -46728,7 +46728,7 @@
         <v>2</v>
       </c>
       <c r="CO143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP143" s="1">
         <v>0</v>
@@ -47107,7 +47107,7 @@
         <v>0</v>
       </c>
       <c r="P145" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="2">
         <v>34</v>
@@ -47359,7 +47359,7 @@
         <v>5</v>
       </c>
       <c r="CV145" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="CW145" s="1">
         <v>117</v>
@@ -47696,7 +47696,7 @@
         <v>3</v>
       </c>
       <c r="I147" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J147" s="1">
         <v>20</v>
@@ -47972,7 +47972,7 @@
         <v>14</v>
       </c>
       <c r="CW147" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:101">
@@ -48013,7 +48013,7 @@
         <v>17</v>
       </c>
       <c r="M148" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N148" s="1">
         <v>3255</v>
@@ -48097,7 +48097,7 @@
         <v>2</v>
       </c>
       <c r="AO148" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AP148" s="1">
         <v>30</v>
@@ -48241,7 +48241,7 @@
         <v>22</v>
       </c>
       <c r="CK148" s="2">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="CL148" s="1">
         <v>16</v>
@@ -48277,7 +48277,7 @@
         <v>100</v>
       </c>
       <c r="CW148" s="1">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:101">
@@ -48716,7 +48716,7 @@
         <v>1</v>
       </c>
       <c r="AR150" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS150" s="2">
         <v>5</v>
@@ -48860,7 +48860,7 @@
         <v>1</v>
       </c>
       <c r="CN150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO150" s="2">
         <v>3</v>
@@ -48884,7 +48884,7 @@
         <v>2</v>
       </c>
       <c r="CV150" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CW150" s="1">
         <v>13</v>
@@ -49009,10 +49009,10 @@
         <v>0</v>
       </c>
       <c r="AN151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO151" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP151" s="1">
         <v>64</v>
@@ -49024,7 +49024,7 @@
         <v>2</v>
       </c>
       <c r="AS151" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT151" s="1">
         <v>0</v>
@@ -49105,7 +49105,7 @@
         <v>0</v>
       </c>
       <c r="BT151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU151" s="2">
         <v>1</v>
@@ -49153,10 +49153,10 @@
         <v>2</v>
       </c>
       <c r="CJ151" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CK151" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CL151" s="1">
         <v>29</v>
@@ -49189,10 +49189,10 @@
         <v>4</v>
       </c>
       <c r="CV151" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CW151" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="152" spans="1:101">
@@ -49293,7 +49293,7 @@
         <v>10</v>
       </c>
       <c r="AG152" s="2">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="AH152" s="1">
         <v>0</v>
@@ -49326,7 +49326,7 @@
         <v>1</v>
       </c>
       <c r="AR152" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS152" s="2">
         <v>4</v>
@@ -49458,7 +49458,7 @@
         <v>2</v>
       </c>
       <c r="CJ152" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="CK152" s="2">
         <v>32</v>
@@ -49494,10 +49494,10 @@
         <v>4</v>
       </c>
       <c r="CV152" s="1">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="CW152" s="1">
-        <v>257</v>
+        <v>141</v>
       </c>
     </row>
     <row r="153" spans="1:101">
@@ -50160,7 +50160,7 @@
         <v>18</v>
       </c>
       <c r="Q155" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R155" s="1">
         <v>1</v>
@@ -50412,7 +50412,7 @@
         <v>44</v>
       </c>
       <c r="CW155" s="1">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156" spans="1:101">
@@ -50450,7 +50450,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M156" s="2">
         <v>85</v>
@@ -50513,7 +50513,7 @@
         <v>72</v>
       </c>
       <c r="AG156" s="2">
-        <v>332</v>
+        <v>71</v>
       </c>
       <c r="AH156" s="1">
         <v>0</v>
@@ -50528,16 +50528,16 @@
         <v>0</v>
       </c>
       <c r="AL156" s="1">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN156" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO156" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP156" s="1">
         <v>55</v>
@@ -50546,7 +50546,7 @@
         <v>1</v>
       </c>
       <c r="AR156" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS156" s="2">
         <v>2</v>
@@ -50672,16 +50672,16 @@
         <v>0</v>
       </c>
       <c r="CH156" s="1">
-        <v>2789</v>
+        <v>2799</v>
       </c>
       <c r="CI156" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="CJ156" s="2">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="CK156" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="CL156" s="1">
         <v>13</v>
@@ -50708,16 +50708,16 @@
         <v>0</v>
       </c>
       <c r="CT156" s="1">
-        <v>71544</v>
+        <v>71555</v>
       </c>
       <c r="CU156" s="1">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="CV156" s="1">
-        <v>1073</v>
+        <v>1044</v>
       </c>
       <c r="CW156" s="1">
-        <v>2484</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="157" spans="1:101">
@@ -50758,7 +50758,7 @@
         <v>151</v>
       </c>
       <c r="M157" s="2">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="N157" s="1">
         <v>11983</v>
@@ -50842,7 +50842,7 @@
         <v>9</v>
       </c>
       <c r="AO157" s="2">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="AP157" s="1">
         <v>49</v>
@@ -50986,7 +50986,7 @@
         <v>100</v>
       </c>
       <c r="CK157" s="2">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="CL157" s="1">
         <v>9</v>
@@ -51022,7 +51022,7 @@
         <v>5231</v>
       </c>
       <c r="CW157" s="1">
-        <v>5637</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="158" spans="1:101">
@@ -51036,7 +51036,7 @@
         <v>54</v>
       </c>
       <c r="D158" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="E158" s="2">
         <v>325</v>
@@ -51063,7 +51063,7 @@
         <v>174</v>
       </c>
       <c r="M158" s="2">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="N158" s="1">
         <v>3028</v>
@@ -51075,7 +51075,7 @@
         <v>59</v>
       </c>
       <c r="Q158" s="2">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="R158" s="1">
         <v>0</v>
@@ -51147,7 +51147,7 @@
         <v>22</v>
       </c>
       <c r="AO158" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="AP158" s="1">
         <v>3</v>
@@ -51291,7 +51291,7 @@
         <v>380</v>
       </c>
       <c r="CK158" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="CL158" s="1">
         <v>0</v>
@@ -51324,10 +51324,10 @@
         <v>246</v>
       </c>
       <c r="CV158" s="1">
-        <v>836</v>
+        <v>776</v>
       </c>
       <c r="CW158" s="1">
-        <v>1637</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="159" spans="1:101">
@@ -51978,7 +51978,7 @@
         <v>74</v>
       </c>
       <c r="M161" s="2">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="N161" s="1">
         <v>10033</v>
@@ -52059,7 +52059,7 @@
         <v>0</v>
       </c>
       <c r="AN161" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO161" s="2">
         <v>12</v>
@@ -52203,7 +52203,7 @@
         <v>0</v>
       </c>
       <c r="CJ161" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CK161" s="2">
         <v>36</v>
@@ -52239,10 +52239,10 @@
         <v>26</v>
       </c>
       <c r="CV161" s="1">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="CW161" s="1">
-        <v>1099</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="162" spans="1:101">
@@ -52597,7 +52597,7 @@
         <v>0</v>
       </c>
       <c r="P163" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q163" s="2">
         <v>10</v>
@@ -52849,7 +52849,7 @@
         <v>4</v>
       </c>
       <c r="CV163" s="1">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="CW163" s="1">
         <v>34</v>
@@ -52896,16 +52896,16 @@
         <v>26</v>
       </c>
       <c r="N164" s="1">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O164" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P164" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q164" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="R164" s="1">
         <v>1</v>
@@ -53148,16 +53148,16 @@
         <v>0</v>
       </c>
       <c r="CT164" s="1">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="CU164" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV164" s="1">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="CW164" s="1">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="165" spans="1:101">
@@ -53470,16 +53470,16 @@
         <v>265</v>
       </c>
       <c r="B166" s="1">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C166" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D166" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E166" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F166" s="1">
         <v>8</v>
@@ -53596,7 +53596,7 @@
         <v>0</v>
       </c>
       <c r="AR166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS166" s="2">
         <v>4</v>
@@ -53728,7 +53728,7 @@
         <v>0</v>
       </c>
       <c r="CJ166" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CK166" s="2">
         <v>8</v>
@@ -53758,16 +53758,16 @@
         <v>0</v>
       </c>
       <c r="CT166" s="1">
-        <v>5290</v>
+        <v>5292</v>
       </c>
       <c r="CU166" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CV166" s="1">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="CW166" s="1">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="167" spans="1:101">
@@ -54173,7 +54173,7 @@
         <v>49</v>
       </c>
       <c r="AG168" s="2">
-        <v>336</v>
+        <v>49</v>
       </c>
       <c r="AH168" s="1">
         <v>0</v>
@@ -54200,16 +54200,16 @@
         <v>1</v>
       </c>
       <c r="AP168" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR168" s="2">
         <v>2</v>
       </c>
       <c r="AS168" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT168" s="1">
         <v>0</v>
@@ -54332,16 +54332,16 @@
         <v>0</v>
       </c>
       <c r="CH168" s="1">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="CI168" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CJ168" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CK168" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CL168" s="1">
         <v>4</v>
@@ -54368,16 +54368,16 @@
         <v>0</v>
       </c>
       <c r="CT168" s="1">
-        <v>5976</v>
+        <v>5981</v>
       </c>
       <c r="CU168" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CV168" s="1">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="CW168" s="1">
-        <v>517</v>
+        <v>235</v>
       </c>
     </row>
     <row r="169" spans="1:101">
@@ -54783,7 +54783,7 @@
         <v>127</v>
       </c>
       <c r="AG170" s="2">
-        <v>414</v>
+        <v>127</v>
       </c>
       <c r="AH170" s="1">
         <v>10</v>
@@ -54987,7 +54987,7 @@
         <v>499</v>
       </c>
       <c r="CW170" s="1">
-        <v>1241</v>
+        <v>954</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55253,7 +55253,7 @@
         <v>6</v>
       </c>
       <c r="CJ171" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CK171" s="2">
         <v>14</v>
@@ -55289,7 +55289,7 @@
         <v>16</v>
       </c>
       <c r="CV171" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="CW171" s="1">
         <v>106</v>
@@ -55931,7 +55931,7 @@
         <v>2</v>
       </c>
       <c r="I174" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J174" s="1">
         <v>0</v>
@@ -56207,7 +56207,7 @@
         <v>23</v>
       </c>
       <c r="CW174" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="175" spans="1:101">
@@ -57136,7 +57136,7 @@
         <v>0</v>
       </c>
       <c r="D178" s="2">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E178" s="2">
         <v>124</v>
@@ -57160,7 +57160,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M178" s="2">
         <v>63</v>
@@ -57424,7 +57424,7 @@
         <v>31</v>
       </c>
       <c r="CV178" s="1">
-        <v>2169</v>
+        <v>2124</v>
       </c>
       <c r="CW178" s="1">
         <v>4515</v>
@@ -57782,7 +57782,7 @@
         <v>0</v>
       </c>
       <c r="P180" s="2">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="Q180" s="2">
         <v>2069</v>
@@ -57938,22 +57938,22 @@
         <v>0</v>
       </c>
       <c r="BP180" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BQ180" s="2">
         <v>44</v>
       </c>
       <c r="BR180" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BS180" s="2">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="BT180" s="2">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="BU180" s="2">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="BV180" s="1">
         <v>0</v>
@@ -58028,16 +58028,16 @@
         <v>0</v>
       </c>
       <c r="CT180" s="1">
-        <v>51316</v>
+        <v>51308</v>
       </c>
       <c r="CU180" s="1">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="CV180" s="1">
-        <v>1272</v>
+        <v>271</v>
       </c>
       <c r="CW180" s="1">
-        <v>2629</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="181" spans="1:101">
@@ -58856,7 +58856,7 @@
         <v>1</v>
       </c>
       <c r="BQ183" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BR183" s="1">
         <v>14</v>
@@ -58952,7 +58952,7 @@
         <v>1</v>
       </c>
       <c r="CW183" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:101">
@@ -59286,7 +59286,7 @@
         <v>3</v>
       </c>
       <c r="I185" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J185" s="1">
         <v>0</v>
@@ -59562,7 +59562,7 @@
         <v>10</v>
       </c>
       <c r="CW185" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:101">
@@ -59896,7 +59896,7 @@
         <v>3</v>
       </c>
       <c r="I187" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J187" s="1">
         <v>0</v>
@@ -60172,7 +60172,7 @@
         <v>3</v>
       </c>
       <c r="CW187" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:101">
@@ -62408,7 +62408,7 @@
         <v>0</v>
       </c>
       <c r="AG195" s="2">
-        <v>5225</v>
+        <v>3325</v>
       </c>
       <c r="AH195" s="1">
         <v>0</v>
@@ -62576,7 +62576,7 @@
         <v>16</v>
       </c>
       <c r="CK195" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="CL195" s="1">
         <v>9</v>
@@ -62612,7 +62612,7 @@
         <v>45</v>
       </c>
       <c r="CW195" s="1">
-        <v>5334</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -62737,7 +62737,7 @@
         <v>6</v>
       </c>
       <c r="AO196" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP196" s="1">
         <v>15</v>
@@ -62881,7 +62881,7 @@
         <v>14</v>
       </c>
       <c r="CK196" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="CL196" s="1">
         <v>3</v>
@@ -62917,7 +62917,7 @@
         <v>39</v>
       </c>
       <c r="CW196" s="1">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="197" spans="1:101">
@@ -64178,7 +64178,7 @@
         <v>105</v>
       </c>
       <c r="M201" s="2">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="N201" s="1">
         <v>23255</v>
@@ -64238,7 +64238,7 @@
         <v>1606</v>
       </c>
       <c r="AG201" s="2">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64274,7 +64274,7 @@
         <v>0</v>
       </c>
       <c r="AS201" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT201" s="1">
         <v>0</v>
@@ -64337,16 +64337,16 @@
         <v>0</v>
       </c>
       <c r="BN201" s="1">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BO201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ201" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR201" s="1">
         <v>5</v>
@@ -64403,7 +64403,7 @@
         <v>26</v>
       </c>
       <c r="CJ201" s="2">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="CK201" s="2">
         <v>122</v>
@@ -64433,16 +64433,16 @@
         <v>0</v>
       </c>
       <c r="CT201" s="1">
-        <v>88299</v>
+        <v>88300</v>
       </c>
       <c r="CU201" s="1">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="CV201" s="1">
-        <v>2157</v>
+        <v>2141</v>
       </c>
       <c r="CW201" s="1">
-        <v>2918</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -64567,7 +64567,7 @@
         <v>19</v>
       </c>
       <c r="AO202" s="2">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP202" s="1">
         <v>0</v>
@@ -64711,7 +64711,7 @@
         <v>10</v>
       </c>
       <c r="CK202" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="CL202" s="1">
         <v>0</v>
@@ -64747,7 +64747,7 @@
         <v>32</v>
       </c>
       <c r="CW202" s="1">
-        <v>140</v>
+        <v>88</v>
       </c>
     </row>
     <row r="203" spans="1:101">
@@ -65984,7 +65984,7 @@
         <v>39</v>
       </c>
       <c r="E207" s="2">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F207" s="1">
         <v>1</v>
@@ -66008,7 +66008,7 @@
         <v>27</v>
       </c>
       <c r="M207" s="2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="N207" s="1">
         <v>5091</v>
@@ -66017,7 +66017,7 @@
         <v>0</v>
       </c>
       <c r="P207" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q207" s="2">
         <v>106</v>
@@ -66065,7 +66065,7 @@
         <v>0</v>
       </c>
       <c r="AF207" s="2">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="AG207" s="2">
         <v>195</v>
@@ -66101,10 +66101,10 @@
         <v>1</v>
       </c>
       <c r="AR207" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS207" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT207" s="1">
         <v>0</v>
@@ -66185,7 +66185,7 @@
         <v>0</v>
       </c>
       <c r="BT207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU207" s="2">
         <v>1</v>
@@ -66233,10 +66233,10 @@
         <v>8</v>
       </c>
       <c r="CJ207" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="CK207" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="CL207" s="1">
         <v>14</v>
@@ -66269,10 +66269,10 @@
         <v>35</v>
       </c>
       <c r="CV207" s="1">
-        <v>315</v>
+        <v>102</v>
       </c>
       <c r="CW207" s="1">
-        <v>548</v>
+        <v>515</v>
       </c>
     </row>
     <row r="208" spans="1:101">
@@ -67225,22 +67225,22 @@
         <v>15</v>
       </c>
       <c r="L211" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M211" s="2">
         <v>75</v>
       </c>
       <c r="N211" s="1">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="O211" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P211" s="2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="Q211" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="R211" s="1">
         <v>0</v>
@@ -67483,16 +67483,16 @@
         <v>0</v>
       </c>
       <c r="CT211" s="1">
-        <v>6305</v>
+        <v>6320</v>
       </c>
       <c r="CU211" s="1">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="CV211" s="1">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="CW211" s="1">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -68557,7 +68557,7 @@
         <v>538</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>716</v>
@@ -69537,7 +69537,7 @@
         <v>576</v>
       </c>
       <c r="D56">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E56" t="s">
         <v>716</v>
@@ -70626,7 +70626,7 @@
         <v>627</v>
       </c>
       <c r="D110">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E110" t="s">
         <v>716</v>
@@ -71189,7 +71189,7 @@
         <v>651</v>
       </c>
       <c r="D138">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E138" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -3782,7 +3782,7 @@
         <v>4286</v>
       </c>
       <c r="K3" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
         <v>66</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="2">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2">
         <v>856</v>
@@ -4016,7 +4016,7 @@
         <v>41</v>
       </c>
       <c r="CK3" s="2">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="CL3" s="1">
         <v>3</v>
@@ -4046,13 +4046,13 @@
         <v>46759</v>
       </c>
       <c r="CU3" s="1">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="CV3" s="1">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="CW3" s="1">
-        <v>1578</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="4" spans="1:101">
@@ -4177,7 +4177,7 @@
         <v>6</v>
       </c>
       <c r="AO4" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP4" s="1">
         <v>0</v>
@@ -4321,7 +4321,7 @@
         <v>67</v>
       </c>
       <c r="CK4" s="2">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="CL4" s="1">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>583</v>
       </c>
       <c r="CW4" s="1">
-        <v>976</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:101">
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="CJ5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CK5" s="2">
         <v>13</v>
@@ -4659,7 +4659,7 @@
         <v>37</v>
       </c>
       <c r="CV5" s="1">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="CW5" s="1">
         <v>423</v>
@@ -5711,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="AR9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS9" s="2">
         <v>5</v>
@@ -5843,7 +5843,7 @@
         <v>4</v>
       </c>
       <c r="CJ9" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CK9" s="2">
         <v>9</v>
@@ -5879,7 +5879,7 @@
         <v>17</v>
       </c>
       <c r="CV9" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CW9" s="1">
         <v>102</v>
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>213</v>
       </c>
       <c r="CW12" s="1">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:101">
@@ -7457,7 +7457,7 @@
         <v>49</v>
       </c>
       <c r="P15" s="2">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="Q15" s="2">
         <v>204</v>
@@ -7709,7 +7709,7 @@
         <v>55</v>
       </c>
       <c r="CV15" s="1">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="CW15" s="1">
         <v>235</v>
@@ -7759,7 +7759,7 @@
         <v>345</v>
       </c>
       <c r="O16" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2">
         <v>7</v>
@@ -7843,7 +7843,7 @@
         <v>68</v>
       </c>
       <c r="AQ16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="2">
         <v>3</v>
@@ -7987,7 +7987,7 @@
         <v>31</v>
       </c>
       <c r="CM16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN16" s="2">
         <v>2</v>
@@ -8011,7 +8011,7 @@
         <v>982</v>
       </c>
       <c r="CU16" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CV16" s="1">
         <v>23</v>
@@ -8046,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>575</v>
       </c>
       <c r="AM17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="2">
         <v>3</v>
@@ -8280,7 +8280,7 @@
         <v>1132</v>
       </c>
       <c r="CI17" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ17" s="2">
         <v>12</v>
@@ -8316,13 +8316,13 @@
         <v>1836</v>
       </c>
       <c r="CU17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CV17" s="1">
         <v>15</v>
       </c>
       <c r="CW17" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:101">
@@ -8351,7 +8351,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v>3</v>
       </c>
       <c r="CW18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:101">
@@ -9368,7 +9368,7 @@
         <v>18</v>
       </c>
       <c r="AQ21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR21" s="2">
         <v>2</v>
@@ -9500,7 +9500,7 @@
         <v>237</v>
       </c>
       <c r="CI21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ21" s="2">
         <v>19</v>
@@ -9536,7 +9536,7 @@
         <v>384</v>
       </c>
       <c r="CU21" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CV21" s="1">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>88</v>
       </c>
       <c r="AM27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" s="2">
         <v>13</v>
@@ -11366,7 +11366,7 @@
         <v>554</v>
       </c>
       <c r="CU27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV27" s="1">
         <v>31</v>
@@ -11410,7 +11410,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M28" s="2">
         <v>58</v>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="AF28" s="2">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="2">
         <v>173</v>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
       <c r="AR28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS28" s="2">
         <v>5</v>
@@ -11638,7 +11638,7 @@
         <v>3</v>
       </c>
       <c r="CJ28" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CK28" s="2">
         <v>26</v>
@@ -11674,7 +11674,7 @@
         <v>24</v>
       </c>
       <c r="CV28" s="1">
-        <v>240</v>
+        <v>44</v>
       </c>
       <c r="CW28" s="1">
         <v>303</v>
@@ -12603,7 +12603,7 @@
         <v>2635</v>
       </c>
       <c r="C32" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2">
         <v>54</v>
@@ -12891,7 +12891,7 @@
         <v>11168</v>
       </c>
       <c r="CU32" s="1">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="CV32" s="1">
         <v>133</v>
@@ -12911,7 +12911,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
@@ -12923,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" s="2">
         <v>4</v>
@@ -13199,7 +13199,7 @@
         <v>3</v>
       </c>
       <c r="CV33" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="CW33" s="1">
         <v>18</v>
@@ -13324,7 +13324,7 @@
         <v>0</v>
       </c>
       <c r="AN34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" s="2">
         <v>3</v>
@@ -13468,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="CJ34" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CK34" s="2">
         <v>8</v>
@@ -13504,7 +13504,7 @@
         <v>32</v>
       </c>
       <c r="CV34" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="CW34" s="1">
         <v>117</v>
@@ -13841,7 +13841,7 @@
         <v>3</v>
       </c>
       <c r="I36" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -14117,7 +14117,7 @@
         <v>3</v>
       </c>
       <c r="CW36" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:101">
@@ -14852,7 +14852,7 @@
         <v>7</v>
       </c>
       <c r="AO39" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP39" s="1">
         <v>14</v>
@@ -14996,7 +14996,7 @@
         <v>53</v>
       </c>
       <c r="CK39" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="CL39" s="1">
         <v>2</v>
@@ -15032,7 +15032,7 @@
         <v>65</v>
       </c>
       <c r="CW39" s="1">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:101">
@@ -15082,7 +15082,7 @@
         <v>8</v>
       </c>
       <c r="P40" s="2">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="Q40" s="2">
         <v>779</v>
@@ -15238,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="BP40" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BQ40" s="2">
         <v>2</v>
@@ -15334,7 +15334,7 @@
         <v>45</v>
       </c>
       <c r="CV40" s="1">
-        <v>342</v>
+        <v>171</v>
       </c>
       <c r="CW40" s="1">
         <v>1739</v>
@@ -18512,7 +18512,7 @@
         <v>158</v>
       </c>
       <c r="AO51" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AP51" s="1">
         <v>31</v>
@@ -18656,7 +18656,7 @@
         <v>1795</v>
       </c>
       <c r="CK51" s="2">
-        <v>1891</v>
+        <v>1855</v>
       </c>
       <c r="CL51" s="1">
         <v>0</v>
@@ -18692,7 +18692,7 @@
         <v>2002</v>
       </c>
       <c r="CW51" s="1">
-        <v>2112</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="52" spans="1:101">
@@ -20877,7 +20877,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="2">
         <v>8</v>
@@ -20949,7 +20949,7 @@
         <v>0</v>
       </c>
       <c r="AN59" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO59" s="2">
         <v>3</v>
@@ -21093,7 +21093,7 @@
         <v>1</v>
       </c>
       <c r="CJ59" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CK59" s="2">
         <v>12</v>
@@ -21129,7 +21129,7 @@
         <v>10</v>
       </c>
       <c r="CV59" s="1">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="CW59" s="1">
         <v>58</v>
@@ -21475,7 +21475,7 @@
         <v>7</v>
       </c>
       <c r="L61" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M61" s="2">
         <v>46</v>
@@ -21568,7 +21568,7 @@
         <v>38</v>
       </c>
       <c r="AQ61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR61" s="2">
         <v>2</v>
@@ -21700,7 +21700,7 @@
         <v>5342</v>
       </c>
       <c r="CI61" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CJ61" s="2">
         <v>24</v>
@@ -21736,10 +21736,10 @@
         <v>65867</v>
       </c>
       <c r="CU61" s="1">
-        <v>-41</v>
+        <v>-52</v>
       </c>
       <c r="CV61" s="1">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="CW61" s="1">
         <v>721</v>
@@ -22085,7 +22085,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M63" s="2">
         <v>17</v>
@@ -22265,7 +22265,7 @@
         <v>1</v>
       </c>
       <c r="BT63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU63" s="2">
         <v>2</v>
@@ -22349,7 +22349,7 @@
         <v>32</v>
       </c>
       <c r="CV63" s="1">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="CW63" s="1">
         <v>197</v>
@@ -22447,7 +22447,7 @@
         <v>2041</v>
       </c>
       <c r="AE64" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF64" s="2">
         <v>48</v>
@@ -22651,7 +22651,7 @@
         <v>8148</v>
       </c>
       <c r="CU64" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="CV64" s="1">
         <v>236</v>
@@ -22692,10 +22692,10 @@
         <v>1800</v>
       </c>
       <c r="K65" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="M65" s="2">
         <v>88</v>
@@ -22734,7 +22734,7 @@
         <v>0</v>
       </c>
       <c r="Y65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z65" s="1">
         <v>115</v>
@@ -22956,13 +22956,13 @@
         <v>67260</v>
       </c>
       <c r="CU65" s="1">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="CV65" s="1">
-        <v>1773</v>
+        <v>1752</v>
       </c>
       <c r="CW65" s="1">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="66" spans="1:101">
@@ -25108,7 +25108,7 @@
         <v>54</v>
       </c>
       <c r="C73" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73" s="2">
         <v>5</v>
@@ -25219,7 +25219,7 @@
         <v>0</v>
       </c>
       <c r="AN73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO73" s="2">
         <v>4</v>
@@ -25360,10 +25360,10 @@
         <v>525</v>
       </c>
       <c r="CI73" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ73" s="2">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="CK73" s="2">
         <v>63</v>
@@ -25396,10 +25396,10 @@
         <v>748</v>
       </c>
       <c r="CU73" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="CV73" s="1">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="CW73" s="1">
         <v>79</v>
@@ -25437,7 +25437,7 @@
         <v>10199</v>
       </c>
       <c r="K74" s="2">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="L74" s="2">
         <v>124</v>
@@ -25524,10 +25524,10 @@
         <v>37</v>
       </c>
       <c r="AN74" s="2">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="AO74" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="AP74" s="1">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>32</v>
       </c>
       <c r="CJ74" s="2">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="CK74" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="CL74" s="1">
         <v>0</v>
@@ -25701,13 +25701,13 @@
         <v>171880</v>
       </c>
       <c r="CU74" s="1">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="CV74" s="1">
-        <v>585</v>
+        <v>528</v>
       </c>
       <c r="CW74" s="1">
-        <v>3834</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="75" spans="1:101">
@@ -26098,7 +26098,7 @@
         <v>0</v>
       </c>
       <c r="AB76" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC76" s="2">
         <v>8</v>
@@ -26314,7 +26314,7 @@
         <v>71</v>
       </c>
       <c r="CV76" s="1">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="CW76" s="1">
         <v>3073</v>
@@ -26334,7 +26334,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="2">
-        <v>-1298</v>
+        <v>2</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -26352,10 +26352,10 @@
         <v>4920</v>
       </c>
       <c r="K77" s="2">
-        <v>42</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="2">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="M77" s="2">
         <v>271</v>
@@ -26439,7 +26439,7 @@
         <v>2</v>
       </c>
       <c r="AN77" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AO77" s="2">
         <v>68</v>
@@ -26583,7 +26583,7 @@
         <v>50</v>
       </c>
       <c r="CJ77" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="CK77" s="2">
         <v>529</v>
@@ -26616,13 +26616,13 @@
         <v>391010</v>
       </c>
       <c r="CU77" s="1">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="CV77" s="1">
-        <v>10159</v>
+        <v>10110</v>
       </c>
       <c r="CW77" s="1">
-        <v>18783</v>
+        <v>20083</v>
       </c>
     </row>
     <row r="78" spans="1:101">
@@ -26645,7 +26645,7 @@
         <v>29</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
         <v>2</v>
@@ -26921,7 +26921,7 @@
         <v>286</v>
       </c>
       <c r="CU78" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CV78" s="1">
         <v>32</v>
@@ -27133,7 +27133,7 @@
         <v>0</v>
       </c>
       <c r="BP79" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ79" s="2">
         <v>15</v>
@@ -27229,7 +27229,7 @@
         <v>90</v>
       </c>
       <c r="CV79" s="1">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="CW79" s="1">
         <v>1541</v>
@@ -27351,7 +27351,7 @@
         <v>813</v>
       </c>
       <c r="AM80" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AN80" s="2">
         <v>41</v>
@@ -27495,7 +27495,7 @@
         <v>824</v>
       </c>
       <c r="CI80" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CJ80" s="2">
         <v>38</v>
@@ -27531,7 +27531,7 @@
         <v>1807</v>
       </c>
       <c r="CU80" s="1">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="CV80" s="1">
         <v>94</v>
@@ -27551,7 +27551,7 @@
         <v>2</v>
       </c>
       <c r="D81" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E81" s="2">
         <v>15</v>
@@ -27572,7 +27572,7 @@
         <v>1604</v>
       </c>
       <c r="K81" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L81" s="2">
         <v>53</v>
@@ -27656,7 +27656,7 @@
         <v>47</v>
       </c>
       <c r="AM81" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN81" s="2">
         <v>6</v>
@@ -27800,7 +27800,7 @@
         <v>157</v>
       </c>
       <c r="CI81" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ81" s="2">
         <v>4</v>
@@ -27836,10 +27836,10 @@
         <v>6451</v>
       </c>
       <c r="CU81" s="1">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="CV81" s="1">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="CW81" s="1">
         <v>366</v>
@@ -28197,7 +28197,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="2">
-        <v>269</v>
+        <v>-1</v>
       </c>
       <c r="Q83" s="2">
         <v>990</v>
@@ -28266,10 +28266,10 @@
         <v>3401</v>
       </c>
       <c r="AM83" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN83" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO83" s="2">
         <v>16</v>
@@ -28410,10 +28410,10 @@
         <v>13813</v>
       </c>
       <c r="CI83" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CJ83" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="CK83" s="2">
         <v>238</v>
@@ -28446,10 +28446,10 @@
         <v>423966</v>
       </c>
       <c r="CU83" s="1">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="CV83" s="1">
-        <v>632</v>
+        <v>288</v>
       </c>
       <c r="CW83" s="1">
         <v>1958</v>
@@ -29486,10 +29486,10 @@
         <v>505</v>
       </c>
       <c r="AM87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN87" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO87" s="2">
         <v>1</v>
@@ -29630,10 +29630,10 @@
         <v>2402</v>
       </c>
       <c r="CI87" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ87" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="CK87" s="2">
         <v>71</v>
@@ -29666,10 +29666,10 @@
         <v>2988</v>
       </c>
       <c r="CU87" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="CV87" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CW87" s="1">
         <v>79</v>
@@ -30625,7 +30625,7 @@
         <v>53</v>
       </c>
       <c r="L91" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="M91" s="2">
         <v>307</v>
@@ -30637,7 +30637,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="2">
         <v>66</v>
@@ -30889,7 +30889,7 @@
         <v>175</v>
       </c>
       <c r="CV91" s="1">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="CW91" s="1">
         <v>809</v>
@@ -33361,7 +33361,7 @@
         <v>3</v>
       </c>
       <c r="I100" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -33637,7 +33637,7 @@
         <v>14</v>
       </c>
       <c r="CW100" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:101">
@@ -33977,7 +33977,7 @@
         <v>5162</v>
       </c>
       <c r="K102" s="2">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="L102" s="2">
         <v>101</v>
@@ -33992,7 +33992,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="2">
         <v>534</v>
@@ -34241,10 +34241,10 @@
         <v>43217</v>
       </c>
       <c r="CU102" s="1">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="CV102" s="1">
-        <v>583</v>
+        <v>383</v>
       </c>
       <c r="CW102" s="1">
         <v>1643</v>
@@ -34372,7 +34372,7 @@
         <v>26</v>
       </c>
       <c r="AO103" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP103" s="1">
         <v>0</v>
@@ -34516,7 +34516,7 @@
         <v>184</v>
       </c>
       <c r="CK103" s="2">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="CL103" s="1">
         <v>0</v>
@@ -34552,7 +34552,7 @@
         <v>213</v>
       </c>
       <c r="CW103" s="1">
-        <v>284</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" spans="1:101">
@@ -34868,7 +34868,7 @@
         <v>531</v>
       </c>
       <c r="C105" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D105" s="2">
         <v>7</v>
@@ -34895,7 +34895,7 @@
         <v>29</v>
       </c>
       <c r="L105" s="2">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M105" s="2">
         <v>81</v>
@@ -34955,7 +34955,7 @@
         <v>0</v>
       </c>
       <c r="AF105" s="2">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="AG105" s="2">
         <v>375</v>
@@ -35156,10 +35156,10 @@
         <v>8053</v>
       </c>
       <c r="CU105" s="1">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="CV105" s="1">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="CW105" s="1">
         <v>549</v>
@@ -35176,7 +35176,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="2">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="E106" s="2">
         <v>327</v>
@@ -35212,7 +35212,7 @@
         <v>-1</v>
       </c>
       <c r="P106" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="Q106" s="2">
         <v>488</v>
@@ -35284,7 +35284,7 @@
         <v>0</v>
       </c>
       <c r="AN106" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO106" s="2">
         <v>13</v>
@@ -35425,10 +35425,10 @@
         <v>6493</v>
       </c>
       <c r="CI106" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="CJ106" s="2">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="CK106" s="2">
         <v>294</v>
@@ -35461,10 +35461,10 @@
         <v>92789</v>
       </c>
       <c r="CU106" s="1">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="CV106" s="1">
-        <v>1015</v>
+        <v>889</v>
       </c>
       <c r="CW106" s="1">
         <v>2013</v>
@@ -36420,7 +36420,7 @@
         <v>82</v>
       </c>
       <c r="L110" s="2">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="M110" s="2">
         <v>381</v>
@@ -36480,7 +36480,7 @@
         <v>0</v>
       </c>
       <c r="AF110" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG110" s="2">
         <v>50</v>
@@ -36684,7 +36684,7 @@
         <v>154</v>
       </c>
       <c r="CV110" s="1">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="CW110" s="1">
         <v>765</v>
@@ -37042,7 +37042,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="2">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="2">
         <v>484</v>
@@ -37123,10 +37123,10 @@
         <v>74</v>
       </c>
       <c r="AQ112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS112" s="2">
         <v>5</v>
@@ -37255,10 +37255,10 @@
         <v>264</v>
       </c>
       <c r="CI112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ112" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CK112" s="2">
         <v>22</v>
@@ -37291,10 +37291,10 @@
         <v>8319</v>
       </c>
       <c r="CU112" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CV112" s="1">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="CW112" s="1">
         <v>630</v>
@@ -37347,7 +37347,7 @@
         <v>0</v>
       </c>
       <c r="P113" s="2">
-        <v>175</v>
+        <v>-2</v>
       </c>
       <c r="Q113" s="2">
         <v>449</v>
@@ -37566,7 +37566,7 @@
         <v>66</v>
       </c>
       <c r="CK113" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="CL113" s="1">
         <v>1</v>
@@ -37599,10 +37599,10 @@
         <v>1310</v>
       </c>
       <c r="CV113" s="1">
-        <v>1710</v>
+        <v>1533</v>
       </c>
       <c r="CW113" s="1">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="114" spans="1:101">
@@ -38250,7 +38250,7 @@
         <v>36</v>
       </c>
       <c r="L116" s="2">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="M116" s="2">
         <v>207</v>
@@ -38310,7 +38310,7 @@
         <v>0</v>
       </c>
       <c r="AF116" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG116" s="2">
         <v>40</v>
@@ -38334,7 +38334,7 @@
         <v>3</v>
       </c>
       <c r="AN116" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO116" s="2">
         <v>8</v>
@@ -38478,7 +38478,7 @@
         <v>29</v>
       </c>
       <c r="CJ116" s="2">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="CK116" s="2">
         <v>75</v>
@@ -38514,7 +38514,7 @@
         <v>254</v>
       </c>
       <c r="CV116" s="1">
-        <v>448</v>
+        <v>351</v>
       </c>
       <c r="CW116" s="1">
         <v>869</v>
@@ -38528,7 +38528,7 @@
         <v>9560</v>
       </c>
       <c r="C117" s="2">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2">
         <v>372</v>
@@ -38816,7 +38816,7 @@
         <v>13371</v>
       </c>
       <c r="CU117" s="1">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="CV117" s="1">
         <v>388</v>
@@ -42206,7 +42206,7 @@
         <v>2</v>
       </c>
       <c r="I129" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J129" s="1">
         <v>0</v>
@@ -42227,7 +42227,7 @@
         <v>0</v>
       </c>
       <c r="P129" s="2">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="2">
         <v>78</v>
@@ -42296,7 +42296,7 @@
         <v>416</v>
       </c>
       <c r="AM129" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN129" s="2">
         <v>4</v>
@@ -42311,7 +42311,7 @@
         <v>0</v>
       </c>
       <c r="AR129" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS129" s="2">
         <v>4</v>
@@ -42440,10 +42440,10 @@
         <v>502</v>
       </c>
       <c r="CI129" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CJ129" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="CK129" s="2">
         <v>26</v>
@@ -42476,13 +42476,13 @@
         <v>3573</v>
       </c>
       <c r="CU129" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CV129" s="1">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="CW129" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="130" spans="1:101">
@@ -42601,7 +42601,7 @@
         <v>157</v>
       </c>
       <c r="AM130" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN130" s="2">
         <v>8</v>
@@ -42745,7 +42745,7 @@
         <v>219</v>
       </c>
       <c r="CI130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ130" s="2">
         <v>5</v>
@@ -42781,7 +42781,7 @@
         <v>1099</v>
       </c>
       <c r="CU130" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CV130" s="1">
         <v>18</v>
@@ -43118,7 +43118,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I132" s="2">
         <v>4</v>
@@ -43394,7 +43394,7 @@
         <v>0</v>
       </c>
       <c r="CV132" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CW132" s="1">
         <v>4</v>
@@ -43420,7 +43420,7 @@
         <v>73</v>
       </c>
       <c r="G133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="2">
         <v>2</v>
@@ -43696,7 +43696,7 @@
         <v>97</v>
       </c>
       <c r="CU133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV133" s="1">
         <v>2</v>
@@ -43821,7 +43821,7 @@
         <v>1330</v>
       </c>
       <c r="AM134" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN134" s="2">
         <v>5</v>
@@ -43965,7 +43965,7 @@
         <v>2750</v>
       </c>
       <c r="CI134" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CJ134" s="2">
         <v>26</v>
@@ -44001,7 +44001,7 @@
         <v>134467</v>
       </c>
       <c r="CU134" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="CV134" s="1">
         <v>1789</v>
@@ -44018,7 +44018,7 @@
         <v>7706</v>
       </c>
       <c r="C135" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D135" s="2">
         <v>81</v>
@@ -44042,7 +44042,7 @@
         <v>6596</v>
       </c>
       <c r="K135" s="2">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L135" s="2">
         <v>118</v>
@@ -44096,7 +44096,7 @@
         <v>0</v>
       </c>
       <c r="AC135" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD135" s="1">
         <v>11840</v>
@@ -44108,7 +44108,7 @@
         <v>203</v>
       </c>
       <c r="AG135" s="2">
-        <v>802</v>
+        <v>213</v>
       </c>
       <c r="AH135" s="1">
         <v>0</v>
@@ -44129,7 +44129,7 @@
         <v>4</v>
       </c>
       <c r="AN135" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO135" s="2">
         <v>8</v>
@@ -44273,7 +44273,7 @@
         <v>18</v>
       </c>
       <c r="CJ135" s="2">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="CK135" s="2">
         <v>126</v>
@@ -44306,13 +44306,13 @@
         <v>62814</v>
       </c>
       <c r="CU135" s="1">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="CV135" s="1">
-        <v>883</v>
+        <v>850</v>
       </c>
       <c r="CW135" s="1">
-        <v>2537</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="136" spans="1:101">
@@ -44353,7 +44353,7 @@
         <v>1</v>
       </c>
       <c r="M136" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N136" s="1">
         <v>1439</v>
@@ -44578,7 +44578,7 @@
         <v>1</v>
       </c>
       <c r="CJ136" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CK136" s="2">
         <v>19</v>
@@ -44614,10 +44614,10 @@
         <v>-4</v>
       </c>
       <c r="CV136" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="CW136" s="1">
-        <v>5130</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="137" spans="1:101">
@@ -45851,7 +45851,7 @@
         <v>0</v>
       </c>
       <c r="D141" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E141" s="2">
         <v>10</v>
@@ -46055,7 +46055,7 @@
         <v>0</v>
       </c>
       <c r="BT141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU141" s="2">
         <v>1</v>
@@ -46139,7 +46139,7 @@
         <v>1</v>
       </c>
       <c r="CV141" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CW141" s="1">
         <v>28</v>
@@ -46470,7 +46470,7 @@
         <v>73</v>
       </c>
       <c r="G143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
         <v>2</v>
@@ -46578,7 +46578,7 @@
         <v>82</v>
       </c>
       <c r="AQ143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR143" s="2">
         <v>2</v>
@@ -46722,7 +46722,7 @@
         <v>74</v>
       </c>
       <c r="CM143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN143" s="2">
         <v>2</v>
@@ -46746,7 +46746,7 @@
         <v>301</v>
       </c>
       <c r="CU143" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CV143" s="1">
         <v>11</v>
@@ -47155,7 +47155,7 @@
         <v>0</v>
       </c>
       <c r="AF145" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AG145" s="2">
         <v>9</v>
@@ -47359,7 +47359,7 @@
         <v>5</v>
       </c>
       <c r="CV145" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CW145" s="1">
         <v>117</v>
@@ -48713,7 +48713,7 @@
         <v>87</v>
       </c>
       <c r="AQ150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR150" s="2">
         <v>2</v>
@@ -48857,7 +48857,7 @@
         <v>53</v>
       </c>
       <c r="CM150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN150" s="2">
         <v>1</v>
@@ -48881,7 +48881,7 @@
         <v>310</v>
       </c>
       <c r="CU150" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CV150" s="1">
         <v>5</v>
@@ -50142,7 +50142,7 @@
         <v>563</v>
       </c>
       <c r="K155" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2">
         <v>10</v>
@@ -50406,7 +50406,7 @@
         <v>2670</v>
       </c>
       <c r="CU155" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CV155" s="1">
         <v>44</v>
@@ -50543,7 +50543,7 @@
         <v>55</v>
       </c>
       <c r="AQ156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR156" s="2">
         <v>1</v>
@@ -50675,7 +50675,7 @@
         <v>2799</v>
       </c>
       <c r="CI156" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CJ156" s="2">
         <v>32</v>
@@ -50711,7 +50711,7 @@
         <v>71555</v>
       </c>
       <c r="CU156" s="1">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="CV156" s="1">
         <v>1044</v>
@@ -51987,7 +51987,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="2">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="Q161" s="2">
         <v>478</v>
@@ -52239,7 +52239,7 @@
         <v>26</v>
       </c>
       <c r="CV161" s="1">
-        <v>377</v>
+        <v>123</v>
       </c>
       <c r="CW161" s="1">
         <v>1071</v>
@@ -52564,7 +52564,7 @@
         <v>1</v>
       </c>
       <c r="E163" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1">
         <v>31</v>
@@ -52669,7 +52669,7 @@
         <v>0</v>
       </c>
       <c r="AN163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO163" s="2">
         <v>1</v>
@@ -52813,7 +52813,7 @@
         <v>2</v>
       </c>
       <c r="CJ163" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CK163" s="2">
         <v>14</v>
@@ -52849,10 +52849,10 @@
         <v>4</v>
       </c>
       <c r="CV163" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CW163" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:101">
@@ -52950,7 +52950,7 @@
         <v>0</v>
       </c>
       <c r="AF164" s="2">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AG164" s="2">
         <v>120</v>
@@ -52974,7 +52974,7 @@
         <v>0</v>
       </c>
       <c r="AN164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO164" s="2">
         <v>1</v>
@@ -52983,7 +52983,7 @@
         <v>18</v>
       </c>
       <c r="AQ164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR164" s="2">
         <v>2</v>
@@ -53115,10 +53115,10 @@
         <v>154</v>
       </c>
       <c r="CI164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ164" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CK164" s="2">
         <v>7</v>
@@ -53151,10 +53151,10 @@
         <v>1137</v>
       </c>
       <c r="CU164" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV164" s="1">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="CW164" s="1">
         <v>180</v>
@@ -53512,7 +53512,7 @@
         <v>0</v>
       </c>
       <c r="P166" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="Q166" s="2">
         <v>169</v>
@@ -53764,7 +53764,7 @@
         <v>23</v>
       </c>
       <c r="CV166" s="1">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="CW166" s="1">
         <v>494</v>
@@ -54696,7 +54696,7 @@
         <v>25</v>
       </c>
       <c r="D170" s="2">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="E170" s="2">
         <v>141</v>
@@ -54723,7 +54723,7 @@
         <v>145</v>
       </c>
       <c r="M170" s="2">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="N170" s="1">
         <v>2774</v>
@@ -54771,7 +54771,7 @@
         <v>4</v>
       </c>
       <c r="AC170" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AD170" s="1">
         <v>3603</v>
@@ -54780,7 +54780,7 @@
         <v>1</v>
       </c>
       <c r="AF170" s="2">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="AG170" s="2">
         <v>127</v>
@@ -54807,7 +54807,7 @@
         <v>4</v>
       </c>
       <c r="AO170" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP170" s="1">
         <v>36</v>
@@ -54951,7 +54951,7 @@
         <v>68</v>
       </c>
       <c r="CK170" s="2">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="CL170" s="1">
         <v>17</v>
@@ -54984,10 +54984,10 @@
         <v>118</v>
       </c>
       <c r="CV170" s="1">
-        <v>499</v>
+        <v>378</v>
       </c>
       <c r="CW170" s="1">
-        <v>954</v>
+        <v>816</v>
       </c>
     </row>
     <row r="171" spans="1:101">
@@ -55106,7 +55106,7 @@
         <v>1190</v>
       </c>
       <c r="AM171" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN171" s="2">
         <v>4</v>
@@ -55286,7 +55286,7 @@
         <v>5854</v>
       </c>
       <c r="CU171" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CV171" s="1">
         <v>49</v>
@@ -56529,7 +56529,7 @@
         <v>1</v>
       </c>
       <c r="E176" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F176" s="1">
         <v>53</v>
@@ -56634,7 +56634,7 @@
         <v>1</v>
       </c>
       <c r="AN176" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AO176" s="2">
         <v>40</v>
@@ -56778,7 +56778,7 @@
         <v>11</v>
       </c>
       <c r="CJ176" s="2">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="CK176" s="2">
         <v>89</v>
@@ -56814,10 +56814,10 @@
         <v>13</v>
       </c>
       <c r="CV176" s="1">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="CW176" s="1">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="177" spans="1:101">
@@ -57232,7 +57232,7 @@
         <v>1</v>
       </c>
       <c r="AJ178" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK178" s="2">
         <v>2</v>
@@ -57241,10 +57241,10 @@
         <v>172</v>
       </c>
       <c r="AM178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN178" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO178" s="2">
         <v>28</v>
@@ -57385,10 +57385,10 @@
         <v>1176</v>
       </c>
       <c r="CI178" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CJ178" s="2">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="CK178" s="2">
         <v>131</v>
@@ -57421,10 +57421,10 @@
         <v>84925</v>
       </c>
       <c r="CU178" s="1">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="CV178" s="1">
-        <v>2124</v>
+        <v>2102</v>
       </c>
       <c r="CW178" s="1">
         <v>4515</v>
@@ -57549,7 +57549,7 @@
         <v>0</v>
       </c>
       <c r="AN179" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AO179" s="2">
         <v>29</v>
@@ -57693,7 +57693,7 @@
         <v>0</v>
       </c>
       <c r="CJ179" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CK179" s="2">
         <v>24</v>
@@ -57729,7 +57729,7 @@
         <v>2</v>
       </c>
       <c r="CV179" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CW179" s="1">
         <v>60</v>
@@ -58066,7 +58066,7 @@
         <v>3</v>
       </c>
       <c r="I181" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J181" s="1">
         <v>0</v>
@@ -58342,7 +58342,7 @@
         <v>3</v>
       </c>
       <c r="CW181" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:101">
@@ -62052,7 +62052,7 @@
         <v>0</v>
       </c>
       <c r="P194" s="2">
-        <v>499</v>
+        <v>17</v>
       </c>
       <c r="Q194" s="2">
         <v>1228</v>
@@ -62220,7 +62220,7 @@
         <v>-1</v>
       </c>
       <c r="BT194" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BU194" s="2">
         <v>0</v>
@@ -62304,7 +62304,7 @@
         <v>37</v>
       </c>
       <c r="CV194" s="1">
-        <v>598</v>
+        <v>115</v>
       </c>
       <c r="CW194" s="1">
         <v>1382</v>
@@ -62336,7 +62336,7 @@
         <v>1</v>
       </c>
       <c r="I195" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J195" s="1">
         <v>170</v>
@@ -62573,7 +62573,7 @@
         <v>0</v>
       </c>
       <c r="CJ195" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CK195" s="2">
         <v>23</v>
@@ -62609,10 +62609,10 @@
         <v>3</v>
       </c>
       <c r="CV195" s="1">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="CW195" s="1">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="196" spans="1:101">
@@ -63882,7 +63882,7 @@
         <v>-1</v>
       </c>
       <c r="P200" s="2">
-        <v>31</v>
+        <v>-1</v>
       </c>
       <c r="Q200" s="2">
         <v>84</v>
@@ -64134,7 +64134,7 @@
         <v>59</v>
       </c>
       <c r="CV200" s="1">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="CW200" s="1">
         <v>466</v>
@@ -64235,10 +64235,10 @@
         <v>0</v>
       </c>
       <c r="AF201" s="2">
-        <v>1606</v>
+        <v>0</v>
       </c>
       <c r="AG201" s="2">
-        <v>1648</v>
+        <v>1636</v>
       </c>
       <c r="AH201" s="1">
         <v>0</v>
@@ -64256,10 +64256,10 @@
         <v>334</v>
       </c>
       <c r="AM201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN201" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO201" s="2">
         <v>5</v>
@@ -64400,7 +64400,7 @@
         <v>3616</v>
       </c>
       <c r="CI201" s="2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CJ201" s="2">
         <v>47</v>
@@ -64436,13 +64436,13 @@
         <v>88300</v>
       </c>
       <c r="CU201" s="1">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="CV201" s="1">
-        <v>2141</v>
+        <v>534</v>
       </c>
       <c r="CW201" s="1">
-        <v>2856</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="202" spans="1:101">
@@ -66699,7 +66699,7 @@
         <v>0</v>
       </c>
       <c r="AN209" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO209" s="2">
         <v>8</v>
@@ -66843,7 +66843,7 @@
         <v>0</v>
       </c>
       <c r="CJ209" s="2">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="CK209" s="2">
         <v>57</v>
@@ -66879,7 +66879,7 @@
         <v>0</v>
       </c>
       <c r="CV209" s="1">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="CW209" s="1">
         <v>84</v>
@@ -67201,7 +67201,7 @@
         <v>3</v>
       </c>
       <c r="D211" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E211" s="2">
         <v>12</v>
@@ -67228,7 +67228,7 @@
         <v>31</v>
       </c>
       <c r="M211" s="2">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N211" s="1">
         <v>835</v>
@@ -67285,7 +67285,7 @@
         <v>0</v>
       </c>
       <c r="AF211" s="2">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AG211" s="2">
         <v>382</v>
@@ -67489,10 +67489,10 @@
         <v>46</v>
       </c>
       <c r="CV211" s="1">
-        <v>500</v>
+        <v>116</v>
       </c>
       <c r="CW211" s="1">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="212" spans="1:101">
@@ -69057,7 +69057,7 @@
         <v>559</v>
       </c>
       <c r="D32">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
         <v>716</v>
@@ -70140,7 +70140,7 @@
         <v>604</v>
       </c>
       <c r="D86">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E86" t="s">
         <v>716</v>
@@ -70746,7 +70746,7 @@
         <v>631</v>
       </c>
       <c r="D116">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E116" t="s">
         <v>716</v>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="489">
   <si>
     <t>ati_all</t>
   </si>
@@ -980,31 +980,7 @@
     <t>16342451 Canada Inc.  | 16342451 Canada Inc</t>
   </si>
   <si>
-    <t>Agriculture and Agri-Food Canada | Agriculture et Agroalimentaire Canada</t>
-  </si>
-  <si>
-    <t>Crown-Indigenous Relations and Northern Affairs Canada | Relations Couronne-Autochtones et Affaires du Nord Canada</t>
-  </si>
-  <si>
-    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
-  </si>
-  <si>
     <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
-  </si>
-  <si>
-    <t>Atlantic Pilotage Authority Canada | Administration de pilotage de l'Atlantique Canada</t>
-  </si>
-  <si>
-    <t>Asia-Pacific Foundation of Canada | Fondation Asie Pacifique du Canada</t>
-  </si>
-  <si>
-    <t>Administrative Tribunals Support Service of Canada | Service canadien d'appui aux tribunaux administratifs</t>
-  </si>
-  <si>
-    <t>Bank of Canada | Banque du Canada</t>
-  </si>
-  <si>
-    <t>British Columbia Treaty Commission | Commission des Traités de la Colombie-Britannique</t>
   </si>
   <si>
     <t>Business Development Bank of Canada | Banque de développement du Canada</t>
@@ -1016,43 +992,67 @@
     <t>Courts Administration Service | Service administratif des tribunaux judiciaires</t>
   </si>
   <si>
-    <t>Accessibility Standards Canada | Normes d’accessibilité Canada</t>
+    <t>Canadian Broadcasting Company | Radio-Canada</t>
   </si>
   <si>
-    <t>Canadian Air Transport Security Authority | Administration canadienne de la sûreté du transport aérien</t>
-  </si>
-  <si>
-    <t>Canadian Commercial Corporation | Corporation commerciale canadienne</t>
-  </si>
-  <si>
-    <t>Canadian Cultural Property Export Review Board | Commission canadienne d'examen des exportations de biens culturels</t>
-  </si>
-  <si>
-    <t>Canadian Dairy Commission | Commission canadienne du lait</t>
+    <t>Canada Border Services Agency | Agence des services frontaliers du Canada</t>
   </si>
   <si>
     <t>Canada Enterprise Emergency Funding Corporation | La Corporation de financement d’urgence d’entreprises du Canada</t>
   </si>
   <si>
-    <t>Canadian Forces Morale and Welfare Services | Services de bien-être et moral des Forces canadiennes</t>
+    <t>Canadian Food Inspection Agency | Agence canadienne d'inspection des aliments</t>
   </si>
   <si>
-    <t>Canada Growth Fund Inc. | Fonds de Croissance du Canada Inc.</t>
+    <t>Canadian Grain Commission | Commission canadienne des grains</t>
   </si>
   <si>
-    <t>Canadian Nuclear Safety Commission | Commission canadienne de sûreté nucléaire</t>
+    <t>Canadian Human Rights Commission | Commission canadienne des droits de la personne</t>
   </si>
   <si>
-    <t>Communications Security Establishment Canada | Centre de la sécurité des télécommunications Canada</t>
+    <t>College of Immigration and Citizenship Consultants | Collège des Consultants en Immigration et en Citoyenneté</t>
   </si>
   <si>
-    <t>Canada School of Public Service | École de la fonction publique du Canada</t>
+    <t>Canada-Newfoundland and Labrador Offshore Petroleum Board | Office Canada–Terre-Neuve-et Labrador des hydrocarbures extracôtiers</t>
   </si>
   <si>
-    <t>Great Lakes Pilotage Authority Canada | Administration de pilotage des Grands Lacs Canada</t>
+    <t>College of Patent Agents and Trademark Agents | Collège des agents de brevets et des agents de marques de commerce</t>
   </si>
   <si>
-    <t>International Joint Commission | Commission mixte internationale</t>
+    <t>Canada Post | Postes Canada</t>
+  </si>
+  <si>
+    <t>National Defence | Défense nationale</t>
+  </si>
+  <si>
+    <t>Environment and Climate Change Canada | Environnement et Changement climatique Canada</t>
+  </si>
+  <si>
+    <t>Employment and Social Development Canada | Emploi et Développement social Canada</t>
+  </si>
+  <si>
+    <t>First Nations Tax Commission | Commission de la fiscalité des premières nations</t>
+  </si>
+  <si>
+    <t>Office of the Administrator of the Fund for Railway Accidents Involving Designated Goods; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
+  </si>
+  <si>
+    <t>VIA HFR - VIA TGF Inc. | VIA HFR - VIA TGF Inc.</t>
+  </si>
+  <si>
+    <t>Impact Assessment Agency of Canada | Agence d'évaluation d'impact du Canada</t>
+  </si>
+  <si>
+    <t>Marine Atlantic Inc. | Marine Atlantique S.C.C.</t>
+  </si>
+  <si>
+    <t>Military Grievances External Review Committee | Comité externe d’examen des griefs militaires</t>
+  </si>
+  <si>
+    <t>Mackenzie Valley Land and Water Board | Office des terres et des eaux de la vallée du Mackenzie Valley</t>
+  </si>
+  <si>
+    <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
   </si>
   <si>
     <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
@@ -1061,49 +1061,34 @@
     <t>Office of the Privacy Commissioner of Canada | Commissariat à la protection de la vie privée du Canada</t>
   </si>
   <si>
-    <t>Port Alberni Port Authority | Administration portuaire de Port Alberni</t>
+    <t>Public Health Agency of Canada | Agence de la santé publique du Canada</t>
   </si>
   <si>
-    <t>Parole Board of Canada | Commission des libérations conditionnelles du Canada</t>
+    <t>President of the King’s Privy Council for Canada | Président du Conseil privé du Roi pour le Canada</t>
   </si>
   <si>
-    <t>The Seaway International Bridge Corporation | Corporation du pont international de la voie maritime, Ltée</t>
+    <t>Polar Knowledge Canada | Savoir polaire Canada</t>
   </si>
   <si>
-    <t>Office of the Administrator of the Ship-source Oil Pollution Fund; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation des dommages dus à la pollution par les hydrocarbures causée par les navires; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
+    <t>Prince Rupert Port Authority | L’Administration portuaire de Prince Rupert</t>
   </si>
   <si>
-    <t>Saguenay Port Authority | Administration portuaire du Saguenay</t>
+    <t>Revera Inc. | Revera Inc.</t>
+  </si>
+  <si>
+    <t>St. John's Port Authority | Administration portuaire de St. John's</t>
+  </si>
+  <si>
+    <t>Toronto Port Authority | Administration portuaire de Toronto</t>
+  </si>
+  <si>
+    <t>Transportation Safety Board of Canada | Bureau de la sécurité des transports du Canada</t>
   </si>
   <si>
     <t>atip-aiprp@cdev.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@agr.gc.ca</t>
-  </si>
-  <si>
-    <t>aadnc.atiprequest-aiprpdemande.aandc@canada.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@acoa-apeca.gc.ca</t>
-  </si>
-  <si>
     <t>igaudreault@aecl.ca</t>
-  </si>
-  <si>
-    <t>bbradley@atlanticpilotage.com</t>
-  </si>
-  <si>
-    <t>atip.coordinator@asiapacific.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@tribunal.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@bankofcanada.ca</t>
-  </si>
-  <si>
-    <t>sgustin@bctreaty.ca</t>
   </si>
   <si>
     <t>atip-aiprp@bdc.ca</t>
@@ -1112,34 +1097,64 @@
     <t>atip-aiprp@cannor.gc.ca</t>
   </si>
   <si>
+    <t>Peter.Hull@cbc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
+  </si>
+  <si>
+    <t>ATIP-CFIA-AIPRP@inspection.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@grainscanada.gc.ca</t>
+  </si>
+  <si>
+    <t>atip.aiprp@chrc-ccdp.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@college-ic.ca</t>
+  </si>
+  <si>
+    <t>tsaunders@cnloer.ca</t>
+  </si>
+  <si>
+    <t>adiaz@cpata-cabamc.ca</t>
+  </si>
+  <si>
+    <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
+  </si>
+  <si>
+    <t>ATIP-AIPRP@forces.gc.ca</t>
+  </si>
+  <si>
+    <t>ecatip-ecaiprp@ec.gc.ca</t>
+  </si>
+  <si>
     <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
   </si>
   <si>
-    <t>atip@catsa.gc.ca</t>
+    <t>atip@fntc.ca</t>
   </si>
   <si>
-    <t>atip.aiprp@ccc.ca</t>
+    <t>atip-aiprp@sr-nr.gc.ca</t>
   </si>
   <si>
-    <t>priscilla.revolus@cdc-ccl.gc.ca</t>
+    <t>atip-aiprp@hfr-tgf.ca</t>
   </si>
   <si>
-    <t>ATIP.AIPRP@cfmws.com</t>
+    <t>atip-aiprp@iaac-aeic.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@cnsc-ccsn.gc.ca</t>
+    <t>atip-aiprp@ma.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@cse-cst.gc.ca</t>
+    <t>mgerc.atip-aiprp.ceegm@mgerc-ceegm.gc.ca</t>
   </si>
   <si>
-    <t>atipaiprp@csps-efpc.gc.ca</t>
+    <t>snorrish@wlwb.ca</t>
   </si>
   <si>
-    <t>mpoirier@glpa-apgl.com</t>
-  </si>
-  <si>
-    <t>PortalSupport-Soutienportail@tbs-sct.gc.ca</t>
+    <t>jean-frederic.boulais@oci-bec.gc.ca</t>
   </si>
   <si>
     <t>atip-aiprp@ocl-cal.gc.ca</t>
@@ -1148,19 +1163,28 @@
     <t>atip-aiprp@priv.gc.ca</t>
   </si>
   <si>
-    <t>molson@papa-appa.ca</t>
+    <t>access.informal-demandes.informelles@phac-aspc.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@PBC-CLCC.GC.CA</t>
+    <t>ATIP-AIPRP@pco-bcp.gc.ca</t>
   </si>
   <si>
-    <t>info@federalbridge.ca</t>
+    <t>Brodie.larocque@polar-polaire.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@sr-nr.gc.ca</t>
+    <t>accesstoinformation@rupertport.com</t>
   </si>
   <si>
-    <t>apoudrier@portsaguenay.ca</t>
+    <t>info@investpsp.ca</t>
+  </si>
+  <si>
+    <t>shanrahan@sjpa-apsj.com</t>
+  </si>
+  <si>
+    <t>DEl-Jawhary@portstoronto.com</t>
+  </si>
+  <si>
+    <t>AIPRP-ATIP@bst-tsb.gc.ca</t>
   </si>
   <si>
     <t>2025-09-09</t>
@@ -1169,37 +1193,43 @@
     <t>2016-09-23</t>
   </si>
   <si>
+    <t>2021-01-09</t>
+  </si>
+  <si>
+    <t>2023-03-28</t>
+  </si>
+  <si>
+    <t>2023-09-16</t>
+  </si>
+  <si>
     <t>2018-08-21</t>
   </si>
   <si>
-    <t>2019-12-12</t>
+    <t>2023-12-01</t>
   </si>
   <si>
-    <t>2021-01-09</t>
+    <t>2020-01-31</t>
   </si>
   <si>
-    <t>2019-07-13</t>
-  </si>
-  <si>
-    <t>2024-08-17</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
+    <t>2016-12-14</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>3</t>
+    <t>NA</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>admin@cpata-cabamc.ca</t>
   </si>
   <si>
     <t>ati
@@ -2056,292 +2086,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -2789,7 +2819,7 @@
         <v>77</v>
       </c>
       <c r="AQ3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="2">
         <v>2</v>
@@ -2921,7 +2951,7 @@
         <v>2076</v>
       </c>
       <c r="CI3" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ3" s="2">
         <v>41</v>
@@ -2957,7 +2987,7 @@
         <v>46759</v>
       </c>
       <c r="CU3" s="1">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="CV3" s="1">
         <v>132</v>
@@ -2998,7 +3028,7 @@
         <v>7059</v>
       </c>
       <c r="K4" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2">
         <v>119</v>
@@ -3082,10 +3112,10 @@
         <v>190</v>
       </c>
       <c r="AM4" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="2">
         <v>8</v>
@@ -3226,10 +3256,10 @@
         <v>2175</v>
       </c>
       <c r="CI4" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CJ4" s="2">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="CK4" s="2">
         <v>87</v>
@@ -3262,10 +3292,10 @@
         <v>43183</v>
       </c>
       <c r="CU4" s="1">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="CV4" s="1">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="CW4" s="1">
         <v>917</v>
@@ -3279,7 +3309,7 @@
         <v>238</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>5</v>
@@ -3303,7 +3333,7 @@
         <v>1205</v>
       </c>
       <c r="K5" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>42</v>
@@ -3567,7 +3597,7 @@
         <v>38716</v>
       </c>
       <c r="CU5" s="1">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="CV5" s="1">
         <v>61</v>
@@ -4499,7 +4529,7 @@
         <v>119</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -4619,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="AQ9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" s="2">
         <v>2</v>
@@ -4739,7 +4769,7 @@
         <v>4</v>
       </c>
       <c r="CE9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF9" s="2">
         <v>1</v>
@@ -4751,7 +4781,7 @@
         <v>495</v>
       </c>
       <c r="CI9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CJ9" s="2">
         <v>5</v>
@@ -4787,7 +4817,7 @@
         <v>2878</v>
       </c>
       <c r="CU9" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV9" s="1">
         <v>24</v>
@@ -6368,7 +6398,7 @@
         <v>49</v>
       </c>
       <c r="P15" s="2">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="Q15" s="2">
         <v>204</v>
@@ -6437,7 +6467,7 @@
         <v>122</v>
       </c>
       <c r="AM15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="2">
         <v>1</v>
@@ -6581,7 +6611,7 @@
         <v>378</v>
       </c>
       <c r="CI15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CJ15" s="2">
         <v>17</v>
@@ -6617,10 +6647,10 @@
         <v>3470</v>
       </c>
       <c r="CU15" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="CV15" s="1">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="CW15" s="1">
         <v>235</v>
@@ -6757,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="AR16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS16" s="2">
         <v>4</v>
@@ -6889,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="CJ16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK16" s="2">
         <v>4</v>
@@ -6901,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="CN16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO16" s="2">
         <v>2</v>
@@ -6925,7 +6955,7 @@
         <v>9</v>
       </c>
       <c r="CV16" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CW16" s="1">
         <v>82</v>
@@ -7854,10 +7884,10 @@
         <v>5114</v>
       </c>
       <c r="C20" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2">
         <v>169</v>
@@ -7881,7 +7911,7 @@
         <v>9</v>
       </c>
       <c r="L20" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M20" s="2">
         <v>41</v>
@@ -8106,7 +8136,7 @@
         <v>1078</v>
       </c>
       <c r="CI20" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CJ20" s="2">
         <v>21</v>
@@ -8142,10 +8172,10 @@
         <v>20740</v>
       </c>
       <c r="CU20" s="1">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="CV20" s="1">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="CW20" s="1">
         <v>859</v>
@@ -10297,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2">
         <v>6</v>
@@ -10306,7 +10336,7 @@
         <v>32</v>
       </c>
       <c r="G28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>2</v>
@@ -10318,7 +10348,7 @@
         <v>965</v>
       </c>
       <c r="K28" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2">
         <v>21</v>
@@ -10402,7 +10432,7 @@
         <v>784</v>
       </c>
       <c r="AM28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="2">
         <v>1</v>
@@ -10414,7 +10444,7 @@
         <v>70</v>
       </c>
       <c r="AQ28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR28" s="2">
         <v>2</v>
@@ -10546,7 +10576,7 @@
         <v>3015</v>
       </c>
       <c r="CI28" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CJ28" s="2">
         <v>6</v>
@@ -10582,10 +10612,10 @@
         <v>24094</v>
       </c>
       <c r="CU28" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="CV28" s="1">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="CW28" s="1">
         <v>299</v>
@@ -11464,7 +11494,7 @@
         <v>5</v>
       </c>
       <c r="CJ31" s="2">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="CK31" s="2">
         <v>182</v>
@@ -11500,7 +11530,7 @@
         <v>38</v>
       </c>
       <c r="CV31" s="1">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="CW31" s="1">
         <v>396</v>
@@ -11634,7 +11664,7 @@
         <v>46</v>
       </c>
       <c r="AQ32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR32" s="2">
         <v>1</v>
@@ -11766,7 +11796,7 @@
         <v>471</v>
       </c>
       <c r="CI32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ32" s="2">
         <v>3</v>
@@ -11802,7 +11832,7 @@
         <v>11165</v>
       </c>
       <c r="CU32" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CV32" s="1">
         <v>100</v>
@@ -12151,7 +12181,7 @@
         <v>7</v>
       </c>
       <c r="L34" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M34" s="2">
         <v>41</v>
@@ -12415,7 +12445,7 @@
         <v>32</v>
       </c>
       <c r="CV34" s="1">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="CW34" s="1">
         <v>117</v>
@@ -13344,7 +13374,7 @@
         <v>240</v>
       </c>
       <c r="C38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2">
         <v>5</v>
@@ -13368,7 +13398,7 @@
         <v>394</v>
       </c>
       <c r="K38" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>15</v>
@@ -13632,7 +13662,7 @@
         <v>1957</v>
       </c>
       <c r="CU38" s="1">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="CV38" s="1">
         <v>24</v>
@@ -13649,7 +13679,7 @@
         <v>113</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2">
         <v>3</v>
@@ -13937,7 +13967,7 @@
         <v>620</v>
       </c>
       <c r="CU39" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV39" s="1">
         <v>52</v>
@@ -13978,10 +14008,10 @@
         <v>4215</v>
       </c>
       <c r="K40" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="M40" s="2">
         <v>217</v>
@@ -14206,10 +14236,10 @@
         <v>2367</v>
       </c>
       <c r="CI40" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ40" s="2">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="CK40" s="2">
         <v>65</v>
@@ -14242,10 +14272,10 @@
         <v>53597</v>
       </c>
       <c r="CU40" s="1">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="CV40" s="1">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="CW40" s="1">
         <v>1400</v>
@@ -15285,7 +15315,7 @@
         <v>0</v>
       </c>
       <c r="AN44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO44" s="2">
         <v>8</v>
@@ -15465,7 +15495,7 @@
         <v>1028</v>
       </c>
       <c r="CV44" s="1">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="CW44" s="1">
         <v>3032</v>
@@ -19086,7 +19116,7 @@
         <v>562</v>
       </c>
       <c r="CI56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ56" s="2">
         <v>13</v>
@@ -19122,7 +19152,7 @@
         <v>7812</v>
       </c>
       <c r="CU56" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV56" s="1">
         <v>42</v>
@@ -20383,7 +20413,7 @@
         <v>2000</v>
       </c>
       <c r="K61" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2">
         <v>21</v>
@@ -20554,7 +20584,7 @@
         <v>0</v>
       </c>
       <c r="BP61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ61" s="2">
         <v>1</v>
@@ -20647,10 +20677,10 @@
         <v>65868</v>
       </c>
       <c r="CU61" s="1">
-        <v>-51</v>
+        <v>-58</v>
       </c>
       <c r="CV61" s="1">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="CW61" s="1">
         <v>722</v>
@@ -21666,7 +21696,7 @@
         <v>0</v>
       </c>
       <c r="AF65" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG65" s="2">
         <v>20</v>
@@ -21870,7 +21900,7 @@
         <v>30</v>
       </c>
       <c r="CV65" s="1">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="CW65" s="1">
         <v>3489</v>
@@ -23104,7 +23134,7 @@
         <v>324</v>
       </c>
       <c r="C70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" s="2">
         <v>1</v>
@@ -23392,7 +23422,7 @@
         <v>2272</v>
       </c>
       <c r="CU70" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV70" s="1">
         <v>33</v>
@@ -24327,7 +24357,7 @@
         <v>70</v>
       </c>
       <c r="D74" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="E74" s="2">
         <v>232</v>
@@ -24432,7 +24462,7 @@
         <v>36308</v>
       </c>
       <c r="AM74" s="2">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="AN74" s="2">
         <v>89</v>
@@ -24459,7 +24489,7 @@
         <v>-12</v>
       </c>
       <c r="AV74" s="2">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AW74" s="2">
         <v>-8</v>
@@ -24519,7 +24549,7 @@
         <v>0</v>
       </c>
       <c r="BP74" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BQ74" s="2">
         <v>10</v>
@@ -24576,7 +24606,7 @@
         <v>16239</v>
       </c>
       <c r="CI74" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="CJ74" s="2">
         <v>145</v>
@@ -24612,10 +24642,10 @@
         <v>171863</v>
       </c>
       <c r="CU74" s="1">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="CV74" s="1">
-        <v>498</v>
+        <v>446</v>
       </c>
       <c r="CW74" s="1">
         <v>3798</v>
@@ -24958,10 +24988,10 @@
         <v>5857</v>
       </c>
       <c r="K76" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="M76" s="2">
         <v>329</v>
@@ -25054,7 +25084,7 @@
         <v>50</v>
       </c>
       <c r="AQ76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR76" s="2">
         <v>1</v>
@@ -25177,7 +25207,7 @@
         <v>0</v>
       </c>
       <c r="CF76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG76" s="2">
         <v>1</v>
@@ -25186,7 +25216,7 @@
         <v>2260</v>
       </c>
       <c r="CI76" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CJ76" s="2">
         <v>34</v>
@@ -25222,10 +25252,10 @@
         <v>151137</v>
       </c>
       <c r="CU76" s="1">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="CV76" s="1">
-        <v>295</v>
+        <v>232</v>
       </c>
       <c r="CW76" s="1">
         <v>3070</v>
@@ -25239,7 +25269,7 @@
         <v>10827</v>
       </c>
       <c r="C77" s="2">
-        <v>-31</v>
+        <v>-92</v>
       </c>
       <c r="D77" s="2">
         <v>3</v>
@@ -25347,10 +25377,10 @@
         <v>1921</v>
       </c>
       <c r="AM77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN77" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO77" s="2">
         <v>68</v>
@@ -25491,10 +25521,10 @@
         <v>7411</v>
       </c>
       <c r="CI77" s="2">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="CJ77" s="2">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="CK77" s="2">
         <v>542</v>
@@ -25527,10 +25557,10 @@
         <v>391015</v>
       </c>
       <c r="CU77" s="1">
-        <v>37</v>
+        <v>-33</v>
       </c>
       <c r="CV77" s="1">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="CW77" s="1">
         <v>20088</v>
@@ -25652,7 +25682,7 @@
         <v>99</v>
       </c>
       <c r="AM78" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AN78" s="2">
         <v>12</v>
@@ -25796,7 +25826,7 @@
         <v>158</v>
       </c>
       <c r="CI78" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CJ78" s="2">
         <v>18</v>
@@ -25832,7 +25862,7 @@
         <v>286</v>
       </c>
       <c r="CU78" s="1">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="CV78" s="1">
         <v>32</v>
@@ -25888,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="2">
         <v>1139</v>
@@ -25969,7 +25999,7 @@
         <v>36</v>
       </c>
       <c r="AQ79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR79" s="2">
         <v>1</v>
@@ -26101,7 +26131,7 @@
         <v>2061</v>
       </c>
       <c r="CI79" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="CJ79" s="2">
         <v>47</v>
@@ -26137,10 +26167,10 @@
         <v>90732</v>
       </c>
       <c r="CU79" s="1">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="CV79" s="1">
-        <v>594</v>
+        <v>203</v>
       </c>
       <c r="CW79" s="1">
         <v>1569</v>
@@ -27093,7 +27123,7 @@
         <v>8700</v>
       </c>
       <c r="K83" s="2">
-        <v>62</v>
+        <v>-10</v>
       </c>
       <c r="L83" s="2">
         <v>123</v>
@@ -27357,7 +27387,7 @@
         <v>423944</v>
       </c>
       <c r="CU83" s="1">
-        <v>42</v>
+        <v>-30</v>
       </c>
       <c r="CV83" s="1">
         <v>266</v>
@@ -28606,7 +28636,7 @@
         <v>19</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2">
         <v>1</v>
@@ -28618,7 +28648,7 @@
         <v>817</v>
       </c>
       <c r="K88" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2">
         <v>19</v>
@@ -28681,7 +28711,7 @@
         <v>0</v>
       </c>
       <c r="AF88" s="2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="AG88" s="2">
         <v>74</v>
@@ -28882,10 +28912,10 @@
         <v>9593</v>
       </c>
       <c r="CU88" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="CV88" s="1">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="CW88" s="1">
         <v>165</v>
@@ -29512,7 +29542,7 @@
         <v>65</v>
       </c>
       <c r="D91" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="E91" s="2">
         <v>197</v>
@@ -29533,7 +29563,7 @@
         <v>5470</v>
       </c>
       <c r="K91" s="2">
-        <v>52</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="2">
         <v>106</v>
@@ -29617,10 +29647,10 @@
         <v>768</v>
       </c>
       <c r="AM91" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN91" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO91" s="2">
         <v>12</v>
@@ -29761,10 +29791,10 @@
         <v>7789</v>
       </c>
       <c r="CI91" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CJ91" s="2">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="CK91" s="2">
         <v>163</v>
@@ -29797,10 +29827,10 @@
         <v>26027</v>
       </c>
       <c r="CU91" s="1">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="CV91" s="1">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="CW91" s="1">
         <v>763</v>
@@ -29925,7 +29955,7 @@
         <v>0</v>
       </c>
       <c r="AN92" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO92" s="2">
         <v>5</v>
@@ -30066,10 +30096,10 @@
         <v>685</v>
       </c>
       <c r="CI92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ92" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CK92" s="2">
         <v>16</v>
@@ -30102,10 +30132,10 @@
         <v>3796</v>
       </c>
       <c r="CU92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV92" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW92" s="1">
         <v>84</v>
@@ -30158,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="2">
         <v>44</v>
@@ -30410,7 +30440,7 @@
         <v>3</v>
       </c>
       <c r="CV93" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="CW93" s="1">
         <v>64</v>
@@ -32374,7 +32404,7 @@
         <v>1</v>
       </c>
       <c r="AQ100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR100" s="2">
         <v>1</v>
@@ -32518,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="CM100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN100" s="2">
         <v>1</v>
@@ -32542,7 +32572,7 @@
         <v>163</v>
       </c>
       <c r="CU100" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CV100" s="1">
         <v>10</v>
@@ -32864,7 +32894,7 @@
         <v>17591</v>
       </c>
       <c r="C102" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2">
         <v>210</v>
@@ -32996,7 +33026,7 @@
         <v>53</v>
       </c>
       <c r="AU102" s="2">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="AV102" s="2">
         <v>-6</v>
@@ -33152,7 +33182,7 @@
         <v>43220</v>
       </c>
       <c r="CU102" s="1">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="CV102" s="1">
         <v>386</v>
@@ -33489,7 +33519,7 @@
         <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" s="2">
         <v>6</v>
@@ -33765,7 +33795,7 @@
         <v>2</v>
       </c>
       <c r="CV104" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CW104" s="1">
         <v>6</v>
@@ -33803,7 +33833,7 @@
         <v>1026</v>
       </c>
       <c r="K105" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L105" s="2">
         <v>42</v>
@@ -33971,7 +34001,7 @@
         <v>27</v>
       </c>
       <c r="BO105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP105" s="2">
         <v>1</v>
@@ -34031,10 +34061,10 @@
         <v>281</v>
       </c>
       <c r="CI105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ105" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CK105" s="2">
         <v>23</v>
@@ -34067,10 +34097,10 @@
         <v>8047</v>
       </c>
       <c r="CU105" s="1">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="CV105" s="1">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="CW105" s="1">
         <v>543</v>
@@ -34108,7 +34138,7 @@
         <v>10918</v>
       </c>
       <c r="K106" s="2">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2">
         <v>256</v>
@@ -34123,7 +34153,7 @@
         <v>201</v>
       </c>
       <c r="P106" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q106" s="2">
         <v>690</v>
@@ -34204,7 +34234,7 @@
         <v>9</v>
       </c>
       <c r="AQ106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR106" s="2">
         <v>1</v>
@@ -34372,10 +34402,10 @@
         <v>92989</v>
       </c>
       <c r="CU106" s="1">
-        <v>331</v>
+        <v>204</v>
       </c>
       <c r="CV106" s="1">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="CW106" s="1">
         <v>2214</v>
@@ -34946,7 +34976,7 @@
         <v>278</v>
       </c>
       <c r="CI108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ108" s="2">
         <v>7</v>
@@ -34982,7 +35012,7 @@
         <v>943</v>
       </c>
       <c r="CU108" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CV108" s="1">
         <v>16</v>
@@ -35328,7 +35358,7 @@
         <v>4995</v>
       </c>
       <c r="K110" s="2">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2">
         <v>170</v>
@@ -35412,7 +35442,7 @@
         <v>154</v>
       </c>
       <c r="AM110" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN110" s="2">
         <v>9</v>
@@ -35556,7 +35586,7 @@
         <v>1897</v>
       </c>
       <c r="CI110" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ110" s="2">
         <v>41</v>
@@ -35592,7 +35622,7 @@
         <v>13489</v>
       </c>
       <c r="CU110" s="1">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="CV110" s="1">
         <v>307</v>
@@ -35717,7 +35747,7 @@
         <v>121</v>
       </c>
       <c r="AM111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN111" s="2">
         <v>2</v>
@@ -35729,7 +35759,7 @@
         <v>46</v>
       </c>
       <c r="AQ111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR111" s="2">
         <v>2</v>
@@ -35861,7 +35891,7 @@
         <v>488</v>
       </c>
       <c r="CI111" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CJ111" s="2">
         <v>12</v>
@@ -35897,7 +35927,7 @@
         <v>785</v>
       </c>
       <c r="CU111" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CV111" s="1">
         <v>19</v>
@@ -36246,7 +36276,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="2">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="M113" s="2">
         <v>302</v>
@@ -36327,7 +36357,7 @@
         <v>107</v>
       </c>
       <c r="AM113" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN113" s="2">
         <v>2</v>
@@ -36471,7 +36501,7 @@
         <v>1493</v>
       </c>
       <c r="CI113" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CJ113" s="2">
         <v>47</v>
@@ -36507,10 +36537,10 @@
         <v>175155</v>
       </c>
       <c r="CU113" s="1">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="CV113" s="1">
-        <v>1506</v>
+        <v>1446</v>
       </c>
       <c r="CW113" s="1">
         <v>2200</v>
@@ -37158,7 +37188,7 @@
         <v>4940</v>
       </c>
       <c r="K116" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2">
         <v>86</v>
@@ -37242,7 +37272,7 @@
         <v>369</v>
       </c>
       <c r="AM116" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN116" s="2">
         <v>3</v>
@@ -37386,7 +37416,7 @@
         <v>1228</v>
       </c>
       <c r="CI116" s="2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CJ116" s="2">
         <v>39</v>
@@ -37422,7 +37452,7 @@
         <v>21994</v>
       </c>
       <c r="CU116" s="1">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="CV116" s="1">
         <v>341</v>
@@ -37586,7 +37616,7 @@
         <v>-1</v>
       </c>
       <c r="AZ117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA117" s="2">
         <v>1</v>
@@ -37730,7 +37760,7 @@
         <v>200</v>
       </c>
       <c r="CV117" s="1">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="CW117" s="1">
         <v>1187</v>
@@ -43016,7 +43046,7 @@
         <v>51</v>
       </c>
       <c r="AF135" s="2">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="AG135" s="2">
         <v>213</v>
@@ -43037,7 +43067,7 @@
         <v>841</v>
       </c>
       <c r="AM135" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN135" s="2">
         <v>4</v>
@@ -43181,7 +43211,7 @@
         <v>3179</v>
       </c>
       <c r="CI135" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CJ135" s="2">
         <v>62</v>
@@ -43217,10 +43247,10 @@
         <v>62811</v>
       </c>
       <c r="CU135" s="1">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="CV135" s="1">
-        <v>469</v>
+        <v>323</v>
       </c>
       <c r="CW135" s="1">
         <v>1941</v>
@@ -44454,7 +44484,7 @@
         <v>120</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140" s="2">
         <v>4</v>
@@ -44706,7 +44736,7 @@
         <v>146</v>
       </c>
       <c r="CI140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ140" s="2">
         <v>1</v>
@@ -44742,7 +44772,7 @@
         <v>574</v>
       </c>
       <c r="CU140" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CV140" s="1">
         <v>10</v>
@@ -44771,7 +44801,7 @@
         <v>50</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="2">
         <v>1</v>
@@ -45047,7 +45077,7 @@
         <v>577</v>
       </c>
       <c r="CU141" s="1">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="CV141" s="1">
         <v>-3</v>
@@ -45979,7 +46009,7 @@
         <v>665</v>
       </c>
       <c r="C145" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D145" s="2">
         <v>11</v>
@@ -46099,7 +46129,7 @@
         <v>79</v>
       </c>
       <c r="AQ145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR145" s="2">
         <v>2</v>
@@ -46126,7 +46156,7 @@
         <v>-7</v>
       </c>
       <c r="AZ145" s="2">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="BA145" s="2">
         <v>1</v>
@@ -46243,7 +46273,7 @@
         <v>41</v>
       </c>
       <c r="CM145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN145" s="2">
         <v>1</v>
@@ -46267,10 +46297,10 @@
         <v>2476</v>
       </c>
       <c r="CU145" s="1">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="CV145" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW145" s="1">
         <v>110</v>
@@ -47929,7 +47959,7 @@
         <v>64</v>
       </c>
       <c r="AQ151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR151" s="2">
         <v>2</v>
@@ -48061,7 +48091,7 @@
         <v>144</v>
       </c>
       <c r="CI151" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ151" s="2">
         <v>3</v>
@@ -48073,7 +48103,7 @@
         <v>29</v>
       </c>
       <c r="CM151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN151" s="2">
         <v>1</v>
@@ -48097,7 +48127,7 @@
         <v>460</v>
       </c>
       <c r="CU151" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CV151" s="1">
         <v>6</v>
@@ -49068,7 +49098,7 @@
         <v>0</v>
       </c>
       <c r="P155" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q155" s="2">
         <v>18</v>
@@ -49149,10 +49179,10 @@
         <v>35</v>
       </c>
       <c r="AQ155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR155" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS155" s="2">
         <v>5</v>
@@ -49281,10 +49311,10 @@
         <v>413</v>
       </c>
       <c r="CI155" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CJ155" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CK155" s="2">
         <v>18</v>
@@ -49317,10 +49347,10 @@
         <v>2670</v>
       </c>
       <c r="CU155" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CV155" s="1">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="CW155" s="1">
         <v>79</v>
@@ -49337,7 +49367,7 @@
         <v>35</v>
       </c>
       <c r="D156" s="2">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E156" s="2">
         <v>77</v>
@@ -49625,7 +49655,7 @@
         <v>44</v>
       </c>
       <c r="CV156" s="1">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="CW156" s="1">
         <v>2232</v>
@@ -49639,7 +49669,7 @@
         <v>5004</v>
       </c>
       <c r="C157" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D157" s="2">
         <v>63</v>
@@ -49663,7 +49693,7 @@
         <v>3516</v>
       </c>
       <c r="K157" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L157" s="2">
         <v>151</v>
@@ -49678,7 +49708,7 @@
         <v>0</v>
       </c>
       <c r="P157" s="2">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="2">
         <v>274</v>
@@ -49927,10 +49957,10 @@
         <v>166428</v>
       </c>
       <c r="CU157" s="1">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="CV157" s="1">
-        <v>458</v>
+        <v>287</v>
       </c>
       <c r="CW157" s="1">
         <v>5535</v>
@@ -49944,7 +49974,7 @@
         <v>8297</v>
       </c>
       <c r="C158" s="2">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D158" s="2">
         <v>136</v>
@@ -49968,7 +49998,7 @@
         <v>7116</v>
       </c>
       <c r="K158" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2">
         <v>104</v>
@@ -50052,7 +50082,7 @@
         <v>530</v>
       </c>
       <c r="AM158" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN158" s="2">
         <v>18</v>
@@ -50196,7 +50226,7 @@
         <v>6072</v>
       </c>
       <c r="CI158" s="2">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="CJ158" s="2">
         <v>270</v>
@@ -50232,7 +50262,7 @@
         <v>25708</v>
       </c>
       <c r="CU158" s="1">
-        <v>246</v>
+        <v>8</v>
       </c>
       <c r="CV158" s="1">
         <v>592</v>
@@ -50859,7 +50889,7 @@
         <v>2092</v>
       </c>
       <c r="C161" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D161" s="2">
         <v>24</v>
@@ -50883,10 +50913,10 @@
         <v>3333</v>
       </c>
       <c r="K161" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="M161" s="2">
         <v>123</v>
@@ -51147,10 +51177,10 @@
         <v>22417</v>
       </c>
       <c r="CU161" s="1">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="CV161" s="1">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="CW161" s="1">
         <v>1076</v>
@@ -51813,7 +51843,7 @@
         <v>6</v>
       </c>
       <c r="P164" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q164" s="2">
         <v>14</v>
@@ -52065,7 +52095,7 @@
         <v>11</v>
       </c>
       <c r="CV164" s="1">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="CW164" s="1">
         <v>181</v>
@@ -53628,7 +53658,7 @@
         <v>6413</v>
       </c>
       <c r="K170" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L170" s="2">
         <v>145</v>
@@ -53712,7 +53742,7 @@
         <v>230</v>
       </c>
       <c r="AM170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN170" s="2">
         <v>2</v>
@@ -53799,7 +53829,7 @@
         <v>0</v>
       </c>
       <c r="BP170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ170" s="2">
         <v>1</v>
@@ -53856,7 +53886,7 @@
         <v>1492</v>
       </c>
       <c r="CI170" s="2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="CJ170" s="2">
         <v>57</v>
@@ -53892,10 +53922,10 @@
         <v>19654</v>
       </c>
       <c r="CU170" s="1">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="CV170" s="1">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="CW170" s="1">
         <v>816</v>
@@ -54020,7 +54050,7 @@
         <v>0</v>
       </c>
       <c r="AN171" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO171" s="2">
         <v>9</v>
@@ -54161,10 +54191,10 @@
         <v>826</v>
       </c>
       <c r="CI171" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ171" s="2">
         <v>6</v>
-      </c>
-      <c r="CJ171" s="2">
-        <v>12</v>
       </c>
       <c r="CK171" s="2">
         <v>14</v>
@@ -54197,10 +54227,10 @@
         <v>5854</v>
       </c>
       <c r="CU171" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CV171" s="1">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="CW171" s="1">
         <v>106</v>
@@ -54827,7 +54857,7 @@
         <v>0</v>
       </c>
       <c r="D174" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" s="2">
         <v>3</v>
@@ -54839,7 +54869,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174" s="2">
         <v>3</v>
@@ -54947,7 +54977,7 @@
         <v>0</v>
       </c>
       <c r="AR174" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS174" s="2">
         <v>3</v>
@@ -55091,7 +55121,7 @@
         <v>0</v>
       </c>
       <c r="CN174" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO174" s="2">
         <v>4</v>
@@ -55115,7 +55145,7 @@
         <v>0</v>
       </c>
       <c r="CV174" s="1">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="CW174" s="1">
         <v>33</v>
@@ -55542,7 +55572,7 @@
         <v>400</v>
       </c>
       <c r="AM176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN176" s="2">
         <v>6</v>
@@ -55686,7 +55716,7 @@
         <v>759</v>
       </c>
       <c r="CI176" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CJ176" s="2">
         <v>33</v>
@@ -55722,7 +55752,7 @@
         <v>1327</v>
       </c>
       <c r="CU176" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="CV176" s="1">
         <v>42</v>
@@ -56654,7 +56684,7 @@
         <v>8175</v>
       </c>
       <c r="C180" s="2">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D180" s="2">
         <v>134</v>
@@ -56942,7 +56972,7 @@
         <v>51320</v>
       </c>
       <c r="CU180" s="1">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="CV180" s="1">
         <v>237</v>
@@ -57764,7 +57794,7 @@
         <v>0</v>
       </c>
       <c r="BP183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ183" s="2">
         <v>1</v>
@@ -57860,7 +57890,7 @@
         <v>0</v>
       </c>
       <c r="CV183" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW183" s="1">
         <v>1</v>
@@ -58801,10 +58831,10 @@
         <v>74</v>
       </c>
       <c r="G187" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187" s="2">
         <v>5</v>
@@ -59077,10 +59107,10 @@
         <v>82</v>
       </c>
       <c r="CU187" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV187" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CW187" s="1">
         <v>5</v>
@@ -60948,7 +60978,7 @@
         <v>974</v>
       </c>
       <c r="K194" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L194" s="2">
         <v>33</v>
@@ -61212,7 +61242,7 @@
         <v>32901</v>
       </c>
       <c r="CU194" s="1">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="CV194" s="1">
         <v>100</v>
@@ -61642,7 +61672,7 @@
         <v>106</v>
       </c>
       <c r="AM196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN196" s="2">
         <v>2</v>
@@ -61786,7 +61816,7 @@
         <v>412</v>
       </c>
       <c r="CI196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ196" s="2">
         <v>4</v>
@@ -61822,7 +61852,7 @@
         <v>5490</v>
       </c>
       <c r="CU196" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CV196" s="1">
         <v>18</v>
@@ -62778,7 +62808,7 @@
         <v>2058</v>
       </c>
       <c r="K200" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L200" s="2">
         <v>32</v>
@@ -62889,7 +62919,7 @@
         <v>-9</v>
       </c>
       <c r="AV200" s="2">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="AW200" s="2">
         <v>-4</v>
@@ -63042,10 +63072,10 @@
         <v>16380</v>
       </c>
       <c r="CU200" s="1">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="CV200" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="CW200" s="1">
         <v>453</v>
@@ -63083,7 +63113,7 @@
         <v>3568</v>
       </c>
       <c r="K201" s="2">
-        <v>28</v>
+        <v>-1</v>
       </c>
       <c r="L201" s="2">
         <v>63</v>
@@ -63347,7 +63377,7 @@
         <v>88300</v>
       </c>
       <c r="CU201" s="1">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="CV201" s="1">
         <v>283</v>
@@ -64889,7 +64919,7 @@
         <v>1397</v>
       </c>
       <c r="C207" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D207" s="2">
         <v>34</v>
@@ -64913,7 +64943,7 @@
         <v>623</v>
       </c>
       <c r="K207" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L207" s="2">
         <v>12</v>
@@ -65009,7 +65039,7 @@
         <v>67</v>
       </c>
       <c r="AQ207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR207" s="2">
         <v>2</v>
@@ -65141,7 +65171,7 @@
         <v>3212</v>
       </c>
       <c r="CI207" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CJ207" s="2">
         <v>27</v>
@@ -65153,7 +65183,7 @@
         <v>14</v>
       </c>
       <c r="CM207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN207" s="2">
         <v>1</v>
@@ -65177,7 +65207,7 @@
         <v>14198</v>
       </c>
       <c r="CU207" s="1">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="CV207" s="1">
         <v>186</v>
@@ -66133,7 +66163,7 @@
         <v>1277</v>
       </c>
       <c r="K211" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L211" s="2">
         <v>31</v>
@@ -66397,7 +66427,7 @@
         <v>6315</v>
       </c>
       <c r="CU211" s="1">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="CV211" s="1">
         <v>93</v>
@@ -67328,7 +67358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -67362,522 +67392,525 @@
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F2" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F3" t="s">
         <v>400</v>
       </c>
-      <c r="E3" t="s">
-        <v>383</v>
-      </c>
-      <c r="F3" t="s">
-        <v>391</v>
+      <c r="G3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D4">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F4" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F5" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
-      <c r="C6" t="s">
-        <v>357</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F6" t="s">
-        <v>393</v>
-      </c>
-      <c r="G6" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F7" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F9" t="s">
-        <v>392</v>
+        <v>402</v>
+      </c>
+      <c r="G9" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F10" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F11" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
       <c r="C12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F12" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="F13" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
+      <c r="C14" t="s">
+        <v>366</v>
+      </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F14" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F15" t="s">
-        <v>390</v>
+        <v>402</v>
+      </c>
+      <c r="G15" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F16" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="E17" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F17" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1216</v>
       </c>
       <c r="E18" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F18" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="E19" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F19" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F20" t="s">
-        <v>394</v>
-      </c>
-      <c r="G20" t="s">
-        <v>353</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F21" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F22" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D23">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F23" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s">
         <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D24">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F24" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
         <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F25" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s">
         <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F26" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F27" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>240</v>
       </c>
@@ -67885,19 +67918,19 @@
         <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D28">
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F28" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -67905,116 +67938,179 @@
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D29">
         <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F29" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s">
         <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="E30" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F30" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s">
         <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="F31" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s">
         <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F32" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s">
         <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F33" t="s">
-        <v>394</v>
+        <v>402</v>
+      </c>
+      <c r="G33" t="s">
+        <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s">
         <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F34" t="s">
-        <v>394</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>286</v>
+      </c>
+      <c r="B35" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35" t="s">
+        <v>387</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>391</v>
+      </c>
+      <c r="F35" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>304</v>
+      </c>
+      <c r="B36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C36" t="s">
+        <v>388</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>391</v>
+      </c>
+      <c r="F36" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>305</v>
+      </c>
+      <c r="B37" t="s">
+        <v>355</v>
+      </c>
+      <c r="C37" t="s">
+        <v>389</v>
+      </c>
+      <c r="D37">
+        <v>446</v>
+      </c>
+      <c r="E37" t="s">
+        <v>391</v>
+      </c>
+      <c r="F37" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/PD_CHANGES_RPT/PD_Activity.xlsx
+++ b/PD_CHANGES_RPT/PD_Activity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="461">
   <si>
     <t>ati_all</t>
   </si>
@@ -980,10 +980,16 @@
     <t>16342451 Canada Inc.  | 16342451 Canada Inc</t>
   </si>
   <si>
+    <t>Agriculture and Agri-Food Canada | Agriculture et Agroalimentaire Canada</t>
+  </si>
+  <si>
+    <t>Atlantic Canada Opportunities Agency | Agence de promotion économique du Canada atlantique</t>
+  </si>
+  <si>
     <t>Atomic Energy of Canada Limited | Énergie atomique du Canada, Limitée</t>
   </si>
   <si>
-    <t>Business Development Bank of Canada | Banque de développement du Canada</t>
+    <t>Belledune Port Authority | Administration portuaire de Belledune</t>
   </si>
   <si>
     <t>Canadian Northern Economic Development Agency | Agence canadienne de développement économique du Nord</t>
@@ -992,199 +998,109 @@
     <t>Courts Administration Service | Service administratif des tribunaux judiciaires</t>
   </si>
   <si>
-    <t>Canadian Broadcasting Company | Radio-Canada</t>
+    <t>Accessibility Standards Canada | Normes d’accessibilité Canada</t>
   </si>
   <si>
-    <t>Canada Border Services Agency | Agence des services frontaliers du Canada</t>
+    <t>Canada Council for the Arts | Conseil des arts du Canada</t>
   </si>
   <si>
     <t>Canada Enterprise Emergency Funding Corporation | La Corporation de financement d’urgence d’entreprises du Canada</t>
   </si>
   <si>
-    <t>Canadian Food Inspection Agency | Agence canadienne d'inspection des aliments</t>
-  </si>
-  <si>
-    <t>Canadian Grain Commission | Commission canadienne des grains</t>
-  </si>
-  <si>
-    <t>Canadian Human Rights Commission | Commission canadienne des droits de la personne</t>
-  </si>
-  <si>
-    <t>College of Immigration and Citizenship Consultants | Collège des Consultants en Immigration et en Citoyenneté</t>
-  </si>
-  <si>
-    <t>Canada-Newfoundland and Labrador Offshore Petroleum Board | Office Canada–Terre-Neuve-et Labrador des hydrocarbures extracôtiers</t>
-  </si>
-  <si>
     <t>College of Patent Agents and Trademark Agents | Collège des agents de brevets et des agents de marques de commerce</t>
   </si>
   <si>
-    <t>Canada Post | Postes Canada</t>
+    <t>Canadian Radio-television and Telecommunications Commission | Conseil de la radiodiffusion et des télécommunications canadiennes</t>
   </si>
   <si>
-    <t>National Defence | Défense nationale</t>
-  </si>
-  <si>
-    <t>Environment and Climate Change Canada | Environnement et Changement climatique Canada</t>
-  </si>
-  <si>
-    <t>Employment and Social Development Canada | Emploi et Développement social Canada</t>
+    <t>Destination Canada | Destination Canada</t>
   </si>
   <si>
     <t>First Nations Tax Commission | Commission de la fiscalité des premières nations</t>
   </si>
   <si>
-    <t>Office of the Administrator of the Fund for Railway Accidents Involving Designated Goods; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
+    <t>Health Canada | Santé Canada</t>
   </si>
   <si>
-    <t>VIA HFR - VIA TGF Inc. | VIA HFR - VIA TGF Inc.</t>
+    <t>Historic Sites and Monuments Board of Canada | Commission des lieux et monuments historiques du Canada</t>
   </si>
   <si>
-    <t>Impact Assessment Agency of Canada | Agence d'évaluation d'impact du Canada</t>
+    <t>The Joint Federal/Provincial Commission into the April 2020 Nova Scotia Mass Casualty | Commission fédérale-provinciale sur les événements d’avril 2020 en Nouvelle Écosse</t>
   </si>
   <si>
-    <t>Marine Atlantic Inc. | Marine Atlantique S.C.C.</t>
+    <t>Law Commission of Canada | Commission du droit du Canada</t>
   </si>
   <si>
-    <t>Military Grievances External Review Committee | Comité externe d’examen des griefs militaires</t>
+    <t>Office of the Veterans Ombudsman | Bureau de l'ombudsman des vétérans</t>
   </si>
   <si>
-    <t>Mackenzie Valley Land and Water Board | Office des terres et des eaux de la vallée du Mackenzie Valley</t>
+    <t>Office of the Administrator of the Ship-source Oil Pollution Fund; (operating under the name) Ship and Rail Compensation Canada | Bureau de l’administrateur de la Caisse d’indemnisation des dommages dus à la pollution par les hydrocarbures causée par les navires; (qui mène ses activités sous le nom de) Indemnisation Navire et Rail Canada</t>
   </si>
   <si>
-    <t>The Correctional Investigator Canada | L'Enquêteur correctionnel Canada</t>
+    <t>Social Sciences and Humanities Research Council of Canada | Conseil de recherches en sciences humaines du Canada</t>
   </si>
   <si>
-    <t>Office of the Commissioner of Lobbying of Canada | Commissariat au lobbying du Canada</t>
-  </si>
-  <si>
-    <t>Office of the Privacy Commissioner of Canada | Commissariat à la protection de la vie privée du Canada</t>
-  </si>
-  <si>
-    <t>Public Health Agency of Canada | Agence de la santé publique du Canada</t>
-  </si>
-  <si>
-    <t>President of the King’s Privy Council for Canada | Président du Conseil privé du Roi pour le Canada</t>
-  </si>
-  <si>
-    <t>Polar Knowledge Canada | Savoir polaire Canada</t>
-  </si>
-  <si>
-    <t>Prince Rupert Port Authority | L’Administration portuaire de Prince Rupert</t>
-  </si>
-  <si>
-    <t>Revera Inc. | Revera Inc.</t>
-  </si>
-  <si>
-    <t>St. John's Port Authority | Administration portuaire de St. John's</t>
-  </si>
-  <si>
-    <t>Toronto Port Authority | Administration portuaire de Toronto</t>
-  </si>
-  <si>
-    <t>Transportation Safety Board of Canada | Bureau de la sécurité des transports du Canada</t>
+    <t>Yukon Environmental and Socio-economic Assessment Board | Office d’évaluation environnementale et socio-économique du Yukon</t>
   </si>
   <si>
     <t>atip-aiprp@cdev.gc.ca</t>
   </si>
   <si>
+    <t>ATIP-AIPRP@agr.gc.ca</t>
+  </si>
+  <si>
+    <t>atip-aiprp@acoa-apeca.gc.ca</t>
+  </si>
+  <si>
     <t>igaudreault@aecl.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@bdc.ca</t>
+    <t>moffitt@portofbelledune.ca</t>
   </si>
   <si>
     <t>atip-aiprp@cannor.gc.ca</t>
   </si>
   <si>
-    <t>Peter.Hull@cbc.ca</t>
+    <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@cbsa-asfc.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-CFIA-AIPRP@inspection.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@grainscanada.gc.ca</t>
-  </si>
-  <si>
-    <t>atip.aiprp@chrc-ccdp.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@college-ic.ca</t>
-  </si>
-  <si>
-    <t>tsaunders@cnloer.ca</t>
+    <t>atip-aiprp@canadacouncil.ca</t>
   </si>
   <si>
     <t>adiaz@cpata-cabamc.ca</t>
   </si>
   <si>
-    <t>ATIP_AIPRP@canadapost.postescanada.ca</t>
+    <t>AIPRP-ATIP@crtc.gc.ca</t>
   </si>
   <si>
-    <t>ATIP-AIPRP@forces.gc.ca</t>
-  </si>
-  <si>
-    <t>ecatip-ecaiprp@ec.gc.ca</t>
-  </si>
-  <si>
-    <t>NC-COMM-ATIP-AIPRP-GD@hrsdc-rhdcc.gc.ca</t>
+    <t>atip-aiprp@destinationcanada.com</t>
   </si>
   <si>
     <t>atip@fntc.ca</t>
   </si>
   <si>
+    <t>access.informal-demandes.informelles@hc-sc.gc.ca</t>
+  </si>
+  <si>
+    <t>pc.clmhc-hsmbc.pc@canada.ca</t>
+  </si>
+  <si>
+    <t>PortalSupport-Soutienportail@tbs-sct.gc.ca</t>
+  </si>
+  <si>
+    <t>BMS-SGA@lcc-cdc.gc.ca</t>
+  </si>
+  <si>
+    <t>ovoatip-bovaiprp@ombudsman-veterans.gc.ca</t>
+  </si>
+  <si>
     <t>atip-aiprp@sr-nr.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@hfr-tgf.ca</t>
+    <t>ATIP-AIPRP@sshrc-crsh.gc.ca</t>
   </si>
   <si>
-    <t>atip-aiprp@iaac-aeic.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@ma.ca</t>
-  </si>
-  <si>
-    <t>mgerc.atip-aiprp.ceegm@mgerc-ceegm.gc.ca</t>
-  </si>
-  <si>
-    <t>snorrish@wlwb.ca</t>
-  </si>
-  <si>
-    <t>jean-frederic.boulais@oci-bec.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@ocl-cal.gc.ca</t>
-  </si>
-  <si>
-    <t>atip-aiprp@priv.gc.ca</t>
-  </si>
-  <si>
-    <t>access.informal-demandes.informelles@phac-aspc.gc.ca</t>
-  </si>
-  <si>
-    <t>ATIP-AIPRP@pco-bcp.gc.ca</t>
-  </si>
-  <si>
-    <t>Brodie.larocque@polar-polaire.gc.ca</t>
-  </si>
-  <si>
-    <t>accesstoinformation@rupertport.com</t>
-  </si>
-  <si>
-    <t>info@investpsp.ca</t>
-  </si>
-  <si>
-    <t>shanrahan@sjpa-apsj.com</t>
-  </si>
-  <si>
-    <t>DEl-Jawhary@portstoronto.com</t>
-  </si>
-  <si>
-    <t>AIPRP-ATIP@bst-tsb.gc.ca</t>
+    <t>atip@yesab.ca</t>
   </si>
   <si>
     <t>2025-09-09</t>
@@ -1193,43 +1109,43 @@
     <t>2016-09-23</t>
   </si>
   <si>
-    <t>2021-01-09</t>
+    <t>2023-09-16</t>
   </si>
   <si>
-    <t>2023-03-28</t>
+    <t>2019-12-12</t>
   </si>
   <si>
-    <t>2023-09-16</t>
+    <t>2021-01-09</t>
   </si>
   <si>
     <t>2018-08-21</t>
   </si>
   <si>
-    <t>2023-12-01</t>
+    <t>2021-03-25</t>
   </si>
   <si>
-    <t>2020-01-31</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
+    <t>2017-05-20</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>3</t>
+    <t>1</t>
   </si>
   <si>
     <t>1.1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>1</t>
+    <t>admin@cpata-cabamc.ca</t>
   </si>
   <si>
-    <t>admin@cpata-cabamc.ca</t>
+    <t>open-ouvert@tbs-sct.gc.ca</t>
   </si>
   <si>
     <t>ati
@@ -2086,292 +2002,292 @@
         <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="BF1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>459</v>
+        <v>431</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="BN1" s="3" t="s">
         <v>64</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>466</v>
+        <v>438</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="BV1" s="3" t="s">
         <v>72</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>472</v>
+        <v>444</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>474</v>
+        <v>446</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="CD1" s="3" t="s">
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>84</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="CP1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>486</v>
+        <v>458</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="CT1" s="3" t="s">
         <v>96</v>
@@ -13569,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="BP38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ38" s="2">
         <v>1</v>
@@ -13665,7 +13581,7 @@
         <v>-1</v>
       </c>
       <c r="CV38" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CW38" s="1">
         <v>91</v>
@@ -25524,7 +25440,7 @@
         <v>55</v>
       </c>
       <c r="CJ77" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="CK77" s="2">
         <v>542</v>
@@ -25560,7 +25476,7 @@
         <v>-33</v>
       </c>
       <c r="CV77" s="1">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="CW77" s="1">
         <v>20088</v>
@@ -33516,7 +33432,7 @@
         <v>41</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2">
         <v>3</v>
@@ -33792,7 +33708,7 @@
         <v>42</v>
       </c>
       <c r="CU104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CV104" s="1">
         <v>3</v>
@@ -49364,7 +49280,7 @@
         <v>2061</v>
       </c>
       <c r="C156" s="2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D156" s="2">
         <v>47</v>
@@ -49652,7 +49568,7 @@
         <v>71553</v>
       </c>
       <c r="CU156" s="1">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="CV156" s="1">
         <v>124</v>
@@ -67358,7 +67274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="30" customHeight="1">
@@ -67392,725 +67308,445 @@
         <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
         <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
         <v>322</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F4" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F5" t="s">
-        <v>401</v>
+        <v>373</v>
+      </c>
+      <c r="G5" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
         <v>324</v>
       </c>
+      <c r="C6" t="s">
+        <v>346</v>
+      </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="F6" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
         <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F7" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
         <v>326</v>
       </c>
-      <c r="C8" t="s">
-        <v>361</v>
-      </c>
       <c r="D8">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F8" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="F9" t="s">
-        <v>402</v>
-      </c>
-      <c r="G9" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D10">
-        <v>288</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F10" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="F11" t="s">
-        <v>401</v>
+        <v>374</v>
+      </c>
+      <c r="G11" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
         <v>330</v>
       </c>
       <c r="C12" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
         <v>364</v>
       </c>
-      <c r="D12">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>391</v>
-      </c>
       <c r="F12" t="s">
-        <v>401</v>
+        <v>374</v>
+      </c>
+      <c r="G12" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="F13" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F14" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
-      </c>
-      <c r="G15" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2987</v>
       </c>
       <c r="E16" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F16" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D17">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="F17" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
       <c r="C18" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="D18">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="F18" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="B19" t="s">
         <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="D19">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F19" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="F20" t="s">
-        <v>402</v>
+        <v>374</v>
+      </c>
+      <c r="G20" t="s">
+        <v>376</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>291</v>
       </c>
       <c r="B21" t="s">
         <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="F21" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="F22" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="B23" t="s">
         <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="D23">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F23" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" t="s">
-        <v>342</v>
-      </c>
-      <c r="C24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>391</v>
-      </c>
-      <c r="F24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>218</v>
-      </c>
-      <c r="B25" t="s">
-        <v>343</v>
-      </c>
-      <c r="C25" t="s">
-        <v>377</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>391</v>
-      </c>
-      <c r="F25" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>220</v>
-      </c>
-      <c r="B26" t="s">
-        <v>344</v>
-      </c>
-      <c r="C26" t="s">
-        <v>378</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>395</v>
-      </c>
-      <c r="F26" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" t="s">
-        <v>345</v>
-      </c>
-      <c r="C27" t="s">
-        <v>379</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>391</v>
-      </c>
-      <c r="F27" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>240</v>
-      </c>
-      <c r="B28" t="s">
-        <v>346</v>
-      </c>
-      <c r="C28" t="s">
-        <v>380</v>
-      </c>
-      <c r="D28">
-        <v>26</v>
-      </c>
-      <c r="E28" t="s">
-        <v>391</v>
-      </c>
-      <c r="F28" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" t="s">
-        <v>347</v>
-      </c>
-      <c r="C29" t="s">
-        <v>381</v>
-      </c>
-      <c r="D29">
-        <v>51</v>
-      </c>
-      <c r="E29" t="s">
-        <v>391</v>
-      </c>
-      <c r="F29" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B30" t="s">
-        <v>348</v>
-      </c>
-      <c r="C30" t="s">
-        <v>382</v>
-      </c>
-      <c r="D30">
-        <v>761</v>
-      </c>
-      <c r="E30" t="s">
-        <v>391</v>
-      </c>
-      <c r="F30" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>261</v>
-      </c>
-      <c r="B31" t="s">
-        <v>349</v>
-      </c>
-      <c r="C31" t="s">
-        <v>383</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>397</v>
-      </c>
-      <c r="F31" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" t="s">
-        <v>350</v>
-      </c>
-      <c r="C32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>391</v>
-      </c>
-      <c r="F32" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" t="s">
-        <v>351</v>
-      </c>
-      <c r="C33" t="s">
-        <v>385</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>398</v>
-      </c>
-      <c r="F33" t="s">
-        <v>402</v>
-      </c>
-      <c r="G33" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>280</v>
-      </c>
-      <c r="B34" t="s">
-        <v>352</v>
-      </c>
-      <c r="C34" t="s">
-        <v>386</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>391</v>
-      </c>
-      <c r="F34" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>286</v>
-      </c>
-      <c r="B35" t="s">
-        <v>353</v>
-      </c>
-      <c r="C35" t="s">
-        <v>387</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>391</v>
-      </c>
-      <c r="F35" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>304</v>
-      </c>
-      <c r="B36" t="s">
-        <v>354</v>
-      </c>
-      <c r="C36" t="s">
-        <v>388</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>391</v>
-      </c>
-      <c r="F36" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>305</v>
-      </c>
-      <c r="B37" t="s">
-        <v>355</v>
-      </c>
-      <c r="C37" t="s">
-        <v>389</v>
-      </c>
-      <c r="D37">
-        <v>446</v>
-      </c>
-      <c r="E37" t="s">
-        <v>391</v>
-      </c>
-      <c r="F37" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
